--- a/알바로_부작_화_목록.xlsx
+++ b/알바로_부작_화_목록.xlsx
@@ -47963,7 +47963,7 @@
       </c>
       <c r="G5" s="2" t="n">
         <f aca="false">SUMIF('화 목록'!$B$2:$B$980,A5,'화 목록'!$F$2:$F$980)</f>
-        <v>997</v>
+        <v>1041</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>18</v>
@@ -49759,7 +49759,7 @@
       </c>
       <c r="G67" s="7" t="n">
         <f aca="false">SUM(G2:G66)</f>
-        <v>13706</v>
+        <v>13750</v>
       </c>
     </row>
   </sheetData>
@@ -50576,7 +50576,7 @@
         <v>833</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>184</v>
@@ -50597,7 +50597,7 @@
         <v>16</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>922</v>
+        <v>966</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>39</v>
@@ -50621,7 +50621,7 @@
         <v>16</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>965</v>
+        <v>1009</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>28</v>
@@ -50645,7 +50645,7 @@
         <v>16</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>997</v>
+        <v>1041</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>23</v>
@@ -50669,7 +50669,7 @@
         <v>16</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>1024</v>
+        <v>1068</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>10</v>
@@ -50693,7 +50693,7 @@
         <v>16</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1037</v>
+        <v>1081</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>18</v>
@@ -50717,7 +50717,7 @@
         <v>16</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>1058</v>
+        <v>1102</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>28</v>
@@ -50741,7 +50741,7 @@
         <v>16</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>1089</v>
+        <v>1133</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>29</v>
@@ -50765,7 +50765,7 @@
         <v>16</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>1123</v>
+        <v>1167</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>56</v>
@@ -50789,7 +50789,7 @@
         <v>16</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>1183</v>
+        <v>1227</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>34</v>
@@ -50813,7 +50813,7 @@
         <v>16</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>1221</v>
+        <v>1265</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>40</v>
@@ -50837,7 +50837,7 @@
         <v>16</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>1265</v>
+        <v>1309</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>34</v>
@@ -50861,7 +50861,7 @@
         <v>16</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>1304</v>
+        <v>1348</v>
       </c>
       <c r="F45" s="2" t="n">
         <v>36</v>
@@ -50885,7 +50885,7 @@
         <v>16</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>1344</v>
+        <v>1388</v>
       </c>
       <c r="F46" s="2" t="n">
         <v>30</v>
@@ -50909,7 +50909,7 @@
         <v>16</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>1378</v>
+        <v>1422</v>
       </c>
       <c r="F47" s="2" t="n">
         <v>93</v>
@@ -50933,7 +50933,7 @@
         <v>16</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>1477</v>
+        <v>1521</v>
       </c>
       <c r="F48" s="2" t="n">
         <v>36</v>
@@ -50957,7 +50957,7 @@
         <v>16</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>1517</v>
+        <v>1561</v>
       </c>
       <c r="F49" s="2" t="n">
         <v>56</v>
@@ -50981,7 +50981,7 @@
         <v>16</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>1579</v>
+        <v>1623</v>
       </c>
       <c r="F50" s="2" t="n">
         <v>31</v>
@@ -51005,7 +51005,7 @@
         <v>16</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>1614</v>
+        <v>1658</v>
       </c>
       <c r="F51" s="2" t="n">
         <v>37</v>
@@ -51029,7 +51029,7 @@
         <v>16</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>1656</v>
+        <v>1700</v>
       </c>
       <c r="F52" s="2" t="n">
         <v>44</v>
@@ -51053,7 +51053,7 @@
         <v>16</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>1705</v>
+        <v>1749</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>39</v>
@@ -51077,7 +51077,7 @@
         <v>16</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>1749</v>
+        <v>1793</v>
       </c>
       <c r="F54" s="2" t="n">
         <v>41</v>
@@ -51101,7 +51101,7 @@
         <v>16</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>1794</v>
+        <v>1838</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>32</v>
@@ -51125,7 +51125,7 @@
         <v>16</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>1829</v>
+        <v>1873</v>
       </c>
       <c r="F56" s="2" t="n">
         <v>32</v>
@@ -51149,7 +51149,7 @@
         <v>16</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>1864</v>
+        <v>1908</v>
       </c>
       <c r="F57" s="2" t="n">
         <v>35</v>
@@ -51173,7 +51173,7 @@
         <v>16</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>1903</v>
+        <v>1947</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>37</v>
@@ -51197,7 +51197,7 @@
         <v>16</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>1944</v>
+        <v>1988</v>
       </c>
       <c r="F59" s="2" t="n">
         <v>30</v>
@@ -51221,7 +51221,7 @@
         <v>16</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>1978</v>
+        <v>2022</v>
       </c>
       <c r="F60" s="2" t="n">
         <v>32</v>
@@ -51245,7 +51245,7 @@
         <v>16</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>2014</v>
+        <v>2058</v>
       </c>
       <c r="F61" s="2" t="n">
         <v>16</v>
@@ -51269,7 +51269,7 @@
         <v>16</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>2032</v>
+        <v>2076</v>
       </c>
       <c r="F62" s="2" t="n">
         <v>30</v>
@@ -51293,7 +51293,7 @@
         <v>16</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>2066</v>
+        <v>2110</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>31</v>
@@ -51317,7 +51317,7 @@
         <v>16</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>2101</v>
+        <v>2145</v>
       </c>
       <c r="F64" s="2" t="n">
         <v>27</v>
@@ -51341,7 +51341,7 @@
         <v>16</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>2132</v>
+        <v>2176</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>28</v>
@@ -51365,7 +51365,7 @@
         <v>16</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>2163</v>
+        <v>2207</v>
       </c>
       <c r="F66" s="2" t="n">
         <v>26</v>
@@ -51389,7 +51389,7 @@
         <v>16</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>2193</v>
+        <v>2237</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>28</v>
@@ -51413,7 +51413,7 @@
         <v>16</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>2225</v>
+        <v>2269</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>30</v>
@@ -51437,7 +51437,7 @@
         <v>16</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>2259</v>
+        <v>2303</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>23</v>
@@ -51461,7 +51461,7 @@
         <v>16</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>2285</v>
+        <v>2329</v>
       </c>
       <c r="F70" s="2" t="n">
         <v>27</v>
@@ -51485,7 +51485,7 @@
         <v>16</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>2315</v>
+        <v>2359</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>25</v>
@@ -51509,7 +51509,7 @@
         <v>16</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>2344</v>
+        <v>2388</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>30</v>
@@ -51533,7 +51533,7 @@
         <v>16</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>2377</v>
+        <v>2421</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>26</v>
@@ -51557,7 +51557,7 @@
         <v>16</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>2407</v>
+        <v>2451</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>23</v>
@@ -51581,7 +51581,7 @@
         <v>16</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>2433</v>
+        <v>2477</v>
       </c>
       <c r="F75" s="2" t="n">
         <v>26</v>
@@ -51605,7 +51605,7 @@
         <v>16</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>2463</v>
+        <v>2507</v>
       </c>
       <c r="F76" s="2" t="n">
         <v>22</v>
@@ -51629,7 +51629,7 @@
         <v>16</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>2488</v>
+        <v>2532</v>
       </c>
       <c r="F77" s="2" t="n">
         <v>22</v>
@@ -51653,7 +51653,7 @@
         <v>16</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>2513</v>
+        <v>2557</v>
       </c>
       <c r="F78" s="2" t="n">
         <v>21</v>
@@ -51677,7 +51677,7 @@
         <v>16</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>2538</v>
+        <v>2582</v>
       </c>
       <c r="F79" s="2" t="n">
         <v>25</v>
@@ -51701,7 +51701,7 @@
         <v>16</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>2567</v>
+        <v>2611</v>
       </c>
       <c r="F80" s="2" t="n">
         <v>25</v>
@@ -51725,7 +51725,7 @@
         <v>16</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>2595</v>
+        <v>2639</v>
       </c>
       <c r="F81" s="2" t="n">
         <v>32</v>
@@ -51749,7 +51749,7 @@
         <v>16</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>2631</v>
+        <v>2675</v>
       </c>
       <c r="F82" s="2" t="n">
         <v>34</v>
@@ -51773,7 +51773,7 @@
         <v>16</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>2669</v>
+        <v>2713</v>
       </c>
       <c r="F83" s="2" t="n">
         <v>26</v>
@@ -51797,7 +51797,7 @@
         <v>16</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>2698</v>
+        <v>2742</v>
       </c>
       <c r="F84" s="2" t="n">
         <v>23</v>
@@ -51821,7 +51821,7 @@
         <v>16</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>2724</v>
+        <v>2768</v>
       </c>
       <c r="F85" s="2" t="n">
         <v>28</v>
@@ -51845,7 +51845,7 @@
         <v>16</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>2756</v>
+        <v>2800</v>
       </c>
       <c r="F86" s="2" t="n">
         <v>28</v>
@@ -51869,7 +51869,7 @@
         <v>16</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>2787</v>
+        <v>2831</v>
       </c>
       <c r="F87" s="2" t="n">
         <v>22</v>
@@ -51893,7 +51893,7 @@
         <v>16</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>2812</v>
+        <v>2856</v>
       </c>
       <c r="F88" s="2" t="n">
         <v>23</v>
@@ -51917,7 +51917,7 @@
         <v>16</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>2838</v>
+        <v>2882</v>
       </c>
       <c r="F89" s="2" t="n">
         <v>29</v>
@@ -51941,7 +51941,7 @@
         <v>16</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>2871</v>
+        <v>2915</v>
       </c>
       <c r="F90" s="2" t="n">
         <v>23</v>
@@ -51965,7 +51965,7 @@
         <v>16</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>2897</v>
+        <v>2941</v>
       </c>
       <c r="F91" s="2" t="n">
         <v>25</v>
@@ -51989,7 +51989,7 @@
         <v>16</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>2925</v>
+        <v>2969</v>
       </c>
       <c r="F92" s="2" t="n">
         <v>19</v>
@@ -52013,7 +52013,7 @@
         <v>16</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>2947</v>
+        <v>2991</v>
       </c>
       <c r="F93" s="2" t="n">
         <v>20</v>
@@ -52037,7 +52037,7 @@
         <v>16</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>2970</v>
+        <v>3014</v>
       </c>
       <c r="F94" s="2" t="n">
         <v>18</v>
@@ -52061,7 +52061,7 @@
         <v>16</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>2992</v>
+        <v>3036</v>
       </c>
       <c r="F95" s="2" t="n">
         <v>28</v>
@@ -52085,7 +52085,7 @@
         <v>16</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>3023</v>
+        <v>3067</v>
       </c>
       <c r="F96" s="2" t="n">
         <v>19</v>
@@ -52109,7 +52109,7 @@
         <v>16</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>3045</v>
+        <v>3089</v>
       </c>
       <c r="F97" s="2" t="n">
         <v>22</v>
@@ -52133,7 +52133,7 @@
         <v>16</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>3070</v>
+        <v>3114</v>
       </c>
       <c r="F98" s="2" t="n">
         <v>19</v>
@@ -52157,7 +52157,7 @@
         <v>16</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>3092</v>
+        <v>3136</v>
       </c>
       <c r="F99" s="2" t="n">
         <v>18</v>
@@ -52181,7 +52181,7 @@
         <v>16</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>3113</v>
+        <v>3157</v>
       </c>
       <c r="F100" s="2" t="n">
         <v>22</v>
@@ -52205,7 +52205,7 @@
         <v>16</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>3138</v>
+        <v>3182</v>
       </c>
       <c r="F101" s="2" t="n">
         <v>21</v>
@@ -52229,7 +52229,7 @@
         <v>16</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>3163</v>
+        <v>3207</v>
       </c>
       <c r="F102" s="2" t="n">
         <v>22</v>
@@ -52253,7 +52253,7 @@
         <v>16</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>3190</v>
+        <v>3234</v>
       </c>
       <c r="F103" s="2" t="n">
         <v>23</v>
@@ -52277,7 +52277,7 @@
         <v>16</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>3216</v>
+        <v>3260</v>
       </c>
       <c r="F104" s="2" t="n">
         <v>17</v>
@@ -52301,7 +52301,7 @@
         <v>16</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>3236</v>
+        <v>3280</v>
       </c>
       <c r="F105" s="2" t="n">
         <v>17</v>
@@ -52325,7 +52325,7 @@
         <v>16</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>3256</v>
+        <v>3300</v>
       </c>
       <c r="F106" s="2" t="n">
         <v>16</v>
@@ -52349,7 +52349,7 @@
         <v>16</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>3275</v>
+        <v>3319</v>
       </c>
       <c r="F107" s="2" t="n">
         <v>21</v>
@@ -52373,7 +52373,7 @@
         <v>16</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>3299</v>
+        <v>3343</v>
       </c>
       <c r="F108" s="2" t="n">
         <v>21</v>
@@ -52397,7 +52397,7 @@
         <v>16</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>3323</v>
+        <v>3367</v>
       </c>
       <c r="F109" s="2" t="n">
         <v>18</v>
@@ -52421,7 +52421,7 @@
         <v>16</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>3344</v>
+        <v>3388</v>
       </c>
       <c r="F110" s="2" t="n">
         <v>21</v>
@@ -52445,7 +52445,7 @@
         <v>16</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>3368</v>
+        <v>3412</v>
       </c>
       <c r="F111" s="2" t="n">
         <v>18</v>
@@ -52469,7 +52469,7 @@
         <v>16</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>3389</v>
+        <v>3433</v>
       </c>
       <c r="F112" s="2" t="n">
         <v>20</v>
@@ -52493,7 +52493,7 @@
         <v>16</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>3412</v>
+        <v>3456</v>
       </c>
       <c r="F113" s="2" t="n">
         <v>16</v>
@@ -52517,7 +52517,7 @@
         <v>16</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>3431</v>
+        <v>3475</v>
       </c>
       <c r="F114" s="2" t="n">
         <v>15</v>
@@ -52541,7 +52541,7 @@
         <v>16</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>3449</v>
+        <v>3493</v>
       </c>
       <c r="F115" s="2" t="n">
         <v>16</v>
@@ -52565,7 +52565,7 @@
         <v>16</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>3467</v>
+        <v>3511</v>
       </c>
       <c r="F116" s="2" t="n">
         <v>19</v>
@@ -52589,7 +52589,7 @@
         <v>16</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>3489</v>
+        <v>3533</v>
       </c>
       <c r="F117" s="2" t="n">
         <v>19</v>
@@ -52613,7 +52613,7 @@
         <v>16</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>3511</v>
+        <v>3555</v>
       </c>
       <c r="F118" s="2" t="n">
         <v>19</v>
@@ -52637,7 +52637,7 @@
         <v>16</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>3533</v>
+        <v>3577</v>
       </c>
       <c r="F119" s="2" t="n">
         <v>16</v>
@@ -52661,7 +52661,7 @@
         <v>16</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>3552</v>
+        <v>3596</v>
       </c>
       <c r="F120" s="2" t="n">
         <v>17</v>
@@ -52685,7 +52685,7 @@
         <v>16</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>3572</v>
+        <v>3616</v>
       </c>
       <c r="F121" s="2" t="n">
         <v>14</v>
@@ -52709,7 +52709,7 @@
         <v>16</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>3589</v>
+        <v>3633</v>
       </c>
       <c r="F122" s="2" t="n">
         <v>10</v>
@@ -52733,7 +52733,7 @@
         <v>16</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>3601</v>
+        <v>3645</v>
       </c>
       <c r="F123" s="2" t="n">
         <v>19</v>
@@ -52757,7 +52757,7 @@
         <v>16</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>3623</v>
+        <v>3667</v>
       </c>
       <c r="F124" s="2" t="n">
         <v>26</v>
@@ -52781,7 +52781,7 @@
         <v>16</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>3653</v>
+        <v>3697</v>
       </c>
       <c r="F125" s="2" t="n">
         <v>20</v>
@@ -52805,7 +52805,7 @@
         <v>16</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>3676</v>
+        <v>3720</v>
       </c>
       <c r="F126" s="2" t="n">
         <v>17</v>
@@ -52829,7 +52829,7 @@
         <v>16</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>3696</v>
+        <v>3740</v>
       </c>
       <c r="F127" s="2" t="n">
         <v>20</v>
@@ -52853,7 +52853,7 @@
         <v>16</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>3719</v>
+        <v>3763</v>
       </c>
       <c r="F128" s="2" t="n">
         <v>16</v>
@@ -52877,7 +52877,7 @@
         <v>16</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>3738</v>
+        <v>3782</v>
       </c>
       <c r="F129" s="2" t="n">
         <v>22</v>
@@ -52901,7 +52901,7 @@
         <v>16</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>3763</v>
+        <v>3807</v>
       </c>
       <c r="F130" s="2" t="n">
         <v>13</v>
@@ -52925,7 +52925,7 @@
         <v>16</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>3778</v>
+        <v>3822</v>
       </c>
       <c r="F131" s="2" t="n">
         <v>12</v>
@@ -52949,7 +52949,7 @@
         <v>16</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>3793</v>
+        <v>3837</v>
       </c>
       <c r="F132" s="2" t="n">
         <v>16</v>
@@ -52973,7 +52973,7 @@
         <v>16</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>3813</v>
+        <v>3857</v>
       </c>
       <c r="F133" s="2" t="n">
         <v>16</v>
@@ -52997,7 +52997,7 @@
         <v>16</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>3832</v>
+        <v>3876</v>
       </c>
       <c r="F134" s="2" t="n">
         <v>10</v>
@@ -53021,7 +53021,7 @@
         <v>16</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>3844</v>
+        <v>3888</v>
       </c>
       <c r="F135" s="2" t="n">
         <v>14</v>
@@ -53045,7 +53045,7 @@
         <v>16</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>3861</v>
+        <v>3905</v>
       </c>
       <c r="F136" s="2" t="n">
         <v>10</v>
@@ -53069,7 +53069,7 @@
         <v>16</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>3874</v>
+        <v>3918</v>
       </c>
       <c r="F137" s="2" t="n">
         <v>12</v>
@@ -53093,7 +53093,7 @@
         <v>16</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>3888</v>
+        <v>3932</v>
       </c>
       <c r="F138" s="2" t="n">
         <v>13</v>
@@ -53117,7 +53117,7 @@
         <v>16</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>3904</v>
+        <v>3948</v>
       </c>
       <c r="F139" s="2" t="n">
         <v>18</v>
@@ -53141,7 +53141,7 @@
         <v>16</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>3926</v>
+        <v>3970</v>
       </c>
       <c r="F140" s="2" t="n">
         <v>15</v>
@@ -53165,7 +53165,7 @@
         <v>16</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>3944</v>
+        <v>3988</v>
       </c>
       <c r="F141" s="2" t="n">
         <v>15</v>
@@ -53189,7 +53189,7 @@
         <v>16</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>3962</v>
+        <v>4006</v>
       </c>
       <c r="F142" s="2" t="n">
         <v>10</v>
@@ -53213,7 +53213,7 @@
         <v>16</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>3974</v>
+        <v>4018</v>
       </c>
       <c r="F143" s="2" t="n">
         <v>13</v>
@@ -53237,7 +53237,7 @@
         <v>16</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>3990</v>
+        <v>4034</v>
       </c>
       <c r="F144" s="2" t="n">
         <v>11</v>
@@ -53261,7 +53261,7 @@
         <v>16</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>4004</v>
+        <v>4048</v>
       </c>
       <c r="F145" s="2" t="n">
         <v>11</v>
@@ -53285,7 +53285,7 @@
         <v>16</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>4017</v>
+        <v>4061</v>
       </c>
       <c r="F146" s="2" t="n">
         <v>13</v>
@@ -53309,7 +53309,7 @@
         <v>16</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>4033</v>
+        <v>4077</v>
       </c>
       <c r="F147" s="2" t="n">
         <v>9</v>
@@ -53333,7 +53333,7 @@
         <v>16</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>4046</v>
+        <v>4090</v>
       </c>
       <c r="F148" s="2" t="n">
         <v>10</v>
@@ -53357,7 +53357,7 @@
         <v>16</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>4058</v>
+        <v>4102</v>
       </c>
       <c r="F149" s="2" t="n">
         <v>8</v>
@@ -53381,7 +53381,7 @@
         <v>16</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>4069</v>
+        <v>4113</v>
       </c>
       <c r="F150" s="2" t="n">
         <v>12</v>
@@ -53405,7 +53405,7 @@
         <v>16</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>4084</v>
+        <v>4128</v>
       </c>
       <c r="F151" s="2" t="n">
         <v>12</v>
@@ -53429,7 +53429,7 @@
         <v>16</v>
       </c>
       <c r="E152" s="2" t="n">
-        <v>4098</v>
+        <v>4142</v>
       </c>
       <c r="F152" s="2" t="n">
         <v>10</v>
@@ -53453,7 +53453,7 @@
         <v>16</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>4111</v>
+        <v>4155</v>
       </c>
       <c r="F153" s="2" t="n">
         <v>18</v>
@@ -53477,7 +53477,7 @@
         <v>16</v>
       </c>
       <c r="E154" s="2" t="n">
-        <v>4132</v>
+        <v>4176</v>
       </c>
       <c r="F154" s="2" t="n">
         <v>10</v>
@@ -53501,7 +53501,7 @@
         <v>16</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>4147</v>
+        <v>4191</v>
       </c>
       <c r="F155" s="2" t="n">
         <v>11</v>
@@ -53525,7 +53525,7 @@
         <v>16</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>4160</v>
+        <v>4204</v>
       </c>
       <c r="F156" s="2" t="n">
         <v>11</v>
@@ -53549,7 +53549,7 @@
         <v>16</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>4174</v>
+        <v>4218</v>
       </c>
       <c r="F157" s="2" t="n">
         <v>9</v>
@@ -53573,7 +53573,7 @@
         <v>16</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>4185</v>
+        <v>4229</v>
       </c>
       <c r="F158" s="2" t="n">
         <v>9</v>
@@ -53597,7 +53597,7 @@
         <v>16</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>4197</v>
+        <v>4241</v>
       </c>
       <c r="F159" s="2" t="n">
         <v>13</v>
@@ -53621,7 +53621,7 @@
         <v>16</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>4212</v>
+        <v>4256</v>
       </c>
       <c r="F160" s="2" t="n">
         <v>13</v>
@@ -53645,7 +53645,7 @@
         <v>16</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>4228</v>
+        <v>4272</v>
       </c>
       <c r="F161" s="2" t="n">
         <v>12</v>
@@ -53669,7 +53669,7 @@
         <v>16</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>4243</v>
+        <v>4287</v>
       </c>
       <c r="F162" s="2" t="n">
         <v>11</v>
@@ -53693,7 +53693,7 @@
         <v>16</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>4257</v>
+        <v>4301</v>
       </c>
       <c r="F163" s="2" t="n">
         <v>11</v>
@@ -53717,7 +53717,7 @@
         <v>16</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>4270</v>
+        <v>4314</v>
       </c>
       <c r="F164" s="2" t="n">
         <v>11</v>
@@ -53741,7 +53741,7 @@
         <v>16</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>4284</v>
+        <v>4328</v>
       </c>
       <c r="F165" s="2" t="n">
         <v>8</v>
@@ -53765,7 +53765,7 @@
         <v>16</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>4294</v>
+        <v>4338</v>
       </c>
       <c r="F166" s="2" t="n">
         <v>11</v>
@@ -53789,7 +53789,7 @@
         <v>16</v>
       </c>
       <c r="E167" s="2" t="n">
-        <v>4309</v>
+        <v>4353</v>
       </c>
       <c r="F167" s="2" t="n">
         <v>14</v>
@@ -53813,7 +53813,7 @@
         <v>16</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>4326</v>
+        <v>4370</v>
       </c>
       <c r="F168" s="2" t="n">
         <v>12</v>
@@ -53837,7 +53837,7 @@
         <v>16</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>4341</v>
+        <v>4385</v>
       </c>
       <c r="F169" s="2" t="n">
         <v>11</v>
@@ -53861,7 +53861,7 @@
         <v>16</v>
       </c>
       <c r="E170" s="2" t="n">
-        <v>4355</v>
+        <v>4399</v>
       </c>
       <c r="F170" s="2" t="n">
         <v>13</v>
@@ -53885,7 +53885,7 @@
         <v>16</v>
       </c>
       <c r="E171" s="2" t="n">
-        <v>4371</v>
+        <v>4415</v>
       </c>
       <c r="F171" s="2" t="n">
         <v>12</v>
@@ -53909,7 +53909,7 @@
         <v>16</v>
       </c>
       <c r="E172" s="2" t="n">
-        <v>4386</v>
+        <v>4430</v>
       </c>
       <c r="F172" s="2" t="n">
         <v>11</v>
@@ -53933,7 +53933,7 @@
         <v>16</v>
       </c>
       <c r="E173" s="2" t="n">
-        <v>4399</v>
+        <v>4443</v>
       </c>
       <c r="F173" s="2" t="n">
         <v>17</v>
@@ -53957,7 +53957,7 @@
         <v>16</v>
       </c>
       <c r="E174" s="2" t="n">
-        <v>4419</v>
+        <v>4463</v>
       </c>
       <c r="F174" s="2" t="n">
         <v>18</v>
@@ -53981,7 +53981,7 @@
         <v>16</v>
       </c>
       <c r="E175" s="2" t="n">
-        <v>4440</v>
+        <v>4484</v>
       </c>
       <c r="F175" s="2" t="n">
         <v>17</v>
@@ -54005,7 +54005,7 @@
         <v>16</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>4460</v>
+        <v>4504</v>
       </c>
       <c r="F176" s="2" t="n">
         <v>14</v>
@@ -54029,7 +54029,7 @@
         <v>16</v>
       </c>
       <c r="E177" s="2" t="n">
-        <v>4477</v>
+        <v>4521</v>
       </c>
       <c r="F177" s="2" t="n">
         <v>11</v>
@@ -54053,7 +54053,7 @@
         <v>16</v>
       </c>
       <c r="E178" s="2" t="n">
-        <v>4490</v>
+        <v>4534</v>
       </c>
       <c r="F178" s="2" t="n">
         <v>16</v>
@@ -54077,7 +54077,7 @@
         <v>16</v>
       </c>
       <c r="E179" s="2" t="n">
-        <v>4508</v>
+        <v>4552</v>
       </c>
       <c r="F179" s="2" t="n">
         <v>13</v>
@@ -54101,7 +54101,7 @@
         <v>16</v>
       </c>
       <c r="E180" s="2" t="n">
-        <v>4524</v>
+        <v>4568</v>
       </c>
       <c r="F180" s="2" t="n">
         <v>18</v>
@@ -54125,7 +54125,7 @@
         <v>16</v>
       </c>
       <c r="E181" s="2" t="n">
-        <v>4545</v>
+        <v>4589</v>
       </c>
       <c r="F181" s="2" t="n">
         <v>15</v>
@@ -54149,7 +54149,7 @@
         <v>16</v>
       </c>
       <c r="E182" s="2" t="n">
-        <v>4563</v>
+        <v>4607</v>
       </c>
       <c r="F182" s="2" t="n">
         <v>18</v>
@@ -54173,7 +54173,7 @@
         <v>16</v>
       </c>
       <c r="E183" s="2" t="n">
-        <v>4584</v>
+        <v>4628</v>
       </c>
       <c r="F183" s="2" t="n">
         <v>13</v>
@@ -54197,7 +54197,7 @@
         <v>16</v>
       </c>
       <c r="E184" s="2" t="n">
-        <v>4600</v>
+        <v>4644</v>
       </c>
       <c r="F184" s="2" t="n">
         <v>20</v>
@@ -54221,7 +54221,7 @@
         <v>16</v>
       </c>
       <c r="E185" s="2" t="n">
-        <v>4623</v>
+        <v>4667</v>
       </c>
       <c r="F185" s="2" t="n">
         <v>13</v>
@@ -54245,7 +54245,7 @@
         <v>16</v>
       </c>
       <c r="E186" s="2" t="n">
-        <v>4639</v>
+        <v>4683</v>
       </c>
       <c r="F186" s="2" t="n">
         <v>13</v>
@@ -54269,7 +54269,7 @@
         <v>16</v>
       </c>
       <c r="E187" s="2" t="n">
-        <v>4654</v>
+        <v>4698</v>
       </c>
       <c r="F187" s="2" t="n">
         <v>12</v>
@@ -54293,7 +54293,7 @@
         <v>16</v>
       </c>
       <c r="E188" s="2" t="n">
-        <v>4669</v>
+        <v>4713</v>
       </c>
       <c r="F188" s="2" t="n">
         <v>12</v>
@@ -54317,7 +54317,7 @@
         <v>16</v>
       </c>
       <c r="E189" s="2" t="n">
-        <v>4684</v>
+        <v>4728</v>
       </c>
       <c r="F189" s="2" t="n">
         <v>10</v>
@@ -54341,7 +54341,7 @@
         <v>16</v>
       </c>
       <c r="E190" s="2" t="n">
-        <v>4696</v>
+        <v>4740</v>
       </c>
       <c r="F190" s="2" t="n">
         <v>12</v>
@@ -54365,7 +54365,7 @@
         <v>16</v>
       </c>
       <c r="E191" s="2" t="n">
-        <v>4711</v>
+        <v>4755</v>
       </c>
       <c r="F191" s="2" t="n">
         <v>14</v>
@@ -54389,7 +54389,7 @@
         <v>16</v>
       </c>
       <c r="E192" s="2" t="n">
-        <v>4728</v>
+        <v>4772</v>
       </c>
       <c r="F192" s="2" t="n">
         <v>15</v>
@@ -54413,7 +54413,7 @@
         <v>16</v>
       </c>
       <c r="E193" s="2" t="n">
-        <v>4746</v>
+        <v>4790</v>
       </c>
       <c r="F193" s="2" t="n">
         <v>12</v>
@@ -54437,7 +54437,7 @@
         <v>16</v>
       </c>
       <c r="E194" s="2" t="n">
-        <v>4760</v>
+        <v>4804</v>
       </c>
       <c r="F194" s="2" t="n">
         <v>15</v>
@@ -54461,7 +54461,7 @@
         <v>16</v>
       </c>
       <c r="E195" s="2" t="n">
-        <v>4778</v>
+        <v>4822</v>
       </c>
       <c r="F195" s="2" t="n">
         <v>12</v>
@@ -54485,7 +54485,7 @@
         <v>16</v>
       </c>
       <c r="E196" s="2" t="n">
-        <v>4793</v>
+        <v>4837</v>
       </c>
       <c r="F196" s="2" t="n">
         <v>15</v>
@@ -54509,7 +54509,7 @@
         <v>16</v>
       </c>
       <c r="E197" s="2" t="n">
-        <v>4811</v>
+        <v>4855</v>
       </c>
       <c r="F197" s="2" t="n">
         <v>13</v>
@@ -54533,7 +54533,7 @@
         <v>16</v>
       </c>
       <c r="E198" s="2" t="n">
-        <v>4827</v>
+        <v>4871</v>
       </c>
       <c r="F198" s="2" t="n">
         <v>15</v>
@@ -54557,7 +54557,7 @@
         <v>16</v>
       </c>
       <c r="E199" s="2" t="n">
-        <v>4845</v>
+        <v>4889</v>
       </c>
       <c r="F199" s="2" t="n">
         <v>15</v>
@@ -54581,7 +54581,7 @@
         <v>16</v>
       </c>
       <c r="E200" s="2" t="n">
-        <v>4863</v>
+        <v>4907</v>
       </c>
       <c r="F200" s="2" t="n">
         <v>12</v>
@@ -54605,7 +54605,7 @@
         <v>16</v>
       </c>
       <c r="E201" s="2" t="n">
-        <v>4878</v>
+        <v>4922</v>
       </c>
       <c r="F201" s="2" t="n">
         <v>11</v>
@@ -54629,7 +54629,7 @@
         <v>16</v>
       </c>
       <c r="E202" s="2" t="n">
-        <v>4891</v>
+        <v>4935</v>
       </c>
       <c r="F202" s="2" t="n">
         <v>14</v>
@@ -54653,7 +54653,7 @@
         <v>16</v>
       </c>
       <c r="E203" s="2" t="n">
-        <v>4908</v>
+        <v>4952</v>
       </c>
       <c r="F203" s="2" t="n">
         <v>11</v>
@@ -54677,7 +54677,7 @@
         <v>16</v>
       </c>
       <c r="E204" s="2" t="n">
-        <v>4922</v>
+        <v>4966</v>
       </c>
       <c r="F204" s="2" t="n">
         <v>17</v>
@@ -54701,7 +54701,7 @@
         <v>16</v>
       </c>
       <c r="E205" s="2" t="n">
-        <v>4942</v>
+        <v>4986</v>
       </c>
       <c r="F205" s="2" t="n">
         <v>12</v>
@@ -54725,7 +54725,7 @@
         <v>16</v>
       </c>
       <c r="E206" s="2" t="n">
-        <v>4956</v>
+        <v>5000</v>
       </c>
       <c r="F206" s="2" t="n">
         <v>14</v>
@@ -54749,7 +54749,7 @@
         <v>16</v>
       </c>
       <c r="E207" s="2" t="n">
-        <v>4973</v>
+        <v>5017</v>
       </c>
       <c r="F207" s="2" t="n">
         <v>14</v>
@@ -54773,7 +54773,7 @@
         <v>16</v>
       </c>
       <c r="E208" s="2" t="n">
-        <v>4990</v>
+        <v>5034</v>
       </c>
       <c r="F208" s="2" t="n">
         <v>12</v>
@@ -54797,7 +54797,7 @@
         <v>16</v>
       </c>
       <c r="E209" s="2" t="n">
-        <v>5004</v>
+        <v>5048</v>
       </c>
       <c r="F209" s="2" t="n">
         <v>12</v>
@@ -54821,7 +54821,7 @@
         <v>16</v>
       </c>
       <c r="E210" s="2" t="n">
-        <v>5018</v>
+        <v>5062</v>
       </c>
       <c r="F210" s="2" t="n">
         <v>12</v>
@@ -54845,7 +54845,7 @@
         <v>16</v>
       </c>
       <c r="E211" s="2" t="n">
-        <v>5033</v>
+        <v>5077</v>
       </c>
       <c r="F211" s="2" t="n">
         <v>12</v>
@@ -54869,7 +54869,7 @@
         <v>16</v>
       </c>
       <c r="E212" s="2" t="n">
-        <v>5047</v>
+        <v>5091</v>
       </c>
       <c r="F212" s="2" t="n">
         <v>11</v>
@@ -54893,7 +54893,7 @@
         <v>16</v>
       </c>
       <c r="E213" s="2" t="n">
-        <v>5060</v>
+        <v>5104</v>
       </c>
       <c r="F213" s="2" t="n">
         <v>12</v>
@@ -54917,7 +54917,7 @@
         <v>16</v>
       </c>
       <c r="E214" s="2" t="n">
-        <v>5075</v>
+        <v>5119</v>
       </c>
       <c r="F214" s="2" t="n">
         <v>10</v>
@@ -54941,7 +54941,7 @@
         <v>16</v>
       </c>
       <c r="E215" s="2" t="n">
-        <v>5087</v>
+        <v>5131</v>
       </c>
       <c r="F215" s="2" t="n">
         <v>10</v>
@@ -54965,7 +54965,7 @@
         <v>16</v>
       </c>
       <c r="E216" s="2" t="n">
-        <v>5100</v>
+        <v>5144</v>
       </c>
       <c r="F216" s="2" t="n">
         <v>12</v>
@@ -54989,7 +54989,7 @@
         <v>16</v>
       </c>
       <c r="E217" s="2" t="n">
-        <v>5115</v>
+        <v>5159</v>
       </c>
       <c r="F217" s="2" t="n">
         <v>12</v>
@@ -55013,7 +55013,7 @@
         <v>16</v>
       </c>
       <c r="E218" s="2" t="n">
-        <v>5130</v>
+        <v>5174</v>
       </c>
       <c r="F218" s="2" t="n">
         <v>11</v>
@@ -55037,7 +55037,7 @@
         <v>16</v>
       </c>
       <c r="E219" s="2" t="n">
-        <v>5143</v>
+        <v>5187</v>
       </c>
       <c r="F219" s="2" t="n">
         <v>10</v>
@@ -55061,7 +55061,7 @@
         <v>16</v>
       </c>
       <c r="E220" s="2" t="n">
-        <v>5156</v>
+        <v>5200</v>
       </c>
       <c r="F220" s="2" t="n">
         <v>10</v>
@@ -55085,7 +55085,7 @@
         <v>16</v>
       </c>
       <c r="E221" s="2" t="n">
-        <v>5168</v>
+        <v>5212</v>
       </c>
       <c r="F221" s="2" t="n">
         <v>16</v>
@@ -55109,7 +55109,7 @@
         <v>16</v>
       </c>
       <c r="E222" s="2" t="n">
-        <v>5187</v>
+        <v>5231</v>
       </c>
       <c r="F222" s="2" t="n">
         <v>12</v>
@@ -55133,7 +55133,7 @@
         <v>16</v>
       </c>
       <c r="E223" s="2" t="n">
-        <v>5202</v>
+        <v>5246</v>
       </c>
       <c r="F223" s="2" t="n">
         <v>12</v>
@@ -55157,7 +55157,7 @@
         <v>16</v>
       </c>
       <c r="E224" s="2" t="n">
-        <v>5217</v>
+        <v>5261</v>
       </c>
       <c r="F224" s="2" t="n">
         <v>12</v>
@@ -55181,7 +55181,7 @@
         <v>16</v>
       </c>
       <c r="E225" s="2" t="n">
-        <v>5231</v>
+        <v>5275</v>
       </c>
       <c r="F225" s="2" t="n">
         <v>12</v>
@@ -55205,7 +55205,7 @@
         <v>16</v>
       </c>
       <c r="E226" s="2" t="n">
-        <v>5246</v>
+        <v>5290</v>
       </c>
       <c r="F226" s="2" t="n">
         <v>11</v>
@@ -55229,7 +55229,7 @@
         <v>16</v>
       </c>
       <c r="E227" s="2" t="n">
-        <v>5260</v>
+        <v>5304</v>
       </c>
       <c r="F227" s="2" t="n">
         <v>10</v>
@@ -55253,7 +55253,7 @@
         <v>16</v>
       </c>
       <c r="E228" s="2" t="n">
-        <v>5272</v>
+        <v>5316</v>
       </c>
       <c r="F228" s="2" t="n">
         <v>12</v>
@@ -55277,7 +55277,7 @@
         <v>16</v>
       </c>
       <c r="E229" s="2" t="n">
-        <v>5287</v>
+        <v>5331</v>
       </c>
       <c r="F229" s="2" t="n">
         <v>15</v>
@@ -55301,7 +55301,7 @@
         <v>16</v>
       </c>
       <c r="E230" s="2" t="n">
-        <v>5305</v>
+        <v>5349</v>
       </c>
       <c r="F230" s="2" t="n">
         <v>15</v>
@@ -55325,7 +55325,7 @@
         <v>16</v>
       </c>
       <c r="E231" s="2" t="n">
-        <v>5323</v>
+        <v>5367</v>
       </c>
       <c r="F231" s="2" t="n">
         <v>12</v>
@@ -55349,7 +55349,7 @@
         <v>16</v>
       </c>
       <c r="E232" s="2" t="n">
-        <v>5337</v>
+        <v>5381</v>
       </c>
       <c r="F232" s="2" t="n">
         <v>12</v>
@@ -55373,7 +55373,7 @@
         <v>16</v>
       </c>
       <c r="E233" s="2" t="n">
-        <v>5352</v>
+        <v>5396</v>
       </c>
       <c r="F233" s="2" t="n">
         <v>13</v>
@@ -55397,7 +55397,7 @@
         <v>16</v>
       </c>
       <c r="E234" s="2" t="n">
-        <v>5368</v>
+        <v>5412</v>
       </c>
       <c r="F234" s="2" t="n">
         <v>12</v>
@@ -55421,7 +55421,7 @@
         <v>16</v>
       </c>
       <c r="E235" s="2" t="n">
-        <v>5382</v>
+        <v>5426</v>
       </c>
       <c r="F235" s="2" t="n">
         <v>12</v>
@@ -55445,7 +55445,7 @@
         <v>16</v>
       </c>
       <c r="E236" s="2" t="n">
-        <v>5396</v>
+        <v>5440</v>
       </c>
       <c r="F236" s="2" t="n">
         <v>9</v>
@@ -55469,7 +55469,7 @@
         <v>16</v>
       </c>
       <c r="E237" s="2" t="n">
-        <v>5408</v>
+        <v>5452</v>
       </c>
       <c r="F237" s="2" t="n">
         <v>12</v>
@@ -55493,7 +55493,7 @@
         <v>16</v>
       </c>
       <c r="E238" s="2" t="n">
-        <v>5422</v>
+        <v>5466</v>
       </c>
       <c r="F238" s="2" t="n">
         <v>12</v>
@@ -55517,7 +55517,7 @@
         <v>16</v>
       </c>
       <c r="E239" s="2" t="n">
-        <v>5436</v>
+        <v>5480</v>
       </c>
       <c r="F239" s="2" t="n">
         <v>13</v>
@@ -55541,7 +55541,7 @@
         <v>16</v>
       </c>
       <c r="E240" s="2" t="n">
-        <v>5452</v>
+        <v>5496</v>
       </c>
       <c r="F240" s="2" t="n">
         <v>10</v>
@@ -55565,7 +55565,7 @@
         <v>16</v>
       </c>
       <c r="E241" s="2" t="n">
-        <v>5464</v>
+        <v>5508</v>
       </c>
       <c r="F241" s="2" t="n">
         <v>12</v>
@@ -55589,7 +55589,7 @@
         <v>16</v>
       </c>
       <c r="E242" s="2" t="n">
-        <v>5478</v>
+        <v>5522</v>
       </c>
       <c r="F242" s="2" t="n">
         <v>9</v>
@@ -55613,7 +55613,7 @@
         <v>16</v>
       </c>
       <c r="E243" s="2" t="n">
-        <v>5490</v>
+        <v>5534</v>
       </c>
       <c r="F243" s="2" t="n">
         <v>12</v>
@@ -55637,7 +55637,7 @@
         <v>16</v>
       </c>
       <c r="E244" s="2" t="n">
-        <v>5504</v>
+        <v>5548</v>
       </c>
       <c r="F244" s="2" t="n">
         <v>10</v>
@@ -55661,7 +55661,7 @@
         <v>16</v>
       </c>
       <c r="E245" s="2" t="n">
-        <v>5517</v>
+        <v>5561</v>
       </c>
       <c r="F245" s="2" t="n">
         <v>13</v>
@@ -55685,7 +55685,7 @@
         <v>16</v>
       </c>
       <c r="E246" s="2" t="n">
-        <v>5533</v>
+        <v>5577</v>
       </c>
       <c r="F246" s="2" t="n">
         <v>10</v>
@@ -55709,7 +55709,7 @@
         <v>16</v>
       </c>
       <c r="E247" s="2" t="n">
-        <v>5545</v>
+        <v>5589</v>
       </c>
       <c r="F247" s="2" t="n">
         <v>11</v>
@@ -55733,7 +55733,7 @@
         <v>16</v>
       </c>
       <c r="E248" s="2" t="n">
-        <v>5559</v>
+        <v>5603</v>
       </c>
       <c r="F248" s="2" t="n">
         <v>12</v>
@@ -55757,7 +55757,7 @@
         <v>16</v>
       </c>
       <c r="E249" s="2" t="n">
-        <v>5574</v>
+        <v>5618</v>
       </c>
       <c r="F249" s="2" t="n">
         <v>10</v>
@@ -55781,7 +55781,7 @@
         <v>16</v>
       </c>
       <c r="E250" s="2" t="n">
-        <v>5586</v>
+        <v>5630</v>
       </c>
       <c r="F250" s="2" t="n">
         <v>17</v>
@@ -55805,7 +55805,7 @@
         <v>16</v>
       </c>
       <c r="E251" s="2" t="n">
-        <v>5606</v>
+        <v>5650</v>
       </c>
       <c r="F251" s="2" t="n">
         <v>14</v>
@@ -55829,7 +55829,7 @@
         <v>16</v>
       </c>
       <c r="E252" s="2" t="n">
-        <v>5623</v>
+        <v>5667</v>
       </c>
       <c r="F252" s="2" t="n">
         <v>14</v>
@@ -55853,7 +55853,7 @@
         <v>16</v>
       </c>
       <c r="E253" s="2" t="n">
-        <v>5640</v>
+        <v>5684</v>
       </c>
       <c r="F253" s="2" t="n">
         <v>14</v>
@@ -55877,7 +55877,7 @@
         <v>16</v>
       </c>
       <c r="E254" s="2" t="n">
-        <v>5657</v>
+        <v>5701</v>
       </c>
       <c r="F254" s="2" t="n">
         <v>10</v>
@@ -55901,7 +55901,7 @@
         <v>16</v>
       </c>
       <c r="E255" s="2" t="n">
-        <v>5669</v>
+        <v>5713</v>
       </c>
       <c r="F255" s="2" t="n">
         <v>15</v>
@@ -55925,7 +55925,7 @@
         <v>16</v>
       </c>
       <c r="E256" s="2" t="n">
-        <v>5687</v>
+        <v>5731</v>
       </c>
       <c r="F256" s="2" t="n">
         <v>10</v>
@@ -55949,7 +55949,7 @@
         <v>16</v>
       </c>
       <c r="E257" s="2" t="n">
-        <v>5700</v>
+        <v>5744</v>
       </c>
       <c r="F257" s="2" t="n">
         <v>13</v>
@@ -55973,7 +55973,7 @@
         <v>16</v>
       </c>
       <c r="E258" s="2" t="n">
-        <v>5715</v>
+        <v>5759</v>
       </c>
       <c r="F258" s="2" t="n">
         <v>11</v>
@@ -55997,7 +55997,7 @@
         <v>16</v>
       </c>
       <c r="E259" s="2" t="n">
-        <v>5729</v>
+        <v>5773</v>
       </c>
       <c r="F259" s="2" t="n">
         <v>12</v>
@@ -56021,7 +56021,7 @@
         <v>16</v>
       </c>
       <c r="E260" s="2" t="n">
-        <v>5744</v>
+        <v>5788</v>
       </c>
       <c r="F260" s="2" t="n">
         <v>10</v>
@@ -56045,7 +56045,7 @@
         <v>16</v>
       </c>
       <c r="E261" s="2" t="n">
-        <v>5756</v>
+        <v>5800</v>
       </c>
       <c r="F261" s="2" t="n">
         <v>12</v>
@@ -56069,7 +56069,7 @@
         <v>16</v>
       </c>
       <c r="E262" s="2" t="n">
-        <v>5771</v>
+        <v>5815</v>
       </c>
       <c r="F262" s="2" t="n">
         <v>12</v>
@@ -56093,7 +56093,7 @@
         <v>16</v>
       </c>
       <c r="E263" s="2" t="n">
-        <v>5786</v>
+        <v>5830</v>
       </c>
       <c r="F263" s="2" t="n">
         <v>11</v>
@@ -56117,7 +56117,7 @@
         <v>16</v>
       </c>
       <c r="E264" s="2" t="n">
-        <v>5799</v>
+        <v>5843</v>
       </c>
       <c r="F264" s="2" t="n">
         <v>10</v>
@@ -56141,7 +56141,7 @@
         <v>16</v>
       </c>
       <c r="E265" s="2" t="n">
-        <v>5812</v>
+        <v>5856</v>
       </c>
       <c r="F265" s="2" t="n">
         <v>10</v>
@@ -56165,7 +56165,7 @@
         <v>16</v>
       </c>
       <c r="E266" s="2" t="n">
-        <v>5824</v>
+        <v>5868</v>
       </c>
       <c r="F266" s="2" t="n">
         <v>12</v>
@@ -56189,7 +56189,7 @@
         <v>16</v>
       </c>
       <c r="E267" s="2" t="n">
-        <v>5839</v>
+        <v>5883</v>
       </c>
       <c r="F267" s="2" t="n">
         <v>13</v>
@@ -56213,7 +56213,7 @@
         <v>16</v>
       </c>
       <c r="E268" s="2" t="n">
-        <v>5855</v>
+        <v>5899</v>
       </c>
       <c r="F268" s="2" t="n">
         <v>10</v>
@@ -56237,7 +56237,7 @@
         <v>16</v>
       </c>
       <c r="E269" s="2" t="n">
-        <v>5867</v>
+        <v>5911</v>
       </c>
       <c r="F269" s="2" t="n">
         <v>12</v>
@@ -56261,7 +56261,7 @@
         <v>16</v>
       </c>
       <c r="E270" s="2" t="n">
-        <v>5882</v>
+        <v>5926</v>
       </c>
       <c r="F270" s="2" t="n">
         <v>10</v>
@@ -56285,7 +56285,7 @@
         <v>16</v>
       </c>
       <c r="E271" s="2" t="n">
-        <v>5894</v>
+        <v>5938</v>
       </c>
       <c r="F271" s="2" t="n">
         <v>11</v>
@@ -56309,7 +56309,7 @@
         <v>16</v>
       </c>
       <c r="E272" s="2" t="n">
-        <v>5907</v>
+        <v>5951</v>
       </c>
       <c r="F272" s="2" t="n">
         <v>13</v>
@@ -56333,7 +56333,7 @@
         <v>16</v>
       </c>
       <c r="E273" s="2" t="n">
-        <v>5923</v>
+        <v>5967</v>
       </c>
       <c r="F273" s="2" t="n">
         <v>9</v>
@@ -56357,7 +56357,7 @@
         <v>16</v>
       </c>
       <c r="E274" s="2" t="n">
-        <v>5934</v>
+        <v>5978</v>
       </c>
       <c r="F274" s="2" t="n">
         <v>13</v>
@@ -56381,7 +56381,7 @@
         <v>16</v>
       </c>
       <c r="E275" s="2" t="n">
-        <v>5950</v>
+        <v>5994</v>
       </c>
       <c r="F275" s="2" t="n">
         <v>11</v>
@@ -56405,7 +56405,7 @@
         <v>16</v>
       </c>
       <c r="E276" s="2" t="n">
-        <v>5964</v>
+        <v>6008</v>
       </c>
       <c r="F276" s="2" t="n">
         <v>11</v>
@@ -56429,7 +56429,7 @@
         <v>16</v>
       </c>
       <c r="E277" s="2" t="n">
-        <v>5977</v>
+        <v>6021</v>
       </c>
       <c r="F277" s="2" t="n">
         <v>10</v>
@@ -56453,7 +56453,7 @@
         <v>16</v>
       </c>
       <c r="E278" s="2" t="n">
-        <v>5990</v>
+        <v>6034</v>
       </c>
       <c r="F278" s="2" t="n">
         <v>11</v>
@@ -56477,7 +56477,7 @@
         <v>16</v>
       </c>
       <c r="E279" s="2" t="n">
-        <v>6004</v>
+        <v>6048</v>
       </c>
       <c r="F279" s="2" t="n">
         <v>10</v>
@@ -56501,7 +56501,7 @@
         <v>16</v>
       </c>
       <c r="E280" s="2" t="n">
-        <v>6016</v>
+        <v>6060</v>
       </c>
       <c r="F280" s="2" t="n">
         <v>12</v>
@@ -56525,7 +56525,7 @@
         <v>16</v>
       </c>
       <c r="E281" s="2" t="n">
-        <v>6031</v>
+        <v>6075</v>
       </c>
       <c r="F281" s="2" t="n">
         <v>10</v>
@@ -56549,7 +56549,7 @@
         <v>16</v>
       </c>
       <c r="E282" s="2" t="n">
-        <v>6043</v>
+        <v>6087</v>
       </c>
       <c r="F282" s="2" t="n">
         <v>11</v>
@@ -56573,7 +56573,7 @@
         <v>16</v>
       </c>
       <c r="E283" s="2" t="n">
-        <v>6056</v>
+        <v>6100</v>
       </c>
       <c r="F283" s="2" t="n">
         <v>14</v>
@@ -56597,7 +56597,7 @@
         <v>16</v>
       </c>
       <c r="E284" s="2" t="n">
-        <v>6073</v>
+        <v>6117</v>
       </c>
       <c r="F284" s="2" t="n">
         <v>12</v>
@@ -56621,7 +56621,7 @@
         <v>16</v>
       </c>
       <c r="E285" s="2" t="n">
-        <v>6087</v>
+        <v>6131</v>
       </c>
       <c r="F285" s="2" t="n">
         <v>10</v>
@@ -56645,7 +56645,7 @@
         <v>16</v>
       </c>
       <c r="E286" s="2" t="n">
-        <v>6100</v>
+        <v>6144</v>
       </c>
       <c r="F286" s="2" t="n">
         <v>10</v>
@@ -56669,7 +56669,7 @@
         <v>16</v>
       </c>
       <c r="E287" s="2" t="n">
-        <v>6113</v>
+        <v>6157</v>
       </c>
       <c r="F287" s="2" t="n">
         <v>11</v>
@@ -56693,7 +56693,7 @@
         <v>16</v>
       </c>
       <c r="E288" s="2" t="n">
-        <v>6126</v>
+        <v>6170</v>
       </c>
       <c r="F288" s="2" t="n">
         <v>9</v>
@@ -56717,7 +56717,7 @@
         <v>16</v>
       </c>
       <c r="E289" s="2" t="n">
-        <v>6138</v>
+        <v>6182</v>
       </c>
       <c r="F289" s="2" t="n">
         <v>9</v>
@@ -56741,7 +56741,7 @@
         <v>16</v>
       </c>
       <c r="E290" s="2" t="n">
-        <v>6149</v>
+        <v>6193</v>
       </c>
       <c r="F290" s="2" t="n">
         <v>10</v>
@@ -56765,7 +56765,7 @@
         <v>16</v>
       </c>
       <c r="E291" s="2" t="n">
-        <v>6162</v>
+        <v>6206</v>
       </c>
       <c r="F291" s="2" t="n">
         <v>16</v>
@@ -56789,7 +56789,7 @@
         <v>16</v>
       </c>
       <c r="E292" s="2" t="n">
-        <v>6181</v>
+        <v>6225</v>
       </c>
       <c r="F292" s="2" t="n">
         <v>16</v>
@@ -56813,7 +56813,7 @@
         <v>16</v>
       </c>
       <c r="E293" s="2" t="n">
-        <v>6200</v>
+        <v>6244</v>
       </c>
       <c r="F293" s="2" t="n">
         <v>12</v>
@@ -56837,7 +56837,7 @@
         <v>16</v>
       </c>
       <c r="E294" s="2" t="n">
-        <v>6214</v>
+        <v>6258</v>
       </c>
       <c r="F294" s="2" t="n">
         <v>10</v>
@@ -56861,7 +56861,7 @@
         <v>16</v>
       </c>
       <c r="E295" s="2" t="n">
-        <v>6227</v>
+        <v>6271</v>
       </c>
       <c r="F295" s="2" t="n">
         <v>10</v>
@@ -56885,7 +56885,7 @@
         <v>16</v>
       </c>
       <c r="E296" s="2" t="n">
-        <v>6239</v>
+        <v>6283</v>
       </c>
       <c r="F296" s="2" t="n">
         <v>13</v>
@@ -56909,7 +56909,7 @@
         <v>16</v>
       </c>
       <c r="E297" s="2" t="n">
-        <v>6254</v>
+        <v>6298</v>
       </c>
       <c r="F297" s="2" t="n">
         <v>10</v>
@@ -56933,7 +56933,7 @@
         <v>16</v>
       </c>
       <c r="E298" s="2" t="n">
-        <v>6267</v>
+        <v>6311</v>
       </c>
       <c r="F298" s="2" t="n">
         <v>10</v>
@@ -56957,7 +56957,7 @@
         <v>16</v>
       </c>
       <c r="E299" s="2" t="n">
-        <v>6279</v>
+        <v>6323</v>
       </c>
       <c r="F299" s="2" t="n">
         <v>12</v>
@@ -56981,7 +56981,7 @@
         <v>16</v>
       </c>
       <c r="E300" s="2" t="n">
-        <v>6294</v>
+        <v>6338</v>
       </c>
       <c r="F300" s="2" t="n">
         <v>11</v>
@@ -57005,7 +57005,7 @@
         <v>16</v>
       </c>
       <c r="E301" s="2" t="n">
-        <v>6307</v>
+        <v>6351</v>
       </c>
       <c r="F301" s="2" t="n">
         <v>11</v>
@@ -57029,7 +57029,7 @@
         <v>16</v>
       </c>
       <c r="E302" s="2" t="n">
-        <v>6320</v>
+        <v>6364</v>
       </c>
       <c r="F302" s="2" t="n">
         <v>10</v>
@@ -57053,7 +57053,7 @@
         <v>16</v>
       </c>
       <c r="E303" s="2" t="n">
-        <v>6333</v>
+        <v>6377</v>
       </c>
       <c r="F303" s="2" t="n">
         <v>9</v>
@@ -57077,7 +57077,7 @@
         <v>16</v>
       </c>
       <c r="E304" s="2" t="n">
-        <v>6344</v>
+        <v>6388</v>
       </c>
       <c r="F304" s="2" t="n">
         <v>10</v>
@@ -57101,7 +57101,7 @@
         <v>16</v>
       </c>
       <c r="E305" s="2" t="n">
-        <v>6357</v>
+        <v>6401</v>
       </c>
       <c r="F305" s="2" t="n">
         <v>10</v>
@@ -57125,7 +57125,7 @@
         <v>16</v>
       </c>
       <c r="E306" s="2" t="n">
-        <v>6369</v>
+        <v>6413</v>
       </c>
       <c r="F306" s="2" t="n">
         <v>11</v>
@@ -57149,7 +57149,7 @@
         <v>16</v>
       </c>
       <c r="E307" s="2" t="n">
-        <v>6383</v>
+        <v>6427</v>
       </c>
       <c r="F307" s="2" t="n">
         <v>12</v>
@@ -57173,7 +57173,7 @@
         <v>16</v>
       </c>
       <c r="E308" s="2" t="n">
-        <v>6398</v>
+        <v>6442</v>
       </c>
       <c r="F308" s="2" t="n">
         <v>12</v>
@@ -57197,7 +57197,7 @@
         <v>16</v>
       </c>
       <c r="E309" s="2" t="n">
-        <v>6412</v>
+        <v>6456</v>
       </c>
       <c r="F309" s="2" t="n">
         <v>13</v>
@@ -57221,7 +57221,7 @@
         <v>16</v>
       </c>
       <c r="E310" s="2" t="n">
-        <v>6428</v>
+        <v>6472</v>
       </c>
       <c r="F310" s="2" t="n">
         <v>29</v>
@@ -57245,7 +57245,7 @@
         <v>16</v>
       </c>
       <c r="E311" s="2" t="n">
-        <v>6461</v>
+        <v>6505</v>
       </c>
       <c r="F311" s="2" t="n">
         <v>19</v>
@@ -57269,7 +57269,7 @@
         <v>16</v>
       </c>
       <c r="E312" s="2" t="n">
-        <v>6483</v>
+        <v>6527</v>
       </c>
       <c r="F312" s="2" t="n">
         <v>15</v>
@@ -57293,7 +57293,7 @@
         <v>16</v>
       </c>
       <c r="E313" s="2" t="n">
-        <v>6500</v>
+        <v>6544</v>
       </c>
       <c r="F313" s="2" t="n">
         <v>13</v>
@@ -57317,7 +57317,7 @@
         <v>16</v>
       </c>
       <c r="E314" s="2" t="n">
-        <v>6515</v>
+        <v>6559</v>
       </c>
       <c r="F314" s="2" t="n">
         <v>18</v>
@@ -57341,7 +57341,7 @@
         <v>16</v>
       </c>
       <c r="E315" s="2" t="n">
-        <v>6536</v>
+        <v>6580</v>
       </c>
       <c r="F315" s="2" t="n">
         <v>16</v>
@@ -57365,7 +57365,7 @@
         <v>16</v>
       </c>
       <c r="E316" s="2" t="n">
-        <v>6555</v>
+        <v>6599</v>
       </c>
       <c r="F316" s="2" t="n">
         <v>21</v>
@@ -57389,7 +57389,7 @@
         <v>16</v>
       </c>
       <c r="E317" s="2" t="n">
-        <v>6579</v>
+        <v>6623</v>
       </c>
       <c r="F317" s="2" t="n">
         <v>17</v>
@@ -57413,7 +57413,7 @@
         <v>16</v>
       </c>
       <c r="E318" s="2" t="n">
-        <v>6599</v>
+        <v>6643</v>
       </c>
       <c r="F318" s="2" t="n">
         <v>13</v>
@@ -57437,7 +57437,7 @@
         <v>16</v>
       </c>
       <c r="E319" s="2" t="n">
-        <v>6615</v>
+        <v>6659</v>
       </c>
       <c r="F319" s="2" t="n">
         <v>11</v>
@@ -57461,7 +57461,7 @@
         <v>16</v>
       </c>
       <c r="E320" s="2" t="n">
-        <v>6629</v>
+        <v>6673</v>
       </c>
       <c r="F320" s="2" t="n">
         <v>16</v>
@@ -57485,7 +57485,7 @@
         <v>16</v>
       </c>
       <c r="E321" s="2" t="n">
-        <v>6647</v>
+        <v>6691</v>
       </c>
       <c r="F321" s="2" t="n">
         <v>12</v>
@@ -57509,7 +57509,7 @@
         <v>16</v>
       </c>
       <c r="E322" s="2" t="n">
-        <v>6662</v>
+        <v>6706</v>
       </c>
       <c r="F322" s="2" t="n">
         <v>16</v>
@@ -57533,7 +57533,7 @@
         <v>16</v>
       </c>
       <c r="E323" s="2" t="n">
-        <v>6681</v>
+        <v>6725</v>
       </c>
       <c r="F323" s="2" t="n">
         <v>10</v>
@@ -57557,7 +57557,7 @@
         <v>16</v>
       </c>
       <c r="E324" s="2" t="n">
-        <v>6694</v>
+        <v>6738</v>
       </c>
       <c r="F324" s="2" t="n">
         <v>13</v>
@@ -57581,7 +57581,7 @@
         <v>16</v>
       </c>
       <c r="E325" s="2" t="n">
-        <v>6709</v>
+        <v>6753</v>
       </c>
       <c r="F325" s="2" t="n">
         <v>10</v>
@@ -57605,7 +57605,7 @@
         <v>16</v>
       </c>
       <c r="E326" s="2" t="n">
-        <v>6722</v>
+        <v>6766</v>
       </c>
       <c r="F326" s="2" t="n">
         <v>15</v>
@@ -57629,7 +57629,7 @@
         <v>16</v>
       </c>
       <c r="E327" s="2" t="n">
-        <v>6740</v>
+        <v>6784</v>
       </c>
       <c r="F327" s="2" t="n">
         <v>14</v>
@@ -57653,7 +57653,7 @@
         <v>16</v>
       </c>
       <c r="E328" s="2" t="n">
-        <v>6756</v>
+        <v>6800</v>
       </c>
       <c r="F328" s="2" t="n">
         <v>10</v>
@@ -57677,7 +57677,7 @@
         <v>16</v>
       </c>
       <c r="E329" s="2" t="n">
-        <v>6769</v>
+        <v>6813</v>
       </c>
       <c r="F329" s="2" t="n">
         <v>11</v>
@@ -57701,7 +57701,7 @@
         <v>16</v>
       </c>
       <c r="E330" s="2" t="n">
-        <v>6782</v>
+        <v>6826</v>
       </c>
       <c r="F330" s="2" t="n">
         <v>8</v>
@@ -57725,7 +57725,7 @@
         <v>16</v>
       </c>
       <c r="E331" s="2" t="n">
-        <v>6792</v>
+        <v>6836</v>
       </c>
       <c r="F331" s="2" t="n">
         <v>7</v>
@@ -57749,7 +57749,7 @@
         <v>16</v>
       </c>
       <c r="E332" s="2" t="n">
-        <v>6801</v>
+        <v>6845</v>
       </c>
       <c r="F332" s="2" t="n">
         <v>11</v>
@@ -57773,7 +57773,7 @@
         <v>16</v>
       </c>
       <c r="E333" s="2" t="n">
-        <v>6815</v>
+        <v>6859</v>
       </c>
       <c r="F333" s="2" t="n">
         <v>9</v>
@@ -57797,7 +57797,7 @@
         <v>16</v>
       </c>
       <c r="E334" s="2" t="n">
-        <v>6827</v>
+        <v>6871</v>
       </c>
       <c r="F334" s="2" t="n">
         <v>13</v>
@@ -57821,7 +57821,7 @@
         <v>16</v>
       </c>
       <c r="E335" s="2" t="n">
-        <v>6842</v>
+        <v>6886</v>
       </c>
       <c r="F335" s="2" t="n">
         <v>9</v>
@@ -57845,7 +57845,7 @@
         <v>16</v>
       </c>
       <c r="E336" s="2" t="n">
-        <v>6853</v>
+        <v>6897</v>
       </c>
       <c r="F336" s="2" t="n">
         <v>9</v>
@@ -57869,7 +57869,7 @@
         <v>16</v>
       </c>
       <c r="E337" s="2" t="n">
-        <v>6865</v>
+        <v>6909</v>
       </c>
       <c r="F337" s="2" t="n">
         <v>11</v>
@@ -57893,7 +57893,7 @@
         <v>16</v>
       </c>
       <c r="E338" s="2" t="n">
-        <v>6878</v>
+        <v>6922</v>
       </c>
       <c r="F338" s="2" t="n">
         <v>12</v>
@@ -57917,7 +57917,7 @@
         <v>16</v>
       </c>
       <c r="E339" s="2" t="n">
-        <v>6893</v>
+        <v>6937</v>
       </c>
       <c r="F339" s="2" t="n">
         <v>12</v>
@@ -57941,7 +57941,7 @@
         <v>16</v>
       </c>
       <c r="E340" s="2" t="n">
-        <v>6908</v>
+        <v>6952</v>
       </c>
       <c r="F340" s="2" t="n">
         <v>16</v>
@@ -57965,7 +57965,7 @@
         <v>16</v>
       </c>
       <c r="E341" s="2" t="n">
-        <v>6927</v>
+        <v>6971</v>
       </c>
       <c r="F341" s="2" t="n">
         <v>10</v>
@@ -57989,7 +57989,7 @@
         <v>16</v>
       </c>
       <c r="E342" s="2" t="n">
-        <v>6939</v>
+        <v>6983</v>
       </c>
       <c r="F342" s="2" t="n">
         <v>17</v>
@@ -58013,7 +58013,7 @@
         <v>16</v>
       </c>
       <c r="E343" s="2" t="n">
-        <v>6959</v>
+        <v>7003</v>
       </c>
       <c r="F343" s="2" t="n">
         <v>11</v>
@@ -58037,7 +58037,7 @@
         <v>16</v>
       </c>
       <c r="E344" s="2" t="n">
-        <v>6973</v>
+        <v>7017</v>
       </c>
       <c r="F344" s="2" t="n">
         <v>10</v>
@@ -58061,7 +58061,7 @@
         <v>16</v>
       </c>
       <c r="E345" s="2" t="n">
-        <v>6985</v>
+        <v>7029</v>
       </c>
       <c r="F345" s="2" t="n">
         <v>23</v>
@@ -58085,7 +58085,7 @@
         <v>16</v>
       </c>
       <c r="E346" s="2" t="n">
-        <v>7012</v>
+        <v>7056</v>
       </c>
       <c r="F346" s="2" t="n">
         <v>12</v>
@@ -58109,7 +58109,7 @@
         <v>16</v>
       </c>
       <c r="E347" s="2" t="n">
-        <v>7026</v>
+        <v>7070</v>
       </c>
       <c r="F347" s="2" t="n">
         <v>14</v>
@@ -58133,7 +58133,7 @@
         <v>16</v>
       </c>
       <c r="E348" s="2" t="n">
-        <v>7043</v>
+        <v>7087</v>
       </c>
       <c r="F348" s="2" t="n">
         <v>14</v>
@@ -58157,7 +58157,7 @@
         <v>16</v>
       </c>
       <c r="E349" s="2" t="n">
-        <v>7060</v>
+        <v>7104</v>
       </c>
       <c r="F349" s="2" t="n">
         <v>11</v>
@@ -58181,7 +58181,7 @@
         <v>16</v>
       </c>
       <c r="E350" s="2" t="n">
-        <v>7073</v>
+        <v>7117</v>
       </c>
       <c r="F350" s="2" t="n">
         <v>12</v>
@@ -58205,7 +58205,7 @@
         <v>16</v>
       </c>
       <c r="E351" s="2" t="n">
-        <v>7088</v>
+        <v>7132</v>
       </c>
       <c r="F351" s="2" t="n">
         <v>13</v>
@@ -58229,7 +58229,7 @@
         <v>16</v>
       </c>
       <c r="E352" s="2" t="n">
-        <v>7103</v>
+        <v>7147</v>
       </c>
       <c r="F352" s="2" t="n">
         <v>11</v>
@@ -58253,7 +58253,7 @@
         <v>16</v>
       </c>
       <c r="E353" s="2" t="n">
-        <v>7116</v>
+        <v>7160</v>
       </c>
       <c r="F353" s="2" t="n">
         <v>12</v>
@@ -58277,7 +58277,7 @@
         <v>16</v>
       </c>
       <c r="E354" s="2" t="n">
-        <v>7131</v>
+        <v>7175</v>
       </c>
       <c r="F354" s="2" t="n">
         <v>9</v>
@@ -58301,7 +58301,7 @@
         <v>16</v>
       </c>
       <c r="E355" s="2" t="n">
-        <v>7142</v>
+        <v>7186</v>
       </c>
       <c r="F355" s="2" t="n">
         <v>15</v>
@@ -58325,7 +58325,7 @@
         <v>16</v>
       </c>
       <c r="E356" s="2" t="n">
-        <v>7160</v>
+        <v>7204</v>
       </c>
       <c r="F356" s="2" t="n">
         <v>13</v>
@@ -58349,7 +58349,7 @@
         <v>16</v>
       </c>
       <c r="E357" s="2" t="n">
-        <v>7176</v>
+        <v>7220</v>
       </c>
       <c r="F357" s="2" t="n">
         <v>9</v>
@@ -58373,7 +58373,7 @@
         <v>16</v>
       </c>
       <c r="E358" s="2" t="n">
-        <v>7187</v>
+        <v>7231</v>
       </c>
       <c r="F358" s="2" t="n">
         <v>12</v>
@@ -58397,7 +58397,7 @@
         <v>16</v>
       </c>
       <c r="E359" s="2" t="n">
-        <v>7201</v>
+        <v>7245</v>
       </c>
       <c r="F359" s="2" t="n">
         <v>10</v>
@@ -58421,7 +58421,7 @@
         <v>16</v>
       </c>
       <c r="E360" s="2" t="n">
-        <v>7214</v>
+        <v>7258</v>
       </c>
       <c r="F360" s="2" t="n">
         <v>8</v>
@@ -58445,7 +58445,7 @@
         <v>16</v>
       </c>
       <c r="E361" s="2" t="n">
-        <v>7224</v>
+        <v>7268</v>
       </c>
       <c r="F361" s="2" t="n">
         <v>15</v>
@@ -58469,7 +58469,7 @@
         <v>16</v>
       </c>
       <c r="E362" s="2" t="n">
-        <v>7242</v>
+        <v>7286</v>
       </c>
       <c r="F362" s="2" t="n">
         <v>12</v>
@@ -58493,7 +58493,7 @@
         <v>16</v>
       </c>
       <c r="E363" s="2" t="n">
-        <v>7257</v>
+        <v>7301</v>
       </c>
       <c r="F363" s="2" t="n">
         <v>12</v>
@@ -58517,7 +58517,7 @@
         <v>16</v>
       </c>
       <c r="E364" s="2" t="n">
-        <v>7271</v>
+        <v>7315</v>
       </c>
       <c r="F364" s="2" t="n">
         <v>13</v>
@@ -58541,7 +58541,7 @@
         <v>16</v>
       </c>
       <c r="E365" s="2" t="n">
-        <v>7288</v>
+        <v>7332</v>
       </c>
       <c r="F365" s="2" t="n">
         <v>12</v>
@@ -58565,7 +58565,7 @@
         <v>16</v>
       </c>
       <c r="E366" s="2" t="n">
-        <v>7303</v>
+        <v>7347</v>
       </c>
       <c r="F366" s="2" t="n">
         <v>11</v>
@@ -58589,7 +58589,7 @@
         <v>16</v>
       </c>
       <c r="E367" s="2" t="n">
-        <v>7316</v>
+        <v>7360</v>
       </c>
       <c r="F367" s="2" t="n">
         <v>12</v>
@@ -58613,7 +58613,7 @@
         <v>16</v>
       </c>
       <c r="E368" s="2" t="n">
-        <v>7331</v>
+        <v>7375</v>
       </c>
       <c r="F368" s="2" t="n">
         <v>9</v>
@@ -58637,7 +58637,7 @@
         <v>16</v>
       </c>
       <c r="E369" s="2" t="n">
-        <v>7342</v>
+        <v>7386</v>
       </c>
       <c r="F369" s="2" t="n">
         <v>11</v>
@@ -58661,7 +58661,7 @@
         <v>16</v>
       </c>
       <c r="E370" s="2" t="n">
-        <v>7356</v>
+        <v>7400</v>
       </c>
       <c r="F370" s="2" t="n">
         <v>8</v>
@@ -58685,7 +58685,7 @@
         <v>16</v>
       </c>
       <c r="E371" s="2" t="n">
-        <v>7366</v>
+        <v>7410</v>
       </c>
       <c r="F371" s="2" t="n">
         <v>12</v>
@@ -58709,7 +58709,7 @@
         <v>16</v>
       </c>
       <c r="E372" s="2" t="n">
-        <v>7380</v>
+        <v>7424</v>
       </c>
       <c r="F372" s="2" t="n">
         <v>16</v>
@@ -58733,7 +58733,7 @@
         <v>16</v>
       </c>
       <c r="E373" s="2" t="n">
-        <v>7399</v>
+        <v>7443</v>
       </c>
       <c r="F373" s="2" t="n">
         <v>11</v>
@@ -58757,7 +58757,7 @@
         <v>16</v>
       </c>
       <c r="E374" s="2" t="n">
-        <v>7412</v>
+        <v>7456</v>
       </c>
       <c r="F374" s="2" t="n">
         <v>12</v>
@@ -58781,7 +58781,7 @@
         <v>16</v>
       </c>
       <c r="E375" s="2" t="n">
-        <v>7426</v>
+        <v>7470</v>
       </c>
       <c r="F375" s="2" t="n">
         <v>10</v>
@@ -58805,7 +58805,7 @@
         <v>16</v>
       </c>
       <c r="E376" s="2" t="n">
-        <v>7439</v>
+        <v>7483</v>
       </c>
       <c r="F376" s="2" t="n">
         <v>15</v>
@@ -58829,7 +58829,7 @@
         <v>77</v>
       </c>
       <c r="E377" s="2" t="n">
-        <v>7457</v>
+        <v>7501</v>
       </c>
       <c r="F377" s="2" t="n">
         <v>23</v>
@@ -58853,7 +58853,7 @@
         <v>77</v>
       </c>
       <c r="E378" s="2" t="n">
-        <v>7483</v>
+        <v>7527</v>
       </c>
       <c r="F378" s="2" t="n">
         <v>20</v>
@@ -58877,7 +58877,7 @@
         <v>77</v>
       </c>
       <c r="E379" s="2" t="n">
-        <v>7506</v>
+        <v>7550</v>
       </c>
       <c r="F379" s="2" t="n">
         <v>15</v>
@@ -58901,7 +58901,7 @@
         <v>77</v>
       </c>
       <c r="E380" s="2" t="n">
-        <v>7524</v>
+        <v>7568</v>
       </c>
       <c r="F380" s="2" t="n">
         <v>12</v>
@@ -58925,7 +58925,7 @@
         <v>77</v>
       </c>
       <c r="E381" s="2" t="n">
-        <v>7539</v>
+        <v>7583</v>
       </c>
       <c r="F381" s="2" t="n">
         <v>17</v>
@@ -58949,7 +58949,7 @@
         <v>77</v>
       </c>
       <c r="E382" s="2" t="n">
-        <v>7559</v>
+        <v>7603</v>
       </c>
       <c r="F382" s="2" t="n">
         <v>19</v>
@@ -58973,7 +58973,7 @@
         <v>77</v>
       </c>
       <c r="E383" s="2" t="n">
-        <v>7581</v>
+        <v>7625</v>
       </c>
       <c r="F383" s="2" t="n">
         <v>16</v>
@@ -58997,7 +58997,7 @@
         <v>77</v>
       </c>
       <c r="E384" s="2" t="n">
-        <v>7599</v>
+        <v>7643</v>
       </c>
       <c r="F384" s="2" t="n">
         <v>16</v>
@@ -59021,7 +59021,7 @@
         <v>77</v>
       </c>
       <c r="E385" s="2" t="n">
-        <v>7618</v>
+        <v>7662</v>
       </c>
       <c r="F385" s="2" t="n">
         <v>16</v>
@@ -59045,7 +59045,7 @@
         <v>77</v>
       </c>
       <c r="E386" s="2" t="n">
-        <v>7637</v>
+        <v>7681</v>
       </c>
       <c r="F386" s="2" t="n">
         <v>15</v>
@@ -59069,7 +59069,7 @@
         <v>77</v>
       </c>
       <c r="E387" s="2" t="n">
-        <v>7655</v>
+        <v>7699</v>
       </c>
       <c r="F387" s="2" t="n">
         <v>14</v>
@@ -59093,7 +59093,7 @@
         <v>77</v>
       </c>
       <c r="E388" s="2" t="n">
-        <v>7672</v>
+        <v>7716</v>
       </c>
       <c r="F388" s="2" t="n">
         <v>18</v>
@@ -59117,7 +59117,7 @@
         <v>77</v>
       </c>
       <c r="E389" s="2" t="n">
-        <v>7693</v>
+        <v>7737</v>
       </c>
       <c r="F389" s="2" t="n">
         <v>14</v>
@@ -59141,7 +59141,7 @@
         <v>77</v>
       </c>
       <c r="E390" s="2" t="n">
-        <v>7710</v>
+        <v>7754</v>
       </c>
       <c r="F390" s="2" t="n">
         <v>13</v>
@@ -59165,7 +59165,7 @@
         <v>77</v>
       </c>
       <c r="E391" s="2" t="n">
-        <v>7725</v>
+        <v>7769</v>
       </c>
       <c r="F391" s="2" t="n">
         <v>11</v>
@@ -59189,7 +59189,7 @@
         <v>77</v>
       </c>
       <c r="E392" s="2" t="n">
-        <v>7739</v>
+        <v>7783</v>
       </c>
       <c r="F392" s="2" t="n">
         <v>12</v>
@@ -59213,7 +59213,7 @@
         <v>77</v>
       </c>
       <c r="E393" s="2" t="n">
-        <v>7754</v>
+        <v>7798</v>
       </c>
       <c r="F393" s="2" t="n">
         <v>11</v>
@@ -59237,7 +59237,7 @@
         <v>77</v>
       </c>
       <c r="E394" s="2" t="n">
-        <v>7767</v>
+        <v>7811</v>
       </c>
       <c r="F394" s="2" t="n">
         <v>14</v>
@@ -59261,7 +59261,7 @@
         <v>77</v>
       </c>
       <c r="E395" s="2" t="n">
-        <v>7784</v>
+        <v>7828</v>
       </c>
       <c r="F395" s="2" t="n">
         <v>14</v>
@@ -59285,7 +59285,7 @@
         <v>77</v>
       </c>
       <c r="E396" s="2" t="n">
-        <v>7801</v>
+        <v>7845</v>
       </c>
       <c r="F396" s="2" t="n">
         <v>12</v>
@@ -59309,7 +59309,7 @@
         <v>77</v>
       </c>
       <c r="E397" s="2" t="n">
-        <v>7816</v>
+        <v>7860</v>
       </c>
       <c r="F397" s="2" t="n">
         <v>11</v>
@@ -59333,7 +59333,7 @@
         <v>77</v>
       </c>
       <c r="E398" s="2" t="n">
-        <v>7829</v>
+        <v>7873</v>
       </c>
       <c r="F398" s="2" t="n">
         <v>14</v>
@@ -59357,7 +59357,7 @@
         <v>77</v>
       </c>
       <c r="E399" s="2" t="n">
-        <v>7846</v>
+        <v>7890</v>
       </c>
       <c r="F399" s="2" t="n">
         <v>11</v>
@@ -59381,7 +59381,7 @@
         <v>77</v>
       </c>
       <c r="E400" s="2" t="n">
-        <v>7860</v>
+        <v>7904</v>
       </c>
       <c r="F400" s="2" t="n">
         <v>11</v>
@@ -59405,7 +59405,7 @@
         <v>77</v>
       </c>
       <c r="E401" s="2" t="n">
-        <v>7873</v>
+        <v>7917</v>
       </c>
       <c r="F401" s="2" t="n">
         <v>13</v>
@@ -59429,7 +59429,7 @@
         <v>77</v>
       </c>
       <c r="E402" s="2" t="n">
-        <v>7889</v>
+        <v>7933</v>
       </c>
       <c r="F402" s="2" t="n">
         <v>20</v>
@@ -59453,7 +59453,7 @@
         <v>77</v>
       </c>
       <c r="E403" s="2" t="n">
-        <v>7912</v>
+        <v>7956</v>
       </c>
       <c r="F403" s="2" t="n">
         <v>11</v>
@@ -59477,7 +59477,7 @@
         <v>77</v>
       </c>
       <c r="E404" s="2" t="n">
-        <v>7926</v>
+        <v>7970</v>
       </c>
       <c r="F404" s="2" t="n">
         <v>13</v>
@@ -59501,7 +59501,7 @@
         <v>77</v>
       </c>
       <c r="E405" s="2" t="n">
-        <v>7942</v>
+        <v>7986</v>
       </c>
       <c r="F405" s="2" t="n">
         <v>13</v>
@@ -59525,7 +59525,7 @@
         <v>77</v>
       </c>
       <c r="E406" s="2" t="n">
-        <v>7957</v>
+        <v>8001</v>
       </c>
       <c r="F406" s="2" t="n">
         <v>14</v>
@@ -59549,7 +59549,7 @@
         <v>77</v>
       </c>
       <c r="E407" s="2" t="n">
-        <v>7974</v>
+        <v>8018</v>
       </c>
       <c r="F407" s="2" t="n">
         <v>15</v>
@@ -59573,7 +59573,7 @@
         <v>77</v>
       </c>
       <c r="E408" s="2" t="n">
-        <v>7992</v>
+        <v>8036</v>
       </c>
       <c r="F408" s="2" t="n">
         <v>15</v>
@@ -59597,7 +59597,7 @@
         <v>77</v>
       </c>
       <c r="E409" s="2" t="n">
-        <v>8010</v>
+        <v>8054</v>
       </c>
       <c r="F409" s="2" t="n">
         <v>14</v>
@@ -59621,7 +59621,7 @@
         <v>77</v>
       </c>
       <c r="E410" s="2" t="n">
-        <v>8027</v>
+        <v>8071</v>
       </c>
       <c r="F410" s="2" t="n">
         <v>14</v>
@@ -59645,7 +59645,7 @@
         <v>77</v>
       </c>
       <c r="E411" s="2" t="n">
-        <v>8043</v>
+        <v>8087</v>
       </c>
       <c r="F411" s="2" t="n">
         <v>17</v>
@@ -59669,7 +59669,7 @@
         <v>77</v>
       </c>
       <c r="E412" s="2" t="n">
-        <v>8063</v>
+        <v>8107</v>
       </c>
       <c r="F412" s="2" t="n">
         <v>15</v>
@@ -59693,7 +59693,7 @@
         <v>77</v>
       </c>
       <c r="E413" s="2" t="n">
-        <v>8081</v>
+        <v>8125</v>
       </c>
       <c r="F413" s="2" t="n">
         <v>16</v>
@@ -59717,7 +59717,7 @@
         <v>77</v>
       </c>
       <c r="E414" s="2" t="n">
-        <v>8100</v>
+        <v>8144</v>
       </c>
       <c r="F414" s="2" t="n">
         <v>19</v>
@@ -59741,7 +59741,7 @@
         <v>77</v>
       </c>
       <c r="E415" s="2" t="n">
-        <v>8122</v>
+        <v>8166</v>
       </c>
       <c r="F415" s="2" t="n">
         <v>19</v>
@@ -59765,7 +59765,7 @@
         <v>77</v>
       </c>
       <c r="E416" s="2" t="n">
-        <v>8144</v>
+        <v>8188</v>
       </c>
       <c r="F416" s="2" t="n">
         <v>14</v>
@@ -59789,7 +59789,7 @@
         <v>77</v>
       </c>
       <c r="E417" s="2" t="n">
-        <v>8161</v>
+        <v>8205</v>
       </c>
       <c r="F417" s="2" t="n">
         <v>13</v>
@@ -59813,7 +59813,7 @@
         <v>77</v>
       </c>
       <c r="E418" s="2" t="n">
-        <v>8177</v>
+        <v>8221</v>
       </c>
       <c r="F418" s="2" t="n">
         <v>12</v>
@@ -59837,7 +59837,7 @@
         <v>77</v>
       </c>
       <c r="E419" s="2" t="n">
-        <v>8191</v>
+        <v>8235</v>
       </c>
       <c r="F419" s="2" t="n">
         <v>10</v>
@@ -59861,7 +59861,7 @@
         <v>77</v>
       </c>
       <c r="E420" s="2" t="n">
-        <v>8204</v>
+        <v>8248</v>
       </c>
       <c r="F420" s="2" t="n">
         <v>11</v>
@@ -59885,7 +59885,7 @@
         <v>77</v>
       </c>
       <c r="E421" s="2" t="n">
-        <v>8218</v>
+        <v>8262</v>
       </c>
       <c r="F421" s="2" t="n">
         <v>11</v>
@@ -59909,7 +59909,7 @@
         <v>77</v>
       </c>
       <c r="E422" s="2" t="n">
-        <v>8231</v>
+        <v>8275</v>
       </c>
       <c r="F422" s="2" t="n">
         <v>13</v>
@@ -59933,7 +59933,7 @@
         <v>77</v>
       </c>
       <c r="E423" s="2" t="n">
-        <v>8247</v>
+        <v>8291</v>
       </c>
       <c r="F423" s="2" t="n">
         <v>18</v>
@@ -59957,7 +59957,7 @@
         <v>77</v>
       </c>
       <c r="E424" s="2" t="n">
-        <v>8268</v>
+        <v>8312</v>
       </c>
       <c r="F424" s="2" t="n">
         <v>11</v>
@@ -59981,7 +59981,7 @@
         <v>77</v>
       </c>
       <c r="E425" s="2" t="n">
-        <v>8282</v>
+        <v>8326</v>
       </c>
       <c r="F425" s="2" t="n">
         <v>12</v>
@@ -60005,7 +60005,7 @@
         <v>77</v>
       </c>
       <c r="E426" s="2" t="n">
-        <v>8296</v>
+        <v>8340</v>
       </c>
       <c r="F426" s="2" t="n">
         <v>9</v>
@@ -60029,7 +60029,7 @@
         <v>77</v>
       </c>
       <c r="E427" s="2" t="n">
-        <v>8308</v>
+        <v>8352</v>
       </c>
       <c r="F427" s="2" t="n">
         <v>10</v>
@@ -60053,7 +60053,7 @@
         <v>77</v>
       </c>
       <c r="E428" s="2" t="n">
-        <v>8320</v>
+        <v>8364</v>
       </c>
       <c r="F428" s="2" t="n">
         <v>10</v>
@@ -60077,7 +60077,7 @@
         <v>77</v>
       </c>
       <c r="E429" s="2" t="n">
-        <v>8332</v>
+        <v>8376</v>
       </c>
       <c r="F429" s="2" t="n">
         <v>11</v>
@@ -60101,7 +60101,7 @@
         <v>77</v>
       </c>
       <c r="E430" s="2" t="n">
-        <v>8346</v>
+        <v>8390</v>
       </c>
       <c r="F430" s="2" t="n">
         <v>14</v>
@@ -60125,7 +60125,7 @@
         <v>77</v>
       </c>
       <c r="E431" s="2" t="n">
-        <v>8362</v>
+        <v>8406</v>
       </c>
       <c r="F431" s="2" t="n">
         <v>11</v>
@@ -60149,7 +60149,7 @@
         <v>77</v>
       </c>
       <c r="E432" s="2" t="n">
-        <v>8376</v>
+        <v>8420</v>
       </c>
       <c r="F432" s="2" t="n">
         <v>13</v>
@@ -60173,7 +60173,7 @@
         <v>77</v>
       </c>
       <c r="E433" s="2" t="n">
-        <v>8392</v>
+        <v>8436</v>
       </c>
       <c r="F433" s="2" t="n">
         <v>11</v>
@@ -60197,7 +60197,7 @@
         <v>77</v>
       </c>
       <c r="E434" s="2" t="n">
-        <v>8405</v>
+        <v>8449</v>
       </c>
       <c r="F434" s="2" t="n">
         <v>11</v>
@@ -60221,7 +60221,7 @@
         <v>77</v>
       </c>
       <c r="E435" s="2" t="n">
-        <v>8418</v>
+        <v>8462</v>
       </c>
       <c r="F435" s="2" t="n">
         <v>11</v>
@@ -60245,7 +60245,7 @@
         <v>77</v>
       </c>
       <c r="E436" s="2" t="n">
-        <v>8432</v>
+        <v>8476</v>
       </c>
       <c r="F436" s="2" t="n">
         <v>11</v>
@@ -60269,7 +60269,7 @@
         <v>77</v>
       </c>
       <c r="E437" s="2" t="n">
-        <v>8445</v>
+        <v>8489</v>
       </c>
       <c r="F437" s="2" t="n">
         <v>11</v>
@@ -60293,7 +60293,7 @@
         <v>77</v>
       </c>
       <c r="E438" s="2" t="n">
-        <v>8459</v>
+        <v>8503</v>
       </c>
       <c r="F438" s="2" t="n">
         <v>12</v>
@@ -60317,7 +60317,7 @@
         <v>77</v>
       </c>
       <c r="E439" s="2" t="n">
-        <v>8474</v>
+        <v>8518</v>
       </c>
       <c r="F439" s="2" t="n">
         <v>11</v>
@@ -60341,7 +60341,7 @@
         <v>77</v>
       </c>
       <c r="E440" s="2" t="n">
-        <v>8487</v>
+        <v>8531</v>
       </c>
       <c r="F440" s="2" t="n">
         <v>20</v>
@@ -60365,7 +60365,7 @@
         <v>77</v>
       </c>
       <c r="E441" s="2" t="n">
-        <v>8510</v>
+        <v>8554</v>
       </c>
       <c r="F441" s="2" t="n">
         <v>13</v>
@@ -60389,7 +60389,7 @@
         <v>77</v>
       </c>
       <c r="E442" s="2" t="n">
-        <v>8526</v>
+        <v>8570</v>
       </c>
       <c r="F442" s="2" t="n">
         <v>12</v>
@@ -60413,7 +60413,7 @@
         <v>77</v>
       </c>
       <c r="E443" s="2" t="n">
-        <v>8541</v>
+        <v>8585</v>
       </c>
       <c r="F443" s="2" t="n">
         <v>16</v>
@@ -60437,7 +60437,7 @@
         <v>77</v>
       </c>
       <c r="E444" s="2" t="n">
-        <v>8560</v>
+        <v>8604</v>
       </c>
       <c r="F444" s="2" t="n">
         <v>10</v>
@@ -60461,7 +60461,7 @@
         <v>77</v>
       </c>
       <c r="E445" s="2" t="n">
-        <v>8572</v>
+        <v>8616</v>
       </c>
       <c r="F445" s="2" t="n">
         <v>17</v>
@@ -60485,7 +60485,7 @@
         <v>77</v>
       </c>
       <c r="E446" s="2" t="n">
-        <v>8592</v>
+        <v>8636</v>
       </c>
       <c r="F446" s="2" t="n">
         <v>13</v>
@@ -60509,7 +60509,7 @@
         <v>77</v>
       </c>
       <c r="E447" s="2" t="n">
-        <v>8608</v>
+        <v>8652</v>
       </c>
       <c r="F447" s="2" t="n">
         <v>12</v>
@@ -60533,7 +60533,7 @@
         <v>77</v>
       </c>
       <c r="E448" s="2" t="n">
-        <v>8623</v>
+        <v>8667</v>
       </c>
       <c r="F448" s="2" t="n">
         <v>12</v>
@@ -60557,7 +60557,7 @@
         <v>77</v>
       </c>
       <c r="E449" s="2" t="n">
-        <v>8637</v>
+        <v>8681</v>
       </c>
       <c r="F449" s="2" t="n">
         <v>12</v>
@@ -60581,7 +60581,7 @@
         <v>77</v>
       </c>
       <c r="E450" s="2" t="n">
-        <v>8652</v>
+        <v>8696</v>
       </c>
       <c r="F450" s="2" t="n">
         <v>10</v>
@@ -60605,7 +60605,7 @@
         <v>77</v>
       </c>
       <c r="E451" s="2" t="n">
-        <v>8665</v>
+        <v>8709</v>
       </c>
       <c r="F451" s="2" t="n">
         <v>12</v>
@@ -60629,7 +60629,7 @@
         <v>77</v>
       </c>
       <c r="E452" s="2" t="n">
-        <v>8679</v>
+        <v>8723</v>
       </c>
       <c r="F452" s="2" t="n">
         <v>13</v>
@@ -60653,7 +60653,7 @@
         <v>77</v>
       </c>
       <c r="E453" s="2" t="n">
-        <v>8695</v>
+        <v>8739</v>
       </c>
       <c r="F453" s="2" t="n">
         <v>12</v>
@@ -60677,7 +60677,7 @@
         <v>77</v>
       </c>
       <c r="E454" s="2" t="n">
-        <v>8710</v>
+        <v>8754</v>
       </c>
       <c r="F454" s="2" t="n">
         <v>8</v>
@@ -60701,7 +60701,7 @@
         <v>77</v>
       </c>
       <c r="E455" s="2" t="n">
-        <v>8720</v>
+        <v>8764</v>
       </c>
       <c r="F455" s="2" t="n">
         <v>13</v>
@@ -60725,7 +60725,7 @@
         <v>77</v>
       </c>
       <c r="E456" s="2" t="n">
-        <v>8736</v>
+        <v>8780</v>
       </c>
       <c r="F456" s="2" t="n">
         <v>13</v>
@@ -60749,7 +60749,7 @@
         <v>77</v>
       </c>
       <c r="E457" s="2" t="n">
-        <v>8752</v>
+        <v>8796</v>
       </c>
       <c r="F457" s="2" t="n">
         <v>13</v>
@@ -60773,7 +60773,7 @@
         <v>77</v>
       </c>
       <c r="E458" s="2" t="n">
-        <v>8767</v>
+        <v>8811</v>
       </c>
       <c r="F458" s="2" t="n">
         <v>10</v>
@@ -60797,7 +60797,7 @@
         <v>77</v>
       </c>
       <c r="E459" s="2" t="n">
-        <v>8779</v>
+        <v>8823</v>
       </c>
       <c r="F459" s="2" t="n">
         <v>13</v>
@@ -60821,7 +60821,7 @@
         <v>77</v>
       </c>
       <c r="E460" s="2" t="n">
-        <v>8795</v>
+        <v>8839</v>
       </c>
       <c r="F460" s="2" t="n">
         <v>6</v>
@@ -60845,7 +60845,7 @@
         <v>81</v>
       </c>
       <c r="E461" s="2" t="n">
-        <v>8803</v>
+        <v>8847</v>
       </c>
       <c r="F461" s="2" t="n">
         <v>21</v>
@@ -60869,7 +60869,7 @@
         <v>81</v>
       </c>
       <c r="E462" s="2" t="n">
-        <v>8827</v>
+        <v>8871</v>
       </c>
       <c r="F462" s="2" t="n">
         <v>16</v>
@@ -60893,7 +60893,7 @@
         <v>81</v>
       </c>
       <c r="E463" s="2" t="n">
-        <v>8846</v>
+        <v>8890</v>
       </c>
       <c r="F463" s="2" t="n">
         <v>10</v>
@@ -60917,7 +60917,7 @@
         <v>81</v>
       </c>
       <c r="E464" s="2" t="n">
-        <v>8859</v>
+        <v>8903</v>
       </c>
       <c r="F464" s="2" t="n">
         <v>16</v>
@@ -60941,7 +60941,7 @@
         <v>81</v>
       </c>
       <c r="E465" s="2" t="n">
-        <v>8878</v>
+        <v>8922</v>
       </c>
       <c r="F465" s="2" t="n">
         <v>9</v>
@@ -60965,7 +60965,7 @@
         <v>81</v>
       </c>
       <c r="E466" s="2" t="n">
-        <v>8889</v>
+        <v>8933</v>
       </c>
       <c r="F466" s="2" t="n">
         <v>14</v>
@@ -60989,7 +60989,7 @@
         <v>81</v>
       </c>
       <c r="E467" s="2" t="n">
-        <v>8906</v>
+        <v>8950</v>
       </c>
       <c r="F467" s="2" t="n">
         <v>12</v>
@@ -61013,7 +61013,7 @@
         <v>81</v>
       </c>
       <c r="E468" s="2" t="n">
-        <v>8921</v>
+        <v>8965</v>
       </c>
       <c r="F468" s="2" t="n">
         <v>13</v>
@@ -61037,7 +61037,7 @@
         <v>81</v>
       </c>
       <c r="E469" s="2" t="n">
-        <v>8937</v>
+        <v>8981</v>
       </c>
       <c r="F469" s="2" t="n">
         <v>12</v>
@@ -61061,7 +61061,7 @@
         <v>81</v>
       </c>
       <c r="E470" s="2" t="n">
-        <v>8951</v>
+        <v>8995</v>
       </c>
       <c r="F470" s="2" t="n">
         <v>12</v>
@@ -61085,7 +61085,7 @@
         <v>81</v>
       </c>
       <c r="E471" s="2" t="n">
-        <v>8965</v>
+        <v>9009</v>
       </c>
       <c r="F471" s="2" t="n">
         <v>9</v>
@@ -61109,7 +61109,7 @@
         <v>81</v>
       </c>
       <c r="E472" s="2" t="n">
-        <v>8977</v>
+        <v>9021</v>
       </c>
       <c r="F472" s="2" t="n">
         <v>22</v>
@@ -61133,7 +61133,7 @@
         <v>81</v>
       </c>
       <c r="E473" s="2" t="n">
-        <v>9002</v>
+        <v>9046</v>
       </c>
       <c r="F473" s="2" t="n">
         <v>15</v>
@@ -61157,7 +61157,7 @@
         <v>81</v>
       </c>
       <c r="E474" s="2" t="n">
-        <v>9020</v>
+        <v>9064</v>
       </c>
       <c r="F474" s="2" t="n">
         <v>12</v>
@@ -61181,7 +61181,7 @@
         <v>81</v>
       </c>
       <c r="E475" s="2" t="n">
-        <v>9035</v>
+        <v>9079</v>
       </c>
       <c r="F475" s="2" t="n">
         <v>11</v>
@@ -61205,7 +61205,7 @@
         <v>81</v>
       </c>
       <c r="E476" s="2" t="n">
-        <v>9048</v>
+        <v>9092</v>
       </c>
       <c r="F476" s="2" t="n">
         <v>13</v>
@@ -61229,7 +61229,7 @@
         <v>81</v>
       </c>
       <c r="E477" s="2" t="n">
-        <v>9064</v>
+        <v>9108</v>
       </c>
       <c r="F477" s="2" t="n">
         <v>14</v>
@@ -61253,7 +61253,7 @@
         <v>81</v>
       </c>
       <c r="E478" s="2" t="n">
-        <v>9081</v>
+        <v>9125</v>
       </c>
       <c r="F478" s="2" t="n">
         <v>19</v>
@@ -61277,7 +61277,7 @@
         <v>81</v>
       </c>
       <c r="E479" s="2" t="n">
-        <v>9103</v>
+        <v>9147</v>
       </c>
       <c r="F479" s="2" t="n">
         <v>16</v>
@@ -61301,7 +61301,7 @@
         <v>81</v>
       </c>
       <c r="E480" s="2" t="n">
-        <v>9122</v>
+        <v>9166</v>
       </c>
       <c r="F480" s="2" t="n">
         <v>16</v>
@@ -61325,7 +61325,7 @@
         <v>81</v>
       </c>
       <c r="E481" s="2" t="n">
-        <v>9141</v>
+        <v>9185</v>
       </c>
       <c r="F481" s="2" t="n">
         <v>12</v>
@@ -61349,7 +61349,7 @@
         <v>81</v>
       </c>
       <c r="E482" s="2" t="n">
-        <v>9155</v>
+        <v>9199</v>
       </c>
       <c r="F482" s="2" t="n">
         <v>14</v>
@@ -61373,7 +61373,7 @@
         <v>81</v>
       </c>
       <c r="E483" s="2" t="n">
-        <v>9172</v>
+        <v>9216</v>
       </c>
       <c r="F483" s="2" t="n">
         <v>17</v>
@@ -61397,7 +61397,7 @@
         <v>81</v>
       </c>
       <c r="E484" s="2" t="n">
-        <v>9192</v>
+        <v>9236</v>
       </c>
       <c r="F484" s="2" t="n">
         <v>18</v>
@@ -61421,7 +61421,7 @@
         <v>81</v>
       </c>
       <c r="E485" s="2" t="n">
-        <v>9213</v>
+        <v>9257</v>
       </c>
       <c r="F485" s="2" t="n">
         <v>20</v>
@@ -61445,7 +61445,7 @@
         <v>81</v>
       </c>
       <c r="E486" s="2" t="n">
-        <v>9236</v>
+        <v>9280</v>
       </c>
       <c r="F486" s="2" t="n">
         <v>23</v>
@@ -61469,7 +61469,7 @@
         <v>81</v>
       </c>
       <c r="E487" s="2" t="n">
-        <v>9262</v>
+        <v>9306</v>
       </c>
       <c r="F487" s="2" t="n">
         <v>21</v>
@@ -61493,7 +61493,7 @@
         <v>81</v>
       </c>
       <c r="E488" s="2" t="n">
-        <v>9286</v>
+        <v>9330</v>
       </c>
       <c r="F488" s="2" t="n">
         <v>19</v>
@@ -61517,7 +61517,7 @@
         <v>81</v>
       </c>
       <c r="E489" s="2" t="n">
-        <v>9308</v>
+        <v>9352</v>
       </c>
       <c r="F489" s="2" t="n">
         <v>15</v>
@@ -61541,7 +61541,7 @@
         <v>81</v>
       </c>
       <c r="E490" s="2" t="n">
-        <v>9326</v>
+        <v>9370</v>
       </c>
       <c r="F490" s="2" t="n">
         <v>20</v>
@@ -61565,7 +61565,7 @@
         <v>81</v>
       </c>
       <c r="E491" s="2" t="n">
-        <v>9349</v>
+        <v>9393</v>
       </c>
       <c r="F491" s="2" t="n">
         <v>17</v>
@@ -61589,7 +61589,7 @@
         <v>81</v>
       </c>
       <c r="E492" s="2" t="n">
-        <v>9369</v>
+        <v>9413</v>
       </c>
       <c r="F492" s="2" t="n">
         <v>19</v>
@@ -61613,7 +61613,7 @@
         <v>81</v>
       </c>
       <c r="E493" s="2" t="n">
-        <v>9390</v>
+        <v>9434</v>
       </c>
       <c r="F493" s="2" t="n">
         <v>19</v>
@@ -61637,7 +61637,7 @@
         <v>81</v>
       </c>
       <c r="E494" s="2" t="n">
-        <v>9412</v>
+        <v>9456</v>
       </c>
       <c r="F494" s="2" t="n">
         <v>10</v>
@@ -61661,7 +61661,7 @@
         <v>81</v>
       </c>
       <c r="E495" s="2" t="n">
-        <v>9424</v>
+        <v>9468</v>
       </c>
       <c r="F495" s="2" t="n">
         <v>11</v>
@@ -61685,7 +61685,7 @@
         <v>81</v>
       </c>
       <c r="E496" s="2" t="n">
-        <v>9438</v>
+        <v>9482</v>
       </c>
       <c r="F496" s="2" t="n">
         <v>12</v>
@@ -61709,7 +61709,7 @@
         <v>81</v>
       </c>
       <c r="E497" s="2" t="n">
-        <v>9452</v>
+        <v>9496</v>
       </c>
       <c r="F497" s="2" t="n">
         <v>10</v>
@@ -61733,7 +61733,7 @@
         <v>81</v>
       </c>
       <c r="E498" s="2" t="n">
-        <v>9464</v>
+        <v>9508</v>
       </c>
       <c r="F498" s="2" t="n">
         <v>12</v>
@@ -61757,7 +61757,7 @@
         <v>81</v>
       </c>
       <c r="E499" s="2" t="n">
-        <v>9479</v>
+        <v>9523</v>
       </c>
       <c r="F499" s="2" t="n">
         <v>9</v>
@@ -61781,7 +61781,7 @@
         <v>81</v>
       </c>
       <c r="E500" s="2" t="n">
-        <v>9490</v>
+        <v>9534</v>
       </c>
       <c r="F500" s="2" t="n">
         <v>12</v>
@@ -61805,7 +61805,7 @@
         <v>81</v>
       </c>
       <c r="E501" s="2" t="n">
-        <v>9505</v>
+        <v>9549</v>
       </c>
       <c r="F501" s="2" t="n">
         <v>10</v>
@@ -61829,7 +61829,7 @@
         <v>81</v>
       </c>
       <c r="E502" s="2" t="n">
-        <v>9518</v>
+        <v>9562</v>
       </c>
       <c r="F502" s="2" t="n">
         <v>9</v>
@@ -61853,7 +61853,7 @@
         <v>81</v>
       </c>
       <c r="E503" s="2" t="n">
-        <v>9529</v>
+        <v>9573</v>
       </c>
       <c r="F503" s="2" t="n">
         <v>17</v>
@@ -61877,7 +61877,7 @@
         <v>81</v>
       </c>
       <c r="E504" s="2" t="n">
-        <v>9549</v>
+        <v>9593</v>
       </c>
       <c r="F504" s="2" t="n">
         <v>13</v>
@@ -61901,7 +61901,7 @@
         <v>81</v>
       </c>
       <c r="E505" s="2" t="n">
-        <v>9565</v>
+        <v>9609</v>
       </c>
       <c r="F505" s="2" t="n">
         <v>15</v>
@@ -61925,7 +61925,7 @@
         <v>81</v>
       </c>
       <c r="E506" s="2" t="n">
-        <v>9582</v>
+        <v>9626</v>
       </c>
       <c r="F506" s="2" t="n">
         <v>22</v>
@@ -61949,7 +61949,7 @@
         <v>81</v>
       </c>
       <c r="E507" s="2" t="n">
-        <v>9606</v>
+        <v>9650</v>
       </c>
       <c r="F507" s="2" t="n">
         <v>15</v>
@@ -61973,7 +61973,7 @@
         <v>81</v>
       </c>
       <c r="E508" s="2" t="n">
-        <v>9623</v>
+        <v>9667</v>
       </c>
       <c r="F508" s="2" t="n">
         <v>17</v>
@@ -61997,7 +61997,7 @@
         <v>81</v>
       </c>
       <c r="E509" s="2" t="n">
-        <v>9643</v>
+        <v>9687</v>
       </c>
       <c r="F509" s="2" t="n">
         <v>20</v>
@@ -62021,7 +62021,7 @@
         <v>81</v>
       </c>
       <c r="E510" s="2" t="n">
-        <v>9666</v>
+        <v>9710</v>
       </c>
       <c r="F510" s="2" t="n">
         <v>13</v>
@@ -62045,7 +62045,7 @@
         <v>81</v>
       </c>
       <c r="E511" s="2" t="n">
-        <v>9682</v>
+        <v>9726</v>
       </c>
       <c r="F511" s="2" t="n">
         <v>12</v>
@@ -62069,7 +62069,7 @@
         <v>81</v>
       </c>
       <c r="E512" s="2" t="n">
-        <v>9697</v>
+        <v>9741</v>
       </c>
       <c r="F512" s="2" t="n">
         <v>11</v>
@@ -62093,7 +62093,7 @@
         <v>81</v>
       </c>
       <c r="E513" s="2" t="n">
-        <v>9710</v>
+        <v>9754</v>
       </c>
       <c r="F513" s="2" t="n">
         <v>8</v>
@@ -62117,7 +62117,7 @@
         <v>81</v>
       </c>
       <c r="E514" s="2" t="n">
-        <v>9721</v>
+        <v>9765</v>
       </c>
       <c r="F514" s="2" t="n">
         <v>23</v>
@@ -62141,7 +62141,7 @@
         <v>81</v>
       </c>
       <c r="E515" s="2" t="n">
-        <v>9747</v>
+        <v>9791</v>
       </c>
       <c r="F515" s="2" t="n">
         <v>13</v>
@@ -62165,7 +62165,7 @@
         <v>81</v>
       </c>
       <c r="E516" s="2" t="n">
-        <v>9763</v>
+        <v>9807</v>
       </c>
       <c r="F516" s="2" t="n">
         <v>7</v>
@@ -62189,7 +62189,7 @@
         <v>81</v>
       </c>
       <c r="E517" s="2" t="n">
-        <v>9772</v>
+        <v>9816</v>
       </c>
       <c r="F517" s="2" t="n">
         <v>10</v>
@@ -62213,7 +62213,7 @@
         <v>81</v>
       </c>
       <c r="E518" s="2" t="n">
-        <v>9785</v>
+        <v>9829</v>
       </c>
       <c r="F518" s="2" t="n">
         <v>10</v>
@@ -62237,7 +62237,7 @@
         <v>81</v>
       </c>
       <c r="E519" s="2" t="n">
-        <v>9798</v>
+        <v>9842</v>
       </c>
       <c r="F519" s="2" t="n">
         <v>10</v>
@@ -62261,7 +62261,7 @@
         <v>81</v>
       </c>
       <c r="E520" s="2" t="n">
-        <v>9810</v>
+        <v>9854</v>
       </c>
       <c r="F520" s="2" t="n">
         <v>7</v>
@@ -62285,7 +62285,7 @@
         <v>81</v>
       </c>
       <c r="E521" s="2" t="n">
-        <v>9820</v>
+        <v>9864</v>
       </c>
       <c r="F521" s="2" t="n">
         <v>17</v>
@@ -62309,7 +62309,7 @@
         <v>81</v>
       </c>
       <c r="E522" s="2" t="n">
-        <v>9839</v>
+        <v>9883</v>
       </c>
       <c r="F522" s="2" t="n">
         <v>15</v>
@@ -62333,7 +62333,7 @@
         <v>81</v>
       </c>
       <c r="E523" s="2" t="n">
-        <v>9856</v>
+        <v>9900</v>
       </c>
       <c r="F523" s="2" t="n">
         <v>14</v>
@@ -62357,7 +62357,7 @@
         <v>81</v>
       </c>
       <c r="E524" s="2" t="n">
-        <v>9873</v>
+        <v>9917</v>
       </c>
       <c r="F524" s="2" t="n">
         <v>21</v>
@@ -62381,7 +62381,7 @@
         <v>81</v>
       </c>
       <c r="E525" s="2" t="n">
-        <v>9897</v>
+        <v>9941</v>
       </c>
       <c r="F525" s="2" t="n">
         <v>13</v>
@@ -62405,7 +62405,7 @@
         <v>81</v>
       </c>
       <c r="E526" s="2" t="n">
-        <v>9913</v>
+        <v>9957</v>
       </c>
       <c r="F526" s="2" t="n">
         <v>16</v>
@@ -62429,7 +62429,7 @@
         <v>81</v>
       </c>
       <c r="E527" s="2" t="n">
-        <v>9932</v>
+        <v>9976</v>
       </c>
       <c r="F527" s="2" t="n">
         <v>15</v>
@@ -62453,7 +62453,7 @@
         <v>81</v>
       </c>
       <c r="E528" s="2" t="n">
-        <v>9950</v>
+        <v>9994</v>
       </c>
       <c r="F528" s="2" t="n">
         <v>17</v>
@@ -62477,7 +62477,7 @@
         <v>81</v>
       </c>
       <c r="E529" s="2" t="n">
-        <v>9970</v>
+        <v>10014</v>
       </c>
       <c r="F529" s="2" t="n">
         <v>18</v>
@@ -62501,7 +62501,7 @@
         <v>81</v>
       </c>
       <c r="E530" s="2" t="n">
-        <v>9990</v>
+        <v>10034</v>
       </c>
       <c r="F530" s="2" t="n">
         <v>16</v>
@@ -62525,7 +62525,7 @@
         <v>81</v>
       </c>
       <c r="E531" s="2" t="n">
-        <v>10009</v>
+        <v>10053</v>
       </c>
       <c r="F531" s="2" t="n">
         <v>17</v>
@@ -62549,7 +62549,7 @@
         <v>81</v>
       </c>
       <c r="E532" s="2" t="n">
-        <v>10029</v>
+        <v>10073</v>
       </c>
       <c r="F532" s="2" t="n">
         <v>11</v>
@@ -62573,7 +62573,7 @@
         <v>81</v>
       </c>
       <c r="E533" s="2" t="n">
-        <v>10043</v>
+        <v>10087</v>
       </c>
       <c r="F533" s="2" t="n">
         <v>13</v>
@@ -62597,7 +62597,7 @@
         <v>81</v>
       </c>
       <c r="E534" s="2" t="n">
-        <v>10059</v>
+        <v>10103</v>
       </c>
       <c r="F534" s="2" t="n">
         <v>16</v>
@@ -62621,7 +62621,7 @@
         <v>81</v>
       </c>
       <c r="E535" s="2" t="n">
-        <v>10078</v>
+        <v>10122</v>
       </c>
       <c r="F535" s="2" t="n">
         <v>20</v>
@@ -62645,7 +62645,7 @@
         <v>81</v>
       </c>
       <c r="E536" s="2" t="n">
-        <v>10101</v>
+        <v>10145</v>
       </c>
       <c r="F536" s="2" t="n">
         <v>10</v>
@@ -62669,7 +62669,7 @@
         <v>81</v>
       </c>
       <c r="E537" s="2" t="n">
-        <v>10113</v>
+        <v>10157</v>
       </c>
       <c r="F537" s="2" t="n">
         <v>15</v>
@@ -62693,7 +62693,7 @@
         <v>81</v>
       </c>
       <c r="E538" s="2" t="n">
-        <v>10131</v>
+        <v>10175</v>
       </c>
       <c r="F538" s="2" t="n">
         <v>15</v>
@@ -62717,7 +62717,7 @@
         <v>81</v>
       </c>
       <c r="E539" s="2" t="n">
-        <v>10149</v>
+        <v>10193</v>
       </c>
       <c r="F539" s="2" t="n">
         <v>15</v>
@@ -62741,7 +62741,7 @@
         <v>81</v>
       </c>
       <c r="E540" s="2" t="n">
-        <v>10167</v>
+        <v>10211</v>
       </c>
       <c r="F540" s="2" t="n">
         <v>14</v>
@@ -62765,7 +62765,7 @@
         <v>81</v>
       </c>
       <c r="E541" s="2" t="n">
-        <v>10184</v>
+        <v>10228</v>
       </c>
       <c r="F541" s="2" t="n">
         <v>14</v>
@@ -62789,7 +62789,7 @@
         <v>81</v>
       </c>
       <c r="E542" s="2" t="n">
-        <v>10201</v>
+        <v>10245</v>
       </c>
       <c r="F542" s="2" t="n">
         <v>17</v>
@@ -62813,7 +62813,7 @@
         <v>81</v>
       </c>
       <c r="E543" s="2" t="n">
-        <v>10221</v>
+        <v>10265</v>
       </c>
       <c r="F543" s="2" t="n">
         <v>15</v>
@@ -62837,7 +62837,7 @@
         <v>81</v>
       </c>
       <c r="E544" s="2" t="n">
-        <v>10238</v>
+        <v>10282</v>
       </c>
       <c r="F544" s="2" t="n">
         <v>20</v>
@@ -62861,7 +62861,7 @@
         <v>81</v>
       </c>
       <c r="E545" s="2" t="n">
-        <v>10263</v>
+        <v>10307</v>
       </c>
       <c r="F545" s="2" t="n">
         <v>13</v>
@@ -62885,7 +62885,7 @@
         <v>81</v>
       </c>
       <c r="E546" s="2" t="n">
-        <v>10279</v>
+        <v>10323</v>
       </c>
       <c r="F546" s="2" t="n">
         <v>15</v>
@@ -62909,7 +62909,7 @@
         <v>81</v>
       </c>
       <c r="E547" s="2" t="n">
-        <v>10297</v>
+        <v>10341</v>
       </c>
       <c r="F547" s="2" t="n">
         <v>16</v>
@@ -62933,7 +62933,7 @@
         <v>81</v>
       </c>
       <c r="E548" s="2" t="n">
-        <v>10316</v>
+        <v>10360</v>
       </c>
       <c r="F548" s="2" t="n">
         <v>4</v>
@@ -62957,7 +62957,7 @@
         <v>94</v>
       </c>
       <c r="E549" s="2" t="n">
-        <v>10322</v>
+        <v>10366</v>
       </c>
       <c r="F549" s="2" t="n">
         <v>14</v>
@@ -62981,7 +62981,7 @@
         <v>94</v>
       </c>
       <c r="E550" s="2" t="n">
-        <v>10339</v>
+        <v>10383</v>
       </c>
       <c r="F550" s="2" t="n">
         <v>16</v>
@@ -63005,7 +63005,7 @@
         <v>94</v>
       </c>
       <c r="E551" s="2" t="n">
-        <v>10358</v>
+        <v>10402</v>
       </c>
       <c r="F551" s="2" t="n">
         <v>14</v>
@@ -63029,7 +63029,7 @@
         <v>94</v>
       </c>
       <c r="E552" s="2" t="n">
-        <v>10375</v>
+        <v>10419</v>
       </c>
       <c r="F552" s="2" t="n">
         <v>15</v>
@@ -63053,7 +63053,7 @@
         <v>94</v>
       </c>
       <c r="E553" s="2" t="n">
-        <v>10392</v>
+        <v>10436</v>
       </c>
       <c r="F553" s="2" t="n">
         <v>15</v>
@@ -63077,7 +63077,7 @@
         <v>94</v>
       </c>
       <c r="E554" s="2" t="n">
-        <v>10409</v>
+        <v>10453</v>
       </c>
       <c r="F554" s="2" t="n">
         <v>11</v>
@@ -63101,7 +63101,7 @@
         <v>94</v>
       </c>
       <c r="E555" s="2" t="n">
-        <v>10423</v>
+        <v>10467</v>
       </c>
       <c r="F555" s="2" t="n">
         <v>15</v>
@@ -63125,7 +63125,7 @@
         <v>94</v>
       </c>
       <c r="E556" s="2" t="n">
-        <v>10441</v>
+        <v>10485</v>
       </c>
       <c r="F556" s="2" t="n">
         <v>14</v>
@@ -63149,7 +63149,7 @@
         <v>94</v>
       </c>
       <c r="E557" s="2" t="n">
-        <v>10457</v>
+        <v>10501</v>
       </c>
       <c r="F557" s="2" t="n">
         <v>15</v>
@@ -63173,7 +63173,7 @@
         <v>94</v>
       </c>
       <c r="E558" s="2" t="n">
-        <v>10474</v>
+        <v>10518</v>
       </c>
       <c r="F558" s="2" t="n">
         <v>14</v>
@@ -63197,7 +63197,7 @@
         <v>94</v>
       </c>
       <c r="E559" s="2" t="n">
-        <v>10491</v>
+        <v>10535</v>
       </c>
       <c r="F559" s="2" t="n">
         <v>14</v>
@@ -63221,7 +63221,7 @@
         <v>94</v>
       </c>
       <c r="E560" s="2" t="n">
-        <v>10508</v>
+        <v>10552</v>
       </c>
       <c r="F560" s="2" t="n">
         <v>14</v>
@@ -63245,7 +63245,7 @@
         <v>94</v>
       </c>
       <c r="E561" s="2" t="n">
-        <v>10525</v>
+        <v>10569</v>
       </c>
       <c r="F561" s="2" t="n">
         <v>13</v>
@@ -63269,7 +63269,7 @@
         <v>94</v>
       </c>
       <c r="E562" s="2" t="n">
-        <v>10541</v>
+        <v>10585</v>
       </c>
       <c r="F562" s="2" t="n">
         <v>15</v>
@@ -63293,7 +63293,7 @@
         <v>94</v>
       </c>
       <c r="E563" s="2" t="n">
-        <v>10559</v>
+        <v>10603</v>
       </c>
       <c r="F563" s="2" t="n">
         <v>14</v>
@@ -63317,7 +63317,7 @@
         <v>94</v>
       </c>
       <c r="E564" s="2" t="n">
-        <v>10575</v>
+        <v>10619</v>
       </c>
       <c r="F564" s="2" t="n">
         <v>14</v>
@@ -63341,7 +63341,7 @@
         <v>94</v>
       </c>
       <c r="E565" s="2" t="n">
-        <v>10592</v>
+        <v>10636</v>
       </c>
       <c r="F565" s="2" t="n">
         <v>14</v>
@@ -63365,7 +63365,7 @@
         <v>94</v>
       </c>
       <c r="E566" s="2" t="n">
-        <v>10609</v>
+        <v>10653</v>
       </c>
       <c r="F566" s="2" t="n">
         <v>13</v>
@@ -63389,7 +63389,7 @@
         <v>94</v>
       </c>
       <c r="E567" s="2" t="n">
-        <v>10624</v>
+        <v>10668</v>
       </c>
       <c r="F567" s="2" t="n">
         <v>10</v>
@@ -63413,7 +63413,7 @@
         <v>94</v>
       </c>
       <c r="E568" s="2" t="n">
-        <v>10636</v>
+        <v>10680</v>
       </c>
       <c r="F568" s="2" t="n">
         <v>10</v>
@@ -63437,7 +63437,7 @@
         <v>94</v>
       </c>
       <c r="E569" s="2" t="n">
-        <v>10649</v>
+        <v>10693</v>
       </c>
       <c r="F569" s="2" t="n">
         <v>11</v>
@@ -63461,7 +63461,7 @@
         <v>94</v>
       </c>
       <c r="E570" s="2" t="n">
-        <v>10663</v>
+        <v>10707</v>
       </c>
       <c r="F570" s="2" t="n">
         <v>10</v>
@@ -63485,7 +63485,7 @@
         <v>94</v>
       </c>
       <c r="E571" s="2" t="n">
-        <v>10675</v>
+        <v>10719</v>
       </c>
       <c r="F571" s="2" t="n">
         <v>10</v>
@@ -63509,7 +63509,7 @@
         <v>94</v>
       </c>
       <c r="E572" s="2" t="n">
-        <v>10688</v>
+        <v>10732</v>
       </c>
       <c r="F572" s="2" t="n">
         <v>11</v>
@@ -63533,7 +63533,7 @@
         <v>94</v>
       </c>
       <c r="E573" s="2" t="n">
-        <v>10702</v>
+        <v>10746</v>
       </c>
       <c r="F573" s="2" t="n">
         <v>8</v>
@@ -63557,7 +63557,7 @@
         <v>94</v>
       </c>
       <c r="E574" s="2" t="n">
-        <v>10712</v>
+        <v>10756</v>
       </c>
       <c r="F574" s="2" t="n">
         <v>11</v>
@@ -63581,7 +63581,7 @@
         <v>94</v>
       </c>
       <c r="E575" s="2" t="n">
-        <v>10726</v>
+        <v>10770</v>
       </c>
       <c r="F575" s="2" t="n">
         <v>8</v>
@@ -63605,7 +63605,7 @@
         <v>94</v>
       </c>
       <c r="E576" s="2" t="n">
-        <v>10736</v>
+        <v>10780</v>
       </c>
       <c r="F576" s="2" t="n">
         <v>12</v>
@@ -63629,7 +63629,7 @@
         <v>94</v>
       </c>
       <c r="E577" s="2" t="n">
-        <v>10751</v>
+        <v>10795</v>
       </c>
       <c r="F577" s="2" t="n">
         <v>15</v>
@@ -63653,7 +63653,7 @@
         <v>94</v>
       </c>
       <c r="E578" s="2" t="n">
-        <v>10769</v>
+        <v>10813</v>
       </c>
       <c r="F578" s="2" t="n">
         <v>13</v>
@@ -63677,7 +63677,7 @@
         <v>94</v>
       </c>
       <c r="E579" s="2" t="n">
-        <v>10785</v>
+        <v>10829</v>
       </c>
       <c r="F579" s="2" t="n">
         <v>14</v>
@@ -63701,7 +63701,7 @@
         <v>94</v>
       </c>
       <c r="E580" s="2" t="n">
-        <v>10802</v>
+        <v>10846</v>
       </c>
       <c r="F580" s="2" t="n">
         <v>12</v>
@@ -63725,7 +63725,7 @@
         <v>94</v>
       </c>
       <c r="E581" s="2" t="n">
-        <v>10817</v>
+        <v>10861</v>
       </c>
       <c r="F581" s="2" t="n">
         <v>13</v>
@@ -63749,7 +63749,7 @@
         <v>94</v>
       </c>
       <c r="E582" s="2" t="n">
-        <v>10832</v>
+        <v>10876</v>
       </c>
       <c r="F582" s="2" t="n">
         <v>12</v>
@@ -63773,7 +63773,7 @@
         <v>94</v>
       </c>
       <c r="E583" s="2" t="n">
-        <v>10846</v>
+        <v>10890</v>
       </c>
       <c r="F583" s="2" t="n">
         <v>9</v>
@@ -63797,7 +63797,7 @@
         <v>94</v>
       </c>
       <c r="E584" s="2" t="n">
-        <v>10858</v>
+        <v>10902</v>
       </c>
       <c r="F584" s="2" t="n">
         <v>8</v>
@@ -63821,7 +63821,7 @@
         <v>94</v>
       </c>
       <c r="E585" s="2" t="n">
-        <v>10868</v>
+        <v>10912</v>
       </c>
       <c r="F585" s="2" t="n">
         <v>7</v>
@@ -63845,7 +63845,7 @@
         <v>94</v>
       </c>
       <c r="E586" s="2" t="n">
-        <v>10877</v>
+        <v>10921</v>
       </c>
       <c r="F586" s="2" t="n">
         <v>12</v>
@@ -63869,7 +63869,7 @@
         <v>94</v>
       </c>
       <c r="E587" s="2" t="n">
-        <v>10891</v>
+        <v>10935</v>
       </c>
       <c r="F587" s="2" t="n">
         <v>10</v>
@@ -63893,7 +63893,7 @@
         <v>94</v>
       </c>
       <c r="E588" s="2" t="n">
-        <v>10904</v>
+        <v>10948</v>
       </c>
       <c r="F588" s="2" t="n">
         <v>11</v>
@@ -63917,7 +63917,7 @@
         <v>94</v>
       </c>
       <c r="E589" s="2" t="n">
-        <v>10918</v>
+        <v>10962</v>
       </c>
       <c r="F589" s="2" t="n">
         <v>10</v>
@@ -63941,7 +63941,7 @@
         <v>94</v>
       </c>
       <c r="E590" s="2" t="n">
-        <v>10930</v>
+        <v>10974</v>
       </c>
       <c r="F590" s="2" t="n">
         <v>11</v>
@@ -63965,7 +63965,7 @@
         <v>94</v>
       </c>
       <c r="E591" s="2" t="n">
-        <v>10944</v>
+        <v>10988</v>
       </c>
       <c r="F591" s="2" t="n">
         <v>10</v>
@@ -63989,7 +63989,7 @@
         <v>94</v>
       </c>
       <c r="E592" s="2" t="n">
-        <v>10957</v>
+        <v>11001</v>
       </c>
       <c r="F592" s="2" t="n">
         <v>8</v>
@@ -64013,7 +64013,7 @@
         <v>94</v>
       </c>
       <c r="E593" s="2" t="n">
-        <v>10967</v>
+        <v>11011</v>
       </c>
       <c r="F593" s="2" t="n">
         <v>11</v>
@@ -64037,7 +64037,7 @@
         <v>94</v>
       </c>
       <c r="E594" s="2" t="n">
-        <v>10981</v>
+        <v>11025</v>
       </c>
       <c r="F594" s="2" t="n">
         <v>11</v>
@@ -64061,7 +64061,7 @@
         <v>94</v>
       </c>
       <c r="E595" s="2" t="n">
-        <v>10995</v>
+        <v>11039</v>
       </c>
       <c r="F595" s="2" t="n">
         <v>9</v>
@@ -64085,7 +64085,7 @@
         <v>94</v>
       </c>
       <c r="E596" s="2" t="n">
-        <v>11006</v>
+        <v>11050</v>
       </c>
       <c r="F596" s="2" t="n">
         <v>11</v>
@@ -64109,7 +64109,7 @@
         <v>94</v>
       </c>
       <c r="E597" s="2" t="n">
-        <v>11020</v>
+        <v>11064</v>
       </c>
       <c r="F597" s="2" t="n">
         <v>13</v>
@@ -64133,7 +64133,7 @@
         <v>94</v>
       </c>
       <c r="E598" s="2" t="n">
-        <v>11036</v>
+        <v>11080</v>
       </c>
       <c r="F598" s="2" t="n">
         <v>10</v>
@@ -64157,7 +64157,7 @@
         <v>94</v>
       </c>
       <c r="E599" s="2" t="n">
-        <v>11048</v>
+        <v>11092</v>
       </c>
       <c r="F599" s="2" t="n">
         <v>12</v>
@@ -64181,7 +64181,7 @@
         <v>94</v>
       </c>
       <c r="E600" s="2" t="n">
-        <v>11063</v>
+        <v>11107</v>
       </c>
       <c r="F600" s="2" t="n">
         <v>10</v>
@@ -64205,7 +64205,7 @@
         <v>94</v>
       </c>
       <c r="E601" s="2" t="n">
-        <v>11076</v>
+        <v>11120</v>
       </c>
       <c r="F601" s="2" t="n">
         <v>10</v>
@@ -64229,7 +64229,7 @@
         <v>94</v>
       </c>
       <c r="E602" s="2" t="n">
-        <v>11088</v>
+        <v>11132</v>
       </c>
       <c r="F602" s="2" t="n">
         <v>10</v>
@@ -64253,7 +64253,7 @@
         <v>94</v>
       </c>
       <c r="E603" s="2" t="n">
-        <v>11101</v>
+        <v>11145</v>
       </c>
       <c r="F603" s="2" t="n">
         <v>10</v>
@@ -64277,7 +64277,7 @@
         <v>94</v>
       </c>
       <c r="E604" s="2" t="n">
-        <v>11114</v>
+        <v>11158</v>
       </c>
       <c r="F604" s="2" t="n">
         <v>8</v>
@@ -64301,7 +64301,7 @@
         <v>94</v>
       </c>
       <c r="E605" s="2" t="n">
-        <v>11124</v>
+        <v>11168</v>
       </c>
       <c r="F605" s="2" t="n">
         <v>11</v>
@@ -64325,7 +64325,7 @@
         <v>94</v>
       </c>
       <c r="E606" s="2" t="n">
-        <v>11138</v>
+        <v>11182</v>
       </c>
       <c r="F606" s="2" t="n">
         <v>8</v>
@@ -64349,7 +64349,7 @@
         <v>94</v>
       </c>
       <c r="E607" s="2" t="n">
-        <v>11148</v>
+        <v>11192</v>
       </c>
       <c r="F607" s="2" t="n">
         <v>10</v>
@@ -64373,7 +64373,7 @@
         <v>94</v>
       </c>
       <c r="E608" s="2" t="n">
-        <v>11160</v>
+        <v>11204</v>
       </c>
       <c r="F608" s="2" t="n">
         <v>11</v>
@@ -64397,7 +64397,7 @@
         <v>94</v>
       </c>
       <c r="E609" s="2" t="n">
-        <v>11174</v>
+        <v>11218</v>
       </c>
       <c r="F609" s="2" t="n">
         <v>7</v>
@@ -64421,7 +64421,7 @@
         <v>94</v>
       </c>
       <c r="E610" s="2" t="n">
-        <v>11183</v>
+        <v>11227</v>
       </c>
       <c r="F610" s="2" t="n">
         <v>6</v>
@@ -64445,7 +64445,7 @@
         <v>94</v>
       </c>
       <c r="E611" s="2" t="n">
-        <v>11192</v>
+        <v>11236</v>
       </c>
       <c r="F611" s="2" t="n">
         <v>4</v>
@@ -64469,7 +64469,7 @@
         <v>94</v>
       </c>
       <c r="E612" s="2" t="n">
-        <v>11198</v>
+        <v>11242</v>
       </c>
       <c r="F612" s="2" t="n">
         <v>5</v>
@@ -64493,7 +64493,7 @@
         <v>94</v>
       </c>
       <c r="E613" s="2" t="n">
-        <v>11205</v>
+        <v>11249</v>
       </c>
       <c r="F613" s="2" t="n">
         <v>1</v>
@@ -64517,7 +64517,7 @@
         <v>94</v>
       </c>
       <c r="E614" s="2" t="n">
-        <v>11208</v>
+        <v>11252</v>
       </c>
       <c r="F614" s="2" t="n">
         <v>8</v>
@@ -64541,7 +64541,7 @@
         <v>94</v>
       </c>
       <c r="E615" s="2" t="n">
-        <v>11219</v>
+        <v>11263</v>
       </c>
       <c r="F615" s="2" t="n">
         <v>9</v>
@@ -64565,7 +64565,7 @@
         <v>94</v>
       </c>
       <c r="E616" s="2" t="n">
-        <v>11231</v>
+        <v>11275</v>
       </c>
       <c r="F616" s="2" t="n">
         <v>8</v>
@@ -64589,7 +64589,7 @@
         <v>94</v>
       </c>
       <c r="E617" s="2" t="n">
-        <v>11241</v>
+        <v>11285</v>
       </c>
       <c r="F617" s="2" t="n">
         <v>8</v>
@@ -64613,7 +64613,7 @@
         <v>94</v>
       </c>
       <c r="E618" s="2" t="n">
-        <v>11252</v>
+        <v>11296</v>
       </c>
       <c r="F618" s="2" t="n">
         <v>8</v>
@@ -64637,7 +64637,7 @@
         <v>94</v>
       </c>
       <c r="E619" s="2" t="n">
-        <v>11262</v>
+        <v>11306</v>
       </c>
       <c r="F619" s="2" t="n">
         <v>8</v>
@@ -64661,7 +64661,7 @@
         <v>94</v>
       </c>
       <c r="E620" s="2" t="n">
-        <v>11273</v>
+        <v>11317</v>
       </c>
       <c r="F620" s="2" t="n">
         <v>8</v>
@@ -64685,7 +64685,7 @@
         <v>94</v>
       </c>
       <c r="E621" s="2" t="n">
-        <v>11283</v>
+        <v>11327</v>
       </c>
       <c r="F621" s="2" t="n">
         <v>9</v>
@@ -64709,7 +64709,7 @@
         <v>94</v>
       </c>
       <c r="E622" s="2" t="n">
-        <v>11295</v>
+        <v>11339</v>
       </c>
       <c r="F622" s="2" t="n">
         <v>8</v>
@@ -64733,7 +64733,7 @@
         <v>94</v>
       </c>
       <c r="E623" s="2" t="n">
-        <v>11305</v>
+        <v>11349</v>
       </c>
       <c r="F623" s="2" t="n">
         <v>8</v>
@@ -64757,7 +64757,7 @@
         <v>94</v>
       </c>
       <c r="E624" s="2" t="n">
-        <v>11316</v>
+        <v>11360</v>
       </c>
       <c r="F624" s="2" t="n">
         <v>8</v>
@@ -64781,7 +64781,7 @@
         <v>94</v>
       </c>
       <c r="E625" s="2" t="n">
-        <v>11327</v>
+        <v>11371</v>
       </c>
       <c r="F625" s="2" t="n">
         <v>8</v>
@@ -64805,7 +64805,7 @@
         <v>94</v>
       </c>
       <c r="E626" s="2" t="n">
-        <v>11337</v>
+        <v>11381</v>
       </c>
       <c r="F626" s="2" t="n">
         <v>8</v>
@@ -64829,7 +64829,7 @@
         <v>94</v>
       </c>
       <c r="E627" s="2" t="n">
-        <v>11348</v>
+        <v>11392</v>
       </c>
       <c r="F627" s="2" t="n">
         <v>8</v>
@@ -64853,7 +64853,7 @@
         <v>94</v>
       </c>
       <c r="E628" s="2" t="n">
-        <v>11358</v>
+        <v>11402</v>
       </c>
       <c r="F628" s="2" t="n">
         <v>8</v>
@@ -64877,7 +64877,7 @@
         <v>94</v>
       </c>
       <c r="E629" s="2" t="n">
-        <v>11369</v>
+        <v>11413</v>
       </c>
       <c r="F629" s="2" t="n">
         <v>6</v>
@@ -64901,7 +64901,7 @@
         <v>94</v>
       </c>
       <c r="E630" s="2" t="n">
-        <v>11377</v>
+        <v>11421</v>
       </c>
       <c r="F630" s="2" t="n">
         <v>2</v>
@@ -64925,7 +64925,7 @@
         <v>94</v>
       </c>
       <c r="E631" s="2" t="n">
-        <v>11381</v>
+        <v>11425</v>
       </c>
       <c r="F631" s="2" t="n">
         <v>8</v>
@@ -64949,7 +64949,7 @@
         <v>94</v>
       </c>
       <c r="E632" s="2" t="n">
-        <v>11392</v>
+        <v>11436</v>
       </c>
       <c r="F632" s="2" t="n">
         <v>1</v>
@@ -64973,7 +64973,7 @@
         <v>94</v>
       </c>
       <c r="E633" s="2" t="n">
-        <v>11395</v>
+        <v>11439</v>
       </c>
       <c r="F633" s="2" t="n">
         <v>4</v>
@@ -64997,7 +64997,7 @@
         <v>94</v>
       </c>
       <c r="E634" s="2" t="n">
-        <v>11401</v>
+        <v>11445</v>
       </c>
       <c r="F634" s="2" t="n">
         <v>1</v>
@@ -65021,7 +65021,7 @@
         <v>94</v>
       </c>
       <c r="E635" s="2" t="n">
-        <v>11404</v>
+        <v>11448</v>
       </c>
       <c r="F635" s="2" t="n">
         <v>1</v>
@@ -65045,7 +65045,7 @@
         <v>94</v>
       </c>
       <c r="E636" s="2" t="n">
-        <v>11408</v>
+        <v>11452</v>
       </c>
       <c r="F636" s="2" t="n">
         <v>1</v>
@@ -65069,7 +65069,7 @@
         <v>94</v>
       </c>
       <c r="E637" s="2" t="n">
-        <v>11411</v>
+        <v>11455</v>
       </c>
       <c r="F637" s="2" t="n">
         <v>1</v>
@@ -65093,7 +65093,7 @@
         <v>94</v>
       </c>
       <c r="E638" s="2" t="n">
-        <v>11414</v>
+        <v>11458</v>
       </c>
       <c r="F638" s="2" t="n">
         <v>10</v>
@@ -65117,7 +65117,7 @@
         <v>94</v>
       </c>
       <c r="E639" s="2" t="n">
-        <v>11426</v>
+        <v>11470</v>
       </c>
       <c r="F639" s="2" t="n">
         <v>8</v>
@@ -65141,7 +65141,7 @@
         <v>94</v>
       </c>
       <c r="E640" s="2" t="n">
-        <v>11436</v>
+        <v>11480</v>
       </c>
       <c r="F640" s="2" t="n">
         <v>11</v>
@@ -65165,7 +65165,7 @@
         <v>94</v>
       </c>
       <c r="E641" s="2" t="n">
-        <v>11450</v>
+        <v>11494</v>
       </c>
       <c r="F641" s="2" t="n">
         <v>6</v>
@@ -65189,7 +65189,7 @@
         <v>94</v>
       </c>
       <c r="E642" s="2" t="n">
-        <v>11458</v>
+        <v>11502</v>
       </c>
       <c r="F642" s="2" t="n">
         <v>8</v>
@@ -65213,7 +65213,7 @@
         <v>94</v>
       </c>
       <c r="E643" s="2" t="n">
-        <v>11469</v>
+        <v>11513</v>
       </c>
       <c r="F643" s="2" t="n">
         <v>5</v>
@@ -65237,7 +65237,7 @@
         <v>94</v>
       </c>
       <c r="E644" s="2" t="n">
-        <v>11476</v>
+        <v>11520</v>
       </c>
       <c r="F644" s="2" t="n">
         <v>4</v>
@@ -65261,7 +65261,7 @@
         <v>94</v>
       </c>
       <c r="E645" s="2" t="n">
-        <v>11482</v>
+        <v>11526</v>
       </c>
       <c r="F645" s="2" t="n">
         <v>1</v>
@@ -65285,7 +65285,7 @@
         <v>94</v>
       </c>
       <c r="E646" s="2" t="n">
-        <v>11485</v>
+        <v>11529</v>
       </c>
       <c r="F646" s="2" t="n">
         <v>8</v>
@@ -65309,7 +65309,7 @@
         <v>94</v>
       </c>
       <c r="E647" s="2" t="n">
-        <v>11495</v>
+        <v>11539</v>
       </c>
       <c r="F647" s="2" t="n">
         <v>8</v>
@@ -65333,7 +65333,7 @@
         <v>94</v>
       </c>
       <c r="E648" s="2" t="n">
-        <v>11506</v>
+        <v>11550</v>
       </c>
       <c r="F648" s="2" t="n">
         <v>8</v>
@@ -65357,7 +65357,7 @@
         <v>94</v>
       </c>
       <c r="E649" s="2" t="n">
-        <v>11516</v>
+        <v>11560</v>
       </c>
       <c r="F649" s="2" t="n">
         <v>7</v>
@@ -65381,7 +65381,7 @@
         <v>94</v>
       </c>
       <c r="E650" s="2" t="n">
-        <v>11526</v>
+        <v>11570</v>
       </c>
       <c r="F650" s="2" t="n">
         <v>8</v>
@@ -65405,7 +65405,7 @@
         <v>94</v>
       </c>
       <c r="E651" s="2" t="n">
-        <v>11536</v>
+        <v>11580</v>
       </c>
       <c r="F651" s="2" t="n">
         <v>8</v>
@@ -65429,7 +65429,7 @@
         <v>94</v>
       </c>
       <c r="E652" s="2" t="n">
-        <v>11547</v>
+        <v>11591</v>
       </c>
       <c r="F652" s="2" t="n">
         <v>4</v>
@@ -65453,7 +65453,7 @@
         <v>94</v>
       </c>
       <c r="E653" s="2" t="n">
-        <v>11553</v>
+        <v>11597</v>
       </c>
       <c r="F653" s="2" t="n">
         <v>32</v>
@@ -65477,7 +65477,7 @@
         <v>94</v>
       </c>
       <c r="E654" s="2" t="n">
-        <v>11589</v>
+        <v>11633</v>
       </c>
       <c r="F654" s="2" t="n">
         <v>20</v>
@@ -65501,7 +65501,7 @@
         <v>94</v>
       </c>
       <c r="E655" s="2" t="n">
-        <v>11612</v>
+        <v>11656</v>
       </c>
       <c r="F655" s="2" t="n">
         <v>59</v>
@@ -65525,7 +65525,7 @@
         <v>94</v>
       </c>
       <c r="E656" s="2" t="n">
-        <v>11676</v>
+        <v>11720</v>
       </c>
       <c r="F656" s="2" t="n">
         <v>61</v>
@@ -65549,7 +65549,7 @@
         <v>94</v>
       </c>
       <c r="E657" s="2" t="n">
-        <v>11743</v>
+        <v>11787</v>
       </c>
       <c r="F657" s="2" t="n">
         <v>18</v>
@@ -65573,7 +65573,7 @@
         <v>94</v>
       </c>
       <c r="E658" s="2" t="n">
-        <v>11764</v>
+        <v>11808</v>
       </c>
       <c r="F658" s="2" t="n">
         <v>40</v>
@@ -65597,7 +65597,7 @@
         <v>94</v>
       </c>
       <c r="E659" s="2" t="n">
-        <v>11808</v>
+        <v>11852</v>
       </c>
       <c r="F659" s="2" t="n">
         <v>47</v>
@@ -65621,7 +65621,7 @@
         <v>94</v>
       </c>
       <c r="E660" s="2" t="n">
-        <v>11860</v>
+        <v>11904</v>
       </c>
       <c r="F660" s="2" t="n">
         <v>40</v>
@@ -65645,7 +65645,7 @@
         <v>94</v>
       </c>
       <c r="E661" s="2" t="n">
-        <v>11904</v>
+        <v>11948</v>
       </c>
       <c r="F661" s="2" t="n">
         <v>14</v>
@@ -65669,7 +65669,7 @@
         <v>94</v>
       </c>
       <c r="E662" s="2" t="n">
-        <v>11920</v>
+        <v>11964</v>
       </c>
       <c r="F662" s="2" t="n">
         <v>12</v>
@@ -65693,7 +65693,7 @@
         <v>94</v>
       </c>
       <c r="E663" s="2" t="n">
-        <v>11935</v>
+        <v>11979</v>
       </c>
       <c r="F663" s="2" t="n">
         <v>12</v>
@@ -65717,7 +65717,7 @@
         <v>94</v>
       </c>
       <c r="E664" s="2" t="n">
-        <v>11950</v>
+        <v>11994</v>
       </c>
       <c r="F664" s="2" t="n">
         <v>12</v>
@@ -65741,7 +65741,7 @@
         <v>94</v>
       </c>
       <c r="E665" s="2" t="n">
-        <v>11965</v>
+        <v>12009</v>
       </c>
       <c r="F665" s="2" t="n">
         <v>12</v>
@@ -65765,7 +65765,7 @@
         <v>94</v>
       </c>
       <c r="E666" s="2" t="n">
-        <v>11979</v>
+        <v>12023</v>
       </c>
       <c r="F666" s="2" t="n">
         <v>12</v>
@@ -65789,7 +65789,7 @@
         <v>94</v>
       </c>
       <c r="E667" s="2" t="n">
-        <v>11993</v>
+        <v>12037</v>
       </c>
       <c r="F667" s="2" t="n">
         <v>10</v>
@@ -65813,7 +65813,7 @@
         <v>94</v>
       </c>
       <c r="E668" s="2" t="n">
-        <v>12006</v>
+        <v>12050</v>
       </c>
       <c r="F668" s="2" t="n">
         <v>13</v>
@@ -65837,7 +65837,7 @@
         <v>94</v>
       </c>
       <c r="E669" s="2" t="n">
-        <v>12022</v>
+        <v>12066</v>
       </c>
       <c r="F669" s="2" t="n">
         <v>12</v>
@@ -65861,7 +65861,7 @@
         <v>94</v>
       </c>
       <c r="E670" s="2" t="n">
-        <v>12036</v>
+        <v>12080</v>
       </c>
       <c r="F670" s="2" t="n">
         <v>13</v>
@@ -65885,7 +65885,7 @@
         <v>94</v>
       </c>
       <c r="E671" s="2" t="n">
-        <v>12051</v>
+        <v>12095</v>
       </c>
       <c r="F671" s="2" t="n">
         <v>75</v>
@@ -65909,7 +65909,7 @@
         <v>94</v>
       </c>
       <c r="E672" s="2" t="n">
-        <v>12133</v>
+        <v>12177</v>
       </c>
       <c r="F672" s="2" t="n">
         <v>121</v>
@@ -65933,7 +65933,7 @@
         <v>94</v>
       </c>
       <c r="E673" s="2" t="n">
-        <v>12263</v>
+        <v>12307</v>
       </c>
       <c r="F673" s="2" t="n">
         <v>45</v>
@@ -65957,7 +65957,7 @@
         <v>94</v>
       </c>
       <c r="E674" s="2" t="n">
-        <v>12313</v>
+        <v>12357</v>
       </c>
       <c r="F674" s="2" t="n">
         <v>64</v>
@@ -65981,7 +65981,7 @@
         <v>94</v>
       </c>
       <c r="E675" s="2" t="n">
-        <v>12383</v>
+        <v>12427</v>
       </c>
       <c r="F675" s="2" t="n">
         <v>54</v>
@@ -66005,7 +66005,7 @@
         <v>94</v>
       </c>
       <c r="E676" s="2" t="n">
-        <v>12442</v>
+        <v>12486</v>
       </c>
       <c r="F676" s="2" t="n">
         <v>8</v>
@@ -66029,7 +66029,7 @@
         <v>94</v>
       </c>
       <c r="E677" s="2" t="n">
-        <v>12453</v>
+        <v>12497</v>
       </c>
       <c r="F677" s="2" t="n">
         <v>11</v>
@@ -66053,7 +66053,7 @@
         <v>94</v>
       </c>
       <c r="E678" s="2" t="n">
-        <v>12467</v>
+        <v>12511</v>
       </c>
       <c r="F678" s="2" t="n">
         <v>9</v>
@@ -66077,7 +66077,7 @@
         <v>94</v>
       </c>
       <c r="E679" s="2" t="n">
-        <v>12478</v>
+        <v>12522</v>
       </c>
       <c r="F679" s="2" t="n">
         <v>26</v>
@@ -66101,7 +66101,7 @@
         <v>94</v>
       </c>
       <c r="E680" s="2" t="n">
-        <v>12508</v>
+        <v>12552</v>
       </c>
       <c r="F680" s="2" t="n">
         <v>27</v>
@@ -66125,7 +66125,7 @@
         <v>94</v>
       </c>
       <c r="E681" s="2" t="n">
-        <v>12539</v>
+        <v>12583</v>
       </c>
       <c r="F681" s="2" t="n">
         <v>18</v>
@@ -66149,7 +66149,7 @@
         <v>94</v>
       </c>
       <c r="E682" s="2" t="n">
-        <v>12560</v>
+        <v>12604</v>
       </c>
       <c r="F682" s="2" t="n">
         <v>23</v>
@@ -66173,7 +66173,7 @@
         <v>94</v>
       </c>
       <c r="E683" s="2" t="n">
-        <v>12586</v>
+        <v>12630</v>
       </c>
       <c r="F683" s="2" t="n">
         <v>19</v>
@@ -66197,7 +66197,7 @@
         <v>94</v>
       </c>
       <c r="E684" s="2" t="n">
-        <v>12608</v>
+        <v>12652</v>
       </c>
       <c r="F684" s="2" t="n">
         <v>21</v>
@@ -66221,7 +66221,7 @@
         <v>94</v>
       </c>
       <c r="E685" s="2" t="n">
-        <v>12633</v>
+        <v>12677</v>
       </c>
       <c r="F685" s="2" t="n">
         <v>18</v>
@@ -66245,7 +66245,7 @@
         <v>94</v>
       </c>
       <c r="E686" s="2" t="n">
-        <v>12654</v>
+        <v>12698</v>
       </c>
       <c r="F686" s="2" t="n">
         <v>18</v>
@@ -66269,7 +66269,7 @@
         <v>94</v>
       </c>
       <c r="E687" s="2" t="n">
-        <v>12675</v>
+        <v>12719</v>
       </c>
       <c r="F687" s="2" t="n">
         <v>17</v>
@@ -66293,7 +66293,7 @@
         <v>94</v>
       </c>
       <c r="E688" s="2" t="n">
-        <v>12695</v>
+        <v>12739</v>
       </c>
       <c r="F688" s="2" t="n">
         <v>11</v>
@@ -66317,7 +66317,7 @@
         <v>94</v>
       </c>
       <c r="E689" s="2" t="n">
-        <v>12708</v>
+        <v>12752</v>
       </c>
       <c r="F689" s="2" t="n">
         <v>18</v>
@@ -66341,7 +66341,7 @@
         <v>94</v>
       </c>
       <c r="E690" s="2" t="n">
-        <v>12731</v>
+        <v>12775</v>
       </c>
       <c r="F690" s="2" t="n">
         <v>19</v>
@@ -66365,7 +66365,7 @@
         <v>94</v>
       </c>
       <c r="E691" s="2" t="n">
-        <v>12753</v>
+        <v>12797</v>
       </c>
       <c r="F691" s="2" t="n">
         <v>19</v>
@@ -66389,7 +66389,7 @@
         <v>94</v>
       </c>
       <c r="E692" s="2" t="n">
-        <v>12775</v>
+        <v>12819</v>
       </c>
       <c r="F692" s="2" t="n">
         <v>19</v>
@@ -66413,7 +66413,7 @@
         <v>94</v>
       </c>
       <c r="E693" s="2" t="n">
-        <v>12797</v>
+        <v>12841</v>
       </c>
       <c r="F693" s="2" t="n">
         <v>18</v>
@@ -66437,7 +66437,7 @@
         <v>94</v>
       </c>
       <c r="E694" s="2" t="n">
-        <v>12818</v>
+        <v>12862</v>
       </c>
       <c r="F694" s="2" t="n">
         <v>18</v>
@@ -66461,7 +66461,7 @@
         <v>94</v>
       </c>
       <c r="E695" s="2" t="n">
-        <v>12839</v>
+        <v>12883</v>
       </c>
       <c r="F695" s="2" t="n">
         <v>18</v>
@@ -66485,7 +66485,7 @@
         <v>94</v>
       </c>
       <c r="E696" s="2" t="n">
-        <v>12860</v>
+        <v>12904</v>
       </c>
       <c r="F696" s="2" t="n">
         <v>17</v>
@@ -66509,7 +66509,7 @@
         <v>94</v>
       </c>
       <c r="E697" s="2" t="n">
-        <v>12880</v>
+        <v>12924</v>
       </c>
       <c r="F697" s="2" t="n">
         <v>18</v>
@@ -66533,7 +66533,7 @@
         <v>94</v>
       </c>
       <c r="E698" s="2" t="n">
-        <v>12901</v>
+        <v>12945</v>
       </c>
       <c r="F698" s="2" t="n">
         <v>17</v>
@@ -66557,7 +66557,7 @@
         <v>94</v>
       </c>
       <c r="E699" s="2" t="n">
-        <v>12921</v>
+        <v>12965</v>
       </c>
       <c r="F699" s="2" t="n">
         <v>19</v>
@@ -66581,7 +66581,7 @@
         <v>94</v>
       </c>
       <c r="E700" s="2" t="n">
-        <v>12943</v>
+        <v>12987</v>
       </c>
       <c r="F700" s="2" t="n">
         <v>25</v>
@@ -66605,7 +66605,7 @@
         <v>94</v>
       </c>
       <c r="E701" s="2" t="n">
-        <v>12972</v>
+        <v>13016</v>
       </c>
       <c r="F701" s="2" t="n">
         <v>17</v>
@@ -66629,7 +66629,7 @@
         <v>94</v>
       </c>
       <c r="E702" s="2" t="n">
-        <v>12992</v>
+        <v>13036</v>
       </c>
       <c r="F702" s="2" t="n">
         <v>15</v>
@@ -66653,7 +66653,7 @@
         <v>94</v>
       </c>
       <c r="E703" s="2" t="n">
-        <v>13010</v>
+        <v>13054</v>
       </c>
       <c r="F703" s="2" t="n">
         <v>20</v>
@@ -66677,7 +66677,7 @@
         <v>94</v>
       </c>
       <c r="E704" s="2" t="n">
-        <v>13033</v>
+        <v>13077</v>
       </c>
       <c r="F704" s="2" t="n">
         <v>17</v>
@@ -66701,7 +66701,7 @@
         <v>94</v>
       </c>
       <c r="E705" s="2" t="n">
-        <v>13053</v>
+        <v>13097</v>
       </c>
       <c r="F705" s="2" t="n">
         <v>18</v>
@@ -66725,7 +66725,7 @@
         <v>94</v>
       </c>
       <c r="E706" s="2" t="n">
-        <v>13074</v>
+        <v>13118</v>
       </c>
       <c r="F706" s="2" t="n">
         <v>18</v>
@@ -66749,7 +66749,7 @@
         <v>94</v>
       </c>
       <c r="E707" s="2" t="n">
-        <v>13095</v>
+        <v>13139</v>
       </c>
       <c r="F707" s="2" t="n">
         <v>18</v>
@@ -66773,7 +66773,7 @@
         <v>94</v>
       </c>
       <c r="E708" s="2" t="n">
-        <v>13116</v>
+        <v>13160</v>
       </c>
       <c r="F708" s="2" t="n">
         <v>17</v>
@@ -66797,7 +66797,7 @@
         <v>94</v>
       </c>
       <c r="E709" s="2" t="n">
-        <v>13136</v>
+        <v>13180</v>
       </c>
       <c r="F709" s="2" t="n">
         <v>26</v>
@@ -66821,7 +66821,7 @@
         <v>94</v>
       </c>
       <c r="E710" s="2" t="n">
-        <v>13165</v>
+        <v>13209</v>
       </c>
       <c r="F710" s="2" t="n">
         <v>28</v>
@@ -66845,7 +66845,7 @@
         <v>94</v>
       </c>
       <c r="E711" s="2" t="n">
-        <v>13196</v>
+        <v>13240</v>
       </c>
       <c r="F711" s="2" t="n">
         <v>17</v>
@@ -66869,7 +66869,7 @@
         <v>94</v>
       </c>
       <c r="E712" s="2" t="n">
-        <v>13216</v>
+        <v>13260</v>
       </c>
       <c r="F712" s="2" t="n">
         <v>16</v>
@@ -66893,7 +66893,7 @@
         <v>94</v>
       </c>
       <c r="E713" s="2" t="n">
-        <v>13235</v>
+        <v>13279</v>
       </c>
       <c r="F713" s="2" t="n">
         <v>16</v>
@@ -66917,7 +66917,7 @@
         <v>94</v>
       </c>
       <c r="E714" s="2" t="n">
-        <v>13254</v>
+        <v>13298</v>
       </c>
       <c r="F714" s="2" t="n">
         <v>21</v>
@@ -66941,7 +66941,7 @@
         <v>94</v>
       </c>
       <c r="E715" s="2" t="n">
-        <v>13278</v>
+        <v>13322</v>
       </c>
       <c r="F715" s="2" t="n">
         <v>17</v>
@@ -66965,7 +66965,7 @@
         <v>94</v>
       </c>
       <c r="E716" s="2" t="n">
-        <v>13298</v>
+        <v>13342</v>
       </c>
       <c r="F716" s="2" t="n">
         <v>16</v>
@@ -66989,7 +66989,7 @@
         <v>94</v>
       </c>
       <c r="E717" s="2" t="n">
-        <v>13317</v>
+        <v>13361</v>
       </c>
       <c r="F717" s="2" t="n">
         <v>17</v>
@@ -67013,7 +67013,7 @@
         <v>94</v>
       </c>
       <c r="E718" s="2" t="n">
-        <v>13337</v>
+        <v>13381</v>
       </c>
       <c r="F718" s="2" t="n">
         <v>15</v>
@@ -67037,7 +67037,7 @@
         <v>94</v>
       </c>
       <c r="E719" s="2" t="n">
-        <v>13355</v>
+        <v>13399</v>
       </c>
       <c r="F719" s="2" t="n">
         <v>11</v>
@@ -67061,7 +67061,7 @@
         <v>94</v>
       </c>
       <c r="E720" s="2" t="n">
-        <v>13369</v>
+        <v>13413</v>
       </c>
       <c r="F720" s="2" t="n">
         <v>16</v>
@@ -67085,7 +67085,7 @@
         <v>94</v>
       </c>
       <c r="E721" s="2" t="n">
-        <v>13388</v>
+        <v>13432</v>
       </c>
       <c r="F721" s="2" t="n">
         <v>17</v>
@@ -67109,7 +67109,7 @@
         <v>94</v>
       </c>
       <c r="E722" s="2" t="n">
-        <v>13408</v>
+        <v>13452</v>
       </c>
       <c r="F722" s="2" t="n">
         <v>14</v>
@@ -67133,7 +67133,7 @@
         <v>94</v>
       </c>
       <c r="E723" s="2" t="n">
-        <v>13425</v>
+        <v>13469</v>
       </c>
       <c r="F723" s="2" t="n">
         <v>18</v>
@@ -67157,7 +67157,7 @@
         <v>94</v>
       </c>
       <c r="E724" s="2" t="n">
-        <v>13446</v>
+        <v>13490</v>
       </c>
       <c r="F724" s="2" t="n">
         <v>17</v>
@@ -67181,7 +67181,7 @@
         <v>94</v>
       </c>
       <c r="E725" s="2" t="n">
-        <v>13466</v>
+        <v>13510</v>
       </c>
       <c r="F725" s="2" t="n">
         <v>15</v>
@@ -67205,7 +67205,7 @@
         <v>94</v>
       </c>
       <c r="E726" s="2" t="n">
-        <v>13484</v>
+        <v>13528</v>
       </c>
       <c r="F726" s="2" t="n">
         <v>8</v>
@@ -67229,7 +67229,7 @@
         <v>94</v>
       </c>
       <c r="E727" s="2" t="n">
-        <v>13494</v>
+        <v>13538</v>
       </c>
       <c r="F727" s="2" t="n">
         <v>14</v>
@@ -67253,7 +67253,7 @@
         <v>94</v>
       </c>
       <c r="E728" s="2" t="n">
-        <v>13511</v>
+        <v>13555</v>
       </c>
       <c r="F728" s="2" t="n">
         <v>17</v>
@@ -67277,7 +67277,7 @@
         <v>94</v>
       </c>
       <c r="E729" s="2" t="n">
-        <v>13531</v>
+        <v>13575</v>
       </c>
       <c r="F729" s="2" t="n">
         <v>17</v>
@@ -67301,7 +67301,7 @@
         <v>94</v>
       </c>
       <c r="E730" s="2" t="n">
-        <v>13551</v>
+        <v>13595</v>
       </c>
       <c r="F730" s="2" t="n">
         <v>16</v>
@@ -67325,7 +67325,7 @@
         <v>94</v>
       </c>
       <c r="E731" s="2" t="n">
-        <v>13570</v>
+        <v>13614</v>
       </c>
       <c r="F731" s="2" t="n">
         <v>7</v>
@@ -67349,7 +67349,7 @@
         <v>94</v>
       </c>
       <c r="E732" s="2" t="n">
-        <v>13579</v>
+        <v>13623</v>
       </c>
       <c r="F732" s="2" t="n">
         <v>9</v>
@@ -67373,7 +67373,7 @@
         <v>94</v>
       </c>
       <c r="E733" s="2" t="n">
-        <v>13591</v>
+        <v>13635</v>
       </c>
       <c r="F733" s="2" t="n">
         <v>10</v>
@@ -67397,7 +67397,7 @@
         <v>94</v>
       </c>
       <c r="E734" s="2" t="n">
-        <v>13603</v>
+        <v>13647</v>
       </c>
       <c r="F734" s="2" t="n">
         <v>29</v>
@@ -67421,7 +67421,7 @@
         <v>94</v>
       </c>
       <c r="E735" s="2" t="n">
-        <v>13636</v>
+        <v>13680</v>
       </c>
       <c r="F735" s="2" t="n">
         <v>17</v>
@@ -67445,7 +67445,7 @@
         <v>94</v>
       </c>
       <c r="E736" s="2" t="n">
-        <v>13656</v>
+        <v>13700</v>
       </c>
       <c r="F736" s="2" t="n">
         <v>16</v>
@@ -67469,7 +67469,7 @@
         <v>94</v>
       </c>
       <c r="E737" s="2" t="n">
-        <v>13675</v>
+        <v>13719</v>
       </c>
       <c r="F737" s="2" t="n">
         <v>18</v>
@@ -67493,7 +67493,7 @@
         <v>94</v>
       </c>
       <c r="E738" s="2" t="n">
-        <v>13696</v>
+        <v>13740</v>
       </c>
       <c r="F738" s="2" t="n">
         <v>11</v>
@@ -67517,7 +67517,7 @@
         <v>94</v>
       </c>
       <c r="E739" s="2" t="n">
-        <v>13709</v>
+        <v>13753</v>
       </c>
       <c r="F739" s="2" t="n">
         <v>18</v>
@@ -67541,7 +67541,7 @@
         <v>94</v>
       </c>
       <c r="E740" s="2" t="n">
-        <v>13730</v>
+        <v>13774</v>
       </c>
       <c r="F740" s="2" t="n">
         <v>9</v>
@@ -67565,7 +67565,7 @@
         <v>94</v>
       </c>
       <c r="E741" s="2" t="n">
-        <v>13742</v>
+        <v>13786</v>
       </c>
       <c r="F741" s="2" t="n">
         <v>10</v>
@@ -67589,7 +67589,7 @@
         <v>94</v>
       </c>
       <c r="E742" s="2" t="n">
-        <v>13754</v>
+        <v>13798</v>
       </c>
       <c r="F742" s="2" t="n">
         <v>10</v>
@@ -67613,7 +67613,7 @@
         <v>94</v>
       </c>
       <c r="E743" s="2" t="n">
-        <v>13767</v>
+        <v>13811</v>
       </c>
       <c r="F743" s="2" t="n">
         <v>20</v>
@@ -67637,7 +67637,7 @@
         <v>94</v>
       </c>
       <c r="E744" s="2" t="n">
-        <v>13790</v>
+        <v>13834</v>
       </c>
       <c r="F744" s="2" t="n">
         <v>9</v>
@@ -67661,7 +67661,7 @@
         <v>94</v>
       </c>
       <c r="E745" s="2" t="n">
-        <v>13802</v>
+        <v>13846</v>
       </c>
       <c r="F745" s="2" t="n">
         <v>9</v>
@@ -67685,7 +67685,7 @@
         <v>94</v>
       </c>
       <c r="E746" s="2" t="n">
-        <v>13813</v>
+        <v>13857</v>
       </c>
       <c r="F746" s="2" t="n">
         <v>10</v>
@@ -67709,7 +67709,7 @@
         <v>94</v>
       </c>
       <c r="E747" s="2" t="n">
-        <v>13826</v>
+        <v>13870</v>
       </c>
       <c r="F747" s="2" t="n">
         <v>11</v>
@@ -67733,7 +67733,7 @@
         <v>94</v>
       </c>
       <c r="E748" s="2" t="n">
-        <v>13840</v>
+        <v>13884</v>
       </c>
       <c r="F748" s="2" t="n">
         <v>28</v>
@@ -67757,7 +67757,7 @@
         <v>94</v>
       </c>
       <c r="E749" s="2" t="n">
-        <v>13871</v>
+        <v>13915</v>
       </c>
       <c r="F749" s="2" t="n">
         <v>16</v>
@@ -67781,7 +67781,7 @@
         <v>94</v>
       </c>
       <c r="E750" s="2" t="n">
-        <v>13890</v>
+        <v>13934</v>
       </c>
       <c r="F750" s="2" t="n">
         <v>15</v>
@@ -67805,7 +67805,7 @@
         <v>94</v>
       </c>
       <c r="E751" s="2" t="n">
-        <v>13908</v>
+        <v>13952</v>
       </c>
       <c r="F751" s="2" t="n">
         <v>15</v>
@@ -67829,7 +67829,7 @@
         <v>94</v>
       </c>
       <c r="E752" s="2" t="n">
-        <v>13926</v>
+        <v>13970</v>
       </c>
       <c r="F752" s="2" t="n">
         <v>9</v>
@@ -67853,7 +67853,7 @@
         <v>94</v>
       </c>
       <c r="E753" s="2" t="n">
-        <v>13938</v>
+        <v>13982</v>
       </c>
       <c r="F753" s="2" t="n">
         <v>15</v>
@@ -67877,7 +67877,7 @@
         <v>94</v>
       </c>
       <c r="E754" s="2" t="n">
-        <v>13956</v>
+        <v>14000</v>
       </c>
       <c r="F754" s="2" t="n">
         <v>8</v>
@@ -67901,7 +67901,7 @@
         <v>94</v>
       </c>
       <c r="E755" s="2" t="n">
-        <v>13966</v>
+        <v>14010</v>
       </c>
       <c r="F755" s="2" t="n">
         <v>9</v>
@@ -67925,7 +67925,7 @@
         <v>94</v>
       </c>
       <c r="E756" s="2" t="n">
-        <v>13980</v>
+        <v>14024</v>
       </c>
       <c r="F756" s="2" t="n">
         <v>17</v>
@@ -67949,7 +67949,7 @@
         <v>94</v>
       </c>
       <c r="E757" s="2" t="n">
-        <v>14000</v>
+        <v>14044</v>
       </c>
       <c r="F757" s="2" t="n">
         <v>7</v>
@@ -67973,7 +67973,7 @@
         <v>94</v>
       </c>
       <c r="E758" s="2" t="n">
-        <v>14009</v>
+        <v>14053</v>
       </c>
       <c r="F758" s="2" t="n">
         <v>10</v>
@@ -67997,7 +67997,7 @@
         <v>94</v>
       </c>
       <c r="E759" s="2" t="n">
-        <v>14022</v>
+        <v>14066</v>
       </c>
       <c r="F759" s="2" t="n">
         <v>8</v>
@@ -68021,7 +68021,7 @@
         <v>94</v>
       </c>
       <c r="E760" s="2" t="n">
-        <v>14033</v>
+        <v>14077</v>
       </c>
       <c r="F760" s="2" t="n">
         <v>10</v>
@@ -68045,7 +68045,7 @@
         <v>94</v>
       </c>
       <c r="E761" s="2" t="n">
-        <v>14045</v>
+        <v>14089</v>
       </c>
       <c r="F761" s="2" t="n">
         <v>9</v>
@@ -68069,7 +68069,7 @@
         <v>94</v>
       </c>
       <c r="E762" s="2" t="n">
-        <v>14057</v>
+        <v>14101</v>
       </c>
       <c r="F762" s="2" t="n">
         <v>9</v>
@@ -68093,7 +68093,7 @@
         <v>94</v>
       </c>
       <c r="E763" s="2" t="n">
-        <v>14068</v>
+        <v>14112</v>
       </c>
       <c r="F763" s="2" t="n">
         <v>9</v>
@@ -68117,7 +68117,7 @@
         <v>94</v>
       </c>
       <c r="E764" s="2" t="n">
-        <v>14080</v>
+        <v>14124</v>
       </c>
       <c r="F764" s="2" t="n">
         <v>8</v>
@@ -68141,7 +68141,7 @@
         <v>94</v>
       </c>
       <c r="E765" s="2" t="n">
-        <v>14090</v>
+        <v>14134</v>
       </c>
       <c r="F765" s="2" t="n">
         <v>8</v>
@@ -68165,7 +68165,7 @@
         <v>94</v>
       </c>
       <c r="E766" s="2" t="n">
-        <v>14100</v>
+        <v>14144</v>
       </c>
       <c r="F766" s="2" t="n">
         <v>8</v>
@@ -68189,7 +68189,7 @@
         <v>94</v>
       </c>
       <c r="E767" s="2" t="n">
-        <v>14110</v>
+        <v>14154</v>
       </c>
       <c r="F767" s="2" t="n">
         <v>8</v>
@@ -68213,7 +68213,7 @@
         <v>94</v>
       </c>
       <c r="E768" s="2" t="n">
-        <v>14120</v>
+        <v>14164</v>
       </c>
       <c r="F768" s="2" t="n">
         <v>10</v>
@@ -68237,7 +68237,7 @@
         <v>94</v>
       </c>
       <c r="E769" s="2" t="n">
-        <v>14133</v>
+        <v>14177</v>
       </c>
       <c r="F769" s="2" t="n">
         <v>9</v>
@@ -68261,7 +68261,7 @@
         <v>94</v>
       </c>
       <c r="E770" s="2" t="n">
-        <v>14144</v>
+        <v>14188</v>
       </c>
       <c r="F770" s="2" t="n">
         <v>9</v>
@@ -68285,7 +68285,7 @@
         <v>94</v>
       </c>
       <c r="E771" s="2" t="n">
-        <v>14156</v>
+        <v>14200</v>
       </c>
       <c r="F771" s="2" t="n">
         <v>7</v>
@@ -68309,7 +68309,7 @@
         <v>94</v>
       </c>
       <c r="E772" s="2" t="n">
-        <v>14165</v>
+        <v>14209</v>
       </c>
       <c r="F772" s="2" t="n">
         <v>8</v>
@@ -68333,7 +68333,7 @@
         <v>94</v>
       </c>
       <c r="E773" s="2" t="n">
-        <v>14176</v>
+        <v>14220</v>
       </c>
       <c r="F773" s="2" t="n">
         <v>8</v>
@@ -68357,7 +68357,7 @@
         <v>94</v>
       </c>
       <c r="E774" s="2" t="n">
-        <v>14186</v>
+        <v>14230</v>
       </c>
       <c r="F774" s="2" t="n">
         <v>6</v>
@@ -68381,7 +68381,7 @@
         <v>94</v>
       </c>
       <c r="E775" s="2" t="n">
-        <v>14195</v>
+        <v>14239</v>
       </c>
       <c r="F775" s="2" t="n">
         <v>7</v>
@@ -68405,7 +68405,7 @@
         <v>94</v>
       </c>
       <c r="E776" s="2" t="n">
-        <v>14203</v>
+        <v>14247</v>
       </c>
       <c r="F776" s="2" t="n">
         <v>16</v>
@@ -68429,7 +68429,7 @@
         <v>94</v>
       </c>
       <c r="E777" s="2" t="n">
-        <v>14222</v>
+        <v>14266</v>
       </c>
       <c r="F777" s="2" t="n">
         <v>8</v>
@@ -68453,7 +68453,7 @@
         <v>94</v>
       </c>
       <c r="E778" s="2" t="n">
-        <v>14232</v>
+        <v>14276</v>
       </c>
       <c r="F778" s="2" t="n">
         <v>8</v>
@@ -68477,7 +68477,7 @@
         <v>94</v>
       </c>
       <c r="E779" s="2" t="n">
-        <v>14242</v>
+        <v>14286</v>
       </c>
       <c r="F779" s="2" t="n">
         <v>11</v>
@@ -68501,7 +68501,7 @@
         <v>94</v>
       </c>
       <c r="E780" s="2" t="n">
-        <v>14256</v>
+        <v>14300</v>
       </c>
       <c r="F780" s="2" t="n">
         <v>8</v>
@@ -68525,7 +68525,7 @@
         <v>94</v>
       </c>
       <c r="E781" s="2" t="n">
-        <v>14266</v>
+        <v>14310</v>
       </c>
       <c r="F781" s="2" t="n">
         <v>9</v>
@@ -68549,7 +68549,7 @@
         <v>94</v>
       </c>
       <c r="E782" s="2" t="n">
-        <v>14278</v>
+        <v>14322</v>
       </c>
       <c r="F782" s="2" t="n">
         <v>8</v>
@@ -68573,7 +68573,7 @@
         <v>94</v>
       </c>
       <c r="E783" s="2" t="n">
-        <v>14288</v>
+        <v>14332</v>
       </c>
       <c r="F783" s="2" t="n">
         <v>8</v>
@@ -68597,7 +68597,7 @@
         <v>94</v>
       </c>
       <c r="E784" s="2" t="n">
-        <v>14299</v>
+        <v>14343</v>
       </c>
       <c r="F784" s="2" t="n">
         <v>8</v>
@@ -68621,7 +68621,7 @@
         <v>94</v>
       </c>
       <c r="E785" s="2" t="n">
-        <v>14309</v>
+        <v>14353</v>
       </c>
       <c r="F785" s="2" t="n">
         <v>8</v>
@@ -68645,7 +68645,7 @@
         <v>94</v>
       </c>
       <c r="E786" s="2" t="n">
-        <v>14320</v>
+        <v>14364</v>
       </c>
       <c r="F786" s="2" t="n">
         <v>8</v>
@@ -68669,7 +68669,7 @@
         <v>94</v>
       </c>
       <c r="E787" s="2" t="n">
-        <v>14330</v>
+        <v>14374</v>
       </c>
       <c r="F787" s="2" t="n">
         <v>8</v>
@@ -68693,7 +68693,7 @@
         <v>94</v>
       </c>
       <c r="E788" s="2" t="n">
-        <v>14341</v>
+        <v>14385</v>
       </c>
       <c r="F788" s="2" t="n">
         <v>8</v>
@@ -68717,7 +68717,7 @@
         <v>94</v>
       </c>
       <c r="E789" s="2" t="n">
-        <v>14351</v>
+        <v>14395</v>
       </c>
       <c r="F789" s="2" t="n">
         <v>8</v>
@@ -68741,7 +68741,7 @@
         <v>94</v>
       </c>
       <c r="E790" s="2" t="n">
-        <v>14362</v>
+        <v>14406</v>
       </c>
       <c r="F790" s="2" t="n">
         <v>8</v>
@@ -68765,7 +68765,7 @@
         <v>94</v>
       </c>
       <c r="E791" s="2" t="n">
-        <v>14372</v>
+        <v>14416</v>
       </c>
       <c r="F791" s="2" t="n">
         <v>8</v>
@@ -68789,7 +68789,7 @@
         <v>94</v>
       </c>
       <c r="E792" s="2" t="n">
-        <v>14383</v>
+        <v>14427</v>
       </c>
       <c r="F792" s="2" t="n">
         <v>6</v>
@@ -68813,7 +68813,7 @@
         <v>94</v>
       </c>
       <c r="E793" s="2" t="n">
-        <v>14391</v>
+        <v>14435</v>
       </c>
       <c r="F793" s="2" t="n">
         <v>8</v>
@@ -68837,7 +68837,7 @@
         <v>94</v>
       </c>
       <c r="E794" s="2" t="n">
-        <v>14402</v>
+        <v>14446</v>
       </c>
       <c r="F794" s="2" t="n">
         <v>8</v>
@@ -68861,7 +68861,7 @@
         <v>94</v>
       </c>
       <c r="E795" s="2" t="n">
-        <v>14412</v>
+        <v>14456</v>
       </c>
       <c r="F795" s="2" t="n">
         <v>9</v>
@@ -68885,7 +68885,7 @@
         <v>94</v>
       </c>
       <c r="E796" s="2" t="n">
-        <v>14424</v>
+        <v>14468</v>
       </c>
       <c r="F796" s="2" t="n">
         <v>9</v>
@@ -68909,7 +68909,7 @@
         <v>94</v>
       </c>
       <c r="E797" s="2" t="n">
-        <v>14435</v>
+        <v>14479</v>
       </c>
       <c r="F797" s="2" t="n">
         <v>9</v>
@@ -68933,7 +68933,7 @@
         <v>94</v>
       </c>
       <c r="E798" s="2" t="n">
-        <v>14447</v>
+        <v>14491</v>
       </c>
       <c r="F798" s="2" t="n">
         <v>8</v>
@@ -68957,7 +68957,7 @@
         <v>94</v>
       </c>
       <c r="E799" s="2" t="n">
-        <v>14457</v>
+        <v>14501</v>
       </c>
       <c r="F799" s="2" t="n">
         <v>5</v>
@@ -68981,7 +68981,7 @@
         <v>94</v>
       </c>
       <c r="E800" s="2" t="n">
-        <v>14465</v>
+        <v>14509</v>
       </c>
       <c r="F800" s="2" t="n">
         <v>13</v>
@@ -69005,7 +69005,7 @@
         <v>94</v>
       </c>
       <c r="E801" s="2" t="n">
-        <v>14480</v>
+        <v>14524</v>
       </c>
       <c r="F801" s="2" t="n">
         <v>17</v>
@@ -69029,7 +69029,7 @@
         <v>94</v>
       </c>
       <c r="E802" s="2" t="n">
-        <v>14500</v>
+        <v>14544</v>
       </c>
       <c r="F802" s="2" t="n">
         <v>8</v>
@@ -69053,7 +69053,7 @@
         <v>94</v>
       </c>
       <c r="E803" s="2" t="n">
-        <v>14511</v>
+        <v>14555</v>
       </c>
       <c r="F803" s="2" t="n">
         <v>8</v>
@@ -69077,7 +69077,7 @@
         <v>94</v>
       </c>
       <c r="E804" s="2" t="n">
-        <v>14521</v>
+        <v>14565</v>
       </c>
       <c r="F804" s="2" t="n">
         <v>13</v>
@@ -69101,7 +69101,7 @@
         <v>94</v>
       </c>
       <c r="E805" s="2" t="n">
-        <v>14537</v>
+        <v>14581</v>
       </c>
       <c r="F805" s="2" t="n">
         <v>9</v>
@@ -69125,7 +69125,7 @@
         <v>94</v>
       </c>
       <c r="E806" s="2" t="n">
-        <v>14548</v>
+        <v>14592</v>
       </c>
       <c r="F806" s="2" t="n">
         <v>7</v>
@@ -69149,7 +69149,7 @@
         <v>94</v>
       </c>
       <c r="E807" s="2" t="n">
-        <v>14557</v>
+        <v>14601</v>
       </c>
       <c r="F807" s="2" t="n">
         <v>9</v>
@@ -69173,7 +69173,7 @@
         <v>94</v>
       </c>
       <c r="E808" s="2" t="n">
-        <v>14569</v>
+        <v>14613</v>
       </c>
       <c r="F808" s="2" t="n">
         <v>12</v>
@@ -69197,7 +69197,7 @@
         <v>94</v>
       </c>
       <c r="E809" s="2" t="n">
-        <v>14583</v>
+        <v>14627</v>
       </c>
       <c r="F809" s="2" t="n">
         <v>11</v>
@@ -69221,7 +69221,7 @@
         <v>94</v>
       </c>
       <c r="E810" s="2" t="n">
-        <v>14597</v>
+        <v>14641</v>
       </c>
       <c r="F810" s="2" t="n">
         <v>10</v>
@@ -69245,7 +69245,7 @@
         <v>94</v>
       </c>
       <c r="E811" s="2" t="n">
-        <v>14610</v>
+        <v>14654</v>
       </c>
       <c r="F811" s="2" t="n">
         <v>10</v>
@@ -69269,7 +69269,7 @@
         <v>94</v>
       </c>
       <c r="E812" s="2" t="n">
-        <v>14622</v>
+        <v>14666</v>
       </c>
       <c r="F812" s="2" t="n">
         <v>11</v>
@@ -69293,7 +69293,7 @@
         <v>94</v>
       </c>
       <c r="E813" s="2" t="n">
-        <v>14636</v>
+        <v>14680</v>
       </c>
       <c r="F813" s="2" t="n">
         <v>11</v>
@@ -69317,7 +69317,7 @@
         <v>94</v>
       </c>
       <c r="E814" s="2" t="n">
-        <v>14650</v>
+        <v>14694</v>
       </c>
       <c r="F814" s="2" t="n">
         <v>9</v>
@@ -69341,7 +69341,7 @@
         <v>94</v>
       </c>
       <c r="E815" s="2" t="n">
-        <v>14661</v>
+        <v>14705</v>
       </c>
       <c r="F815" s="2" t="n">
         <v>11</v>
@@ -69365,7 +69365,7 @@
         <v>94</v>
       </c>
       <c r="E816" s="2" t="n">
-        <v>14674</v>
+        <v>14718</v>
       </c>
       <c r="F816" s="2" t="n">
         <v>10</v>
@@ -69389,7 +69389,7 @@
         <v>94</v>
       </c>
       <c r="E817" s="2" t="n">
-        <v>14687</v>
+        <v>14731</v>
       </c>
       <c r="F817" s="2" t="n">
         <v>9</v>
@@ -69413,7 +69413,7 @@
         <v>94</v>
       </c>
       <c r="E818" s="2" t="n">
-        <v>14698</v>
+        <v>14742</v>
       </c>
       <c r="F818" s="2" t="n">
         <v>9</v>
@@ -69437,7 +69437,7 @@
         <v>94</v>
       </c>
       <c r="E819" s="2" t="n">
-        <v>14710</v>
+        <v>14754</v>
       </c>
       <c r="F819" s="2" t="n">
         <v>10</v>
@@ -69461,7 +69461,7 @@
         <v>94</v>
       </c>
       <c r="E820" s="2" t="n">
-        <v>14723</v>
+        <v>14767</v>
       </c>
       <c r="F820" s="2" t="n">
         <v>15</v>
@@ -69485,7 +69485,7 @@
         <v>94</v>
       </c>
       <c r="E821" s="2" t="n">
-        <v>14740</v>
+        <v>14784</v>
       </c>
       <c r="F821" s="2" t="n">
         <v>16</v>
@@ -69509,7 +69509,7 @@
         <v>94</v>
       </c>
       <c r="E822" s="2" t="n">
-        <v>14759</v>
+        <v>14803</v>
       </c>
       <c r="F822" s="2" t="n">
         <v>10</v>
@@ -69533,7 +69533,7 @@
         <v>94</v>
       </c>
       <c r="E823" s="2" t="n">
-        <v>14771</v>
+        <v>14815</v>
       </c>
       <c r="F823" s="2" t="n">
         <v>9</v>
@@ -69557,7 +69557,7 @@
         <v>94</v>
       </c>
       <c r="E824" s="2" t="n">
-        <v>14783</v>
+        <v>14827</v>
       </c>
       <c r="F824" s="2" t="n">
         <v>8</v>
@@ -69581,7 +69581,7 @@
         <v>94</v>
       </c>
       <c r="E825" s="2" t="n">
-        <v>14793</v>
+        <v>14837</v>
       </c>
       <c r="F825" s="2" t="n">
         <v>8</v>
@@ -69605,7 +69605,7 @@
         <v>94</v>
       </c>
       <c r="E826" s="2" t="n">
-        <v>14804</v>
+        <v>14848</v>
       </c>
       <c r="F826" s="2" t="n">
         <v>8</v>
@@ -69629,7 +69629,7 @@
         <v>94</v>
       </c>
       <c r="E827" s="2" t="n">
-        <v>14814</v>
+        <v>14858</v>
       </c>
       <c r="F827" s="2" t="n">
         <v>9</v>
@@ -69653,7 +69653,7 @@
         <v>94</v>
       </c>
       <c r="E828" s="2" t="n">
-        <v>14826</v>
+        <v>14870</v>
       </c>
       <c r="F828" s="2" t="n">
         <v>8</v>
@@ -69677,7 +69677,7 @@
         <v>94</v>
       </c>
       <c r="E829" s="2" t="n">
-        <v>14836</v>
+        <v>14880</v>
       </c>
       <c r="F829" s="2" t="n">
         <v>8</v>
@@ -69701,7 +69701,7 @@
         <v>94</v>
       </c>
       <c r="E830" s="2" t="n">
-        <v>14847</v>
+        <v>14891</v>
       </c>
       <c r="F830" s="2" t="n">
         <v>8</v>
@@ -69725,7 +69725,7 @@
         <v>94</v>
       </c>
       <c r="E831" s="2" t="n">
-        <v>14857</v>
+        <v>14901</v>
       </c>
       <c r="F831" s="2" t="n">
         <v>8</v>
@@ -69749,7 +69749,7 @@
         <v>94</v>
       </c>
       <c r="E832" s="2" t="n">
-        <v>14868</v>
+        <v>14912</v>
       </c>
       <c r="F832" s="2" t="n">
         <v>8</v>
@@ -69773,7 +69773,7 @@
         <v>94</v>
       </c>
       <c r="E833" s="2" t="n">
-        <v>14878</v>
+        <v>14922</v>
       </c>
       <c r="F833" s="2" t="n">
         <v>8</v>
@@ -69797,7 +69797,7 @@
         <v>94</v>
       </c>
       <c r="E834" s="2" t="n">
-        <v>14889</v>
+        <v>14933</v>
       </c>
       <c r="F834" s="2" t="n">
         <v>8</v>
@@ -69821,7 +69821,7 @@
         <v>94</v>
       </c>
       <c r="E835" s="2" t="n">
-        <v>14899</v>
+        <v>14943</v>
       </c>
       <c r="F835" s="2" t="n">
         <v>8</v>
@@ -69845,7 +69845,7 @@
         <v>94</v>
       </c>
       <c r="E836" s="2" t="n">
-        <v>14910</v>
+        <v>14954</v>
       </c>
       <c r="F836" s="2" t="n">
         <v>7</v>
@@ -69869,7 +69869,7 @@
         <v>94</v>
       </c>
       <c r="E837" s="2" t="n">
-        <v>14919</v>
+        <v>14963</v>
       </c>
       <c r="F837" s="2" t="n">
         <v>8</v>
@@ -69893,7 +69893,7 @@
         <v>94</v>
       </c>
       <c r="E838" s="2" t="n">
-        <v>14930</v>
+        <v>14974</v>
       </c>
       <c r="F838" s="2" t="n">
         <v>7</v>
@@ -69917,7 +69917,7 @@
         <v>94</v>
       </c>
       <c r="E839" s="2" t="n">
-        <v>14939</v>
+        <v>14983</v>
       </c>
       <c r="F839" s="2" t="n">
         <v>6</v>
@@ -69941,7 +69941,7 @@
         <v>94</v>
       </c>
       <c r="E840" s="2" t="n">
-        <v>14948</v>
+        <v>14992</v>
       </c>
       <c r="F840" s="2" t="n">
         <v>8</v>
@@ -69965,7 +69965,7 @@
         <v>94</v>
       </c>
       <c r="E841" s="2" t="n">
-        <v>14958</v>
+        <v>15002</v>
       </c>
       <c r="F841" s="2" t="n">
         <v>15</v>
@@ -69989,7 +69989,7 @@
         <v>94</v>
       </c>
       <c r="E842" s="2" t="n">
-        <v>14976</v>
+        <v>15020</v>
       </c>
       <c r="F842" s="2" t="n">
         <v>9</v>
@@ -70013,7 +70013,7 @@
         <v>94</v>
       </c>
       <c r="E843" s="2" t="n">
-        <v>14988</v>
+        <v>15032</v>
       </c>
       <c r="F843" s="2" t="n">
         <v>9</v>
@@ -70037,7 +70037,7 @@
         <v>94</v>
       </c>
       <c r="E844" s="2" t="n">
-        <v>14999</v>
+        <v>15043</v>
       </c>
       <c r="F844" s="2" t="n">
         <v>9</v>
@@ -70061,7 +70061,7 @@
         <v>94</v>
       </c>
       <c r="E845" s="2" t="n">
-        <v>15011</v>
+        <v>15055</v>
       </c>
       <c r="F845" s="2" t="n">
         <v>8</v>
@@ -70085,7 +70085,7 @@
         <v>94</v>
       </c>
       <c r="E846" s="2" t="n">
-        <v>15021</v>
+        <v>15065</v>
       </c>
       <c r="F846" s="2" t="n">
         <v>8</v>
@@ -70109,7 +70109,7 @@
         <v>94</v>
       </c>
       <c r="E847" s="2" t="n">
-        <v>15032</v>
+        <v>15076</v>
       </c>
       <c r="F847" s="2" t="n">
         <v>9</v>
@@ -70133,7 +70133,7 @@
         <v>94</v>
       </c>
       <c r="E848" s="2" t="n">
-        <v>15043</v>
+        <v>15087</v>
       </c>
       <c r="F848" s="2" t="n">
         <v>9</v>
@@ -70157,7 +70157,7 @@
         <v>94</v>
       </c>
       <c r="E849" s="2" t="n">
-        <v>15055</v>
+        <v>15099</v>
       </c>
       <c r="F849" s="2" t="n">
         <v>8</v>
@@ -70181,7 +70181,7 @@
         <v>94</v>
       </c>
       <c r="E850" s="2" t="n">
-        <v>15065</v>
+        <v>15109</v>
       </c>
       <c r="F850" s="2" t="n">
         <v>9</v>
@@ -70205,7 +70205,7 @@
         <v>94</v>
       </c>
       <c r="E851" s="2" t="n">
-        <v>15077</v>
+        <v>15121</v>
       </c>
       <c r="F851" s="2" t="n">
         <v>9</v>
@@ -70229,7 +70229,7 @@
         <v>94</v>
       </c>
       <c r="E852" s="2" t="n">
-        <v>15088</v>
+        <v>15132</v>
       </c>
       <c r="F852" s="2" t="n">
         <v>9</v>
@@ -70253,7 +70253,7 @@
         <v>94</v>
       </c>
       <c r="E853" s="2" t="n">
-        <v>15100</v>
+        <v>15144</v>
       </c>
       <c r="F853" s="2" t="n">
         <v>9</v>
@@ -70277,7 +70277,7 @@
         <v>94</v>
       </c>
       <c r="E854" s="2" t="n">
-        <v>15111</v>
+        <v>15155</v>
       </c>
       <c r="F854" s="2" t="n">
         <v>8</v>
@@ -70301,7 +70301,7 @@
         <v>94</v>
       </c>
       <c r="E855" s="2" t="n">
-        <v>15122</v>
+        <v>15166</v>
       </c>
       <c r="F855" s="2" t="n">
         <v>7</v>
@@ -70325,7 +70325,7 @@
         <v>94</v>
       </c>
       <c r="E856" s="2" t="n">
-        <v>15131</v>
+        <v>15175</v>
       </c>
       <c r="F856" s="2" t="n">
         <v>7</v>
@@ -70349,7 +70349,7 @@
         <v>94</v>
       </c>
       <c r="E857" s="2" t="n">
-        <v>15141</v>
+        <v>15185</v>
       </c>
       <c r="F857" s="2" t="n">
         <v>8</v>
@@ -70373,7 +70373,7 @@
         <v>94</v>
       </c>
       <c r="E858" s="2" t="n">
-        <v>15151</v>
+        <v>15195</v>
       </c>
       <c r="F858" s="2" t="n">
         <v>9</v>
@@ -70397,7 +70397,7 @@
         <v>94</v>
       </c>
       <c r="E859" s="2" t="n">
-        <v>15163</v>
+        <v>15207</v>
       </c>
       <c r="F859" s="2" t="n">
         <v>8</v>
@@ -70421,7 +70421,7 @@
         <v>94</v>
       </c>
       <c r="E860" s="2" t="n">
-        <v>15173</v>
+        <v>15217</v>
       </c>
       <c r="F860" s="2" t="n">
         <v>10</v>
@@ -70445,7 +70445,7 @@
         <v>94</v>
       </c>
       <c r="E861" s="2" t="n">
-        <v>15186</v>
+        <v>15230</v>
       </c>
       <c r="F861" s="2" t="n">
         <v>9</v>
@@ -70469,7 +70469,7 @@
         <v>94</v>
       </c>
       <c r="E862" s="2" t="n">
-        <v>15197</v>
+        <v>15241</v>
       </c>
       <c r="F862" s="2" t="n">
         <v>8</v>
@@ -70493,7 +70493,7 @@
         <v>94</v>
       </c>
       <c r="E863" s="2" t="n">
-        <v>15208</v>
+        <v>15252</v>
       </c>
       <c r="F863" s="2" t="n">
         <v>8</v>
@@ -70517,7 +70517,7 @@
         <v>94</v>
       </c>
       <c r="E864" s="2" t="n">
-        <v>15218</v>
+        <v>15262</v>
       </c>
       <c r="F864" s="2" t="n">
         <v>7</v>
@@ -70541,7 +70541,7 @@
         <v>94</v>
       </c>
       <c r="E865" s="2" t="n">
-        <v>15228</v>
+        <v>15272</v>
       </c>
       <c r="F865" s="2" t="n">
         <v>9</v>
@@ -70565,7 +70565,7 @@
         <v>94</v>
       </c>
       <c r="E866" s="2" t="n">
-        <v>15239</v>
+        <v>15283</v>
       </c>
       <c r="F866" s="2" t="n">
         <v>9</v>
@@ -70589,7 +70589,7 @@
         <v>94</v>
       </c>
       <c r="E867" s="2" t="n">
-        <v>15251</v>
+        <v>15295</v>
       </c>
       <c r="F867" s="2" t="n">
         <v>8</v>
@@ -70613,7 +70613,7 @@
         <v>94</v>
       </c>
       <c r="E868" s="2" t="n">
-        <v>15261</v>
+        <v>15305</v>
       </c>
       <c r="F868" s="2" t="n">
         <v>8</v>
@@ -70637,7 +70637,7 @@
         <v>94</v>
       </c>
       <c r="E869" s="2" t="n">
-        <v>15272</v>
+        <v>15316</v>
       </c>
       <c r="F869" s="2" t="n">
         <v>9</v>
@@ -70661,7 +70661,7 @@
         <v>94</v>
       </c>
       <c r="E870" s="2" t="n">
-        <v>15283</v>
+        <v>15327</v>
       </c>
       <c r="F870" s="2" t="n">
         <v>8</v>
@@ -70685,7 +70685,7 @@
         <v>94</v>
       </c>
       <c r="E871" s="2" t="n">
-        <v>15294</v>
+        <v>15338</v>
       </c>
       <c r="F871" s="2" t="n">
         <v>8</v>
@@ -70709,7 +70709,7 @@
         <v>94</v>
       </c>
       <c r="E872" s="2" t="n">
-        <v>15304</v>
+        <v>15348</v>
       </c>
       <c r="F872" s="2" t="n">
         <v>8</v>
@@ -70733,7 +70733,7 @@
         <v>94</v>
       </c>
       <c r="E873" s="2" t="n">
-        <v>15315</v>
+        <v>15359</v>
       </c>
       <c r="F873" s="2" t="n">
         <v>8</v>
@@ -70757,7 +70757,7 @@
         <v>94</v>
       </c>
       <c r="E874" s="2" t="n">
-        <v>15325</v>
+        <v>15369</v>
       </c>
       <c r="F874" s="2" t="n">
         <v>8</v>
@@ -70781,7 +70781,7 @@
         <v>94</v>
       </c>
       <c r="E875" s="2" t="n">
-        <v>15336</v>
+        <v>15380</v>
       </c>
       <c r="F875" s="2" t="n">
         <v>8</v>
@@ -70805,7 +70805,7 @@
         <v>94</v>
       </c>
       <c r="E876" s="2" t="n">
-        <v>15346</v>
+        <v>15390</v>
       </c>
       <c r="F876" s="2" t="n">
         <v>6</v>
@@ -70829,7 +70829,7 @@
         <v>94</v>
       </c>
       <c r="E877" s="2" t="n">
-        <v>15355</v>
+        <v>15399</v>
       </c>
       <c r="F877" s="2" t="n">
         <v>7</v>
@@ -70853,7 +70853,7 @@
         <v>94</v>
       </c>
       <c r="E878" s="2" t="n">
-        <v>15364</v>
+        <v>15408</v>
       </c>
       <c r="F878" s="2" t="n">
         <v>8</v>
@@ -70877,7 +70877,7 @@
         <v>94</v>
       </c>
       <c r="E879" s="2" t="n">
-        <v>15375</v>
+        <v>15419</v>
       </c>
       <c r="F879" s="2" t="n">
         <v>8</v>
@@ -70901,7 +70901,7 @@
         <v>94</v>
       </c>
       <c r="E880" s="2" t="n">
-        <v>15385</v>
+        <v>15429</v>
       </c>
       <c r="F880" s="2" t="n">
         <v>9</v>
@@ -70925,7 +70925,7 @@
         <v>94</v>
       </c>
       <c r="E881" s="2" t="n">
-        <v>15397</v>
+        <v>15441</v>
       </c>
       <c r="F881" s="2" t="n">
         <v>7</v>
@@ -70949,7 +70949,7 @@
         <v>94</v>
       </c>
       <c r="E882" s="2" t="n">
-        <v>15406</v>
+        <v>15450</v>
       </c>
       <c r="F882" s="2" t="n">
         <v>9</v>
@@ -70973,7 +70973,7 @@
         <v>94</v>
       </c>
       <c r="E883" s="2" t="n">
-        <v>15418</v>
+        <v>15462</v>
       </c>
       <c r="F883" s="2" t="n">
         <v>8</v>
@@ -70997,7 +70997,7 @@
         <v>94</v>
       </c>
       <c r="E884" s="2" t="n">
-        <v>15428</v>
+        <v>15472</v>
       </c>
       <c r="F884" s="2" t="n">
         <v>6</v>
@@ -71021,7 +71021,7 @@
         <v>94</v>
       </c>
       <c r="E885" s="2" t="n">
-        <v>15437</v>
+        <v>15481</v>
       </c>
       <c r="F885" s="2" t="n">
         <v>8</v>
@@ -71045,7 +71045,7 @@
         <v>94</v>
       </c>
       <c r="E886" s="2" t="n">
-        <v>15447</v>
+        <v>15491</v>
       </c>
       <c r="F886" s="2" t="n">
         <v>9</v>
@@ -71069,7 +71069,7 @@
         <v>94</v>
       </c>
       <c r="E887" s="2" t="n">
-        <v>15459</v>
+        <v>15503</v>
       </c>
       <c r="F887" s="2" t="n">
         <v>7</v>
@@ -71093,7 +71093,7 @@
         <v>94</v>
       </c>
       <c r="E888" s="2" t="n">
-        <v>15468</v>
+        <v>15512</v>
       </c>
       <c r="F888" s="2" t="n">
         <v>8</v>
@@ -71117,7 +71117,7 @@
         <v>94</v>
       </c>
       <c r="E889" s="2" t="n">
-        <v>15479</v>
+        <v>15523</v>
       </c>
       <c r="F889" s="2" t="n">
         <v>7</v>
@@ -71141,7 +71141,7 @@
         <v>94</v>
       </c>
       <c r="E890" s="2" t="n">
-        <v>15488</v>
+        <v>15532</v>
       </c>
       <c r="F890" s="2" t="n">
         <v>7</v>
@@ -71165,7 +71165,7 @@
         <v>94</v>
       </c>
       <c r="E891" s="2" t="n">
-        <v>15498</v>
+        <v>15542</v>
       </c>
       <c r="F891" s="2" t="n">
         <v>8</v>
@@ -71189,7 +71189,7 @@
         <v>94</v>
       </c>
       <c r="E892" s="2" t="n">
-        <v>15508</v>
+        <v>15552</v>
       </c>
       <c r="F892" s="2" t="n">
         <v>9</v>
@@ -71213,7 +71213,7 @@
         <v>94</v>
       </c>
       <c r="E893" s="2" t="n">
-        <v>15520</v>
+        <v>15564</v>
       </c>
       <c r="F893" s="2" t="n">
         <v>8</v>
@@ -71237,7 +71237,7 @@
         <v>94</v>
       </c>
       <c r="E894" s="2" t="n">
-        <v>15530</v>
+        <v>15574</v>
       </c>
       <c r="F894" s="2" t="n">
         <v>6</v>
@@ -71261,7 +71261,7 @@
         <v>94</v>
       </c>
       <c r="E895" s="2" t="n">
-        <v>15539</v>
+        <v>15583</v>
       </c>
       <c r="F895" s="2" t="n">
         <v>7</v>
@@ -71285,7 +71285,7 @@
         <v>94</v>
       </c>
       <c r="E896" s="2" t="n">
-        <v>15548</v>
+        <v>15592</v>
       </c>
       <c r="F896" s="2" t="n">
         <v>8</v>
@@ -71309,7 +71309,7 @@
         <v>94</v>
       </c>
       <c r="E897" s="2" t="n">
-        <v>15558</v>
+        <v>15602</v>
       </c>
       <c r="F897" s="2" t="n">
         <v>7</v>
@@ -71333,7 +71333,7 @@
         <v>94</v>
       </c>
       <c r="E898" s="2" t="n">
-        <v>15567</v>
+        <v>15611</v>
       </c>
       <c r="F898" s="2" t="n">
         <v>8</v>
@@ -71357,7 +71357,7 @@
         <v>94</v>
       </c>
       <c r="E899" s="2" t="n">
-        <v>15577</v>
+        <v>15621</v>
       </c>
       <c r="F899" s="2" t="n">
         <v>8</v>
@@ -71381,7 +71381,7 @@
         <v>94</v>
       </c>
       <c r="E900" s="2" t="n">
-        <v>15588</v>
+        <v>15632</v>
       </c>
       <c r="F900" s="2" t="n">
         <v>7</v>
@@ -71405,7 +71405,7 @@
         <v>94</v>
       </c>
       <c r="E901" s="2" t="n">
-        <v>15597</v>
+        <v>15641</v>
       </c>
       <c r="F901" s="2" t="n">
         <v>7</v>
@@ -71429,7 +71429,7 @@
         <v>94</v>
       </c>
       <c r="E902" s="2" t="n">
-        <v>15607</v>
+        <v>15651</v>
       </c>
       <c r="F902" s="2" t="n">
         <v>7</v>
@@ -71453,7 +71453,7 @@
         <v>94</v>
       </c>
       <c r="E903" s="2" t="n">
-        <v>15616</v>
+        <v>15660</v>
       </c>
       <c r="F903" s="2" t="n">
         <v>8</v>
@@ -71477,7 +71477,7 @@
         <v>94</v>
       </c>
       <c r="E904" s="2" t="n">
-        <v>15627</v>
+        <v>15671</v>
       </c>
       <c r="F904" s="2" t="n">
         <v>8</v>
@@ -71501,7 +71501,7 @@
         <v>94</v>
       </c>
       <c r="E905" s="2" t="n">
-        <v>15637</v>
+        <v>15681</v>
       </c>
       <c r="F905" s="2" t="n">
         <v>8</v>
@@ -71525,7 +71525,7 @@
         <v>94</v>
       </c>
       <c r="E906" s="2" t="n">
-        <v>15648</v>
+        <v>15692</v>
       </c>
       <c r="F906" s="2" t="n">
         <v>8</v>
@@ -71549,7 +71549,7 @@
         <v>94</v>
       </c>
       <c r="E907" s="2" t="n">
-        <v>15658</v>
+        <v>15702</v>
       </c>
       <c r="F907" s="2" t="n">
         <v>9</v>
@@ -71573,7 +71573,7 @@
         <v>94</v>
       </c>
       <c r="E908" s="2" t="n">
-        <v>15670</v>
+        <v>15714</v>
       </c>
       <c r="F908" s="2" t="n">
         <v>9</v>
@@ -71597,7 +71597,7 @@
         <v>94</v>
       </c>
       <c r="E909" s="2" t="n">
-        <v>15681</v>
+        <v>15725</v>
       </c>
       <c r="F909" s="2" t="n">
         <v>9</v>
@@ -71621,7 +71621,7 @@
         <v>94</v>
       </c>
       <c r="E910" s="2" t="n">
-        <v>15693</v>
+        <v>15737</v>
       </c>
       <c r="F910" s="2" t="n">
         <v>9</v>
@@ -71645,7 +71645,7 @@
         <v>94</v>
       </c>
       <c r="E911" s="2" t="n">
-        <v>15704</v>
+        <v>15748</v>
       </c>
       <c r="F911" s="2" t="n">
         <v>8</v>
@@ -71669,7 +71669,7 @@
         <v>94</v>
       </c>
       <c r="E912" s="2" t="n">
-        <v>15715</v>
+        <v>15759</v>
       </c>
       <c r="F912" s="2" t="n">
         <v>7</v>
@@ -71693,7 +71693,7 @@
         <v>94</v>
       </c>
       <c r="E913" s="2" t="n">
-        <v>15724</v>
+        <v>15768</v>
       </c>
       <c r="F913" s="2" t="n">
         <v>8</v>
@@ -71717,7 +71717,7 @@
         <v>94</v>
       </c>
       <c r="E914" s="2" t="n">
-        <v>15735</v>
+        <v>15779</v>
       </c>
       <c r="F914" s="2" t="n">
         <v>7</v>
@@ -71741,7 +71741,7 @@
         <v>94</v>
       </c>
       <c r="E915" s="2" t="n">
-        <v>15744</v>
+        <v>15788</v>
       </c>
       <c r="F915" s="2" t="n">
         <v>7</v>
@@ -71765,7 +71765,7 @@
         <v>94</v>
       </c>
       <c r="E916" s="2" t="n">
-        <v>15753</v>
+        <v>15797</v>
       </c>
       <c r="F916" s="2" t="n">
         <v>6</v>
@@ -71789,7 +71789,7 @@
         <v>94</v>
       </c>
       <c r="E917" s="2" t="n">
-        <v>15762</v>
+        <v>15806</v>
       </c>
       <c r="F917" s="2" t="n">
         <v>5</v>
@@ -71813,7 +71813,7 @@
         <v>94</v>
       </c>
       <c r="E918" s="2" t="n">
-        <v>15769</v>
+        <v>15813</v>
       </c>
       <c r="F918" s="2" t="n">
         <v>7</v>
@@ -71837,7 +71837,7 @@
         <v>94</v>
       </c>
       <c r="E919" s="2" t="n">
-        <v>15778</v>
+        <v>15822</v>
       </c>
       <c r="F919" s="2" t="n">
         <v>6</v>
@@ -71861,7 +71861,7 @@
         <v>94</v>
       </c>
       <c r="E920" s="2" t="n">
-        <v>15787</v>
+        <v>15831</v>
       </c>
       <c r="F920" s="2" t="n">
         <v>7</v>
@@ -71885,7 +71885,7 @@
         <v>94</v>
       </c>
       <c r="E921" s="2" t="n">
-        <v>15796</v>
+        <v>15840</v>
       </c>
       <c r="F921" s="2" t="n">
         <v>8</v>
@@ -71909,7 +71909,7 @@
         <v>94</v>
       </c>
       <c r="E922" s="2" t="n">
-        <v>15807</v>
+        <v>15851</v>
       </c>
       <c r="F922" s="2" t="n">
         <v>7</v>
@@ -71933,7 +71933,7 @@
         <v>94</v>
       </c>
       <c r="E923" s="2" t="n">
-        <v>15816</v>
+        <v>15860</v>
       </c>
       <c r="F923" s="2" t="n">
         <v>14</v>
@@ -71957,7 +71957,7 @@
         <v>94</v>
       </c>
       <c r="E924" s="2" t="n">
-        <v>15833</v>
+        <v>15877</v>
       </c>
       <c r="F924" s="2" t="n">
         <v>7</v>
@@ -71981,7 +71981,7 @@
         <v>94</v>
       </c>
       <c r="E925" s="2" t="n">
-        <v>15842</v>
+        <v>15886</v>
       </c>
       <c r="F925" s="2" t="n">
         <v>8</v>
@@ -72005,7 +72005,7 @@
         <v>94</v>
       </c>
       <c r="E926" s="2" t="n">
-        <v>15853</v>
+        <v>15897</v>
       </c>
       <c r="F926" s="2" t="n">
         <v>6</v>
@@ -72029,7 +72029,7 @@
         <v>94</v>
       </c>
       <c r="E927" s="2" t="n">
-        <v>15861</v>
+        <v>15905</v>
       </c>
       <c r="F927" s="2" t="n">
         <v>7</v>
@@ -72053,7 +72053,7 @@
         <v>94</v>
       </c>
       <c r="E928" s="2" t="n">
-        <v>15870</v>
+        <v>15914</v>
       </c>
       <c r="F928" s="2" t="n">
         <v>5</v>
@@ -72077,7 +72077,7 @@
         <v>94</v>
       </c>
       <c r="E929" s="2" t="n">
-        <v>15878</v>
+        <v>15922</v>
       </c>
       <c r="F929" s="2" t="n">
         <v>7</v>
@@ -72101,7 +72101,7 @@
         <v>94</v>
       </c>
       <c r="E930" s="2" t="n">
-        <v>15887</v>
+        <v>15931</v>
       </c>
       <c r="F930" s="2" t="n">
         <v>7</v>
@@ -72125,7 +72125,7 @@
         <v>94</v>
       </c>
       <c r="E931" s="2" t="n">
-        <v>15897</v>
+        <v>15941</v>
       </c>
       <c r="F931" s="2" t="n">
         <v>8</v>
@@ -72149,7 +72149,7 @@
         <v>94</v>
       </c>
       <c r="E932" s="2" t="n">
-        <v>15907</v>
+        <v>15951</v>
       </c>
       <c r="F932" s="2" t="n">
         <v>8</v>
@@ -72173,7 +72173,7 @@
         <v>94</v>
       </c>
       <c r="E933" s="2" t="n">
-        <v>15918</v>
+        <v>15962</v>
       </c>
       <c r="F933" s="2" t="n">
         <v>7</v>
@@ -72197,7 +72197,7 @@
         <v>94</v>
       </c>
       <c r="E934" s="2" t="n">
-        <v>15927</v>
+        <v>15971</v>
       </c>
       <c r="F934" s="2" t="n">
         <v>7</v>
@@ -72221,7 +72221,7 @@
         <v>94</v>
       </c>
       <c r="E935" s="2" t="n">
-        <v>15936</v>
+        <v>15980</v>
       </c>
       <c r="F935" s="2" t="n">
         <v>7</v>
@@ -72245,7 +72245,7 @@
         <v>94</v>
       </c>
       <c r="E936" s="2" t="n">
-        <v>15945</v>
+        <v>15989</v>
       </c>
       <c r="F936" s="2" t="n">
         <v>5</v>
@@ -72269,7 +72269,7 @@
         <v>94</v>
       </c>
       <c r="E937" s="2" t="n">
-        <v>15952</v>
+        <v>15996</v>
       </c>
       <c r="F937" s="2" t="n">
         <v>15</v>
@@ -72293,7 +72293,7 @@
         <v>94</v>
       </c>
       <c r="E938" s="2" t="n">
-        <v>15970</v>
+        <v>16014</v>
       </c>
       <c r="F938" s="2" t="n">
         <v>15</v>
@@ -72317,7 +72317,7 @@
         <v>94</v>
       </c>
       <c r="E939" s="2" t="n">
-        <v>15988</v>
+        <v>16032</v>
       </c>
       <c r="F939" s="2" t="n">
         <v>8</v>
@@ -72341,7 +72341,7 @@
         <v>94</v>
       </c>
       <c r="E940" s="2" t="n">
-        <v>15998</v>
+        <v>16042</v>
       </c>
       <c r="F940" s="2" t="n">
         <v>7</v>
@@ -72365,7 +72365,7 @@
         <v>94</v>
       </c>
       <c r="E941" s="2" t="n">
-        <v>16008</v>
+        <v>16052</v>
       </c>
       <c r="F941" s="2" t="n">
         <v>6</v>
@@ -72389,7 +72389,7 @@
         <v>94</v>
       </c>
       <c r="E942" s="2" t="n">
-        <v>16016</v>
+        <v>16060</v>
       </c>
       <c r="F942" s="2" t="n">
         <v>6</v>
@@ -72413,7 +72413,7 @@
         <v>94</v>
       </c>
       <c r="E943" s="2" t="n">
-        <v>16024</v>
+        <v>16068</v>
       </c>
       <c r="F943" s="2" t="n">
         <v>7</v>
@@ -72437,7 +72437,7 @@
         <v>94</v>
       </c>
       <c r="E944" s="2" t="n">
-        <v>16034</v>
+        <v>16078</v>
       </c>
       <c r="F944" s="2" t="n">
         <v>4</v>
@@ -72461,7 +72461,7 @@
         <v>94</v>
       </c>
       <c r="E945" s="2" t="n">
-        <v>16040</v>
+        <v>16084</v>
       </c>
       <c r="F945" s="2" t="n">
         <v>6</v>
@@ -72485,7 +72485,7 @@
         <v>94</v>
       </c>
       <c r="E946" s="2" t="n">
-        <v>16048</v>
+        <v>16092</v>
       </c>
       <c r="F946" s="2" t="n">
         <v>7</v>
@@ -72509,7 +72509,7 @@
         <v>94</v>
       </c>
       <c r="E947" s="2" t="n">
-        <v>16058</v>
+        <v>16102</v>
       </c>
       <c r="F947" s="2" t="n">
         <v>6</v>
@@ -72533,7 +72533,7 @@
         <v>94</v>
       </c>
       <c r="E948" s="2" t="n">
-        <v>16066</v>
+        <v>16110</v>
       </c>
       <c r="F948" s="2" t="n">
         <v>9</v>
@@ -72557,7 +72557,7 @@
         <v>94</v>
       </c>
       <c r="E949" s="2" t="n">
-        <v>16078</v>
+        <v>16122</v>
       </c>
       <c r="F949" s="2" t="n">
         <v>6</v>
@@ -72581,7 +72581,7 @@
         <v>94</v>
       </c>
       <c r="E950" s="2" t="n">
-        <v>16086</v>
+        <v>16130</v>
       </c>
       <c r="F950" s="2" t="n">
         <v>7</v>
@@ -72605,7 +72605,7 @@
         <v>94</v>
       </c>
       <c r="E951" s="2" t="n">
-        <v>16095</v>
+        <v>16139</v>
       </c>
       <c r="F951" s="2" t="n">
         <v>6</v>
@@ -72629,7 +72629,7 @@
         <v>94</v>
       </c>
       <c r="E952" s="2" t="n">
-        <v>16103</v>
+        <v>16147</v>
       </c>
       <c r="F952" s="2" t="n">
         <v>6</v>
@@ -72653,7 +72653,7 @@
         <v>94</v>
       </c>
       <c r="E953" s="2" t="n">
-        <v>16111</v>
+        <v>16155</v>
       </c>
       <c r="F953" s="2" t="n">
         <v>7</v>
@@ -72677,7 +72677,7 @@
         <v>94</v>
       </c>
       <c r="E954" s="2" t="n">
-        <v>16121</v>
+        <v>16165</v>
       </c>
       <c r="F954" s="2" t="n">
         <v>7</v>
@@ -72701,7 +72701,7 @@
         <v>94</v>
       </c>
       <c r="E955" s="2" t="n">
-        <v>16130</v>
+        <v>16174</v>
       </c>
       <c r="F955" s="2" t="n">
         <v>7</v>
@@ -72725,7 +72725,7 @@
         <v>94</v>
       </c>
       <c r="E956" s="2" t="n">
-        <v>16139</v>
+        <v>16183</v>
       </c>
       <c r="F956" s="2" t="n">
         <v>7</v>
@@ -72749,7 +72749,7 @@
         <v>94</v>
       </c>
       <c r="E957" s="2" t="n">
-        <v>16148</v>
+        <v>16192</v>
       </c>
       <c r="F957" s="2" t="n">
         <v>7</v>
@@ -72773,7 +72773,7 @@
         <v>94</v>
       </c>
       <c r="E958" s="2" t="n">
-        <v>16157</v>
+        <v>16201</v>
       </c>
       <c r="F958" s="2" t="n">
         <v>5</v>
@@ -72797,7 +72797,7 @@
         <v>94</v>
       </c>
       <c r="E959" s="2" t="n">
-        <v>16165</v>
+        <v>16209</v>
       </c>
       <c r="F959" s="2" t="n">
         <v>5</v>
@@ -72821,7 +72821,7 @@
         <v>94</v>
       </c>
       <c r="E960" s="2" t="n">
-        <v>16172</v>
+        <v>16216</v>
       </c>
       <c r="F960" s="2" t="n">
         <v>5</v>
@@ -72845,7 +72845,7 @@
         <v>94</v>
       </c>
       <c r="E961" s="2" t="n">
-        <v>16180</v>
+        <v>16224</v>
       </c>
       <c r="F961" s="2" t="n">
         <v>6</v>
@@ -72869,7 +72869,7 @@
         <v>94</v>
       </c>
       <c r="E962" s="2" t="n">
-        <v>16188</v>
+        <v>16232</v>
       </c>
       <c r="F962" s="2" t="n">
         <v>7</v>
@@ -72893,7 +72893,7 @@
         <v>94</v>
       </c>
       <c r="E963" s="2" t="n">
-        <v>16197</v>
+        <v>16241</v>
       </c>
       <c r="F963" s="2" t="n">
         <v>6</v>
@@ -72917,7 +72917,7 @@
         <v>94</v>
       </c>
       <c r="E964" s="2" t="n">
-        <v>16205</v>
+        <v>16249</v>
       </c>
       <c r="F964" s="2" t="n">
         <v>7</v>
@@ -72941,7 +72941,7 @@
         <v>94</v>
       </c>
       <c r="E965" s="2" t="n">
-        <v>16214</v>
+        <v>16258</v>
       </c>
       <c r="F965" s="2" t="n">
         <v>8</v>
@@ -72965,7 +72965,7 @@
         <v>94</v>
       </c>
       <c r="E966" s="2" t="n">
-        <v>16225</v>
+        <v>16269</v>
       </c>
       <c r="F966" s="2" t="n">
         <v>7</v>
@@ -72989,7 +72989,7 @@
         <v>94</v>
       </c>
       <c r="E967" s="2" t="n">
-        <v>16234</v>
+        <v>16278</v>
       </c>
       <c r="F967" s="2" t="n">
         <v>6</v>
@@ -73013,7 +73013,7 @@
         <v>94</v>
       </c>
       <c r="E968" s="2" t="n">
-        <v>16243</v>
+        <v>16287</v>
       </c>
       <c r="F968" s="2" t="n">
         <v>7</v>
@@ -73037,7 +73037,7 @@
         <v>94</v>
       </c>
       <c r="E969" s="2" t="n">
-        <v>16252</v>
+        <v>16296</v>
       </c>
       <c r="F969" s="2" t="n">
         <v>6</v>
@@ -73061,7 +73061,7 @@
         <v>94</v>
       </c>
       <c r="E970" s="2" t="n">
-        <v>16260</v>
+        <v>16304</v>
       </c>
       <c r="F970" s="2" t="n">
         <v>7</v>
@@ -73085,7 +73085,7 @@
         <v>94</v>
       </c>
       <c r="E971" s="2" t="n">
-        <v>16270</v>
+        <v>16314</v>
       </c>
       <c r="F971" s="2" t="n">
         <v>7</v>
@@ -73109,7 +73109,7 @@
         <v>94</v>
       </c>
       <c r="E972" s="2" t="n">
-        <v>16279</v>
+        <v>16323</v>
       </c>
       <c r="F972" s="2" t="n">
         <v>3</v>
@@ -73133,7 +73133,7 @@
         <v>94</v>
       </c>
       <c r="E973" s="2" t="n">
-        <v>16285</v>
+        <v>16329</v>
       </c>
       <c r="F973" s="2" t="n">
         <v>2</v>
@@ -73157,7 +73157,7 @@
         <v>94</v>
       </c>
       <c r="E974" s="2" t="n">
-        <v>16289</v>
+        <v>16333</v>
       </c>
       <c r="F974" s="2" t="n">
         <v>5</v>
@@ -73181,7 +73181,7 @@
         <v>94</v>
       </c>
       <c r="E975" s="2" t="n">
-        <v>16296</v>
+        <v>16340</v>
       </c>
       <c r="F975" s="2" t="n">
         <v>13</v>
@@ -73205,7 +73205,7 @@
         <v>94</v>
       </c>
       <c r="E976" s="2" t="n">
-        <v>16312</v>
+        <v>16356</v>
       </c>
       <c r="F976" s="2" t="n">
         <v>24</v>
@@ -73229,7 +73229,7 @@
         <v>94</v>
       </c>
       <c r="E977" s="2" t="n">
-        <v>16339</v>
+        <v>16383</v>
       </c>
       <c r="F977" s="2" t="n">
         <v>23</v>
@@ -73253,7 +73253,7 @@
         <v>94</v>
       </c>
       <c r="E978" s="2" t="n">
-        <v>16366</v>
+        <v>16410</v>
       </c>
       <c r="F978" s="2" t="n">
         <v>19</v>
@@ -73277,7 +73277,7 @@
         <v>94</v>
       </c>
       <c r="E979" s="2" t="n">
-        <v>16388</v>
+        <v>16432</v>
       </c>
       <c r="F979" s="2" t="n">
         <v>18</v>
@@ -73301,7 +73301,7 @@
         <v>94</v>
       </c>
       <c r="E980" s="2" t="n">
-        <v>16409</v>
+        <v>16453</v>
       </c>
       <c r="F980" s="2" t="n">
         <v>19</v>

--- a/알바로_부작_화_목록.xlsx
+++ b/알바로_부작_화_목록.xlsx
@@ -21279,7 +21279,7 @@
         <v>11941</v>
       </c>
       <c r="F657" s="13" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G657" s="15" t="inlineStr">
         <is>
@@ -21304,10 +21304,10 @@
         </is>
       </c>
       <c r="E658" s="13" t="n">
-        <v>12008</v>
+        <v>12005</v>
       </c>
       <c r="F658" s="13" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G658" s="15" t="inlineStr">
         <is>
@@ -21332,10 +21332,10 @@
         </is>
       </c>
       <c r="E659" s="13" t="n">
-        <v>12029</v>
+        <v>12032</v>
       </c>
       <c r="F659" s="13" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G659" s="15" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         </is>
       </c>
       <c r="E660" s="13" t="n">
-        <v>12073</v>
+        <v>12075</v>
       </c>
       <c r="F660" s="13" t="n">
         <v>47</v>
@@ -21388,7 +21388,7 @@
         </is>
       </c>
       <c r="E661" s="13" t="n">
-        <v>12125</v>
+        <v>12127</v>
       </c>
       <c r="F661" s="13" t="n">
         <v>40</v>
@@ -21416,7 +21416,7 @@
         </is>
       </c>
       <c r="E662" s="13" t="n">
-        <v>12169</v>
+        <v>12171</v>
       </c>
       <c r="F662" s="13" t="n">
         <v>14</v>
@@ -21444,7 +21444,7 @@
         </is>
       </c>
       <c r="E663" s="13" t="n">
-        <v>12185</v>
+        <v>12187</v>
       </c>
       <c r="F663" s="13" t="n">
         <v>12</v>
@@ -21472,7 +21472,7 @@
         </is>
       </c>
       <c r="E664" s="13" t="n">
-        <v>12200</v>
+        <v>12202</v>
       </c>
       <c r="F664" s="13" t="n">
         <v>12</v>
@@ -21500,7 +21500,7 @@
         </is>
       </c>
       <c r="E665" s="13" t="n">
-        <v>12215</v>
+        <v>12217</v>
       </c>
       <c r="F665" s="13" t="n">
         <v>12</v>
@@ -21528,7 +21528,7 @@
         </is>
       </c>
       <c r="E666" s="13" t="n">
-        <v>12230</v>
+        <v>12232</v>
       </c>
       <c r="F666" s="13" t="n">
         <v>12</v>
@@ -21556,7 +21556,7 @@
         </is>
       </c>
       <c r="E667" s="13" t="n">
-        <v>12244</v>
+        <v>12246</v>
       </c>
       <c r="F667" s="13" t="n">
         <v>12</v>
@@ -21584,7 +21584,7 @@
         </is>
       </c>
       <c r="E668" s="13" t="n">
-        <v>12258</v>
+        <v>12260</v>
       </c>
       <c r="F668" s="13" t="n">
         <v>10</v>
@@ -21612,10 +21612,10 @@
         </is>
       </c>
       <c r="E669" s="13" t="n">
-        <v>12271</v>
+        <v>12273</v>
       </c>
       <c r="F669" s="13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G669" s="15" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         </is>
       </c>
       <c r="E670" s="13" t="n">
-        <v>12287</v>
+        <v>12288</v>
       </c>
       <c r="F670" s="13" t="n">
         <v>12</v>
@@ -21668,7 +21668,7 @@
         </is>
       </c>
       <c r="E671" s="13" t="n">
-        <v>12301</v>
+        <v>12302</v>
       </c>
       <c r="F671" s="13" t="n">
         <v>13</v>
@@ -21696,10 +21696,10 @@
         </is>
       </c>
       <c r="E672" s="13" t="n">
-        <v>12316</v>
+        <v>12317</v>
       </c>
       <c r="F672" s="13" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G672" s="15" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>12398</v>
       </c>
       <c r="F673" s="13" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G673" s="15" t="inlineStr">
         <is>
@@ -21752,10 +21752,10 @@
         </is>
       </c>
       <c r="E674" s="13" t="n">
-        <v>12528</v>
+        <v>12527</v>
       </c>
       <c r="F674" s="13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G674" s="15" t="inlineStr">
         <is>
@@ -21780,10 +21780,10 @@
         </is>
       </c>
       <c r="E675" s="13" t="n">
-        <v>12578</v>
+        <v>12576</v>
       </c>
       <c r="F675" s="13" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G675" s="15" t="inlineStr">
         <is>
@@ -21808,10 +21808,10 @@
         </is>
       </c>
       <c r="E676" s="13" t="n">
-        <v>12648</v>
+        <v>12643</v>
       </c>
       <c r="F676" s="13" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G676" s="15" t="inlineStr">
         <is>
@@ -21836,10 +21836,10 @@
         </is>
       </c>
       <c r="E677" s="13" t="n">
-        <v>12707</v>
+        <v>12700</v>
       </c>
       <c r="F677" s="13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G677" s="15" t="inlineStr">
         <is>
@@ -21864,10 +21864,10 @@
         </is>
       </c>
       <c r="E678" s="13" t="n">
-        <v>12718</v>
+        <v>12713</v>
       </c>
       <c r="F678" s="13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G678" s="15" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         </is>
       </c>
       <c r="E679" s="13" t="n">
-        <v>12732</v>
+        <v>12726</v>
       </c>
       <c r="F679" s="13" t="n">
         <v>9</v>
@@ -21920,7 +21920,7 @@
         </is>
       </c>
       <c r="E680" s="13" t="n">
-        <v>12743</v>
+        <v>12737</v>
       </c>
       <c r="F680" s="13" t="n">
         <v>26</v>
@@ -21948,10 +21948,10 @@
         </is>
       </c>
       <c r="E681" s="13" t="n">
-        <v>12773</v>
+        <v>12767</v>
       </c>
       <c r="F681" s="13" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G681" s="15" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         </is>
       </c>
       <c r="E682" s="13" t="n">
-        <v>12804</v>
+        <v>12796</v>
       </c>
       <c r="F682" s="13" t="n">
         <v>18</v>
@@ -22004,10 +22004,10 @@
         </is>
       </c>
       <c r="E683" s="13" t="n">
-        <v>12825</v>
+        <v>12817</v>
       </c>
       <c r="F683" s="13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G683" s="15" t="inlineStr">
         <is>
@@ -22032,7 +22032,7 @@
         </is>
       </c>
       <c r="E684" s="13" t="n">
-        <v>12851</v>
+        <v>12842</v>
       </c>
       <c r="F684" s="13" t="n">
         <v>19</v>
@@ -22060,10 +22060,10 @@
         </is>
       </c>
       <c r="E685" s="13" t="n">
-        <v>12873</v>
+        <v>12864</v>
       </c>
       <c r="F685" s="13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G685" s="15" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         </is>
       </c>
       <c r="E686" s="13" t="n">
-        <v>12898</v>
+        <v>12888</v>
       </c>
       <c r="F686" s="13" t="n">
         <v>18</v>
@@ -22116,7 +22116,7 @@
         </is>
       </c>
       <c r="E687" s="13" t="n">
-        <v>12919</v>
+        <v>12909</v>
       </c>
       <c r="F687" s="13" t="n">
         <v>18</v>
@@ -22144,7 +22144,7 @@
         </is>
       </c>
       <c r="E688" s="13" t="n">
-        <v>12940</v>
+        <v>12930</v>
       </c>
       <c r="F688" s="13" t="n">
         <v>17</v>
@@ -22172,7 +22172,7 @@
         </is>
       </c>
       <c r="E689" s="13" t="n">
-        <v>12960</v>
+        <v>12950</v>
       </c>
       <c r="F689" s="13" t="n">
         <v>11</v>
@@ -22200,14 +22200,14 @@
         </is>
       </c>
       <c r="E690" s="13" t="n">
-        <v>12973</v>
+        <v>12963</v>
       </c>
       <c r="F690" s="13" t="n">
         <v>18</v>
       </c>
       <c r="G690" s="15" t="inlineStr">
         <is>
-          <t>새로운 세션. 빅토르가 '마레아 작전'을 설명합니다 — 북방의 교향곡과 바벨탑이 인프라라면, 마레아는 특정 선거를 겨냥해 그 인프라 전체를 가동시키는 실행 단계입니다. 특정 정당이나 후 보는 언급하지 않고, 기법 자체에 초점을 맞춥니다.</t>
+          <t>새로운 세션. 빅토르가 '마레아 작전'을 설명합니다 — 북방의 교향곡과 바벨탑이 인프라라면, 마레아는 특정 선거를 겨냥해 그 인프라 전체를 가동시키는 실행 단계입니다. 특정 정당이나 후보는 언급하지 않고, 기법 자체에 초점을 맞춥니다.</t>
         </is>
       </c>
     </row>
@@ -22228,10 +22228,10 @@
         </is>
       </c>
       <c r="E691" s="13" t="n">
-        <v>12996</v>
+        <v>12985</v>
       </c>
       <c r="F691" s="13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G691" s="15" t="inlineStr">
         <is>
@@ -22256,7 +22256,7 @@
         </is>
       </c>
       <c r="E692" s="13" t="n">
-        <v>13018</v>
+        <v>13006</v>
       </c>
       <c r="F692" s="13" t="n">
         <v>19</v>
@@ -22284,10 +22284,10 @@
         </is>
       </c>
       <c r="E693" s="13" t="n">
-        <v>13040</v>
+        <v>13028</v>
       </c>
       <c r="F693" s="13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G693" s="15" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         </is>
       </c>
       <c r="E694" s="13" t="n">
-        <v>13062</v>
+        <v>13049</v>
       </c>
       <c r="F694" s="13" t="n">
         <v>18</v>
@@ -22340,7 +22340,7 @@
         </is>
       </c>
       <c r="E695" s="13" t="n">
-        <v>13083</v>
+        <v>13070</v>
       </c>
       <c r="F695" s="13" t="n">
         <v>18</v>
@@ -22368,7 +22368,7 @@
         </is>
       </c>
       <c r="E696" s="13" t="n">
-        <v>13104</v>
+        <v>13091</v>
       </c>
       <c r="F696" s="13" t="n">
         <v>18</v>
@@ -22396,10 +22396,10 @@
         </is>
       </c>
       <c r="E697" s="13" t="n">
-        <v>13125</v>
+        <v>13112</v>
       </c>
       <c r="F697" s="13" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G697" s="15" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         </is>
       </c>
       <c r="E698" s="13" t="n">
-        <v>13145</v>
+        <v>13134</v>
       </c>
       <c r="F698" s="13" t="n">
         <v>18</v>
@@ -22452,7 +22452,7 @@
         </is>
       </c>
       <c r="E699" s="13" t="n">
-        <v>13166</v>
+        <v>13155</v>
       </c>
       <c r="F699" s="13" t="n">
         <v>17</v>
@@ -22480,7 +22480,7 @@
         </is>
       </c>
       <c r="E700" s="13" t="n">
-        <v>13186</v>
+        <v>13175</v>
       </c>
       <c r="F700" s="13" t="n">
         <v>19</v>
@@ -22508,14 +22508,14 @@
         </is>
       </c>
       <c r="E701" s="13" t="n">
-        <v>13208</v>
+        <v>13197</v>
       </c>
       <c r="F701" s="13" t="n">
         <v>25</v>
       </c>
       <c r="G701" s="15" t="inlineStr">
         <is>
-          <t>새로운 세션. 빅토르가 '돈키호테 작전'을 밝히기 전, 유독 무거운 표정으로 망설입니다. 알바로 가 지금까지 겪었던 '아슬아슬한 추적'들이 사실은 의도된 기만이었다는 사실이 드러나기 시작 합니다.</t>
+          <t>새로운 세션. 빅토르가 '돈키호테 작전'을 밝히기 전, 유독 무거운 표정으로 망설입니다. 알바로가 지금까지 겪었던 '아슬아슬한 추적'들이 사실은 의도된 기만이었다는 사실이 드러나기 시작 합니다.</t>
         </is>
       </c>
     </row>
@@ -22536,10 +22536,10 @@
         </is>
       </c>
       <c r="E702" s="13" t="n">
-        <v>13237</v>
+        <v>13225</v>
       </c>
       <c r="F702" s="13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G702" s="15" t="inlineStr">
         <is>
@@ -22564,10 +22564,10 @@
         </is>
       </c>
       <c r="E703" s="13" t="n">
-        <v>13257</v>
+        <v>13246</v>
       </c>
       <c r="F703" s="13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G703" s="15" t="inlineStr">
         <is>
@@ -22592,7 +22592,7 @@
         </is>
       </c>
       <c r="E704" s="13" t="n">
-        <v>13275</v>
+        <v>13263</v>
       </c>
       <c r="F704" s="13" t="n">
         <v>20</v>
@@ -22620,10 +22620,10 @@
         </is>
       </c>
       <c r="E705" s="13" t="n">
-        <v>13298</v>
+        <v>13286</v>
       </c>
       <c r="F705" s="13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G705" s="15" t="inlineStr">
         <is>
@@ -22648,10 +22648,10 @@
         </is>
       </c>
       <c r="E706" s="13" t="n">
-        <v>13318</v>
+        <v>13305</v>
       </c>
       <c r="F706" s="13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G706" s="15" t="inlineStr">
         <is>
@@ -22676,7 +22676,7 @@
         </is>
       </c>
       <c r="E707" s="13" t="n">
-        <v>13339</v>
+        <v>13325</v>
       </c>
       <c r="F707" s="13" t="n">
         <v>18</v>
@@ -22704,7 +22704,7 @@
         </is>
       </c>
       <c r="E708" s="13" t="n">
-        <v>13360</v>
+        <v>13346</v>
       </c>
       <c r="F708" s="13" t="n">
         <v>18</v>
@@ -22732,7 +22732,7 @@
         </is>
       </c>
       <c r="E709" s="13" t="n">
-        <v>13381</v>
+        <v>13367</v>
       </c>
       <c r="F709" s="13" t="n">
         <v>17</v>
@@ -22760,7 +22760,7 @@
         </is>
       </c>
       <c r="E710" s="13" t="n">
-        <v>13401</v>
+        <v>13387</v>
       </c>
       <c r="F710" s="13" t="n">
         <v>26</v>
@@ -22788,7 +22788,7 @@
         </is>
       </c>
       <c r="E711" s="13" t="n">
-        <v>13430</v>
+        <v>13416</v>
       </c>
       <c r="F711" s="13" t="n">
         <v>28</v>
@@ -22816,10 +22816,10 @@
         </is>
       </c>
       <c r="E712" s="13" t="n">
-        <v>13461</v>
+        <v>13447</v>
       </c>
       <c r="F712" s="13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G712" s="15" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         </is>
       </c>
       <c r="E713" s="13" t="n">
-        <v>13481</v>
+        <v>13466</v>
       </c>
       <c r="F713" s="13" t="n">
         <v>16</v>
@@ -22872,7 +22872,7 @@
         </is>
       </c>
       <c r="E714" s="13" t="n">
-        <v>13500</v>
+        <v>13485</v>
       </c>
       <c r="F714" s="13" t="n">
         <v>16</v>
@@ -22900,10 +22900,10 @@
         </is>
       </c>
       <c r="E715" s="13" t="n">
-        <v>13519</v>
+        <v>13504</v>
       </c>
       <c r="F715" s="13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G715" s="15" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         </is>
       </c>
       <c r="E716" s="13" t="n">
-        <v>13543</v>
+        <v>13527</v>
       </c>
       <c r="F716" s="13" t="n">
         <v>17</v>
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="E717" s="13" t="n">
-        <v>13563</v>
+        <v>13547</v>
       </c>
       <c r="F717" s="13" t="n">
         <v>16</v>
@@ -22984,7 +22984,7 @@
         </is>
       </c>
       <c r="E718" s="13" t="n">
-        <v>13582</v>
+        <v>13566</v>
       </c>
       <c r="F718" s="13" t="n">
         <v>17</v>
@@ -23012,10 +23012,10 @@
         </is>
       </c>
       <c r="E719" s="13" t="n">
-        <v>13602</v>
+        <v>13586</v>
       </c>
       <c r="F719" s="13" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G719" s="15" t="inlineStr">
         <is>
@@ -23040,10 +23040,10 @@
         </is>
       </c>
       <c r="E720" s="13" t="n">
-        <v>13620</v>
+        <v>13606</v>
       </c>
       <c r="F720" s="13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G720" s="15" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         </is>
       </c>
       <c r="E721" s="13" t="n">
-        <v>13634</v>
+        <v>13619</v>
       </c>
       <c r="F721" s="13" t="n">
         <v>16</v>
@@ -23096,7 +23096,7 @@
         </is>
       </c>
       <c r="E722" s="13" t="n">
-        <v>13653</v>
+        <v>13638</v>
       </c>
       <c r="F722" s="13" t="n">
         <v>17</v>
@@ -23124,7 +23124,7 @@
         </is>
       </c>
       <c r="E723" s="13" t="n">
-        <v>13673</v>
+        <v>13658</v>
       </c>
       <c r="F723" s="13" t="n">
         <v>14</v>
@@ -23152,7 +23152,7 @@
         </is>
       </c>
       <c r="E724" s="13" t="n">
-        <v>13690</v>
+        <v>13675</v>
       </c>
       <c r="F724" s="13" t="n">
         <v>18</v>
@@ -23180,7 +23180,7 @@
         </is>
       </c>
       <c r="E725" s="13" t="n">
-        <v>13711</v>
+        <v>13696</v>
       </c>
       <c r="F725" s="13" t="n">
         <v>17</v>
@@ -23208,7 +23208,7 @@
         </is>
       </c>
       <c r="E726" s="13" t="n">
-        <v>13731</v>
+        <v>13716</v>
       </c>
       <c r="F726" s="13" t="n">
         <v>15</v>
@@ -23236,7 +23236,7 @@
         </is>
       </c>
       <c r="E727" s="13" t="n">
-        <v>13749</v>
+        <v>13734</v>
       </c>
       <c r="F727" s="13" t="n">
         <v>8</v>
@@ -23264,7 +23264,7 @@
         </is>
       </c>
       <c r="E728" s="13" t="n">
-        <v>13759</v>
+        <v>13744</v>
       </c>
       <c r="F728" s="13" t="n">
         <v>14</v>
@@ -23292,10 +23292,10 @@
         </is>
       </c>
       <c r="E729" s="13" t="n">
-        <v>13776</v>
+        <v>13761</v>
       </c>
       <c r="F729" s="13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G729" s="17" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         </is>
       </c>
       <c r="E730" s="13" t="n">
-        <v>13796</v>
+        <v>13781</v>
       </c>
       <c r="F730" s="13" t="n">
         <v>17</v>
@@ -23348,7 +23348,7 @@
         </is>
       </c>
       <c r="E731" s="13" t="n">
-        <v>13816</v>
+        <v>13801</v>
       </c>
       <c r="F731" s="13" t="n">
         <v>16</v>
@@ -23376,7 +23376,7 @@
         </is>
       </c>
       <c r="E732" s="13" t="n">
-        <v>13835</v>
+        <v>13821</v>
       </c>
       <c r="F732" s="13" t="n">
         <v>7</v>
@@ -23404,7 +23404,7 @@
         </is>
       </c>
       <c r="E733" s="13" t="n">
-        <v>13844</v>
+        <v>13830</v>
       </c>
       <c r="F733" s="13" t="n">
         <v>9</v>
@@ -23432,7 +23432,7 @@
         </is>
       </c>
       <c r="E734" s="13" t="n">
-        <v>13856</v>
+        <v>13842</v>
       </c>
       <c r="F734" s="13" t="n">
         <v>10</v>
@@ -23460,10 +23460,10 @@
         </is>
       </c>
       <c r="E735" s="13" t="n">
-        <v>13868</v>
+        <v>13854</v>
       </c>
       <c r="F735" s="13" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G735" s="15" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         </is>
       </c>
       <c r="E736" s="13" t="n">
-        <v>13901</v>
+        <v>13885</v>
       </c>
       <c r="F736" s="13" t="n">
         <v>17</v>
@@ -23516,10 +23516,10 @@
         </is>
       </c>
       <c r="E737" s="13" t="n">
-        <v>13921</v>
+        <v>13905</v>
       </c>
       <c r="F737" s="13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G737" s="15" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         </is>
       </c>
       <c r="E738" s="13" t="n">
-        <v>13940</v>
+        <v>13926</v>
       </c>
       <c r="F738" s="13" t="n">
         <v>18</v>
@@ -23572,7 +23572,7 @@
         </is>
       </c>
       <c r="E739" s="13" t="n">
-        <v>13961</v>
+        <v>13947</v>
       </c>
       <c r="F739" s="13" t="n">
         <v>11</v>
@@ -23600,7 +23600,7 @@
         </is>
       </c>
       <c r="E740" s="13" t="n">
-        <v>13974</v>
+        <v>13960</v>
       </c>
       <c r="F740" s="13" t="n">
         <v>18</v>
@@ -23628,7 +23628,7 @@
         </is>
       </c>
       <c r="E741" s="13" t="n">
-        <v>13995</v>
+        <v>13981</v>
       </c>
       <c r="F741" s="13" t="n">
         <v>9</v>
@@ -23656,7 +23656,7 @@
         </is>
       </c>
       <c r="E742" s="13" t="n">
-        <v>14007</v>
+        <v>13993</v>
       </c>
       <c r="F742" s="13" t="n">
         <v>10</v>
@@ -23684,7 +23684,7 @@
         </is>
       </c>
       <c r="E743" s="13" t="n">
-        <v>14019</v>
+        <v>14005</v>
       </c>
       <c r="F743" s="13" t="n">
         <v>10</v>
@@ -23712,10 +23712,10 @@
         </is>
       </c>
       <c r="E744" s="13" t="n">
-        <v>14032</v>
+        <v>14018</v>
       </c>
       <c r="F744" s="13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G744" s="15" t="inlineStr">
         <is>
@@ -23740,10 +23740,10 @@
         </is>
       </c>
       <c r="E745" s="13" t="n">
-        <v>14055</v>
+        <v>14042</v>
       </c>
       <c r="F745" s="13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G745" s="15" t="inlineStr">
         <is>
@@ -23768,7 +23768,7 @@
         </is>
       </c>
       <c r="E746" s="13" t="n">
-        <v>14067</v>
+        <v>14056</v>
       </c>
       <c r="F746" s="13" t="n">
         <v>9</v>
@@ -23796,7 +23796,7 @@
         </is>
       </c>
       <c r="E747" s="13" t="n">
-        <v>14078</v>
+        <v>14067</v>
       </c>
       <c r="F747" s="13" t="n">
         <v>10</v>
@@ -23824,10 +23824,10 @@
         </is>
       </c>
       <c r="E748" s="13" t="n">
-        <v>14091</v>
+        <v>14080</v>
       </c>
       <c r="F748" s="13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G748" s="15" t="inlineStr">
         <is>
@@ -23852,10 +23852,10 @@
         </is>
       </c>
       <c r="E749" s="13" t="n">
-        <v>14105</v>
+        <v>14093</v>
       </c>
       <c r="F749" s="13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G749" s="15" t="inlineStr">
         <is>
@@ -23880,7 +23880,7 @@
         </is>
       </c>
       <c r="E750" s="13" t="n">
-        <v>14136</v>
+        <v>14125</v>
       </c>
       <c r="F750" s="13" t="n">
         <v>16</v>
@@ -23908,7 +23908,7 @@
         </is>
       </c>
       <c r="E751" s="13" t="n">
-        <v>14155</v>
+        <v>14144</v>
       </c>
       <c r="F751" s="13" t="n">
         <v>15</v>
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="E752" s="13" t="n">
-        <v>14173</v>
+        <v>14162</v>
       </c>
       <c r="F752" s="13" t="n">
         <v>15</v>
@@ -23964,7 +23964,7 @@
         </is>
       </c>
       <c r="E753" s="13" t="n">
-        <v>14191</v>
+        <v>14181</v>
       </c>
       <c r="F753" s="13" t="n">
         <v>9</v>
@@ -23992,7 +23992,7 @@
         </is>
       </c>
       <c r="E754" s="13" t="n">
-        <v>14203</v>
+        <v>14193</v>
       </c>
       <c r="F754" s="13" t="n">
         <v>15</v>
@@ -24020,7 +24020,7 @@
         </is>
       </c>
       <c r="E755" s="13" t="n">
-        <v>14221</v>
+        <v>14211</v>
       </c>
       <c r="F755" s="13" t="n">
         <v>8</v>
@@ -24048,7 +24048,7 @@
         </is>
       </c>
       <c r="E756" s="13" t="n">
-        <v>14231</v>
+        <v>14221</v>
       </c>
       <c r="F756" s="13" t="n">
         <v>9</v>
@@ -24076,7 +24076,7 @@
         </is>
       </c>
       <c r="E757" s="13" t="n">
-        <v>14245</v>
+        <v>14235</v>
       </c>
       <c r="F757" s="13" t="n">
         <v>17</v>
@@ -24104,7 +24104,7 @@
         </is>
       </c>
       <c r="E758" s="13" t="n">
-        <v>14265</v>
+        <v>14255</v>
       </c>
       <c r="F758" s="13" t="n">
         <v>7</v>
@@ -24132,7 +24132,7 @@
         </is>
       </c>
       <c r="E759" s="13" t="n">
-        <v>14274</v>
+        <v>14264</v>
       </c>
       <c r="F759" s="13" t="n">
         <v>10</v>
@@ -24160,7 +24160,7 @@
         </is>
       </c>
       <c r="E760" s="13" t="n">
-        <v>14287</v>
+        <v>14277</v>
       </c>
       <c r="F760" s="13" t="n">
         <v>8</v>
@@ -24188,7 +24188,7 @@
         </is>
       </c>
       <c r="E761" s="13" t="n">
-        <v>14298</v>
+        <v>14288</v>
       </c>
       <c r="F761" s="13" t="n">
         <v>10</v>
@@ -24216,7 +24216,7 @@
         </is>
       </c>
       <c r="E762" s="13" t="n">
-        <v>14310</v>
+        <v>14300</v>
       </c>
       <c r="F762" s="13" t="n">
         <v>9</v>
@@ -24244,7 +24244,7 @@
         </is>
       </c>
       <c r="E763" s="13" t="n">
-        <v>14322</v>
+        <v>14312</v>
       </c>
       <c r="F763" s="13" t="n">
         <v>9</v>
@@ -24272,7 +24272,7 @@
         </is>
       </c>
       <c r="E764" s="13" t="n">
-        <v>14333</v>
+        <v>14323</v>
       </c>
       <c r="F764" s="13" t="n">
         <v>9</v>
@@ -24300,7 +24300,7 @@
         </is>
       </c>
       <c r="E765" s="13" t="n">
-        <v>14345</v>
+        <v>14335</v>
       </c>
       <c r="F765" s="13" t="n">
         <v>8</v>
@@ -24328,7 +24328,7 @@
         </is>
       </c>
       <c r="E766" s="13" t="n">
-        <v>14355</v>
+        <v>14345</v>
       </c>
       <c r="F766" s="13" t="n">
         <v>8</v>
@@ -24356,7 +24356,7 @@
         </is>
       </c>
       <c r="E767" s="13" t="n">
-        <v>14365</v>
+        <v>14355</v>
       </c>
       <c r="F767" s="13" t="n">
         <v>8</v>
@@ -24384,7 +24384,7 @@
         </is>
       </c>
       <c r="E768" s="13" t="n">
-        <v>14375</v>
+        <v>14365</v>
       </c>
       <c r="F768" s="13" t="n">
         <v>8</v>
@@ -24412,7 +24412,7 @@
         </is>
       </c>
       <c r="E769" s="13" t="n">
-        <v>14385</v>
+        <v>14375</v>
       </c>
       <c r="F769" s="13" t="n">
         <v>10</v>
@@ -24440,7 +24440,7 @@
         </is>
       </c>
       <c r="E770" s="13" t="n">
-        <v>14398</v>
+        <v>14388</v>
       </c>
       <c r="F770" s="13" t="n">
         <v>9</v>
@@ -24468,7 +24468,7 @@
         </is>
       </c>
       <c r="E771" s="13" t="n">
-        <v>14409</v>
+        <v>14399</v>
       </c>
       <c r="F771" s="13" t="n">
         <v>9</v>
@@ -24496,7 +24496,7 @@
         </is>
       </c>
       <c r="E772" s="13" t="n">
-        <v>14421</v>
+        <v>14411</v>
       </c>
       <c r="F772" s="13" t="n">
         <v>7</v>
@@ -24524,7 +24524,7 @@
         </is>
       </c>
       <c r="E773" s="13" t="n">
-        <v>14430</v>
+        <v>14420</v>
       </c>
       <c r="F773" s="13" t="n">
         <v>8</v>
@@ -24552,7 +24552,7 @@
         </is>
       </c>
       <c r="E774" s="13" t="n">
-        <v>14441</v>
+        <v>14431</v>
       </c>
       <c r="F774" s="13" t="n">
         <v>8</v>
@@ -24580,7 +24580,7 @@
         </is>
       </c>
       <c r="E775" s="13" t="n">
-        <v>14451</v>
+        <v>14441</v>
       </c>
       <c r="F775" s="13" t="n">
         <v>6</v>
@@ -24608,7 +24608,7 @@
         </is>
       </c>
       <c r="E776" s="13" t="n">
-        <v>14460</v>
+        <v>14450</v>
       </c>
       <c r="F776" s="13" t="n">
         <v>7</v>
@@ -24636,7 +24636,7 @@
         </is>
       </c>
       <c r="E777" s="13" t="n">
-        <v>14468</v>
+        <v>14458</v>
       </c>
       <c r="F777" s="13" t="n">
         <v>16</v>
@@ -24664,7 +24664,7 @@
         </is>
       </c>
       <c r="E778" s="13" t="n">
-        <v>14487</v>
+        <v>14477</v>
       </c>
       <c r="F778" s="13" t="n">
         <v>8</v>
@@ -24692,7 +24692,7 @@
         </is>
       </c>
       <c r="E779" s="13" t="n">
-        <v>14497</v>
+        <v>14487</v>
       </c>
       <c r="F779" s="13" t="n">
         <v>8</v>
@@ -24720,7 +24720,7 @@
         </is>
       </c>
       <c r="E780" s="13" t="n">
-        <v>14507</v>
+        <v>14497</v>
       </c>
       <c r="F780" s="13" t="n">
         <v>11</v>
@@ -24748,7 +24748,7 @@
         </is>
       </c>
       <c r="E781" s="13" t="n">
-        <v>14521</v>
+        <v>14511</v>
       </c>
       <c r="F781" s="13" t="n">
         <v>8</v>
@@ -24776,7 +24776,7 @@
         </is>
       </c>
       <c r="E782" s="13" t="n">
-        <v>14531</v>
+        <v>14521</v>
       </c>
       <c r="F782" s="13" t="n">
         <v>9</v>
@@ -24804,7 +24804,7 @@
         </is>
       </c>
       <c r="E783" s="13" t="n">
-        <v>14543</v>
+        <v>14533</v>
       </c>
       <c r="F783" s="13" t="n">
         <v>8</v>
@@ -24832,7 +24832,7 @@
         </is>
       </c>
       <c r="E784" s="13" t="n">
-        <v>14553</v>
+        <v>14543</v>
       </c>
       <c r="F784" s="13" t="n">
         <v>8</v>
@@ -24860,7 +24860,7 @@
         </is>
       </c>
       <c r="E785" s="13" t="n">
-        <v>14564</v>
+        <v>14554</v>
       </c>
       <c r="F785" s="13" t="n">
         <v>8</v>
@@ -24888,7 +24888,7 @@
         </is>
       </c>
       <c r="E786" s="13" t="n">
-        <v>14574</v>
+        <v>14564</v>
       </c>
       <c r="F786" s="13" t="n">
         <v>8</v>
@@ -24916,7 +24916,7 @@
         </is>
       </c>
       <c r="E787" s="13" t="n">
-        <v>14585</v>
+        <v>14575</v>
       </c>
       <c r="F787" s="13" t="n">
         <v>8</v>
@@ -24944,7 +24944,7 @@
         </is>
       </c>
       <c r="E788" s="13" t="n">
-        <v>14595</v>
+        <v>14585</v>
       </c>
       <c r="F788" s="13" t="n">
         <v>8</v>
@@ -24972,7 +24972,7 @@
         </is>
       </c>
       <c r="E789" s="13" t="n">
-        <v>14606</v>
+        <v>14596</v>
       </c>
       <c r="F789" s="13" t="n">
         <v>8</v>
@@ -25000,7 +25000,7 @@
         </is>
       </c>
       <c r="E790" s="13" t="n">
-        <v>14616</v>
+        <v>14606</v>
       </c>
       <c r="F790" s="13" t="n">
         <v>8</v>
@@ -25028,7 +25028,7 @@
         </is>
       </c>
       <c r="E791" s="13" t="n">
-        <v>14627</v>
+        <v>14617</v>
       </c>
       <c r="F791" s="13" t="n">
         <v>8</v>
@@ -25056,7 +25056,7 @@
         </is>
       </c>
       <c r="E792" s="13" t="n">
-        <v>14637</v>
+        <v>14627</v>
       </c>
       <c r="F792" s="13" t="n">
         <v>8</v>
@@ -25084,7 +25084,7 @@
         </is>
       </c>
       <c r="E793" s="13" t="n">
-        <v>14648</v>
+        <v>14638</v>
       </c>
       <c r="F793" s="13" t="n">
         <v>6</v>
@@ -25112,7 +25112,7 @@
         </is>
       </c>
       <c r="E794" s="13" t="n">
-        <v>14656</v>
+        <v>14646</v>
       </c>
       <c r="F794" s="13" t="n">
         <v>8</v>
@@ -25140,7 +25140,7 @@
         </is>
       </c>
       <c r="E795" s="13" t="n">
-        <v>14667</v>
+        <v>14657</v>
       </c>
       <c r="F795" s="13" t="n">
         <v>8</v>
@@ -25168,7 +25168,7 @@
         </is>
       </c>
       <c r="E796" s="13" t="n">
-        <v>14677</v>
+        <v>14667</v>
       </c>
       <c r="F796" s="13" t="n">
         <v>9</v>
@@ -25196,7 +25196,7 @@
         </is>
       </c>
       <c r="E797" s="13" t="n">
-        <v>14689</v>
+        <v>14679</v>
       </c>
       <c r="F797" s="13" t="n">
         <v>9</v>
@@ -25224,7 +25224,7 @@
         </is>
       </c>
       <c r="E798" s="13" t="n">
-        <v>14700</v>
+        <v>14690</v>
       </c>
       <c r="F798" s="13" t="n">
         <v>9</v>
@@ -25252,7 +25252,7 @@
         </is>
       </c>
       <c r="E799" s="13" t="n">
-        <v>14712</v>
+        <v>14702</v>
       </c>
       <c r="F799" s="13" t="n">
         <v>8</v>
@@ -25280,7 +25280,7 @@
         </is>
       </c>
       <c r="E800" s="13" t="n">
-        <v>14722</v>
+        <v>14712</v>
       </c>
       <c r="F800" s="13" t="n">
         <v>5</v>
@@ -25308,7 +25308,7 @@
         </is>
       </c>
       <c r="E801" s="13" t="n">
-        <v>14730</v>
+        <v>14720</v>
       </c>
       <c r="F801" s="13" t="n">
         <v>13</v>
@@ -25336,7 +25336,7 @@
         </is>
       </c>
       <c r="E802" s="13" t="n">
-        <v>14745</v>
+        <v>14735</v>
       </c>
       <c r="F802" s="13" t="n">
         <v>17</v>
@@ -25364,7 +25364,7 @@
         </is>
       </c>
       <c r="E803" s="13" t="n">
-        <v>14765</v>
+        <v>14755</v>
       </c>
       <c r="F803" s="13" t="n">
         <v>8</v>
@@ -25392,7 +25392,7 @@
         </is>
       </c>
       <c r="E804" s="13" t="n">
-        <v>14776</v>
+        <v>14766</v>
       </c>
       <c r="F804" s="13" t="n">
         <v>8</v>
@@ -25420,7 +25420,7 @@
         </is>
       </c>
       <c r="E805" s="13" t="n">
-        <v>14786</v>
+        <v>14776</v>
       </c>
       <c r="F805" s="13" t="n">
         <v>13</v>
@@ -25448,7 +25448,7 @@
         </is>
       </c>
       <c r="E806" s="13" t="n">
-        <v>14802</v>
+        <v>14792</v>
       </c>
       <c r="F806" s="13" t="n">
         <v>9</v>
@@ -25476,7 +25476,7 @@
         </is>
       </c>
       <c r="E807" s="13" t="n">
-        <v>14813</v>
+        <v>14803</v>
       </c>
       <c r="F807" s="13" t="n">
         <v>7</v>
@@ -25504,7 +25504,7 @@
         </is>
       </c>
       <c r="E808" s="13" t="n">
-        <v>14822</v>
+        <v>14812</v>
       </c>
       <c r="F808" s="13" t="n">
         <v>9</v>
@@ -25532,7 +25532,7 @@
         </is>
       </c>
       <c r="E809" s="13" t="n">
-        <v>14834</v>
+        <v>14824</v>
       </c>
       <c r="F809" s="13" t="n">
         <v>12</v>
@@ -25560,7 +25560,7 @@
         </is>
       </c>
       <c r="E810" s="13" t="n">
-        <v>14848</v>
+        <v>14838</v>
       </c>
       <c r="F810" s="13" t="n">
         <v>11</v>
@@ -25588,7 +25588,7 @@
         </is>
       </c>
       <c r="E811" s="13" t="n">
-        <v>14862</v>
+        <v>14852</v>
       </c>
       <c r="F811" s="13" t="n">
         <v>10</v>
@@ -25616,7 +25616,7 @@
         </is>
       </c>
       <c r="E812" s="13" t="n">
-        <v>14875</v>
+        <v>14865</v>
       </c>
       <c r="F812" s="13" t="n">
         <v>10</v>
@@ -25644,7 +25644,7 @@
         </is>
       </c>
       <c r="E813" s="13" t="n">
-        <v>14887</v>
+        <v>14877</v>
       </c>
       <c r="F813" s="13" t="n">
         <v>11</v>
@@ -25672,7 +25672,7 @@
         </is>
       </c>
       <c r="E814" s="13" t="n">
-        <v>14901</v>
+        <v>14891</v>
       </c>
       <c r="F814" s="13" t="n">
         <v>11</v>
@@ -25700,7 +25700,7 @@
         </is>
       </c>
       <c r="E815" s="13" t="n">
-        <v>14915</v>
+        <v>14905</v>
       </c>
       <c r="F815" s="13" t="n">
         <v>9</v>
@@ -25728,7 +25728,7 @@
         </is>
       </c>
       <c r="E816" s="13" t="n">
-        <v>14926</v>
+        <v>14916</v>
       </c>
       <c r="F816" s="13" t="n">
         <v>11</v>
@@ -25756,7 +25756,7 @@
         </is>
       </c>
       <c r="E817" s="13" t="n">
-        <v>14939</v>
+        <v>14929</v>
       </c>
       <c r="F817" s="13" t="n">
         <v>10</v>
@@ -25784,7 +25784,7 @@
         </is>
       </c>
       <c r="E818" s="13" t="n">
-        <v>14952</v>
+        <v>14942</v>
       </c>
       <c r="F818" s="13" t="n">
         <v>9</v>
@@ -25812,7 +25812,7 @@
         </is>
       </c>
       <c r="E819" s="13" t="n">
-        <v>14963</v>
+        <v>14953</v>
       </c>
       <c r="F819" s="13" t="n">
         <v>9</v>
@@ -25840,7 +25840,7 @@
         </is>
       </c>
       <c r="E820" s="13" t="n">
-        <v>14975</v>
+        <v>14965</v>
       </c>
       <c r="F820" s="13" t="n">
         <v>10</v>
@@ -25868,7 +25868,7 @@
         </is>
       </c>
       <c r="E821" s="13" t="n">
-        <v>14988</v>
+        <v>14978</v>
       </c>
       <c r="F821" s="13" t="n">
         <v>15</v>
@@ -25896,7 +25896,7 @@
         </is>
       </c>
       <c r="E822" s="13" t="n">
-        <v>15005</v>
+        <v>14995</v>
       </c>
       <c r="F822" s="13" t="n">
         <v>16</v>
@@ -25924,7 +25924,7 @@
         </is>
       </c>
       <c r="E823" s="13" t="n">
-        <v>15024</v>
+        <v>15014</v>
       </c>
       <c r="F823" s="13" t="n">
         <v>10</v>
@@ -25952,7 +25952,7 @@
         </is>
       </c>
       <c r="E824" s="13" t="n">
-        <v>15036</v>
+        <v>15026</v>
       </c>
       <c r="F824" s="13" t="n">
         <v>9</v>
@@ -25980,7 +25980,7 @@
         </is>
       </c>
       <c r="E825" s="13" t="n">
-        <v>15048</v>
+        <v>15038</v>
       </c>
       <c r="F825" s="13" t="n">
         <v>8</v>
@@ -26008,7 +26008,7 @@
         </is>
       </c>
       <c r="E826" s="13" t="n">
-        <v>15058</v>
+        <v>15048</v>
       </c>
       <c r="F826" s="13" t="n">
         <v>8</v>
@@ -26036,7 +26036,7 @@
         </is>
       </c>
       <c r="E827" s="13" t="n">
-        <v>15069</v>
+        <v>15059</v>
       </c>
       <c r="F827" s="13" t="n">
         <v>8</v>
@@ -26064,7 +26064,7 @@
         </is>
       </c>
       <c r="E828" s="13" t="n">
-        <v>15079</v>
+        <v>15069</v>
       </c>
       <c r="F828" s="13" t="n">
         <v>9</v>
@@ -26092,7 +26092,7 @@
         </is>
       </c>
       <c r="E829" s="13" t="n">
-        <v>15091</v>
+        <v>15081</v>
       </c>
       <c r="F829" s="13" t="n">
         <v>8</v>
@@ -26120,7 +26120,7 @@
         </is>
       </c>
       <c r="E830" s="13" t="n">
-        <v>15101</v>
+        <v>15091</v>
       </c>
       <c r="F830" s="13" t="n">
         <v>8</v>
@@ -26148,7 +26148,7 @@
         </is>
       </c>
       <c r="E831" s="13" t="n">
-        <v>15112</v>
+        <v>15102</v>
       </c>
       <c r="F831" s="13" t="n">
         <v>8</v>
@@ -26176,7 +26176,7 @@
         </is>
       </c>
       <c r="E832" s="13" t="n">
-        <v>15122</v>
+        <v>15112</v>
       </c>
       <c r="F832" s="13" t="n">
         <v>8</v>
@@ -26204,7 +26204,7 @@
         </is>
       </c>
       <c r="E833" s="13" t="n">
-        <v>15133</v>
+        <v>15123</v>
       </c>
       <c r="F833" s="13" t="n">
         <v>8</v>
@@ -26232,7 +26232,7 @@
         </is>
       </c>
       <c r="E834" s="13" t="n">
-        <v>15143</v>
+        <v>15133</v>
       </c>
       <c r="F834" s="13" t="n">
         <v>8</v>
@@ -26260,7 +26260,7 @@
         </is>
       </c>
       <c r="E835" s="13" t="n">
-        <v>15154</v>
+        <v>15144</v>
       </c>
       <c r="F835" s="13" t="n">
         <v>8</v>
@@ -26288,7 +26288,7 @@
         </is>
       </c>
       <c r="E836" s="13" t="n">
-        <v>15164</v>
+        <v>15154</v>
       </c>
       <c r="F836" s="13" t="n">
         <v>8</v>
@@ -26316,7 +26316,7 @@
         </is>
       </c>
       <c r="E837" s="13" t="n">
-        <v>15175</v>
+        <v>15165</v>
       </c>
       <c r="F837" s="13" t="n">
         <v>7</v>
@@ -26344,7 +26344,7 @@
         </is>
       </c>
       <c r="E838" s="13" t="n">
-        <v>15184</v>
+        <v>15174</v>
       </c>
       <c r="F838" s="13" t="n">
         <v>8</v>
@@ -26372,7 +26372,7 @@
         </is>
       </c>
       <c r="E839" s="13" t="n">
-        <v>15195</v>
+        <v>15185</v>
       </c>
       <c r="F839" s="13" t="n">
         <v>7</v>
@@ -26400,7 +26400,7 @@
         </is>
       </c>
       <c r="E840" s="13" t="n">
-        <v>15204</v>
+        <v>15194</v>
       </c>
       <c r="F840" s="13" t="n">
         <v>6</v>
@@ -26428,7 +26428,7 @@
         </is>
       </c>
       <c r="E841" s="13" t="n">
-        <v>15213</v>
+        <v>15203</v>
       </c>
       <c r="F841" s="13" t="n">
         <v>8</v>
@@ -26456,7 +26456,7 @@
         </is>
       </c>
       <c r="E842" s="13" t="n">
-        <v>15223</v>
+        <v>15213</v>
       </c>
       <c r="F842" s="13" t="n">
         <v>15</v>
@@ -26484,7 +26484,7 @@
         </is>
       </c>
       <c r="E843" s="13" t="n">
-        <v>15241</v>
+        <v>15231</v>
       </c>
       <c r="F843" s="13" t="n">
         <v>9</v>
@@ -26512,7 +26512,7 @@
         </is>
       </c>
       <c r="E844" s="13" t="n">
-        <v>15253</v>
+        <v>15243</v>
       </c>
       <c r="F844" s="13" t="n">
         <v>9</v>
@@ -26540,7 +26540,7 @@
         </is>
       </c>
       <c r="E845" s="13" t="n">
-        <v>15264</v>
+        <v>15254</v>
       </c>
       <c r="F845" s="13" t="n">
         <v>9</v>
@@ -26568,7 +26568,7 @@
         </is>
       </c>
       <c r="E846" s="13" t="n">
-        <v>15276</v>
+        <v>15266</v>
       </c>
       <c r="F846" s="13" t="n">
         <v>8</v>
@@ -26596,7 +26596,7 @@
         </is>
       </c>
       <c r="E847" s="13" t="n">
-        <v>15286</v>
+        <v>15276</v>
       </c>
       <c r="F847" s="13" t="n">
         <v>8</v>
@@ -26624,7 +26624,7 @@
         </is>
       </c>
       <c r="E848" s="13" t="n">
-        <v>15297</v>
+        <v>15287</v>
       </c>
       <c r="F848" s="13" t="n">
         <v>9</v>
@@ -26652,7 +26652,7 @@
         </is>
       </c>
       <c r="E849" s="13" t="n">
-        <v>15308</v>
+        <v>15298</v>
       </c>
       <c r="F849" s="13" t="n">
         <v>9</v>
@@ -26680,7 +26680,7 @@
         </is>
       </c>
       <c r="E850" s="13" t="n">
-        <v>15320</v>
+        <v>15310</v>
       </c>
       <c r="F850" s="13" t="n">
         <v>8</v>
@@ -26708,7 +26708,7 @@
         </is>
       </c>
       <c r="E851" s="13" t="n">
-        <v>15330</v>
+        <v>15320</v>
       </c>
       <c r="F851" s="13" t="n">
         <v>9</v>
@@ -26736,7 +26736,7 @@
         </is>
       </c>
       <c r="E852" s="13" t="n">
-        <v>15342</v>
+        <v>15332</v>
       </c>
       <c r="F852" s="13" t="n">
         <v>9</v>
@@ -26764,7 +26764,7 @@
         </is>
       </c>
       <c r="E853" s="13" t="n">
-        <v>15353</v>
+        <v>15343</v>
       </c>
       <c r="F853" s="13" t="n">
         <v>9</v>
@@ -26792,7 +26792,7 @@
         </is>
       </c>
       <c r="E854" s="13" t="n">
-        <v>15365</v>
+        <v>15355</v>
       </c>
       <c r="F854" s="13" t="n">
         <v>9</v>
@@ -26820,7 +26820,7 @@
         </is>
       </c>
       <c r="E855" s="13" t="n">
-        <v>15376</v>
+        <v>15366</v>
       </c>
       <c r="F855" s="13" t="n">
         <v>8</v>
@@ -26848,7 +26848,7 @@
         </is>
       </c>
       <c r="E856" s="13" t="n">
-        <v>15387</v>
+        <v>15377</v>
       </c>
       <c r="F856" s="13" t="n">
         <v>7</v>
@@ -26876,7 +26876,7 @@
         </is>
       </c>
       <c r="E857" s="13" t="n">
-        <v>15396</v>
+        <v>15386</v>
       </c>
       <c r="F857" s="13" t="n">
         <v>7</v>
@@ -26904,7 +26904,7 @@
         </is>
       </c>
       <c r="E858" s="13" t="n">
-        <v>15406</v>
+        <v>15396</v>
       </c>
       <c r="F858" s="13" t="n">
         <v>8</v>
@@ -26932,7 +26932,7 @@
         </is>
       </c>
       <c r="E859" s="13" t="n">
-        <v>15416</v>
+        <v>15406</v>
       </c>
       <c r="F859" s="13" t="n">
         <v>9</v>
@@ -26960,7 +26960,7 @@
         </is>
       </c>
       <c r="E860" s="13" t="n">
-        <v>15428</v>
+        <v>15418</v>
       </c>
       <c r="F860" s="13" t="n">
         <v>8</v>
@@ -26988,7 +26988,7 @@
         </is>
       </c>
       <c r="E861" s="13" t="n">
-        <v>15438</v>
+        <v>15428</v>
       </c>
       <c r="F861" s="13" t="n">
         <v>10</v>
@@ -27016,7 +27016,7 @@
         </is>
       </c>
       <c r="E862" s="13" t="n">
-        <v>15451</v>
+        <v>15441</v>
       </c>
       <c r="F862" s="13" t="n">
         <v>9</v>
@@ -27044,7 +27044,7 @@
         </is>
       </c>
       <c r="E863" s="13" t="n">
-        <v>15462</v>
+        <v>15452</v>
       </c>
       <c r="F863" s="13" t="n">
         <v>8</v>
@@ -27072,7 +27072,7 @@
         </is>
       </c>
       <c r="E864" s="13" t="n">
-        <v>15473</v>
+        <v>15463</v>
       </c>
       <c r="F864" s="13" t="n">
         <v>8</v>
@@ -27100,7 +27100,7 @@
         </is>
       </c>
       <c r="E865" s="13" t="n">
-        <v>15483</v>
+        <v>15473</v>
       </c>
       <c r="F865" s="13" t="n">
         <v>7</v>
@@ -27128,7 +27128,7 @@
         </is>
       </c>
       <c r="E866" s="13" t="n">
-        <v>15493</v>
+        <v>15483</v>
       </c>
       <c r="F866" s="13" t="n">
         <v>9</v>
@@ -27156,7 +27156,7 @@
         </is>
       </c>
       <c r="E867" s="13" t="n">
-        <v>15504</v>
+        <v>15494</v>
       </c>
       <c r="F867" s="13" t="n">
         <v>9</v>
@@ -27184,7 +27184,7 @@
         </is>
       </c>
       <c r="E868" s="13" t="n">
-        <v>15516</v>
+        <v>15506</v>
       </c>
       <c r="F868" s="13" t="n">
         <v>8</v>
@@ -27212,7 +27212,7 @@
         </is>
       </c>
       <c r="E869" s="13" t="n">
-        <v>15526</v>
+        <v>15516</v>
       </c>
       <c r="F869" s="13" t="n">
         <v>8</v>
@@ -27240,7 +27240,7 @@
         </is>
       </c>
       <c r="E870" s="13" t="n">
-        <v>15537</v>
+        <v>15527</v>
       </c>
       <c r="F870" s="13" t="n">
         <v>9</v>
@@ -27268,7 +27268,7 @@
         </is>
       </c>
       <c r="E871" s="13" t="n">
-        <v>15548</v>
+        <v>15538</v>
       </c>
       <c r="F871" s="13" t="n">
         <v>8</v>
@@ -27296,7 +27296,7 @@
         </is>
       </c>
       <c r="E872" s="13" t="n">
-        <v>15559</v>
+        <v>15549</v>
       </c>
       <c r="F872" s="13" t="n">
         <v>8</v>
@@ -27324,7 +27324,7 @@
         </is>
       </c>
       <c r="E873" s="13" t="n">
-        <v>15569</v>
+        <v>15559</v>
       </c>
       <c r="F873" s="13" t="n">
         <v>8</v>
@@ -27352,7 +27352,7 @@
         </is>
       </c>
       <c r="E874" s="13" t="n">
-        <v>15580</v>
+        <v>15570</v>
       </c>
       <c r="F874" s="13" t="n">
         <v>8</v>
@@ -27380,7 +27380,7 @@
         </is>
       </c>
       <c r="E875" s="13" t="n">
-        <v>15590</v>
+        <v>15580</v>
       </c>
       <c r="F875" s="13" t="n">
         <v>8</v>
@@ -27408,7 +27408,7 @@
         </is>
       </c>
       <c r="E876" s="13" t="n">
-        <v>15601</v>
+        <v>15591</v>
       </c>
       <c r="F876" s="13" t="n">
         <v>8</v>
@@ -27436,7 +27436,7 @@
         </is>
       </c>
       <c r="E877" s="13" t="n">
-        <v>15611</v>
+        <v>15601</v>
       </c>
       <c r="F877" s="13" t="n">
         <v>6</v>
@@ -27464,7 +27464,7 @@
         </is>
       </c>
       <c r="E878" s="13" t="n">
-        <v>15620</v>
+        <v>15610</v>
       </c>
       <c r="F878" s="13" t="n">
         <v>7</v>
@@ -27492,7 +27492,7 @@
         </is>
       </c>
       <c r="E879" s="13" t="n">
-        <v>15629</v>
+        <v>15619</v>
       </c>
       <c r="F879" s="13" t="n">
         <v>8</v>
@@ -27520,7 +27520,7 @@
         </is>
       </c>
       <c r="E880" s="13" t="n">
-        <v>15640</v>
+        <v>15630</v>
       </c>
       <c r="F880" s="13" t="n">
         <v>8</v>
@@ -27548,7 +27548,7 @@
         </is>
       </c>
       <c r="E881" s="13" t="n">
-        <v>15650</v>
+        <v>15640</v>
       </c>
       <c r="F881" s="13" t="n">
         <v>9</v>
@@ -27576,7 +27576,7 @@
         </is>
       </c>
       <c r="E882" s="13" t="n">
-        <v>15662</v>
+        <v>15652</v>
       </c>
       <c r="F882" s="13" t="n">
         <v>7</v>
@@ -27604,7 +27604,7 @@
         </is>
       </c>
       <c r="E883" s="13" t="n">
-        <v>15671</v>
+        <v>15661</v>
       </c>
       <c r="F883" s="13" t="n">
         <v>9</v>
@@ -27632,7 +27632,7 @@
         </is>
       </c>
       <c r="E884" s="13" t="n">
-        <v>15683</v>
+        <v>15673</v>
       </c>
       <c r="F884" s="13" t="n">
         <v>8</v>
@@ -27660,7 +27660,7 @@
         </is>
       </c>
       <c r="E885" s="13" t="n">
-        <v>15693</v>
+        <v>15683</v>
       </c>
       <c r="F885" s="13" t="n">
         <v>6</v>
@@ -27688,7 +27688,7 @@
         </is>
       </c>
       <c r="E886" s="13" t="n">
-        <v>15702</v>
+        <v>15692</v>
       </c>
       <c r="F886" s="13" t="n">
         <v>8</v>
@@ -27716,7 +27716,7 @@
         </is>
       </c>
       <c r="E887" s="13" t="n">
-        <v>15712</v>
+        <v>15702</v>
       </c>
       <c r="F887" s="13" t="n">
         <v>9</v>
@@ -27744,7 +27744,7 @@
         </is>
       </c>
       <c r="E888" s="13" t="n">
-        <v>15724</v>
+        <v>15714</v>
       </c>
       <c r="F888" s="13" t="n">
         <v>7</v>
@@ -27772,7 +27772,7 @@
         </is>
       </c>
       <c r="E889" s="13" t="n">
-        <v>15733</v>
+        <v>15723</v>
       </c>
       <c r="F889" s="13" t="n">
         <v>8</v>
@@ -27800,7 +27800,7 @@
         </is>
       </c>
       <c r="E890" s="13" t="n">
-        <v>15744</v>
+        <v>15734</v>
       </c>
       <c r="F890" s="13" t="n">
         <v>7</v>
@@ -27828,7 +27828,7 @@
         </is>
       </c>
       <c r="E891" s="13" t="n">
-        <v>15753</v>
+        <v>15743</v>
       </c>
       <c r="F891" s="13" t="n">
         <v>7</v>
@@ -27856,7 +27856,7 @@
         </is>
       </c>
       <c r="E892" s="13" t="n">
-        <v>15763</v>
+        <v>15753</v>
       </c>
       <c r="F892" s="13" t="n">
         <v>8</v>
@@ -27884,7 +27884,7 @@
         </is>
       </c>
       <c r="E893" s="13" t="n">
-        <v>15773</v>
+        <v>15763</v>
       </c>
       <c r="F893" s="13" t="n">
         <v>9</v>
@@ -27912,7 +27912,7 @@
         </is>
       </c>
       <c r="E894" s="13" t="n">
-        <v>15785</v>
+        <v>15775</v>
       </c>
       <c r="F894" s="13" t="n">
         <v>8</v>
@@ -27940,7 +27940,7 @@
         </is>
       </c>
       <c r="E895" s="13" t="n">
-        <v>15795</v>
+        <v>15785</v>
       </c>
       <c r="F895" s="13" t="n">
         <v>6</v>
@@ -27968,7 +27968,7 @@
         </is>
       </c>
       <c r="E896" s="13" t="n">
-        <v>15804</v>
+        <v>15794</v>
       </c>
       <c r="F896" s="13" t="n">
         <v>7</v>
@@ -27996,7 +27996,7 @@
         </is>
       </c>
       <c r="E897" s="13" t="n">
-        <v>15813</v>
+        <v>15803</v>
       </c>
       <c r="F897" s="13" t="n">
         <v>8</v>
@@ -28024,7 +28024,7 @@
         </is>
       </c>
       <c r="E898" s="13" t="n">
-        <v>15823</v>
+        <v>15813</v>
       </c>
       <c r="F898" s="13" t="n">
         <v>7</v>
@@ -28052,7 +28052,7 @@
         </is>
       </c>
       <c r="E899" s="13" t="n">
-        <v>15832</v>
+        <v>15822</v>
       </c>
       <c r="F899" s="13" t="n">
         <v>8</v>
@@ -28080,7 +28080,7 @@
         </is>
       </c>
       <c r="E900" s="13" t="n">
-        <v>15842</v>
+        <v>15832</v>
       </c>
       <c r="F900" s="13" t="n">
         <v>8</v>
@@ -28108,7 +28108,7 @@
         </is>
       </c>
       <c r="E901" s="13" t="n">
-        <v>15853</v>
+        <v>15843</v>
       </c>
       <c r="F901" s="13" t="n">
         <v>7</v>
@@ -28136,7 +28136,7 @@
         </is>
       </c>
       <c r="E902" s="13" t="n">
-        <v>15862</v>
+        <v>15852</v>
       </c>
       <c r="F902" s="13" t="n">
         <v>7</v>
@@ -28164,7 +28164,7 @@
         </is>
       </c>
       <c r="E903" s="13" t="n">
-        <v>15872</v>
+        <v>15862</v>
       </c>
       <c r="F903" s="13" t="n">
         <v>7</v>
@@ -28192,7 +28192,7 @@
         </is>
       </c>
       <c r="E904" s="13" t="n">
-        <v>15881</v>
+        <v>15871</v>
       </c>
       <c r="F904" s="13" t="n">
         <v>8</v>
@@ -28220,7 +28220,7 @@
         </is>
       </c>
       <c r="E905" s="13" t="n">
-        <v>15892</v>
+        <v>15882</v>
       </c>
       <c r="F905" s="13" t="n">
         <v>8</v>
@@ -28248,7 +28248,7 @@
         </is>
       </c>
       <c r="E906" s="13" t="n">
-        <v>15902</v>
+        <v>15892</v>
       </c>
       <c r="F906" s="13" t="n">
         <v>8</v>
@@ -28276,7 +28276,7 @@
         </is>
       </c>
       <c r="E907" s="13" t="n">
-        <v>15913</v>
+        <v>15903</v>
       </c>
       <c r="F907" s="13" t="n">
         <v>8</v>
@@ -28304,7 +28304,7 @@
         </is>
       </c>
       <c r="E908" s="13" t="n">
-        <v>15923</v>
+        <v>15913</v>
       </c>
       <c r="F908" s="13" t="n">
         <v>9</v>
@@ -28332,7 +28332,7 @@
         </is>
       </c>
       <c r="E909" s="13" t="n">
-        <v>15935</v>
+        <v>15925</v>
       </c>
       <c r="F909" s="13" t="n">
         <v>9</v>
@@ -28360,7 +28360,7 @@
         </is>
       </c>
       <c r="E910" s="13" t="n">
-        <v>15946</v>
+        <v>15936</v>
       </c>
       <c r="F910" s="13" t="n">
         <v>9</v>
@@ -28388,7 +28388,7 @@
         </is>
       </c>
       <c r="E911" s="13" t="n">
-        <v>15958</v>
+        <v>15948</v>
       </c>
       <c r="F911" s="13" t="n">
         <v>9</v>
@@ -28416,7 +28416,7 @@
         </is>
       </c>
       <c r="E912" s="13" t="n">
-        <v>15969</v>
+        <v>15959</v>
       </c>
       <c r="F912" s="13" t="n">
         <v>8</v>
@@ -28444,7 +28444,7 @@
         </is>
       </c>
       <c r="E913" s="13" t="n">
-        <v>15980</v>
+        <v>15970</v>
       </c>
       <c r="F913" s="13" t="n">
         <v>7</v>
@@ -28472,7 +28472,7 @@
         </is>
       </c>
       <c r="E914" s="13" t="n">
-        <v>15989</v>
+        <v>15979</v>
       </c>
       <c r="F914" s="13" t="n">
         <v>8</v>
@@ -28500,7 +28500,7 @@
         </is>
       </c>
       <c r="E915" s="13" t="n">
-        <v>16000</v>
+        <v>15990</v>
       </c>
       <c r="F915" s="13" t="n">
         <v>7</v>
@@ -28528,7 +28528,7 @@
         </is>
       </c>
       <c r="E916" s="13" t="n">
-        <v>16009</v>
+        <v>15999</v>
       </c>
       <c r="F916" s="13" t="n">
         <v>7</v>
@@ -28556,7 +28556,7 @@
         </is>
       </c>
       <c r="E917" s="13" t="n">
-        <v>16018</v>
+        <v>16008</v>
       </c>
       <c r="F917" s="13" t="n">
         <v>6</v>
@@ -28584,7 +28584,7 @@
         </is>
       </c>
       <c r="E918" s="13" t="n">
-        <v>16027</v>
+        <v>16017</v>
       </c>
       <c r="F918" s="13" t="n">
         <v>5</v>
@@ -28612,7 +28612,7 @@
         </is>
       </c>
       <c r="E919" s="13" t="n">
-        <v>16034</v>
+        <v>16024</v>
       </c>
       <c r="F919" s="13" t="n">
         <v>7</v>
@@ -28640,7 +28640,7 @@
         </is>
       </c>
       <c r="E920" s="13" t="n">
-        <v>16043</v>
+        <v>16033</v>
       </c>
       <c r="F920" s="13" t="n">
         <v>6</v>
@@ -28668,7 +28668,7 @@
         </is>
       </c>
       <c r="E921" s="13" t="n">
-        <v>16052</v>
+        <v>16042</v>
       </c>
       <c r="F921" s="13" t="n">
         <v>7</v>
@@ -28696,7 +28696,7 @@
         </is>
       </c>
       <c r="E922" s="13" t="n">
-        <v>16061</v>
+        <v>16051</v>
       </c>
       <c r="F922" s="13" t="n">
         <v>8</v>
@@ -28724,7 +28724,7 @@
         </is>
       </c>
       <c r="E923" s="13" t="n">
-        <v>16072</v>
+        <v>16062</v>
       </c>
       <c r="F923" s="13" t="n">
         <v>7</v>
@@ -28752,7 +28752,7 @@
         </is>
       </c>
       <c r="E924" s="13" t="n">
-        <v>16081</v>
+        <v>16071</v>
       </c>
       <c r="F924" s="13" t="n">
         <v>14</v>
@@ -28780,7 +28780,7 @@
         </is>
       </c>
       <c r="E925" s="13" t="n">
-        <v>16098</v>
+        <v>16088</v>
       </c>
       <c r="F925" s="13" t="n">
         <v>7</v>
@@ -28808,7 +28808,7 @@
         </is>
       </c>
       <c r="E926" s="13" t="n">
-        <v>16107</v>
+        <v>16097</v>
       </c>
       <c r="F926" s="13" t="n">
         <v>8</v>
@@ -28836,7 +28836,7 @@
         </is>
       </c>
       <c r="E927" s="13" t="n">
-        <v>16118</v>
+        <v>16108</v>
       </c>
       <c r="F927" s="13" t="n">
         <v>6</v>
@@ -28864,7 +28864,7 @@
         </is>
       </c>
       <c r="E928" s="13" t="n">
-        <v>16126</v>
+        <v>16116</v>
       </c>
       <c r="F928" s="13" t="n">
         <v>7</v>
@@ -28892,7 +28892,7 @@
         </is>
       </c>
       <c r="E929" s="13" t="n">
-        <v>16135</v>
+        <v>16125</v>
       </c>
       <c r="F929" s="13" t="n">
         <v>5</v>
@@ -28920,7 +28920,7 @@
         </is>
       </c>
       <c r="E930" s="13" t="n">
-        <v>16143</v>
+        <v>16133</v>
       </c>
       <c r="F930" s="13" t="n">
         <v>7</v>
@@ -28948,7 +28948,7 @@
         </is>
       </c>
       <c r="E931" s="13" t="n">
-        <v>16152</v>
+        <v>16142</v>
       </c>
       <c r="F931" s="13" t="n">
         <v>7</v>
@@ -28976,7 +28976,7 @@
         </is>
       </c>
       <c r="E932" s="13" t="n">
-        <v>16162</v>
+        <v>16152</v>
       </c>
       <c r="F932" s="13" t="n">
         <v>8</v>
@@ -29004,7 +29004,7 @@
         </is>
       </c>
       <c r="E933" s="13" t="n">
-        <v>16172</v>
+        <v>16162</v>
       </c>
       <c r="F933" s="13" t="n">
         <v>8</v>
@@ -29032,7 +29032,7 @@
         </is>
       </c>
       <c r="E934" s="13" t="n">
-        <v>16183</v>
+        <v>16173</v>
       </c>
       <c r="F934" s="13" t="n">
         <v>7</v>
@@ -29060,7 +29060,7 @@
         </is>
       </c>
       <c r="E935" s="13" t="n">
-        <v>16192</v>
+        <v>16182</v>
       </c>
       <c r="F935" s="13" t="n">
         <v>7</v>
@@ -29088,7 +29088,7 @@
         </is>
       </c>
       <c r="E936" s="13" t="n">
-        <v>16201</v>
+        <v>16191</v>
       </c>
       <c r="F936" s="13" t="n">
         <v>7</v>
@@ -29116,7 +29116,7 @@
         </is>
       </c>
       <c r="E937" s="13" t="n">
-        <v>16210</v>
+        <v>16200</v>
       </c>
       <c r="F937" s="13" t="n">
         <v>5</v>
@@ -29144,7 +29144,7 @@
         </is>
       </c>
       <c r="E938" s="13" t="n">
-        <v>16217</v>
+        <v>16207</v>
       </c>
       <c r="F938" s="13" t="n">
         <v>15</v>
@@ -29172,7 +29172,7 @@
         </is>
       </c>
       <c r="E939" s="13" t="n">
-        <v>16235</v>
+        <v>16225</v>
       </c>
       <c r="F939" s="13" t="n">
         <v>15</v>
@@ -29200,7 +29200,7 @@
         </is>
       </c>
       <c r="E940" s="13" t="n">
-        <v>16253</v>
+        <v>16243</v>
       </c>
       <c r="F940" s="13" t="n">
         <v>8</v>
@@ -29228,7 +29228,7 @@
         </is>
       </c>
       <c r="E941" s="13" t="n">
-        <v>16263</v>
+        <v>16253</v>
       </c>
       <c r="F941" s="13" t="n">
         <v>7</v>
@@ -29256,7 +29256,7 @@
         </is>
       </c>
       <c r="E942" s="13" t="n">
-        <v>16273</v>
+        <v>16263</v>
       </c>
       <c r="F942" s="13" t="n">
         <v>6</v>
@@ -29284,7 +29284,7 @@
         </is>
       </c>
       <c r="E943" s="13" t="n">
-        <v>16281</v>
+        <v>16271</v>
       </c>
       <c r="F943" s="13" t="n">
         <v>6</v>
@@ -29312,7 +29312,7 @@
         </is>
       </c>
       <c r="E944" s="13" t="n">
-        <v>16289</v>
+        <v>16279</v>
       </c>
       <c r="F944" s="13" t="n">
         <v>7</v>
@@ -29340,7 +29340,7 @@
         </is>
       </c>
       <c r="E945" s="13" t="n">
-        <v>16299</v>
+        <v>16289</v>
       </c>
       <c r="F945" s="13" t="n">
         <v>4</v>
@@ -29368,7 +29368,7 @@
         </is>
       </c>
       <c r="E946" s="13" t="n">
-        <v>16305</v>
+        <v>16295</v>
       </c>
       <c r="F946" s="13" t="n">
         <v>6</v>
@@ -29396,7 +29396,7 @@
         </is>
       </c>
       <c r="E947" s="13" t="n">
-        <v>16313</v>
+        <v>16303</v>
       </c>
       <c r="F947" s="13" t="n">
         <v>7</v>
@@ -29424,7 +29424,7 @@
         </is>
       </c>
       <c r="E948" s="13" t="n">
-        <v>16323</v>
+        <v>16313</v>
       </c>
       <c r="F948" s="13" t="n">
         <v>6</v>
@@ -29452,7 +29452,7 @@
         </is>
       </c>
       <c r="E949" s="13" t="n">
-        <v>16331</v>
+        <v>16321</v>
       </c>
       <c r="F949" s="13" t="n">
         <v>9</v>
@@ -29480,7 +29480,7 @@
         </is>
       </c>
       <c r="E950" s="13" t="n">
-        <v>16343</v>
+        <v>16333</v>
       </c>
       <c r="F950" s="13" t="n">
         <v>6</v>
@@ -29508,7 +29508,7 @@
         </is>
       </c>
       <c r="E951" s="13" t="n">
-        <v>16351</v>
+        <v>16341</v>
       </c>
       <c r="F951" s="13" t="n">
         <v>7</v>
@@ -29536,7 +29536,7 @@
         </is>
       </c>
       <c r="E952" s="13" t="n">
-        <v>16360</v>
+        <v>16350</v>
       </c>
       <c r="F952" s="13" t="n">
         <v>6</v>
@@ -29564,7 +29564,7 @@
         </is>
       </c>
       <c r="E953" s="13" t="n">
-        <v>16368</v>
+        <v>16358</v>
       </c>
       <c r="F953" s="13" t="n">
         <v>6</v>
@@ -29592,7 +29592,7 @@
         </is>
       </c>
       <c r="E954" s="13" t="n">
-        <v>16376</v>
+        <v>16366</v>
       </c>
       <c r="F954" s="13" t="n">
         <v>7</v>
@@ -29620,7 +29620,7 @@
         </is>
       </c>
       <c r="E955" s="13" t="n">
-        <v>16386</v>
+        <v>16376</v>
       </c>
       <c r="F955" s="13" t="n">
         <v>7</v>
@@ -29648,7 +29648,7 @@
         </is>
       </c>
       <c r="E956" s="13" t="n">
-        <v>16395</v>
+        <v>16385</v>
       </c>
       <c r="F956" s="13" t="n">
         <v>7</v>
@@ -29676,7 +29676,7 @@
         </is>
       </c>
       <c r="E957" s="13" t="n">
-        <v>16404</v>
+        <v>16394</v>
       </c>
       <c r="F957" s="13" t="n">
         <v>7</v>
@@ -29704,7 +29704,7 @@
         </is>
       </c>
       <c r="E958" s="13" t="n">
-        <v>16413</v>
+        <v>16403</v>
       </c>
       <c r="F958" s="13" t="n">
         <v>7</v>
@@ -29732,7 +29732,7 @@
         </is>
       </c>
       <c r="E959" s="13" t="n">
-        <v>16422</v>
+        <v>16412</v>
       </c>
       <c r="F959" s="13" t="n">
         <v>5</v>
@@ -29760,7 +29760,7 @@
         </is>
       </c>
       <c r="E960" s="13" t="n">
-        <v>16430</v>
+        <v>16420</v>
       </c>
       <c r="F960" s="13" t="n">
         <v>5</v>
@@ -29788,7 +29788,7 @@
         </is>
       </c>
       <c r="E961" s="13" t="n">
-        <v>16437</v>
+        <v>16427</v>
       </c>
       <c r="F961" s="13" t="n">
         <v>5</v>
@@ -29816,7 +29816,7 @@
         </is>
       </c>
       <c r="E962" s="13" t="n">
-        <v>16445</v>
+        <v>16435</v>
       </c>
       <c r="F962" s="13" t="n">
         <v>6</v>
@@ -29844,7 +29844,7 @@
         </is>
       </c>
       <c r="E963" s="13" t="n">
-        <v>16453</v>
+        <v>16443</v>
       </c>
       <c r="F963" s="13" t="n">
         <v>7</v>
@@ -29872,7 +29872,7 @@
         </is>
       </c>
       <c r="E964" s="13" t="n">
-        <v>16462</v>
+        <v>16452</v>
       </c>
       <c r="F964" s="13" t="n">
         <v>6</v>
@@ -29900,7 +29900,7 @@
         </is>
       </c>
       <c r="E965" s="13" t="n">
-        <v>16470</v>
+        <v>16460</v>
       </c>
       <c r="F965" s="13" t="n">
         <v>7</v>
@@ -29928,7 +29928,7 @@
         </is>
       </c>
       <c r="E966" s="13" t="n">
-        <v>16479</v>
+        <v>16469</v>
       </c>
       <c r="F966" s="13" t="n">
         <v>8</v>
@@ -29956,7 +29956,7 @@
         </is>
       </c>
       <c r="E967" s="13" t="n">
-        <v>16490</v>
+        <v>16480</v>
       </c>
       <c r="F967" s="13" t="n">
         <v>7</v>
@@ -29984,7 +29984,7 @@
         </is>
       </c>
       <c r="E968" s="13" t="n">
-        <v>16499</v>
+        <v>16489</v>
       </c>
       <c r="F968" s="13" t="n">
         <v>6</v>
@@ -30012,7 +30012,7 @@
         </is>
       </c>
       <c r="E969" s="13" t="n">
-        <v>16508</v>
+        <v>16498</v>
       </c>
       <c r="F969" s="13" t="n">
         <v>7</v>
@@ -30040,7 +30040,7 @@
         </is>
       </c>
       <c r="E970" s="13" t="n">
-        <v>16517</v>
+        <v>16507</v>
       </c>
       <c r="F970" s="13" t="n">
         <v>6</v>
@@ -30068,7 +30068,7 @@
         </is>
       </c>
       <c r="E971" s="13" t="n">
-        <v>16525</v>
+        <v>16515</v>
       </c>
       <c r="F971" s="13" t="n">
         <v>7</v>
@@ -30096,7 +30096,7 @@
         </is>
       </c>
       <c r="E972" s="13" t="n">
-        <v>16535</v>
+        <v>16525</v>
       </c>
       <c r="F972" s="13" t="n">
         <v>7</v>
@@ -30124,7 +30124,7 @@
         </is>
       </c>
       <c r="E973" s="13" t="n">
-        <v>16544</v>
+        <v>16534</v>
       </c>
       <c r="F973" s="13" t="n">
         <v>3</v>
@@ -30152,7 +30152,7 @@
         </is>
       </c>
       <c r="E974" s="13" t="n">
-        <v>16550</v>
+        <v>16540</v>
       </c>
       <c r="F974" s="13" t="n">
         <v>2</v>
@@ -30180,7 +30180,7 @@
         </is>
       </c>
       <c r="E975" s="13" t="n">
-        <v>16554</v>
+        <v>16544</v>
       </c>
       <c r="F975" s="13" t="n">
         <v>5</v>
@@ -30208,7 +30208,7 @@
         </is>
       </c>
       <c r="E976" s="13" t="n">
-        <v>16561</v>
+        <v>16551</v>
       </c>
       <c r="F976" s="13" t="n">
         <v>13</v>
@@ -30236,7 +30236,7 @@
         </is>
       </c>
       <c r="E977" s="13" t="n">
-        <v>16577</v>
+        <v>16567</v>
       </c>
       <c r="F977" s="13" t="n">
         <v>24</v>
@@ -30264,7 +30264,7 @@
         </is>
       </c>
       <c r="E978" s="13" t="n">
-        <v>16604</v>
+        <v>16594</v>
       </c>
       <c r="F978" s="13" t="n">
         <v>23</v>
@@ -30292,7 +30292,7 @@
         </is>
       </c>
       <c r="E979" s="13" t="n">
-        <v>16631</v>
+        <v>16621</v>
       </c>
       <c r="F979" s="13" t="n">
         <v>19</v>
@@ -30320,7 +30320,7 @@
         </is>
       </c>
       <c r="E980" s="13" t="n">
-        <v>16653</v>
+        <v>16643</v>
       </c>
       <c r="F980" s="13" t="n">
         <v>18</v>
@@ -30348,7 +30348,7 @@
         </is>
       </c>
       <c r="E981" s="13" t="n">
-        <v>16674</v>
+        <v>16664</v>
       </c>
       <c r="F981" s="13" t="n">
         <v>19</v>

--- a/알바로_부작_화_목록.xlsx
+++ b/알바로_부작_화_목록.xlsx
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>이바라 전 장관 협박과 후속 보도</t>
+          <t>에스키벨 전 장관 협박과 후속 보도</t>
         </is>
       </c>
       <c r="D23" s="16" t="n">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="H23" s="15" t="inlineStr">
         <is>
-          <t>특종 이후 협박 전화, 리히텐슈타인 신탁, 제보자 펠리시아노, 스위스 공조, 판결</t>
+          <t>특종 이후 협박 전화, 리히텐슈타인 신탁, 제보자 펠리시아노, 스위스 공조, 입건</t>
         </is>
       </c>
       <c r="I23" s="14" t="n"/>
@@ -4615,7 +4615,7 @@
       </c>
       <c r="G69" s="15" t="inlineStr">
         <is>
-          <t>며칠 후, 하비에르가 베르데갈 캐피털의 자금 출처를 더 깊이 파고들다가 충격적인 사실을 발견 합니다. 이 펀드가 사실 예전 무기밀매 조직의 잔존 자금을 세탁하는 위장 기구였다는 것입니 다. 카를로스가 개입하면서, 알바로가 다시 위장 잠입에 나서야 하는 상황이 됩니다.</t>
+          <t>며칠 후, 하비에르가 베르데갈 캐피털의 자금 출처를 더 깊이 파고들다가 충격적인 사실을 발견 합니다. 이 펀드가 사실 예전 무기밀매 조직의 잔존 자금을 세탁하는 위장 기구였다는 것입니다. 카를로스가 개입하면서, 알바로가 다시 위장 잠입에 나서야 하는 상황이 됩니다.</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="E70" s="13" t="n">
-        <v>2524</v>
+        <v>2523</v>
       </c>
       <c r="F70" s="13" t="n">
         <v>23</v>
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="E71" s="13" t="n">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="F71" s="13" t="n">
         <v>27</v>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="E72" s="13" t="n">
-        <v>2580</v>
+        <v>2579</v>
       </c>
       <c r="F72" s="13" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G72" s="15" t="inlineStr">
         <is>
@@ -4720,10 +4720,10 @@
         </is>
       </c>
       <c r="E73" s="13" t="n">
-        <v>2609</v>
+        <v>2606</v>
       </c>
       <c r="F73" s="13" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G73" s="15" t="inlineStr">
         <is>
@@ -4748,7 +4748,7 @@
         </is>
       </c>
       <c r="E74" s="13" t="n">
-        <v>2642</v>
+        <v>2637</v>
       </c>
       <c r="F74" s="13" t="n">
         <v>26</v>
@@ -4776,7 +4776,7 @@
         </is>
       </c>
       <c r="E75" s="13" t="n">
-        <v>2672</v>
+        <v>2667</v>
       </c>
       <c r="F75" s="13" t="n">
         <v>23</v>
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="E76" s="13" t="n">
-        <v>2698</v>
+        <v>2693</v>
       </c>
       <c r="F76" s="13" t="n">
         <v>26</v>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="E77" s="13" t="n">
-        <v>2728</v>
+        <v>2723</v>
       </c>
       <c r="F77" s="13" t="n">
         <v>22</v>
@@ -4860,10 +4860,10 @@
         </is>
       </c>
       <c r="E78" s="13" t="n">
-        <v>2753</v>
+        <v>2748</v>
       </c>
       <c r="F78" s="13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G78" s="15" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="E79" s="13" t="n">
-        <v>2778</v>
+        <v>2774</v>
       </c>
       <c r="F79" s="13" t="n">
         <v>21</v>
@@ -4916,14 +4916,14 @@
         </is>
       </c>
       <c r="E80" s="13" t="n">
-        <v>2803</v>
+        <v>2799</v>
       </c>
       <c r="F80" s="13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G80" s="15" t="inlineStr">
         <is>
-          <t>며칠 후, 마테오가 제네바 쪽 접촉을 시도하다가 누군가 자신을 미행하고 있다는 것을 눈치챕니 다. 알바로와 카를로스에게 다급히 연락합니다.</t>
+          <t>며칠 후, 마테오가 제네바 쪽 접촉을 시도하다가 누군가 자신을 미행하고 있다는 것을 눈치챕니다. 알바로와 카를로스에게 다급히 연락합니다.</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
         </is>
       </c>
       <c r="E81" s="13" t="n">
-        <v>2832</v>
+        <v>2826</v>
       </c>
       <c r="F81" s="13" t="n">
         <v>25</v>
@@ -4972,10 +4972,10 @@
         </is>
       </c>
       <c r="E82" s="13" t="n">
-        <v>2860</v>
+        <v>2854</v>
       </c>
       <c r="F82" s="13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G82" s="15" t="inlineStr">
         <is>
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="E83" s="13" t="n">
-        <v>2896</v>
+        <v>2888</v>
       </c>
       <c r="F83" s="13" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G83" s="15" t="inlineStr">
         <is>
@@ -5028,10 +5028,10 @@
         </is>
       </c>
       <c r="E84" s="13" t="n">
-        <v>2934</v>
+        <v>2923</v>
       </c>
       <c r="F84" s="13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G84" s="15" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         </is>
       </c>
       <c r="E85" s="13" t="n">
-        <v>2963</v>
+        <v>2951</v>
       </c>
       <c r="F85" s="13" t="n">
         <v>23</v>
@@ -5084,10 +5084,10 @@
         </is>
       </c>
       <c r="E86" s="13" t="n">
-        <v>2989</v>
+        <v>2977</v>
       </c>
       <c r="F86" s="13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G86" s="15" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="E87" s="13" t="n">
-        <v>3021</v>
+        <v>3008</v>
       </c>
       <c r="F87" s="13" t="n">
         <v>28</v>
@@ -5140,7 +5140,7 @@
         </is>
       </c>
       <c r="E88" s="13" t="n">
-        <v>3052</v>
+        <v>3039</v>
       </c>
       <c r="F88" s="13" t="n">
         <v>22</v>
@@ -5168,10 +5168,10 @@
         </is>
       </c>
       <c r="E89" s="13" t="n">
-        <v>3077</v>
+        <v>3064</v>
       </c>
       <c r="F89" s="13" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G89" s="15" t="inlineStr">
         <is>
@@ -5196,10 +5196,10 @@
         </is>
       </c>
       <c r="E90" s="13" t="n">
-        <v>3103</v>
+        <v>3088</v>
       </c>
       <c r="F90" s="13" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G90" s="15" t="inlineStr">
         <is>
@@ -5224,10 +5224,10 @@
         </is>
       </c>
       <c r="E91" s="13" t="n">
-        <v>3136</v>
+        <v>3118</v>
       </c>
       <c r="F91" s="13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G91" s="15" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="E92" s="13" t="n">
-        <v>3162</v>
+        <v>3143</v>
       </c>
       <c r="F92" s="13" t="n">
         <v>25</v>
@@ -5280,10 +5280,10 @@
         </is>
       </c>
       <c r="E93" s="13" t="n">
-        <v>3190</v>
+        <v>3171</v>
       </c>
       <c r="F93" s="13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G93" s="15" t="inlineStr">
         <is>
@@ -5308,10 +5308,10 @@
         </is>
       </c>
       <c r="E94" s="13" t="n">
-        <v>3212</v>
+        <v>3192</v>
       </c>
       <c r="F94" s="13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G94" s="15" t="inlineStr">
         <is>
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="E95" s="13" t="n">
-        <v>3235</v>
+        <v>3213</v>
       </c>
       <c r="F95" s="13" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G95" s="15" t="inlineStr">
         <is>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="E96" s="13" t="n">
-        <v>3257</v>
+        <v>3238</v>
       </c>
       <c r="F96" s="13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G96" s="15" t="inlineStr">
         <is>
@@ -5392,14 +5392,14 @@
         </is>
       </c>
       <c r="E97" s="13" t="n">
-        <v>3288</v>
+        <v>3268</v>
       </c>
       <c r="F97" s="13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G97" s="15" t="inlineStr">
         <is>
-          <t>라몬의 재판 준비 과정에서 새로운 자금 흐름이 포착됩니다. 알바로와 하비에르가 이 단서를 추 적하기 시작합니다. 이번 아크는 총 600문장 분량으로, 정치자금 세탁부터 청문회·법정 공방까지 다룰 예정입니다.</t>
+          <t>라몬의 재판 준비 과정에서 새로운 자금 흐름이 포착됩니다. 알바로와 하비에르가 이 단서를 추적하기 시작합니다.</t>
         </is>
       </c>
     </row>
@@ -5420,10 +5420,10 @@
         </is>
       </c>
       <c r="E98" s="13" t="n">
-        <v>3310</v>
+        <v>3289</v>
       </c>
       <c r="F98" s="13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G98" s="15" t="inlineStr">
         <is>
@@ -5448,10 +5448,10 @@
         </is>
       </c>
       <c r="E99" s="13" t="n">
-        <v>3335</v>
+        <v>3313</v>
       </c>
       <c r="F99" s="13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G99" s="15" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         </is>
       </c>
       <c r="E100" s="13" t="n">
-        <v>3357</v>
+        <v>3336</v>
       </c>
       <c r="F100" s="13" t="n">
         <v>18</v>
@@ -5504,10 +5504,10 @@
         </is>
       </c>
       <c r="E101" s="13" t="n">
-        <v>3378</v>
+        <v>3357</v>
       </c>
       <c r="F101" s="13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G101" s="15" t="inlineStr">
         <is>
@@ -5532,14 +5532,14 @@
         </is>
       </c>
       <c r="E102" s="13" t="n">
-        <v>3403</v>
+        <v>3381</v>
       </c>
       <c r="F102" s="13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G102" s="15" t="inlineStr">
         <is>
-          <t>며칠 후, 하비에르의 대학 동창을 통해 건설사 내부 인물 프란 이바녜스와의 접선이 성사됩니 다. 익명을 조건으로, 그가 계약 체결 과정에 대해 증언합니다.</t>
+          <t>며칠 후, 하비에르의 대학 동창을 통해 건설사 내부 인물 프란 이바녜스와의 접선이 성사됩니다. 익명을 조건으로, 그가 계약 체결 과정에 대해 증언합니다.</t>
         </is>
       </c>
     </row>
@@ -5560,14 +5560,14 @@
         </is>
       </c>
       <c r="E103" s="13" t="n">
-        <v>3428</v>
+        <v>3404</v>
       </c>
       <c r="F103" s="13" t="n">
         <v>22</v>
       </c>
       <c r="G103" s="15" t="inlineStr">
         <is>
-          <t>확보한 증거가 충분하다고 판단한 데스크가 보도를 승인합니다. 기사가 나가자마자, 의회에서 마누엘 수아소를 소환하는 청문회가 열립니다.</t>
+          <t>확보한 증거가 충분하다고 판단한 데스크가 보도를 승인합니다. 기사가 나가자마자, 의회에서마누엘 수아소를 소환하는 청문회가 열립니다.</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
         </is>
       </c>
       <c r="E104" s="13" t="n">
-        <v>3455</v>
+        <v>3430</v>
       </c>
       <c r="F104" s="13" t="n">
         <v>23</v>
@@ -5616,10 +5616,10 @@
         </is>
       </c>
       <c r="E105" s="13" t="n">
-        <v>3481</v>
+        <v>3456</v>
       </c>
       <c r="F105" s="13" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G105" s="15" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c r="E106" s="13" t="n">
-        <v>3501</v>
+        <v>3473</v>
       </c>
       <c r="F106" s="13" t="n">
         <v>17</v>
@@ -5672,14 +5672,14 @@
         </is>
       </c>
       <c r="E107" s="13" t="n">
-        <v>3521</v>
+        <v>3493</v>
       </c>
       <c r="F107" s="13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G107" s="15" t="inlineStr">
         <is>
-          <t>며칠 후, 압수된 자료에서 결정적인 증거가 발견됩니다. 마리나가 알바로와 하비에르에게 이를 알립니다.</t>
+          <t>며칠 후, 압수된 자료에서 결정적인 증거가 발견됩니다. 판사가 수사 비공개를 해제하자, 알바로와 하비에르는 공개된 법원 결정문에서 이를 확인합니다.</t>
         </is>
       </c>
     </row>
@@ -5700,10 +5700,10 @@
         </is>
       </c>
       <c r="E108" s="13" t="n">
-        <v>3540</v>
+        <v>3510</v>
       </c>
       <c r="F108" s="13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G108" s="15" t="inlineStr">
         <is>
@@ -5728,10 +5728,10 @@
         </is>
       </c>
       <c r="E109" s="13" t="n">
-        <v>3564</v>
+        <v>3533</v>
       </c>
       <c r="F109" s="13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G109" s="15" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
         </is>
       </c>
       <c r="E110" s="13" t="n">
-        <v>3588</v>
+        <v>3558</v>
       </c>
       <c r="F110" s="13" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G110" s="15" t="inlineStr">
         <is>
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="E111" s="13" t="n">
-        <v>3609</v>
+        <v>3581</v>
       </c>
       <c r="F111" s="13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G111" s="15" t="inlineStr">
         <is>
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="E112" s="13" t="n">
-        <v>3633</v>
+        <v>3603</v>
       </c>
       <c r="F112" s="13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G112" s="15" t="inlineStr">
         <is>
@@ -5840,10 +5840,10 @@
         </is>
       </c>
       <c r="E113" s="13" t="n">
-        <v>3654</v>
+        <v>3623</v>
       </c>
       <c r="F113" s="13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G113" s="15" t="inlineStr">
         <is>
@@ -5868,10 +5868,10 @@
         </is>
       </c>
       <c r="E114" s="13" t="n">
-        <v>3677</v>
+        <v>3645</v>
       </c>
       <c r="F114" s="13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G114" s="15" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="E115" s="13" t="n">
-        <v>3696</v>
+        <v>3663</v>
       </c>
       <c r="F115" s="13" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G115" s="15" t="inlineStr">
         <is>
@@ -5924,10 +5924,10 @@
         </is>
       </c>
       <c r="E116" s="13" t="n">
-        <v>3714</v>
+        <v>3684</v>
       </c>
       <c r="F116" s="13" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G116" s="15" t="inlineStr">
         <is>
@@ -5952,14 +5952,14 @@
         </is>
       </c>
       <c r="E117" s="13" t="n">
-        <v>3732</v>
+        <v>3699</v>
       </c>
       <c r="F117" s="13" t="n">
         <v>19</v>
       </c>
       <c r="G117" s="15" t="inlineStr">
         <is>
-          <t>새로운 사건. 카를로스가 톰포드 슈트·향수·선글라스와 스페인 명품 의류를 위조해 유통하는 대 규모 조직에 대한 정보를 갖고 알바로를 찾아옵니다. 이번 아크는 200~250문장 분량으로 계획 합니다.</t>
+          <t>새로운 사건. 카를로스가 톰포드 슈트·향수·선글라스와 스페인 명품 의류를 위조해 유통하는 대규모 조직에 대한 정보를 갖고 알바로를 찾아옵니다. CNI 소관이 아니어서 사건은 경찰과 세관이 맡고, 카를로스는 연락책 역할만 합니다.</t>
         </is>
       </c>
     </row>
@@ -5980,14 +5980,14 @@
         </is>
       </c>
       <c r="E118" s="13" t="n">
-        <v>3754</v>
+        <v>3721</v>
       </c>
       <c r="F118" s="13" t="n">
         <v>19</v>
       </c>
       <c r="G118" s="15" t="inlineStr">
         <is>
-          <t>알바로가 '알레한드로 푸익'이라는 위장 신분으로 브루노 살라스의 명품 중고매장을 찾아갑니다. 까다로운 고객을 위한 구매 대행이라는 명분으로 접근합니다.</t>
+          <t>알바로가 '알레한드로 폰스'라는 위장 신분으로 브루노 살라스의 명품 중고매장을 찾아갑니다. 까다로운 고객을 위한 구매 대행이라는 명분으로 접근합니다.</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
         </is>
       </c>
       <c r="E119" s="13" t="n">
-        <v>3776</v>
+        <v>3743</v>
       </c>
       <c r="F119" s="13" t="n">
         <v>19</v>
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="E120" s="13" t="n">
-        <v>3798</v>
+        <v>3765</v>
       </c>
       <c r="F120" s="13" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G120" s="15" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         </is>
       </c>
       <c r="E121" s="13" t="n">
-        <v>3817</v>
+        <v>3787</v>
       </c>
       <c r="F121" s="13" t="n">
         <v>17</v>
@@ -6092,10 +6092,10 @@
         </is>
       </c>
       <c r="E122" s="13" t="n">
-        <v>3837</v>
+        <v>3807</v>
       </c>
       <c r="F122" s="13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G122" s="15" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="E123" s="13" t="n">
-        <v>3854</v>
+        <v>3823</v>
       </c>
       <c r="F123" s="13" t="n">
         <v>10</v>
@@ -6148,14 +6148,14 @@
         </is>
       </c>
       <c r="E124" s="13" t="n">
-        <v>3866</v>
+        <v>3835</v>
       </c>
       <c r="F124" s="13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G124" s="15" t="inlineStr">
         <is>
-          <t>카를로스가 알바로에게 새로운 사건을 제안합니다. 가짜 백신과 미허가 시술을 판매하는 의료관 광 클리닉 네트워크에 대한 것입니다. 이번 아크는 250~300문장 분량으로 계획합니다.</t>
+          <t>카를로스가 알바로에게 새로운 사건을 제안합니다. 가짜 백신과 미허가 시술을 판매하는 의료관광 클리닉 네트워크에 대한 것입니다.</t>
         </is>
       </c>
     </row>
@@ -6176,10 +6176,10 @@
         </is>
       </c>
       <c r="E125" s="13" t="n">
-        <v>3888</v>
+        <v>3856</v>
       </c>
       <c r="F125" s="13" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G125" s="15" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
         </is>
       </c>
       <c r="E126" s="13" t="n">
-        <v>3918</v>
+        <v>3883</v>
       </c>
       <c r="F126" s="13" t="n">
         <v>20</v>
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="E127" s="13" t="n">
-        <v>3941</v>
+        <v>3906</v>
       </c>
       <c r="F127" s="13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G127" s="15" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         </is>
       </c>
       <c r="E128" s="13" t="n">
-        <v>3961</v>
+        <v>3925</v>
       </c>
       <c r="F128" s="13" t="n">
         <v>20</v>
@@ -6288,7 +6288,7 @@
         </is>
       </c>
       <c r="E129" s="13" t="n">
-        <v>3984</v>
+        <v>3948</v>
       </c>
       <c r="F129" s="13" t="n">
         <v>16</v>
@@ -6316,7 +6316,7 @@
         </is>
       </c>
       <c r="E130" s="13" t="n">
-        <v>4003</v>
+        <v>3967</v>
       </c>
       <c r="F130" s="13" t="n">
         <v>22</v>
@@ -6344,7 +6344,7 @@
         </is>
       </c>
       <c r="E131" s="13" t="n">
-        <v>4028</v>
+        <v>3992</v>
       </c>
       <c r="F131" s="13" t="n">
         <v>13</v>
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="E132" s="13" t="n">
-        <v>4043</v>
+        <v>4007</v>
       </c>
       <c r="F132" s="13" t="n">
         <v>12</v>
@@ -6400,10 +6400,10 @@
         </is>
       </c>
       <c r="E133" s="13" t="n">
-        <v>4058</v>
+        <v>4022</v>
       </c>
       <c r="F133" s="13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G133" s="15" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="E134" s="13" t="n">
-        <v>4078</v>
+        <v>4040</v>
       </c>
       <c r="F134" s="13" t="n">
         <v>16</v>
@@ -6456,10 +6456,10 @@
         </is>
       </c>
       <c r="E135" s="13" t="n">
-        <v>4097</v>
+        <v>4059</v>
       </c>
       <c r="F135" s="13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G135" s="15" t="inlineStr">
         <is>
@@ -6484,14 +6484,14 @@
         </is>
       </c>
       <c r="E136" s="13" t="n">
-        <v>4109</v>
+        <v>4073</v>
       </c>
       <c r="F136" s="13" t="n">
         <v>14</v>
       </c>
       <c r="G136" s="15" t="inlineStr">
         <is>
-          <t>알바로가 카를로스의 도움으로 소피아 엘로르사의 배후를 확인합니다.</t>
+          <t>알바로가 공개 등기부와 하비에르의 취재원을 통해 소피아 엘로르사의 배후를 확인합니다.</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6512,7 @@
         </is>
       </c>
       <c r="E137" s="13" t="n">
-        <v>4126</v>
+        <v>4090</v>
       </c>
       <c r="F137" s="13" t="n">
         <v>10</v>
@@ -6540,7 +6540,7 @@
         </is>
       </c>
       <c r="E138" s="13" t="n">
-        <v>4139</v>
+        <v>4103</v>
       </c>
       <c r="F138" s="13" t="n">
         <v>12</v>
@@ -6568,10 +6568,10 @@
         </is>
       </c>
       <c r="E139" s="13" t="n">
-        <v>4153</v>
+        <v>4117</v>
       </c>
       <c r="F139" s="13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G139" s="15" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         </is>
       </c>
       <c r="E140" s="13" t="n">
-        <v>4169</v>
+        <v>4132</v>
       </c>
       <c r="F140" s="13" t="n">
         <v>18</v>
@@ -6624,7 +6624,7 @@
         </is>
       </c>
       <c r="E141" s="13" t="n">
-        <v>4191</v>
+        <v>4153</v>
       </c>
       <c r="F141" s="13" t="n">
         <v>15</v>
@@ -6652,10 +6652,10 @@
         </is>
       </c>
       <c r="E142" s="13" t="n">
-        <v>4209</v>
+        <v>4171</v>
       </c>
       <c r="F142" s="13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G142" s="15" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         </is>
       </c>
       <c r="E143" s="13" t="n">
-        <v>4227</v>
+        <v>4188</v>
       </c>
       <c r="F143" s="13" t="n">
         <v>10</v>
@@ -6708,10 +6708,10 @@
         </is>
       </c>
       <c r="E144" s="13" t="n">
-        <v>4239</v>
+        <v>4200</v>
       </c>
       <c r="F144" s="13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G144" s="15" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="E145" s="13" t="n">
-        <v>4255</v>
+        <v>4218</v>
       </c>
       <c r="F145" s="13" t="n">
         <v>11</v>
@@ -6764,7 +6764,7 @@
         </is>
       </c>
       <c r="E146" s="13" t="n">
-        <v>4269</v>
+        <v>4232</v>
       </c>
       <c r="F146" s="13" t="n">
         <v>11</v>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="E147" s="13" t="n">
-        <v>4282</v>
+        <v>4245</v>
       </c>
       <c r="F147" s="13" t="n">
         <v>13</v>
@@ -6820,10 +6820,10 @@
         </is>
       </c>
       <c r="E148" s="13" t="n">
-        <v>4298</v>
+        <v>4261</v>
       </c>
       <c r="F148" s="13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G148" s="15" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         </is>
       </c>
       <c r="E149" s="13" t="n">
-        <v>4311</v>
+        <v>4276</v>
       </c>
       <c r="F149" s="13" t="n">
         <v>10</v>
@@ -6876,7 +6876,7 @@
         </is>
       </c>
       <c r="E150" s="13" t="n">
-        <v>4323</v>
+        <v>4288</v>
       </c>
       <c r="F150" s="13" t="n">
         <v>8</v>
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="E151" s="13" t="n">
-        <v>4334</v>
+        <v>4299</v>
       </c>
       <c r="F151" s="13" t="n">
         <v>12</v>
@@ -6932,10 +6932,10 @@
         </is>
       </c>
       <c r="E152" s="13" t="n">
-        <v>4349</v>
+        <v>4314</v>
       </c>
       <c r="F152" s="13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G152" s="15" t="inlineStr">
         <is>
@@ -6960,10 +6960,10 @@
         </is>
       </c>
       <c r="E153" s="13" t="n">
-        <v>4363</v>
+        <v>4327</v>
       </c>
       <c r="F153" s="13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G153" s="15" t="inlineStr">
         <is>
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="E154" s="13" t="n">
-        <v>4376</v>
+        <v>4339</v>
       </c>
       <c r="F154" s="13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G154" s="15" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         </is>
       </c>
       <c r="E155" s="13" t="n">
-        <v>4397</v>
+        <v>4362</v>
       </c>
       <c r="F155" s="13" t="n">
         <v>10</v>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="E156" s="13" t="n">
-        <v>4412</v>
+        <v>4375</v>
       </c>
       <c r="F156" s="13" t="n">
         <v>11</v>
@@ -7072,10 +7072,10 @@
         </is>
       </c>
       <c r="E157" s="13" t="n">
-        <v>4425</v>
+        <v>4388</v>
       </c>
       <c r="F157" s="13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G157" s="15" t="inlineStr">
         <is>
@@ -7100,10 +7100,10 @@
         </is>
       </c>
       <c r="E158" s="13" t="n">
-        <v>4439</v>
+        <v>4401</v>
       </c>
       <c r="F158" s="13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G158" s="15" t="inlineStr">
         <is>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="E159" s="13" t="n">
-        <v>4450</v>
+        <v>4411</v>
       </c>
       <c r="F159" s="13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G159" s="15" t="inlineStr">
         <is>
@@ -7156,10 +7156,10 @@
         </is>
       </c>
       <c r="E160" s="13" t="n">
-        <v>4462</v>
+        <v>4421</v>
       </c>
       <c r="F160" s="13" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G160" s="15" t="inlineStr">
         <is>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="E161" s="13" t="n">
-        <v>4477</v>
+        <v>4433</v>
       </c>
       <c r="F161" s="13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G161" s="15" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         </is>
       </c>
       <c r="E162" s="13" t="n">
-        <v>4493</v>
+        <v>4447</v>
       </c>
       <c r="F162" s="13" t="n">
         <v>12</v>
@@ -7240,7 +7240,7 @@
         </is>
       </c>
       <c r="E163" s="13" t="n">
-        <v>4508</v>
+        <v>4462</v>
       </c>
       <c r="F163" s="13" t="n">
         <v>11</v>
@@ -7268,10 +7268,10 @@
         </is>
       </c>
       <c r="E164" s="13" t="n">
-        <v>4522</v>
+        <v>4476</v>
       </c>
       <c r="F164" s="13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G164" s="15" t="inlineStr">
         <is>
@@ -7296,10 +7296,10 @@
         </is>
       </c>
       <c r="E165" s="13" t="n">
-        <v>4535</v>
+        <v>4488</v>
       </c>
       <c r="F165" s="13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G165" s="15" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         </is>
       </c>
       <c r="E166" s="13" t="n">
-        <v>4549</v>
+        <v>4500</v>
       </c>
       <c r="F166" s="13" t="n">
         <v>8</v>
@@ -7352,10 +7352,10 @@
         </is>
       </c>
       <c r="E167" s="13" t="n">
-        <v>4559</v>
+        <v>4510</v>
       </c>
       <c r="F167" s="13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G167" s="15" t="inlineStr">
         <is>
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="E168" s="13" t="n">
-        <v>4574</v>
+        <v>4523</v>
       </c>
       <c r="F168" s="13" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G168" s="15" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         </is>
       </c>
       <c r="E169" s="13" t="n">
-        <v>4591</v>
+        <v>4537</v>
       </c>
       <c r="F169" s="13" t="n">
         <v>12</v>
@@ -7436,10 +7436,10 @@
         </is>
       </c>
       <c r="E170" s="13" t="n">
-        <v>4606</v>
+        <v>4552</v>
       </c>
       <c r="F170" s="13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G170" s="15" t="inlineStr">
         <is>
@@ -7464,10 +7464,10 @@
         </is>
       </c>
       <c r="E171" s="13" t="n">
-        <v>4620</v>
+        <v>4563</v>
       </c>
       <c r="F171" s="13" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G171" s="15" t="inlineStr">
         <is>
@@ -7492,10 +7492,10 @@
         </is>
       </c>
       <c r="E172" s="13" t="n">
-        <v>4636</v>
+        <v>4576</v>
       </c>
       <c r="F172" s="13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G172" s="15" t="inlineStr">
         <is>
@@ -7520,14 +7520,14 @@
         </is>
       </c>
       <c r="E173" s="13" t="n">
-        <v>4651</v>
+        <v>4588</v>
       </c>
       <c r="F173" s="13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G173" s="15" t="inlineStr">
         <is>
-          <t>확인 결과, 마르코스라는 아이는 존재하지 않는다는 것이 드러나며 보도가 나갑니다.</t>
+          <t>확인 결과, 루카스라는 아이는 존재하지 않는다는 것이 드러나며 보도가 나갑니다.</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
         </is>
       </c>
       <c r="E174" s="13" t="n">
-        <v>4664</v>
+        <v>4600</v>
       </c>
       <c r="F174" s="13" t="n">
         <v>17</v>
@@ -7576,7 +7576,7 @@
         </is>
       </c>
       <c r="E175" s="13" t="n">
-        <v>4684</v>
+        <v>4620</v>
       </c>
       <c r="F175" s="13" t="n">
         <v>18</v>
@@ -7604,10 +7604,10 @@
         </is>
       </c>
       <c r="E176" s="13" t="n">
-        <v>4705</v>
+        <v>4641</v>
       </c>
       <c r="F176" s="13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G176" s="15" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         </is>
       </c>
       <c r="E177" s="13" t="n">
-        <v>4725</v>
+        <v>4660</v>
       </c>
       <c r="F177" s="13" t="n">
         <v>14</v>
@@ -7660,14 +7660,14 @@
         </is>
       </c>
       <c r="E178" s="13" t="n">
-        <v>4742</v>
+        <v>4677</v>
       </c>
       <c r="F178" s="13" t="n">
         <v>11</v>
       </c>
       <c r="G178" s="15" t="inlineStr">
         <is>
-          <t>몇 주 후, 수사와 보도가 결실을 맺습니다.</t>
+          <t>몇 주 후, 수사와 보도가 결실을 향해 한 걸음 더 나아갑니다.</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
         </is>
       </c>
       <c r="E179" s="13" t="n">
-        <v>4755</v>
+        <v>4690</v>
       </c>
       <c r="F179" s="13" t="n">
         <v>16</v>
@@ -7716,10 +7716,10 @@
         </is>
       </c>
       <c r="E180" s="13" t="n">
-        <v>4773</v>
+        <v>4708</v>
       </c>
       <c r="F180" s="13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G180" s="15" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="E181" s="13" t="n">
-        <v>4789</v>
+        <v>4723</v>
       </c>
       <c r="F181" s="13" t="n">
         <v>15</v>
@@ -7772,7 +7772,7 @@
         </is>
       </c>
       <c r="E182" s="13" t="n">
-        <v>4807</v>
+        <v>4741</v>
       </c>
       <c r="F182" s="13" t="n">
         <v>15</v>
@@ -7800,14 +7800,14 @@
         </is>
       </c>
       <c r="E183" s="13" t="n">
-        <v>4825</v>
+        <v>4759</v>
       </c>
       <c r="F183" s="13" t="n">
         <v>12</v>
       </c>
       <c r="G183" s="15" t="inlineStr">
         <is>
-          <t>알바로가 컨설턴트 '다니엘 로메로'(재사용 위장 신분)로 페냐 알타 발전소에 처음 출입합니다. 보안 책임자 마우리시오 델가도가 그를 맞이합니다.</t>
+          <t>알바로가 컨설턴트 '휴고 라사르테'(이번 작전을 위해 새로 만든 위장 신분)로 페냐 알타 발전소에 처음 출입합니다. 보안 책임자 마우리시오 델가도가 그를 맞이합니다.</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="E184" s="13" t="n">
-        <v>4839</v>
+        <v>4773</v>
       </c>
       <c r="F184" s="13" t="n">
         <v>12</v>
@@ -7856,7 +7856,7 @@
         </is>
       </c>
       <c r="E185" s="13" t="n">
-        <v>4854</v>
+        <v>4788</v>
       </c>
       <c r="F185" s="13" t="n">
         <v>13</v>
@@ -7884,7 +7884,7 @@
         </is>
       </c>
       <c r="E186" s="13" t="n">
-        <v>4870</v>
+        <v>4804</v>
       </c>
       <c r="F186" s="13" t="n">
         <v>12</v>
@@ -7912,7 +7912,7 @@
         </is>
       </c>
       <c r="E187" s="13" t="n">
-        <v>4884</v>
+        <v>4818</v>
       </c>
       <c r="F187" s="13" t="n">
         <v>12</v>
@@ -7940,10 +7940,10 @@
         </is>
       </c>
       <c r="E188" s="13" t="n">
-        <v>4898</v>
+        <v>4832</v>
       </c>
       <c r="F188" s="13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G188" s="15" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         </is>
       </c>
       <c r="E189" s="13" t="n">
-        <v>4910</v>
+        <v>4846</v>
       </c>
       <c r="F189" s="13" t="n">
         <v>12</v>
@@ -7996,7 +7996,7 @@
         </is>
       </c>
       <c r="E190" s="13" t="n">
-        <v>4924</v>
+        <v>4860</v>
       </c>
       <c r="F190" s="13" t="n">
         <v>12</v>
@@ -8024,7 +8024,7 @@
         </is>
       </c>
       <c r="E191" s="13" t="n">
-        <v>4938</v>
+        <v>4874</v>
       </c>
       <c r="F191" s="13" t="n">
         <v>13</v>
@@ -8052,14 +8052,14 @@
         </is>
       </c>
       <c r="E192" s="13" t="n">
-        <v>4954</v>
+        <v>4890</v>
       </c>
       <c r="F192" s="13" t="n">
         <v>10</v>
       </c>
       <c r="G192" s="15" t="inlineStr">
         <is>
-          <t>다음 날 밤, 알바로가 안전거리에서 지켜보는 가운데 CNI가 접선 현장을 급습합니다.</t>
+          <t>다음 날 밤, 알바로가 안전거리에서 지켜보는 가운데 CNI의 정보에 따라 치안경비대(Guardia Civil)가 접선 현장을 급습하고, 카를로스가 현장에 함께합니다.</t>
         </is>
       </c>
     </row>
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="E193" s="13" t="n">
-        <v>4966</v>
+        <v>4902</v>
       </c>
       <c r="F193" s="13" t="n">
         <v>12</v>
@@ -8108,10 +8108,10 @@
         </is>
       </c>
       <c r="E194" s="13" t="n">
-        <v>4980</v>
+        <v>4916</v>
       </c>
       <c r="F194" s="13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G194" s="15" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="E195" s="13" t="n">
-        <v>4992</v>
+        <v>4929</v>
       </c>
       <c r="F195" s="13" t="n">
         <v>12</v>
@@ -8164,10 +8164,10 @@
         </is>
       </c>
       <c r="E196" s="13" t="n">
-        <v>5006</v>
+        <v>4943</v>
       </c>
       <c r="F196" s="13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G196" s="15" t="inlineStr">
         <is>
@@ -8192,10 +8192,10 @@
         </is>
       </c>
       <c r="E197" s="13" t="n">
-        <v>5019</v>
+        <v>4958</v>
       </c>
       <c r="F197" s="13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G197" s="15" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         </is>
       </c>
       <c r="E198" s="13" t="n">
-        <v>5035</v>
+        <v>4973</v>
       </c>
       <c r="F198" s="13" t="n">
         <v>10</v>
@@ -8248,10 +8248,10 @@
         </is>
       </c>
       <c r="E199" s="13" t="n">
-        <v>5047</v>
+        <v>4985</v>
       </c>
       <c r="F199" s="13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G199" s="15" t="inlineStr">
         <is>
@@ -8276,10 +8276,10 @@
         </is>
       </c>
       <c r="E200" s="13" t="n">
-        <v>5061</v>
+        <v>4998</v>
       </c>
       <c r="F200" s="13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G200" s="15" t="inlineStr">
         <is>
@@ -8304,10 +8304,10 @@
         </is>
       </c>
       <c r="E201" s="13" t="n">
-        <v>5076</v>
+        <v>5015</v>
       </c>
       <c r="F201" s="13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G201" s="15" t="inlineStr">
         <is>
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="E202" s="13" t="n">
-        <v>5088</v>
+        <v>5029</v>
       </c>
       <c r="F202" s="13" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G202" s="15" t="inlineStr">
         <is>
@@ -8360,14 +8360,14 @@
         </is>
       </c>
       <c r="E203" s="13" t="n">
-        <v>5108</v>
+        <v>5051</v>
       </c>
       <c r="F203" s="13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G203" s="15" t="inlineStr">
         <is>
-          <t>새로운 작전. 카를로스가 알바로에게 역외 페이퍼컴퍼니를 이용한 대규모 탈세 네트워크를 조사 해달라고 요청합니다. 이번 아크는 300문장 분량으로 계획합니다.</t>
+          <t>새로운 작전. 카를로스가 알바로에게 역외 페이퍼컴퍼니를 이용한 대규모 탈세 네트워크를 조사 해달라고 요청합니다.</t>
         </is>
       </c>
     </row>
@@ -8388,14 +8388,14 @@
         </is>
       </c>
       <c r="E204" s="13" t="n">
-        <v>5125</v>
+        <v>5069</v>
       </c>
       <c r="F204" s="13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G204" s="15" t="inlineStr">
         <is>
-          <t>경제 전문가 로드리고 casal이 알바로에게 역외 금융·조세 구조 관련 지식을 속성으로 가르칩니 다.</t>
+          <t>경제 전문가 로드리고 카살이 알바로에게 역외 금융·조세 구조 관련 지식을 속성으로 가르칩니다.</t>
         </is>
       </c>
     </row>
@@ -8416,14 +8416,14 @@
         </is>
       </c>
       <c r="E205" s="13" t="n">
-        <v>5142</v>
+        <v>5085</v>
       </c>
       <c r="F205" s="13" t="n">
         <v>14</v>
       </c>
       <c r="G205" s="15" t="inlineStr">
         <is>
-          <t>알바로가 '알레한드로 푸익' 위장 신분으로 페란 이 아소시아도스 사무실을 방문해 대표 쿠스토 디오 페란을 만납니다.</t>
+          <t>알바로가 '곤살로 발카르셀' 위장 신분으로 페란 이 아소시아도스 사무실을 방문해 대표 쿠스토디오 페란을 만납니다.</t>
         </is>
       </c>
     </row>
@@ -8444,7 +8444,7 @@
         </is>
       </c>
       <c r="E206" s="13" t="n">
-        <v>5159</v>
+        <v>5102</v>
       </c>
       <c r="F206" s="13" t="n">
         <v>10</v>
@@ -8472,7 +8472,7 @@
         </is>
       </c>
       <c r="E207" s="13" t="n">
-        <v>5171</v>
+        <v>5114</v>
       </c>
       <c r="F207" s="13" t="n">
         <v>15</v>
@@ -8500,7 +8500,7 @@
         </is>
       </c>
       <c r="E208" s="13" t="n">
-        <v>5189</v>
+        <v>5132</v>
       </c>
       <c r="F208" s="13" t="n">
         <v>10</v>
@@ -8528,7 +8528,7 @@
         </is>
       </c>
       <c r="E209" s="13" t="n">
-        <v>5202</v>
+        <v>5145</v>
       </c>
       <c r="F209" s="13" t="n">
         <v>13</v>
@@ -8556,7 +8556,7 @@
         </is>
       </c>
       <c r="E210" s="13" t="n">
-        <v>5217</v>
+        <v>5160</v>
       </c>
       <c r="F210" s="13" t="n">
         <v>11</v>
@@ -8584,7 +8584,7 @@
         </is>
       </c>
       <c r="E211" s="13" t="n">
-        <v>5231</v>
+        <v>5174</v>
       </c>
       <c r="F211" s="13" t="n">
         <v>12</v>
@@ -8612,7 +8612,7 @@
         </is>
       </c>
       <c r="E212" s="13" t="n">
-        <v>5246</v>
+        <v>5189</v>
       </c>
       <c r="F212" s="13" t="n">
         <v>10</v>
@@ -8640,14 +8640,14 @@
         </is>
       </c>
       <c r="E213" s="13" t="n">
-        <v>5258</v>
+        <v>5201</v>
       </c>
       <c r="F213" s="13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G213" s="15" t="inlineStr">
         <is>
-          <t>판사의 승인을 받아, 페란 이 아소시아도스 사무실에 대한 압수수색이 집행됩니다.</t>
+          <t>판사의 승인을 받아, 페란 이 아소시아도스 사무실에 대한 압수수색이 집행됩니다. 수색은 UCO와 세무청이 맡고, 카를로스는 정보만 공유합니다.</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="E214" s="13" t="n">
-        <v>5273</v>
+        <v>5215</v>
       </c>
       <c r="F214" s="13" t="n">
         <v>12</v>
@@ -8696,7 +8696,7 @@
         </is>
       </c>
       <c r="E215" s="13" t="n">
-        <v>5288</v>
+        <v>5230</v>
       </c>
       <c r="F215" s="13" t="n">
         <v>11</v>
@@ -8724,7 +8724,7 @@
         </is>
       </c>
       <c r="E216" s="13" t="n">
-        <v>5301</v>
+        <v>5243</v>
       </c>
       <c r="F216" s="13" t="n">
         <v>10</v>
@@ -8752,7 +8752,7 @@
         </is>
       </c>
       <c r="E217" s="13" t="n">
-        <v>5314</v>
+        <v>5256</v>
       </c>
       <c r="F217" s="13" t="n">
         <v>10</v>
@@ -8780,14 +8780,14 @@
         </is>
       </c>
       <c r="E218" s="13" t="n">
-        <v>5326</v>
+        <v>5268</v>
       </c>
       <c r="F218" s="13" t="n">
         <v>12</v>
       </c>
       <c r="G218" s="15" t="inlineStr">
         <is>
-          <t>페란 사건 특종이 보도된 직후, 예상치 못한 압박이 시작됩니다. 정치권 고객 중 한 명, 전직 장 관 알베르토 이바라의 이름이 확인되면서 사건이 새로운 국면으로 접어듭니다.</t>
+          <t>페란 사건 특종이 보도된 직후, 예상치 못한 압박이 시작됩니다. 정치권 고객 중 한 명, 전직 장관 알베르토 에스키벨의 이름이 확인되면서 사건이 새로운 국면으로 접어듭니다.</t>
         </is>
       </c>
     </row>
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="E219" s="13" t="n">
-        <v>5341</v>
+        <v>5283</v>
       </c>
       <c r="F219" s="13" t="n">
         <v>13</v>
@@ -8836,14 +8836,14 @@
         </is>
       </c>
       <c r="E220" s="13" t="n">
-        <v>5357</v>
+        <v>5299</v>
       </c>
       <c r="F220" s="13" t="n">
         <v>10</v>
       </c>
       <c r="G220" s="15" t="inlineStr">
         <is>
-          <t>알바로와 하비에르가 이바라 전 장관에게 공식 답변을 요청하며 직접 접촉을 시도합니다.</t>
+          <t>알바로와 하비에르가 에스키벨 전 장관에게 공식 답변을 요청하며 직접 접촉을 시도합니다.</t>
         </is>
       </c>
     </row>
@@ -8864,14 +8864,14 @@
         </is>
       </c>
       <c r="E221" s="13" t="n">
-        <v>5369</v>
+        <v>5311</v>
       </c>
       <c r="F221" s="13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G221" s="15" t="inlineStr">
         <is>
-          <t>카를로스가 이바라 명의의 역외 구조에 대한 세부 정보를 알바로와 공유합니다.</t>
+          <t>카를로스가 에스키벨 명의의 역외 구조에 대한 세부 정보를 알바로와 공유합니다.</t>
         </is>
       </c>
     </row>
@@ -8892,14 +8892,14 @@
         </is>
       </c>
       <c r="E222" s="13" t="n">
-        <v>5384</v>
+        <v>5327</v>
       </c>
       <c r="F222" s="13" t="n">
         <v>10</v>
       </c>
       <c r="G222" s="15" t="inlineStr">
         <is>
-          <t>이틀 후, 이바라 측에서 서면 답변이 도착합니다. 예상대로 회피성입니다.</t>
+          <t>이틀 후, 에스키벨 측에서 서면 답변이 도착합니다. 예상대로 회피성입니다.</t>
         </is>
       </c>
     </row>
@@ -8920,7 +8920,7 @@
         </is>
       </c>
       <c r="E223" s="13" t="n">
-        <v>5396</v>
+        <v>5339</v>
       </c>
       <c r="F223" s="13" t="n">
         <v>11</v>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="E224" s="13" t="n">
-        <v>5409</v>
+        <v>5352</v>
       </c>
       <c r="F224" s="13" t="n">
         <v>13</v>
@@ -8976,7 +8976,7 @@
         </is>
       </c>
       <c r="E225" s="13" t="n">
-        <v>5425</v>
+        <v>5368</v>
       </c>
       <c r="F225" s="13" t="n">
         <v>9</v>
@@ -9004,7 +9004,7 @@
         </is>
       </c>
       <c r="E226" s="13" t="n">
-        <v>5436</v>
+        <v>5379</v>
       </c>
       <c r="F226" s="13" t="n">
         <v>13</v>
@@ -9032,7 +9032,7 @@
         </is>
       </c>
       <c r="E227" s="13" t="n">
-        <v>5452</v>
+        <v>5395</v>
       </c>
       <c r="F227" s="13" t="n">
         <v>11</v>
@@ -9060,7 +9060,7 @@
         </is>
       </c>
       <c r="E228" s="13" t="n">
-        <v>5466</v>
+        <v>5409</v>
       </c>
       <c r="F228" s="13" t="n">
         <v>11</v>
@@ -9088,7 +9088,7 @@
         </is>
       </c>
       <c r="E229" s="13" t="n">
-        <v>5479</v>
+        <v>5422</v>
       </c>
       <c r="F229" s="13" t="n">
         <v>10</v>
@@ -9116,7 +9116,7 @@
         </is>
       </c>
       <c r="E230" s="13" t="n">
-        <v>5492</v>
+        <v>5435</v>
       </c>
       <c r="F230" s="13" t="n">
         <v>11</v>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="E231" s="13" t="n">
-        <v>5506</v>
+        <v>5449</v>
       </c>
       <c r="F231" s="13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G231" s="15" t="inlineStr">
         <is>
@@ -9172,10 +9172,10 @@
         </is>
       </c>
       <c r="E232" s="13" t="n">
-        <v>5518</v>
+        <v>5463</v>
       </c>
       <c r="F232" s="13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G232" s="15" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         </is>
       </c>
       <c r="E233" s="13" t="n">
-        <v>5533</v>
+        <v>5477</v>
       </c>
       <c r="F233" s="13" t="n">
         <v>10</v>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="E234" s="13" t="n">
-        <v>5545</v>
+        <v>5489</v>
       </c>
       <c r="F234" s="13" t="n">
         <v>11</v>
@@ -9256,10 +9256,10 @@
         </is>
       </c>
       <c r="E235" s="13" t="n">
-        <v>5558</v>
+        <v>5502</v>
       </c>
       <c r="F235" s="13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G235" s="15" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         </is>
       </c>
       <c r="E236" s="13" t="n">
-        <v>5575</v>
+        <v>5518</v>
       </c>
       <c r="F236" s="13" t="n">
         <v>12</v>
@@ -9312,7 +9312,7 @@
         </is>
       </c>
       <c r="E237" s="13" t="n">
-        <v>5589</v>
+        <v>5532</v>
       </c>
       <c r="F237" s="13" t="n">
         <v>10</v>
@@ -9340,7 +9340,7 @@
         </is>
       </c>
       <c r="E238" s="13" t="n">
-        <v>5602</v>
+        <v>5545</v>
       </c>
       <c r="F238" s="13" t="n">
         <v>10</v>
@@ -9368,7 +9368,7 @@
         </is>
       </c>
       <c r="E239" s="13" t="n">
-        <v>5615</v>
+        <v>5558</v>
       </c>
       <c r="F239" s="13" t="n">
         <v>11</v>
@@ -9396,14 +9396,14 @@
         </is>
       </c>
       <c r="E240" s="13" t="n">
-        <v>5628</v>
+        <v>5571</v>
       </c>
       <c r="F240" s="13" t="n">
         <v>9</v>
       </c>
       <c r="G240" s="15" t="inlineStr">
         <is>
-          <t>압수 자료를 근거로, 검찰이 이바라 전 장관에 대한 정식 수사를 개시합니다.</t>
+          <t>압수 자료를 근거로, 검찰이 에스키벨 전 장관에 대한 정식 수사를 개시합니다.</t>
         </is>
       </c>
     </row>
@@ -9424,7 +9424,7 @@
         </is>
       </c>
       <c r="E241" s="13" t="n">
-        <v>5640</v>
+        <v>5583</v>
       </c>
       <c r="F241" s="13" t="n">
         <v>9</v>
@@ -9452,7 +9452,7 @@
         </is>
       </c>
       <c r="E242" s="13" t="n">
-        <v>5651</v>
+        <v>5594</v>
       </c>
       <c r="F242" s="13" t="n">
         <v>10</v>
@@ -9480,7 +9480,7 @@
         </is>
       </c>
       <c r="E243" s="13" t="n">
-        <v>5664</v>
+        <v>5607</v>
       </c>
       <c r="F243" s="13" t="n">
         <v>16</v>
@@ -9508,14 +9508,14 @@
         </is>
       </c>
       <c r="E244" s="13" t="n">
-        <v>5683</v>
+        <v>5626</v>
       </c>
       <c r="F244" s="13" t="n">
         <v>16</v>
       </c>
       <c r="G244" s="15" t="inlineStr">
         <is>
-          <t>새로운 작전. 카를로스가 알바로에게 '가짜 주권 클라우드' 사건을 제안합니다. 스페인 공공기관 데이터를 EU 역내에만 저장한다고 광고해온 기업 '누베 이베리카'가, 실제로는 데이터를 역외로 우회시키고 있다는 의혹입니다. 등장인물은 전원 남성으로 구성합니다.</t>
+          <t>새로운 작전. 카를로스가 알바로에게 '가짜 주권 클라우드' 사건을 제안합니다. 스페인 공공기관 데이터를 EU 역내에만 저장한다고 광고해온 기업 '누베 이베리카'가, 실제로는 데이터를 역외로 우회시키고 있다는 의혹입니다.</t>
         </is>
       </c>
     </row>
@@ -9536,14 +9536,14 @@
         </is>
       </c>
       <c r="E245" s="13" t="n">
-        <v>5702</v>
+        <v>5645</v>
       </c>
       <c r="F245" s="13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G245" s="15" t="inlineStr">
         <is>
-          <t>기술 전문가 마르코스 utrero가 알바로에게 클라우드 인프라와 데이터 주권 관련 지식을 속성으 로 가르칩니다.</t>
+          <t>기술 전문가 마르코스 우트레로가 알바로에게 클라우드 인프라와 데이터 주권 관련 지식을 속성으로 가르칩니다.</t>
         </is>
       </c>
     </row>
@@ -9564,14 +9564,14 @@
         </is>
       </c>
       <c r="E246" s="13" t="n">
-        <v>5716</v>
+        <v>5661</v>
       </c>
       <c r="F246" s="13" t="n">
         <v>10</v>
       </c>
       <c r="G246" s="15" t="inlineStr">
         <is>
-          <t>알바로가 컨설턴트 신분으로 누베 이베리카 본사에 출입합니다. 기술이사 헤라르도 몰리나가 그 를 맞이합니다.</t>
+          <t>알바로가 컨설턴트 신분으로 누베 이베리카 본사에 출입합니다. 이번에는 새로 만든 위장 신분 '세르히오 알칸타라'를 씁니다. 기술이사 헤라르도 몰리나가 그를 맞이합니다.</t>
         </is>
       </c>
     </row>
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="E247" s="13" t="n">
-        <v>5729</v>
+        <v>5674</v>
       </c>
       <c r="F247" s="13" t="n">
         <v>10</v>
@@ -9620,14 +9620,14 @@
         </is>
       </c>
       <c r="E248" s="13" t="n">
-        <v>5741</v>
+        <v>5686</v>
       </c>
       <c r="F248" s="13" t="n">
         <v>13</v>
       </c>
       <c r="G248" s="15" t="inlineStr">
         <is>
-          <t>알바로가 시스템 엔지니어 사무엘 로카와 자연스럽게 대화를나누며 정보를 캐냅니다.</t>
+          <t>알바로가 시스템 엔지니어 사무엘 로카와 자연스럽게 대화를 나누며 정보를 캐냅니다.</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9648,7 @@
         </is>
       </c>
       <c r="E249" s="13" t="n">
-        <v>5756</v>
+        <v>5701</v>
       </c>
       <c r="F249" s="13" t="n">
         <v>10</v>
@@ -9676,7 +9676,7 @@
         </is>
       </c>
       <c r="E250" s="13" t="n">
-        <v>5769</v>
+        <v>5714</v>
       </c>
       <c r="F250" s="13" t="n">
         <v>10</v>
@@ -9704,10 +9704,10 @@
         </is>
       </c>
       <c r="E251" s="13" t="n">
-        <v>5781</v>
+        <v>5726</v>
       </c>
       <c r="F251" s="13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G251" s="15" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         </is>
       </c>
       <c r="E252" s="13" t="n">
-        <v>5796</v>
+        <v>5740</v>
       </c>
       <c r="F252" s="13" t="n">
         <v>11</v>
@@ -9760,7 +9760,7 @@
         </is>
       </c>
       <c r="E253" s="13" t="n">
-        <v>5809</v>
+        <v>5753</v>
       </c>
       <c r="F253" s="13" t="n">
         <v>11</v>
@@ -9788,7 +9788,7 @@
         </is>
       </c>
       <c r="E254" s="13" t="n">
-        <v>5822</v>
+        <v>5766</v>
       </c>
       <c r="F254" s="13" t="n">
         <v>10</v>
@@ -9816,7 +9816,7 @@
         </is>
       </c>
       <c r="E255" s="13" t="n">
-        <v>5835</v>
+        <v>5779</v>
       </c>
       <c r="F255" s="13" t="n">
         <v>9</v>
@@ -9844,7 +9844,7 @@
         </is>
       </c>
       <c r="E256" s="13" t="n">
-        <v>5846</v>
+        <v>5790</v>
       </c>
       <c r="F256" s="13" t="n">
         <v>10</v>
@@ -9872,7 +9872,7 @@
         </is>
       </c>
       <c r="E257" s="13" t="n">
-        <v>5859</v>
+        <v>5803</v>
       </c>
       <c r="F257" s="13" t="n">
         <v>10</v>
@@ -9900,7 +9900,7 @@
         </is>
       </c>
       <c r="E258" s="13" t="n">
-        <v>5871</v>
+        <v>5815</v>
       </c>
       <c r="F258" s="13" t="n">
         <v>11</v>
@@ -9928,7 +9928,7 @@
         </is>
       </c>
       <c r="E259" s="13" t="n">
-        <v>5885</v>
+        <v>5829</v>
       </c>
       <c r="F259" s="13" t="n">
         <v>12</v>
@@ -9956,14 +9956,14 @@
         </is>
       </c>
       <c r="E260" s="13" t="n">
-        <v>5900</v>
+        <v>5844</v>
       </c>
       <c r="F260" s="13" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G260" s="15" t="inlineStr">
         <is>
-          <t>알바로가 하비에르에게 이번 사건의 전모를 설명하며, 이번에도 보도 불가한 사안임을 확인합니 다.</t>
+          <t>알바로가 하비에르에게 이번 사건의 1차 결과를 짧게 알립니다. 수사가 계속되는 동안 보도는 보류됩니다.</t>
         </is>
       </c>
     </row>
@@ -9984,14 +9984,14 @@
         </is>
       </c>
       <c r="E261" s="13" t="n">
-        <v>5914</v>
+        <v>5851</v>
       </c>
       <c r="F261" s="13" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G261" s="15" t="inlineStr">
         <is>
-          <t>며칠 후, 알바로·카를로스·마르코스가 함께 저녁을 먹으며 사건을 정리합니다.</t>
+          <t>며칠 후, 알바로·카를로스·마르코스가 짧게 저녁을 함께합니다. 아직 끝난 사건이 아니어서 축하는 뒤로 미룹니다.</t>
         </is>
       </c>
     </row>
@@ -10012,7 +10012,7 @@
         </is>
       </c>
       <c r="E262" s="13" t="n">
-        <v>5930</v>
+        <v>5858</v>
       </c>
       <c r="F262" s="13" t="n">
         <v>29</v>
@@ -10040,14 +10040,14 @@
         </is>
       </c>
       <c r="E263" s="13" t="n">
-        <v>5963</v>
+        <v>5891</v>
       </c>
       <c r="F263" s="13" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G263" s="15" t="inlineStr">
         <is>
-          <t>헤라르도의 이메일을 근거로, 카를로스가 포르투갈·이탈리아 정보기관과의 공조 회의를 주선합 니다. 알바로도 배석합니다.</t>
+          <t>헤라르도의 이메일을 근거로, 카를로스가 포르투갈·이탈리아 정보기관과의 공조 회의를 주선합 니다. 알바로는 회의에 들어가지 않고, 나중에 카를로스에게 결과를 전해 듣습니다.</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10068,7 @@
         </is>
       </c>
       <c r="E264" s="13" t="n">
-        <v>5985</v>
+        <v>5916</v>
       </c>
       <c r="F264" s="13" t="n">
         <v>15</v>
@@ -10096,10 +10096,10 @@
         </is>
       </c>
       <c r="E265" s="13" t="n">
-        <v>6002</v>
+        <v>5933</v>
       </c>
       <c r="F265" s="13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G265" s="15" t="inlineStr">
         <is>
@@ -10124,10 +10124,10 @@
         </is>
       </c>
       <c r="E266" s="13" t="n">
-        <v>6017</v>
+        <v>5949</v>
       </c>
       <c r="F266" s="13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G266" s="15" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         </is>
       </c>
       <c r="E267" s="13" t="n">
-        <v>6038</v>
+        <v>5969</v>
       </c>
       <c r="F267" s="13" t="n">
         <v>16</v>
@@ -10180,10 +10180,10 @@
         </is>
       </c>
       <c r="E268" s="13" t="n">
-        <v>6057</v>
+        <v>5988</v>
       </c>
       <c r="F268" s="13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G268" s="15" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         </is>
       </c>
       <c r="E269" s="13" t="n">
-        <v>6081</v>
+        <v>6011</v>
       </c>
       <c r="F269" s="13" t="n">
         <v>17</v>
@@ -10236,14 +10236,14 @@
         </is>
       </c>
       <c r="E270" s="13" t="n">
-        <v>6101</v>
+        <v>6031</v>
       </c>
       <c r="F270" s="13" t="n">
         <v>13</v>
       </c>
       <c r="G270" s="15" t="inlineStr">
         <is>
-          <t>새로운 취재. 하비에르가 노동인권 NGO '푼다시온 암파로'로부터 제보를 받습니다. 남부 스페인 의 한 채소 농장 지대에서 이주노동자들이 빚에 묶여 사실상 강제노동을 당하고 있다는 내용입 니다. 등장인물은 전원 남성으로 구성했습니다.</t>
+          <t>새로운 취재. 하비에르가 노동인권 NGO '푼다시온 암파로'로부터 제보를 받습니다. 남부 스페인의 한 채소 농장 지대에서 이주노동자들이 빚에 묶여 사실상 강제노동을 당하고 있다는 내용입니다.</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10264,7 @@
         </is>
       </c>
       <c r="E271" s="13" t="n">
-        <v>6117</v>
+        <v>6047</v>
       </c>
       <c r="F271" s="13" t="n">
         <v>11</v>
@@ -10292,14 +10292,14 @@
         </is>
       </c>
       <c r="E272" s="13" t="n">
-        <v>6131</v>
+        <v>6061</v>
       </c>
       <c r="F272" s="13" t="n">
         <v>16</v>
       </c>
       <c r="G272" s="15" t="inlineStr">
         <is>
-          <t>알바로가 위장 신분 '마놀로 이바라'로 마노스 세구라스 모집 사무소를 찾아갑니다. 채용 담당 오스왈도가 그를 맞이합니다.</t>
+          <t>알바로가 위장 신분 '마놀로 레케나'로 마노스 세구라스 모집 사무소를 찾아갑니다. 채용 담당 오스왈도가 그를 맞이합니다.</t>
         </is>
       </c>
     </row>
@@ -10320,14 +10320,14 @@
         </is>
       </c>
       <c r="E273" s="13" t="n">
-        <v>6149</v>
+        <v>6079</v>
       </c>
       <c r="F273" s="13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G273" s="15" t="inlineStr">
         <is>
-          <t>다음 날 새벽, 알바로가 다른 노동자들과 함께 농장에 도착합니다. 열악한 실태를 처음 목격합</t>
+          <t>다음 날 새벽, 알바로가 다른 노동자들과 함께 농장에 도착합니다. 열악한 실태를 처음 목격합니다.</t>
         </is>
       </c>
     </row>
@@ -10348,7 +10348,7 @@
         </is>
       </c>
       <c r="E274" s="13" t="n">
-        <v>6164</v>
+        <v>6093</v>
       </c>
       <c r="F274" s="13" t="n">
         <v>16</v>
@@ -10376,7 +10376,7 @@
         </is>
       </c>
       <c r="E275" s="13" t="n">
-        <v>6183</v>
+        <v>6112</v>
       </c>
       <c r="F275" s="13" t="n">
         <v>10</v>
@@ -10404,7 +10404,7 @@
         </is>
       </c>
       <c r="E276" s="13" t="n">
-        <v>6196</v>
+        <v>6125</v>
       </c>
       <c r="F276" s="13" t="n">
         <v>13</v>
@@ -10432,7 +10432,7 @@
         </is>
       </c>
       <c r="E277" s="13" t="n">
-        <v>6211</v>
+        <v>6140</v>
       </c>
       <c r="F277" s="13" t="n">
         <v>10</v>
@@ -10460,10 +10460,10 @@
         </is>
       </c>
       <c r="E278" s="13" t="n">
-        <v>6224</v>
+        <v>6153</v>
       </c>
       <c r="F278" s="13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G278" s="15" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         </is>
       </c>
       <c r="E279" s="13" t="n">
-        <v>6242</v>
+        <v>6170</v>
       </c>
       <c r="F279" s="13" t="n">
         <v>14</v>
@@ -10516,10 +10516,10 @@
         </is>
       </c>
       <c r="E280" s="13" t="n">
-        <v>6258</v>
+        <v>6186</v>
       </c>
       <c r="F280" s="13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G280" s="15" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         </is>
       </c>
       <c r="E281" s="13" t="n">
-        <v>6271</v>
+        <v>6198</v>
       </c>
       <c r="F281" s="13" t="n">
         <v>11</v>
@@ -10572,10 +10572,10 @@
         </is>
       </c>
       <c r="E282" s="13" t="n">
-        <v>6284</v>
+        <v>6211</v>
       </c>
       <c r="F282" s="13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G282" s="15" t="inlineStr">
         <is>
@@ -10600,10 +10600,10 @@
         </is>
       </c>
       <c r="E283" s="13" t="n">
-        <v>6294</v>
+        <v>6223</v>
       </c>
       <c r="F283" s="13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G283" s="15" t="inlineStr">
         <is>
@@ -10628,14 +10628,14 @@
         </is>
       </c>
       <c r="E284" s="13" t="n">
-        <v>6303</v>
+        <v>6234</v>
       </c>
       <c r="F284" s="13" t="n">
         <v>11</v>
       </c>
       <c r="G284" s="15" t="inlineStr">
         <is>
-          <t>알바로가 부상당한 트라바하도르1을 인근 병원으로 데려가며, 하비에르에게 긴급 연락합니다.</t>
+          <t>알바로가 부상당한 트라바하도르1을 인근 병원으로 데려가며, 차를 빌려준 이웃의 휴대전화로 하비에르에게 긴급 연락합니다.</t>
         </is>
       </c>
     </row>
@@ -10656,10 +10656,10 @@
         </is>
       </c>
       <c r="E285" s="13" t="n">
-        <v>6317</v>
+        <v>6248</v>
       </c>
       <c r="F285" s="13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G285" s="15" t="inlineStr">
         <is>
@@ -10684,14 +10684,14 @@
         </is>
       </c>
       <c r="E286" s="13" t="n">
-        <v>6329</v>
+        <v>6262</v>
       </c>
       <c r="F286" s="13" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G286" s="15" t="inlineStr">
         <is>
-          <t>루벤이 노동감독관 인마쿨라다... 아니, 정정: 남성 감독관 페르난도 로요 감독관과 긴급 회의를 주선합니다.</t>
+          <t>루벤이 노동감독관 페르난도 로요와의 긴급 회의를 병원에서 주선합니다.</t>
         </is>
       </c>
     </row>
@@ -10712,7 +10712,7 @@
         </is>
       </c>
       <c r="E287" s="13" t="n">
-        <v>6344</v>
+        <v>6281</v>
       </c>
       <c r="F287" s="13" t="n">
         <v>9</v>
@@ -10740,7 +10740,7 @@
         </is>
       </c>
       <c r="E288" s="13" t="n">
-        <v>6355</v>
+        <v>6292</v>
       </c>
       <c r="F288" s="13" t="n">
         <v>9</v>
@@ -10768,7 +10768,7 @@
         </is>
       </c>
       <c r="E289" s="13" t="n">
-        <v>6367</v>
+        <v>6304</v>
       </c>
       <c r="F289" s="13" t="n">
         <v>11</v>
@@ -10796,7 +10796,7 @@
         </is>
       </c>
       <c r="E290" s="13" t="n">
-        <v>6380</v>
+        <v>6317</v>
       </c>
       <c r="F290" s="13" t="n">
         <v>12</v>
@@ -10824,10 +10824,10 @@
         </is>
       </c>
       <c r="E291" s="13" t="n">
-        <v>6395</v>
+        <v>6332</v>
       </c>
       <c r="F291" s="13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G291" s="15" t="inlineStr">
         <is>
@@ -10852,10 +10852,10 @@
         </is>
       </c>
       <c r="E292" s="13" t="n">
-        <v>6410</v>
+        <v>6348</v>
       </c>
       <c r="F292" s="13" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G292" s="15" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         </is>
       </c>
       <c r="E293" s="13" t="n">
-        <v>6429</v>
+        <v>6371</v>
       </c>
       <c r="F293" s="13" t="n">
         <v>10</v>
@@ -10908,10 +10908,10 @@
         </is>
       </c>
       <c r="E294" s="13" t="n">
-        <v>6441</v>
+        <v>6383</v>
       </c>
       <c r="F294" s="13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G294" s="15" t="inlineStr">
         <is>
@@ -10936,10 +10936,10 @@
         </is>
       </c>
       <c r="E295" s="13" t="n">
-        <v>6461</v>
+        <v>6404</v>
       </c>
       <c r="F295" s="13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G295" s="15" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         </is>
       </c>
       <c r="E296" s="13" t="n">
-        <v>6475</v>
+        <v>6417</v>
       </c>
       <c r="F296" s="13" t="n">
         <v>10</v>
@@ -10992,10 +10992,10 @@
         </is>
       </c>
       <c r="E297" s="13" t="n">
-        <v>6487</v>
+        <v>6429</v>
       </c>
       <c r="F297" s="13" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="G297" s="15" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         </is>
       </c>
       <c r="E298" s="13" t="n">
-        <v>6514</v>
+        <v>6466</v>
       </c>
       <c r="F298" s="13" t="n">
         <v>12</v>
@@ -11048,10 +11048,10 @@
         </is>
       </c>
       <c r="E299" s="13" t="n">
-        <v>6528</v>
+        <v>6480</v>
       </c>
       <c r="F299" s="13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G299" s="15" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         </is>
       </c>
       <c r="E300" s="13" t="n">
-        <v>6545</v>
+        <v>6496</v>
       </c>
       <c r="F300" s="13" t="n">
         <v>14</v>
@@ -11104,7 +11104,7 @@
         </is>
       </c>
       <c r="E301" s="13" t="n">
-        <v>6562</v>
+        <v>6513</v>
       </c>
       <c r="F301" s="13" t="n">
         <v>11</v>
@@ -11132,7 +11132,7 @@
         </is>
       </c>
       <c r="E302" s="13" t="n">
-        <v>6575</v>
+        <v>6526</v>
       </c>
       <c r="F302" s="13" t="n">
         <v>12</v>
@@ -11160,7 +11160,7 @@
         </is>
       </c>
       <c r="E303" s="13" t="n">
-        <v>6590</v>
+        <v>6541</v>
       </c>
       <c r="F303" s="13" t="n">
         <v>13</v>
@@ -11188,10 +11188,10 @@
         </is>
       </c>
       <c r="E304" s="13" t="n">
-        <v>6605</v>
+        <v>6556</v>
       </c>
       <c r="F304" s="13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G304" s="15" t="inlineStr">
         <is>
@@ -11216,10 +11216,10 @@
         </is>
       </c>
       <c r="E305" s="13" t="n">
-        <v>6618</v>
+        <v>6571</v>
       </c>
       <c r="F305" s="13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G305" s="15" t="inlineStr">
         <is>
@@ -11244,10 +11244,10 @@
         </is>
       </c>
       <c r="E306" s="13" t="n">
-        <v>6633</v>
+        <v>6588</v>
       </c>
       <c r="F306" s="13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G306" s="15" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         </is>
       </c>
       <c r="E307" s="13" t="n">
-        <v>6644</v>
+        <v>6601</v>
       </c>
       <c r="F307" s="13" t="n">
         <v>15</v>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="E308" s="13" t="n">
-        <v>6662</v>
+        <v>6619</v>
       </c>
       <c r="F308" s="13" t="n">
         <v>13</v>
@@ -11328,10 +11328,10 @@
         </is>
       </c>
       <c r="E309" s="13" t="n">
-        <v>6678</v>
+        <v>6635</v>
       </c>
       <c r="F309" s="13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G309" s="15" t="inlineStr">
         <is>
@@ -11356,10 +11356,10 @@
         </is>
       </c>
       <c r="E310" s="13" t="n">
-        <v>6689</v>
+        <v>6648</v>
       </c>
       <c r="F310" s="13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G310" s="15" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         </is>
       </c>
       <c r="E311" s="13" t="n">
-        <v>6703</v>
+        <v>6663</v>
       </c>
       <c r="F311" s="13" t="n">
         <v>10</v>
@@ -11412,10 +11412,10 @@
         </is>
       </c>
       <c r="E312" s="13" t="n">
-        <v>6716</v>
+        <v>6676</v>
       </c>
       <c r="F312" s="13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G312" s="15" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         </is>
       </c>
       <c r="E313" s="13" t="n">
-        <v>6726</v>
+        <v>6688</v>
       </c>
       <c r="F313" s="13" t="n">
         <v>15</v>
@@ -11468,7 +11468,7 @@
         </is>
       </c>
       <c r="E314" s="13" t="n">
-        <v>6744</v>
+        <v>6706</v>
       </c>
       <c r="F314" s="13" t="n">
         <v>12</v>
@@ -11496,7 +11496,7 @@
         </is>
       </c>
       <c r="E315" s="13" t="n">
-        <v>6759</v>
+        <v>6721</v>
       </c>
       <c r="F315" s="13" t="n">
         <v>12</v>
@@ -11524,14 +11524,14 @@
         </is>
       </c>
       <c r="E316" s="13" t="n">
-        <v>6773</v>
+        <v>6735</v>
       </c>
       <c r="F316" s="13" t="n">
         <v>13</v>
       </c>
       <c r="G316" s="15" t="inlineStr">
         <is>
-          <t>일주일 후, 리고베르토가 비고로 떠난 밤. 카밀라가 금고를 열고 문서를 복사하는 동안 알바로 가 주변을 경계합니다.</t>
+          <t>일주일 후, 리고베르토가 비고로 떠난 밤. 카밀라가 금고를 열고 문서를 복사하는 동안 알바로가 주변을 경계합니다.</t>
         </is>
       </c>
     </row>
@@ -11552,7 +11552,7 @@
         </is>
       </c>
       <c r="E317" s="13" t="n">
-        <v>6790</v>
+        <v>6751</v>
       </c>
       <c r="F317" s="13" t="n">
         <v>12</v>
@@ -11580,10 +11580,10 @@
         </is>
       </c>
       <c r="E318" s="13" t="n">
-        <v>6805</v>
+        <v>6766</v>
       </c>
       <c r="F318" s="13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G318" s="15" t="inlineStr">
         <is>
@@ -11608,10 +11608,10 @@
         </is>
       </c>
       <c r="E319" s="13" t="n">
-        <v>6818</v>
+        <v>6781</v>
       </c>
       <c r="F319" s="13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G319" s="15" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         </is>
       </c>
       <c r="E320" s="13" t="n">
-        <v>6833</v>
+        <v>6795</v>
       </c>
       <c r="F320" s="13" t="n">
         <v>9</v>
@@ -11664,7 +11664,7 @@
         </is>
       </c>
       <c r="E321" s="13" t="n">
-        <v>6844</v>
+        <v>6806</v>
       </c>
       <c r="F321" s="13" t="n">
         <v>11</v>
@@ -11692,10 +11692,10 @@
         </is>
       </c>
       <c r="E322" s="13" t="n">
-        <v>6858</v>
+        <v>6820</v>
       </c>
       <c r="F322" s="13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G322" s="15" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         </is>
       </c>
       <c r="E323" s="13" t="n">
-        <v>6868</v>
+        <v>6832</v>
       </c>
       <c r="F323" s="13" t="n">
         <v>12</v>
@@ -11748,7 +11748,7 @@
         </is>
       </c>
       <c r="E324" s="13" t="n">
-        <v>6882</v>
+        <v>6846</v>
       </c>
       <c r="F324" s="13" t="n">
         <v>16</v>
@@ -11776,10 +11776,10 @@
         </is>
       </c>
       <c r="E325" s="13" t="n">
-        <v>6901</v>
+        <v>6865</v>
       </c>
       <c r="F325" s="13" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G325" s="15" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         </is>
       </c>
       <c r="E326" s="13" t="n">
-        <v>6914</v>
+        <v>6884</v>
       </c>
       <c r="F326" s="13" t="n">
         <v>12</v>
@@ -11832,7 +11832,7 @@
         </is>
       </c>
       <c r="E327" s="13" t="n">
-        <v>6928</v>
+        <v>6898</v>
       </c>
       <c r="F327" s="13" t="n">
         <v>10</v>
@@ -11860,7 +11860,7 @@
         </is>
       </c>
       <c r="E328" s="13" t="n">
-        <v>6941</v>
+        <v>6911</v>
       </c>
       <c r="F328" s="13" t="n">
         <v>15</v>
@@ -11888,7 +11888,7 @@
         </is>
       </c>
       <c r="E329" s="13" t="n">
-        <v>6959</v>
+        <v>6929</v>
       </c>
       <c r="F329" s="13" t="n">
         <v>23</v>
@@ -11916,7 +11916,7 @@
         </is>
       </c>
       <c r="E330" s="13" t="n">
-        <v>6985</v>
+        <v>6955</v>
       </c>
       <c r="F330" s="13" t="n">
         <v>20</v>
@@ -11944,7 +11944,7 @@
         </is>
       </c>
       <c r="E331" s="13" t="n">
-        <v>7008</v>
+        <v>6978</v>
       </c>
       <c r="F331" s="13" t="n">
         <v>15</v>
@@ -11972,10 +11972,10 @@
         </is>
       </c>
       <c r="E332" s="13" t="n">
-        <v>7026</v>
+        <v>6996</v>
       </c>
       <c r="F332" s="13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G332" s="15" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         </is>
       </c>
       <c r="E333" s="13" t="n">
-        <v>7041</v>
+        <v>7010</v>
       </c>
       <c r="F333" s="13" t="n">
         <v>17</v>
@@ -12028,10 +12028,10 @@
         </is>
       </c>
       <c r="E334" s="13" t="n">
-        <v>7061</v>
+        <v>7030</v>
       </c>
       <c r="F334" s="13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G334" s="15" t="inlineStr">
         <is>
@@ -12056,7 +12056,7 @@
         </is>
       </c>
       <c r="E335" s="13" t="n">
-        <v>7083</v>
+        <v>7051</v>
       </c>
       <c r="F335" s="13" t="n">
         <v>16</v>
@@ -12084,7 +12084,7 @@
         </is>
       </c>
       <c r="E336" s="13" t="n">
-        <v>7101</v>
+        <v>7069</v>
       </c>
       <c r="F336" s="13" t="n">
         <v>16</v>
@@ -12112,7 +12112,7 @@
         </is>
       </c>
       <c r="E337" s="13" t="n">
-        <v>7120</v>
+        <v>7088</v>
       </c>
       <c r="F337" s="13" t="n">
         <v>16</v>
@@ -12140,10 +12140,10 @@
         </is>
       </c>
       <c r="E338" s="13" t="n">
-        <v>7139</v>
+        <v>7107</v>
       </c>
       <c r="F338" s="13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G338" s="15" t="inlineStr">
         <is>
@@ -12168,10 +12168,10 @@
         </is>
       </c>
       <c r="E339" s="13" t="n">
-        <v>7157</v>
+        <v>7123</v>
       </c>
       <c r="F339" s="13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G339" s="15" t="inlineStr">
         <is>
@@ -12196,10 +12196,10 @@
         </is>
       </c>
       <c r="E340" s="13" t="n">
-        <v>7174</v>
+        <v>7139</v>
       </c>
       <c r="F340" s="13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G340" s="15" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         </is>
       </c>
       <c r="E341" s="13" t="n">
-        <v>7195</v>
+        <v>7159</v>
       </c>
       <c r="F341" s="13" t="n">
         <v>14</v>
@@ -12252,7 +12252,7 @@
         </is>
       </c>
       <c r="E342" s="13" t="n">
-        <v>7212</v>
+        <v>7176</v>
       </c>
       <c r="F342" s="13" t="n">
         <v>13</v>
@@ -12280,10 +12280,10 @@
         </is>
       </c>
       <c r="E343" s="13" t="n">
-        <v>7227</v>
+        <v>7191</v>
       </c>
       <c r="F343" s="13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G343" s="15" t="inlineStr">
         <is>
@@ -12308,14 +12308,14 @@
         </is>
       </c>
       <c r="E344" s="13" t="n">
-        <v>7241</v>
+        <v>7204</v>
       </c>
       <c r="F344" s="13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G344" s="15" t="inlineStr">
         <is>
-          <t>바로 그 순간, 알바로와 요원들이 개입합니다.</t>
+          <t>바로 그 순간, 알바로와 요원들이 지켜보는 가운데 벨기에 경찰이 사무실로 진입합니다. 그러나 로셀요는 뒷문으로 빠져나가 사라지고, 밖의 차량에서 대기하던 알바로는 끝내 그와 마주치지 못합니다.</t>
         </is>
       </c>
     </row>
@@ -12336,7 +12336,7 @@
         </is>
       </c>
       <c r="E345" s="13" t="n">
-        <v>7256</v>
+        <v>7218</v>
       </c>
       <c r="F345" s="13" t="n">
         <v>11</v>
@@ -12364,10 +12364,10 @@
         </is>
       </c>
       <c r="E346" s="13" t="n">
-        <v>7269</v>
+        <v>7231</v>
       </c>
       <c r="F346" s="13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G346" s="15" t="inlineStr">
         <is>
@@ -12392,10 +12392,10 @@
         </is>
       </c>
       <c r="E347" s="13" t="n">
-        <v>7286</v>
+        <v>7247</v>
       </c>
       <c r="F347" s="13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G347" s="15" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         </is>
       </c>
       <c r="E348" s="13" t="n">
-        <v>7303</v>
+        <v>7263</v>
       </c>
       <c r="F348" s="13" t="n">
         <v>12</v>
@@ -12448,7 +12448,7 @@
         </is>
       </c>
       <c r="E349" s="13" t="n">
-        <v>7318</v>
+        <v>7278</v>
       </c>
       <c r="F349" s="13" t="n">
         <v>11</v>
@@ -12476,14 +12476,14 @@
         </is>
       </c>
       <c r="E350" s="13" t="n">
-        <v>7331</v>
+        <v>7291</v>
       </c>
       <c r="F350" s="13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G350" s="15" t="inlineStr">
         <is>
-          <t>재판 중, 로셀요가 직접 증언대에 서서 알바로와 간접적으로 맞섭니다.</t>
+          <t>재판 중, 로셀요가 직접 증언대에 설 수 없는 상황(도주 중)에서, 대신 카살스가 증언대에 서서 모든 책임을 로셀요에게 떠넘기려 합니다.</t>
         </is>
       </c>
     </row>
@@ -12504,10 +12504,10 @@
         </is>
       </c>
       <c r="E351" s="13" t="n">
-        <v>7348</v>
+        <v>7307</v>
       </c>
       <c r="F351" s="13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G351" s="15" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         </is>
       </c>
       <c r="E352" s="13" t="n">
-        <v>7362</v>
+        <v>7320</v>
       </c>
       <c r="F352" s="13" t="n">
         <v>11</v>
@@ -12560,10 +12560,10 @@
         </is>
       </c>
       <c r="E353" s="13" t="n">
-        <v>7375</v>
+        <v>7333</v>
       </c>
       <c r="F353" s="13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G353" s="15" t="inlineStr">
         <is>
@@ -12588,10 +12588,10 @@
         </is>
       </c>
       <c r="E354" s="13" t="n">
-        <v>7391</v>
+        <v>7348</v>
       </c>
       <c r="F354" s="13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G354" s="15" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         </is>
       </c>
       <c r="E355" s="13" t="n">
-        <v>7414</v>
+        <v>7370</v>
       </c>
       <c r="F355" s="13" t="n">
         <v>11</v>
@@ -12644,7 +12644,7 @@
         </is>
       </c>
       <c r="E356" s="13" t="n">
-        <v>7428</v>
+        <v>7384</v>
       </c>
       <c r="F356" s="13" t="n">
         <v>13</v>
@@ -12672,7 +12672,7 @@
         </is>
       </c>
       <c r="E357" s="13" t="n">
-        <v>7444</v>
+        <v>7400</v>
       </c>
       <c r="F357" s="13" t="n">
         <v>13</v>
@@ -12700,7 +12700,7 @@
         </is>
       </c>
       <c r="E358" s="13" t="n">
-        <v>7459</v>
+        <v>7415</v>
       </c>
       <c r="F358" s="13" t="n">
         <v>14</v>
@@ -12728,7 +12728,7 @@
         </is>
       </c>
       <c r="E359" s="13" t="n">
-        <v>7476</v>
+        <v>7432</v>
       </c>
       <c r="F359" s="13" t="n">
         <v>15</v>
@@ -12756,14 +12756,14 @@
         </is>
       </c>
       <c r="E360" s="13" t="n">
-        <v>7494</v>
+        <v>7450</v>
       </c>
       <c r="F360" s="13" t="n">
         <v>15</v>
       </c>
       <c r="G360" s="15" t="inlineStr">
         <is>
-          <t>몇 주 후, 카밀라의 오빠 마테오(위장 신분과 같은 이름의 우연)가 마드리드에 정착한 뒤 처음 으로 함께 저녁 식사를 합니다.</t>
+          <t>몇 주 후, 카밀라의 오빠 안드레스가 마드리드에 정착한 뒤 처음으로 함께 저녁 식사를 합니다.</t>
         </is>
       </c>
     </row>
@@ -12784,7 +12784,7 @@
         </is>
       </c>
       <c r="E361" s="13" t="n">
-        <v>7512</v>
+        <v>7468</v>
       </c>
       <c r="F361" s="13" t="n">
         <v>14</v>
@@ -12812,7 +12812,7 @@
         </is>
       </c>
       <c r="E362" s="13" t="n">
-        <v>7529</v>
+        <v>7485</v>
       </c>
       <c r="F362" s="13" t="n">
         <v>14</v>
@@ -12840,10 +12840,10 @@
         </is>
       </c>
       <c r="E363" s="13" t="n">
-        <v>7545</v>
+        <v>7501</v>
       </c>
       <c r="F363" s="13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G363" s="15" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         </is>
       </c>
       <c r="E364" s="13" t="n">
-        <v>7565</v>
+        <v>7520</v>
       </c>
       <c r="F364" s="13" t="n">
         <v>15</v>
@@ -12896,14 +12896,14 @@
         </is>
       </c>
       <c r="E365" s="13" t="n">
-        <v>7583</v>
+        <v>7538</v>
       </c>
       <c r="F365" s="13" t="n">
         <v>16</v>
       </c>
       <c r="G365" s="15" t="inlineStr">
         <is>
-          <t>몇 달 후, 새로운 실마리. '엘 아르키텍토'(아드리안 로셀요) 네트워크가 브뤼셀의 로비 회사를 통해 EU 금융규제 완화를 위해 움직이고 있다는 정황이 포착됩니다.</t>
+          <t>몇 달 후, 새로운 실마리. '엘 아르키텍토'(아드리안 로셀요)가 메리디안 급습 때 도주한 뒤, 이번에는 다른 브뤼셀 로비 회사를 통해 EU 금융규제 완화를 위해 움직이고 있다는 정황이 포착됩니다.</t>
         </is>
       </c>
     </row>
@@ -12924,10 +12924,10 @@
         </is>
       </c>
       <c r="E366" s="13" t="n">
-        <v>7602</v>
+        <v>7557</v>
       </c>
       <c r="F366" s="13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G366" s="15" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="E367" s="13" t="n">
-        <v>7624</v>
+        <v>7578</v>
       </c>
       <c r="F367" s="13" t="n">
         <v>19</v>
@@ -12980,7 +12980,7 @@
         </is>
       </c>
       <c r="E368" s="13" t="n">
-        <v>7646</v>
+        <v>7600</v>
       </c>
       <c r="F368" s="13" t="n">
         <v>14</v>
@@ -13008,7 +13008,7 @@
         </is>
       </c>
       <c r="E369" s="13" t="n">
-        <v>7663</v>
+        <v>7617</v>
       </c>
       <c r="F369" s="13" t="n">
         <v>13</v>
@@ -13036,7 +13036,7 @@
         </is>
       </c>
       <c r="E370" s="13" t="n">
-        <v>7679</v>
+        <v>7633</v>
       </c>
       <c r="F370" s="13" t="n">
         <v>12</v>
@@ -13064,7 +13064,7 @@
         </is>
       </c>
       <c r="E371" s="13" t="n">
-        <v>7693</v>
+        <v>7647</v>
       </c>
       <c r="F371" s="13" t="n">
         <v>10</v>
@@ -13092,7 +13092,7 @@
         </is>
       </c>
       <c r="E372" s="13" t="n">
-        <v>7706</v>
+        <v>7660</v>
       </c>
       <c r="F372" s="13" t="n">
         <v>11</v>
@@ -13120,7 +13120,7 @@
         </is>
       </c>
       <c r="E373" s="13" t="n">
-        <v>7720</v>
+        <v>7674</v>
       </c>
       <c r="F373" s="13" t="n">
         <v>11</v>
@@ -13148,7 +13148,7 @@
         </is>
       </c>
       <c r="E374" s="13" t="n">
-        <v>7733</v>
+        <v>7687</v>
       </c>
       <c r="F374" s="13" t="n">
         <v>13</v>
@@ -13176,7 +13176,7 @@
         </is>
       </c>
       <c r="E375" s="13" t="n">
-        <v>7749</v>
+        <v>7703</v>
       </c>
       <c r="F375" s="13" t="n">
         <v>18</v>
@@ -13204,10 +13204,10 @@
         </is>
       </c>
       <c r="E376" s="13" t="n">
-        <v>7770</v>
+        <v>7724</v>
       </c>
       <c r="F376" s="13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G376" s="15" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         </is>
       </c>
       <c r="E377" s="13" t="n">
-        <v>7784</v>
+        <v>7737</v>
       </c>
       <c r="F377" s="13" t="n">
         <v>12</v>
@@ -13260,7 +13260,7 @@
         </is>
       </c>
       <c r="E378" s="13" t="n">
-        <v>7798</v>
+        <v>7751</v>
       </c>
       <c r="F378" s="13" t="n">
         <v>9</v>
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="E379" s="13" t="n">
-        <v>7810</v>
+        <v>7763</v>
       </c>
       <c r="F379" s="13" t="n">
         <v>10</v>
@@ -13316,7 +13316,7 @@
         </is>
       </c>
       <c r="E380" s="13" t="n">
-        <v>7822</v>
+        <v>7775</v>
       </c>
       <c r="F380" s="13" t="n">
         <v>10</v>
@@ -13344,7 +13344,7 @@
         </is>
       </c>
       <c r="E381" s="13" t="n">
-        <v>7834</v>
+        <v>7787</v>
       </c>
       <c r="F381" s="13" t="n">
         <v>11</v>
@@ -13372,7 +13372,7 @@
         </is>
       </c>
       <c r="E382" s="13" t="n">
-        <v>7848</v>
+        <v>7801</v>
       </c>
       <c r="F382" s="13" t="n">
         <v>14</v>
@@ -13400,7 +13400,7 @@
         </is>
       </c>
       <c r="E383" s="13" t="n">
-        <v>7864</v>
+        <v>7817</v>
       </c>
       <c r="F383" s="13" t="n">
         <v>11</v>
@@ -13428,10 +13428,10 @@
         </is>
       </c>
       <c r="E384" s="13" t="n">
-        <v>7878</v>
+        <v>7831</v>
       </c>
       <c r="F384" s="13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G384" s="15" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         </is>
       </c>
       <c r="E385" s="13" t="n">
-        <v>7894</v>
+        <v>7846</v>
       </c>
       <c r="F385" s="13" t="n">
         <v>11</v>
@@ -13484,7 +13484,7 @@
         </is>
       </c>
       <c r="E386" s="13" t="n">
-        <v>7907</v>
+        <v>7859</v>
       </c>
       <c r="F386" s="13" t="n">
         <v>11</v>
@@ -13512,10 +13512,10 @@
         </is>
       </c>
       <c r="E387" s="13" t="n">
-        <v>7920</v>
+        <v>7872</v>
       </c>
       <c r="F387" s="13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G387" s="15" t="inlineStr">
         <is>
@@ -13540,14 +13540,14 @@
         </is>
       </c>
       <c r="E388" s="13" t="n">
-        <v>7934</v>
+        <v>7885</v>
       </c>
       <c r="F388" s="13" t="n">
         <v>11</v>
       </c>
       <c r="G388" s="15" t="inlineStr">
         <is>
-          <t>다음 날, 알바로가 감시하던 중 로셀요(혹은 그의 협력자)에게 정체를 의심받을 뻔한 순간이 벌 어집니다.</t>
+          <t>다음 날, 알바로가 감시하던 중 로셀요의 경호원으로 보이는 남자에게 정체를 의심받을 뻔한 순간이 벌어집니다.</t>
         </is>
       </c>
     </row>
@@ -13568,7 +13568,7 @@
         </is>
       </c>
       <c r="E389" s="13" t="n">
-        <v>7947</v>
+        <v>7898</v>
       </c>
       <c r="F389" s="13" t="n">
         <v>11</v>
@@ -13596,10 +13596,10 @@
         </is>
       </c>
       <c r="E390" s="13" t="n">
-        <v>7961</v>
+        <v>7912</v>
       </c>
       <c r="F390" s="13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G390" s="15" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         </is>
       </c>
       <c r="E391" s="13" t="n">
-        <v>7976</v>
+        <v>7926</v>
       </c>
       <c r="F391" s="13" t="n">
         <v>11</v>
@@ -13652,14 +13652,14 @@
         </is>
       </c>
       <c r="E392" s="13" t="n">
-        <v>7989</v>
+        <v>7939</v>
       </c>
       <c r="F392" s="13" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G392" s="15" t="inlineStr">
         <is>
-          <t>자스퍼 베르호벤이 변호사와 상담 후 전면 협조를 결정하며, 로셀요에 대한 새로운 정보를 제공 합니다.</t>
+          <t>자스퍼 베르호벤이 변호사와 상담 후 전면 협조를 결정하며, 로셀요에 대한 새로운 정보를 제공합니다. 신문은 벨기에 수사관이 맡고, 카를로스와 알바로는 검찰의 허가를 받아 유리창 너머에서 지켜봅니다.</t>
         </is>
       </c>
     </row>
@@ -13680,7 +13680,7 @@
         </is>
       </c>
       <c r="E393" s="13" t="n">
-        <v>8012</v>
+        <v>7965</v>
       </c>
       <c r="F393" s="13" t="n">
         <v>13</v>
@@ -13708,7 +13708,7 @@
         </is>
       </c>
       <c r="E394" s="13" t="n">
-        <v>8028</v>
+        <v>7981</v>
       </c>
       <c r="F394" s="13" t="n">
         <v>12</v>
@@ -13736,10 +13736,10 @@
         </is>
       </c>
       <c r="E395" s="13" t="n">
-        <v>8043</v>
+        <v>7996</v>
       </c>
       <c r="F395" s="13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G395" s="15" t="inlineStr">
         <is>
@@ -13764,10 +13764,10 @@
         </is>
       </c>
       <c r="E396" s="13" t="n">
-        <v>8062</v>
+        <v>8014</v>
       </c>
       <c r="F396" s="13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G396" s="15" t="inlineStr">
         <is>
@@ -13792,10 +13792,10 @@
         </is>
       </c>
       <c r="E397" s="13" t="n">
-        <v>8074</v>
+        <v>8028</v>
       </c>
       <c r="F397" s="13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G397" s="15" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         </is>
       </c>
       <c r="E398" s="13" t="n">
-        <v>8094</v>
+        <v>8047</v>
       </c>
       <c r="F398" s="13" t="n">
         <v>13</v>
@@ -13848,7 +13848,7 @@
         </is>
       </c>
       <c r="E399" s="13" t="n">
-        <v>8110</v>
+        <v>8063</v>
       </c>
       <c r="F399" s="13" t="n">
         <v>12</v>
@@ -13876,7 +13876,7 @@
         </is>
       </c>
       <c r="E400" s="13" t="n">
-        <v>8125</v>
+        <v>8078</v>
       </c>
       <c r="F400" s="13" t="n">
         <v>12</v>
@@ -13904,7 +13904,7 @@
         </is>
       </c>
       <c r="E401" s="13" t="n">
-        <v>8139</v>
+        <v>8092</v>
       </c>
       <c r="F401" s="13" t="n">
         <v>12</v>
@@ -13932,7 +13932,7 @@
         </is>
       </c>
       <c r="E402" s="13" t="n">
-        <v>8154</v>
+        <v>8107</v>
       </c>
       <c r="F402" s="13" t="n">
         <v>10</v>
@@ -13960,7 +13960,7 @@
         </is>
       </c>
       <c r="E403" s="13" t="n">
-        <v>8167</v>
+        <v>8120</v>
       </c>
       <c r="F403" s="13" t="n">
         <v>12</v>
@@ -13988,7 +13988,7 @@
         </is>
       </c>
       <c r="E404" s="13" t="n">
-        <v>8181</v>
+        <v>8134</v>
       </c>
       <c r="F404" s="13" t="n">
         <v>13</v>
@@ -14016,7 +14016,7 @@
         </is>
       </c>
       <c r="E405" s="13" t="n">
-        <v>8197</v>
+        <v>8150</v>
       </c>
       <c r="F405" s="13" t="n">
         <v>12</v>
@@ -14044,10 +14044,10 @@
         </is>
       </c>
       <c r="E406" s="13" t="n">
-        <v>8212</v>
+        <v>8165</v>
       </c>
       <c r="F406" s="13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G406" s="15" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         </is>
       </c>
       <c r="E407" s="13" t="n">
-        <v>8222</v>
+        <v>8177</v>
       </c>
       <c r="F407" s="13" t="n">
         <v>13</v>
@@ -14100,10 +14100,10 @@
         </is>
       </c>
       <c r="E408" s="13" t="n">
-        <v>8238</v>
+        <v>8193</v>
       </c>
       <c r="F408" s="13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G408" s="15" t="inlineStr">
         <is>
@@ -14128,10 +14128,10 @@
         </is>
       </c>
       <c r="E409" s="13" t="n">
-        <v>8254</v>
+        <v>8208</v>
       </c>
       <c r="F409" s="13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G409" s="15" t="inlineStr">
         <is>
@@ -14156,7 +14156,7 @@
         </is>
       </c>
       <c r="E410" s="13" t="n">
-        <v>8269</v>
+        <v>8225</v>
       </c>
       <c r="F410" s="13" t="n">
         <v>10</v>
@@ -14184,7 +14184,7 @@
         </is>
       </c>
       <c r="E411" s="13" t="n">
-        <v>8281</v>
+        <v>8237</v>
       </c>
       <c r="F411" s="13" t="n">
         <v>13</v>
@@ -14212,10 +14212,10 @@
         </is>
       </c>
       <c r="E412" s="13" t="n">
-        <v>8297</v>
+        <v>8253</v>
       </c>
       <c r="F412" s="13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G412" s="15" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         </is>
       </c>
       <c r="E413" s="13" t="n">
-        <v>8305</v>
+        <v>8263</v>
       </c>
       <c r="F413" s="13" t="n">
         <v>21</v>
@@ -14268,10 +14268,10 @@
         </is>
       </c>
       <c r="E414" s="13" t="n">
-        <v>8329</v>
+        <v>8287</v>
       </c>
       <c r="F414" s="13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G414" s="15" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         </is>
       </c>
       <c r="E415" s="13" t="n">
-        <v>8348</v>
+        <v>8307</v>
       </c>
       <c r="F415" s="13" t="n">
         <v>10</v>
@@ -14324,10 +14324,10 @@
         </is>
       </c>
       <c r="E416" s="13" t="n">
-        <v>8361</v>
+        <v>8320</v>
       </c>
       <c r="F416" s="13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G416" s="15" t="inlineStr">
         <is>
@@ -14352,7 +14352,7 @@
         </is>
       </c>
       <c r="E417" s="13" t="n">
-        <v>8380</v>
+        <v>8338</v>
       </c>
       <c r="F417" s="13" t="n">
         <v>9</v>
@@ -14380,10 +14380,10 @@
         </is>
       </c>
       <c r="E418" s="13" t="n">
-        <v>8391</v>
+        <v>8349</v>
       </c>
       <c r="F418" s="13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G418" s="15" t="inlineStr">
         <is>
@@ -14408,7 +14408,7 @@
         </is>
       </c>
       <c r="E419" s="13" t="n">
-        <v>8408</v>
+        <v>8368</v>
       </c>
       <c r="F419" s="13" t="n">
         <v>12</v>
@@ -14436,7 +14436,7 @@
         </is>
       </c>
       <c r="E420" s="13" t="n">
-        <v>8423</v>
+        <v>8383</v>
       </c>
       <c r="F420" s="13" t="n">
         <v>13</v>
@@ -14464,7 +14464,7 @@
         </is>
       </c>
       <c r="E421" s="13" t="n">
-        <v>8439</v>
+        <v>8399</v>
       </c>
       <c r="F421" s="13" t="n">
         <v>12</v>
@@ -14492,7 +14492,7 @@
         </is>
       </c>
       <c r="E422" s="13" t="n">
-        <v>8453</v>
+        <v>8413</v>
       </c>
       <c r="F422" s="13" t="n">
         <v>12</v>
@@ -14520,10 +14520,10 @@
         </is>
       </c>
       <c r="E423" s="13" t="n">
-        <v>8467</v>
+        <v>8427</v>
       </c>
       <c r="F423" s="13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G423" s="15" t="inlineStr">
         <is>
@@ -14548,10 +14548,10 @@
         </is>
       </c>
       <c r="E424" s="13" t="n">
-        <v>8479</v>
+        <v>8438</v>
       </c>
       <c r="F424" s="13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G424" s="15" t="inlineStr">
         <is>
@@ -14576,14 +14576,14 @@
         </is>
       </c>
       <c r="E425" s="13" t="n">
-        <v>8504</v>
+        <v>8462</v>
       </c>
       <c r="F425" s="13" t="n">
         <v>15</v>
       </c>
       <c r="G425" s="15" t="inlineStr">
         <is>
-          <t>알바로와 이그나시오가 함께 조작된 내용을 되돌릴 계획을 세우던 중, 예상치 못한 전화가 걸려 옵니다.</t>
+          <t>알바로와 이그나시오가 함께 조작 내역을 정리하며 위원회에 보낼 공식 통보를 준비하던 중, 예상치 못한 전화가 걸려 옵니다.</t>
         </is>
       </c>
     </row>
@@ -14604,14 +14604,14 @@
         </is>
       </c>
       <c r="E426" s="13" t="n">
-        <v>8522</v>
+        <v>8480</v>
       </c>
       <c r="F426" s="13" t="n">
         <v>12</v>
       </c>
       <c r="G426" s="15" t="inlineStr">
         <is>
-          <t>이그나시오가 서류 수정을 마치고, 알바로가 그동안의 증거를 최종 정리합니다.</t>
+          <t>이그나시오가 서류 수정을 마지막 하나까지 되짚은 보고서를 완성하고, 알바로가 그동안의 증거를 최종 정리합니다. 원본 서류는 손대지 않은 채 증거로 남깁니다.</t>
         </is>
       </c>
     </row>
@@ -14632,10 +14632,10 @@
         </is>
       </c>
       <c r="E427" s="13" t="n">
-        <v>8537</v>
+        <v>8495</v>
       </c>
       <c r="F427" s="13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G427" s="15" t="inlineStr">
         <is>
@@ -14660,10 +14660,10 @@
         </is>
       </c>
       <c r="E428" s="13" t="n">
-        <v>8550</v>
+        <v>8509</v>
       </c>
       <c r="F428" s="13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G428" s="15" t="inlineStr">
         <is>
@@ -14688,14 +14688,14 @@
         </is>
       </c>
       <c r="E429" s="13" t="n">
-        <v>8566</v>
+        <v>8526</v>
       </c>
       <c r="F429" s="13" t="n">
         <v>14</v>
       </c>
       <c r="G429" s="15" t="inlineStr">
         <is>
-          <t>사흘 후, 이사회 투표일. 알바로가 은행에 남아 결과를 지켜봅니다.</t>
+          <t>사흘 후, 이사회 투표일. 알바로가 은행에 남아 결과를 지켜봅니다. 위원회는 이미 검찰의 공식 통보를 받은 상태입니다.</t>
         </is>
       </c>
     </row>
@@ -14716,7 +14716,7 @@
         </is>
       </c>
       <c r="E430" s="13" t="n">
-        <v>8583</v>
+        <v>8543</v>
       </c>
       <c r="F430" s="13" t="n">
         <v>19</v>
@@ -14744,7 +14744,7 @@
         </is>
       </c>
       <c r="E431" s="13" t="n">
-        <v>8605</v>
+        <v>8565</v>
       </c>
       <c r="F431" s="13" t="n">
         <v>16</v>
@@ -14772,7 +14772,7 @@
         </is>
       </c>
       <c r="E432" s="13" t="n">
-        <v>8624</v>
+        <v>8584</v>
       </c>
       <c r="F432" s="13" t="n">
         <v>16</v>
@@ -14800,7 +14800,7 @@
         </is>
       </c>
       <c r="E433" s="13" t="n">
-        <v>8643</v>
+        <v>8603</v>
       </c>
       <c r="F433" s="13" t="n">
         <v>12</v>
@@ -14828,10 +14828,10 @@
         </is>
       </c>
       <c r="E434" s="13" t="n">
-        <v>8657</v>
+        <v>8617</v>
       </c>
       <c r="F434" s="13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G434" s="15" t="inlineStr">
         <is>
@@ -14856,7 +14856,7 @@
         </is>
       </c>
       <c r="E435" s="13" t="n">
-        <v>8674</v>
+        <v>8633</v>
       </c>
       <c r="F435" s="13" t="n">
         <v>17</v>
@@ -14884,10 +14884,10 @@
         </is>
       </c>
       <c r="E436" s="13" t="n">
-        <v>8694</v>
+        <v>8653</v>
       </c>
       <c r="F436" s="13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G436" s="15" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         </is>
       </c>
       <c r="E437" s="13" t="n">
-        <v>8715</v>
+        <v>8673</v>
       </c>
       <c r="F437" s="13" t="n">
         <v>20</v>
@@ -14940,7 +14940,7 @@
         </is>
       </c>
       <c r="E438" s="13" t="n">
-        <v>8738</v>
+        <v>8696</v>
       </c>
       <c r="F438" s="13" t="n">
         <v>23</v>
@@ -14968,7 +14968,7 @@
         </is>
       </c>
       <c r="E439" s="13" t="n">
-        <v>8764</v>
+        <v>8722</v>
       </c>
       <c r="F439" s="13" t="n">
         <v>21</v>
@@ -14996,7 +14996,7 @@
         </is>
       </c>
       <c r="E440" s="13" t="n">
-        <v>8788</v>
+        <v>8746</v>
       </c>
       <c r="F440" s="13" t="n">
         <v>19</v>
@@ -15024,7 +15024,7 @@
         </is>
       </c>
       <c r="E441" s="13" t="n">
-        <v>8810</v>
+        <v>8768</v>
       </c>
       <c r="F441" s="13" t="n">
         <v>15</v>
@@ -15052,7 +15052,7 @@
         </is>
       </c>
       <c r="E442" s="13" t="n">
-        <v>8828</v>
+        <v>8786</v>
       </c>
       <c r="F442" s="13" t="n">
         <v>20</v>
@@ -15080,7 +15080,7 @@
         </is>
       </c>
       <c r="E443" s="13" t="n">
-        <v>8851</v>
+        <v>8809</v>
       </c>
       <c r="F443" s="13" t="n">
         <v>17</v>
@@ -15108,7 +15108,7 @@
         </is>
       </c>
       <c r="E444" s="13" t="n">
-        <v>8871</v>
+        <v>8829</v>
       </c>
       <c r="F444" s="13" t="n">
         <v>19</v>
@@ -15136,7 +15136,7 @@
         </is>
       </c>
       <c r="E445" s="13" t="n">
-        <v>8892</v>
+        <v>8850</v>
       </c>
       <c r="F445" s="13" t="n">
         <v>19</v>
@@ -15164,7 +15164,7 @@
         </is>
       </c>
       <c r="E446" s="13" t="n">
-        <v>8914</v>
+        <v>8872</v>
       </c>
       <c r="F446" s="13" t="n">
         <v>10</v>
@@ -15192,7 +15192,7 @@
         </is>
       </c>
       <c r="E447" s="13" t="n">
-        <v>8926</v>
+        <v>8884</v>
       </c>
       <c r="F447" s="13" t="n">
         <v>11</v>
@@ -15220,7 +15220,7 @@
         </is>
       </c>
       <c r="E448" s="13" t="n">
-        <v>8940</v>
+        <v>8898</v>
       </c>
       <c r="F448" s="13" t="n">
         <v>12</v>
@@ -15248,7 +15248,7 @@
         </is>
       </c>
       <c r="E449" s="13" t="n">
-        <v>8954</v>
+        <v>8912</v>
       </c>
       <c r="F449" s="13" t="n">
         <v>10</v>
@@ -15276,7 +15276,7 @@
         </is>
       </c>
       <c r="E450" s="13" t="n">
-        <v>8966</v>
+        <v>8924</v>
       </c>
       <c r="F450" s="13" t="n">
         <v>12</v>
@@ -15304,7 +15304,7 @@
         </is>
       </c>
       <c r="E451" s="13" t="n">
-        <v>8981</v>
+        <v>8939</v>
       </c>
       <c r="F451" s="13" t="n">
         <v>9</v>
@@ -15332,7 +15332,7 @@
         </is>
       </c>
       <c r="E452" s="13" t="n">
-        <v>8992</v>
+        <v>8950</v>
       </c>
       <c r="F452" s="13" t="n">
         <v>12</v>
@@ -15360,7 +15360,7 @@
         </is>
       </c>
       <c r="E453" s="13" t="n">
-        <v>9007</v>
+        <v>8965</v>
       </c>
       <c r="F453" s="13" t="n">
         <v>10</v>
@@ -15388,7 +15388,7 @@
         </is>
       </c>
       <c r="E454" s="13" t="n">
-        <v>9020</v>
+        <v>8978</v>
       </c>
       <c r="F454" s="13" t="n">
         <v>9</v>
@@ -15416,7 +15416,7 @@
         </is>
       </c>
       <c r="E455" s="13" t="n">
-        <v>9031</v>
+        <v>8989</v>
       </c>
       <c r="F455" s="13" t="n">
         <v>17</v>
@@ -15444,7 +15444,7 @@
         </is>
       </c>
       <c r="E456" s="13" t="n">
-        <v>9051</v>
+        <v>9009</v>
       </c>
       <c r="F456" s="13" t="n">
         <v>13</v>
@@ -15472,7 +15472,7 @@
         </is>
       </c>
       <c r="E457" s="13" t="n">
-        <v>9067</v>
+        <v>9025</v>
       </c>
       <c r="F457" s="13" t="n">
         <v>15</v>
@@ -15500,7 +15500,7 @@
         </is>
       </c>
       <c r="E458" s="13" t="n">
-        <v>9084</v>
+        <v>9042</v>
       </c>
       <c r="F458" s="13" t="n">
         <v>22</v>
@@ -15528,7 +15528,7 @@
         </is>
       </c>
       <c r="E459" s="13" t="n">
-        <v>9108</v>
+        <v>9066</v>
       </c>
       <c r="F459" s="13" t="n">
         <v>15</v>
@@ -15556,7 +15556,7 @@
         </is>
       </c>
       <c r="E460" s="13" t="n">
-        <v>9125</v>
+        <v>9083</v>
       </c>
       <c r="F460" s="13" t="n">
         <v>17</v>
@@ -15584,7 +15584,7 @@
         </is>
       </c>
       <c r="E461" s="13" t="n">
-        <v>9145</v>
+        <v>9103</v>
       </c>
       <c r="F461" s="13" t="n">
         <v>20</v>
@@ -15612,7 +15612,7 @@
         </is>
       </c>
       <c r="E462" s="13" t="n">
-        <v>9168</v>
+        <v>9126</v>
       </c>
       <c r="F462" s="13" t="n">
         <v>13</v>
@@ -15640,7 +15640,7 @@
         </is>
       </c>
       <c r="E463" s="13" t="n">
-        <v>9184</v>
+        <v>9142</v>
       </c>
       <c r="F463" s="13" t="n">
         <v>12</v>
@@ -15668,7 +15668,7 @@
         </is>
       </c>
       <c r="E464" s="13" t="n">
-        <v>9199</v>
+        <v>9157</v>
       </c>
       <c r="F464" s="13" t="n">
         <v>11</v>
@@ -15696,7 +15696,7 @@
         </is>
       </c>
       <c r="E465" s="13" t="n">
-        <v>9212</v>
+        <v>9170</v>
       </c>
       <c r="F465" s="13" t="n">
         <v>8</v>
@@ -15724,7 +15724,7 @@
         </is>
       </c>
       <c r="E466" s="13" t="n">
-        <v>9223</v>
+        <v>9181</v>
       </c>
       <c r="F466" s="13" t="n">
         <v>23</v>
@@ -15752,7 +15752,7 @@
         </is>
       </c>
       <c r="E467" s="13" t="n">
-        <v>9249</v>
+        <v>9207</v>
       </c>
       <c r="F467" s="13" t="n">
         <v>13</v>
@@ -15780,7 +15780,7 @@
         </is>
       </c>
       <c r="E468" s="13" t="n">
-        <v>9265</v>
+        <v>9223</v>
       </c>
       <c r="F468" s="13" t="n">
         <v>7</v>
@@ -15808,7 +15808,7 @@
         </is>
       </c>
       <c r="E469" s="13" t="n">
-        <v>9274</v>
+        <v>9232</v>
       </c>
       <c r="F469" s="13" t="n">
         <v>10</v>
@@ -15836,7 +15836,7 @@
         </is>
       </c>
       <c r="E470" s="13" t="n">
-        <v>9287</v>
+        <v>9245</v>
       </c>
       <c r="F470" s="13" t="n">
         <v>10</v>
@@ -15864,7 +15864,7 @@
         </is>
       </c>
       <c r="E471" s="13" t="n">
-        <v>9300</v>
+        <v>9258</v>
       </c>
       <c r="F471" s="13" t="n">
         <v>10</v>
@@ -15892,7 +15892,7 @@
         </is>
       </c>
       <c r="E472" s="13" t="n">
-        <v>9312</v>
+        <v>9270</v>
       </c>
       <c r="F472" s="13" t="n">
         <v>7</v>
@@ -15920,7 +15920,7 @@
         </is>
       </c>
       <c r="E473" s="13" t="n">
-        <v>9322</v>
+        <v>9280</v>
       </c>
       <c r="F473" s="13" t="n">
         <v>17</v>
@@ -15948,7 +15948,7 @@
         </is>
       </c>
       <c r="E474" s="13" t="n">
-        <v>9341</v>
+        <v>9299</v>
       </c>
       <c r="F474" s="13" t="n">
         <v>15</v>
@@ -15976,7 +15976,7 @@
         </is>
       </c>
       <c r="E475" s="13" t="n">
-        <v>9358</v>
+        <v>9316</v>
       </c>
       <c r="F475" s="13" t="n">
         <v>14</v>
@@ -16004,7 +16004,7 @@
         </is>
       </c>
       <c r="E476" s="13" t="n">
-        <v>9375</v>
+        <v>9333</v>
       </c>
       <c r="F476" s="13" t="n">
         <v>21</v>
@@ -16032,7 +16032,7 @@
         </is>
       </c>
       <c r="E477" s="13" t="n">
-        <v>9399</v>
+        <v>9357</v>
       </c>
       <c r="F477" s="13" t="n">
         <v>13</v>
@@ -16060,7 +16060,7 @@
         </is>
       </c>
       <c r="E478" s="13" t="n">
-        <v>9415</v>
+        <v>9373</v>
       </c>
       <c r="F478" s="13" t="n">
         <v>16</v>
@@ -16088,7 +16088,7 @@
         </is>
       </c>
       <c r="E479" s="13" t="n">
-        <v>9434</v>
+        <v>9392</v>
       </c>
       <c r="F479" s="13" t="n">
         <v>15</v>
@@ -16116,7 +16116,7 @@
         </is>
       </c>
       <c r="E480" s="13" t="n">
-        <v>9452</v>
+        <v>9410</v>
       </c>
       <c r="F480" s="13" t="n">
         <v>17</v>
@@ -16144,7 +16144,7 @@
         </is>
       </c>
       <c r="E481" s="13" t="n">
-        <v>9472</v>
+        <v>9430</v>
       </c>
       <c r="F481" s="13" t="n">
         <v>18</v>
@@ -16172,7 +16172,7 @@
         </is>
       </c>
       <c r="E482" s="13" t="n">
-        <v>9492</v>
+        <v>9450</v>
       </c>
       <c r="F482" s="13" t="n">
         <v>16</v>
@@ -16200,7 +16200,7 @@
         </is>
       </c>
       <c r="E483" s="13" t="n">
-        <v>9511</v>
+        <v>9469</v>
       </c>
       <c r="F483" s="13" t="n">
         <v>17</v>
@@ -16228,7 +16228,7 @@
         </is>
       </c>
       <c r="E484" s="13" t="n">
-        <v>9531</v>
+        <v>9489</v>
       </c>
       <c r="F484" s="13" t="n">
         <v>11</v>
@@ -16256,7 +16256,7 @@
         </is>
       </c>
       <c r="E485" s="13" t="n">
-        <v>9545</v>
+        <v>9503</v>
       </c>
       <c r="F485" s="13" t="n">
         <v>13</v>
@@ -16284,7 +16284,7 @@
         </is>
       </c>
       <c r="E486" s="13" t="n">
-        <v>9561</v>
+        <v>9519</v>
       </c>
       <c r="F486" s="13" t="n">
         <v>16</v>
@@ -16312,7 +16312,7 @@
         </is>
       </c>
       <c r="E487" s="13" t="n">
-        <v>9580</v>
+        <v>9538</v>
       </c>
       <c r="F487" s="13" t="n">
         <v>20</v>
@@ -16340,7 +16340,7 @@
         </is>
       </c>
       <c r="E488" s="13" t="n">
-        <v>9603</v>
+        <v>9561</v>
       </c>
       <c r="F488" s="13" t="n">
         <v>10</v>
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="E489" s="13" t="n">
-        <v>9615</v>
+        <v>9573</v>
       </c>
       <c r="F489" s="13" t="n">
         <v>15</v>
@@ -16396,7 +16396,7 @@
         </is>
       </c>
       <c r="E490" s="13" t="n">
-        <v>9633</v>
+        <v>9591</v>
       </c>
       <c r="F490" s="13" t="n">
         <v>15</v>
@@ -16424,7 +16424,7 @@
         </is>
       </c>
       <c r="E491" s="13" t="n">
-        <v>9651</v>
+        <v>9609</v>
       </c>
       <c r="F491" s="13" t="n">
         <v>15</v>
@@ -16452,7 +16452,7 @@
         </is>
       </c>
       <c r="E492" s="13" t="n">
-        <v>9669</v>
+        <v>9627</v>
       </c>
       <c r="F492" s="13" t="n">
         <v>14</v>
@@ -16480,7 +16480,7 @@
         </is>
       </c>
       <c r="E493" s="13" t="n">
-        <v>9686</v>
+        <v>9644</v>
       </c>
       <c r="F493" s="13" t="n">
         <v>14</v>
@@ -16508,7 +16508,7 @@
         </is>
       </c>
       <c r="E494" s="13" t="n">
-        <v>9703</v>
+        <v>9661</v>
       </c>
       <c r="F494" s="13" t="n">
         <v>17</v>
@@ -16536,7 +16536,7 @@
         </is>
       </c>
       <c r="E495" s="13" t="n">
-        <v>9723</v>
+        <v>9681</v>
       </c>
       <c r="F495" s="13" t="n">
         <v>15</v>
@@ -16564,7 +16564,7 @@
         </is>
       </c>
       <c r="E496" s="13" t="n">
-        <v>9740</v>
+        <v>9698</v>
       </c>
       <c r="F496" s="13" t="n">
         <v>20</v>
@@ -16592,7 +16592,7 @@
         </is>
       </c>
       <c r="E497" s="13" t="n">
-        <v>9765</v>
+        <v>9723</v>
       </c>
       <c r="F497" s="13" t="n">
         <v>13</v>
@@ -16620,7 +16620,7 @@
         </is>
       </c>
       <c r="E498" s="13" t="n">
-        <v>9781</v>
+        <v>9739</v>
       </c>
       <c r="F498" s="13" t="n">
         <v>15</v>
@@ -16648,7 +16648,7 @@
         </is>
       </c>
       <c r="E499" s="13" t="n">
-        <v>9799</v>
+        <v>9757</v>
       </c>
       <c r="F499" s="13" t="n">
         <v>16</v>
@@ -16676,7 +16676,7 @@
         </is>
       </c>
       <c r="E500" s="13" t="n">
-        <v>9818</v>
+        <v>9776</v>
       </c>
       <c r="F500" s="13" t="n">
         <v>4</v>
@@ -16704,7 +16704,7 @@
         </is>
       </c>
       <c r="E501" s="13" t="n">
-        <v>9824</v>
+        <v>9782</v>
       </c>
       <c r="F501" s="13" t="n">
         <v>14</v>
@@ -16732,7 +16732,7 @@
         </is>
       </c>
       <c r="E502" s="13" t="n">
-        <v>9841</v>
+        <v>9799</v>
       </c>
       <c r="F502" s="13" t="n">
         <v>16</v>
@@ -16760,7 +16760,7 @@
         </is>
       </c>
       <c r="E503" s="13" t="n">
-        <v>9860</v>
+        <v>9818</v>
       </c>
       <c r="F503" s="13" t="n">
         <v>14</v>
@@ -16788,7 +16788,7 @@
         </is>
       </c>
       <c r="E504" s="13" t="n">
-        <v>9877</v>
+        <v>9835</v>
       </c>
       <c r="F504" s="13" t="n">
         <v>15</v>
@@ -16816,7 +16816,7 @@
         </is>
       </c>
       <c r="E505" s="13" t="n">
-        <v>9894</v>
+        <v>9852</v>
       </c>
       <c r="F505" s="13" t="n">
         <v>15</v>
@@ -16844,7 +16844,7 @@
         </is>
       </c>
       <c r="E506" s="13" t="n">
-        <v>9911</v>
+        <v>9869</v>
       </c>
       <c r="F506" s="13" t="n">
         <v>11</v>
@@ -16872,7 +16872,7 @@
         </is>
       </c>
       <c r="E507" s="13" t="n">
-        <v>9925</v>
+        <v>9883</v>
       </c>
       <c r="F507" s="13" t="n">
         <v>15</v>
@@ -16900,7 +16900,7 @@
         </is>
       </c>
       <c r="E508" s="13" t="n">
-        <v>9943</v>
+        <v>9901</v>
       </c>
       <c r="F508" s="13" t="n">
         <v>14</v>
@@ -16928,7 +16928,7 @@
         </is>
       </c>
       <c r="E509" s="13" t="n">
-        <v>9959</v>
+        <v>9917</v>
       </c>
       <c r="F509" s="13" t="n">
         <v>15</v>
@@ -16956,7 +16956,7 @@
         </is>
       </c>
       <c r="E510" s="13" t="n">
-        <v>9976</v>
+        <v>9934</v>
       </c>
       <c r="F510" s="13" t="n">
         <v>14</v>
@@ -16984,7 +16984,7 @@
         </is>
       </c>
       <c r="E511" s="13" t="n">
-        <v>9993</v>
+        <v>9951</v>
       </c>
       <c r="F511" s="13" t="n">
         <v>14</v>
@@ -17012,7 +17012,7 @@
         </is>
       </c>
       <c r="E512" s="13" t="n">
-        <v>10010</v>
+        <v>9968</v>
       </c>
       <c r="F512" s="13" t="n">
         <v>14</v>
@@ -17040,7 +17040,7 @@
         </is>
       </c>
       <c r="E513" s="13" t="n">
-        <v>10027</v>
+        <v>9985</v>
       </c>
       <c r="F513" s="13" t="n">
         <v>13</v>
@@ -17068,7 +17068,7 @@
         </is>
       </c>
       <c r="E514" s="13" t="n">
-        <v>10043</v>
+        <v>10001</v>
       </c>
       <c r="F514" s="13" t="n">
         <v>15</v>
@@ -17096,7 +17096,7 @@
         </is>
       </c>
       <c r="E515" s="13" t="n">
-        <v>10061</v>
+        <v>10019</v>
       </c>
       <c r="F515" s="13" t="n">
         <v>14</v>
@@ -17124,7 +17124,7 @@
         </is>
       </c>
       <c r="E516" s="13" t="n">
-        <v>10077</v>
+        <v>10035</v>
       </c>
       <c r="F516" s="13" t="n">
         <v>14</v>
@@ -17152,7 +17152,7 @@
         </is>
       </c>
       <c r="E517" s="13" t="n">
-        <v>10094</v>
+        <v>10052</v>
       </c>
       <c r="F517" s="13" t="n">
         <v>14</v>
@@ -17180,7 +17180,7 @@
         </is>
       </c>
       <c r="E518" s="13" t="n">
-        <v>10111</v>
+        <v>10069</v>
       </c>
       <c r="F518" s="13" t="n">
         <v>13</v>
@@ -17208,7 +17208,7 @@
         </is>
       </c>
       <c r="E519" s="13" t="n">
-        <v>10126</v>
+        <v>10084</v>
       </c>
       <c r="F519" s="13" t="n">
         <v>10</v>
@@ -17236,7 +17236,7 @@
         </is>
       </c>
       <c r="E520" s="13" t="n">
-        <v>10138</v>
+        <v>10096</v>
       </c>
       <c r="F520" s="13" t="n">
         <v>10</v>
@@ -17264,7 +17264,7 @@
         </is>
       </c>
       <c r="E521" s="13" t="n">
-        <v>10151</v>
+        <v>10109</v>
       </c>
       <c r="F521" s="13" t="n">
         <v>11</v>
@@ -17292,7 +17292,7 @@
         </is>
       </c>
       <c r="E522" s="13" t="n">
-        <v>10165</v>
+        <v>10123</v>
       </c>
       <c r="F522" s="13" t="n">
         <v>10</v>
@@ -17320,7 +17320,7 @@
         </is>
       </c>
       <c r="E523" s="13" t="n">
-        <v>10177</v>
+        <v>10135</v>
       </c>
       <c r="F523" s="13" t="n">
         <v>10</v>
@@ -17348,7 +17348,7 @@
         </is>
       </c>
       <c r="E524" s="13" t="n">
-        <v>10190</v>
+        <v>10148</v>
       </c>
       <c r="F524" s="13" t="n">
         <v>11</v>
@@ -17376,7 +17376,7 @@
         </is>
       </c>
       <c r="E525" s="13" t="n">
-        <v>10204</v>
+        <v>10162</v>
       </c>
       <c r="F525" s="13" t="n">
         <v>8</v>
@@ -17404,7 +17404,7 @@
         </is>
       </c>
       <c r="E526" s="13" t="n">
-        <v>10214</v>
+        <v>10172</v>
       </c>
       <c r="F526" s="13" t="n">
         <v>11</v>
@@ -17432,7 +17432,7 @@
         </is>
       </c>
       <c r="E527" s="13" t="n">
-        <v>10228</v>
+        <v>10186</v>
       </c>
       <c r="F527" s="13" t="n">
         <v>8</v>
@@ -17460,7 +17460,7 @@
         </is>
       </c>
       <c r="E528" s="13" t="n">
-        <v>10238</v>
+        <v>10196</v>
       </c>
       <c r="F528" s="13" t="n">
         <v>12</v>
@@ -17488,7 +17488,7 @@
         </is>
       </c>
       <c r="E529" s="13" t="n">
-        <v>10253</v>
+        <v>10211</v>
       </c>
       <c r="F529" s="13" t="n">
         <v>15</v>
@@ -17516,7 +17516,7 @@
         </is>
       </c>
       <c r="E530" s="13" t="n">
-        <v>10271</v>
+        <v>10229</v>
       </c>
       <c r="F530" s="13" t="n">
         <v>13</v>
@@ -17544,7 +17544,7 @@
         </is>
       </c>
       <c r="E531" s="13" t="n">
-        <v>10287</v>
+        <v>10245</v>
       </c>
       <c r="F531" s="13" t="n">
         <v>14</v>
@@ -17572,7 +17572,7 @@
         </is>
       </c>
       <c r="E532" s="13" t="n">
-        <v>10304</v>
+        <v>10262</v>
       </c>
       <c r="F532" s="13" t="n">
         <v>12</v>
@@ -17600,7 +17600,7 @@
         </is>
       </c>
       <c r="E533" s="13" t="n">
-        <v>10319</v>
+        <v>10277</v>
       </c>
       <c r="F533" s="13" t="n">
         <v>13</v>
@@ -17628,7 +17628,7 @@
         </is>
       </c>
       <c r="E534" s="13" t="n">
-        <v>10334</v>
+        <v>10292</v>
       </c>
       <c r="F534" s="13" t="n">
         <v>12</v>
@@ -17656,7 +17656,7 @@
         </is>
       </c>
       <c r="E535" s="13" t="n">
-        <v>10348</v>
+        <v>10306</v>
       </c>
       <c r="F535" s="13" t="n">
         <v>9</v>
@@ -17684,7 +17684,7 @@
         </is>
       </c>
       <c r="E536" s="13" t="n">
-        <v>10360</v>
+        <v>10318</v>
       </c>
       <c r="F536" s="13" t="n">
         <v>8</v>
@@ -17712,7 +17712,7 @@
         </is>
       </c>
       <c r="E537" s="13" t="n">
-        <v>10370</v>
+        <v>10328</v>
       </c>
       <c r="F537" s="13" t="n">
         <v>7</v>
@@ -17740,7 +17740,7 @@
         </is>
       </c>
       <c r="E538" s="13" t="n">
-        <v>10379</v>
+        <v>10337</v>
       </c>
       <c r="F538" s="13" t="n">
         <v>12</v>
@@ -17768,7 +17768,7 @@
         </is>
       </c>
       <c r="E539" s="13" t="n">
-        <v>10393</v>
+        <v>10351</v>
       </c>
       <c r="F539" s="13" t="n">
         <v>10</v>
@@ -17796,7 +17796,7 @@
         </is>
       </c>
       <c r="E540" s="13" t="n">
-        <v>10406</v>
+        <v>10364</v>
       </c>
       <c r="F540" s="13" t="n">
         <v>11</v>
@@ -17824,7 +17824,7 @@
         </is>
       </c>
       <c r="E541" s="13" t="n">
-        <v>10420</v>
+        <v>10378</v>
       </c>
       <c r="F541" s="13" t="n">
         <v>10</v>
@@ -17852,7 +17852,7 @@
         </is>
       </c>
       <c r="E542" s="13" t="n">
-        <v>10432</v>
+        <v>10390</v>
       </c>
       <c r="F542" s="13" t="n">
         <v>11</v>
@@ -17880,7 +17880,7 @@
         </is>
       </c>
       <c r="E543" s="13" t="n">
-        <v>10446</v>
+        <v>10404</v>
       </c>
       <c r="F543" s="13" t="n">
         <v>10</v>
@@ -17908,7 +17908,7 @@
         </is>
       </c>
       <c r="E544" s="13" t="n">
-        <v>10459</v>
+        <v>10417</v>
       </c>
       <c r="F544" s="13" t="n">
         <v>8</v>
@@ -17936,7 +17936,7 @@
         </is>
       </c>
       <c r="E545" s="13" t="n">
-        <v>10469</v>
+        <v>10427</v>
       </c>
       <c r="F545" s="13" t="n">
         <v>11</v>
@@ -17964,7 +17964,7 @@
         </is>
       </c>
       <c r="E546" s="13" t="n">
-        <v>10483</v>
+        <v>10441</v>
       </c>
       <c r="F546" s="13" t="n">
         <v>11</v>
@@ -17992,7 +17992,7 @@
         </is>
       </c>
       <c r="E547" s="13" t="n">
-        <v>10497</v>
+        <v>10455</v>
       </c>
       <c r="F547" s="13" t="n">
         <v>9</v>
@@ -18020,7 +18020,7 @@
         </is>
       </c>
       <c r="E548" s="13" t="n">
-        <v>10508</v>
+        <v>10466</v>
       </c>
       <c r="F548" s="13" t="n">
         <v>11</v>
@@ -18048,7 +18048,7 @@
         </is>
       </c>
       <c r="E549" s="13" t="n">
-        <v>10522</v>
+        <v>10480</v>
       </c>
       <c r="F549" s="13" t="n">
         <v>13</v>
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="E550" s="13" t="n">
-        <v>10538</v>
+        <v>10496</v>
       </c>
       <c r="F550" s="13" t="n">
         <v>10</v>
@@ -18104,7 +18104,7 @@
         </is>
       </c>
       <c r="E551" s="13" t="n">
-        <v>10550</v>
+        <v>10508</v>
       </c>
       <c r="F551" s="13" t="n">
         <v>12</v>
@@ -18132,7 +18132,7 @@
         </is>
       </c>
       <c r="E552" s="13" t="n">
-        <v>10565</v>
+        <v>10523</v>
       </c>
       <c r="F552" s="13" t="n">
         <v>10</v>
@@ -18160,7 +18160,7 @@
         </is>
       </c>
       <c r="E553" s="13" t="n">
-        <v>10578</v>
+        <v>10536</v>
       </c>
       <c r="F553" s="13" t="n">
         <v>10</v>
@@ -18188,7 +18188,7 @@
         </is>
       </c>
       <c r="E554" s="13" t="n">
-        <v>10590</v>
+        <v>10548</v>
       </c>
       <c r="F554" s="13" t="n">
         <v>10</v>
@@ -18216,7 +18216,7 @@
         </is>
       </c>
       <c r="E555" s="13" t="n">
-        <v>10603</v>
+        <v>10561</v>
       </c>
       <c r="F555" s="13" t="n">
         <v>10</v>
@@ -18244,7 +18244,7 @@
         </is>
       </c>
       <c r="E556" s="13" t="n">
-        <v>10616</v>
+        <v>10574</v>
       </c>
       <c r="F556" s="13" t="n">
         <v>8</v>
@@ -18272,7 +18272,7 @@
         </is>
       </c>
       <c r="E557" s="13" t="n">
-        <v>10626</v>
+        <v>10584</v>
       </c>
       <c r="F557" s="13" t="n">
         <v>11</v>
@@ -18300,7 +18300,7 @@
         </is>
       </c>
       <c r="E558" s="13" t="n">
-        <v>10640</v>
+        <v>10598</v>
       </c>
       <c r="F558" s="13" t="n">
         <v>8</v>
@@ -18328,7 +18328,7 @@
         </is>
       </c>
       <c r="E559" s="13" t="n">
-        <v>10650</v>
+        <v>10608</v>
       </c>
       <c r="F559" s="13" t="n">
         <v>10</v>
@@ -18356,7 +18356,7 @@
         </is>
       </c>
       <c r="E560" s="13" t="n">
-        <v>10662</v>
+        <v>10620</v>
       </c>
       <c r="F560" s="13" t="n">
         <v>11</v>
@@ -18384,7 +18384,7 @@
         </is>
       </c>
       <c r="E561" s="13" t="n">
-        <v>10676</v>
+        <v>10634</v>
       </c>
       <c r="F561" s="13" t="n">
         <v>7</v>
@@ -18412,7 +18412,7 @@
         </is>
       </c>
       <c r="E562" s="13" t="n">
-        <v>10685</v>
+        <v>10643</v>
       </c>
       <c r="F562" s="13" t="n">
         <v>6</v>
@@ -18440,7 +18440,7 @@
         </is>
       </c>
       <c r="E563" s="13" t="n">
-        <v>10694</v>
+        <v>10652</v>
       </c>
       <c r="F563" s="13" t="n">
         <v>4</v>
@@ -18468,7 +18468,7 @@
         </is>
       </c>
       <c r="E564" s="13" t="n">
-        <v>10700</v>
+        <v>10658</v>
       </c>
       <c r="F564" s="13" t="n">
         <v>5</v>
@@ -18496,7 +18496,7 @@
         </is>
       </c>
       <c r="E565" s="13" t="n">
-        <v>10707</v>
+        <v>10665</v>
       </c>
       <c r="F565" s="13" t="n">
         <v>1</v>
@@ -18524,7 +18524,7 @@
         </is>
       </c>
       <c r="E566" s="13" t="n">
-        <v>10710</v>
+        <v>10668</v>
       </c>
       <c r="F566" s="13" t="n">
         <v>8</v>
@@ -18552,7 +18552,7 @@
         </is>
       </c>
       <c r="E567" s="13" t="n">
-        <v>10721</v>
+        <v>10679</v>
       </c>
       <c r="F567" s="13" t="n">
         <v>9</v>
@@ -18580,7 +18580,7 @@
         </is>
       </c>
       <c r="E568" s="13" t="n">
-        <v>10733</v>
+        <v>10691</v>
       </c>
       <c r="F568" s="13" t="n">
         <v>8</v>
@@ -18608,7 +18608,7 @@
         </is>
       </c>
       <c r="E569" s="13" t="n">
-        <v>10743</v>
+        <v>10701</v>
       </c>
       <c r="F569" s="13" t="n">
         <v>8</v>
@@ -18636,7 +18636,7 @@
         </is>
       </c>
       <c r="E570" s="13" t="n">
-        <v>10754</v>
+        <v>10712</v>
       </c>
       <c r="F570" s="13" t="n">
         <v>8</v>
@@ -18664,7 +18664,7 @@
         </is>
       </c>
       <c r="E571" s="13" t="n">
-        <v>10764</v>
+        <v>10722</v>
       </c>
       <c r="F571" s="13" t="n">
         <v>8</v>
@@ -18692,7 +18692,7 @@
         </is>
       </c>
       <c r="E572" s="13" t="n">
-        <v>10775</v>
+        <v>10733</v>
       </c>
       <c r="F572" s="13" t="n">
         <v>8</v>
@@ -18720,7 +18720,7 @@
         </is>
       </c>
       <c r="E573" s="13" t="n">
-        <v>10785</v>
+        <v>10743</v>
       </c>
       <c r="F573" s="13" t="n">
         <v>9</v>
@@ -18748,7 +18748,7 @@
         </is>
       </c>
       <c r="E574" s="13" t="n">
-        <v>10797</v>
+        <v>10755</v>
       </c>
       <c r="F574" s="13" t="n">
         <v>8</v>
@@ -18776,7 +18776,7 @@
         </is>
       </c>
       <c r="E575" s="13" t="n">
-        <v>10807</v>
+        <v>10765</v>
       </c>
       <c r="F575" s="13" t="n">
         <v>8</v>
@@ -18804,7 +18804,7 @@
         </is>
       </c>
       <c r="E576" s="13" t="n">
-        <v>10818</v>
+        <v>10776</v>
       </c>
       <c r="F576" s="13" t="n">
         <v>8</v>
@@ -18832,7 +18832,7 @@
         </is>
       </c>
       <c r="E577" s="13" t="n">
-        <v>10829</v>
+        <v>10787</v>
       </c>
       <c r="F577" s="13" t="n">
         <v>8</v>
@@ -18860,7 +18860,7 @@
         </is>
       </c>
       <c r="E578" s="13" t="n">
-        <v>10839</v>
+        <v>10797</v>
       </c>
       <c r="F578" s="13" t="n">
         <v>8</v>
@@ -18888,7 +18888,7 @@
         </is>
       </c>
       <c r="E579" s="13" t="n">
-        <v>10850</v>
+        <v>10808</v>
       </c>
       <c r="F579" s="13" t="n">
         <v>8</v>
@@ -18916,7 +18916,7 @@
         </is>
       </c>
       <c r="E580" s="13" t="n">
-        <v>10860</v>
+        <v>10818</v>
       </c>
       <c r="F580" s="13" t="n">
         <v>8</v>
@@ -18944,7 +18944,7 @@
         </is>
       </c>
       <c r="E581" s="13" t="n">
-        <v>10871</v>
+        <v>10829</v>
       </c>
       <c r="F581" s="13" t="n">
         <v>6</v>
@@ -18972,7 +18972,7 @@
         </is>
       </c>
       <c r="E582" s="13" t="n">
-        <v>10879</v>
+        <v>10837</v>
       </c>
       <c r="F582" s="13" t="n">
         <v>2</v>
@@ -19000,7 +19000,7 @@
         </is>
       </c>
       <c r="E583" s="13" t="n">
-        <v>10883</v>
+        <v>10841</v>
       </c>
       <c r="F583" s="13" t="n">
         <v>8</v>
@@ -19028,7 +19028,7 @@
         </is>
       </c>
       <c r="E584" s="13" t="n">
-        <v>10894</v>
+        <v>10852</v>
       </c>
       <c r="F584" s="13" t="n">
         <v>1</v>
@@ -19056,7 +19056,7 @@
         </is>
       </c>
       <c r="E585" s="13" t="n">
-        <v>10897</v>
+        <v>10855</v>
       </c>
       <c r="F585" s="13" t="n">
         <v>4</v>
@@ -19084,7 +19084,7 @@
         </is>
       </c>
       <c r="E586" s="13" t="n">
-        <v>10903</v>
+        <v>10861</v>
       </c>
       <c r="F586" s="13" t="n">
         <v>1</v>
@@ -19112,7 +19112,7 @@
         </is>
       </c>
       <c r="E587" s="13" t="n">
-        <v>10906</v>
+        <v>10864</v>
       </c>
       <c r="F587" s="13" t="n">
         <v>1</v>
@@ -19140,7 +19140,7 @@
         </is>
       </c>
       <c r="E588" s="13" t="n">
-        <v>10910</v>
+        <v>10868</v>
       </c>
       <c r="F588" s="13" t="n">
         <v>1</v>
@@ -19168,7 +19168,7 @@
         </is>
       </c>
       <c r="E589" s="13" t="n">
-        <v>10913</v>
+        <v>10871</v>
       </c>
       <c r="F589" s="13" t="n">
         <v>1</v>
@@ -19196,7 +19196,7 @@
         </is>
       </c>
       <c r="E590" s="13" t="n">
-        <v>10916</v>
+        <v>10874</v>
       </c>
       <c r="F590" s="13" t="n">
         <v>10</v>
@@ -19224,7 +19224,7 @@
         </is>
       </c>
       <c r="E591" s="13" t="n">
-        <v>10928</v>
+        <v>10886</v>
       </c>
       <c r="F591" s="13" t="n">
         <v>8</v>
@@ -19252,7 +19252,7 @@
         </is>
       </c>
       <c r="E592" s="13" t="n">
-        <v>10938</v>
+        <v>10896</v>
       </c>
       <c r="F592" s="13" t="n">
         <v>11</v>
@@ -19280,7 +19280,7 @@
         </is>
       </c>
       <c r="E593" s="13" t="n">
-        <v>10952</v>
+        <v>10910</v>
       </c>
       <c r="F593" s="13" t="n">
         <v>6</v>
@@ -19308,7 +19308,7 @@
         </is>
       </c>
       <c r="E594" s="13" t="n">
-        <v>10960</v>
+        <v>10918</v>
       </c>
       <c r="F594" s="13" t="n">
         <v>8</v>
@@ -19336,7 +19336,7 @@
         </is>
       </c>
       <c r="E595" s="13" t="n">
-        <v>10971</v>
+        <v>10929</v>
       </c>
       <c r="F595" s="13" t="n">
         <v>5</v>
@@ -19364,7 +19364,7 @@
         </is>
       </c>
       <c r="E596" s="13" t="n">
-        <v>10978</v>
+        <v>10936</v>
       </c>
       <c r="F596" s="13" t="n">
         <v>4</v>
@@ -19392,7 +19392,7 @@
         </is>
       </c>
       <c r="E597" s="13" t="n">
-        <v>10984</v>
+        <v>10942</v>
       </c>
       <c r="F597" s="13" t="n">
         <v>1</v>
@@ -19420,7 +19420,7 @@
         </is>
       </c>
       <c r="E598" s="13" t="n">
-        <v>10987</v>
+        <v>10945</v>
       </c>
       <c r="F598" s="13" t="n">
         <v>8</v>
@@ -19448,7 +19448,7 @@
         </is>
       </c>
       <c r="E599" s="13" t="n">
-        <v>10997</v>
+        <v>10955</v>
       </c>
       <c r="F599" s="13" t="n">
         <v>8</v>
@@ -19476,7 +19476,7 @@
         </is>
       </c>
       <c r="E600" s="13" t="n">
-        <v>11008</v>
+        <v>10966</v>
       </c>
       <c r="F600" s="13" t="n">
         <v>8</v>
@@ -19504,7 +19504,7 @@
         </is>
       </c>
       <c r="E601" s="13" t="n">
-        <v>11018</v>
+        <v>10976</v>
       </c>
       <c r="F601" s="13" t="n">
         <v>7</v>
@@ -19532,7 +19532,7 @@
         </is>
       </c>
       <c r="E602" s="13" t="n">
-        <v>11028</v>
+        <v>10986</v>
       </c>
       <c r="F602" s="13" t="n">
         <v>8</v>
@@ -19560,7 +19560,7 @@
         </is>
       </c>
       <c r="E603" s="13" t="n">
-        <v>11038</v>
+        <v>10996</v>
       </c>
       <c r="F603" s="13" t="n">
         <v>8</v>
@@ -19588,7 +19588,7 @@
         </is>
       </c>
       <c r="E604" s="13" t="n">
-        <v>11049</v>
+        <v>11007</v>
       </c>
       <c r="F604" s="13" t="n">
         <v>4</v>
@@ -19616,7 +19616,7 @@
         </is>
       </c>
       <c r="E605" s="13" t="n">
-        <v>11055</v>
+        <v>11013</v>
       </c>
       <c r="F605" s="13" t="n">
         <v>32</v>
@@ -19644,7 +19644,7 @@
         </is>
       </c>
       <c r="E606" s="13" t="n">
-        <v>11091</v>
+        <v>11049</v>
       </c>
       <c r="F606" s="13" t="n">
         <v>20</v>
@@ -19672,7 +19672,7 @@
         </is>
       </c>
       <c r="E607" s="13" t="n">
-        <v>11114</v>
+        <v>11072</v>
       </c>
       <c r="F607" s="13" t="n">
         <v>59</v>
@@ -19700,7 +19700,7 @@
         </is>
       </c>
       <c r="E608" s="13" t="n">
-        <v>11178</v>
+        <v>11136</v>
       </c>
       <c r="F608" s="13" t="n">
         <v>58</v>
@@ -19728,7 +19728,7 @@
         </is>
       </c>
       <c r="E609" s="13" t="n">
-        <v>11242</v>
+        <v>11200</v>
       </c>
       <c r="F609" s="13" t="n">
         <v>24</v>
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="E610" s="13" t="n">
-        <v>11269</v>
+        <v>11227</v>
       </c>
       <c r="F610" s="13" t="n">
         <v>39</v>
@@ -19784,7 +19784,7 @@
         </is>
       </c>
       <c r="E611" s="13" t="n">
-        <v>11312</v>
+        <v>11270</v>
       </c>
       <c r="F611" s="13" t="n">
         <v>47</v>
@@ -19812,7 +19812,7 @@
         </is>
       </c>
       <c r="E612" s="13" t="n">
-        <v>11364</v>
+        <v>11322</v>
       </c>
       <c r="F612" s="13" t="n">
         <v>14</v>
@@ -19840,7 +19840,7 @@
         </is>
       </c>
       <c r="E613" s="13" t="n">
-        <v>11380</v>
+        <v>11338</v>
       </c>
       <c r="F613" s="13" t="n">
         <v>12</v>
@@ -19868,7 +19868,7 @@
         </is>
       </c>
       <c r="E614" s="13" t="n">
-        <v>11395</v>
+        <v>11353</v>
       </c>
       <c r="F614" s="13" t="n">
         <v>12</v>
@@ -19896,7 +19896,7 @@
         </is>
       </c>
       <c r="E615" s="13" t="n">
-        <v>11410</v>
+        <v>11368</v>
       </c>
       <c r="F615" s="13" t="n">
         <v>12</v>
@@ -19924,7 +19924,7 @@
         </is>
       </c>
       <c r="E616" s="13" t="n">
-        <v>11425</v>
+        <v>11383</v>
       </c>
       <c r="F616" s="13" t="n">
         <v>12</v>
@@ -19952,7 +19952,7 @@
         </is>
       </c>
       <c r="E617" s="13" t="n">
-        <v>11439</v>
+        <v>11397</v>
       </c>
       <c r="F617" s="13" t="n">
         <v>12</v>
@@ -19980,7 +19980,7 @@
         </is>
       </c>
       <c r="E618" s="13" t="n">
-        <v>11453</v>
+        <v>11411</v>
       </c>
       <c r="F618" s="13" t="n">
         <v>10</v>
@@ -20008,7 +20008,7 @@
         </is>
       </c>
       <c r="E619" s="13" t="n">
-        <v>11466</v>
+        <v>11424</v>
       </c>
       <c r="F619" s="13" t="n">
         <v>12</v>
@@ -20036,7 +20036,7 @@
         </is>
       </c>
       <c r="E620" s="13" t="n">
-        <v>11481</v>
+        <v>11439</v>
       </c>
       <c r="F620" s="13" t="n">
         <v>12</v>
@@ -20064,7 +20064,7 @@
         </is>
       </c>
       <c r="E621" s="13" t="n">
-        <v>11495</v>
+        <v>11453</v>
       </c>
       <c r="F621" s="13" t="n">
         <v>13</v>
@@ -20092,7 +20092,7 @@
         </is>
       </c>
       <c r="E622" s="13" t="n">
-        <v>11510</v>
+        <v>11468</v>
       </c>
       <c r="F622" s="13" t="n">
         <v>74</v>
@@ -20120,7 +20120,7 @@
         </is>
       </c>
       <c r="E623" s="13" t="n">
-        <v>11591</v>
+        <v>11549</v>
       </c>
       <c r="F623" s="13" t="n">
         <v>120</v>
@@ -20148,7 +20148,7 @@
         </is>
       </c>
       <c r="E624" s="13" t="n">
-        <v>11720</v>
+        <v>11678</v>
       </c>
       <c r="F624" s="13" t="n">
         <v>44</v>
@@ -20176,7 +20176,7 @@
         </is>
       </c>
       <c r="E625" s="13" t="n">
-        <v>11769</v>
+        <v>11727</v>
       </c>
       <c r="F625" s="13" t="n">
         <v>61</v>
@@ -20204,7 +20204,7 @@
         </is>
       </c>
       <c r="E626" s="13" t="n">
-        <v>11836</v>
+        <v>11794</v>
       </c>
       <c r="F626" s="13" t="n">
         <v>52</v>
@@ -20232,7 +20232,7 @@
         </is>
       </c>
       <c r="E627" s="13" t="n">
-        <v>11893</v>
+        <v>11851</v>
       </c>
       <c r="F627" s="13" t="n">
         <v>10</v>
@@ -20260,7 +20260,7 @@
         </is>
       </c>
       <c r="E628" s="13" t="n">
-        <v>11906</v>
+        <v>11864</v>
       </c>
       <c r="F628" s="13" t="n">
         <v>10</v>
@@ -20288,7 +20288,7 @@
         </is>
       </c>
       <c r="E629" s="13" t="n">
-        <v>11919</v>
+        <v>11877</v>
       </c>
       <c r="F629" s="13" t="n">
         <v>9</v>
@@ -20316,7 +20316,7 @@
         </is>
       </c>
       <c r="E630" s="13" t="n">
-        <v>11930</v>
+        <v>11888</v>
       </c>
       <c r="F630" s="13" t="n">
         <v>26</v>
@@ -20344,7 +20344,7 @@
         </is>
       </c>
       <c r="E631" s="13" t="n">
-        <v>11960</v>
+        <v>11918</v>
       </c>
       <c r="F631" s="13" t="n">
         <v>25</v>
@@ -20372,7 +20372,7 @@
         </is>
       </c>
       <c r="E632" s="13" t="n">
-        <v>11989</v>
+        <v>11947</v>
       </c>
       <c r="F632" s="13" t="n">
         <v>18</v>
@@ -20400,7 +20400,7 @@
         </is>
       </c>
       <c r="E633" s="13" t="n">
-        <v>12010</v>
+        <v>11968</v>
       </c>
       <c r="F633" s="13" t="n">
         <v>22</v>
@@ -20428,7 +20428,7 @@
         </is>
       </c>
       <c r="E634" s="13" t="n">
-        <v>12035</v>
+        <v>11993</v>
       </c>
       <c r="F634" s="13" t="n">
         <v>19</v>
@@ -20456,7 +20456,7 @@
         </is>
       </c>
       <c r="E635" s="13" t="n">
-        <v>12057</v>
+        <v>12015</v>
       </c>
       <c r="F635" s="13" t="n">
         <v>20</v>
@@ -20484,7 +20484,7 @@
         </is>
       </c>
       <c r="E636" s="13" t="n">
-        <v>12081</v>
+        <v>12039</v>
       </c>
       <c r="F636" s="13" t="n">
         <v>18</v>
@@ -20512,7 +20512,7 @@
         </is>
       </c>
       <c r="E637" s="13" t="n">
-        <v>12102</v>
+        <v>12060</v>
       </c>
       <c r="F637" s="13" t="n">
         <v>18</v>
@@ -20540,7 +20540,7 @@
         </is>
       </c>
       <c r="E638" s="13" t="n">
-        <v>12123</v>
+        <v>12081</v>
       </c>
       <c r="F638" s="13" t="n">
         <v>17</v>
@@ -20568,7 +20568,7 @@
         </is>
       </c>
       <c r="E639" s="13" t="n">
-        <v>12143</v>
+        <v>12101</v>
       </c>
       <c r="F639" s="13" t="n">
         <v>11</v>
@@ -20596,7 +20596,7 @@
         </is>
       </c>
       <c r="E640" s="13" t="n">
-        <v>12156</v>
+        <v>12114</v>
       </c>
       <c r="F640" s="13" t="n">
         <v>18</v>
@@ -20624,7 +20624,7 @@
         </is>
       </c>
       <c r="E641" s="13" t="n">
-        <v>12178</v>
+        <v>12136</v>
       </c>
       <c r="F641" s="13" t="n">
         <v>18</v>
@@ -20652,7 +20652,7 @@
         </is>
       </c>
       <c r="E642" s="13" t="n">
-        <v>12199</v>
+        <v>12157</v>
       </c>
       <c r="F642" s="13" t="n">
         <v>19</v>
@@ -20680,7 +20680,7 @@
         </is>
       </c>
       <c r="E643" s="13" t="n">
-        <v>12221</v>
+        <v>12179</v>
       </c>
       <c r="F643" s="13" t="n">
         <v>18</v>
@@ -20708,7 +20708,7 @@
         </is>
       </c>
       <c r="E644" s="13" t="n">
-        <v>12242</v>
+        <v>12200</v>
       </c>
       <c r="F644" s="13" t="n">
         <v>18</v>
@@ -20736,7 +20736,7 @@
         </is>
       </c>
       <c r="E645" s="13" t="n">
-        <v>12263</v>
+        <v>12221</v>
       </c>
       <c r="F645" s="13" t="n">
         <v>18</v>
@@ -20764,7 +20764,7 @@
         </is>
       </c>
       <c r="E646" s="13" t="n">
-        <v>12284</v>
+        <v>12242</v>
       </c>
       <c r="F646" s="13" t="n">
         <v>18</v>
@@ -20792,7 +20792,7 @@
         </is>
       </c>
       <c r="E647" s="13" t="n">
-        <v>12305</v>
+        <v>12263</v>
       </c>
       <c r="F647" s="13" t="n">
         <v>19</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="E648" s="13" t="n">
-        <v>12327</v>
+        <v>12285</v>
       </c>
       <c r="F648" s="13" t="n">
         <v>18</v>
@@ -20848,7 +20848,7 @@
         </is>
       </c>
       <c r="E649" s="13" t="n">
-        <v>12348</v>
+        <v>12306</v>
       </c>
       <c r="F649" s="13" t="n">
         <v>17</v>
@@ -20876,7 +20876,7 @@
         </is>
       </c>
       <c r="E650" s="13" t="n">
-        <v>12368</v>
+        <v>12326</v>
       </c>
       <c r="F650" s="13" t="n">
         <v>19</v>
@@ -20904,7 +20904,7 @@
         </is>
       </c>
       <c r="E651" s="13" t="n">
-        <v>12390</v>
+        <v>12348</v>
       </c>
       <c r="F651" s="13" t="n">
         <v>25</v>
@@ -20932,7 +20932,7 @@
         </is>
       </c>
       <c r="E652" s="13" t="n">
-        <v>12418</v>
+        <v>12376</v>
       </c>
       <c r="F652" s="13" t="n">
         <v>18</v>
@@ -20960,7 +20960,7 @@
         </is>
       </c>
       <c r="E653" s="13" t="n">
-        <v>12439</v>
+        <v>12397</v>
       </c>
       <c r="F653" s="13" t="n">
         <v>14</v>
@@ -20988,7 +20988,7 @@
         </is>
       </c>
       <c r="E654" s="13" t="n">
-        <v>12456</v>
+        <v>12414</v>
       </c>
       <c r="F654" s="13" t="n">
         <v>20</v>
@@ -21016,7 +21016,7 @@
         </is>
       </c>
       <c r="E655" s="13" t="n">
-        <v>12479</v>
+        <v>12437</v>
       </c>
       <c r="F655" s="13" t="n">
         <v>16</v>
@@ -21044,7 +21044,7 @@
         </is>
       </c>
       <c r="E656" s="13" t="n">
-        <v>12498</v>
+        <v>12456</v>
       </c>
       <c r="F656" s="13" t="n">
         <v>17</v>
@@ -21072,7 +21072,7 @@
         </is>
       </c>
       <c r="E657" s="13" t="n">
-        <v>12518</v>
+        <v>12476</v>
       </c>
       <c r="F657" s="13" t="n">
         <v>18</v>
@@ -21100,7 +21100,7 @@
         </is>
       </c>
       <c r="E658" s="13" t="n">
-        <v>12539</v>
+        <v>12497</v>
       </c>
       <c r="F658" s="13" t="n">
         <v>18</v>
@@ -21128,7 +21128,7 @@
         </is>
       </c>
       <c r="E659" s="13" t="n">
-        <v>12560</v>
+        <v>12518</v>
       </c>
       <c r="F659" s="13" t="n">
         <v>17</v>
@@ -21156,7 +21156,7 @@
         </is>
       </c>
       <c r="E660" s="13" t="n">
-        <v>12580</v>
+        <v>12538</v>
       </c>
       <c r="F660" s="13" t="n">
         <v>26</v>
@@ -21184,7 +21184,7 @@
         </is>
       </c>
       <c r="E661" s="13" t="n">
-        <v>12609</v>
+        <v>12567</v>
       </c>
       <c r="F661" s="13" t="n">
         <v>28</v>
@@ -21212,7 +21212,7 @@
         </is>
       </c>
       <c r="E662" s="13" t="n">
-        <v>12640</v>
+        <v>12598</v>
       </c>
       <c r="F662" s="13" t="n">
         <v>16</v>
@@ -21240,7 +21240,7 @@
         </is>
       </c>
       <c r="E663" s="13" t="n">
-        <v>12659</v>
+        <v>12617</v>
       </c>
       <c r="F663" s="13" t="n">
         <v>16</v>
@@ -21268,7 +21268,7 @@
         </is>
       </c>
       <c r="E664" s="13" t="n">
-        <v>12678</v>
+        <v>12636</v>
       </c>
       <c r="F664" s="13" t="n">
         <v>16</v>
@@ -21296,7 +21296,7 @@
         </is>
       </c>
       <c r="E665" s="13" t="n">
-        <v>12697</v>
+        <v>12655</v>
       </c>
       <c r="F665" s="13" t="n">
         <v>20</v>
@@ -21324,7 +21324,7 @@
         </is>
       </c>
       <c r="E666" s="13" t="n">
-        <v>12720</v>
+        <v>12678</v>
       </c>
       <c r="F666" s="13" t="n">
         <v>17</v>
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="E667" s="13" t="n">
-        <v>12740</v>
+        <v>12698</v>
       </c>
       <c r="F667" s="13" t="n">
         <v>16</v>
@@ -21380,7 +21380,7 @@
         </is>
       </c>
       <c r="E668" s="13" t="n">
-        <v>12759</v>
+        <v>12717</v>
       </c>
       <c r="F668" s="13" t="n">
         <v>17</v>
@@ -21408,7 +21408,7 @@
         </is>
       </c>
       <c r="E669" s="13" t="n">
-        <v>12779</v>
+        <v>12737</v>
       </c>
       <c r="F669" s="13" t="n">
         <v>17</v>
@@ -21436,7 +21436,7 @@
         </is>
       </c>
       <c r="E670" s="13" t="n">
-        <v>12799</v>
+        <v>12757</v>
       </c>
       <c r="F670" s="13" t="n">
         <v>10</v>
@@ -21464,7 +21464,7 @@
         </is>
       </c>
       <c r="E671" s="13" t="n">
-        <v>12812</v>
+        <v>12770</v>
       </c>
       <c r="F671" s="13" t="n">
         <v>16</v>
@@ -21492,7 +21492,7 @@
         </is>
       </c>
       <c r="E672" s="13" t="n">
-        <v>12831</v>
+        <v>12789</v>
       </c>
       <c r="F672" s="13" t="n">
         <v>17</v>
@@ -21520,7 +21520,7 @@
         </is>
       </c>
       <c r="E673" s="13" t="n">
-        <v>12851</v>
+        <v>12809</v>
       </c>
       <c r="F673" s="13" t="n">
         <v>14</v>
@@ -21548,7 +21548,7 @@
         </is>
       </c>
       <c r="E674" s="13" t="n">
-        <v>12868</v>
+        <v>12826</v>
       </c>
       <c r="F674" s="13" t="n">
         <v>18</v>
@@ -21576,7 +21576,7 @@
         </is>
       </c>
       <c r="E675" s="13" t="n">
-        <v>12889</v>
+        <v>12847</v>
       </c>
       <c r="F675" s="13" t="n">
         <v>17</v>
@@ -21604,7 +21604,7 @@
         </is>
       </c>
       <c r="E676" s="13" t="n">
-        <v>12909</v>
+        <v>12867</v>
       </c>
       <c r="F676" s="13" t="n">
         <v>15</v>
@@ -21632,7 +21632,7 @@
         </is>
       </c>
       <c r="E677" s="13" t="n">
-        <v>12927</v>
+        <v>12885</v>
       </c>
       <c r="F677" s="13" t="n">
         <v>8</v>
@@ -21660,7 +21660,7 @@
         </is>
       </c>
       <c r="E678" s="13" t="n">
-        <v>12937</v>
+        <v>12895</v>
       </c>
       <c r="F678" s="13" t="n">
         <v>14</v>
@@ -21688,7 +21688,7 @@
         </is>
       </c>
       <c r="E679" s="13" t="n">
-        <v>12954</v>
+        <v>12912</v>
       </c>
       <c r="F679" s="13" t="n">
         <v>16</v>
@@ -21716,7 +21716,7 @@
         </is>
       </c>
       <c r="E680" s="13" t="n">
-        <v>12974</v>
+        <v>12932</v>
       </c>
       <c r="F680" s="13" t="n">
         <v>17</v>
@@ -21744,7 +21744,7 @@
         </is>
       </c>
       <c r="E681" s="13" t="n">
-        <v>12994</v>
+        <v>12952</v>
       </c>
       <c r="F681" s="13" t="n">
         <v>16</v>
@@ -21772,7 +21772,7 @@
         </is>
       </c>
       <c r="E682" s="13" t="n">
-        <v>13014</v>
+        <v>12972</v>
       </c>
       <c r="F682" s="13" t="n">
         <v>7</v>
@@ -21800,7 +21800,7 @@
         </is>
       </c>
       <c r="E683" s="13" t="n">
-        <v>13023</v>
+        <v>12981</v>
       </c>
       <c r="F683" s="13" t="n">
         <v>9</v>
@@ -21828,7 +21828,7 @@
         </is>
       </c>
       <c r="E684" s="13" t="n">
-        <v>13035</v>
+        <v>12993</v>
       </c>
       <c r="F684" s="13" t="n">
         <v>10</v>
@@ -21856,7 +21856,7 @@
         </is>
       </c>
       <c r="E685" s="13" t="n">
-        <v>13047</v>
+        <v>13005</v>
       </c>
       <c r="F685" s="13" t="n">
         <v>27</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="E686" s="13" t="n">
-        <v>13078</v>
+        <v>13036</v>
       </c>
       <c r="F686" s="13" t="n">
         <v>17</v>
@@ -21912,7 +21912,7 @@
         </is>
       </c>
       <c r="E687" s="13" t="n">
-        <v>13098</v>
+        <v>13056</v>
       </c>
       <c r="F687" s="13" t="n">
         <v>18</v>
@@ -21940,7 +21940,7 @@
         </is>
       </c>
       <c r="E688" s="13" t="n">
-        <v>13119</v>
+        <v>13077</v>
       </c>
       <c r="F688" s="13" t="n">
         <v>18</v>
@@ -21968,7 +21968,7 @@
         </is>
       </c>
       <c r="E689" s="13" t="n">
-        <v>13140</v>
+        <v>13098</v>
       </c>
       <c r="F689" s="13" t="n">
         <v>11</v>
@@ -21996,7 +21996,7 @@
         </is>
       </c>
       <c r="E690" s="13" t="n">
-        <v>13153</v>
+        <v>13111</v>
       </c>
       <c r="F690" s="13" t="n">
         <v>18</v>
@@ -22024,7 +22024,7 @@
         </is>
       </c>
       <c r="E691" s="13" t="n">
-        <v>13174</v>
+        <v>13132</v>
       </c>
       <c r="F691" s="13" t="n">
         <v>9</v>
@@ -22052,7 +22052,7 @@
         </is>
       </c>
       <c r="E692" s="13" t="n">
-        <v>13186</v>
+        <v>13144</v>
       </c>
       <c r="F692" s="13" t="n">
         <v>10</v>
@@ -22080,7 +22080,7 @@
         </is>
       </c>
       <c r="E693" s="13" t="n">
-        <v>13198</v>
+        <v>13156</v>
       </c>
       <c r="F693" s="13" t="n">
         <v>10</v>
@@ -22108,7 +22108,7 @@
         </is>
       </c>
       <c r="E694" s="13" t="n">
-        <v>13211</v>
+        <v>13169</v>
       </c>
       <c r="F694" s="13" t="n">
         <v>21</v>
@@ -22136,7 +22136,7 @@
         </is>
       </c>
       <c r="E695" s="13" t="n">
-        <v>13235</v>
+        <v>13193</v>
       </c>
       <c r="F695" s="13" t="n">
         <v>11</v>
@@ -22164,7 +22164,7 @@
         </is>
       </c>
       <c r="E696" s="13" t="n">
-        <v>13249</v>
+        <v>13207</v>
       </c>
       <c r="F696" s="13" t="n">
         <v>9</v>
@@ -22192,7 +22192,7 @@
         </is>
       </c>
       <c r="E697" s="13" t="n">
-        <v>13260</v>
+        <v>13218</v>
       </c>
       <c r="F697" s="13" t="n">
         <v>10</v>
@@ -22220,7 +22220,7 @@
         </is>
       </c>
       <c r="E698" s="13" t="n">
-        <v>13273</v>
+        <v>13231</v>
       </c>
       <c r="F698" s="13" t="n">
         <v>10</v>
@@ -22248,7 +22248,7 @@
         </is>
       </c>
       <c r="E699" s="13" t="n">
-        <v>13286</v>
+        <v>13244</v>
       </c>
       <c r="F699" s="13" t="n">
         <v>29</v>
@@ -22276,7 +22276,7 @@
         </is>
       </c>
       <c r="E700" s="13" t="n">
-        <v>13318</v>
+        <v>13276</v>
       </c>
       <c r="F700" s="13" t="n">
         <v>16</v>
@@ -22304,7 +22304,7 @@
         </is>
       </c>
       <c r="E701" s="13" t="n">
-        <v>13337</v>
+        <v>13295</v>
       </c>
       <c r="F701" s="13" t="n">
         <v>15</v>
@@ -22332,7 +22332,7 @@
         </is>
       </c>
       <c r="E702" s="13" t="n">
-        <v>13355</v>
+        <v>13313</v>
       </c>
       <c r="F702" s="13" t="n">
         <v>15</v>
@@ -22360,7 +22360,7 @@
         </is>
       </c>
       <c r="E703" s="13" t="n">
-        <v>13374</v>
+        <v>13332</v>
       </c>
       <c r="F703" s="13" t="n">
         <v>9</v>
@@ -22388,7 +22388,7 @@
         </is>
       </c>
       <c r="E704" s="13" t="n">
-        <v>13386</v>
+        <v>13344</v>
       </c>
       <c r="F704" s="13" t="n">
         <v>15</v>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="E705" s="13" t="n">
-        <v>13404</v>
+        <v>13362</v>
       </c>
       <c r="F705" s="13" t="n">
         <v>8</v>
@@ -22444,7 +22444,7 @@
         </is>
       </c>
       <c r="E706" s="13" t="n">
-        <v>13414</v>
+        <v>13372</v>
       </c>
       <c r="F706" s="13" t="n">
         <v>9</v>
@@ -22472,7 +22472,7 @@
         </is>
       </c>
       <c r="E707" s="13" t="n">
-        <v>13428</v>
+        <v>13386</v>
       </c>
       <c r="F707" s="13" t="n">
         <v>17</v>
@@ -22500,7 +22500,7 @@
         </is>
       </c>
       <c r="E708" s="13" t="n">
-        <v>13448</v>
+        <v>13406</v>
       </c>
       <c r="F708" s="13" t="n">
         <v>7</v>
@@ -22528,7 +22528,7 @@
         </is>
       </c>
       <c r="E709" s="13" t="n">
-        <v>13457</v>
+        <v>13415</v>
       </c>
       <c r="F709" s="13" t="n">
         <v>10</v>
@@ -22556,7 +22556,7 @@
         </is>
       </c>
       <c r="E710" s="13" t="n">
-        <v>13470</v>
+        <v>13428</v>
       </c>
       <c r="F710" s="13" t="n">
         <v>8</v>
@@ -22584,7 +22584,7 @@
         </is>
       </c>
       <c r="E711" s="13" t="n">
-        <v>13481</v>
+        <v>13439</v>
       </c>
       <c r="F711" s="13" t="n">
         <v>10</v>
@@ -22612,7 +22612,7 @@
         </is>
       </c>
       <c r="E712" s="13" t="n">
-        <v>13493</v>
+        <v>13451</v>
       </c>
       <c r="F712" s="13" t="n">
         <v>9</v>
@@ -22640,7 +22640,7 @@
         </is>
       </c>
       <c r="E713" s="13" t="n">
-        <v>13505</v>
+        <v>13463</v>
       </c>
       <c r="F713" s="13" t="n">
         <v>9</v>
@@ -22668,7 +22668,7 @@
         </is>
       </c>
       <c r="E714" s="13" t="n">
-        <v>13516</v>
+        <v>13474</v>
       </c>
       <c r="F714" s="13" t="n">
         <v>9</v>
@@ -22696,7 +22696,7 @@
         </is>
       </c>
       <c r="E715" s="13" t="n">
-        <v>13528</v>
+        <v>13486</v>
       </c>
       <c r="F715" s="13" t="n">
         <v>8</v>
@@ -22724,7 +22724,7 @@
         </is>
       </c>
       <c r="E716" s="13" t="n">
-        <v>13538</v>
+        <v>13496</v>
       </c>
       <c r="F716" s="13" t="n">
         <v>8</v>
@@ -22752,7 +22752,7 @@
         </is>
       </c>
       <c r="E717" s="13" t="n">
-        <v>13548</v>
+        <v>13506</v>
       </c>
       <c r="F717" s="13" t="n">
         <v>8</v>
@@ -22780,7 +22780,7 @@
         </is>
       </c>
       <c r="E718" s="13" t="n">
-        <v>13558</v>
+        <v>13516</v>
       </c>
       <c r="F718" s="13" t="n">
         <v>8</v>
@@ -22808,7 +22808,7 @@
         </is>
       </c>
       <c r="E719" s="13" t="n">
-        <v>13568</v>
+        <v>13526</v>
       </c>
       <c r="F719" s="13" t="n">
         <v>10</v>
@@ -22836,7 +22836,7 @@
         </is>
       </c>
       <c r="E720" s="13" t="n">
-        <v>13581</v>
+        <v>13539</v>
       </c>
       <c r="F720" s="13" t="n">
         <v>9</v>
@@ -22864,7 +22864,7 @@
         </is>
       </c>
       <c r="E721" s="13" t="n">
-        <v>13592</v>
+        <v>13550</v>
       </c>
       <c r="F721" s="13" t="n">
         <v>9</v>
@@ -22892,7 +22892,7 @@
         </is>
       </c>
       <c r="E722" s="13" t="n">
-        <v>13604</v>
+        <v>13562</v>
       </c>
       <c r="F722" s="13" t="n">
         <v>7</v>
@@ -22920,7 +22920,7 @@
         </is>
       </c>
       <c r="E723" s="13" t="n">
-        <v>13613</v>
+        <v>13571</v>
       </c>
       <c r="F723" s="13" t="n">
         <v>8</v>
@@ -22948,7 +22948,7 @@
         </is>
       </c>
       <c r="E724" s="13" t="n">
-        <v>13624</v>
+        <v>13582</v>
       </c>
       <c r="F724" s="13" t="n">
         <v>8</v>
@@ -22976,7 +22976,7 @@
         </is>
       </c>
       <c r="E725" s="13" t="n">
-        <v>13634</v>
+        <v>13592</v>
       </c>
       <c r="F725" s="13" t="n">
         <v>6</v>
@@ -23004,7 +23004,7 @@
         </is>
       </c>
       <c r="E726" s="13" t="n">
-        <v>13643</v>
+        <v>13601</v>
       </c>
       <c r="F726" s="13" t="n">
         <v>7</v>
@@ -23032,7 +23032,7 @@
         </is>
       </c>
       <c r="E727" s="13" t="n">
-        <v>13651</v>
+        <v>13609</v>
       </c>
       <c r="F727" s="13" t="n">
         <v>16</v>
@@ -23060,7 +23060,7 @@
         </is>
       </c>
       <c r="E728" s="13" t="n">
-        <v>13670</v>
+        <v>13628</v>
       </c>
       <c r="F728" s="13" t="n">
         <v>8</v>
@@ -23088,7 +23088,7 @@
         </is>
       </c>
       <c r="E729" s="13" t="n">
-        <v>13680</v>
+        <v>13638</v>
       </c>
       <c r="F729" s="13" t="n">
         <v>8</v>
@@ -23116,7 +23116,7 @@
         </is>
       </c>
       <c r="E730" s="13" t="n">
-        <v>13690</v>
+        <v>13648</v>
       </c>
       <c r="F730" s="13" t="n">
         <v>11</v>
@@ -23144,7 +23144,7 @@
         </is>
       </c>
       <c r="E731" s="13" t="n">
-        <v>13704</v>
+        <v>13662</v>
       </c>
       <c r="F731" s="13" t="n">
         <v>8</v>
@@ -23172,7 +23172,7 @@
         </is>
       </c>
       <c r="E732" s="13" t="n">
-        <v>13714</v>
+        <v>13672</v>
       </c>
       <c r="F732" s="13" t="n">
         <v>9</v>
@@ -23200,7 +23200,7 @@
         </is>
       </c>
       <c r="E733" s="13" t="n">
-        <v>13726</v>
+        <v>13684</v>
       </c>
       <c r="F733" s="13" t="n">
         <v>8</v>
@@ -23228,7 +23228,7 @@
         </is>
       </c>
       <c r="E734" s="13" t="n">
-        <v>13736</v>
+        <v>13694</v>
       </c>
       <c r="F734" s="13" t="n">
         <v>8</v>
@@ -23256,7 +23256,7 @@
         </is>
       </c>
       <c r="E735" s="13" t="n">
-        <v>13747</v>
+        <v>13705</v>
       </c>
       <c r="F735" s="13" t="n">
         <v>8</v>
@@ -23284,7 +23284,7 @@
         </is>
       </c>
       <c r="E736" s="13" t="n">
-        <v>13757</v>
+        <v>13715</v>
       </c>
       <c r="F736" s="13" t="n">
         <v>8</v>
@@ -23312,7 +23312,7 @@
         </is>
       </c>
       <c r="E737" s="13" t="n">
-        <v>13768</v>
+        <v>13726</v>
       </c>
       <c r="F737" s="13" t="n">
         <v>8</v>
@@ -23340,7 +23340,7 @@
         </is>
       </c>
       <c r="E738" s="13" t="n">
-        <v>13778</v>
+        <v>13736</v>
       </c>
       <c r="F738" s="13" t="n">
         <v>8</v>
@@ -23368,7 +23368,7 @@
         </is>
       </c>
       <c r="E739" s="13" t="n">
-        <v>13789</v>
+        <v>13747</v>
       </c>
       <c r="F739" s="13" t="n">
         <v>8</v>
@@ -23396,7 +23396,7 @@
         </is>
       </c>
       <c r="E740" s="13" t="n">
-        <v>13799</v>
+        <v>13757</v>
       </c>
       <c r="F740" s="13" t="n">
         <v>8</v>
@@ -23424,7 +23424,7 @@
         </is>
       </c>
       <c r="E741" s="13" t="n">
-        <v>13810</v>
+        <v>13768</v>
       </c>
       <c r="F741" s="13" t="n">
         <v>8</v>
@@ -23452,7 +23452,7 @@
         </is>
       </c>
       <c r="E742" s="13" t="n">
-        <v>13820</v>
+        <v>13778</v>
       </c>
       <c r="F742" s="13" t="n">
         <v>8</v>
@@ -23480,7 +23480,7 @@
         </is>
       </c>
       <c r="E743" s="13" t="n">
-        <v>13831</v>
+        <v>13789</v>
       </c>
       <c r="F743" s="13" t="n">
         <v>6</v>
@@ -23508,7 +23508,7 @@
         </is>
       </c>
       <c r="E744" s="13" t="n">
-        <v>13839</v>
+        <v>13797</v>
       </c>
       <c r="F744" s="13" t="n">
         <v>8</v>
@@ -23536,7 +23536,7 @@
         </is>
       </c>
       <c r="E745" s="13" t="n">
-        <v>13850</v>
+        <v>13808</v>
       </c>
       <c r="F745" s="13" t="n">
         <v>8</v>
@@ -23564,7 +23564,7 @@
         </is>
       </c>
       <c r="E746" s="13" t="n">
-        <v>13860</v>
+        <v>13818</v>
       </c>
       <c r="F746" s="13" t="n">
         <v>9</v>
@@ -23592,7 +23592,7 @@
         </is>
       </c>
       <c r="E747" s="13" t="n">
-        <v>13872</v>
+        <v>13830</v>
       </c>
       <c r="F747" s="13" t="n">
         <v>9</v>
@@ -23620,7 +23620,7 @@
         </is>
       </c>
       <c r="E748" s="13" t="n">
-        <v>13883</v>
+        <v>13841</v>
       </c>
       <c r="F748" s="13" t="n">
         <v>9</v>
@@ -23648,7 +23648,7 @@
         </is>
       </c>
       <c r="E749" s="13" t="n">
-        <v>13895</v>
+        <v>13853</v>
       </c>
       <c r="F749" s="13" t="n">
         <v>8</v>
@@ -23676,7 +23676,7 @@
         </is>
       </c>
       <c r="E750" s="13" t="n">
-        <v>13905</v>
+        <v>13863</v>
       </c>
       <c r="F750" s="13" t="n">
         <v>5</v>
@@ -23704,7 +23704,7 @@
         </is>
       </c>
       <c r="E751" s="13" t="n">
-        <v>13913</v>
+        <v>13871</v>
       </c>
       <c r="F751" s="13" t="n">
         <v>13</v>
@@ -23732,7 +23732,7 @@
         </is>
       </c>
       <c r="E752" s="13" t="n">
-        <v>13928</v>
+        <v>13886</v>
       </c>
       <c r="F752" s="13" t="n">
         <v>17</v>
@@ -23760,7 +23760,7 @@
         </is>
       </c>
       <c r="E753" s="13" t="n">
-        <v>13948</v>
+        <v>13906</v>
       </c>
       <c r="F753" s="13" t="n">
         <v>8</v>
@@ -23788,7 +23788,7 @@
         </is>
       </c>
       <c r="E754" s="13" t="n">
-        <v>13959</v>
+        <v>13917</v>
       </c>
       <c r="F754" s="13" t="n">
         <v>8</v>
@@ -23816,7 +23816,7 @@
         </is>
       </c>
       <c r="E755" s="13" t="n">
-        <v>13969</v>
+        <v>13927</v>
       </c>
       <c r="F755" s="13" t="n">
         <v>13</v>
@@ -23844,7 +23844,7 @@
         </is>
       </c>
       <c r="E756" s="13" t="n">
-        <v>13985</v>
+        <v>13943</v>
       </c>
       <c r="F756" s="13" t="n">
         <v>9</v>
@@ -23872,7 +23872,7 @@
         </is>
       </c>
       <c r="E757" s="13" t="n">
-        <v>13996</v>
+        <v>13954</v>
       </c>
       <c r="F757" s="13" t="n">
         <v>7</v>
@@ -23900,7 +23900,7 @@
         </is>
       </c>
       <c r="E758" s="13" t="n">
-        <v>14005</v>
+        <v>13963</v>
       </c>
       <c r="F758" s="13" t="n">
         <v>9</v>
@@ -23928,7 +23928,7 @@
         </is>
       </c>
       <c r="E759" s="13" t="n">
-        <v>14017</v>
+        <v>13975</v>
       </c>
       <c r="F759" s="13" t="n">
         <v>12</v>
@@ -23956,7 +23956,7 @@
         </is>
       </c>
       <c r="E760" s="13" t="n">
-        <v>14031</v>
+        <v>13989</v>
       </c>
       <c r="F760" s="13" t="n">
         <v>11</v>
@@ -23984,7 +23984,7 @@
         </is>
       </c>
       <c r="E761" s="13" t="n">
-        <v>14045</v>
+        <v>14003</v>
       </c>
       <c r="F761" s="13" t="n">
         <v>10</v>
@@ -24012,7 +24012,7 @@
         </is>
       </c>
       <c r="E762" s="13" t="n">
-        <v>14058</v>
+        <v>14016</v>
       </c>
       <c r="F762" s="13" t="n">
         <v>10</v>
@@ -24040,7 +24040,7 @@
         </is>
       </c>
       <c r="E763" s="13" t="n">
-        <v>14070</v>
+        <v>14028</v>
       </c>
       <c r="F763" s="13" t="n">
         <v>11</v>
@@ -24068,7 +24068,7 @@
         </is>
       </c>
       <c r="E764" s="13" t="n">
-        <v>14084</v>
+        <v>14042</v>
       </c>
       <c r="F764" s="13" t="n">
         <v>11</v>
@@ -24096,7 +24096,7 @@
         </is>
       </c>
       <c r="E765" s="13" t="n">
-        <v>14098</v>
+        <v>14056</v>
       </c>
       <c r="F765" s="13" t="n">
         <v>9</v>
@@ -24124,7 +24124,7 @@
         </is>
       </c>
       <c r="E766" s="13" t="n">
-        <v>14109</v>
+        <v>14067</v>
       </c>
       <c r="F766" s="13" t="n">
         <v>11</v>
@@ -24152,7 +24152,7 @@
         </is>
       </c>
       <c r="E767" s="13" t="n">
-        <v>14122</v>
+        <v>14080</v>
       </c>
       <c r="F767" s="13" t="n">
         <v>10</v>
@@ -24180,7 +24180,7 @@
         </is>
       </c>
       <c r="E768" s="13" t="n">
-        <v>14135</v>
+        <v>14093</v>
       </c>
       <c r="F768" s="13" t="n">
         <v>9</v>
@@ -24208,7 +24208,7 @@
         </is>
       </c>
       <c r="E769" s="13" t="n">
-        <v>14146</v>
+        <v>14104</v>
       </c>
       <c r="F769" s="13" t="n">
         <v>9</v>
@@ -24236,7 +24236,7 @@
         </is>
       </c>
       <c r="E770" s="13" t="n">
-        <v>14158</v>
+        <v>14116</v>
       </c>
       <c r="F770" s="13" t="n">
         <v>10</v>
@@ -24264,7 +24264,7 @@
         </is>
       </c>
       <c r="E771" s="13" t="n">
-        <v>14171</v>
+        <v>14129</v>
       </c>
       <c r="F771" s="13" t="n">
         <v>15</v>
@@ -24292,7 +24292,7 @@
         </is>
       </c>
       <c r="E772" s="13" t="n">
-        <v>14188</v>
+        <v>14146</v>
       </c>
       <c r="F772" s="13" t="n">
         <v>16</v>
@@ -24320,7 +24320,7 @@
         </is>
       </c>
       <c r="E773" s="13" t="n">
-        <v>14207</v>
+        <v>14165</v>
       </c>
       <c r="F773" s="13" t="n">
         <v>10</v>
@@ -24348,7 +24348,7 @@
         </is>
       </c>
       <c r="E774" s="13" t="n">
-        <v>14219</v>
+        <v>14177</v>
       </c>
       <c r="F774" s="13" t="n">
         <v>9</v>
@@ -24376,7 +24376,7 @@
         </is>
       </c>
       <c r="E775" s="13" t="n">
-        <v>14231</v>
+        <v>14189</v>
       </c>
       <c r="F775" s="13" t="n">
         <v>8</v>
@@ -24404,7 +24404,7 @@
         </is>
       </c>
       <c r="E776" s="13" t="n">
-        <v>14241</v>
+        <v>14199</v>
       </c>
       <c r="F776" s="13" t="n">
         <v>8</v>
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="E777" s="13" t="n">
-        <v>14252</v>
+        <v>14210</v>
       </c>
       <c r="F777" s="13" t="n">
         <v>8</v>
@@ -24460,7 +24460,7 @@
         </is>
       </c>
       <c r="E778" s="13" t="n">
-        <v>14262</v>
+        <v>14220</v>
       </c>
       <c r="F778" s="13" t="n">
         <v>9</v>
@@ -24488,7 +24488,7 @@
         </is>
       </c>
       <c r="E779" s="13" t="n">
-        <v>14274</v>
+        <v>14232</v>
       </c>
       <c r="F779" s="13" t="n">
         <v>8</v>
@@ -24516,7 +24516,7 @@
         </is>
       </c>
       <c r="E780" s="13" t="n">
-        <v>14284</v>
+        <v>14242</v>
       </c>
       <c r="F780" s="13" t="n">
         <v>8</v>
@@ -24544,7 +24544,7 @@
         </is>
       </c>
       <c r="E781" s="13" t="n">
-        <v>14295</v>
+        <v>14253</v>
       </c>
       <c r="F781" s="13" t="n">
         <v>8</v>
@@ -24572,7 +24572,7 @@
         </is>
       </c>
       <c r="E782" s="13" t="n">
-        <v>14305</v>
+        <v>14263</v>
       </c>
       <c r="F782" s="13" t="n">
         <v>8</v>
@@ -24600,7 +24600,7 @@
         </is>
       </c>
       <c r="E783" s="13" t="n">
-        <v>14316</v>
+        <v>14274</v>
       </c>
       <c r="F783" s="13" t="n">
         <v>8</v>
@@ -24628,7 +24628,7 @@
         </is>
       </c>
       <c r="E784" s="13" t="n">
-        <v>14326</v>
+        <v>14284</v>
       </c>
       <c r="F784" s="13" t="n">
         <v>8</v>
@@ -24656,7 +24656,7 @@
         </is>
       </c>
       <c r="E785" s="13" t="n">
-        <v>14337</v>
+        <v>14295</v>
       </c>
       <c r="F785" s="13" t="n">
         <v>8</v>
@@ -24684,7 +24684,7 @@
         </is>
       </c>
       <c r="E786" s="13" t="n">
-        <v>14347</v>
+        <v>14305</v>
       </c>
       <c r="F786" s="13" t="n">
         <v>8</v>
@@ -24712,7 +24712,7 @@
         </is>
       </c>
       <c r="E787" s="13" t="n">
-        <v>14358</v>
+        <v>14316</v>
       </c>
       <c r="F787" s="13" t="n">
         <v>7</v>
@@ -24740,7 +24740,7 @@
         </is>
       </c>
       <c r="E788" s="13" t="n">
-        <v>14367</v>
+        <v>14325</v>
       </c>
       <c r="F788" s="13" t="n">
         <v>8</v>
@@ -24768,7 +24768,7 @@
         </is>
       </c>
       <c r="E789" s="13" t="n">
-        <v>14378</v>
+        <v>14336</v>
       </c>
       <c r="F789" s="13" t="n">
         <v>7</v>
@@ -24796,7 +24796,7 @@
         </is>
       </c>
       <c r="E790" s="13" t="n">
-        <v>14387</v>
+        <v>14345</v>
       </c>
       <c r="F790" s="13" t="n">
         <v>6</v>
@@ -24824,7 +24824,7 @@
         </is>
       </c>
       <c r="E791" s="13" t="n">
-        <v>14396</v>
+        <v>14354</v>
       </c>
       <c r="F791" s="13" t="n">
         <v>8</v>
@@ -24852,7 +24852,7 @@
         </is>
       </c>
       <c r="E792" s="13" t="n">
-        <v>14406</v>
+        <v>14364</v>
       </c>
       <c r="F792" s="13" t="n">
         <v>15</v>
@@ -24880,7 +24880,7 @@
         </is>
       </c>
       <c r="E793" s="13" t="n">
-        <v>14424</v>
+        <v>14382</v>
       </c>
       <c r="F793" s="13" t="n">
         <v>9</v>
@@ -24908,7 +24908,7 @@
         </is>
       </c>
       <c r="E794" s="13" t="n">
-        <v>14436</v>
+        <v>14394</v>
       </c>
       <c r="F794" s="13" t="n">
         <v>9</v>
@@ -24936,7 +24936,7 @@
         </is>
       </c>
       <c r="E795" s="13" t="n">
-        <v>14447</v>
+        <v>14405</v>
       </c>
       <c r="F795" s="13" t="n">
         <v>9</v>
@@ -24964,7 +24964,7 @@
         </is>
       </c>
       <c r="E796" s="13" t="n">
-        <v>14459</v>
+        <v>14417</v>
       </c>
       <c r="F796" s="13" t="n">
         <v>8</v>
@@ -24992,7 +24992,7 @@
         </is>
       </c>
       <c r="E797" s="13" t="n">
-        <v>14469</v>
+        <v>14427</v>
       </c>
       <c r="F797" s="13" t="n">
         <v>8</v>
@@ -25020,7 +25020,7 @@
         </is>
       </c>
       <c r="E798" s="13" t="n">
-        <v>14480</v>
+        <v>14438</v>
       </c>
       <c r="F798" s="13" t="n">
         <v>9</v>
@@ -25048,7 +25048,7 @@
         </is>
       </c>
       <c r="E799" s="13" t="n">
-        <v>14491</v>
+        <v>14449</v>
       </c>
       <c r="F799" s="13" t="n">
         <v>9</v>
@@ -25076,7 +25076,7 @@
         </is>
       </c>
       <c r="E800" s="13" t="n">
-        <v>14503</v>
+        <v>14461</v>
       </c>
       <c r="F800" s="13" t="n">
         <v>8</v>
@@ -25104,7 +25104,7 @@
         </is>
       </c>
       <c r="E801" s="13" t="n">
-        <v>14513</v>
+        <v>14471</v>
       </c>
       <c r="F801" s="13" t="n">
         <v>9</v>
@@ -25132,7 +25132,7 @@
         </is>
       </c>
       <c r="E802" s="13" t="n">
-        <v>14525</v>
+        <v>14483</v>
       </c>
       <c r="F802" s="13" t="n">
         <v>9</v>
@@ -25160,7 +25160,7 @@
         </is>
       </c>
       <c r="E803" s="13" t="n">
-        <v>14536</v>
+        <v>14494</v>
       </c>
       <c r="F803" s="13" t="n">
         <v>9</v>
@@ -25188,7 +25188,7 @@
         </is>
       </c>
       <c r="E804" s="13" t="n">
-        <v>14548</v>
+        <v>14506</v>
       </c>
       <c r="F804" s="13" t="n">
         <v>9</v>
@@ -25216,7 +25216,7 @@
         </is>
       </c>
       <c r="E805" s="13" t="n">
-        <v>14559</v>
+        <v>14517</v>
       </c>
       <c r="F805" s="13" t="n">
         <v>8</v>
@@ -25244,7 +25244,7 @@
         </is>
       </c>
       <c r="E806" s="13" t="n">
-        <v>14570</v>
+        <v>14528</v>
       </c>
       <c r="F806" s="13" t="n">
         <v>7</v>
@@ -25272,7 +25272,7 @@
         </is>
       </c>
       <c r="E807" s="13" t="n">
-        <v>14579</v>
+        <v>14537</v>
       </c>
       <c r="F807" s="13" t="n">
         <v>7</v>
@@ -25300,7 +25300,7 @@
         </is>
       </c>
       <c r="E808" s="13" t="n">
-        <v>14589</v>
+        <v>14547</v>
       </c>
       <c r="F808" s="13" t="n">
         <v>8</v>
@@ -25328,7 +25328,7 @@
         </is>
       </c>
       <c r="E809" s="13" t="n">
-        <v>14599</v>
+        <v>14557</v>
       </c>
       <c r="F809" s="13" t="n">
         <v>9</v>
@@ -25356,7 +25356,7 @@
         </is>
       </c>
       <c r="E810" s="13" t="n">
-        <v>14611</v>
+        <v>14569</v>
       </c>
       <c r="F810" s="13" t="n">
         <v>8</v>
@@ -25384,7 +25384,7 @@
         </is>
       </c>
       <c r="E811" s="13" t="n">
-        <v>14621</v>
+        <v>14579</v>
       </c>
       <c r="F811" s="13" t="n">
         <v>10</v>
@@ -25412,7 +25412,7 @@
         </is>
       </c>
       <c r="E812" s="13" t="n">
-        <v>14634</v>
+        <v>14592</v>
       </c>
       <c r="F812" s="13" t="n">
         <v>9</v>
@@ -25440,7 +25440,7 @@
         </is>
       </c>
       <c r="E813" s="13" t="n">
-        <v>14645</v>
+        <v>14603</v>
       </c>
       <c r="F813" s="13" t="n">
         <v>8</v>
@@ -25468,7 +25468,7 @@
         </is>
       </c>
       <c r="E814" s="13" t="n">
-        <v>14656</v>
+        <v>14614</v>
       </c>
       <c r="F814" s="13" t="n">
         <v>8</v>
@@ -25496,7 +25496,7 @@
         </is>
       </c>
       <c r="E815" s="13" t="n">
-        <v>14666</v>
+        <v>14624</v>
       </c>
       <c r="F815" s="13" t="n">
         <v>7</v>
@@ -25524,7 +25524,7 @@
         </is>
       </c>
       <c r="E816" s="13" t="n">
-        <v>14676</v>
+        <v>14634</v>
       </c>
       <c r="F816" s="13" t="n">
         <v>9</v>
@@ -25552,7 +25552,7 @@
         </is>
       </c>
       <c r="E817" s="13" t="n">
-        <v>14687</v>
+        <v>14645</v>
       </c>
       <c r="F817" s="13" t="n">
         <v>9</v>
@@ -25580,7 +25580,7 @@
         </is>
       </c>
       <c r="E818" s="13" t="n">
-        <v>14699</v>
+        <v>14657</v>
       </c>
       <c r="F818" s="13" t="n">
         <v>8</v>
@@ -25608,7 +25608,7 @@
         </is>
       </c>
       <c r="E819" s="13" t="n">
-        <v>14709</v>
+        <v>14667</v>
       </c>
       <c r="F819" s="13" t="n">
         <v>8</v>
@@ -25636,7 +25636,7 @@
         </is>
       </c>
       <c r="E820" s="13" t="n">
-        <v>14720</v>
+        <v>14678</v>
       </c>
       <c r="F820" s="13" t="n">
         <v>9</v>
@@ -25664,7 +25664,7 @@
         </is>
       </c>
       <c r="E821" s="13" t="n">
-        <v>14731</v>
+        <v>14689</v>
       </c>
       <c r="F821" s="13" t="n">
         <v>8</v>
@@ -25692,7 +25692,7 @@
         </is>
       </c>
       <c r="E822" s="13" t="n">
-        <v>14742</v>
+        <v>14700</v>
       </c>
       <c r="F822" s="13" t="n">
         <v>8</v>
@@ -25720,7 +25720,7 @@
         </is>
       </c>
       <c r="E823" s="13" t="n">
-        <v>14752</v>
+        <v>14710</v>
       </c>
       <c r="F823" s="13" t="n">
         <v>8</v>
@@ -25748,7 +25748,7 @@
         </is>
       </c>
       <c r="E824" s="13" t="n">
-        <v>14763</v>
+        <v>14721</v>
       </c>
       <c r="F824" s="13" t="n">
         <v>8</v>
@@ -25776,7 +25776,7 @@
         </is>
       </c>
       <c r="E825" s="13" t="n">
-        <v>14773</v>
+        <v>14731</v>
       </c>
       <c r="F825" s="13" t="n">
         <v>8</v>
@@ -25804,7 +25804,7 @@
         </is>
       </c>
       <c r="E826" s="13" t="n">
-        <v>14784</v>
+        <v>14742</v>
       </c>
       <c r="F826" s="13" t="n">
         <v>8</v>
@@ -25832,7 +25832,7 @@
         </is>
       </c>
       <c r="E827" s="13" t="n">
-        <v>14794</v>
+        <v>14752</v>
       </c>
       <c r="F827" s="13" t="n">
         <v>6</v>
@@ -25860,7 +25860,7 @@
         </is>
       </c>
       <c r="E828" s="13" t="n">
-        <v>14803</v>
+        <v>14761</v>
       </c>
       <c r="F828" s="13" t="n">
         <v>7</v>
@@ -25888,7 +25888,7 @@
         </is>
       </c>
       <c r="E829" s="13" t="n">
-        <v>14812</v>
+        <v>14770</v>
       </c>
       <c r="F829" s="13" t="n">
         <v>8</v>
@@ -25916,7 +25916,7 @@
         </is>
       </c>
       <c r="E830" s="13" t="n">
-        <v>14823</v>
+        <v>14781</v>
       </c>
       <c r="F830" s="13" t="n">
         <v>8</v>
@@ -25944,7 +25944,7 @@
         </is>
       </c>
       <c r="E831" s="13" t="n">
-        <v>14833</v>
+        <v>14791</v>
       </c>
       <c r="F831" s="13" t="n">
         <v>9</v>
@@ -25972,7 +25972,7 @@
         </is>
       </c>
       <c r="E832" s="13" t="n">
-        <v>14845</v>
+        <v>14803</v>
       </c>
       <c r="F832" s="13" t="n">
         <v>7</v>
@@ -26000,7 +26000,7 @@
         </is>
       </c>
       <c r="E833" s="13" t="n">
-        <v>14854</v>
+        <v>14812</v>
       </c>
       <c r="F833" s="13" t="n">
         <v>9</v>
@@ -26028,7 +26028,7 @@
         </is>
       </c>
       <c r="E834" s="13" t="n">
-        <v>14866</v>
+        <v>14824</v>
       </c>
       <c r="F834" s="13" t="n">
         <v>8</v>
@@ -26056,7 +26056,7 @@
         </is>
       </c>
       <c r="E835" s="13" t="n">
-        <v>14876</v>
+        <v>14834</v>
       </c>
       <c r="F835" s="13" t="n">
         <v>6</v>
@@ -26084,7 +26084,7 @@
         </is>
       </c>
       <c r="E836" s="13" t="n">
-        <v>14885</v>
+        <v>14843</v>
       </c>
       <c r="F836" s="13" t="n">
         <v>8</v>
@@ -26112,7 +26112,7 @@
         </is>
       </c>
       <c r="E837" s="13" t="n">
-        <v>14895</v>
+        <v>14853</v>
       </c>
       <c r="F837" s="13" t="n">
         <v>9</v>
@@ -26140,7 +26140,7 @@
         </is>
       </c>
       <c r="E838" s="13" t="n">
-        <v>14907</v>
+        <v>14865</v>
       </c>
       <c r="F838" s="13" t="n">
         <v>7</v>
@@ -26168,7 +26168,7 @@
         </is>
       </c>
       <c r="E839" s="13" t="n">
-        <v>14916</v>
+        <v>14874</v>
       </c>
       <c r="F839" s="13" t="n">
         <v>8</v>
@@ -26196,7 +26196,7 @@
         </is>
       </c>
       <c r="E840" s="13" t="n">
-        <v>14927</v>
+        <v>14885</v>
       </c>
       <c r="F840" s="13" t="n">
         <v>7</v>
@@ -26224,7 +26224,7 @@
         </is>
       </c>
       <c r="E841" s="13" t="n">
-        <v>14936</v>
+        <v>14894</v>
       </c>
       <c r="F841" s="13" t="n">
         <v>7</v>
@@ -26252,7 +26252,7 @@
         </is>
       </c>
       <c r="E842" s="13" t="n">
-        <v>14946</v>
+        <v>14904</v>
       </c>
       <c r="F842" s="13" t="n">
         <v>8</v>
@@ -26280,7 +26280,7 @@
         </is>
       </c>
       <c r="E843" s="13" t="n">
-        <v>14956</v>
+        <v>14914</v>
       </c>
       <c r="F843" s="13" t="n">
         <v>9</v>
@@ -26308,7 +26308,7 @@
         </is>
       </c>
       <c r="E844" s="13" t="n">
-        <v>14968</v>
+        <v>14926</v>
       </c>
       <c r="F844" s="13" t="n">
         <v>8</v>
@@ -26336,7 +26336,7 @@
         </is>
       </c>
       <c r="E845" s="13" t="n">
-        <v>14978</v>
+        <v>14936</v>
       </c>
       <c r="F845" s="13" t="n">
         <v>6</v>
@@ -26364,7 +26364,7 @@
         </is>
       </c>
       <c r="E846" s="13" t="n">
-        <v>14987</v>
+        <v>14945</v>
       </c>
       <c r="F846" s="13" t="n">
         <v>7</v>
@@ -26392,7 +26392,7 @@
         </is>
       </c>
       <c r="E847" s="13" t="n">
-        <v>14996</v>
+        <v>14954</v>
       </c>
       <c r="F847" s="13" t="n">
         <v>8</v>
@@ -26420,7 +26420,7 @@
         </is>
       </c>
       <c r="E848" s="13" t="n">
-        <v>15006</v>
+        <v>14964</v>
       </c>
       <c r="F848" s="13" t="n">
         <v>7</v>
@@ -26448,7 +26448,7 @@
         </is>
       </c>
       <c r="E849" s="13" t="n">
-        <v>15015</v>
+        <v>14973</v>
       </c>
       <c r="F849" s="13" t="n">
         <v>8</v>
@@ -26476,7 +26476,7 @@
         </is>
       </c>
       <c r="E850" s="13" t="n">
-        <v>15025</v>
+        <v>14983</v>
       </c>
       <c r="F850" s="13" t="n">
         <v>8</v>
@@ -26504,7 +26504,7 @@
         </is>
       </c>
       <c r="E851" s="13" t="n">
-        <v>15036</v>
+        <v>14994</v>
       </c>
       <c r="F851" s="13" t="n">
         <v>7</v>
@@ -26532,7 +26532,7 @@
         </is>
       </c>
       <c r="E852" s="13" t="n">
-        <v>15045</v>
+        <v>15003</v>
       </c>
       <c r="F852" s="13" t="n">
         <v>7</v>
@@ -26560,7 +26560,7 @@
         </is>
       </c>
       <c r="E853" s="13" t="n">
-        <v>15055</v>
+        <v>15013</v>
       </c>
       <c r="F853" s="13" t="n">
         <v>7</v>
@@ -26588,7 +26588,7 @@
         </is>
       </c>
       <c r="E854" s="13" t="n">
-        <v>15064</v>
+        <v>15022</v>
       </c>
       <c r="F854" s="13" t="n">
         <v>8</v>
@@ -26616,7 +26616,7 @@
         </is>
       </c>
       <c r="E855" s="13" t="n">
-        <v>15075</v>
+        <v>15033</v>
       </c>
       <c r="F855" s="13" t="n">
         <v>8</v>
@@ -26644,7 +26644,7 @@
         </is>
       </c>
       <c r="E856" s="13" t="n">
-        <v>15085</v>
+        <v>15043</v>
       </c>
       <c r="F856" s="13" t="n">
         <v>8</v>
@@ -26672,7 +26672,7 @@
         </is>
       </c>
       <c r="E857" s="13" t="n">
-        <v>15096</v>
+        <v>15054</v>
       </c>
       <c r="F857" s="13" t="n">
         <v>8</v>
@@ -26700,7 +26700,7 @@
         </is>
       </c>
       <c r="E858" s="13" t="n">
-        <v>15106</v>
+        <v>15064</v>
       </c>
       <c r="F858" s="13" t="n">
         <v>9</v>
@@ -26728,7 +26728,7 @@
         </is>
       </c>
       <c r="E859" s="13" t="n">
-        <v>15118</v>
+        <v>15076</v>
       </c>
       <c r="F859" s="13" t="n">
         <v>9</v>
@@ -26756,7 +26756,7 @@
         </is>
       </c>
       <c r="E860" s="13" t="n">
-        <v>15129</v>
+        <v>15087</v>
       </c>
       <c r="F860" s="13" t="n">
         <v>9</v>
@@ -26784,7 +26784,7 @@
         </is>
       </c>
       <c r="E861" s="13" t="n">
-        <v>15141</v>
+        <v>15099</v>
       </c>
       <c r="F861" s="13" t="n">
         <v>9</v>
@@ -26812,7 +26812,7 @@
         </is>
       </c>
       <c r="E862" s="13" t="n">
-        <v>15152</v>
+        <v>15110</v>
       </c>
       <c r="F862" s="13" t="n">
         <v>8</v>
@@ -26840,7 +26840,7 @@
         </is>
       </c>
       <c r="E863" s="13" t="n">
-        <v>15163</v>
+        <v>15121</v>
       </c>
       <c r="F863" s="13" t="n">
         <v>7</v>
@@ -26868,7 +26868,7 @@
         </is>
       </c>
       <c r="E864" s="13" t="n">
-        <v>15172</v>
+        <v>15130</v>
       </c>
       <c r="F864" s="13" t="n">
         <v>8</v>
@@ -26896,7 +26896,7 @@
         </is>
       </c>
       <c r="E865" s="13" t="n">
-        <v>15183</v>
+        <v>15141</v>
       </c>
       <c r="F865" s="13" t="n">
         <v>7</v>
@@ -26924,7 +26924,7 @@
         </is>
       </c>
       <c r="E866" s="13" t="n">
-        <v>15192</v>
+        <v>15150</v>
       </c>
       <c r="F866" s="13" t="n">
         <v>7</v>
@@ -26952,7 +26952,7 @@
         </is>
       </c>
       <c r="E867" s="13" t="n">
-        <v>15201</v>
+        <v>15159</v>
       </c>
       <c r="F867" s="13" t="n">
         <v>6</v>
@@ -26980,7 +26980,7 @@
         </is>
       </c>
       <c r="E868" s="13" t="n">
-        <v>15210</v>
+        <v>15168</v>
       </c>
       <c r="F868" s="13" t="n">
         <v>5</v>
@@ -27008,7 +27008,7 @@
         </is>
       </c>
       <c r="E869" s="13" t="n">
-        <v>15217</v>
+        <v>15175</v>
       </c>
       <c r="F869" s="13" t="n">
         <v>7</v>
@@ -27036,7 +27036,7 @@
         </is>
       </c>
       <c r="E870" s="13" t="n">
-        <v>15226</v>
+        <v>15184</v>
       </c>
       <c r="F870" s="13" t="n">
         <v>6</v>
@@ -27064,7 +27064,7 @@
         </is>
       </c>
       <c r="E871" s="13" t="n">
-        <v>15235</v>
+        <v>15193</v>
       </c>
       <c r="F871" s="13" t="n">
         <v>7</v>
@@ -27092,7 +27092,7 @@
         </is>
       </c>
       <c r="E872" s="13" t="n">
-        <v>15244</v>
+        <v>15202</v>
       </c>
       <c r="F872" s="13" t="n">
         <v>8</v>
@@ -27120,7 +27120,7 @@
         </is>
       </c>
       <c r="E873" s="13" t="n">
-        <v>15255</v>
+        <v>15213</v>
       </c>
       <c r="F873" s="13" t="n">
         <v>7</v>
@@ -27148,7 +27148,7 @@
         </is>
       </c>
       <c r="E874" s="13" t="n">
-        <v>15264</v>
+        <v>15222</v>
       </c>
       <c r="F874" s="13" t="n">
         <v>14</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="E875" s="13" t="n">
-        <v>15281</v>
+        <v>15239</v>
       </c>
       <c r="F875" s="13" t="n">
         <v>7</v>
@@ -27204,7 +27204,7 @@
         </is>
       </c>
       <c r="E876" s="13" t="n">
-        <v>15290</v>
+        <v>15248</v>
       </c>
       <c r="F876" s="13" t="n">
         <v>8</v>
@@ -27232,7 +27232,7 @@
         </is>
       </c>
       <c r="E877" s="13" t="n">
-        <v>15301</v>
+        <v>15259</v>
       </c>
       <c r="F877" s="13" t="n">
         <v>6</v>
@@ -27260,7 +27260,7 @@
         </is>
       </c>
       <c r="E878" s="13" t="n">
-        <v>15309</v>
+        <v>15267</v>
       </c>
       <c r="F878" s="13" t="n">
         <v>7</v>
@@ -27288,7 +27288,7 @@
         </is>
       </c>
       <c r="E879" s="13" t="n">
-        <v>15318</v>
+        <v>15276</v>
       </c>
       <c r="F879" s="13" t="n">
         <v>5</v>
@@ -27316,7 +27316,7 @@
         </is>
       </c>
       <c r="E880" s="13" t="n">
-        <v>15326</v>
+        <v>15284</v>
       </c>
       <c r="F880" s="13" t="n">
         <v>7</v>
@@ -27344,7 +27344,7 @@
         </is>
       </c>
       <c r="E881" s="13" t="n">
-        <v>15335</v>
+        <v>15293</v>
       </c>
       <c r="F881" s="13" t="n">
         <v>7</v>
@@ -27372,7 +27372,7 @@
         </is>
       </c>
       <c r="E882" s="13" t="n">
-        <v>15345</v>
+        <v>15303</v>
       </c>
       <c r="F882" s="13" t="n">
         <v>8</v>
@@ -27400,7 +27400,7 @@
         </is>
       </c>
       <c r="E883" s="13" t="n">
-        <v>15355</v>
+        <v>15313</v>
       </c>
       <c r="F883" s="13" t="n">
         <v>8</v>
@@ -27428,7 +27428,7 @@
         </is>
       </c>
       <c r="E884" s="13" t="n">
-        <v>15366</v>
+        <v>15324</v>
       </c>
       <c r="F884" s="13" t="n">
         <v>7</v>
@@ -27456,7 +27456,7 @@
         </is>
       </c>
       <c r="E885" s="13" t="n">
-        <v>15375</v>
+        <v>15333</v>
       </c>
       <c r="F885" s="13" t="n">
         <v>7</v>
@@ -27484,7 +27484,7 @@
         </is>
       </c>
       <c r="E886" s="13" t="n">
-        <v>15384</v>
+        <v>15342</v>
       </c>
       <c r="F886" s="13" t="n">
         <v>7</v>
@@ -27512,7 +27512,7 @@
         </is>
       </c>
       <c r="E887" s="13" t="n">
-        <v>15393</v>
+        <v>15351</v>
       </c>
       <c r="F887" s="13" t="n">
         <v>5</v>
@@ -27540,7 +27540,7 @@
         </is>
       </c>
       <c r="E888" s="13" t="n">
-        <v>15400</v>
+        <v>15358</v>
       </c>
       <c r="F888" s="13" t="n">
         <v>15</v>
@@ -27568,7 +27568,7 @@
         </is>
       </c>
       <c r="E889" s="13" t="n">
-        <v>15418</v>
+        <v>15376</v>
       </c>
       <c r="F889" s="13" t="n">
         <v>15</v>
@@ -27596,7 +27596,7 @@
         </is>
       </c>
       <c r="E890" s="13" t="n">
-        <v>15436</v>
+        <v>15394</v>
       </c>
       <c r="F890" s="13" t="n">
         <v>8</v>
@@ -27624,7 +27624,7 @@
         </is>
       </c>
       <c r="E891" s="13" t="n">
-        <v>15446</v>
+        <v>15404</v>
       </c>
       <c r="F891" s="13" t="n">
         <v>7</v>
@@ -27652,7 +27652,7 @@
         </is>
       </c>
       <c r="E892" s="13" t="n">
-        <v>15456</v>
+        <v>15414</v>
       </c>
       <c r="F892" s="13" t="n">
         <v>6</v>
@@ -27680,7 +27680,7 @@
         </is>
       </c>
       <c r="E893" s="13" t="n">
-        <v>15464</v>
+        <v>15422</v>
       </c>
       <c r="F893" s="13" t="n">
         <v>6</v>
@@ -27708,7 +27708,7 @@
         </is>
       </c>
       <c r="E894" s="13" t="n">
-        <v>15472</v>
+        <v>15430</v>
       </c>
       <c r="F894" s="13" t="n">
         <v>7</v>
@@ -27736,7 +27736,7 @@
         </is>
       </c>
       <c r="E895" s="13" t="n">
-        <v>15482</v>
+        <v>15440</v>
       </c>
       <c r="F895" s="13" t="n">
         <v>4</v>
@@ -27764,7 +27764,7 @@
         </is>
       </c>
       <c r="E896" s="13" t="n">
-        <v>15488</v>
+        <v>15446</v>
       </c>
       <c r="F896" s="13" t="n">
         <v>6</v>
@@ -27792,7 +27792,7 @@
         </is>
       </c>
       <c r="E897" s="13" t="n">
-        <v>15496</v>
+        <v>15454</v>
       </c>
       <c r="F897" s="13" t="n">
         <v>7</v>
@@ -27820,7 +27820,7 @@
         </is>
       </c>
       <c r="E898" s="13" t="n">
-        <v>15506</v>
+        <v>15464</v>
       </c>
       <c r="F898" s="13" t="n">
         <v>6</v>
@@ -27848,7 +27848,7 @@
         </is>
       </c>
       <c r="E899" s="13" t="n">
-        <v>15514</v>
+        <v>15472</v>
       </c>
       <c r="F899" s="13" t="n">
         <v>9</v>
@@ -27876,7 +27876,7 @@
         </is>
       </c>
       <c r="E900" s="13" t="n">
-        <v>15526</v>
+        <v>15484</v>
       </c>
       <c r="F900" s="13" t="n">
         <v>6</v>
@@ -27904,7 +27904,7 @@
         </is>
       </c>
       <c r="E901" s="13" t="n">
-        <v>15534</v>
+        <v>15492</v>
       </c>
       <c r="F901" s="13" t="n">
         <v>7</v>
@@ -27932,7 +27932,7 @@
         </is>
       </c>
       <c r="E902" s="13" t="n">
-        <v>15543</v>
+        <v>15501</v>
       </c>
       <c r="F902" s="13" t="n">
         <v>6</v>
@@ -27960,7 +27960,7 @@
         </is>
       </c>
       <c r="E903" s="13" t="n">
-        <v>15551</v>
+        <v>15509</v>
       </c>
       <c r="F903" s="13" t="n">
         <v>6</v>
@@ -27988,7 +27988,7 @@
         </is>
       </c>
       <c r="E904" s="13" t="n">
-        <v>15559</v>
+        <v>15517</v>
       </c>
       <c r="F904" s="13" t="n">
         <v>7</v>
@@ -28016,7 +28016,7 @@
         </is>
       </c>
       <c r="E905" s="13" t="n">
-        <v>15569</v>
+        <v>15527</v>
       </c>
       <c r="F905" s="13" t="n">
         <v>7</v>
@@ -28044,7 +28044,7 @@
         </is>
       </c>
       <c r="E906" s="13" t="n">
-        <v>15578</v>
+        <v>15536</v>
       </c>
       <c r="F906" s="13" t="n">
         <v>7</v>
@@ -28072,7 +28072,7 @@
         </is>
       </c>
       <c r="E907" s="13" t="n">
-        <v>15587</v>
+        <v>15545</v>
       </c>
       <c r="F907" s="13" t="n">
         <v>7</v>
@@ -28100,7 +28100,7 @@
         </is>
       </c>
       <c r="E908" s="13" t="n">
-        <v>15596</v>
+        <v>15554</v>
       </c>
       <c r="F908" s="13" t="n">
         <v>7</v>
@@ -28128,7 +28128,7 @@
         </is>
       </c>
       <c r="E909" s="13" t="n">
-        <v>15605</v>
+        <v>15563</v>
       </c>
       <c r="F909" s="13" t="n">
         <v>5</v>
@@ -28156,7 +28156,7 @@
         </is>
       </c>
       <c r="E910" s="13" t="n">
-        <v>15613</v>
+        <v>15571</v>
       </c>
       <c r="F910" s="13" t="n">
         <v>5</v>
@@ -28184,7 +28184,7 @@
         </is>
       </c>
       <c r="E911" s="13" t="n">
-        <v>15620</v>
+        <v>15578</v>
       </c>
       <c r="F911" s="13" t="n">
         <v>5</v>
@@ -28212,7 +28212,7 @@
         </is>
       </c>
       <c r="E912" s="13" t="n">
-        <v>15628</v>
+        <v>15586</v>
       </c>
       <c r="F912" s="13" t="n">
         <v>6</v>
@@ -28240,7 +28240,7 @@
         </is>
       </c>
       <c r="E913" s="13" t="n">
-        <v>15636</v>
+        <v>15594</v>
       </c>
       <c r="F913" s="13" t="n">
         <v>7</v>
@@ -28268,7 +28268,7 @@
         </is>
       </c>
       <c r="E914" s="13" t="n">
-        <v>15645</v>
+        <v>15603</v>
       </c>
       <c r="F914" s="13" t="n">
         <v>6</v>
@@ -28296,7 +28296,7 @@
         </is>
       </c>
       <c r="E915" s="13" t="n">
-        <v>15653</v>
+        <v>15611</v>
       </c>
       <c r="F915" s="13" t="n">
         <v>7</v>
@@ -28324,7 +28324,7 @@
         </is>
       </c>
       <c r="E916" s="13" t="n">
-        <v>15662</v>
+        <v>15620</v>
       </c>
       <c r="F916" s="13" t="n">
         <v>8</v>
@@ -28352,7 +28352,7 @@
         </is>
       </c>
       <c r="E917" s="13" t="n">
-        <v>15673</v>
+        <v>15631</v>
       </c>
       <c r="F917" s="13" t="n">
         <v>7</v>
@@ -28380,7 +28380,7 @@
         </is>
       </c>
       <c r="E918" s="13" t="n">
-        <v>15682</v>
+        <v>15640</v>
       </c>
       <c r="F918" s="13" t="n">
         <v>6</v>
@@ -28408,7 +28408,7 @@
         </is>
       </c>
       <c r="E919" s="13" t="n">
-        <v>15691</v>
+        <v>15649</v>
       </c>
       <c r="F919" s="13" t="n">
         <v>7</v>
@@ -28436,7 +28436,7 @@
         </is>
       </c>
       <c r="E920" s="13" t="n">
-        <v>15700</v>
+        <v>15658</v>
       </c>
       <c r="F920" s="13" t="n">
         <v>6</v>
@@ -28464,7 +28464,7 @@
         </is>
       </c>
       <c r="E921" s="13" t="n">
-        <v>15708</v>
+        <v>15666</v>
       </c>
       <c r="F921" s="13" t="n">
         <v>7</v>
@@ -28492,7 +28492,7 @@
         </is>
       </c>
       <c r="E922" s="13" t="n">
-        <v>15718</v>
+        <v>15676</v>
       </c>
       <c r="F922" s="13" t="n">
         <v>7</v>
@@ -28520,7 +28520,7 @@
         </is>
       </c>
       <c r="E923" s="13" t="n">
-        <v>15727</v>
+        <v>15685</v>
       </c>
       <c r="F923" s="13" t="n">
         <v>3</v>
@@ -28548,7 +28548,7 @@
         </is>
       </c>
       <c r="E924" s="13" t="n">
-        <v>15733</v>
+        <v>15691</v>
       </c>
       <c r="F924" s="13" t="n">
         <v>2</v>
@@ -28576,7 +28576,7 @@
         </is>
       </c>
       <c r="E925" s="13" t="n">
-        <v>15737</v>
+        <v>15695</v>
       </c>
       <c r="F925" s="13" t="n">
         <v>5</v>
@@ -28604,7 +28604,7 @@
         </is>
       </c>
       <c r="E926" s="13" t="n">
-        <v>15744</v>
+        <v>15702</v>
       </c>
       <c r="F926" s="13" t="n">
         <v>13</v>
@@ -28632,7 +28632,7 @@
         </is>
       </c>
       <c r="E927" s="13" t="n">
-        <v>15760</v>
+        <v>15718</v>
       </c>
       <c r="F927" s="13" t="n">
         <v>24</v>
@@ -28660,7 +28660,7 @@
         </is>
       </c>
       <c r="E928" s="13" t="n">
-        <v>15787</v>
+        <v>15745</v>
       </c>
       <c r="F928" s="13" t="n">
         <v>23</v>
@@ -28688,7 +28688,7 @@
         </is>
       </c>
       <c r="E929" s="13" t="n">
-        <v>15814</v>
+        <v>15772</v>
       </c>
       <c r="F929" s="13" t="n">
         <v>19</v>
@@ -28716,7 +28716,7 @@
         </is>
       </c>
       <c r="E930" s="13" t="n">
-        <v>15836</v>
+        <v>15794</v>
       </c>
       <c r="F930" s="13" t="n">
         <v>18</v>
@@ -28744,7 +28744,7 @@
         </is>
       </c>
       <c r="E931" s="13" t="n">
-        <v>15857</v>
+        <v>15815</v>
       </c>
       <c r="F931" s="13" t="n">
         <v>19</v>

--- a/알바로_부작_화_목록.xlsx
+++ b/알바로_부작_화_목록.xlsx
@@ -1468,7 +1468,7 @@
       </c>
       <c r="H27" s="15" t="inlineStr">
         <is>
-          <t>카밀라 위장 접근, 로셀요 체포, 재판·후일담, 제보자 마르턴, 제네바 잠입, 아일랜드·니스 추적, 독일 확대 예고</t>
+          <t>카밀라 위장 접근, 로셀요 도주·카살스 체포, 재판·후일담, 제보자 마르턴, 제네바 잠입, 아일랜드·니스 추적, 독일 확대 예고</t>
         </is>
       </c>
       <c r="I27" s="14" t="inlineStr">

--- a/알바로_부작_화_목록.xlsx
+++ b/알바로_부작_화_목록.xlsx
@@ -5903,7 +5903,7 @@
       </c>
       <c r="G115" s="15" t="inlineStr">
         <is>
-          <t>며칠 후, 알바로·하비에르·카를로스·마리나가 함께 저녁을 먹으며 이번 사건을 정리합니다.</t>
+          <t>며칠 후, 알바로·하비에르·카를로스·마리나가 함께 저녁을 먹지만, 아무도 건배를 제안하지 않고 분위기는 무겁기만 합니다.</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
         <v>4421</v>
       </c>
       <c r="F160" s="13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G160" s="15" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         </is>
       </c>
       <c r="E161" s="13" t="n">
-        <v>4433</v>
+        <v>4442</v>
       </c>
       <c r="F161" s="13" t="n">
         <v>12</v>
@@ -7212,7 +7212,7 @@
         </is>
       </c>
       <c r="E162" s="13" t="n">
-        <v>4447</v>
+        <v>4456</v>
       </c>
       <c r="F162" s="13" t="n">
         <v>12</v>
@@ -7240,7 +7240,7 @@
         </is>
       </c>
       <c r="E163" s="13" t="n">
-        <v>4462</v>
+        <v>4471</v>
       </c>
       <c r="F163" s="13" t="n">
         <v>11</v>
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="E164" s="13" t="n">
-        <v>4476</v>
+        <v>4485</v>
       </c>
       <c r="F164" s="13" t="n">
         <v>10</v>
@@ -7296,7 +7296,7 @@
         </is>
       </c>
       <c r="E165" s="13" t="n">
-        <v>4488</v>
+        <v>4497</v>
       </c>
       <c r="F165" s="13" t="n">
         <v>9</v>
@@ -7324,7 +7324,7 @@
         </is>
       </c>
       <c r="E166" s="13" t="n">
-        <v>4500</v>
+        <v>4509</v>
       </c>
       <c r="F166" s="13" t="n">
         <v>8</v>
@@ -7352,7 +7352,7 @@
         </is>
       </c>
       <c r="E167" s="13" t="n">
-        <v>4510</v>
+        <v>4519</v>
       </c>
       <c r="F167" s="13" t="n">
         <v>10</v>
@@ -7380,7 +7380,7 @@
         </is>
       </c>
       <c r="E168" s="13" t="n">
-        <v>4523</v>
+        <v>4532</v>
       </c>
       <c r="F168" s="13" t="n">
         <v>11</v>
@@ -7408,7 +7408,7 @@
         </is>
       </c>
       <c r="E169" s="13" t="n">
-        <v>4537</v>
+        <v>4546</v>
       </c>
       <c r="F169" s="13" t="n">
         <v>12</v>
@@ -7436,7 +7436,7 @@
         </is>
       </c>
       <c r="E170" s="13" t="n">
-        <v>4552</v>
+        <v>4561</v>
       </c>
       <c r="F170" s="13" t="n">
         <v>9</v>
@@ -7464,7 +7464,7 @@
         </is>
       </c>
       <c r="E171" s="13" t="n">
-        <v>4563</v>
+        <v>4572</v>
       </c>
       <c r="F171" s="13" t="n">
         <v>10</v>
@@ -7492,7 +7492,7 @@
         </is>
       </c>
       <c r="E172" s="13" t="n">
-        <v>4576</v>
+        <v>4585</v>
       </c>
       <c r="F172" s="13" t="n">
         <v>9</v>
@@ -7520,7 +7520,7 @@
         </is>
       </c>
       <c r="E173" s="13" t="n">
-        <v>4588</v>
+        <v>4597</v>
       </c>
       <c r="F173" s="13" t="n">
         <v>10</v>
@@ -7548,7 +7548,7 @@
         </is>
       </c>
       <c r="E174" s="13" t="n">
-        <v>4600</v>
+        <v>4609</v>
       </c>
       <c r="F174" s="13" t="n">
         <v>17</v>
@@ -7576,7 +7576,7 @@
         </is>
       </c>
       <c r="E175" s="13" t="n">
-        <v>4620</v>
+        <v>4629</v>
       </c>
       <c r="F175" s="13" t="n">
         <v>18</v>
@@ -7604,7 +7604,7 @@
         </is>
       </c>
       <c r="E176" s="13" t="n">
-        <v>4641</v>
+        <v>4650</v>
       </c>
       <c r="F176" s="13" t="n">
         <v>16</v>
@@ -7632,7 +7632,7 @@
         </is>
       </c>
       <c r="E177" s="13" t="n">
-        <v>4660</v>
+        <v>4669</v>
       </c>
       <c r="F177" s="13" t="n">
         <v>14</v>
@@ -7660,7 +7660,7 @@
         </is>
       </c>
       <c r="E178" s="13" t="n">
-        <v>4677</v>
+        <v>4686</v>
       </c>
       <c r="F178" s="13" t="n">
         <v>11</v>
@@ -7688,7 +7688,7 @@
         </is>
       </c>
       <c r="E179" s="13" t="n">
-        <v>4690</v>
+        <v>4699</v>
       </c>
       <c r="F179" s="13" t="n">
         <v>16</v>
@@ -7716,14 +7716,14 @@
         </is>
       </c>
       <c r="E180" s="13" t="n">
-        <v>4708</v>
+        <v>4717</v>
       </c>
       <c r="F180" s="13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G180" s="15" t="inlineStr">
         <is>
-          <t>체포와 보도 이후, 알바로와 하비에르가 뒤풀이 식사를 하며 사건을 정리합니다.</t>
+          <t>체포와 보도 이후, 알바로와 하비에르가 바에서 다시 만나지만, 축배를 들 일은 없습니다. 계약은 중단됐어도 이주민들은 같은 조건의 다른 업체로 옮겨졌을 뿐입니다.</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="E181" s="13" t="n">
-        <v>4723</v>
+        <v>4733</v>
       </c>
       <c r="F181" s="13" t="n">
         <v>15</v>
@@ -7772,7 +7772,7 @@
         </is>
       </c>
       <c r="E182" s="13" t="n">
-        <v>4741</v>
+        <v>4751</v>
       </c>
       <c r="F182" s="13" t="n">
         <v>15</v>
@@ -7800,7 +7800,7 @@
         </is>
       </c>
       <c r="E183" s="13" t="n">
-        <v>4759</v>
+        <v>4769</v>
       </c>
       <c r="F183" s="13" t="n">
         <v>12</v>
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="E184" s="13" t="n">
-        <v>4773</v>
+        <v>4783</v>
       </c>
       <c r="F184" s="13" t="n">
         <v>12</v>
@@ -7856,7 +7856,7 @@
         </is>
       </c>
       <c r="E185" s="13" t="n">
-        <v>4788</v>
+        <v>4798</v>
       </c>
       <c r="F185" s="13" t="n">
         <v>13</v>
@@ -7884,7 +7884,7 @@
         </is>
       </c>
       <c r="E186" s="13" t="n">
-        <v>4804</v>
+        <v>4814</v>
       </c>
       <c r="F186" s="13" t="n">
         <v>12</v>
@@ -7912,7 +7912,7 @@
         </is>
       </c>
       <c r="E187" s="13" t="n">
-        <v>4818</v>
+        <v>4828</v>
       </c>
       <c r="F187" s="13" t="n">
         <v>12</v>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="E188" s="13" t="n">
-        <v>4832</v>
+        <v>4842</v>
       </c>
       <c r="F188" s="13" t="n">
         <v>11</v>
@@ -7968,7 +7968,7 @@
         </is>
       </c>
       <c r="E189" s="13" t="n">
-        <v>4846</v>
+        <v>4856</v>
       </c>
       <c r="F189" s="13" t="n">
         <v>12</v>
@@ -7996,7 +7996,7 @@
         </is>
       </c>
       <c r="E190" s="13" t="n">
-        <v>4860</v>
+        <v>4870</v>
       </c>
       <c r="F190" s="13" t="n">
         <v>12</v>
@@ -8024,7 +8024,7 @@
         </is>
       </c>
       <c r="E191" s="13" t="n">
-        <v>4874</v>
+        <v>4884</v>
       </c>
       <c r="F191" s="13" t="n">
         <v>13</v>
@@ -8052,7 +8052,7 @@
         </is>
       </c>
       <c r="E192" s="13" t="n">
-        <v>4890</v>
+        <v>4900</v>
       </c>
       <c r="F192" s="13" t="n">
         <v>10</v>
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="E193" s="13" t="n">
-        <v>4902</v>
+        <v>4912</v>
       </c>
       <c r="F193" s="13" t="n">
         <v>12</v>
@@ -8108,7 +8108,7 @@
         </is>
       </c>
       <c r="E194" s="13" t="n">
-        <v>4916</v>
+        <v>4926</v>
       </c>
       <c r="F194" s="13" t="n">
         <v>10</v>
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="E195" s="13" t="n">
-        <v>4929</v>
+        <v>4939</v>
       </c>
       <c r="F195" s="13" t="n">
         <v>12</v>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="E196" s="13" t="n">
-        <v>4943</v>
+        <v>4953</v>
       </c>
       <c r="F196" s="13" t="n">
         <v>12</v>
@@ -8192,7 +8192,7 @@
         </is>
       </c>
       <c r="E197" s="13" t="n">
-        <v>4958</v>
+        <v>4968</v>
       </c>
       <c r="F197" s="13" t="n">
         <v>12</v>
@@ -8220,7 +8220,7 @@
         </is>
       </c>
       <c r="E198" s="13" t="n">
-        <v>4973</v>
+        <v>4983</v>
       </c>
       <c r="F198" s="13" t="n">
         <v>10</v>
@@ -8248,7 +8248,7 @@
         </is>
       </c>
       <c r="E199" s="13" t="n">
-        <v>4985</v>
+        <v>4995</v>
       </c>
       <c r="F199" s="13" t="n">
         <v>10</v>
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="E200" s="13" t="n">
-        <v>4998</v>
+        <v>5008</v>
       </c>
       <c r="F200" s="13" t="n">
         <v>14</v>
@@ -8304,7 +8304,7 @@
         </is>
       </c>
       <c r="E201" s="13" t="n">
-        <v>5015</v>
+        <v>5025</v>
       </c>
       <c r="F201" s="13" t="n">
         <v>12</v>
@@ -8332,7 +8332,7 @@
         </is>
       </c>
       <c r="E202" s="13" t="n">
-        <v>5029</v>
+        <v>5039</v>
       </c>
       <c r="F202" s="13" t="n">
         <v>19</v>
@@ -8360,7 +8360,7 @@
         </is>
       </c>
       <c r="E203" s="13" t="n">
-        <v>5051</v>
+        <v>5061</v>
       </c>
       <c r="F203" s="13" t="n">
         <v>15</v>
@@ -8388,7 +8388,7 @@
         </is>
       </c>
       <c r="E204" s="13" t="n">
-        <v>5069</v>
+        <v>5079</v>
       </c>
       <c r="F204" s="13" t="n">
         <v>13</v>
@@ -8416,7 +8416,7 @@
         </is>
       </c>
       <c r="E205" s="13" t="n">
-        <v>5085</v>
+        <v>5095</v>
       </c>
       <c r="F205" s="13" t="n">
         <v>14</v>
@@ -8444,7 +8444,7 @@
         </is>
       </c>
       <c r="E206" s="13" t="n">
-        <v>5102</v>
+        <v>5112</v>
       </c>
       <c r="F206" s="13" t="n">
         <v>10</v>
@@ -8472,7 +8472,7 @@
         </is>
       </c>
       <c r="E207" s="13" t="n">
-        <v>5114</v>
+        <v>5124</v>
       </c>
       <c r="F207" s="13" t="n">
         <v>15</v>
@@ -8500,7 +8500,7 @@
         </is>
       </c>
       <c r="E208" s="13" t="n">
-        <v>5132</v>
+        <v>5142</v>
       </c>
       <c r="F208" s="13" t="n">
         <v>10</v>
@@ -8528,7 +8528,7 @@
         </is>
       </c>
       <c r="E209" s="13" t="n">
-        <v>5145</v>
+        <v>5155</v>
       </c>
       <c r="F209" s="13" t="n">
         <v>13</v>
@@ -8556,7 +8556,7 @@
         </is>
       </c>
       <c r="E210" s="13" t="n">
-        <v>5160</v>
+        <v>5170</v>
       </c>
       <c r="F210" s="13" t="n">
         <v>11</v>
@@ -8584,7 +8584,7 @@
         </is>
       </c>
       <c r="E211" s="13" t="n">
-        <v>5174</v>
+        <v>5184</v>
       </c>
       <c r="F211" s="13" t="n">
         <v>12</v>
@@ -8612,7 +8612,7 @@
         </is>
       </c>
       <c r="E212" s="13" t="n">
-        <v>5189</v>
+        <v>5199</v>
       </c>
       <c r="F212" s="13" t="n">
         <v>10</v>
@@ -8640,7 +8640,7 @@
         </is>
       </c>
       <c r="E213" s="13" t="n">
-        <v>5201</v>
+        <v>5211</v>
       </c>
       <c r="F213" s="13" t="n">
         <v>11</v>
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="E214" s="13" t="n">
-        <v>5215</v>
+        <v>5225</v>
       </c>
       <c r="F214" s="13" t="n">
         <v>12</v>
@@ -8696,7 +8696,7 @@
         </is>
       </c>
       <c r="E215" s="13" t="n">
-        <v>5230</v>
+        <v>5240</v>
       </c>
       <c r="F215" s="13" t="n">
         <v>11</v>
@@ -8724,7 +8724,7 @@
         </is>
       </c>
       <c r="E216" s="13" t="n">
-        <v>5243</v>
+        <v>5253</v>
       </c>
       <c r="F216" s="13" t="n">
         <v>10</v>
@@ -8752,7 +8752,7 @@
         </is>
       </c>
       <c r="E217" s="13" t="n">
-        <v>5256</v>
+        <v>5266</v>
       </c>
       <c r="F217" s="13" t="n">
         <v>10</v>
@@ -8780,7 +8780,7 @@
         </is>
       </c>
       <c r="E218" s="13" t="n">
-        <v>5268</v>
+        <v>5278</v>
       </c>
       <c r="F218" s="13" t="n">
         <v>12</v>
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="E219" s="13" t="n">
-        <v>5283</v>
+        <v>5293</v>
       </c>
       <c r="F219" s="13" t="n">
         <v>13</v>
@@ -8836,7 +8836,7 @@
         </is>
       </c>
       <c r="E220" s="13" t="n">
-        <v>5299</v>
+        <v>5309</v>
       </c>
       <c r="F220" s="13" t="n">
         <v>10</v>
@@ -8864,7 +8864,7 @@
         </is>
       </c>
       <c r="E221" s="13" t="n">
-        <v>5311</v>
+        <v>5321</v>
       </c>
       <c r="F221" s="13" t="n">
         <v>13</v>
@@ -8892,7 +8892,7 @@
         </is>
       </c>
       <c r="E222" s="13" t="n">
-        <v>5327</v>
+        <v>5337</v>
       </c>
       <c r="F222" s="13" t="n">
         <v>10</v>
@@ -8920,7 +8920,7 @@
         </is>
       </c>
       <c r="E223" s="13" t="n">
-        <v>5339</v>
+        <v>5349</v>
       </c>
       <c r="F223" s="13" t="n">
         <v>11</v>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="E224" s="13" t="n">
-        <v>5352</v>
+        <v>5362</v>
       </c>
       <c r="F224" s="13" t="n">
         <v>13</v>
@@ -8976,7 +8976,7 @@
         </is>
       </c>
       <c r="E225" s="13" t="n">
-        <v>5368</v>
+        <v>5378</v>
       </c>
       <c r="F225" s="13" t="n">
         <v>9</v>
@@ -9004,7 +9004,7 @@
         </is>
       </c>
       <c r="E226" s="13" t="n">
-        <v>5379</v>
+        <v>5389</v>
       </c>
       <c r="F226" s="13" t="n">
         <v>13</v>
@@ -9032,7 +9032,7 @@
         </is>
       </c>
       <c r="E227" s="13" t="n">
-        <v>5395</v>
+        <v>5405</v>
       </c>
       <c r="F227" s="13" t="n">
         <v>11</v>
@@ -9060,7 +9060,7 @@
         </is>
       </c>
       <c r="E228" s="13" t="n">
-        <v>5409</v>
+        <v>5419</v>
       </c>
       <c r="F228" s="13" t="n">
         <v>11</v>
@@ -9088,7 +9088,7 @@
         </is>
       </c>
       <c r="E229" s="13" t="n">
-        <v>5422</v>
+        <v>5432</v>
       </c>
       <c r="F229" s="13" t="n">
         <v>10</v>
@@ -9116,7 +9116,7 @@
         </is>
       </c>
       <c r="E230" s="13" t="n">
-        <v>5435</v>
+        <v>5445</v>
       </c>
       <c r="F230" s="13" t="n">
         <v>11</v>
@@ -9144,7 +9144,7 @@
         </is>
       </c>
       <c r="E231" s="13" t="n">
-        <v>5449</v>
+        <v>5459</v>
       </c>
       <c r="F231" s="13" t="n">
         <v>12</v>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="E232" s="13" t="n">
-        <v>5463</v>
+        <v>5473</v>
       </c>
       <c r="F232" s="13" t="n">
         <v>11</v>
@@ -9200,7 +9200,7 @@
         </is>
       </c>
       <c r="E233" s="13" t="n">
-        <v>5477</v>
+        <v>5487</v>
       </c>
       <c r="F233" s="13" t="n">
         <v>10</v>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="E234" s="13" t="n">
-        <v>5489</v>
+        <v>5499</v>
       </c>
       <c r="F234" s="13" t="n">
         <v>11</v>
@@ -9256,7 +9256,7 @@
         </is>
       </c>
       <c r="E235" s="13" t="n">
-        <v>5502</v>
+        <v>5512</v>
       </c>
       <c r="F235" s="13" t="n">
         <v>13</v>
@@ -9284,7 +9284,7 @@
         </is>
       </c>
       <c r="E236" s="13" t="n">
-        <v>5518</v>
+        <v>5528</v>
       </c>
       <c r="F236" s="13" t="n">
         <v>12</v>
@@ -9312,7 +9312,7 @@
         </is>
       </c>
       <c r="E237" s="13" t="n">
-        <v>5532</v>
+        <v>5542</v>
       </c>
       <c r="F237" s="13" t="n">
         <v>10</v>
@@ -9340,7 +9340,7 @@
         </is>
       </c>
       <c r="E238" s="13" t="n">
-        <v>5545</v>
+        <v>5555</v>
       </c>
       <c r="F238" s="13" t="n">
         <v>10</v>
@@ -9368,7 +9368,7 @@
         </is>
       </c>
       <c r="E239" s="13" t="n">
-        <v>5558</v>
+        <v>5568</v>
       </c>
       <c r="F239" s="13" t="n">
         <v>11</v>
@@ -9396,7 +9396,7 @@
         </is>
       </c>
       <c r="E240" s="13" t="n">
-        <v>5571</v>
+        <v>5581</v>
       </c>
       <c r="F240" s="13" t="n">
         <v>9</v>
@@ -9424,7 +9424,7 @@
         </is>
       </c>
       <c r="E241" s="13" t="n">
-        <v>5583</v>
+        <v>5593</v>
       </c>
       <c r="F241" s="13" t="n">
         <v>9</v>
@@ -9452,7 +9452,7 @@
         </is>
       </c>
       <c r="E242" s="13" t="n">
-        <v>5594</v>
+        <v>5604</v>
       </c>
       <c r="F242" s="13" t="n">
         <v>10</v>
@@ -9480,7 +9480,7 @@
         </is>
       </c>
       <c r="E243" s="13" t="n">
-        <v>5607</v>
+        <v>5617</v>
       </c>
       <c r="F243" s="13" t="n">
         <v>16</v>
@@ -9508,7 +9508,7 @@
         </is>
       </c>
       <c r="E244" s="13" t="n">
-        <v>5626</v>
+        <v>5636</v>
       </c>
       <c r="F244" s="13" t="n">
         <v>16</v>
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="E245" s="13" t="n">
-        <v>5645</v>
+        <v>5655</v>
       </c>
       <c r="F245" s="13" t="n">
         <v>14</v>
@@ -9564,7 +9564,7 @@
         </is>
       </c>
       <c r="E246" s="13" t="n">
-        <v>5661</v>
+        <v>5671</v>
       </c>
       <c r="F246" s="13" t="n">
         <v>10</v>
@@ -9592,14 +9592,14 @@
         </is>
       </c>
       <c r="E247" s="13" t="n">
-        <v>5674</v>
+        <v>5684</v>
       </c>
       <c r="F247" s="13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G247" s="15" t="inlineStr">
         <is>
-          <t>알바로가 네트워크 트래픽 기록을 분석하며 이상 징후를 발견합니다.</t>
+          <t>알바로가 네트워크 트래픽 기록을 요청하지만, 접근 권한은 '검증 중'이라는 이유로 계속 미뤄집니다. 마르코스는 외부에서 직접 측정을 시작하자고 제안합니다.</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
         </is>
       </c>
       <c r="E248" s="13" t="n">
-        <v>5686</v>
+        <v>5694</v>
       </c>
       <c r="F248" s="13" t="n">
         <v>13</v>
@@ -9648,7 +9648,7 @@
         </is>
       </c>
       <c r="E249" s="13" t="n">
-        <v>5701</v>
+        <v>5709</v>
       </c>
       <c r="F249" s="13" t="n">
         <v>10</v>
@@ -9676,10 +9676,10 @@
         </is>
       </c>
       <c r="E250" s="13" t="n">
-        <v>5714</v>
+        <v>5722</v>
       </c>
       <c r="F250" s="13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G250" s="15" t="inlineStr">
         <is>
@@ -9704,14 +9704,14 @@
         </is>
       </c>
       <c r="E251" s="13" t="n">
-        <v>5726</v>
+        <v>5735</v>
       </c>
       <c r="F251" s="13" t="n">
         <v>11</v>
       </c>
       <c r="G251" s="15" t="inlineStr">
         <is>
-          <t>그날 밤, 알바로가 자신도 감시당하고 있다는 걸 눈치챕니다.</t>
+          <t>그날 밤, 알바로가 자신도 모르는 사이 위장 신분이 검증받고 있었다는 사실을 알게 됩니다.</t>
         </is>
       </c>
     </row>
@@ -9732,14 +9732,14 @@
         </is>
       </c>
       <c r="E252" s="13" t="n">
-        <v>5740</v>
+        <v>5749</v>
       </c>
       <c r="F252" s="13" t="n">
         <v>11</v>
       </c>
       <c r="G252" s="15" t="inlineStr">
         <is>
-          <t>며칠 후, 헤라르도가 마지못해 계약서 일부를 알바로에게 제공합니다.</t>
+          <t>며칠 후, 헤라르도가 마지못해 하는 얼굴로 알바로를 사무실로 불러, 신원 확인이 되지 않는다는 이유로 감사를 정중하게 종료합니다.</t>
         </is>
       </c>
     </row>
@@ -9760,14 +9760,14 @@
         </is>
       </c>
       <c r="E253" s="13" t="n">
-        <v>5753</v>
+        <v>5762</v>
       </c>
       <c r="F253" s="13" t="n">
         <v>11</v>
       </c>
       <c r="G253" s="15" t="inlineStr">
         <is>
-          <t>카를로스가 노르드링크 솔루션스에 대한 조사 결과를 전합니다.</t>
+          <t>카를로스가 노르드링크 솔루션스에 대한 조사 결과를 전합니다. 그 이름은 감사에서 쫓겨난 알바로가 공공조달 문서의 하도급 부록에서 찾아낸 것입니다.</t>
         </is>
       </c>
     </row>
@@ -9788,14 +9788,14 @@
         </is>
       </c>
       <c r="E254" s="13" t="n">
-        <v>5766</v>
+        <v>5775</v>
       </c>
       <c r="F254" s="13" t="n">
         <v>10</v>
       </c>
       <c r="G254" s="15" t="inlineStr">
         <is>
-          <t>다음 날, 헤라르도가 알바로에게 예상치 못한 질문을 던지며 긴장이 고조됩니다.</t>
+          <t>다음 날, 헤라르도가 알바로를 내보낸 그 회사를, 마르코스는 바깥에서 들여다봅니다. 외부에서 측정한 트래픽과 지연시간 분석 결과가 나옵니다.</t>
         </is>
       </c>
     </row>
@@ -9816,14 +9816,14 @@
         </is>
       </c>
       <c r="E255" s="13" t="n">
-        <v>5779</v>
+        <v>5788</v>
       </c>
       <c r="F255" s="13" t="n">
         <v>9</v>
       </c>
       <c r="G255" s="15" t="inlineStr">
         <is>
-          <t>알바로가 카를로스에게 상황을 보고하며 시간이 촉박함을 알립니다.</t>
+          <t>알바로가 카를로스에게 상황을 보고하며, 회사를 떠난 전직 엔지니어 이레네를 찾아보자고 제안합니다. 보안 기관과의 재계약 서명까지 시간이 촉박합니다.</t>
         </is>
       </c>
     </row>
@@ -9844,14 +9844,14 @@
         </is>
       </c>
       <c r="E256" s="13" t="n">
-        <v>5790</v>
+        <v>5799</v>
       </c>
       <c r="F256" s="13" t="n">
         <v>10</v>
       </c>
       <c r="G256" s="15" t="inlineStr">
         <is>
-          <t>그날 밤, 알바로가 늦게까지 남아 결정적 트래픽 로그를 확보합니다.</t>
+          <t>그날 밤, 알바로가 늦게까지 문을 여는 카페에서 누베 이베리카의 전직 엔지니어 이레네 바스티다를 만납니다.</t>
         </is>
       </c>
     </row>
@@ -9872,14 +9872,14 @@
         </is>
       </c>
       <c r="E257" s="13" t="n">
-        <v>5803</v>
+        <v>5812</v>
       </c>
       <c r="F257" s="13" t="n">
         <v>10</v>
       </c>
       <c r="G257" s="15" t="inlineStr">
         <is>
-          <t>다음 날, 카를로스와 마르코스가 확보한 증거를 분석합니다.</t>
+          <t>다음 날, 카를로스와 마르코스가 알바로와 함께 지금까지 모은 증거—공공조달 문서, 외부 트래픽 측정, 이레네의 메모—를 맞춰 봅니다.</t>
         </is>
       </c>
     </row>
@@ -9900,14 +9900,14 @@
         </is>
       </c>
       <c r="E258" s="13" t="n">
-        <v>5815</v>
+        <v>5824</v>
       </c>
       <c r="F258" s="13" t="n">
         <v>11</v>
       </c>
       <c r="G258" s="15" t="inlineStr">
         <is>
-          <t>판사의 승인을 받아, 누베 이베리카 본사에 대한 개입이 이뤄집니다.</t>
+          <t>판사의 승인을 받아, 누베 이베리카 본사에 대한 개입이 이뤄집니다. 알바로는 현장 대신 휴대폰 속보로 소식을 접합니다.</t>
         </is>
       </c>
     </row>
@@ -9928,7 +9928,7 @@
         </is>
       </c>
       <c r="E259" s="13" t="n">
-        <v>5829</v>
+        <v>5838</v>
       </c>
       <c r="F259" s="13" t="n">
         <v>12</v>
@@ -9956,7 +9956,7 @@
         </is>
       </c>
       <c r="E260" s="13" t="n">
-        <v>5844</v>
+        <v>5853</v>
       </c>
       <c r="F260" s="13" t="n">
         <v>5</v>
@@ -9984,14 +9984,14 @@
         </is>
       </c>
       <c r="E261" s="13" t="n">
-        <v>5851</v>
+        <v>5860</v>
       </c>
       <c r="F261" s="13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G261" s="15" t="inlineStr">
         <is>
-          <t>며칠 후, 알바로·카를로스·마르코스가 짧게 저녁을 함께합니다. 아직 끝난 사건이 아니어서 축하는 뒤로 미룹니다.</t>
+          <t>며칠 후, 알바로·카를로스·마르코스가 경찰청 근처 카페에서 잠깐 만납니다. 아직 끝난 사건이 아니어서 축하는 뒤로 미룹니다.</t>
         </is>
       </c>
     </row>
@@ -10012,10 +10012,10 @@
         </is>
       </c>
       <c r="E262" s="13" t="n">
-        <v>5858</v>
+        <v>5869</v>
       </c>
       <c r="F262" s="13" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G262" s="15" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         </is>
       </c>
       <c r="E263" s="13" t="n">
-        <v>5891</v>
+        <v>5904</v>
       </c>
       <c r="F263" s="13" t="n">
         <v>22</v>
@@ -10068,7 +10068,7 @@
         </is>
       </c>
       <c r="E264" s="13" t="n">
-        <v>5916</v>
+        <v>5929</v>
       </c>
       <c r="F264" s="13" t="n">
         <v>15</v>
@@ -10096,14 +10096,14 @@
         </is>
       </c>
       <c r="E265" s="13" t="n">
-        <v>5933</v>
+        <v>5946</v>
       </c>
       <c r="F265" s="13" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G265" s="15" t="inlineStr">
         <is>
-          <t>몇 주간의 준비 끝에, 스페인·포르투갈·이탈리아가 동시에 관련 기업들을 급습합니다.</t>
+          <t>몇 주간의 준비 끝에, 스페인·포르투갈·이탈리아가 동시에 관련 기업들을 급습합니다. 알바로는 뉴스 속보와 카를로스의 전화로 소식을 듣습니다.</t>
         </is>
       </c>
     </row>
@@ -10124,7 +10124,7 @@
         </is>
       </c>
       <c r="E266" s="13" t="n">
-        <v>5949</v>
+        <v>5955</v>
       </c>
       <c r="F266" s="13" t="n">
         <v>17</v>
@@ -10152,7 +10152,7 @@
         </is>
       </c>
       <c r="E267" s="13" t="n">
-        <v>5969</v>
+        <v>5975</v>
       </c>
       <c r="F267" s="13" t="n">
         <v>16</v>
@@ -10180,14 +10180,14 @@
         </is>
       </c>
       <c r="E268" s="13" t="n">
-        <v>5988</v>
+        <v>5994</v>
       </c>
       <c r="F268" s="13" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G268" s="15" t="inlineStr">
         <is>
-          <t>몇 주 후, 알바로·카를로스·마르코스·하비에르가 함께 저녁을 먹으며 이 긴 국제 수사를 마무리 짓습니다.</t>
+          <t>몇 주 후, 알바로·카를로스가 법원 앞에서, 증언을 마치고 나온 이레네를 기다립니다. 축배는 없지만, 짧은 인사로 충분합니다.</t>
         </is>
       </c>
     </row>
@@ -10208,14 +10208,14 @@
         </is>
       </c>
       <c r="E269" s="13" t="n">
-        <v>6011</v>
+        <v>6014</v>
       </c>
       <c r="F269" s="13" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G269" s="15" t="inlineStr">
         <is>
-          <t>몇 주 후, 카를로스가 알바로에게 이번 사건이 남긴 정책적 여파를 설명합니다.</t>
+          <t>몇 주 후, 카를로스가 알바로에게 이번 사건이 남긴 정책적 여파를 설명합니다. 그날 밤 알바로는 새 인증 기준을 읽으며 마르코스와 짧게 통화합니다.</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
         </is>
       </c>
       <c r="E270" s="13" t="n">
-        <v>6031</v>
+        <v>6042</v>
       </c>
       <c r="F270" s="13" t="n">
         <v>13</v>
@@ -10264,7 +10264,7 @@
         </is>
       </c>
       <c r="E271" s="13" t="n">
-        <v>6047</v>
+        <v>6058</v>
       </c>
       <c r="F271" s="13" t="n">
         <v>11</v>
@@ -10292,7 +10292,7 @@
         </is>
       </c>
       <c r="E272" s="13" t="n">
-        <v>6061</v>
+        <v>6072</v>
       </c>
       <c r="F272" s="13" t="n">
         <v>16</v>
@@ -10320,7 +10320,7 @@
         </is>
       </c>
       <c r="E273" s="13" t="n">
-        <v>6079</v>
+        <v>6090</v>
       </c>
       <c r="F273" s="13" t="n">
         <v>11</v>
@@ -10348,7 +10348,7 @@
         </is>
       </c>
       <c r="E274" s="13" t="n">
-        <v>6093</v>
+        <v>6104</v>
       </c>
       <c r="F274" s="13" t="n">
         <v>16</v>
@@ -10376,7 +10376,7 @@
         </is>
       </c>
       <c r="E275" s="13" t="n">
-        <v>6112</v>
+        <v>6123</v>
       </c>
       <c r="F275" s="13" t="n">
         <v>10</v>
@@ -10404,7 +10404,7 @@
         </is>
       </c>
       <c r="E276" s="13" t="n">
-        <v>6125</v>
+        <v>6136</v>
       </c>
       <c r="F276" s="13" t="n">
         <v>13</v>
@@ -10432,7 +10432,7 @@
         </is>
       </c>
       <c r="E277" s="13" t="n">
-        <v>6140</v>
+        <v>6151</v>
       </c>
       <c r="F277" s="13" t="n">
         <v>10</v>
@@ -10460,7 +10460,7 @@
         </is>
       </c>
       <c r="E278" s="13" t="n">
-        <v>6153</v>
+        <v>6164</v>
       </c>
       <c r="F278" s="13" t="n">
         <v>14</v>
@@ -10488,7 +10488,7 @@
         </is>
       </c>
       <c r="E279" s="13" t="n">
-        <v>6170</v>
+        <v>6181</v>
       </c>
       <c r="F279" s="13" t="n">
         <v>14</v>
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="E280" s="13" t="n">
-        <v>6186</v>
+        <v>6197</v>
       </c>
       <c r="F280" s="13" t="n">
         <v>9</v>
@@ -10544,7 +10544,7 @@
         </is>
       </c>
       <c r="E281" s="13" t="n">
-        <v>6198</v>
+        <v>6209</v>
       </c>
       <c r="F281" s="13" t="n">
         <v>11</v>
@@ -10572,7 +10572,7 @@
         </is>
       </c>
       <c r="E282" s="13" t="n">
-        <v>6211</v>
+        <v>6222</v>
       </c>
       <c r="F282" s="13" t="n">
         <v>10</v>
@@ -10600,7 +10600,7 @@
         </is>
       </c>
       <c r="E283" s="13" t="n">
-        <v>6223</v>
+        <v>6234</v>
       </c>
       <c r="F283" s="13" t="n">
         <v>9</v>
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="E284" s="13" t="n">
-        <v>6234</v>
+        <v>6245</v>
       </c>
       <c r="F284" s="13" t="n">
         <v>11</v>
@@ -10656,7 +10656,7 @@
         </is>
       </c>
       <c r="E285" s="13" t="n">
-        <v>6248</v>
+        <v>6259</v>
       </c>
       <c r="F285" s="13" t="n">
         <v>11</v>
@@ -10684,7 +10684,7 @@
         </is>
       </c>
       <c r="E286" s="13" t="n">
-        <v>6262</v>
+        <v>6273</v>
       </c>
       <c r="F286" s="13" t="n">
         <v>17</v>
@@ -10712,7 +10712,7 @@
         </is>
       </c>
       <c r="E287" s="13" t="n">
-        <v>6281</v>
+        <v>6292</v>
       </c>
       <c r="F287" s="13" t="n">
         <v>9</v>
@@ -10740,7 +10740,7 @@
         </is>
       </c>
       <c r="E288" s="13" t="n">
-        <v>6292</v>
+        <v>6303</v>
       </c>
       <c r="F288" s="13" t="n">
         <v>9</v>
@@ -10768,7 +10768,7 @@
         </is>
       </c>
       <c r="E289" s="13" t="n">
-        <v>6304</v>
+        <v>6315</v>
       </c>
       <c r="F289" s="13" t="n">
         <v>11</v>
@@ -10796,7 +10796,7 @@
         </is>
       </c>
       <c r="E290" s="13" t="n">
-        <v>6317</v>
+        <v>6328</v>
       </c>
       <c r="F290" s="13" t="n">
         <v>12</v>
@@ -10824,7 +10824,7 @@
         </is>
       </c>
       <c r="E291" s="13" t="n">
-        <v>6332</v>
+        <v>6343</v>
       </c>
       <c r="F291" s="13" t="n">
         <v>13</v>
@@ -10852,7 +10852,7 @@
         </is>
       </c>
       <c r="E292" s="13" t="n">
-        <v>6348</v>
+        <v>6359</v>
       </c>
       <c r="F292" s="13" t="n">
         <v>20</v>
@@ -10880,7 +10880,7 @@
         </is>
       </c>
       <c r="E293" s="13" t="n">
-        <v>6371</v>
+        <v>6382</v>
       </c>
       <c r="F293" s="13" t="n">
         <v>10</v>
@@ -10908,7 +10908,7 @@
         </is>
       </c>
       <c r="E294" s="13" t="n">
-        <v>6383</v>
+        <v>6394</v>
       </c>
       <c r="F294" s="13" t="n">
         <v>18</v>
@@ -10936,7 +10936,7 @@
         </is>
       </c>
       <c r="E295" s="13" t="n">
-        <v>6404</v>
+        <v>6415</v>
       </c>
       <c r="F295" s="13" t="n">
         <v>10</v>
@@ -10964,7 +10964,7 @@
         </is>
       </c>
       <c r="E296" s="13" t="n">
-        <v>6417</v>
+        <v>6428</v>
       </c>
       <c r="F296" s="13" t="n">
         <v>10</v>
@@ -10992,7 +10992,7 @@
         </is>
       </c>
       <c r="E297" s="13" t="n">
-        <v>6429</v>
+        <v>6440</v>
       </c>
       <c r="F297" s="13" t="n">
         <v>33</v>
@@ -11020,7 +11020,7 @@
         </is>
       </c>
       <c r="E298" s="13" t="n">
-        <v>6466</v>
+        <v>6477</v>
       </c>
       <c r="F298" s="13" t="n">
         <v>12</v>
@@ -11048,7 +11048,7 @@
         </is>
       </c>
       <c r="E299" s="13" t="n">
-        <v>6480</v>
+        <v>6491</v>
       </c>
       <c r="F299" s="13" t="n">
         <v>13</v>
@@ -11076,7 +11076,7 @@
         </is>
       </c>
       <c r="E300" s="13" t="n">
-        <v>6496</v>
+        <v>6507</v>
       </c>
       <c r="F300" s="13" t="n">
         <v>14</v>
@@ -11104,7 +11104,7 @@
         </is>
       </c>
       <c r="E301" s="13" t="n">
-        <v>6513</v>
+        <v>6524</v>
       </c>
       <c r="F301" s="13" t="n">
         <v>11</v>
@@ -11132,7 +11132,7 @@
         </is>
       </c>
       <c r="E302" s="13" t="n">
-        <v>6526</v>
+        <v>6537</v>
       </c>
       <c r="F302" s="13" t="n">
         <v>12</v>
@@ -11160,7 +11160,7 @@
         </is>
       </c>
       <c r="E303" s="13" t="n">
-        <v>6541</v>
+        <v>6552</v>
       </c>
       <c r="F303" s="13" t="n">
         <v>13</v>
@@ -11188,7 +11188,7 @@
         </is>
       </c>
       <c r="E304" s="13" t="n">
-        <v>6556</v>
+        <v>6567</v>
       </c>
       <c r="F304" s="13" t="n">
         <v>13</v>
@@ -11216,7 +11216,7 @@
         </is>
       </c>
       <c r="E305" s="13" t="n">
-        <v>6571</v>
+        <v>6582</v>
       </c>
       <c r="F305" s="13" t="n">
         <v>14</v>
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="E306" s="13" t="n">
-        <v>6588</v>
+        <v>6599</v>
       </c>
       <c r="F306" s="13" t="n">
         <v>11</v>
@@ -11272,7 +11272,7 @@
         </is>
       </c>
       <c r="E307" s="13" t="n">
-        <v>6601</v>
+        <v>6612</v>
       </c>
       <c r="F307" s="13" t="n">
         <v>15</v>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="E308" s="13" t="n">
-        <v>6619</v>
+        <v>6630</v>
       </c>
       <c r="F308" s="13" t="n">
         <v>13</v>
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="E309" s="13" t="n">
-        <v>6635</v>
+        <v>6646</v>
       </c>
       <c r="F309" s="13" t="n">
         <v>11</v>
@@ -11356,7 +11356,7 @@
         </is>
       </c>
       <c r="E310" s="13" t="n">
-        <v>6648</v>
+        <v>6659</v>
       </c>
       <c r="F310" s="13" t="n">
         <v>13</v>
@@ -11384,7 +11384,7 @@
         </is>
       </c>
       <c r="E311" s="13" t="n">
-        <v>6663</v>
+        <v>6674</v>
       </c>
       <c r="F311" s="13" t="n">
         <v>10</v>
@@ -11412,7 +11412,7 @@
         </is>
       </c>
       <c r="E312" s="13" t="n">
-        <v>6676</v>
+        <v>6687</v>
       </c>
       <c r="F312" s="13" t="n">
         <v>10</v>
@@ -11440,7 +11440,7 @@
         </is>
       </c>
       <c r="E313" s="13" t="n">
-        <v>6688</v>
+        <v>6699</v>
       </c>
       <c r="F313" s="13" t="n">
         <v>15</v>
@@ -11468,7 +11468,7 @@
         </is>
       </c>
       <c r="E314" s="13" t="n">
-        <v>6706</v>
+        <v>6717</v>
       </c>
       <c r="F314" s="13" t="n">
         <v>12</v>
@@ -11496,7 +11496,7 @@
         </is>
       </c>
       <c r="E315" s="13" t="n">
-        <v>6721</v>
+        <v>6732</v>
       </c>
       <c r="F315" s="13" t="n">
         <v>12</v>
@@ -11524,7 +11524,7 @@
         </is>
       </c>
       <c r="E316" s="13" t="n">
-        <v>6735</v>
+        <v>6746</v>
       </c>
       <c r="F316" s="13" t="n">
         <v>13</v>
@@ -11552,7 +11552,7 @@
         </is>
       </c>
       <c r="E317" s="13" t="n">
-        <v>6751</v>
+        <v>6762</v>
       </c>
       <c r="F317" s="13" t="n">
         <v>12</v>
@@ -11580,7 +11580,7 @@
         </is>
       </c>
       <c r="E318" s="13" t="n">
-        <v>6766</v>
+        <v>6777</v>
       </c>
       <c r="F318" s="13" t="n">
         <v>13</v>
@@ -11608,7 +11608,7 @@
         </is>
       </c>
       <c r="E319" s="13" t="n">
-        <v>6781</v>
+        <v>6792</v>
       </c>
       <c r="F319" s="13" t="n">
         <v>11</v>
@@ -11636,7 +11636,7 @@
         </is>
       </c>
       <c r="E320" s="13" t="n">
-        <v>6795</v>
+        <v>6806</v>
       </c>
       <c r="F320" s="13" t="n">
         <v>9</v>
@@ -11664,7 +11664,7 @@
         </is>
       </c>
       <c r="E321" s="13" t="n">
-        <v>6806</v>
+        <v>6817</v>
       </c>
       <c r="F321" s="13" t="n">
         <v>11</v>
@@ -11692,7 +11692,7 @@
         </is>
       </c>
       <c r="E322" s="13" t="n">
-        <v>6820</v>
+        <v>6831</v>
       </c>
       <c r="F322" s="13" t="n">
         <v>10</v>
@@ -11720,7 +11720,7 @@
         </is>
       </c>
       <c r="E323" s="13" t="n">
-        <v>6832</v>
+        <v>6843</v>
       </c>
       <c r="F323" s="13" t="n">
         <v>12</v>
@@ -11748,7 +11748,7 @@
         </is>
       </c>
       <c r="E324" s="13" t="n">
-        <v>6846</v>
+        <v>6857</v>
       </c>
       <c r="F324" s="13" t="n">
         <v>16</v>
@@ -11776,7 +11776,7 @@
         </is>
       </c>
       <c r="E325" s="13" t="n">
-        <v>6865</v>
+        <v>6876</v>
       </c>
       <c r="F325" s="13" t="n">
         <v>17</v>
@@ -11804,7 +11804,7 @@
         </is>
       </c>
       <c r="E326" s="13" t="n">
-        <v>6884</v>
+        <v>6895</v>
       </c>
       <c r="F326" s="13" t="n">
         <v>12</v>
@@ -11832,7 +11832,7 @@
         </is>
       </c>
       <c r="E327" s="13" t="n">
-        <v>6898</v>
+        <v>6909</v>
       </c>
       <c r="F327" s="13" t="n">
         <v>10</v>
@@ -11860,7 +11860,7 @@
         </is>
       </c>
       <c r="E328" s="13" t="n">
-        <v>6911</v>
+        <v>6922</v>
       </c>
       <c r="F328" s="13" t="n">
         <v>15</v>
@@ -11888,7 +11888,7 @@
         </is>
       </c>
       <c r="E329" s="13" t="n">
-        <v>6929</v>
+        <v>6940</v>
       </c>
       <c r="F329" s="13" t="n">
         <v>23</v>
@@ -11916,7 +11916,7 @@
         </is>
       </c>
       <c r="E330" s="13" t="n">
-        <v>6955</v>
+        <v>6966</v>
       </c>
       <c r="F330" s="13" t="n">
         <v>20</v>
@@ -11944,7 +11944,7 @@
         </is>
       </c>
       <c r="E331" s="13" t="n">
-        <v>6978</v>
+        <v>6989</v>
       </c>
       <c r="F331" s="13" t="n">
         <v>15</v>
@@ -11972,7 +11972,7 @@
         </is>
       </c>
       <c r="E332" s="13" t="n">
-        <v>6996</v>
+        <v>7007</v>
       </c>
       <c r="F332" s="13" t="n">
         <v>11</v>
@@ -12000,7 +12000,7 @@
         </is>
       </c>
       <c r="E333" s="13" t="n">
-        <v>7010</v>
+        <v>7021</v>
       </c>
       <c r="F333" s="13" t="n">
         <v>17</v>
@@ -12028,7 +12028,7 @@
         </is>
       </c>
       <c r="E334" s="13" t="n">
-        <v>7030</v>
+        <v>7041</v>
       </c>
       <c r="F334" s="13" t="n">
         <v>18</v>
@@ -12056,7 +12056,7 @@
         </is>
       </c>
       <c r="E335" s="13" t="n">
-        <v>7051</v>
+        <v>7062</v>
       </c>
       <c r="F335" s="13" t="n">
         <v>16</v>
@@ -12084,7 +12084,7 @@
         </is>
       </c>
       <c r="E336" s="13" t="n">
-        <v>7069</v>
+        <v>7080</v>
       </c>
       <c r="F336" s="13" t="n">
         <v>16</v>
@@ -12112,7 +12112,7 @@
         </is>
       </c>
       <c r="E337" s="13" t="n">
-        <v>7088</v>
+        <v>7099</v>
       </c>
       <c r="F337" s="13" t="n">
         <v>16</v>
@@ -12140,7 +12140,7 @@
         </is>
       </c>
       <c r="E338" s="13" t="n">
-        <v>7107</v>
+        <v>7118</v>
       </c>
       <c r="F338" s="13" t="n">
         <v>13</v>
@@ -12168,7 +12168,7 @@
         </is>
       </c>
       <c r="E339" s="13" t="n">
-        <v>7123</v>
+        <v>7134</v>
       </c>
       <c r="F339" s="13" t="n">
         <v>13</v>
@@ -12196,7 +12196,7 @@
         </is>
       </c>
       <c r="E340" s="13" t="n">
-        <v>7139</v>
+        <v>7150</v>
       </c>
       <c r="F340" s="13" t="n">
         <v>17</v>
@@ -12224,7 +12224,7 @@
         </is>
       </c>
       <c r="E341" s="13" t="n">
-        <v>7159</v>
+        <v>7170</v>
       </c>
       <c r="F341" s="13" t="n">
         <v>14</v>
@@ -12252,7 +12252,7 @@
         </is>
       </c>
       <c r="E342" s="13" t="n">
-        <v>7176</v>
+        <v>7187</v>
       </c>
       <c r="F342" s="13" t="n">
         <v>13</v>
@@ -12280,7 +12280,7 @@
         </is>
       </c>
       <c r="E343" s="13" t="n">
-        <v>7191</v>
+        <v>7202</v>
       </c>
       <c r="F343" s="13" t="n">
         <v>10</v>
@@ -12308,7 +12308,7 @@
         </is>
       </c>
       <c r="E344" s="13" t="n">
-        <v>7204</v>
+        <v>7215</v>
       </c>
       <c r="F344" s="13" t="n">
         <v>11</v>
@@ -12336,7 +12336,7 @@
         </is>
       </c>
       <c r="E345" s="13" t="n">
-        <v>7218</v>
+        <v>7229</v>
       </c>
       <c r="F345" s="13" t="n">
         <v>11</v>
@@ -12364,7 +12364,7 @@
         </is>
       </c>
       <c r="E346" s="13" t="n">
-        <v>7231</v>
+        <v>7242</v>
       </c>
       <c r="F346" s="13" t="n">
         <v>13</v>
@@ -12392,7 +12392,7 @@
         </is>
       </c>
       <c r="E347" s="13" t="n">
-        <v>7247</v>
+        <v>7258</v>
       </c>
       <c r="F347" s="13" t="n">
         <v>13</v>
@@ -12420,7 +12420,7 @@
         </is>
       </c>
       <c r="E348" s="13" t="n">
-        <v>7263</v>
+        <v>7274</v>
       </c>
       <c r="F348" s="13" t="n">
         <v>12</v>
@@ -12448,7 +12448,7 @@
         </is>
       </c>
       <c r="E349" s="13" t="n">
-        <v>7278</v>
+        <v>7289</v>
       </c>
       <c r="F349" s="13" t="n">
         <v>11</v>
@@ -12476,7 +12476,7 @@
         </is>
       </c>
       <c r="E350" s="13" t="n">
-        <v>7291</v>
+        <v>7302</v>
       </c>
       <c r="F350" s="13" t="n">
         <v>13</v>
@@ -12504,7 +12504,7 @@
         </is>
       </c>
       <c r="E351" s="13" t="n">
-        <v>7307</v>
+        <v>7318</v>
       </c>
       <c r="F351" s="13" t="n">
         <v>10</v>
@@ -12532,7 +12532,7 @@
         </is>
       </c>
       <c r="E352" s="13" t="n">
-        <v>7320</v>
+        <v>7331</v>
       </c>
       <c r="F352" s="13" t="n">
         <v>11</v>
@@ -12560,7 +12560,7 @@
         </is>
       </c>
       <c r="E353" s="13" t="n">
-        <v>7333</v>
+        <v>7344</v>
       </c>
       <c r="F353" s="13" t="n">
         <v>12</v>
@@ -12588,7 +12588,7 @@
         </is>
       </c>
       <c r="E354" s="13" t="n">
-        <v>7348</v>
+        <v>7359</v>
       </c>
       <c r="F354" s="13" t="n">
         <v>19</v>
@@ -12616,7 +12616,7 @@
         </is>
       </c>
       <c r="E355" s="13" t="n">
-        <v>7370</v>
+        <v>7381</v>
       </c>
       <c r="F355" s="13" t="n">
         <v>11</v>
@@ -12644,7 +12644,7 @@
         </is>
       </c>
       <c r="E356" s="13" t="n">
-        <v>7384</v>
+        <v>7395</v>
       </c>
       <c r="F356" s="13" t="n">
         <v>13</v>
@@ -12672,7 +12672,7 @@
         </is>
       </c>
       <c r="E357" s="13" t="n">
-        <v>7400</v>
+        <v>7411</v>
       </c>
       <c r="F357" s="13" t="n">
         <v>13</v>
@@ -12700,7 +12700,7 @@
         </is>
       </c>
       <c r="E358" s="13" t="n">
-        <v>7415</v>
+        <v>7426</v>
       </c>
       <c r="F358" s="13" t="n">
         <v>14</v>
@@ -12728,7 +12728,7 @@
         </is>
       </c>
       <c r="E359" s="13" t="n">
-        <v>7432</v>
+        <v>7443</v>
       </c>
       <c r="F359" s="13" t="n">
         <v>15</v>
@@ -12756,7 +12756,7 @@
         </is>
       </c>
       <c r="E360" s="13" t="n">
-        <v>7450</v>
+        <v>7461</v>
       </c>
       <c r="F360" s="13" t="n">
         <v>15</v>
@@ -12784,7 +12784,7 @@
         </is>
       </c>
       <c r="E361" s="13" t="n">
-        <v>7468</v>
+        <v>7479</v>
       </c>
       <c r="F361" s="13" t="n">
         <v>14</v>
@@ -12812,7 +12812,7 @@
         </is>
       </c>
       <c r="E362" s="13" t="n">
-        <v>7485</v>
+        <v>7496</v>
       </c>
       <c r="F362" s="13" t="n">
         <v>14</v>
@@ -12840,7 +12840,7 @@
         </is>
       </c>
       <c r="E363" s="13" t="n">
-        <v>7501</v>
+        <v>7512</v>
       </c>
       <c r="F363" s="13" t="n">
         <v>16</v>
@@ -12868,7 +12868,7 @@
         </is>
       </c>
       <c r="E364" s="13" t="n">
-        <v>7520</v>
+        <v>7531</v>
       </c>
       <c r="F364" s="13" t="n">
         <v>15</v>
@@ -12896,7 +12896,7 @@
         </is>
       </c>
       <c r="E365" s="13" t="n">
-        <v>7538</v>
+        <v>7549</v>
       </c>
       <c r="F365" s="13" t="n">
         <v>16</v>
@@ -12924,7 +12924,7 @@
         </is>
       </c>
       <c r="E366" s="13" t="n">
-        <v>7557</v>
+        <v>7568</v>
       </c>
       <c r="F366" s="13" t="n">
         <v>18</v>
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="E367" s="13" t="n">
-        <v>7578</v>
+        <v>7589</v>
       </c>
       <c r="F367" s="13" t="n">
         <v>19</v>
@@ -12980,7 +12980,7 @@
         </is>
       </c>
       <c r="E368" s="13" t="n">
-        <v>7600</v>
+        <v>7611</v>
       </c>
       <c r="F368" s="13" t="n">
         <v>14</v>
@@ -13008,7 +13008,7 @@
         </is>
       </c>
       <c r="E369" s="13" t="n">
-        <v>7617</v>
+        <v>7628</v>
       </c>
       <c r="F369" s="13" t="n">
         <v>13</v>
@@ -13036,7 +13036,7 @@
         </is>
       </c>
       <c r="E370" s="13" t="n">
-        <v>7633</v>
+        <v>7644</v>
       </c>
       <c r="F370" s="13" t="n">
         <v>12</v>
@@ -13064,7 +13064,7 @@
         </is>
       </c>
       <c r="E371" s="13" t="n">
-        <v>7647</v>
+        <v>7658</v>
       </c>
       <c r="F371" s="13" t="n">
         <v>10</v>
@@ -13092,7 +13092,7 @@
         </is>
       </c>
       <c r="E372" s="13" t="n">
-        <v>7660</v>
+        <v>7671</v>
       </c>
       <c r="F372" s="13" t="n">
         <v>11</v>
@@ -13120,7 +13120,7 @@
         </is>
       </c>
       <c r="E373" s="13" t="n">
-        <v>7674</v>
+        <v>7685</v>
       </c>
       <c r="F373" s="13" t="n">
         <v>11</v>
@@ -13148,7 +13148,7 @@
         </is>
       </c>
       <c r="E374" s="13" t="n">
-        <v>7687</v>
+        <v>7698</v>
       </c>
       <c r="F374" s="13" t="n">
         <v>13</v>
@@ -13176,7 +13176,7 @@
         </is>
       </c>
       <c r="E375" s="13" t="n">
-        <v>7703</v>
+        <v>7714</v>
       </c>
       <c r="F375" s="13" t="n">
         <v>18</v>
@@ -13204,7 +13204,7 @@
         </is>
       </c>
       <c r="E376" s="13" t="n">
-        <v>7724</v>
+        <v>7735</v>
       </c>
       <c r="F376" s="13" t="n">
         <v>10</v>
@@ -13232,7 +13232,7 @@
         </is>
       </c>
       <c r="E377" s="13" t="n">
-        <v>7737</v>
+        <v>7748</v>
       </c>
       <c r="F377" s="13" t="n">
         <v>12</v>
@@ -13260,7 +13260,7 @@
         </is>
       </c>
       <c r="E378" s="13" t="n">
-        <v>7751</v>
+        <v>7762</v>
       </c>
       <c r="F378" s="13" t="n">
         <v>9</v>
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="E379" s="13" t="n">
-        <v>7763</v>
+        <v>7774</v>
       </c>
       <c r="F379" s="13" t="n">
         <v>10</v>
@@ -13316,7 +13316,7 @@
         </is>
       </c>
       <c r="E380" s="13" t="n">
-        <v>7775</v>
+        <v>7786</v>
       </c>
       <c r="F380" s="13" t="n">
         <v>10</v>
@@ -13344,7 +13344,7 @@
         </is>
       </c>
       <c r="E381" s="13" t="n">
-        <v>7787</v>
+        <v>7798</v>
       </c>
       <c r="F381" s="13" t="n">
         <v>11</v>
@@ -13372,7 +13372,7 @@
         </is>
       </c>
       <c r="E382" s="13" t="n">
-        <v>7801</v>
+        <v>7812</v>
       </c>
       <c r="F382" s="13" t="n">
         <v>14</v>
@@ -13400,7 +13400,7 @@
         </is>
       </c>
       <c r="E383" s="13" t="n">
-        <v>7817</v>
+        <v>7828</v>
       </c>
       <c r="F383" s="13" t="n">
         <v>11</v>
@@ -13428,7 +13428,7 @@
         </is>
       </c>
       <c r="E384" s="13" t="n">
-        <v>7831</v>
+        <v>7842</v>
       </c>
       <c r="F384" s="13" t="n">
         <v>12</v>
@@ -13456,7 +13456,7 @@
         </is>
       </c>
       <c r="E385" s="13" t="n">
-        <v>7846</v>
+        <v>7857</v>
       </c>
       <c r="F385" s="13" t="n">
         <v>11</v>
@@ -13484,7 +13484,7 @@
         </is>
       </c>
       <c r="E386" s="13" t="n">
-        <v>7859</v>
+        <v>7870</v>
       </c>
       <c r="F386" s="13" t="n">
         <v>11</v>
@@ -13512,7 +13512,7 @@
         </is>
       </c>
       <c r="E387" s="13" t="n">
-        <v>7872</v>
+        <v>7883</v>
       </c>
       <c r="F387" s="13" t="n">
         <v>10</v>
@@ -13540,7 +13540,7 @@
         </is>
       </c>
       <c r="E388" s="13" t="n">
-        <v>7885</v>
+        <v>7896</v>
       </c>
       <c r="F388" s="13" t="n">
         <v>11</v>
@@ -13568,7 +13568,7 @@
         </is>
       </c>
       <c r="E389" s="13" t="n">
-        <v>7898</v>
+        <v>7909</v>
       </c>
       <c r="F389" s="13" t="n">
         <v>11</v>
@@ -13596,7 +13596,7 @@
         </is>
       </c>
       <c r="E390" s="13" t="n">
-        <v>7912</v>
+        <v>7923</v>
       </c>
       <c r="F390" s="13" t="n">
         <v>11</v>
@@ -13624,7 +13624,7 @@
         </is>
       </c>
       <c r="E391" s="13" t="n">
-        <v>7926</v>
+        <v>7937</v>
       </c>
       <c r="F391" s="13" t="n">
         <v>11</v>
@@ -13652,7 +13652,7 @@
         </is>
       </c>
       <c r="E392" s="13" t="n">
-        <v>7939</v>
+        <v>7950</v>
       </c>
       <c r="F392" s="13" t="n">
         <v>23</v>
@@ -13680,7 +13680,7 @@
         </is>
       </c>
       <c r="E393" s="13" t="n">
-        <v>7965</v>
+        <v>7976</v>
       </c>
       <c r="F393" s="13" t="n">
         <v>13</v>
@@ -13708,7 +13708,7 @@
         </is>
       </c>
       <c r="E394" s="13" t="n">
-        <v>7981</v>
+        <v>7992</v>
       </c>
       <c r="F394" s="13" t="n">
         <v>12</v>
@@ -13736,7 +13736,7 @@
         </is>
       </c>
       <c r="E395" s="13" t="n">
-        <v>7996</v>
+        <v>8007</v>
       </c>
       <c r="F395" s="13" t="n">
         <v>15</v>
@@ -13764,7 +13764,7 @@
         </is>
       </c>
       <c r="E396" s="13" t="n">
-        <v>8014</v>
+        <v>8025</v>
       </c>
       <c r="F396" s="13" t="n">
         <v>12</v>
@@ -13792,7 +13792,7 @@
         </is>
       </c>
       <c r="E397" s="13" t="n">
-        <v>8028</v>
+        <v>8039</v>
       </c>
       <c r="F397" s="13" t="n">
         <v>16</v>
@@ -13820,7 +13820,7 @@
         </is>
       </c>
       <c r="E398" s="13" t="n">
-        <v>8047</v>
+        <v>8058</v>
       </c>
       <c r="F398" s="13" t="n">
         <v>13</v>
@@ -13848,7 +13848,7 @@
         </is>
       </c>
       <c r="E399" s="13" t="n">
-        <v>8063</v>
+        <v>8074</v>
       </c>
       <c r="F399" s="13" t="n">
         <v>12</v>
@@ -13876,7 +13876,7 @@
         </is>
       </c>
       <c r="E400" s="13" t="n">
-        <v>8078</v>
+        <v>8089</v>
       </c>
       <c r="F400" s="13" t="n">
         <v>12</v>
@@ -13904,7 +13904,7 @@
         </is>
       </c>
       <c r="E401" s="13" t="n">
-        <v>8092</v>
+        <v>8103</v>
       </c>
       <c r="F401" s="13" t="n">
         <v>12</v>
@@ -13932,7 +13932,7 @@
         </is>
       </c>
       <c r="E402" s="13" t="n">
-        <v>8107</v>
+        <v>8118</v>
       </c>
       <c r="F402" s="13" t="n">
         <v>10</v>
@@ -13960,7 +13960,7 @@
         </is>
       </c>
       <c r="E403" s="13" t="n">
-        <v>8120</v>
+        <v>8131</v>
       </c>
       <c r="F403" s="13" t="n">
         <v>12</v>
@@ -13988,7 +13988,7 @@
         </is>
       </c>
       <c r="E404" s="13" t="n">
-        <v>8134</v>
+        <v>8145</v>
       </c>
       <c r="F404" s="13" t="n">
         <v>13</v>
@@ -14016,7 +14016,7 @@
         </is>
       </c>
       <c r="E405" s="13" t="n">
-        <v>8150</v>
+        <v>8161</v>
       </c>
       <c r="F405" s="13" t="n">
         <v>12</v>
@@ -14044,7 +14044,7 @@
         </is>
       </c>
       <c r="E406" s="13" t="n">
-        <v>8165</v>
+        <v>8176</v>
       </c>
       <c r="F406" s="13" t="n">
         <v>10</v>
@@ -14072,7 +14072,7 @@
         </is>
       </c>
       <c r="E407" s="13" t="n">
-        <v>8177</v>
+        <v>8188</v>
       </c>
       <c r="F407" s="13" t="n">
         <v>13</v>
@@ -14100,7 +14100,7 @@
         </is>
       </c>
       <c r="E408" s="13" t="n">
-        <v>8193</v>
+        <v>8204</v>
       </c>
       <c r="F408" s="13" t="n">
         <v>12</v>
@@ -14128,7 +14128,7 @@
         </is>
       </c>
       <c r="E409" s="13" t="n">
-        <v>8208</v>
+        <v>8219</v>
       </c>
       <c r="F409" s="13" t="n">
         <v>15</v>
@@ -14156,7 +14156,7 @@
         </is>
       </c>
       <c r="E410" s="13" t="n">
-        <v>8225</v>
+        <v>8236</v>
       </c>
       <c r="F410" s="13" t="n">
         <v>10</v>
@@ -14184,7 +14184,7 @@
         </is>
       </c>
       <c r="E411" s="13" t="n">
-        <v>8237</v>
+        <v>8248</v>
       </c>
       <c r="F411" s="13" t="n">
         <v>13</v>
@@ -14212,7 +14212,7 @@
         </is>
       </c>
       <c r="E412" s="13" t="n">
-        <v>8253</v>
+        <v>8264</v>
       </c>
       <c r="F412" s="13" t="n">
         <v>8</v>
@@ -14240,7 +14240,7 @@
         </is>
       </c>
       <c r="E413" s="13" t="n">
-        <v>8263</v>
+        <v>8274</v>
       </c>
       <c r="F413" s="13" t="n">
         <v>21</v>
@@ -14268,7 +14268,7 @@
         </is>
       </c>
       <c r="E414" s="13" t="n">
-        <v>8287</v>
+        <v>8298</v>
       </c>
       <c r="F414" s="13" t="n">
         <v>17</v>
@@ -14296,7 +14296,7 @@
         </is>
       </c>
       <c r="E415" s="13" t="n">
-        <v>8307</v>
+        <v>8318</v>
       </c>
       <c r="F415" s="13" t="n">
         <v>10</v>
@@ -14324,7 +14324,7 @@
         </is>
       </c>
       <c r="E416" s="13" t="n">
-        <v>8320</v>
+        <v>8331</v>
       </c>
       <c r="F416" s="13" t="n">
         <v>15</v>
@@ -14352,7 +14352,7 @@
         </is>
       </c>
       <c r="E417" s="13" t="n">
-        <v>8338</v>
+        <v>8349</v>
       </c>
       <c r="F417" s="13" t="n">
         <v>9</v>
@@ -14380,7 +14380,7 @@
         </is>
       </c>
       <c r="E418" s="13" t="n">
-        <v>8349</v>
+        <v>8360</v>
       </c>
       <c r="F418" s="13" t="n">
         <v>16</v>
@@ -14408,7 +14408,7 @@
         </is>
       </c>
       <c r="E419" s="13" t="n">
-        <v>8368</v>
+        <v>8379</v>
       </c>
       <c r="F419" s="13" t="n">
         <v>12</v>
@@ -14436,7 +14436,7 @@
         </is>
       </c>
       <c r="E420" s="13" t="n">
-        <v>8383</v>
+        <v>8394</v>
       </c>
       <c r="F420" s="13" t="n">
         <v>13</v>
@@ -14464,7 +14464,7 @@
         </is>
       </c>
       <c r="E421" s="13" t="n">
-        <v>8399</v>
+        <v>8410</v>
       </c>
       <c r="F421" s="13" t="n">
         <v>12</v>
@@ -14492,7 +14492,7 @@
         </is>
       </c>
       <c r="E422" s="13" t="n">
-        <v>8413</v>
+        <v>8424</v>
       </c>
       <c r="F422" s="13" t="n">
         <v>12</v>
@@ -14520,7 +14520,7 @@
         </is>
       </c>
       <c r="E423" s="13" t="n">
-        <v>8427</v>
+        <v>8438</v>
       </c>
       <c r="F423" s="13" t="n">
         <v>8</v>
@@ -14548,7 +14548,7 @@
         </is>
       </c>
       <c r="E424" s="13" t="n">
-        <v>8438</v>
+        <v>8449</v>
       </c>
       <c r="F424" s="13" t="n">
         <v>21</v>
@@ -14576,7 +14576,7 @@
         </is>
       </c>
       <c r="E425" s="13" t="n">
-        <v>8462</v>
+        <v>8473</v>
       </c>
       <c r="F425" s="13" t="n">
         <v>15</v>
@@ -14604,7 +14604,7 @@
         </is>
       </c>
       <c r="E426" s="13" t="n">
-        <v>8480</v>
+        <v>8491</v>
       </c>
       <c r="F426" s="13" t="n">
         <v>12</v>
@@ -14632,7 +14632,7 @@
         </is>
       </c>
       <c r="E427" s="13" t="n">
-        <v>8495</v>
+        <v>8506</v>
       </c>
       <c r="F427" s="13" t="n">
         <v>12</v>
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="E428" s="13" t="n">
-        <v>8509</v>
+        <v>8520</v>
       </c>
       <c r="F428" s="13" t="n">
         <v>14</v>
@@ -14688,7 +14688,7 @@
         </is>
       </c>
       <c r="E429" s="13" t="n">
-        <v>8526</v>
+        <v>8537</v>
       </c>
       <c r="F429" s="13" t="n">
         <v>14</v>
@@ -14716,7 +14716,7 @@
         </is>
       </c>
       <c r="E430" s="13" t="n">
-        <v>8543</v>
+        <v>8554</v>
       </c>
       <c r="F430" s="13" t="n">
         <v>19</v>
@@ -14744,7 +14744,7 @@
         </is>
       </c>
       <c r="E431" s="13" t="n">
-        <v>8565</v>
+        <v>8576</v>
       </c>
       <c r="F431" s="13" t="n">
         <v>16</v>
@@ -14772,7 +14772,7 @@
         </is>
       </c>
       <c r="E432" s="13" t="n">
-        <v>8584</v>
+        <v>8595</v>
       </c>
       <c r="F432" s="13" t="n">
         <v>16</v>
@@ -14800,7 +14800,7 @@
         </is>
       </c>
       <c r="E433" s="13" t="n">
-        <v>8603</v>
+        <v>8614</v>
       </c>
       <c r="F433" s="13" t="n">
         <v>12</v>
@@ -14828,7 +14828,7 @@
         </is>
       </c>
       <c r="E434" s="13" t="n">
-        <v>8617</v>
+        <v>8628</v>
       </c>
       <c r="F434" s="13" t="n">
         <v>13</v>
@@ -14856,7 +14856,7 @@
         </is>
       </c>
       <c r="E435" s="13" t="n">
-        <v>8633</v>
+        <v>8644</v>
       </c>
       <c r="F435" s="13" t="n">
         <v>17</v>
@@ -14884,7 +14884,7 @@
         </is>
       </c>
       <c r="E436" s="13" t="n">
-        <v>8653</v>
+        <v>8664</v>
       </c>
       <c r="F436" s="13" t="n">
         <v>17</v>
@@ -14912,7 +14912,7 @@
         </is>
       </c>
       <c r="E437" s="13" t="n">
-        <v>8673</v>
+        <v>8684</v>
       </c>
       <c r="F437" s="13" t="n">
         <v>20</v>
@@ -14940,7 +14940,7 @@
         </is>
       </c>
       <c r="E438" s="13" t="n">
-        <v>8696</v>
+        <v>8707</v>
       </c>
       <c r="F438" s="13" t="n">
         <v>23</v>
@@ -14968,7 +14968,7 @@
         </is>
       </c>
       <c r="E439" s="13" t="n">
-        <v>8722</v>
+        <v>8733</v>
       </c>
       <c r="F439" s="13" t="n">
         <v>21</v>
@@ -14996,7 +14996,7 @@
         </is>
       </c>
       <c r="E440" s="13" t="n">
-        <v>8746</v>
+        <v>8757</v>
       </c>
       <c r="F440" s="13" t="n">
         <v>19</v>
@@ -15024,7 +15024,7 @@
         </is>
       </c>
       <c r="E441" s="13" t="n">
-        <v>8768</v>
+        <v>8779</v>
       </c>
       <c r="F441" s="13" t="n">
         <v>15</v>
@@ -15052,7 +15052,7 @@
         </is>
       </c>
       <c r="E442" s="13" t="n">
-        <v>8786</v>
+        <v>8797</v>
       </c>
       <c r="F442" s="13" t="n">
         <v>20</v>
@@ -15080,7 +15080,7 @@
         </is>
       </c>
       <c r="E443" s="13" t="n">
-        <v>8809</v>
+        <v>8820</v>
       </c>
       <c r="F443" s="13" t="n">
         <v>17</v>
@@ -15108,7 +15108,7 @@
         </is>
       </c>
       <c r="E444" s="13" t="n">
-        <v>8829</v>
+        <v>8840</v>
       </c>
       <c r="F444" s="13" t="n">
         <v>19</v>
@@ -15136,7 +15136,7 @@
         </is>
       </c>
       <c r="E445" s="13" t="n">
-        <v>8850</v>
+        <v>8861</v>
       </c>
       <c r="F445" s="13" t="n">
         <v>19</v>
@@ -15164,7 +15164,7 @@
         </is>
       </c>
       <c r="E446" s="13" t="n">
-        <v>8872</v>
+        <v>8883</v>
       </c>
       <c r="F446" s="13" t="n">
         <v>10</v>
@@ -15192,7 +15192,7 @@
         </is>
       </c>
       <c r="E447" s="13" t="n">
-        <v>8884</v>
+        <v>8895</v>
       </c>
       <c r="F447" s="13" t="n">
         <v>11</v>
@@ -15220,7 +15220,7 @@
         </is>
       </c>
       <c r="E448" s="13" t="n">
-        <v>8898</v>
+        <v>8909</v>
       </c>
       <c r="F448" s="13" t="n">
         <v>12</v>
@@ -15248,7 +15248,7 @@
         </is>
       </c>
       <c r="E449" s="13" t="n">
-        <v>8912</v>
+        <v>8923</v>
       </c>
       <c r="F449" s="13" t="n">
         <v>10</v>
@@ -15276,7 +15276,7 @@
         </is>
       </c>
       <c r="E450" s="13" t="n">
-        <v>8924</v>
+        <v>8935</v>
       </c>
       <c r="F450" s="13" t="n">
         <v>12</v>
@@ -15304,7 +15304,7 @@
         </is>
       </c>
       <c r="E451" s="13" t="n">
-        <v>8939</v>
+        <v>8950</v>
       </c>
       <c r="F451" s="13" t="n">
         <v>9</v>
@@ -15332,7 +15332,7 @@
         </is>
       </c>
       <c r="E452" s="13" t="n">
-        <v>8950</v>
+        <v>8961</v>
       </c>
       <c r="F452" s="13" t="n">
         <v>12</v>
@@ -15360,7 +15360,7 @@
         </is>
       </c>
       <c r="E453" s="13" t="n">
-        <v>8965</v>
+        <v>8976</v>
       </c>
       <c r="F453" s="13" t="n">
         <v>10</v>
@@ -15388,7 +15388,7 @@
         </is>
       </c>
       <c r="E454" s="13" t="n">
-        <v>8978</v>
+        <v>8989</v>
       </c>
       <c r="F454" s="13" t="n">
         <v>9</v>
@@ -15416,7 +15416,7 @@
         </is>
       </c>
       <c r="E455" s="13" t="n">
-        <v>8989</v>
+        <v>9000</v>
       </c>
       <c r="F455" s="13" t="n">
         <v>17</v>
@@ -15444,7 +15444,7 @@
         </is>
       </c>
       <c r="E456" s="13" t="n">
-        <v>9009</v>
+        <v>9020</v>
       </c>
       <c r="F456" s="13" t="n">
         <v>13</v>
@@ -15472,7 +15472,7 @@
         </is>
       </c>
       <c r="E457" s="13" t="n">
-        <v>9025</v>
+        <v>9036</v>
       </c>
       <c r="F457" s="13" t="n">
         <v>15</v>
@@ -15500,7 +15500,7 @@
         </is>
       </c>
       <c r="E458" s="13" t="n">
-        <v>9042</v>
+        <v>9053</v>
       </c>
       <c r="F458" s="13" t="n">
         <v>22</v>
@@ -15528,7 +15528,7 @@
         </is>
       </c>
       <c r="E459" s="13" t="n">
-        <v>9066</v>
+        <v>9077</v>
       </c>
       <c r="F459" s="13" t="n">
         <v>15</v>
@@ -15556,7 +15556,7 @@
         </is>
       </c>
       <c r="E460" s="13" t="n">
-        <v>9083</v>
+        <v>9094</v>
       </c>
       <c r="F460" s="13" t="n">
         <v>17</v>
@@ -15584,7 +15584,7 @@
         </is>
       </c>
       <c r="E461" s="13" t="n">
-        <v>9103</v>
+        <v>9114</v>
       </c>
       <c r="F461" s="13" t="n">
         <v>20</v>
@@ -15612,7 +15612,7 @@
         </is>
       </c>
       <c r="E462" s="13" t="n">
-        <v>9126</v>
+        <v>9137</v>
       </c>
       <c r="F462" s="13" t="n">
         <v>13</v>
@@ -15640,7 +15640,7 @@
         </is>
       </c>
       <c r="E463" s="13" t="n">
-        <v>9142</v>
+        <v>9153</v>
       </c>
       <c r="F463" s="13" t="n">
         <v>12</v>
@@ -15668,7 +15668,7 @@
         </is>
       </c>
       <c r="E464" s="13" t="n">
-        <v>9157</v>
+        <v>9168</v>
       </c>
       <c r="F464" s="13" t="n">
         <v>11</v>
@@ -15696,7 +15696,7 @@
         </is>
       </c>
       <c r="E465" s="13" t="n">
-        <v>9170</v>
+        <v>9181</v>
       </c>
       <c r="F465" s="13" t="n">
         <v>8</v>
@@ -15724,7 +15724,7 @@
         </is>
       </c>
       <c r="E466" s="13" t="n">
-        <v>9181</v>
+        <v>9192</v>
       </c>
       <c r="F466" s="13" t="n">
         <v>23</v>
@@ -15752,7 +15752,7 @@
         </is>
       </c>
       <c r="E467" s="13" t="n">
-        <v>9207</v>
+        <v>9218</v>
       </c>
       <c r="F467" s="13" t="n">
         <v>13</v>
@@ -15780,7 +15780,7 @@
         </is>
       </c>
       <c r="E468" s="13" t="n">
-        <v>9223</v>
+        <v>9234</v>
       </c>
       <c r="F468" s="13" t="n">
         <v>7</v>
@@ -15808,7 +15808,7 @@
         </is>
       </c>
       <c r="E469" s="13" t="n">
-        <v>9232</v>
+        <v>9243</v>
       </c>
       <c r="F469" s="13" t="n">
         <v>10</v>
@@ -15836,7 +15836,7 @@
         </is>
       </c>
       <c r="E470" s="13" t="n">
-        <v>9245</v>
+        <v>9256</v>
       </c>
       <c r="F470" s="13" t="n">
         <v>10</v>
@@ -15864,7 +15864,7 @@
         </is>
       </c>
       <c r="E471" s="13" t="n">
-        <v>9258</v>
+        <v>9269</v>
       </c>
       <c r="F471" s="13" t="n">
         <v>10</v>
@@ -15892,7 +15892,7 @@
         </is>
       </c>
       <c r="E472" s="13" t="n">
-        <v>9270</v>
+        <v>9281</v>
       </c>
       <c r="F472" s="13" t="n">
         <v>7</v>
@@ -15920,7 +15920,7 @@
         </is>
       </c>
       <c r="E473" s="13" t="n">
-        <v>9280</v>
+        <v>9291</v>
       </c>
       <c r="F473" s="13" t="n">
         <v>17</v>
@@ -15948,7 +15948,7 @@
         </is>
       </c>
       <c r="E474" s="13" t="n">
-        <v>9299</v>
+        <v>9310</v>
       </c>
       <c r="F474" s="13" t="n">
         <v>15</v>
@@ -15976,7 +15976,7 @@
         </is>
       </c>
       <c r="E475" s="13" t="n">
-        <v>9316</v>
+        <v>9327</v>
       </c>
       <c r="F475" s="13" t="n">
         <v>14</v>
@@ -16004,7 +16004,7 @@
         </is>
       </c>
       <c r="E476" s="13" t="n">
-        <v>9333</v>
+        <v>9344</v>
       </c>
       <c r="F476" s="13" t="n">
         <v>21</v>
@@ -16032,7 +16032,7 @@
         </is>
       </c>
       <c r="E477" s="13" t="n">
-        <v>9357</v>
+        <v>9368</v>
       </c>
       <c r="F477" s="13" t="n">
         <v>13</v>
@@ -16060,7 +16060,7 @@
         </is>
       </c>
       <c r="E478" s="13" t="n">
-        <v>9373</v>
+        <v>9384</v>
       </c>
       <c r="F478" s="13" t="n">
         <v>16</v>
@@ -16088,7 +16088,7 @@
         </is>
       </c>
       <c r="E479" s="13" t="n">
-        <v>9392</v>
+        <v>9403</v>
       </c>
       <c r="F479" s="13" t="n">
         <v>15</v>
@@ -16116,7 +16116,7 @@
         </is>
       </c>
       <c r="E480" s="13" t="n">
-        <v>9410</v>
+        <v>9421</v>
       </c>
       <c r="F480" s="13" t="n">
         <v>17</v>
@@ -16144,7 +16144,7 @@
         </is>
       </c>
       <c r="E481" s="13" t="n">
-        <v>9430</v>
+        <v>9441</v>
       </c>
       <c r="F481" s="13" t="n">
         <v>18</v>
@@ -16172,7 +16172,7 @@
         </is>
       </c>
       <c r="E482" s="13" t="n">
-        <v>9450</v>
+        <v>9461</v>
       </c>
       <c r="F482" s="13" t="n">
         <v>16</v>
@@ -16200,7 +16200,7 @@
         </is>
       </c>
       <c r="E483" s="13" t="n">
-        <v>9469</v>
+        <v>9480</v>
       </c>
       <c r="F483" s="13" t="n">
         <v>17</v>
@@ -16228,7 +16228,7 @@
         </is>
       </c>
       <c r="E484" s="13" t="n">
-        <v>9489</v>
+        <v>9500</v>
       </c>
       <c r="F484" s="13" t="n">
         <v>11</v>
@@ -16256,7 +16256,7 @@
         </is>
       </c>
       <c r="E485" s="13" t="n">
-        <v>9503</v>
+        <v>9514</v>
       </c>
       <c r="F485" s="13" t="n">
         <v>13</v>
@@ -16284,7 +16284,7 @@
         </is>
       </c>
       <c r="E486" s="13" t="n">
-        <v>9519</v>
+        <v>9530</v>
       </c>
       <c r="F486" s="13" t="n">
         <v>16</v>
@@ -16312,7 +16312,7 @@
         </is>
       </c>
       <c r="E487" s="13" t="n">
-        <v>9538</v>
+        <v>9549</v>
       </c>
       <c r="F487" s="13" t="n">
         <v>20</v>
@@ -16340,7 +16340,7 @@
         </is>
       </c>
       <c r="E488" s="13" t="n">
-        <v>9561</v>
+        <v>9572</v>
       </c>
       <c r="F488" s="13" t="n">
         <v>10</v>
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="E489" s="13" t="n">
-        <v>9573</v>
+        <v>9584</v>
       </c>
       <c r="F489" s="13" t="n">
         <v>15</v>
@@ -16396,7 +16396,7 @@
         </is>
       </c>
       <c r="E490" s="13" t="n">
-        <v>9591</v>
+        <v>9602</v>
       </c>
       <c r="F490" s="13" t="n">
         <v>15</v>
@@ -16424,7 +16424,7 @@
         </is>
       </c>
       <c r="E491" s="13" t="n">
-        <v>9609</v>
+        <v>9620</v>
       </c>
       <c r="F491" s="13" t="n">
         <v>15</v>
@@ -16452,7 +16452,7 @@
         </is>
       </c>
       <c r="E492" s="13" t="n">
-        <v>9627</v>
+        <v>9638</v>
       </c>
       <c r="F492" s="13" t="n">
         <v>14</v>
@@ -16480,7 +16480,7 @@
         </is>
       </c>
       <c r="E493" s="13" t="n">
-        <v>9644</v>
+        <v>9655</v>
       </c>
       <c r="F493" s="13" t="n">
         <v>14</v>
@@ -16508,7 +16508,7 @@
         </is>
       </c>
       <c r="E494" s="13" t="n">
-        <v>9661</v>
+        <v>9672</v>
       </c>
       <c r="F494" s="13" t="n">
         <v>17</v>
@@ -16536,7 +16536,7 @@
         </is>
       </c>
       <c r="E495" s="13" t="n">
-        <v>9681</v>
+        <v>9692</v>
       </c>
       <c r="F495" s="13" t="n">
         <v>15</v>
@@ -16564,7 +16564,7 @@
         </is>
       </c>
       <c r="E496" s="13" t="n">
-        <v>9698</v>
+        <v>9709</v>
       </c>
       <c r="F496" s="13" t="n">
         <v>20</v>
@@ -16592,7 +16592,7 @@
         </is>
       </c>
       <c r="E497" s="13" t="n">
-        <v>9723</v>
+        <v>9734</v>
       </c>
       <c r="F497" s="13" t="n">
         <v>13</v>
@@ -16620,7 +16620,7 @@
         </is>
       </c>
       <c r="E498" s="13" t="n">
-        <v>9739</v>
+        <v>9750</v>
       </c>
       <c r="F498" s="13" t="n">
         <v>15</v>
@@ -16648,7 +16648,7 @@
         </is>
       </c>
       <c r="E499" s="13" t="n">
-        <v>9757</v>
+        <v>9768</v>
       </c>
       <c r="F499" s="13" t="n">
         <v>16</v>
@@ -16676,7 +16676,7 @@
         </is>
       </c>
       <c r="E500" s="13" t="n">
-        <v>9776</v>
+        <v>9787</v>
       </c>
       <c r="F500" s="13" t="n">
         <v>4</v>
@@ -16704,7 +16704,7 @@
         </is>
       </c>
       <c r="E501" s="13" t="n">
-        <v>9782</v>
+        <v>9793</v>
       </c>
       <c r="F501" s="13" t="n">
         <v>14</v>
@@ -16732,7 +16732,7 @@
         </is>
       </c>
       <c r="E502" s="13" t="n">
-        <v>9799</v>
+        <v>9810</v>
       </c>
       <c r="F502" s="13" t="n">
         <v>16</v>
@@ -16760,7 +16760,7 @@
         </is>
       </c>
       <c r="E503" s="13" t="n">
-        <v>9818</v>
+        <v>9829</v>
       </c>
       <c r="F503" s="13" t="n">
         <v>14</v>
@@ -16788,7 +16788,7 @@
         </is>
       </c>
       <c r="E504" s="13" t="n">
-        <v>9835</v>
+        <v>9846</v>
       </c>
       <c r="F504" s="13" t="n">
         <v>15</v>
@@ -16816,7 +16816,7 @@
         </is>
       </c>
       <c r="E505" s="13" t="n">
-        <v>9852</v>
+        <v>9863</v>
       </c>
       <c r="F505" s="13" t="n">
         <v>15</v>
@@ -16844,7 +16844,7 @@
         </is>
       </c>
       <c r="E506" s="13" t="n">
-        <v>9869</v>
+        <v>9880</v>
       </c>
       <c r="F506" s="13" t="n">
         <v>11</v>
@@ -16872,7 +16872,7 @@
         </is>
       </c>
       <c r="E507" s="13" t="n">
-        <v>9883</v>
+        <v>9894</v>
       </c>
       <c r="F507" s="13" t="n">
         <v>15</v>
@@ -16900,7 +16900,7 @@
         </is>
       </c>
       <c r="E508" s="13" t="n">
-        <v>9901</v>
+        <v>9912</v>
       </c>
       <c r="F508" s="13" t="n">
         <v>14</v>
@@ -16928,7 +16928,7 @@
         </is>
       </c>
       <c r="E509" s="13" t="n">
-        <v>9917</v>
+        <v>9928</v>
       </c>
       <c r="F509" s="13" t="n">
         <v>15</v>
@@ -16956,7 +16956,7 @@
         </is>
       </c>
       <c r="E510" s="13" t="n">
-        <v>9934</v>
+        <v>9945</v>
       </c>
       <c r="F510" s="13" t="n">
         <v>14</v>
@@ -16984,7 +16984,7 @@
         </is>
       </c>
       <c r="E511" s="13" t="n">
-        <v>9951</v>
+        <v>9962</v>
       </c>
       <c r="F511" s="13" t="n">
         <v>14</v>
@@ -17012,7 +17012,7 @@
         </is>
       </c>
       <c r="E512" s="13" t="n">
-        <v>9968</v>
+        <v>9979</v>
       </c>
       <c r="F512" s="13" t="n">
         <v>14</v>
@@ -17040,7 +17040,7 @@
         </is>
       </c>
       <c r="E513" s="13" t="n">
-        <v>9985</v>
+        <v>9996</v>
       </c>
       <c r="F513" s="13" t="n">
         <v>13</v>
@@ -17068,7 +17068,7 @@
         </is>
       </c>
       <c r="E514" s="13" t="n">
-        <v>10001</v>
+        <v>10012</v>
       </c>
       <c r="F514" s="13" t="n">
         <v>15</v>
@@ -17096,7 +17096,7 @@
         </is>
       </c>
       <c r="E515" s="13" t="n">
-        <v>10019</v>
+        <v>10030</v>
       </c>
       <c r="F515" s="13" t="n">
         <v>14</v>
@@ -17124,7 +17124,7 @@
         </is>
       </c>
       <c r="E516" s="13" t="n">
-        <v>10035</v>
+        <v>10046</v>
       </c>
       <c r="F516" s="13" t="n">
         <v>14</v>
@@ -17152,7 +17152,7 @@
         </is>
       </c>
       <c r="E517" s="13" t="n">
-        <v>10052</v>
+        <v>10063</v>
       </c>
       <c r="F517" s="13" t="n">
         <v>14</v>
@@ -17180,7 +17180,7 @@
         </is>
       </c>
       <c r="E518" s="13" t="n">
-        <v>10069</v>
+        <v>10080</v>
       </c>
       <c r="F518" s="13" t="n">
         <v>13</v>
@@ -17208,7 +17208,7 @@
         </is>
       </c>
       <c r="E519" s="13" t="n">
-        <v>10084</v>
+        <v>10095</v>
       </c>
       <c r="F519" s="13" t="n">
         <v>10</v>
@@ -17236,7 +17236,7 @@
         </is>
       </c>
       <c r="E520" s="13" t="n">
-        <v>10096</v>
+        <v>10107</v>
       </c>
       <c r="F520" s="13" t="n">
         <v>10</v>
@@ -17264,7 +17264,7 @@
         </is>
       </c>
       <c r="E521" s="13" t="n">
-        <v>10109</v>
+        <v>10120</v>
       </c>
       <c r="F521" s="13" t="n">
         <v>11</v>
@@ -17292,7 +17292,7 @@
         </is>
       </c>
       <c r="E522" s="13" t="n">
-        <v>10123</v>
+        <v>10134</v>
       </c>
       <c r="F522" s="13" t="n">
         <v>10</v>
@@ -17320,7 +17320,7 @@
         </is>
       </c>
       <c r="E523" s="13" t="n">
-        <v>10135</v>
+        <v>10146</v>
       </c>
       <c r="F523" s="13" t="n">
         <v>10</v>
@@ -17348,7 +17348,7 @@
         </is>
       </c>
       <c r="E524" s="13" t="n">
-        <v>10148</v>
+        <v>10159</v>
       </c>
       <c r="F524" s="13" t="n">
         <v>11</v>
@@ -17376,7 +17376,7 @@
         </is>
       </c>
       <c r="E525" s="13" t="n">
-        <v>10162</v>
+        <v>10173</v>
       </c>
       <c r="F525" s="13" t="n">
         <v>8</v>
@@ -17404,7 +17404,7 @@
         </is>
       </c>
       <c r="E526" s="13" t="n">
-        <v>10172</v>
+        <v>10183</v>
       </c>
       <c r="F526" s="13" t="n">
         <v>11</v>
@@ -17432,7 +17432,7 @@
         </is>
       </c>
       <c r="E527" s="13" t="n">
-        <v>10186</v>
+        <v>10197</v>
       </c>
       <c r="F527" s="13" t="n">
         <v>8</v>
@@ -17460,7 +17460,7 @@
         </is>
       </c>
       <c r="E528" s="13" t="n">
-        <v>10196</v>
+        <v>10207</v>
       </c>
       <c r="F528" s="13" t="n">
         <v>12</v>
@@ -17488,7 +17488,7 @@
         </is>
       </c>
       <c r="E529" s="13" t="n">
-        <v>10211</v>
+        <v>10222</v>
       </c>
       <c r="F529" s="13" t="n">
         <v>15</v>
@@ -17516,7 +17516,7 @@
         </is>
       </c>
       <c r="E530" s="13" t="n">
-        <v>10229</v>
+        <v>10240</v>
       </c>
       <c r="F530" s="13" t="n">
         <v>13</v>
@@ -17544,7 +17544,7 @@
         </is>
       </c>
       <c r="E531" s="13" t="n">
-        <v>10245</v>
+        <v>10256</v>
       </c>
       <c r="F531" s="13" t="n">
         <v>14</v>
@@ -17572,7 +17572,7 @@
         </is>
       </c>
       <c r="E532" s="13" t="n">
-        <v>10262</v>
+        <v>10273</v>
       </c>
       <c r="F532" s="13" t="n">
         <v>12</v>
@@ -17600,7 +17600,7 @@
         </is>
       </c>
       <c r="E533" s="13" t="n">
-        <v>10277</v>
+        <v>10288</v>
       </c>
       <c r="F533" s="13" t="n">
         <v>13</v>
@@ -17628,7 +17628,7 @@
         </is>
       </c>
       <c r="E534" s="13" t="n">
-        <v>10292</v>
+        <v>10303</v>
       </c>
       <c r="F534" s="13" t="n">
         <v>12</v>
@@ -17656,7 +17656,7 @@
         </is>
       </c>
       <c r="E535" s="13" t="n">
-        <v>10306</v>
+        <v>10317</v>
       </c>
       <c r="F535" s="13" t="n">
         <v>9</v>
@@ -17684,7 +17684,7 @@
         </is>
       </c>
       <c r="E536" s="13" t="n">
-        <v>10318</v>
+        <v>10329</v>
       </c>
       <c r="F536" s="13" t="n">
         <v>8</v>
@@ -17712,7 +17712,7 @@
         </is>
       </c>
       <c r="E537" s="13" t="n">
-        <v>10328</v>
+        <v>10339</v>
       </c>
       <c r="F537" s="13" t="n">
         <v>7</v>
@@ -17740,7 +17740,7 @@
         </is>
       </c>
       <c r="E538" s="13" t="n">
-        <v>10337</v>
+        <v>10348</v>
       </c>
       <c r="F538" s="13" t="n">
         <v>12</v>
@@ -17768,7 +17768,7 @@
         </is>
       </c>
       <c r="E539" s="13" t="n">
-        <v>10351</v>
+        <v>10362</v>
       </c>
       <c r="F539" s="13" t="n">
         <v>10</v>
@@ -17796,7 +17796,7 @@
         </is>
       </c>
       <c r="E540" s="13" t="n">
-        <v>10364</v>
+        <v>10375</v>
       </c>
       <c r="F540" s="13" t="n">
         <v>11</v>
@@ -17824,7 +17824,7 @@
         </is>
       </c>
       <c r="E541" s="13" t="n">
-        <v>10378</v>
+        <v>10389</v>
       </c>
       <c r="F541" s="13" t="n">
         <v>10</v>
@@ -17852,7 +17852,7 @@
         </is>
       </c>
       <c r="E542" s="13" t="n">
-        <v>10390</v>
+        <v>10401</v>
       </c>
       <c r="F542" s="13" t="n">
         <v>11</v>
@@ -17880,7 +17880,7 @@
         </is>
       </c>
       <c r="E543" s="13" t="n">
-        <v>10404</v>
+        <v>10415</v>
       </c>
       <c r="F543" s="13" t="n">
         <v>10</v>
@@ -17908,7 +17908,7 @@
         </is>
       </c>
       <c r="E544" s="13" t="n">
-        <v>10417</v>
+        <v>10428</v>
       </c>
       <c r="F544" s="13" t="n">
         <v>8</v>
@@ -17936,7 +17936,7 @@
         </is>
       </c>
       <c r="E545" s="13" t="n">
-        <v>10427</v>
+        <v>10438</v>
       </c>
       <c r="F545" s="13" t="n">
         <v>11</v>
@@ -17964,7 +17964,7 @@
         </is>
       </c>
       <c r="E546" s="13" t="n">
-        <v>10441</v>
+        <v>10452</v>
       </c>
       <c r="F546" s="13" t="n">
         <v>11</v>
@@ -17992,7 +17992,7 @@
         </is>
       </c>
       <c r="E547" s="13" t="n">
-        <v>10455</v>
+        <v>10466</v>
       </c>
       <c r="F547" s="13" t="n">
         <v>9</v>
@@ -18020,7 +18020,7 @@
         </is>
       </c>
       <c r="E548" s="13" t="n">
-        <v>10466</v>
+        <v>10477</v>
       </c>
       <c r="F548" s="13" t="n">
         <v>11</v>
@@ -18048,7 +18048,7 @@
         </is>
       </c>
       <c r="E549" s="13" t="n">
-        <v>10480</v>
+        <v>10491</v>
       </c>
       <c r="F549" s="13" t="n">
         <v>13</v>
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="E550" s="13" t="n">
-        <v>10496</v>
+        <v>10507</v>
       </c>
       <c r="F550" s="13" t="n">
         <v>10</v>
@@ -18104,7 +18104,7 @@
         </is>
       </c>
       <c r="E551" s="13" t="n">
-        <v>10508</v>
+        <v>10519</v>
       </c>
       <c r="F551" s="13" t="n">
         <v>12</v>
@@ -18132,7 +18132,7 @@
         </is>
       </c>
       <c r="E552" s="13" t="n">
-        <v>10523</v>
+        <v>10534</v>
       </c>
       <c r="F552" s="13" t="n">
         <v>10</v>
@@ -18160,7 +18160,7 @@
         </is>
       </c>
       <c r="E553" s="13" t="n">
-        <v>10536</v>
+        <v>10547</v>
       </c>
       <c r="F553" s="13" t="n">
         <v>10</v>
@@ -18188,7 +18188,7 @@
         </is>
       </c>
       <c r="E554" s="13" t="n">
-        <v>10548</v>
+        <v>10559</v>
       </c>
       <c r="F554" s="13" t="n">
         <v>10</v>
@@ -18216,7 +18216,7 @@
         </is>
       </c>
       <c r="E555" s="13" t="n">
-        <v>10561</v>
+        <v>10572</v>
       </c>
       <c r="F555" s="13" t="n">
         <v>10</v>
@@ -18244,7 +18244,7 @@
         </is>
       </c>
       <c r="E556" s="13" t="n">
-        <v>10574</v>
+        <v>10585</v>
       </c>
       <c r="F556" s="13" t="n">
         <v>8</v>
@@ -18272,7 +18272,7 @@
         </is>
       </c>
       <c r="E557" s="13" t="n">
-        <v>10584</v>
+        <v>10595</v>
       </c>
       <c r="F557" s="13" t="n">
         <v>11</v>
@@ -18300,7 +18300,7 @@
         </is>
       </c>
       <c r="E558" s="13" t="n">
-        <v>10598</v>
+        <v>10609</v>
       </c>
       <c r="F558" s="13" t="n">
         <v>8</v>
@@ -18328,7 +18328,7 @@
         </is>
       </c>
       <c r="E559" s="13" t="n">
-        <v>10608</v>
+        <v>10619</v>
       </c>
       <c r="F559" s="13" t="n">
         <v>10</v>
@@ -18356,7 +18356,7 @@
         </is>
       </c>
       <c r="E560" s="13" t="n">
-        <v>10620</v>
+        <v>10631</v>
       </c>
       <c r="F560" s="13" t="n">
         <v>11</v>
@@ -18384,7 +18384,7 @@
         </is>
       </c>
       <c r="E561" s="13" t="n">
-        <v>10634</v>
+        <v>10645</v>
       </c>
       <c r="F561" s="13" t="n">
         <v>7</v>
@@ -18412,7 +18412,7 @@
         </is>
       </c>
       <c r="E562" s="13" t="n">
-        <v>10643</v>
+        <v>10654</v>
       </c>
       <c r="F562" s="13" t="n">
         <v>6</v>
@@ -18440,7 +18440,7 @@
         </is>
       </c>
       <c r="E563" s="13" t="n">
-        <v>10652</v>
+        <v>10663</v>
       </c>
       <c r="F563" s="13" t="n">
         <v>4</v>
@@ -18468,7 +18468,7 @@
         </is>
       </c>
       <c r="E564" s="13" t="n">
-        <v>10658</v>
+        <v>10669</v>
       </c>
       <c r="F564" s="13" t="n">
         <v>5</v>
@@ -18496,7 +18496,7 @@
         </is>
       </c>
       <c r="E565" s="13" t="n">
-        <v>10665</v>
+        <v>10676</v>
       </c>
       <c r="F565" s="13" t="n">
         <v>1</v>
@@ -18524,7 +18524,7 @@
         </is>
       </c>
       <c r="E566" s="13" t="n">
-        <v>10668</v>
+        <v>10679</v>
       </c>
       <c r="F566" s="13" t="n">
         <v>8</v>
@@ -18552,7 +18552,7 @@
         </is>
       </c>
       <c r="E567" s="13" t="n">
-        <v>10679</v>
+        <v>10690</v>
       </c>
       <c r="F567" s="13" t="n">
         <v>9</v>
@@ -18580,7 +18580,7 @@
         </is>
       </c>
       <c r="E568" s="13" t="n">
-        <v>10691</v>
+        <v>10702</v>
       </c>
       <c r="F568" s="13" t="n">
         <v>8</v>
@@ -18608,7 +18608,7 @@
         </is>
       </c>
       <c r="E569" s="13" t="n">
-        <v>10701</v>
+        <v>10712</v>
       </c>
       <c r="F569" s="13" t="n">
         <v>8</v>
@@ -18636,7 +18636,7 @@
         </is>
       </c>
       <c r="E570" s="13" t="n">
-        <v>10712</v>
+        <v>10723</v>
       </c>
       <c r="F570" s="13" t="n">
         <v>8</v>
@@ -18664,7 +18664,7 @@
         </is>
       </c>
       <c r="E571" s="13" t="n">
-        <v>10722</v>
+        <v>10733</v>
       </c>
       <c r="F571" s="13" t="n">
         <v>8</v>
@@ -18692,7 +18692,7 @@
         </is>
       </c>
       <c r="E572" s="13" t="n">
-        <v>10733</v>
+        <v>10744</v>
       </c>
       <c r="F572" s="13" t="n">
         <v>8</v>
@@ -18720,7 +18720,7 @@
         </is>
       </c>
       <c r="E573" s="13" t="n">
-        <v>10743</v>
+        <v>10754</v>
       </c>
       <c r="F573" s="13" t="n">
         <v>9</v>
@@ -18748,7 +18748,7 @@
         </is>
       </c>
       <c r="E574" s="13" t="n">
-        <v>10755</v>
+        <v>10766</v>
       </c>
       <c r="F574" s="13" t="n">
         <v>8</v>
@@ -18776,7 +18776,7 @@
         </is>
       </c>
       <c r="E575" s="13" t="n">
-        <v>10765</v>
+        <v>10776</v>
       </c>
       <c r="F575" s="13" t="n">
         <v>8</v>
@@ -18804,7 +18804,7 @@
         </is>
       </c>
       <c r="E576" s="13" t="n">
-        <v>10776</v>
+        <v>10787</v>
       </c>
       <c r="F576" s="13" t="n">
         <v>8</v>
@@ -18832,7 +18832,7 @@
         </is>
       </c>
       <c r="E577" s="13" t="n">
-        <v>10787</v>
+        <v>10798</v>
       </c>
       <c r="F577" s="13" t="n">
         <v>8</v>
@@ -18860,7 +18860,7 @@
         </is>
       </c>
       <c r="E578" s="13" t="n">
-        <v>10797</v>
+        <v>10808</v>
       </c>
       <c r="F578" s="13" t="n">
         <v>8</v>
@@ -18888,7 +18888,7 @@
         </is>
       </c>
       <c r="E579" s="13" t="n">
-        <v>10808</v>
+        <v>10819</v>
       </c>
       <c r="F579" s="13" t="n">
         <v>8</v>
@@ -18916,7 +18916,7 @@
         </is>
       </c>
       <c r="E580" s="13" t="n">
-        <v>10818</v>
+        <v>10829</v>
       </c>
       <c r="F580" s="13" t="n">
         <v>8</v>
@@ -18944,7 +18944,7 @@
         </is>
       </c>
       <c r="E581" s="13" t="n">
-        <v>10829</v>
+        <v>10840</v>
       </c>
       <c r="F581" s="13" t="n">
         <v>6</v>
@@ -18972,7 +18972,7 @@
         </is>
       </c>
       <c r="E582" s="13" t="n">
-        <v>10837</v>
+        <v>10848</v>
       </c>
       <c r="F582" s="13" t="n">
         <v>2</v>
@@ -19000,7 +19000,7 @@
         </is>
       </c>
       <c r="E583" s="13" t="n">
-        <v>10841</v>
+        <v>10852</v>
       </c>
       <c r="F583" s="13" t="n">
         <v>8</v>
@@ -19028,7 +19028,7 @@
         </is>
       </c>
       <c r="E584" s="13" t="n">
-        <v>10852</v>
+        <v>10863</v>
       </c>
       <c r="F584" s="13" t="n">
         <v>1</v>
@@ -19056,7 +19056,7 @@
         </is>
       </c>
       <c r="E585" s="13" t="n">
-        <v>10855</v>
+        <v>10866</v>
       </c>
       <c r="F585" s="13" t="n">
         <v>4</v>
@@ -19084,7 +19084,7 @@
         </is>
       </c>
       <c r="E586" s="13" t="n">
-        <v>10861</v>
+        <v>10872</v>
       </c>
       <c r="F586" s="13" t="n">
         <v>1</v>
@@ -19112,7 +19112,7 @@
         </is>
       </c>
       <c r="E587" s="13" t="n">
-        <v>10864</v>
+        <v>10875</v>
       </c>
       <c r="F587" s="13" t="n">
         <v>1</v>
@@ -19140,7 +19140,7 @@
         </is>
       </c>
       <c r="E588" s="13" t="n">
-        <v>10868</v>
+        <v>10879</v>
       </c>
       <c r="F588" s="13" t="n">
         <v>1</v>
@@ -19168,7 +19168,7 @@
         </is>
       </c>
       <c r="E589" s="13" t="n">
-        <v>10871</v>
+        <v>10882</v>
       </c>
       <c r="F589" s="13" t="n">
         <v>1</v>
@@ -19196,7 +19196,7 @@
         </is>
       </c>
       <c r="E590" s="13" t="n">
-        <v>10874</v>
+        <v>10885</v>
       </c>
       <c r="F590" s="13" t="n">
         <v>10</v>
@@ -19224,7 +19224,7 @@
         </is>
       </c>
       <c r="E591" s="13" t="n">
-        <v>10886</v>
+        <v>10897</v>
       </c>
       <c r="F591" s="13" t="n">
         <v>8</v>
@@ -19252,7 +19252,7 @@
         </is>
       </c>
       <c r="E592" s="13" t="n">
-        <v>10896</v>
+        <v>10907</v>
       </c>
       <c r="F592" s="13" t="n">
         <v>11</v>
@@ -19280,7 +19280,7 @@
         </is>
       </c>
       <c r="E593" s="13" t="n">
-        <v>10910</v>
+        <v>10921</v>
       </c>
       <c r="F593" s="13" t="n">
         <v>6</v>
@@ -19308,7 +19308,7 @@
         </is>
       </c>
       <c r="E594" s="13" t="n">
-        <v>10918</v>
+        <v>10929</v>
       </c>
       <c r="F594" s="13" t="n">
         <v>8</v>
@@ -19336,7 +19336,7 @@
         </is>
       </c>
       <c r="E595" s="13" t="n">
-        <v>10929</v>
+        <v>10940</v>
       </c>
       <c r="F595" s="13" t="n">
         <v>5</v>
@@ -19364,7 +19364,7 @@
         </is>
       </c>
       <c r="E596" s="13" t="n">
-        <v>10936</v>
+        <v>10947</v>
       </c>
       <c r="F596" s="13" t="n">
         <v>4</v>
@@ -19392,7 +19392,7 @@
         </is>
       </c>
       <c r="E597" s="13" t="n">
-        <v>10942</v>
+        <v>10953</v>
       </c>
       <c r="F597" s="13" t="n">
         <v>1</v>
@@ -19420,7 +19420,7 @@
         </is>
       </c>
       <c r="E598" s="13" t="n">
-        <v>10945</v>
+        <v>10956</v>
       </c>
       <c r="F598" s="13" t="n">
         <v>8</v>
@@ -19448,7 +19448,7 @@
         </is>
       </c>
       <c r="E599" s="13" t="n">
-        <v>10955</v>
+        <v>10966</v>
       </c>
       <c r="F599" s="13" t="n">
         <v>8</v>
@@ -19476,7 +19476,7 @@
         </is>
       </c>
       <c r="E600" s="13" t="n">
-        <v>10966</v>
+        <v>10977</v>
       </c>
       <c r="F600" s="13" t="n">
         <v>8</v>
@@ -19504,7 +19504,7 @@
         </is>
       </c>
       <c r="E601" s="13" t="n">
-        <v>10976</v>
+        <v>10987</v>
       </c>
       <c r="F601" s="13" t="n">
         <v>7</v>
@@ -19532,7 +19532,7 @@
         </is>
       </c>
       <c r="E602" s="13" t="n">
-        <v>10986</v>
+        <v>10997</v>
       </c>
       <c r="F602" s="13" t="n">
         <v>8</v>
@@ -19560,7 +19560,7 @@
         </is>
       </c>
       <c r="E603" s="13" t="n">
-        <v>10996</v>
+        <v>11007</v>
       </c>
       <c r="F603" s="13" t="n">
         <v>8</v>
@@ -19588,7 +19588,7 @@
         </is>
       </c>
       <c r="E604" s="13" t="n">
-        <v>11007</v>
+        <v>11018</v>
       </c>
       <c r="F604" s="13" t="n">
         <v>4</v>
@@ -19616,7 +19616,7 @@
         </is>
       </c>
       <c r="E605" s="13" t="n">
-        <v>11013</v>
+        <v>11024</v>
       </c>
       <c r="F605" s="13" t="n">
         <v>32</v>
@@ -19644,7 +19644,7 @@
         </is>
       </c>
       <c r="E606" s="13" t="n">
-        <v>11049</v>
+        <v>11060</v>
       </c>
       <c r="F606" s="13" t="n">
         <v>20</v>
@@ -19672,7 +19672,7 @@
         </is>
       </c>
       <c r="E607" s="13" t="n">
-        <v>11072</v>
+        <v>11083</v>
       </c>
       <c r="F607" s="13" t="n">
         <v>59</v>
@@ -19700,7 +19700,7 @@
         </is>
       </c>
       <c r="E608" s="13" t="n">
-        <v>11136</v>
+        <v>11147</v>
       </c>
       <c r="F608" s="13" t="n">
         <v>58</v>
@@ -19728,7 +19728,7 @@
         </is>
       </c>
       <c r="E609" s="13" t="n">
-        <v>11200</v>
+        <v>11211</v>
       </c>
       <c r="F609" s="13" t="n">
         <v>24</v>
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="E610" s="13" t="n">
-        <v>11227</v>
+        <v>11238</v>
       </c>
       <c r="F610" s="13" t="n">
         <v>39</v>
@@ -19784,7 +19784,7 @@
         </is>
       </c>
       <c r="E611" s="13" t="n">
-        <v>11270</v>
+        <v>11281</v>
       </c>
       <c r="F611" s="13" t="n">
         <v>47</v>
@@ -19812,7 +19812,7 @@
         </is>
       </c>
       <c r="E612" s="13" t="n">
-        <v>11322</v>
+        <v>11333</v>
       </c>
       <c r="F612" s="13" t="n">
         <v>14</v>
@@ -19840,7 +19840,7 @@
         </is>
       </c>
       <c r="E613" s="13" t="n">
-        <v>11338</v>
+        <v>11349</v>
       </c>
       <c r="F613" s="13" t="n">
         <v>12</v>
@@ -19868,7 +19868,7 @@
         </is>
       </c>
       <c r="E614" s="13" t="n">
-        <v>11353</v>
+        <v>11364</v>
       </c>
       <c r="F614" s="13" t="n">
         <v>12</v>
@@ -19896,7 +19896,7 @@
         </is>
       </c>
       <c r="E615" s="13" t="n">
-        <v>11368</v>
+        <v>11379</v>
       </c>
       <c r="F615" s="13" t="n">
         <v>12</v>
@@ -19924,7 +19924,7 @@
         </is>
       </c>
       <c r="E616" s="13" t="n">
-        <v>11383</v>
+        <v>11394</v>
       </c>
       <c r="F616" s="13" t="n">
         <v>12</v>
@@ -19952,7 +19952,7 @@
         </is>
       </c>
       <c r="E617" s="13" t="n">
-        <v>11397</v>
+        <v>11408</v>
       </c>
       <c r="F617" s="13" t="n">
         <v>12</v>
@@ -19980,7 +19980,7 @@
         </is>
       </c>
       <c r="E618" s="13" t="n">
-        <v>11411</v>
+        <v>11422</v>
       </c>
       <c r="F618" s="13" t="n">
         <v>10</v>
@@ -20008,7 +20008,7 @@
         </is>
       </c>
       <c r="E619" s="13" t="n">
-        <v>11424</v>
+        <v>11435</v>
       </c>
       <c r="F619" s="13" t="n">
         <v>12</v>
@@ -20036,7 +20036,7 @@
         </is>
       </c>
       <c r="E620" s="13" t="n">
-        <v>11439</v>
+        <v>11450</v>
       </c>
       <c r="F620" s="13" t="n">
         <v>12</v>
@@ -20064,7 +20064,7 @@
         </is>
       </c>
       <c r="E621" s="13" t="n">
-        <v>11453</v>
+        <v>11464</v>
       </c>
       <c r="F621" s="13" t="n">
         <v>13</v>
@@ -20092,7 +20092,7 @@
         </is>
       </c>
       <c r="E622" s="13" t="n">
-        <v>11468</v>
+        <v>11479</v>
       </c>
       <c r="F622" s="13" t="n">
         <v>74</v>
@@ -20120,7 +20120,7 @@
         </is>
       </c>
       <c r="E623" s="13" t="n">
-        <v>11549</v>
+        <v>11560</v>
       </c>
       <c r="F623" s="13" t="n">
         <v>120</v>
@@ -20148,7 +20148,7 @@
         </is>
       </c>
       <c r="E624" s="13" t="n">
-        <v>11678</v>
+        <v>11689</v>
       </c>
       <c r="F624" s="13" t="n">
         <v>44</v>
@@ -20176,7 +20176,7 @@
         </is>
       </c>
       <c r="E625" s="13" t="n">
-        <v>11727</v>
+        <v>11738</v>
       </c>
       <c r="F625" s="13" t="n">
         <v>61</v>
@@ -20204,7 +20204,7 @@
         </is>
       </c>
       <c r="E626" s="13" t="n">
-        <v>11794</v>
+        <v>11805</v>
       </c>
       <c r="F626" s="13" t="n">
         <v>52</v>
@@ -20232,7 +20232,7 @@
         </is>
       </c>
       <c r="E627" s="13" t="n">
-        <v>11851</v>
+        <v>11862</v>
       </c>
       <c r="F627" s="13" t="n">
         <v>10</v>
@@ -20260,7 +20260,7 @@
         </is>
       </c>
       <c r="E628" s="13" t="n">
-        <v>11864</v>
+        <v>11875</v>
       </c>
       <c r="F628" s="13" t="n">
         <v>10</v>
@@ -20288,7 +20288,7 @@
         </is>
       </c>
       <c r="E629" s="13" t="n">
-        <v>11877</v>
+        <v>11888</v>
       </c>
       <c r="F629" s="13" t="n">
         <v>9</v>
@@ -20316,7 +20316,7 @@
         </is>
       </c>
       <c r="E630" s="13" t="n">
-        <v>11888</v>
+        <v>11899</v>
       </c>
       <c r="F630" s="13" t="n">
         <v>26</v>
@@ -20344,7 +20344,7 @@
         </is>
       </c>
       <c r="E631" s="13" t="n">
-        <v>11918</v>
+        <v>11929</v>
       </c>
       <c r="F631" s="13" t="n">
         <v>25</v>
@@ -20372,7 +20372,7 @@
         </is>
       </c>
       <c r="E632" s="13" t="n">
-        <v>11947</v>
+        <v>11958</v>
       </c>
       <c r="F632" s="13" t="n">
         <v>18</v>
@@ -20400,7 +20400,7 @@
         </is>
       </c>
       <c r="E633" s="13" t="n">
-        <v>11968</v>
+        <v>11979</v>
       </c>
       <c r="F633" s="13" t="n">
         <v>22</v>
@@ -20428,7 +20428,7 @@
         </is>
       </c>
       <c r="E634" s="13" t="n">
-        <v>11993</v>
+        <v>12004</v>
       </c>
       <c r="F634" s="13" t="n">
         <v>19</v>
@@ -20456,7 +20456,7 @@
         </is>
       </c>
       <c r="E635" s="13" t="n">
-        <v>12015</v>
+        <v>12026</v>
       </c>
       <c r="F635" s="13" t="n">
         <v>20</v>
@@ -20484,7 +20484,7 @@
         </is>
       </c>
       <c r="E636" s="13" t="n">
-        <v>12039</v>
+        <v>12050</v>
       </c>
       <c r="F636" s="13" t="n">
         <v>18</v>
@@ -20512,7 +20512,7 @@
         </is>
       </c>
       <c r="E637" s="13" t="n">
-        <v>12060</v>
+        <v>12071</v>
       </c>
       <c r="F637" s="13" t="n">
         <v>18</v>
@@ -20540,7 +20540,7 @@
         </is>
       </c>
       <c r="E638" s="13" t="n">
-        <v>12081</v>
+        <v>12092</v>
       </c>
       <c r="F638" s="13" t="n">
         <v>17</v>
@@ -20568,7 +20568,7 @@
         </is>
       </c>
       <c r="E639" s="13" t="n">
-        <v>12101</v>
+        <v>12112</v>
       </c>
       <c r="F639" s="13" t="n">
         <v>11</v>
@@ -20596,7 +20596,7 @@
         </is>
       </c>
       <c r="E640" s="13" t="n">
-        <v>12114</v>
+        <v>12125</v>
       </c>
       <c r="F640" s="13" t="n">
         <v>18</v>
@@ -20624,7 +20624,7 @@
         </is>
       </c>
       <c r="E641" s="13" t="n">
-        <v>12136</v>
+        <v>12147</v>
       </c>
       <c r="F641" s="13" t="n">
         <v>18</v>
@@ -20652,7 +20652,7 @@
         </is>
       </c>
       <c r="E642" s="13" t="n">
-        <v>12157</v>
+        <v>12168</v>
       </c>
       <c r="F642" s="13" t="n">
         <v>19</v>
@@ -20680,7 +20680,7 @@
         </is>
       </c>
       <c r="E643" s="13" t="n">
-        <v>12179</v>
+        <v>12190</v>
       </c>
       <c r="F643" s="13" t="n">
         <v>18</v>
@@ -20708,7 +20708,7 @@
         </is>
       </c>
       <c r="E644" s="13" t="n">
-        <v>12200</v>
+        <v>12211</v>
       </c>
       <c r="F644" s="13" t="n">
         <v>18</v>
@@ -20736,7 +20736,7 @@
         </is>
       </c>
       <c r="E645" s="13" t="n">
-        <v>12221</v>
+        <v>12232</v>
       </c>
       <c r="F645" s="13" t="n">
         <v>18</v>
@@ -20764,7 +20764,7 @@
         </is>
       </c>
       <c r="E646" s="13" t="n">
-        <v>12242</v>
+        <v>12253</v>
       </c>
       <c r="F646" s="13" t="n">
         <v>18</v>
@@ -20792,7 +20792,7 @@
         </is>
       </c>
       <c r="E647" s="13" t="n">
-        <v>12263</v>
+        <v>12274</v>
       </c>
       <c r="F647" s="13" t="n">
         <v>19</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="E648" s="13" t="n">
-        <v>12285</v>
+        <v>12296</v>
       </c>
       <c r="F648" s="13" t="n">
         <v>18</v>
@@ -20848,7 +20848,7 @@
         </is>
       </c>
       <c r="E649" s="13" t="n">
-        <v>12306</v>
+        <v>12317</v>
       </c>
       <c r="F649" s="13" t="n">
         <v>17</v>
@@ -20876,7 +20876,7 @@
         </is>
       </c>
       <c r="E650" s="13" t="n">
-        <v>12326</v>
+        <v>12337</v>
       </c>
       <c r="F650" s="13" t="n">
         <v>19</v>
@@ -20904,7 +20904,7 @@
         </is>
       </c>
       <c r="E651" s="13" t="n">
-        <v>12348</v>
+        <v>12359</v>
       </c>
       <c r="F651" s="13" t="n">
         <v>25</v>
@@ -20932,7 +20932,7 @@
         </is>
       </c>
       <c r="E652" s="13" t="n">
-        <v>12376</v>
+        <v>12387</v>
       </c>
       <c r="F652" s="13" t="n">
         <v>18</v>
@@ -20960,7 +20960,7 @@
         </is>
       </c>
       <c r="E653" s="13" t="n">
-        <v>12397</v>
+        <v>12408</v>
       </c>
       <c r="F653" s="13" t="n">
         <v>14</v>
@@ -20988,7 +20988,7 @@
         </is>
       </c>
       <c r="E654" s="13" t="n">
-        <v>12414</v>
+        <v>12425</v>
       </c>
       <c r="F654" s="13" t="n">
         <v>20</v>
@@ -21016,7 +21016,7 @@
         </is>
       </c>
       <c r="E655" s="13" t="n">
-        <v>12437</v>
+        <v>12448</v>
       </c>
       <c r="F655" s="13" t="n">
         <v>16</v>
@@ -21044,7 +21044,7 @@
         </is>
       </c>
       <c r="E656" s="13" t="n">
-        <v>12456</v>
+        <v>12467</v>
       </c>
       <c r="F656" s="13" t="n">
         <v>17</v>
@@ -21072,7 +21072,7 @@
         </is>
       </c>
       <c r="E657" s="13" t="n">
-        <v>12476</v>
+        <v>12487</v>
       </c>
       <c r="F657" s="13" t="n">
         <v>18</v>
@@ -21100,7 +21100,7 @@
         </is>
       </c>
       <c r="E658" s="13" t="n">
-        <v>12497</v>
+        <v>12508</v>
       </c>
       <c r="F658" s="13" t="n">
         <v>18</v>
@@ -21128,7 +21128,7 @@
         </is>
       </c>
       <c r="E659" s="13" t="n">
-        <v>12518</v>
+        <v>12529</v>
       </c>
       <c r="F659" s="13" t="n">
         <v>17</v>
@@ -21156,7 +21156,7 @@
         </is>
       </c>
       <c r="E660" s="13" t="n">
-        <v>12538</v>
+        <v>12549</v>
       </c>
       <c r="F660" s="13" t="n">
         <v>26</v>
@@ -21184,7 +21184,7 @@
         </is>
       </c>
       <c r="E661" s="13" t="n">
-        <v>12567</v>
+        <v>12578</v>
       </c>
       <c r="F661" s="13" t="n">
         <v>28</v>
@@ -21212,7 +21212,7 @@
         </is>
       </c>
       <c r="E662" s="13" t="n">
-        <v>12598</v>
+        <v>12609</v>
       </c>
       <c r="F662" s="13" t="n">
         <v>16</v>
@@ -21240,7 +21240,7 @@
         </is>
       </c>
       <c r="E663" s="13" t="n">
-        <v>12617</v>
+        <v>12628</v>
       </c>
       <c r="F663" s="13" t="n">
         <v>16</v>
@@ -21268,7 +21268,7 @@
         </is>
       </c>
       <c r="E664" s="13" t="n">
-        <v>12636</v>
+        <v>12647</v>
       </c>
       <c r="F664" s="13" t="n">
         <v>16</v>
@@ -21296,7 +21296,7 @@
         </is>
       </c>
       <c r="E665" s="13" t="n">
-        <v>12655</v>
+        <v>12666</v>
       </c>
       <c r="F665" s="13" t="n">
         <v>20</v>
@@ -21324,7 +21324,7 @@
         </is>
       </c>
       <c r="E666" s="13" t="n">
-        <v>12678</v>
+        <v>12689</v>
       </c>
       <c r="F666" s="13" t="n">
         <v>17</v>
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="E667" s="13" t="n">
-        <v>12698</v>
+        <v>12709</v>
       </c>
       <c r="F667" s="13" t="n">
         <v>16</v>
@@ -21380,7 +21380,7 @@
         </is>
       </c>
       <c r="E668" s="13" t="n">
-        <v>12717</v>
+        <v>12728</v>
       </c>
       <c r="F668" s="13" t="n">
         <v>17</v>
@@ -21408,7 +21408,7 @@
         </is>
       </c>
       <c r="E669" s="13" t="n">
-        <v>12737</v>
+        <v>12748</v>
       </c>
       <c r="F669" s="13" t="n">
         <v>17</v>
@@ -21436,7 +21436,7 @@
         </is>
       </c>
       <c r="E670" s="13" t="n">
-        <v>12757</v>
+        <v>12768</v>
       </c>
       <c r="F670" s="13" t="n">
         <v>10</v>
@@ -21464,7 +21464,7 @@
         </is>
       </c>
       <c r="E671" s="13" t="n">
-        <v>12770</v>
+        <v>12781</v>
       </c>
       <c r="F671" s="13" t="n">
         <v>16</v>
@@ -21492,7 +21492,7 @@
         </is>
       </c>
       <c r="E672" s="13" t="n">
-        <v>12789</v>
+        <v>12800</v>
       </c>
       <c r="F672" s="13" t="n">
         <v>17</v>
@@ -21520,7 +21520,7 @@
         </is>
       </c>
       <c r="E673" s="13" t="n">
-        <v>12809</v>
+        <v>12820</v>
       </c>
       <c r="F673" s="13" t="n">
         <v>14</v>
@@ -21548,7 +21548,7 @@
         </is>
       </c>
       <c r="E674" s="13" t="n">
-        <v>12826</v>
+        <v>12837</v>
       </c>
       <c r="F674" s="13" t="n">
         <v>18</v>
@@ -21576,7 +21576,7 @@
         </is>
       </c>
       <c r="E675" s="13" t="n">
-        <v>12847</v>
+        <v>12858</v>
       </c>
       <c r="F675" s="13" t="n">
         <v>17</v>
@@ -21604,7 +21604,7 @@
         </is>
       </c>
       <c r="E676" s="13" t="n">
-        <v>12867</v>
+        <v>12878</v>
       </c>
       <c r="F676" s="13" t="n">
         <v>15</v>
@@ -21632,7 +21632,7 @@
         </is>
       </c>
       <c r="E677" s="13" t="n">
-        <v>12885</v>
+        <v>12896</v>
       </c>
       <c r="F677" s="13" t="n">
         <v>8</v>
@@ -21660,7 +21660,7 @@
         </is>
       </c>
       <c r="E678" s="13" t="n">
-        <v>12895</v>
+        <v>12906</v>
       </c>
       <c r="F678" s="13" t="n">
         <v>14</v>
@@ -21688,7 +21688,7 @@
         </is>
       </c>
       <c r="E679" s="13" t="n">
-        <v>12912</v>
+        <v>12923</v>
       </c>
       <c r="F679" s="13" t="n">
         <v>16</v>
@@ -21716,7 +21716,7 @@
         </is>
       </c>
       <c r="E680" s="13" t="n">
-        <v>12932</v>
+        <v>12943</v>
       </c>
       <c r="F680" s="13" t="n">
         <v>17</v>
@@ -21744,7 +21744,7 @@
         </is>
       </c>
       <c r="E681" s="13" t="n">
-        <v>12952</v>
+        <v>12963</v>
       </c>
       <c r="F681" s="13" t="n">
         <v>16</v>
@@ -21772,7 +21772,7 @@
         </is>
       </c>
       <c r="E682" s="13" t="n">
-        <v>12972</v>
+        <v>12983</v>
       </c>
       <c r="F682" s="13" t="n">
         <v>7</v>
@@ -21800,7 +21800,7 @@
         </is>
       </c>
       <c r="E683" s="13" t="n">
-        <v>12981</v>
+        <v>12992</v>
       </c>
       <c r="F683" s="13" t="n">
         <v>9</v>
@@ -21828,7 +21828,7 @@
         </is>
       </c>
       <c r="E684" s="13" t="n">
-        <v>12993</v>
+        <v>13004</v>
       </c>
       <c r="F684" s="13" t="n">
         <v>10</v>
@@ -21856,7 +21856,7 @@
         </is>
       </c>
       <c r="E685" s="13" t="n">
-        <v>13005</v>
+        <v>13016</v>
       </c>
       <c r="F685" s="13" t="n">
         <v>27</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="E686" s="13" t="n">
-        <v>13036</v>
+        <v>13047</v>
       </c>
       <c r="F686" s="13" t="n">
         <v>17</v>
@@ -21912,7 +21912,7 @@
         </is>
       </c>
       <c r="E687" s="13" t="n">
-        <v>13056</v>
+        <v>13067</v>
       </c>
       <c r="F687" s="13" t="n">
         <v>18</v>
@@ -21940,7 +21940,7 @@
         </is>
       </c>
       <c r="E688" s="13" t="n">
-        <v>13077</v>
+        <v>13088</v>
       </c>
       <c r="F688" s="13" t="n">
         <v>18</v>
@@ -21968,7 +21968,7 @@
         </is>
       </c>
       <c r="E689" s="13" t="n">
-        <v>13098</v>
+        <v>13109</v>
       </c>
       <c r="F689" s="13" t="n">
         <v>11</v>
@@ -21996,7 +21996,7 @@
         </is>
       </c>
       <c r="E690" s="13" t="n">
-        <v>13111</v>
+        <v>13122</v>
       </c>
       <c r="F690" s="13" t="n">
         <v>18</v>
@@ -22024,7 +22024,7 @@
         </is>
       </c>
       <c r="E691" s="13" t="n">
-        <v>13132</v>
+        <v>13143</v>
       </c>
       <c r="F691" s="13" t="n">
         <v>9</v>
@@ -22052,7 +22052,7 @@
         </is>
       </c>
       <c r="E692" s="13" t="n">
-        <v>13144</v>
+        <v>13155</v>
       </c>
       <c r="F692" s="13" t="n">
         <v>10</v>
@@ -22080,7 +22080,7 @@
         </is>
       </c>
       <c r="E693" s="13" t="n">
-        <v>13156</v>
+        <v>13167</v>
       </c>
       <c r="F693" s="13" t="n">
         <v>10</v>
@@ -22108,7 +22108,7 @@
         </is>
       </c>
       <c r="E694" s="13" t="n">
-        <v>13169</v>
+        <v>13180</v>
       </c>
       <c r="F694" s="13" t="n">
         <v>21</v>
@@ -22136,7 +22136,7 @@
         </is>
       </c>
       <c r="E695" s="13" t="n">
-        <v>13193</v>
+        <v>13204</v>
       </c>
       <c r="F695" s="13" t="n">
         <v>11</v>
@@ -22164,7 +22164,7 @@
         </is>
       </c>
       <c r="E696" s="13" t="n">
-        <v>13207</v>
+        <v>13218</v>
       </c>
       <c r="F696" s="13" t="n">
         <v>9</v>
@@ -22192,7 +22192,7 @@
         </is>
       </c>
       <c r="E697" s="13" t="n">
-        <v>13218</v>
+        <v>13229</v>
       </c>
       <c r="F697" s="13" t="n">
         <v>10</v>
@@ -22220,7 +22220,7 @@
         </is>
       </c>
       <c r="E698" s="13" t="n">
-        <v>13231</v>
+        <v>13242</v>
       </c>
       <c r="F698" s="13" t="n">
         <v>10</v>
@@ -22248,7 +22248,7 @@
         </is>
       </c>
       <c r="E699" s="13" t="n">
-        <v>13244</v>
+        <v>13255</v>
       </c>
       <c r="F699" s="13" t="n">
         <v>29</v>
@@ -22276,7 +22276,7 @@
         </is>
       </c>
       <c r="E700" s="13" t="n">
-        <v>13276</v>
+        <v>13287</v>
       </c>
       <c r="F700" s="13" t="n">
         <v>16</v>
@@ -22304,7 +22304,7 @@
         </is>
       </c>
       <c r="E701" s="13" t="n">
-        <v>13295</v>
+        <v>13306</v>
       </c>
       <c r="F701" s="13" t="n">
         <v>15</v>
@@ -22332,7 +22332,7 @@
         </is>
       </c>
       <c r="E702" s="13" t="n">
-        <v>13313</v>
+        <v>13324</v>
       </c>
       <c r="F702" s="13" t="n">
         <v>15</v>
@@ -22360,7 +22360,7 @@
         </is>
       </c>
       <c r="E703" s="13" t="n">
-        <v>13332</v>
+        <v>13343</v>
       </c>
       <c r="F703" s="13" t="n">
         <v>9</v>
@@ -22388,7 +22388,7 @@
         </is>
       </c>
       <c r="E704" s="13" t="n">
-        <v>13344</v>
+        <v>13355</v>
       </c>
       <c r="F704" s="13" t="n">
         <v>15</v>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="E705" s="13" t="n">
-        <v>13362</v>
+        <v>13373</v>
       </c>
       <c r="F705" s="13" t="n">
         <v>8</v>
@@ -22444,7 +22444,7 @@
         </is>
       </c>
       <c r="E706" s="13" t="n">
-        <v>13372</v>
+        <v>13383</v>
       </c>
       <c r="F706" s="13" t="n">
         <v>9</v>
@@ -22472,7 +22472,7 @@
         </is>
       </c>
       <c r="E707" s="13" t="n">
-        <v>13386</v>
+        <v>13397</v>
       </c>
       <c r="F707" s="13" t="n">
         <v>17</v>
@@ -22500,7 +22500,7 @@
         </is>
       </c>
       <c r="E708" s="13" t="n">
-        <v>13406</v>
+        <v>13417</v>
       </c>
       <c r="F708" s="13" t="n">
         <v>7</v>
@@ -22528,7 +22528,7 @@
         </is>
       </c>
       <c r="E709" s="13" t="n">
-        <v>13415</v>
+        <v>13426</v>
       </c>
       <c r="F709" s="13" t="n">
         <v>10</v>
@@ -22556,7 +22556,7 @@
         </is>
       </c>
       <c r="E710" s="13" t="n">
-        <v>13428</v>
+        <v>13439</v>
       </c>
       <c r="F710" s="13" t="n">
         <v>8</v>
@@ -22584,7 +22584,7 @@
         </is>
       </c>
       <c r="E711" s="13" t="n">
-        <v>13439</v>
+        <v>13450</v>
       </c>
       <c r="F711" s="13" t="n">
         <v>10</v>
@@ -22612,7 +22612,7 @@
         </is>
       </c>
       <c r="E712" s="13" t="n">
-        <v>13451</v>
+        <v>13462</v>
       </c>
       <c r="F712" s="13" t="n">
         <v>9</v>
@@ -22640,7 +22640,7 @@
         </is>
       </c>
       <c r="E713" s="13" t="n">
-        <v>13463</v>
+        <v>13474</v>
       </c>
       <c r="F713" s="13" t="n">
         <v>9</v>
@@ -22668,7 +22668,7 @@
         </is>
       </c>
       <c r="E714" s="13" t="n">
-        <v>13474</v>
+        <v>13485</v>
       </c>
       <c r="F714" s="13" t="n">
         <v>9</v>
@@ -22696,7 +22696,7 @@
         </is>
       </c>
       <c r="E715" s="13" t="n">
-        <v>13486</v>
+        <v>13497</v>
       </c>
       <c r="F715" s="13" t="n">
         <v>8</v>
@@ -22724,7 +22724,7 @@
         </is>
       </c>
       <c r="E716" s="13" t="n">
-        <v>13496</v>
+        <v>13507</v>
       </c>
       <c r="F716" s="13" t="n">
         <v>8</v>
@@ -22752,7 +22752,7 @@
         </is>
       </c>
       <c r="E717" s="13" t="n">
-        <v>13506</v>
+        <v>13517</v>
       </c>
       <c r="F717" s="13" t="n">
         <v>8</v>
@@ -22780,7 +22780,7 @@
         </is>
       </c>
       <c r="E718" s="13" t="n">
-        <v>13516</v>
+        <v>13527</v>
       </c>
       <c r="F718" s="13" t="n">
         <v>8</v>
@@ -22808,7 +22808,7 @@
         </is>
       </c>
       <c r="E719" s="13" t="n">
-        <v>13526</v>
+        <v>13537</v>
       </c>
       <c r="F719" s="13" t="n">
         <v>10</v>
@@ -22836,7 +22836,7 @@
         </is>
       </c>
       <c r="E720" s="13" t="n">
-        <v>13539</v>
+        <v>13550</v>
       </c>
       <c r="F720" s="13" t="n">
         <v>9</v>
@@ -22864,7 +22864,7 @@
         </is>
       </c>
       <c r="E721" s="13" t="n">
-        <v>13550</v>
+        <v>13561</v>
       </c>
       <c r="F721" s="13" t="n">
         <v>9</v>
@@ -22892,7 +22892,7 @@
         </is>
       </c>
       <c r="E722" s="13" t="n">
-        <v>13562</v>
+        <v>13573</v>
       </c>
       <c r="F722" s="13" t="n">
         <v>7</v>
@@ -22920,7 +22920,7 @@
         </is>
       </c>
       <c r="E723" s="13" t="n">
-        <v>13571</v>
+        <v>13582</v>
       </c>
       <c r="F723" s="13" t="n">
         <v>8</v>
@@ -22948,7 +22948,7 @@
         </is>
       </c>
       <c r="E724" s="13" t="n">
-        <v>13582</v>
+        <v>13593</v>
       </c>
       <c r="F724" s="13" t="n">
         <v>8</v>
@@ -22976,7 +22976,7 @@
         </is>
       </c>
       <c r="E725" s="13" t="n">
-        <v>13592</v>
+        <v>13603</v>
       </c>
       <c r="F725" s="13" t="n">
         <v>6</v>
@@ -23004,7 +23004,7 @@
         </is>
       </c>
       <c r="E726" s="13" t="n">
-        <v>13601</v>
+        <v>13612</v>
       </c>
       <c r="F726" s="13" t="n">
         <v>7</v>
@@ -23032,7 +23032,7 @@
         </is>
       </c>
       <c r="E727" s="13" t="n">
-        <v>13609</v>
+        <v>13620</v>
       </c>
       <c r="F727" s="13" t="n">
         <v>16</v>
@@ -23060,7 +23060,7 @@
         </is>
       </c>
       <c r="E728" s="13" t="n">
-        <v>13628</v>
+        <v>13639</v>
       </c>
       <c r="F728" s="13" t="n">
         <v>8</v>
@@ -23088,7 +23088,7 @@
         </is>
       </c>
       <c r="E729" s="13" t="n">
-        <v>13638</v>
+        <v>13649</v>
       </c>
       <c r="F729" s="13" t="n">
         <v>8</v>
@@ -23116,7 +23116,7 @@
         </is>
       </c>
       <c r="E730" s="13" t="n">
-        <v>13648</v>
+        <v>13659</v>
       </c>
       <c r="F730" s="13" t="n">
         <v>11</v>
@@ -23144,7 +23144,7 @@
         </is>
       </c>
       <c r="E731" s="13" t="n">
-        <v>13662</v>
+        <v>13673</v>
       </c>
       <c r="F731" s="13" t="n">
         <v>8</v>
@@ -23172,7 +23172,7 @@
         </is>
       </c>
       <c r="E732" s="13" t="n">
-        <v>13672</v>
+        <v>13683</v>
       </c>
       <c r="F732" s="13" t="n">
         <v>9</v>
@@ -23200,7 +23200,7 @@
         </is>
       </c>
       <c r="E733" s="13" t="n">
-        <v>13684</v>
+        <v>13695</v>
       </c>
       <c r="F733" s="13" t="n">
         <v>8</v>
@@ -23228,7 +23228,7 @@
         </is>
       </c>
       <c r="E734" s="13" t="n">
-        <v>13694</v>
+        <v>13705</v>
       </c>
       <c r="F734" s="13" t="n">
         <v>8</v>
@@ -23256,7 +23256,7 @@
         </is>
       </c>
       <c r="E735" s="13" t="n">
-        <v>13705</v>
+        <v>13716</v>
       </c>
       <c r="F735" s="13" t="n">
         <v>8</v>
@@ -23284,7 +23284,7 @@
         </is>
       </c>
       <c r="E736" s="13" t="n">
-        <v>13715</v>
+        <v>13726</v>
       </c>
       <c r="F736" s="13" t="n">
         <v>8</v>
@@ -23312,7 +23312,7 @@
         </is>
       </c>
       <c r="E737" s="13" t="n">
-        <v>13726</v>
+        <v>13737</v>
       </c>
       <c r="F737" s="13" t="n">
         <v>8</v>
@@ -23340,7 +23340,7 @@
         </is>
       </c>
       <c r="E738" s="13" t="n">
-        <v>13736</v>
+        <v>13747</v>
       </c>
       <c r="F738" s="13" t="n">
         <v>8</v>
@@ -23368,7 +23368,7 @@
         </is>
       </c>
       <c r="E739" s="13" t="n">
-        <v>13747</v>
+        <v>13758</v>
       </c>
       <c r="F739" s="13" t="n">
         <v>8</v>
@@ -23396,7 +23396,7 @@
         </is>
       </c>
       <c r="E740" s="13" t="n">
-        <v>13757</v>
+        <v>13768</v>
       </c>
       <c r="F740" s="13" t="n">
         <v>8</v>
@@ -23424,7 +23424,7 @@
         </is>
       </c>
       <c r="E741" s="13" t="n">
-        <v>13768</v>
+        <v>13779</v>
       </c>
       <c r="F741" s="13" t="n">
         <v>8</v>
@@ -23452,7 +23452,7 @@
         </is>
       </c>
       <c r="E742" s="13" t="n">
-        <v>13778</v>
+        <v>13789</v>
       </c>
       <c r="F742" s="13" t="n">
         <v>8</v>
@@ -23480,7 +23480,7 @@
         </is>
       </c>
       <c r="E743" s="13" t="n">
-        <v>13789</v>
+        <v>13800</v>
       </c>
       <c r="F743" s="13" t="n">
         <v>6</v>
@@ -23508,7 +23508,7 @@
         </is>
       </c>
       <c r="E744" s="13" t="n">
-        <v>13797</v>
+        <v>13808</v>
       </c>
       <c r="F744" s="13" t="n">
         <v>8</v>
@@ -23536,7 +23536,7 @@
         </is>
       </c>
       <c r="E745" s="13" t="n">
-        <v>13808</v>
+        <v>13819</v>
       </c>
       <c r="F745" s="13" t="n">
         <v>8</v>
@@ -23564,7 +23564,7 @@
         </is>
       </c>
       <c r="E746" s="13" t="n">
-        <v>13818</v>
+        <v>13829</v>
       </c>
       <c r="F746" s="13" t="n">
         <v>9</v>
@@ -23592,7 +23592,7 @@
         </is>
       </c>
       <c r="E747" s="13" t="n">
-        <v>13830</v>
+        <v>13841</v>
       </c>
       <c r="F747" s="13" t="n">
         <v>9</v>
@@ -23620,7 +23620,7 @@
         </is>
       </c>
       <c r="E748" s="13" t="n">
-        <v>13841</v>
+        <v>13852</v>
       </c>
       <c r="F748" s="13" t="n">
         <v>9</v>
@@ -23648,7 +23648,7 @@
         </is>
       </c>
       <c r="E749" s="13" t="n">
-        <v>13853</v>
+        <v>13864</v>
       </c>
       <c r="F749" s="13" t="n">
         <v>8</v>
@@ -23676,7 +23676,7 @@
         </is>
       </c>
       <c r="E750" s="13" t="n">
-        <v>13863</v>
+        <v>13874</v>
       </c>
       <c r="F750" s="13" t="n">
         <v>5</v>
@@ -23704,7 +23704,7 @@
         </is>
       </c>
       <c r="E751" s="13" t="n">
-        <v>13871</v>
+        <v>13882</v>
       </c>
       <c r="F751" s="13" t="n">
         <v>13</v>
@@ -23732,7 +23732,7 @@
         </is>
       </c>
       <c r="E752" s="13" t="n">
-        <v>13886</v>
+        <v>13897</v>
       </c>
       <c r="F752" s="13" t="n">
         <v>17</v>
@@ -23760,7 +23760,7 @@
         </is>
       </c>
       <c r="E753" s="13" t="n">
-        <v>13906</v>
+        <v>13917</v>
       </c>
       <c r="F753" s="13" t="n">
         <v>8</v>
@@ -23788,7 +23788,7 @@
         </is>
       </c>
       <c r="E754" s="13" t="n">
-        <v>13917</v>
+        <v>13928</v>
       </c>
       <c r="F754" s="13" t="n">
         <v>8</v>
@@ -23816,7 +23816,7 @@
         </is>
       </c>
       <c r="E755" s="13" t="n">
-        <v>13927</v>
+        <v>13938</v>
       </c>
       <c r="F755" s="13" t="n">
         <v>13</v>
@@ -23844,7 +23844,7 @@
         </is>
       </c>
       <c r="E756" s="13" t="n">
-        <v>13943</v>
+        <v>13954</v>
       </c>
       <c r="F756" s="13" t="n">
         <v>9</v>
@@ -23872,7 +23872,7 @@
         </is>
       </c>
       <c r="E757" s="13" t="n">
-        <v>13954</v>
+        <v>13965</v>
       </c>
       <c r="F757" s="13" t="n">
         <v>7</v>
@@ -23900,7 +23900,7 @@
         </is>
       </c>
       <c r="E758" s="13" t="n">
-        <v>13963</v>
+        <v>13974</v>
       </c>
       <c r="F758" s="13" t="n">
         <v>9</v>
@@ -23928,7 +23928,7 @@
         </is>
       </c>
       <c r="E759" s="13" t="n">
-        <v>13975</v>
+        <v>13986</v>
       </c>
       <c r="F759" s="13" t="n">
         <v>12</v>
@@ -23956,7 +23956,7 @@
         </is>
       </c>
       <c r="E760" s="13" t="n">
-        <v>13989</v>
+        <v>14000</v>
       </c>
       <c r="F760" s="13" t="n">
         <v>11</v>
@@ -23984,7 +23984,7 @@
         </is>
       </c>
       <c r="E761" s="13" t="n">
-        <v>14003</v>
+        <v>14014</v>
       </c>
       <c r="F761" s="13" t="n">
         <v>10</v>
@@ -24012,7 +24012,7 @@
         </is>
       </c>
       <c r="E762" s="13" t="n">
-        <v>14016</v>
+        <v>14027</v>
       </c>
       <c r="F762" s="13" t="n">
         <v>10</v>
@@ -24040,7 +24040,7 @@
         </is>
       </c>
       <c r="E763" s="13" t="n">
-        <v>14028</v>
+        <v>14039</v>
       </c>
       <c r="F763" s="13" t="n">
         <v>11</v>
@@ -24068,7 +24068,7 @@
         </is>
       </c>
       <c r="E764" s="13" t="n">
-        <v>14042</v>
+        <v>14053</v>
       </c>
       <c r="F764" s="13" t="n">
         <v>11</v>
@@ -24096,7 +24096,7 @@
         </is>
       </c>
       <c r="E765" s="13" t="n">
-        <v>14056</v>
+        <v>14067</v>
       </c>
       <c r="F765" s="13" t="n">
         <v>9</v>
@@ -24124,7 +24124,7 @@
         </is>
       </c>
       <c r="E766" s="13" t="n">
-        <v>14067</v>
+        <v>14078</v>
       </c>
       <c r="F766" s="13" t="n">
         <v>11</v>
@@ -24152,7 +24152,7 @@
         </is>
       </c>
       <c r="E767" s="13" t="n">
-        <v>14080</v>
+        <v>14091</v>
       </c>
       <c r="F767" s="13" t="n">
         <v>10</v>
@@ -24180,7 +24180,7 @@
         </is>
       </c>
       <c r="E768" s="13" t="n">
-        <v>14093</v>
+        <v>14104</v>
       </c>
       <c r="F768" s="13" t="n">
         <v>9</v>
@@ -24208,7 +24208,7 @@
         </is>
       </c>
       <c r="E769" s="13" t="n">
-        <v>14104</v>
+        <v>14115</v>
       </c>
       <c r="F769" s="13" t="n">
         <v>9</v>
@@ -24236,7 +24236,7 @@
         </is>
       </c>
       <c r="E770" s="13" t="n">
-        <v>14116</v>
+        <v>14127</v>
       </c>
       <c r="F770" s="13" t="n">
         <v>10</v>
@@ -24264,7 +24264,7 @@
         </is>
       </c>
       <c r="E771" s="13" t="n">
-        <v>14129</v>
+        <v>14140</v>
       </c>
       <c r="F771" s="13" t="n">
         <v>15</v>
@@ -24292,7 +24292,7 @@
         </is>
       </c>
       <c r="E772" s="13" t="n">
-        <v>14146</v>
+        <v>14157</v>
       </c>
       <c r="F772" s="13" t="n">
         <v>16</v>
@@ -24320,7 +24320,7 @@
         </is>
       </c>
       <c r="E773" s="13" t="n">
-        <v>14165</v>
+        <v>14176</v>
       </c>
       <c r="F773" s="13" t="n">
         <v>10</v>
@@ -24348,7 +24348,7 @@
         </is>
       </c>
       <c r="E774" s="13" t="n">
-        <v>14177</v>
+        <v>14188</v>
       </c>
       <c r="F774" s="13" t="n">
         <v>9</v>
@@ -24376,7 +24376,7 @@
         </is>
       </c>
       <c r="E775" s="13" t="n">
-        <v>14189</v>
+        <v>14200</v>
       </c>
       <c r="F775" s="13" t="n">
         <v>8</v>
@@ -24404,7 +24404,7 @@
         </is>
       </c>
       <c r="E776" s="13" t="n">
-        <v>14199</v>
+        <v>14210</v>
       </c>
       <c r="F776" s="13" t="n">
         <v>8</v>
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="E777" s="13" t="n">
-        <v>14210</v>
+        <v>14221</v>
       </c>
       <c r="F777" s="13" t="n">
         <v>8</v>
@@ -24460,7 +24460,7 @@
         </is>
       </c>
       <c r="E778" s="13" t="n">
-        <v>14220</v>
+        <v>14231</v>
       </c>
       <c r="F778" s="13" t="n">
         <v>9</v>
@@ -24488,7 +24488,7 @@
         </is>
       </c>
       <c r="E779" s="13" t="n">
-        <v>14232</v>
+        <v>14243</v>
       </c>
       <c r="F779" s="13" t="n">
         <v>8</v>
@@ -24516,7 +24516,7 @@
         </is>
       </c>
       <c r="E780" s="13" t="n">
-        <v>14242</v>
+        <v>14253</v>
       </c>
       <c r="F780" s="13" t="n">
         <v>8</v>
@@ -24544,7 +24544,7 @@
         </is>
       </c>
       <c r="E781" s="13" t="n">
-        <v>14253</v>
+        <v>14264</v>
       </c>
       <c r="F781" s="13" t="n">
         <v>8</v>
@@ -24572,7 +24572,7 @@
         </is>
       </c>
       <c r="E782" s="13" t="n">
-        <v>14263</v>
+        <v>14274</v>
       </c>
       <c r="F782" s="13" t="n">
         <v>8</v>
@@ -24600,7 +24600,7 @@
         </is>
       </c>
       <c r="E783" s="13" t="n">
-        <v>14274</v>
+        <v>14285</v>
       </c>
       <c r="F783" s="13" t="n">
         <v>8</v>
@@ -24628,7 +24628,7 @@
         </is>
       </c>
       <c r="E784" s="13" t="n">
-        <v>14284</v>
+        <v>14295</v>
       </c>
       <c r="F784" s="13" t="n">
         <v>8</v>
@@ -24656,7 +24656,7 @@
         </is>
       </c>
       <c r="E785" s="13" t="n">
-        <v>14295</v>
+        <v>14306</v>
       </c>
       <c r="F785" s="13" t="n">
         <v>8</v>
@@ -24684,7 +24684,7 @@
         </is>
       </c>
       <c r="E786" s="13" t="n">
-        <v>14305</v>
+        <v>14316</v>
       </c>
       <c r="F786" s="13" t="n">
         <v>8</v>
@@ -24712,7 +24712,7 @@
         </is>
       </c>
       <c r="E787" s="13" t="n">
-        <v>14316</v>
+        <v>14327</v>
       </c>
       <c r="F787" s="13" t="n">
         <v>7</v>
@@ -24740,7 +24740,7 @@
         </is>
       </c>
       <c r="E788" s="13" t="n">
-        <v>14325</v>
+        <v>14336</v>
       </c>
       <c r="F788" s="13" t="n">
         <v>8</v>
@@ -24768,7 +24768,7 @@
         </is>
       </c>
       <c r="E789" s="13" t="n">
-        <v>14336</v>
+        <v>14347</v>
       </c>
       <c r="F789" s="13" t="n">
         <v>7</v>
@@ -24796,7 +24796,7 @@
         </is>
       </c>
       <c r="E790" s="13" t="n">
-        <v>14345</v>
+        <v>14356</v>
       </c>
       <c r="F790" s="13" t="n">
         <v>6</v>
@@ -24824,7 +24824,7 @@
         </is>
       </c>
       <c r="E791" s="13" t="n">
-        <v>14354</v>
+        <v>14365</v>
       </c>
       <c r="F791" s="13" t="n">
         <v>8</v>
@@ -24852,7 +24852,7 @@
         </is>
       </c>
       <c r="E792" s="13" t="n">
-        <v>14364</v>
+        <v>14375</v>
       </c>
       <c r="F792" s="13" t="n">
         <v>15</v>
@@ -24880,7 +24880,7 @@
         </is>
       </c>
       <c r="E793" s="13" t="n">
-        <v>14382</v>
+        <v>14393</v>
       </c>
       <c r="F793" s="13" t="n">
         <v>9</v>
@@ -24908,7 +24908,7 @@
         </is>
       </c>
       <c r="E794" s="13" t="n">
-        <v>14394</v>
+        <v>14405</v>
       </c>
       <c r="F794" s="13" t="n">
         <v>9</v>
@@ -24936,7 +24936,7 @@
         </is>
       </c>
       <c r="E795" s="13" t="n">
-        <v>14405</v>
+        <v>14416</v>
       </c>
       <c r="F795" s="13" t="n">
         <v>9</v>
@@ -24964,7 +24964,7 @@
         </is>
       </c>
       <c r="E796" s="13" t="n">
-        <v>14417</v>
+        <v>14428</v>
       </c>
       <c r="F796" s="13" t="n">
         <v>8</v>
@@ -24992,7 +24992,7 @@
         </is>
       </c>
       <c r="E797" s="13" t="n">
-        <v>14427</v>
+        <v>14438</v>
       </c>
       <c r="F797" s="13" t="n">
         <v>8</v>
@@ -25020,7 +25020,7 @@
         </is>
       </c>
       <c r="E798" s="13" t="n">
-        <v>14438</v>
+        <v>14449</v>
       </c>
       <c r="F798" s="13" t="n">
         <v>9</v>
@@ -25048,7 +25048,7 @@
         </is>
       </c>
       <c r="E799" s="13" t="n">
-        <v>14449</v>
+        <v>14460</v>
       </c>
       <c r="F799" s="13" t="n">
         <v>9</v>
@@ -25076,7 +25076,7 @@
         </is>
       </c>
       <c r="E800" s="13" t="n">
-        <v>14461</v>
+        <v>14472</v>
       </c>
       <c r="F800" s="13" t="n">
         <v>8</v>
@@ -25104,7 +25104,7 @@
         </is>
       </c>
       <c r="E801" s="13" t="n">
-        <v>14471</v>
+        <v>14482</v>
       </c>
       <c r="F801" s="13" t="n">
         <v>9</v>
@@ -25132,7 +25132,7 @@
         </is>
       </c>
       <c r="E802" s="13" t="n">
-        <v>14483</v>
+        <v>14494</v>
       </c>
       <c r="F802" s="13" t="n">
         <v>9</v>
@@ -25160,7 +25160,7 @@
         </is>
       </c>
       <c r="E803" s="13" t="n">
-        <v>14494</v>
+        <v>14505</v>
       </c>
       <c r="F803" s="13" t="n">
         <v>9</v>
@@ -25188,7 +25188,7 @@
         </is>
       </c>
       <c r="E804" s="13" t="n">
-        <v>14506</v>
+        <v>14517</v>
       </c>
       <c r="F804" s="13" t="n">
         <v>9</v>
@@ -25216,7 +25216,7 @@
         </is>
       </c>
       <c r="E805" s="13" t="n">
-        <v>14517</v>
+        <v>14528</v>
       </c>
       <c r="F805" s="13" t="n">
         <v>8</v>
@@ -25244,7 +25244,7 @@
         </is>
       </c>
       <c r="E806" s="13" t="n">
-        <v>14528</v>
+        <v>14539</v>
       </c>
       <c r="F806" s="13" t="n">
         <v>7</v>
@@ -25272,7 +25272,7 @@
         </is>
       </c>
       <c r="E807" s="13" t="n">
-        <v>14537</v>
+        <v>14548</v>
       </c>
       <c r="F807" s="13" t="n">
         <v>7</v>
@@ -25300,7 +25300,7 @@
         </is>
       </c>
       <c r="E808" s="13" t="n">
-        <v>14547</v>
+        <v>14558</v>
       </c>
       <c r="F808" s="13" t="n">
         <v>8</v>
@@ -25328,7 +25328,7 @@
         </is>
       </c>
       <c r="E809" s="13" t="n">
-        <v>14557</v>
+        <v>14568</v>
       </c>
       <c r="F809" s="13" t="n">
         <v>9</v>
@@ -25356,7 +25356,7 @@
         </is>
       </c>
       <c r="E810" s="13" t="n">
-        <v>14569</v>
+        <v>14580</v>
       </c>
       <c r="F810" s="13" t="n">
         <v>8</v>
@@ -25384,7 +25384,7 @@
         </is>
       </c>
       <c r="E811" s="13" t="n">
-        <v>14579</v>
+        <v>14590</v>
       </c>
       <c r="F811" s="13" t="n">
         <v>10</v>
@@ -25412,7 +25412,7 @@
         </is>
       </c>
       <c r="E812" s="13" t="n">
-        <v>14592</v>
+        <v>14603</v>
       </c>
       <c r="F812" s="13" t="n">
         <v>9</v>
@@ -25440,7 +25440,7 @@
         </is>
       </c>
       <c r="E813" s="13" t="n">
-        <v>14603</v>
+        <v>14614</v>
       </c>
       <c r="F813" s="13" t="n">
         <v>8</v>
@@ -25468,7 +25468,7 @@
         </is>
       </c>
       <c r="E814" s="13" t="n">
-        <v>14614</v>
+        <v>14625</v>
       </c>
       <c r="F814" s="13" t="n">
         <v>8</v>
@@ -25496,7 +25496,7 @@
         </is>
       </c>
       <c r="E815" s="13" t="n">
-        <v>14624</v>
+        <v>14635</v>
       </c>
       <c r="F815" s="13" t="n">
         <v>7</v>
@@ -25524,7 +25524,7 @@
         </is>
       </c>
       <c r="E816" s="13" t="n">
-        <v>14634</v>
+        <v>14645</v>
       </c>
       <c r="F816" s="13" t="n">
         <v>9</v>
@@ -25552,7 +25552,7 @@
         </is>
       </c>
       <c r="E817" s="13" t="n">
-        <v>14645</v>
+        <v>14656</v>
       </c>
       <c r="F817" s="13" t="n">
         <v>9</v>
@@ -25580,7 +25580,7 @@
         </is>
       </c>
       <c r="E818" s="13" t="n">
-        <v>14657</v>
+        <v>14668</v>
       </c>
       <c r="F818" s="13" t="n">
         <v>8</v>
@@ -25608,7 +25608,7 @@
         </is>
       </c>
       <c r="E819" s="13" t="n">
-        <v>14667</v>
+        <v>14678</v>
       </c>
       <c r="F819" s="13" t="n">
         <v>8</v>
@@ -25636,7 +25636,7 @@
         </is>
       </c>
       <c r="E820" s="13" t="n">
-        <v>14678</v>
+        <v>14689</v>
       </c>
       <c r="F820" s="13" t="n">
         <v>9</v>
@@ -25664,7 +25664,7 @@
         </is>
       </c>
       <c r="E821" s="13" t="n">
-        <v>14689</v>
+        <v>14700</v>
       </c>
       <c r="F821" s="13" t="n">
         <v>8</v>
@@ -25692,7 +25692,7 @@
         </is>
       </c>
       <c r="E822" s="13" t="n">
-        <v>14700</v>
+        <v>14711</v>
       </c>
       <c r="F822" s="13" t="n">
         <v>8</v>
@@ -25720,7 +25720,7 @@
         </is>
       </c>
       <c r="E823" s="13" t="n">
-        <v>14710</v>
+        <v>14721</v>
       </c>
       <c r="F823" s="13" t="n">
         <v>8</v>
@@ -25748,7 +25748,7 @@
         </is>
       </c>
       <c r="E824" s="13" t="n">
-        <v>14721</v>
+        <v>14732</v>
       </c>
       <c r="F824" s="13" t="n">
         <v>8</v>
@@ -25776,7 +25776,7 @@
         </is>
       </c>
       <c r="E825" s="13" t="n">
-        <v>14731</v>
+        <v>14742</v>
       </c>
       <c r="F825" s="13" t="n">
         <v>8</v>
@@ -25804,7 +25804,7 @@
         </is>
       </c>
       <c r="E826" s="13" t="n">
-        <v>14742</v>
+        <v>14753</v>
       </c>
       <c r="F826" s="13" t="n">
         <v>8</v>
@@ -25832,7 +25832,7 @@
         </is>
       </c>
       <c r="E827" s="13" t="n">
-        <v>14752</v>
+        <v>14763</v>
       </c>
       <c r="F827" s="13" t="n">
         <v>6</v>
@@ -25860,7 +25860,7 @@
         </is>
       </c>
       <c r="E828" s="13" t="n">
-        <v>14761</v>
+        <v>14772</v>
       </c>
       <c r="F828" s="13" t="n">
         <v>7</v>
@@ -25888,7 +25888,7 @@
         </is>
       </c>
       <c r="E829" s="13" t="n">
-        <v>14770</v>
+        <v>14781</v>
       </c>
       <c r="F829" s="13" t="n">
         <v>8</v>
@@ -25916,7 +25916,7 @@
         </is>
       </c>
       <c r="E830" s="13" t="n">
-        <v>14781</v>
+        <v>14792</v>
       </c>
       <c r="F830" s="13" t="n">
         <v>8</v>
@@ -25944,7 +25944,7 @@
         </is>
       </c>
       <c r="E831" s="13" t="n">
-        <v>14791</v>
+        <v>14802</v>
       </c>
       <c r="F831" s="13" t="n">
         <v>9</v>
@@ -25972,7 +25972,7 @@
         </is>
       </c>
       <c r="E832" s="13" t="n">
-        <v>14803</v>
+        <v>14814</v>
       </c>
       <c r="F832" s="13" t="n">
         <v>7</v>
@@ -26000,7 +26000,7 @@
         </is>
       </c>
       <c r="E833" s="13" t="n">
-        <v>14812</v>
+        <v>14823</v>
       </c>
       <c r="F833" s="13" t="n">
         <v>9</v>
@@ -26028,7 +26028,7 @@
         </is>
       </c>
       <c r="E834" s="13" t="n">
-        <v>14824</v>
+        <v>14835</v>
       </c>
       <c r="F834" s="13" t="n">
         <v>8</v>
@@ -26056,7 +26056,7 @@
         </is>
       </c>
       <c r="E835" s="13" t="n">
-        <v>14834</v>
+        <v>14845</v>
       </c>
       <c r="F835" s="13" t="n">
         <v>6</v>
@@ -26084,7 +26084,7 @@
         </is>
       </c>
       <c r="E836" s="13" t="n">
-        <v>14843</v>
+        <v>14854</v>
       </c>
       <c r="F836" s="13" t="n">
         <v>8</v>
@@ -26112,7 +26112,7 @@
         </is>
       </c>
       <c r="E837" s="13" t="n">
-        <v>14853</v>
+        <v>14864</v>
       </c>
       <c r="F837" s="13" t="n">
         <v>9</v>
@@ -26140,7 +26140,7 @@
         </is>
       </c>
       <c r="E838" s="13" t="n">
-        <v>14865</v>
+        <v>14876</v>
       </c>
       <c r="F838" s="13" t="n">
         <v>7</v>
@@ -26168,7 +26168,7 @@
         </is>
       </c>
       <c r="E839" s="13" t="n">
-        <v>14874</v>
+        <v>14885</v>
       </c>
       <c r="F839" s="13" t="n">
         <v>8</v>
@@ -26196,7 +26196,7 @@
         </is>
       </c>
       <c r="E840" s="13" t="n">
-        <v>14885</v>
+        <v>14896</v>
       </c>
       <c r="F840" s="13" t="n">
         <v>7</v>
@@ -26224,7 +26224,7 @@
         </is>
       </c>
       <c r="E841" s="13" t="n">
-        <v>14894</v>
+        <v>14905</v>
       </c>
       <c r="F841" s="13" t="n">
         <v>7</v>
@@ -26252,7 +26252,7 @@
         </is>
       </c>
       <c r="E842" s="13" t="n">
-        <v>14904</v>
+        <v>14915</v>
       </c>
       <c r="F842" s="13" t="n">
         <v>8</v>
@@ -26280,7 +26280,7 @@
         </is>
       </c>
       <c r="E843" s="13" t="n">
-        <v>14914</v>
+        <v>14925</v>
       </c>
       <c r="F843" s="13" t="n">
         <v>9</v>
@@ -26308,7 +26308,7 @@
         </is>
       </c>
       <c r="E844" s="13" t="n">
-        <v>14926</v>
+        <v>14937</v>
       </c>
       <c r="F844" s="13" t="n">
         <v>8</v>
@@ -26336,7 +26336,7 @@
         </is>
       </c>
       <c r="E845" s="13" t="n">
-        <v>14936</v>
+        <v>14947</v>
       </c>
       <c r="F845" s="13" t="n">
         <v>6</v>
@@ -26364,7 +26364,7 @@
         </is>
       </c>
       <c r="E846" s="13" t="n">
-        <v>14945</v>
+        <v>14956</v>
       </c>
       <c r="F846" s="13" t="n">
         <v>7</v>
@@ -26392,7 +26392,7 @@
         </is>
       </c>
       <c r="E847" s="13" t="n">
-        <v>14954</v>
+        <v>14965</v>
       </c>
       <c r="F847" s="13" t="n">
         <v>8</v>
@@ -26420,7 +26420,7 @@
         </is>
       </c>
       <c r="E848" s="13" t="n">
-        <v>14964</v>
+        <v>14975</v>
       </c>
       <c r="F848" s="13" t="n">
         <v>7</v>
@@ -26448,7 +26448,7 @@
         </is>
       </c>
       <c r="E849" s="13" t="n">
-        <v>14973</v>
+        <v>14984</v>
       </c>
       <c r="F849" s="13" t="n">
         <v>8</v>
@@ -26476,7 +26476,7 @@
         </is>
       </c>
       <c r="E850" s="13" t="n">
-        <v>14983</v>
+        <v>14994</v>
       </c>
       <c r="F850" s="13" t="n">
         <v>8</v>
@@ -26504,7 +26504,7 @@
         </is>
       </c>
       <c r="E851" s="13" t="n">
-        <v>14994</v>
+        <v>15005</v>
       </c>
       <c r="F851" s="13" t="n">
         <v>7</v>
@@ -26532,7 +26532,7 @@
         </is>
       </c>
       <c r="E852" s="13" t="n">
-        <v>15003</v>
+        <v>15014</v>
       </c>
       <c r="F852" s="13" t="n">
         <v>7</v>
@@ -26560,7 +26560,7 @@
         </is>
       </c>
       <c r="E853" s="13" t="n">
-        <v>15013</v>
+        <v>15024</v>
       </c>
       <c r="F853" s="13" t="n">
         <v>7</v>
@@ -26588,7 +26588,7 @@
         </is>
       </c>
       <c r="E854" s="13" t="n">
-        <v>15022</v>
+        <v>15033</v>
       </c>
       <c r="F854" s="13" t="n">
         <v>8</v>
@@ -26616,7 +26616,7 @@
         </is>
       </c>
       <c r="E855" s="13" t="n">
-        <v>15033</v>
+        <v>15044</v>
       </c>
       <c r="F855" s="13" t="n">
         <v>8</v>
@@ -26644,7 +26644,7 @@
         </is>
       </c>
       <c r="E856" s="13" t="n">
-        <v>15043</v>
+        <v>15054</v>
       </c>
       <c r="F856" s="13" t="n">
         <v>8</v>
@@ -26672,7 +26672,7 @@
         </is>
       </c>
       <c r="E857" s="13" t="n">
-        <v>15054</v>
+        <v>15065</v>
       </c>
       <c r="F857" s="13" t="n">
         <v>8</v>
@@ -26700,7 +26700,7 @@
         </is>
       </c>
       <c r="E858" s="13" t="n">
-        <v>15064</v>
+        <v>15075</v>
       </c>
       <c r="F858" s="13" t="n">
         <v>9</v>
@@ -26728,7 +26728,7 @@
         </is>
       </c>
       <c r="E859" s="13" t="n">
-        <v>15076</v>
+        <v>15087</v>
       </c>
       <c r="F859" s="13" t="n">
         <v>9</v>
@@ -26756,7 +26756,7 @@
         </is>
       </c>
       <c r="E860" s="13" t="n">
-        <v>15087</v>
+        <v>15098</v>
       </c>
       <c r="F860" s="13" t="n">
         <v>9</v>
@@ -26784,7 +26784,7 @@
         </is>
       </c>
       <c r="E861" s="13" t="n">
-        <v>15099</v>
+        <v>15110</v>
       </c>
       <c r="F861" s="13" t="n">
         <v>9</v>
@@ -26812,7 +26812,7 @@
         </is>
       </c>
       <c r="E862" s="13" t="n">
-        <v>15110</v>
+        <v>15121</v>
       </c>
       <c r="F862" s="13" t="n">
         <v>8</v>
@@ -26840,7 +26840,7 @@
         </is>
       </c>
       <c r="E863" s="13" t="n">
-        <v>15121</v>
+        <v>15132</v>
       </c>
       <c r="F863" s="13" t="n">
         <v>7</v>
@@ -26868,7 +26868,7 @@
         </is>
       </c>
       <c r="E864" s="13" t="n">
-        <v>15130</v>
+        <v>15141</v>
       </c>
       <c r="F864" s="13" t="n">
         <v>8</v>
@@ -26896,7 +26896,7 @@
         </is>
       </c>
       <c r="E865" s="13" t="n">
-        <v>15141</v>
+        <v>15152</v>
       </c>
       <c r="F865" s="13" t="n">
         <v>7</v>
@@ -26924,7 +26924,7 @@
         </is>
       </c>
       <c r="E866" s="13" t="n">
-        <v>15150</v>
+        <v>15161</v>
       </c>
       <c r="F866" s="13" t="n">
         <v>7</v>
@@ -26952,7 +26952,7 @@
         </is>
       </c>
       <c r="E867" s="13" t="n">
-        <v>15159</v>
+        <v>15170</v>
       </c>
       <c r="F867" s="13" t="n">
         <v>6</v>
@@ -26980,7 +26980,7 @@
         </is>
       </c>
       <c r="E868" s="13" t="n">
-        <v>15168</v>
+        <v>15179</v>
       </c>
       <c r="F868" s="13" t="n">
         <v>5</v>
@@ -27008,7 +27008,7 @@
         </is>
       </c>
       <c r="E869" s="13" t="n">
-        <v>15175</v>
+        <v>15186</v>
       </c>
       <c r="F869" s="13" t="n">
         <v>7</v>
@@ -27036,7 +27036,7 @@
         </is>
       </c>
       <c r="E870" s="13" t="n">
-        <v>15184</v>
+        <v>15195</v>
       </c>
       <c r="F870" s="13" t="n">
         <v>6</v>
@@ -27064,7 +27064,7 @@
         </is>
       </c>
       <c r="E871" s="13" t="n">
-        <v>15193</v>
+        <v>15204</v>
       </c>
       <c r="F871" s="13" t="n">
         <v>7</v>
@@ -27092,7 +27092,7 @@
         </is>
       </c>
       <c r="E872" s="13" t="n">
-        <v>15202</v>
+        <v>15213</v>
       </c>
       <c r="F872" s="13" t="n">
         <v>8</v>
@@ -27120,7 +27120,7 @@
         </is>
       </c>
       <c r="E873" s="13" t="n">
-        <v>15213</v>
+        <v>15224</v>
       </c>
       <c r="F873" s="13" t="n">
         <v>7</v>
@@ -27148,7 +27148,7 @@
         </is>
       </c>
       <c r="E874" s="13" t="n">
-        <v>15222</v>
+        <v>15233</v>
       </c>
       <c r="F874" s="13" t="n">
         <v>14</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="E875" s="13" t="n">
-        <v>15239</v>
+        <v>15250</v>
       </c>
       <c r="F875" s="13" t="n">
         <v>7</v>
@@ -27204,7 +27204,7 @@
         </is>
       </c>
       <c r="E876" s="13" t="n">
-        <v>15248</v>
+        <v>15259</v>
       </c>
       <c r="F876" s="13" t="n">
         <v>8</v>
@@ -27232,7 +27232,7 @@
         </is>
       </c>
       <c r="E877" s="13" t="n">
-        <v>15259</v>
+        <v>15270</v>
       </c>
       <c r="F877" s="13" t="n">
         <v>6</v>
@@ -27260,7 +27260,7 @@
         </is>
       </c>
       <c r="E878" s="13" t="n">
-        <v>15267</v>
+        <v>15278</v>
       </c>
       <c r="F878" s="13" t="n">
         <v>7</v>
@@ -27288,7 +27288,7 @@
         </is>
       </c>
       <c r="E879" s="13" t="n">
-        <v>15276</v>
+        <v>15287</v>
       </c>
       <c r="F879" s="13" t="n">
         <v>5</v>
@@ -27316,7 +27316,7 @@
         </is>
       </c>
       <c r="E880" s="13" t="n">
-        <v>15284</v>
+        <v>15295</v>
       </c>
       <c r="F880" s="13" t="n">
         <v>7</v>
@@ -27344,7 +27344,7 @@
         </is>
       </c>
       <c r="E881" s="13" t="n">
-        <v>15293</v>
+        <v>15304</v>
       </c>
       <c r="F881" s="13" t="n">
         <v>7</v>
@@ -27372,7 +27372,7 @@
         </is>
       </c>
       <c r="E882" s="13" t="n">
-        <v>15303</v>
+        <v>15314</v>
       </c>
       <c r="F882" s="13" t="n">
         <v>8</v>
@@ -27400,7 +27400,7 @@
         </is>
       </c>
       <c r="E883" s="13" t="n">
-        <v>15313</v>
+        <v>15324</v>
       </c>
       <c r="F883" s="13" t="n">
         <v>8</v>
@@ -27428,7 +27428,7 @@
         </is>
       </c>
       <c r="E884" s="13" t="n">
-        <v>15324</v>
+        <v>15335</v>
       </c>
       <c r="F884" s="13" t="n">
         <v>7</v>
@@ -27456,7 +27456,7 @@
         </is>
       </c>
       <c r="E885" s="13" t="n">
-        <v>15333</v>
+        <v>15344</v>
       </c>
       <c r="F885" s="13" t="n">
         <v>7</v>
@@ -27484,7 +27484,7 @@
         </is>
       </c>
       <c r="E886" s="13" t="n">
-        <v>15342</v>
+        <v>15353</v>
       </c>
       <c r="F886" s="13" t="n">
         <v>7</v>
@@ -27512,7 +27512,7 @@
         </is>
       </c>
       <c r="E887" s="13" t="n">
-        <v>15351</v>
+        <v>15362</v>
       </c>
       <c r="F887" s="13" t="n">
         <v>5</v>
@@ -27540,7 +27540,7 @@
         </is>
       </c>
       <c r="E888" s="13" t="n">
-        <v>15358</v>
+        <v>15369</v>
       </c>
       <c r="F888" s="13" t="n">
         <v>15</v>
@@ -27568,7 +27568,7 @@
         </is>
       </c>
       <c r="E889" s="13" t="n">
-        <v>15376</v>
+        <v>15387</v>
       </c>
       <c r="F889" s="13" t="n">
         <v>15</v>
@@ -27596,7 +27596,7 @@
         </is>
       </c>
       <c r="E890" s="13" t="n">
-        <v>15394</v>
+        <v>15405</v>
       </c>
       <c r="F890" s="13" t="n">
         <v>8</v>
@@ -27624,7 +27624,7 @@
         </is>
       </c>
       <c r="E891" s="13" t="n">
-        <v>15404</v>
+        <v>15415</v>
       </c>
       <c r="F891" s="13" t="n">
         <v>7</v>
@@ -27652,7 +27652,7 @@
         </is>
       </c>
       <c r="E892" s="13" t="n">
-        <v>15414</v>
+        <v>15425</v>
       </c>
       <c r="F892" s="13" t="n">
         <v>6</v>
@@ -27680,7 +27680,7 @@
         </is>
       </c>
       <c r="E893" s="13" t="n">
-        <v>15422</v>
+        <v>15433</v>
       </c>
       <c r="F893" s="13" t="n">
         <v>6</v>
@@ -27708,7 +27708,7 @@
         </is>
       </c>
       <c r="E894" s="13" t="n">
-        <v>15430</v>
+        <v>15441</v>
       </c>
       <c r="F894" s="13" t="n">
         <v>7</v>
@@ -27736,7 +27736,7 @@
         </is>
       </c>
       <c r="E895" s="13" t="n">
-        <v>15440</v>
+        <v>15451</v>
       </c>
       <c r="F895" s="13" t="n">
         <v>4</v>
@@ -27764,7 +27764,7 @@
         </is>
       </c>
       <c r="E896" s="13" t="n">
-        <v>15446</v>
+        <v>15457</v>
       </c>
       <c r="F896" s="13" t="n">
         <v>6</v>
@@ -27792,7 +27792,7 @@
         </is>
       </c>
       <c r="E897" s="13" t="n">
-        <v>15454</v>
+        <v>15465</v>
       </c>
       <c r="F897" s="13" t="n">
         <v>7</v>
@@ -27820,7 +27820,7 @@
         </is>
       </c>
       <c r="E898" s="13" t="n">
-        <v>15464</v>
+        <v>15475</v>
       </c>
       <c r="F898" s="13" t="n">
         <v>6</v>
@@ -27848,7 +27848,7 @@
         </is>
       </c>
       <c r="E899" s="13" t="n">
-        <v>15472</v>
+        <v>15483</v>
       </c>
       <c r="F899" s="13" t="n">
         <v>9</v>
@@ -27876,7 +27876,7 @@
         </is>
       </c>
       <c r="E900" s="13" t="n">
-        <v>15484</v>
+        <v>15495</v>
       </c>
       <c r="F900" s="13" t="n">
         <v>6</v>
@@ -27904,7 +27904,7 @@
         </is>
       </c>
       <c r="E901" s="13" t="n">
-        <v>15492</v>
+        <v>15503</v>
       </c>
       <c r="F901" s="13" t="n">
         <v>7</v>
@@ -27932,7 +27932,7 @@
         </is>
       </c>
       <c r="E902" s="13" t="n">
-        <v>15501</v>
+        <v>15512</v>
       </c>
       <c r="F902" s="13" t="n">
         <v>6</v>
@@ -27960,7 +27960,7 @@
         </is>
       </c>
       <c r="E903" s="13" t="n">
-        <v>15509</v>
+        <v>15520</v>
       </c>
       <c r="F903" s="13" t="n">
         <v>6</v>
@@ -27988,7 +27988,7 @@
         </is>
       </c>
       <c r="E904" s="13" t="n">
-        <v>15517</v>
+        <v>15528</v>
       </c>
       <c r="F904" s="13" t="n">
         <v>7</v>
@@ -28016,7 +28016,7 @@
         </is>
       </c>
       <c r="E905" s="13" t="n">
-        <v>15527</v>
+        <v>15538</v>
       </c>
       <c r="F905" s="13" t="n">
         <v>7</v>
@@ -28044,7 +28044,7 @@
         </is>
       </c>
       <c r="E906" s="13" t="n">
-        <v>15536</v>
+        <v>15547</v>
       </c>
       <c r="F906" s="13" t="n">
         <v>7</v>
@@ -28072,7 +28072,7 @@
         </is>
       </c>
       <c r="E907" s="13" t="n">
-        <v>15545</v>
+        <v>15556</v>
       </c>
       <c r="F907" s="13" t="n">
         <v>7</v>
@@ -28100,7 +28100,7 @@
         </is>
       </c>
       <c r="E908" s="13" t="n">
-        <v>15554</v>
+        <v>15565</v>
       </c>
       <c r="F908" s="13" t="n">
         <v>7</v>
@@ -28128,7 +28128,7 @@
         </is>
       </c>
       <c r="E909" s="13" t="n">
-        <v>15563</v>
+        <v>15574</v>
       </c>
       <c r="F909" s="13" t="n">
         <v>5</v>
@@ -28156,7 +28156,7 @@
         </is>
       </c>
       <c r="E910" s="13" t="n">
-        <v>15571</v>
+        <v>15582</v>
       </c>
       <c r="F910" s="13" t="n">
         <v>5</v>
@@ -28184,7 +28184,7 @@
         </is>
       </c>
       <c r="E911" s="13" t="n">
-        <v>15578</v>
+        <v>15589</v>
       </c>
       <c r="F911" s="13" t="n">
         <v>5</v>
@@ -28212,7 +28212,7 @@
         </is>
       </c>
       <c r="E912" s="13" t="n">
-        <v>15586</v>
+        <v>15597</v>
       </c>
       <c r="F912" s="13" t="n">
         <v>6</v>
@@ -28240,7 +28240,7 @@
         </is>
       </c>
       <c r="E913" s="13" t="n">
-        <v>15594</v>
+        <v>15605</v>
       </c>
       <c r="F913" s="13" t="n">
         <v>7</v>
@@ -28268,7 +28268,7 @@
         </is>
       </c>
       <c r="E914" s="13" t="n">
-        <v>15603</v>
+        <v>15614</v>
       </c>
       <c r="F914" s="13" t="n">
         <v>6</v>
@@ -28296,7 +28296,7 @@
         </is>
       </c>
       <c r="E915" s="13" t="n">
-        <v>15611</v>
+        <v>15622</v>
       </c>
       <c r="F915" s="13" t="n">
         <v>7</v>
@@ -28324,7 +28324,7 @@
         </is>
       </c>
       <c r="E916" s="13" t="n">
-        <v>15620</v>
+        <v>15631</v>
       </c>
       <c r="F916" s="13" t="n">
         <v>8</v>
@@ -28352,7 +28352,7 @@
         </is>
       </c>
       <c r="E917" s="13" t="n">
-        <v>15631</v>
+        <v>15642</v>
       </c>
       <c r="F917" s="13" t="n">
         <v>7</v>
@@ -28380,7 +28380,7 @@
         </is>
       </c>
       <c r="E918" s="13" t="n">
-        <v>15640</v>
+        <v>15651</v>
       </c>
       <c r="F918" s="13" t="n">
         <v>6</v>
@@ -28408,7 +28408,7 @@
         </is>
       </c>
       <c r="E919" s="13" t="n">
-        <v>15649</v>
+        <v>15660</v>
       </c>
       <c r="F919" s="13" t="n">
         <v>7</v>
@@ -28436,7 +28436,7 @@
         </is>
       </c>
       <c r="E920" s="13" t="n">
-        <v>15658</v>
+        <v>15669</v>
       </c>
       <c r="F920" s="13" t="n">
         <v>6</v>
@@ -28464,7 +28464,7 @@
         </is>
       </c>
       <c r="E921" s="13" t="n">
-        <v>15666</v>
+        <v>15677</v>
       </c>
       <c r="F921" s="13" t="n">
         <v>7</v>
@@ -28492,7 +28492,7 @@
         </is>
       </c>
       <c r="E922" s="13" t="n">
-        <v>15676</v>
+        <v>15687</v>
       </c>
       <c r="F922" s="13" t="n">
         <v>7</v>
@@ -28520,7 +28520,7 @@
         </is>
       </c>
       <c r="E923" s="13" t="n">
-        <v>15685</v>
+        <v>15696</v>
       </c>
       <c r="F923" s="13" t="n">
         <v>3</v>
@@ -28548,7 +28548,7 @@
         </is>
       </c>
       <c r="E924" s="13" t="n">
-        <v>15691</v>
+        <v>15702</v>
       </c>
       <c r="F924" s="13" t="n">
         <v>2</v>
@@ -28576,7 +28576,7 @@
         </is>
       </c>
       <c r="E925" s="13" t="n">
-        <v>15695</v>
+        <v>15706</v>
       </c>
       <c r="F925" s="13" t="n">
         <v>5</v>
@@ -28604,7 +28604,7 @@
         </is>
       </c>
       <c r="E926" s="13" t="n">
-        <v>15702</v>
+        <v>15713</v>
       </c>
       <c r="F926" s="13" t="n">
         <v>13</v>
@@ -28632,7 +28632,7 @@
         </is>
       </c>
       <c r="E927" s="13" t="n">
-        <v>15718</v>
+        <v>15729</v>
       </c>
       <c r="F927" s="13" t="n">
         <v>24</v>
@@ -28660,7 +28660,7 @@
         </is>
       </c>
       <c r="E928" s="13" t="n">
-        <v>15745</v>
+        <v>15756</v>
       </c>
       <c r="F928" s="13" t="n">
         <v>23</v>
@@ -28688,7 +28688,7 @@
         </is>
       </c>
       <c r="E929" s="13" t="n">
-        <v>15772</v>
+        <v>15783</v>
       </c>
       <c r="F929" s="13" t="n">
         <v>19</v>
@@ -28716,7 +28716,7 @@
         </is>
       </c>
       <c r="E930" s="13" t="n">
-        <v>15794</v>
+        <v>15805</v>
       </c>
       <c r="F930" s="13" t="n">
         <v>18</v>
@@ -28744,7 +28744,7 @@
         </is>
       </c>
       <c r="E931" s="13" t="n">
-        <v>15815</v>
+        <v>15826</v>
       </c>
       <c r="F931" s="13" t="n">
         <v>19</v>

--- a/알바로_부작_화_목록.xlsx
+++ b/알바로_부작_화_목록.xlsx
@@ -2791,7 +2791,7 @@
         <v>88</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G4" s="15" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>268</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>352</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="E15" s="13" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F15" s="13" t="n">
         <v>17</v>
@@ -3124,10 +3124,10 @@
         </is>
       </c>
       <c r="E16" s="13" t="n">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G16" s="15" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         </is>
       </c>
       <c r="E17" s="13" t="n">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F17" s="13" t="n">
         <v>15</v>
@@ -3180,7 +3180,7 @@
         </is>
       </c>
       <c r="E18" s="13" t="n">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F18" s="13" t="n">
         <v>15</v>
@@ -3208,7 +3208,7 @@
         </is>
       </c>
       <c r="E19" s="13" t="n">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F19" s="13" t="n">
         <v>14</v>
@@ -3236,7 +3236,7 @@
         </is>
       </c>
       <c r="E20" s="13" t="n">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F20" s="13" t="n">
         <v>16</v>
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="E21" s="13" t="n">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F21" s="13" t="n">
         <v>16</v>
@@ -3292,7 +3292,7 @@
         </is>
       </c>
       <c r="E22" s="13" t="n">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F22" s="13" t="n">
         <v>13</v>
@@ -3320,7 +3320,7 @@
         </is>
       </c>
       <c r="E23" s="13" t="n">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F23" s="13" t="n">
         <v>13</v>
@@ -3348,7 +3348,7 @@
         </is>
       </c>
       <c r="E24" s="13" t="n">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F24" s="13" t="n">
         <v>17</v>
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="E25" s="13" t="n">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="F25" s="13" t="n">
         <v>10</v>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="E26" s="13" t="n">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="F26" s="13" t="n">
         <v>17</v>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="E27" s="13" t="n">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="F27" s="13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         </is>
       </c>
       <c r="E28" s="13" t="n">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="F28" s="13" t="n">
         <v>27</v>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="E29" s="13" t="n">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F29" s="13" t="n">
         <v>35</v>
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="E30" s="13" t="n">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F30" s="13" t="n">
         <v>17</v>
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="E31" s="13" t="n">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F31" s="13" t="n">
         <v>31</v>
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="E32" s="13" t="n">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="F32" s="13" t="n">
         <v>95</v>
@@ -3600,7 +3600,7 @@
         </is>
       </c>
       <c r="E33" s="13" t="n">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="F33" s="13" t="n">
         <v>176</v>
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="E34" s="13" t="n">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F34" s="13" t="n">
         <v>161</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="E35" s="13" t="n">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="F35" s="13" t="n">
         <v>45</v>
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="E36" s="13" t="n">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="F36" s="13" t="n">
         <v>28</v>
@@ -3712,10 +3712,10 @@
         </is>
       </c>
       <c r="E37" s="13" t="n">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="F37" s="13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         </is>
       </c>
       <c r="E38" s="13" t="n">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="F38" s="13" t="n">
         <v>10</v>
@@ -3768,7 +3768,7 @@
         </is>
       </c>
       <c r="E39" s="13" t="n">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="F39" s="13" t="n">
         <v>18</v>
@@ -3796,7 +3796,7 @@
         </is>
       </c>
       <c r="E40" s="13" t="n">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="F40" s="13" t="n">
         <v>28</v>
@@ -3824,10 +3824,10 @@
         </is>
       </c>
       <c r="E41" s="13" t="n">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="F41" s="13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G41" s="15" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="E42" s="13" t="n">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="F42" s="13" t="n">
         <v>56</v>
@@ -3880,7 +3880,7 @@
         </is>
       </c>
       <c r="E43" s="13" t="n">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="F43" s="13" t="n">
         <v>34</v>
@@ -3908,7 +3908,7 @@
         </is>
       </c>
       <c r="E44" s="13" t="n">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="F44" s="13" t="n">
         <v>40</v>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="E45" s="13" t="n">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="F45" s="13" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G45" s="15" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="E46" s="13" t="n">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="F46" s="13" t="n">
         <v>36</v>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="E47" s="13" t="n">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="F47" s="13" t="n">
         <v>30</v>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="E48" s="13" t="n">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="F48" s="13" t="n">
         <v>93</v>
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="E49" s="13" t="n">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="F49" s="13" t="n">
         <v>36</v>
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="E50" s="13" t="n">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="F50" s="13" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G50" s="15" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         </is>
       </c>
       <c r="E51" s="13" t="n">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="F51" s="13" t="n">
         <v>31</v>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="E52" s="13" t="n">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="F52" s="13" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G52" s="15" t="inlineStr">
         <is>
@@ -4160,10 +4160,10 @@
         </is>
       </c>
       <c r="E53" s="13" t="n">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="F53" s="13" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G53" s="15" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         </is>
       </c>
       <c r="E54" s="13" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="F54" s="13" t="n">
         <v>42</v>
@@ -4216,7 +4216,7 @@
         </is>
       </c>
       <c r="E55" s="13" t="n">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="F55" s="13" t="n">
         <v>41</v>
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="E56" s="13" t="n">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="F56" s="13" t="n">
         <v>31</v>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="E57" s="13" t="n">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="F57" s="13" t="n">
         <v>30</v>
@@ -4300,7 +4300,7 @@
         </is>
       </c>
       <c r="E58" s="13" t="n">
-        <v>2155</v>
+        <v>2154</v>
       </c>
       <c r="F58" s="13" t="n">
         <v>34</v>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="E59" s="13" t="n">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="F59" s="13" t="n">
         <v>36</v>
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="E60" s="13" t="n">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="F60" s="13" t="n">
         <v>29</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="E61" s="13" t="n">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="F61" s="13" t="n">
         <v>32</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="E62" s="13" t="n">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="F62" s="13" t="n">
         <v>15</v>
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="E63" s="13" t="n">
-        <v>2311</v>
+        <v>2310</v>
       </c>
       <c r="F63" s="13" t="n">
         <v>29</v>
@@ -4468,7 +4468,7 @@
         </is>
       </c>
       <c r="E64" s="13" t="n">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="F64" s="13" t="n">
         <v>30</v>
@@ -4496,7 +4496,7 @@
         </is>
       </c>
       <c r="E65" s="13" t="n">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="F65" s="13" t="n">
         <v>25</v>
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="E66" s="13" t="n">
-        <v>2401</v>
+        <v>2400</v>
       </c>
       <c r="F66" s="13" t="n">
         <v>27</v>
@@ -4552,7 +4552,7 @@
         </is>
       </c>
       <c r="E67" s="13" t="n">
-        <v>2430</v>
+        <v>2429</v>
       </c>
       <c r="F67" s="13" t="n">
         <v>26</v>
@@ -4580,7 +4580,7 @@
         </is>
       </c>
       <c r="E68" s="13" t="n">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="F68" s="13" t="n">
         <v>28</v>
@@ -4608,7 +4608,7 @@
         </is>
       </c>
       <c r="E69" s="13" t="n">
-        <v>2490</v>
+        <v>2489</v>
       </c>
       <c r="F69" s="13" t="n">
         <v>30</v>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="E70" s="13" t="n">
-        <v>2523</v>
+        <v>2522</v>
       </c>
       <c r="F70" s="13" t="n">
         <v>23</v>
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="E71" s="13" t="n">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="F71" s="13" t="n">
         <v>27</v>
@@ -4692,7 +4692,7 @@
         </is>
       </c>
       <c r="E72" s="13" t="n">
-        <v>2579</v>
+        <v>2578</v>
       </c>
       <c r="F72" s="13" t="n">
         <v>23</v>
@@ -4720,7 +4720,7 @@
         </is>
       </c>
       <c r="E73" s="13" t="n">
-        <v>2606</v>
+        <v>2605</v>
       </c>
       <c r="F73" s="13" t="n">
         <v>28</v>
@@ -4748,7 +4748,7 @@
         </is>
       </c>
       <c r="E74" s="13" t="n">
-        <v>2637</v>
+        <v>2636</v>
       </c>
       <c r="F74" s="13" t="n">
         <v>26</v>
@@ -4776,7 +4776,7 @@
         </is>
       </c>
       <c r="E75" s="13" t="n">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="F75" s="13" t="n">
         <v>23</v>
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="E76" s="13" t="n">
-        <v>2693</v>
+        <v>2692</v>
       </c>
       <c r="F76" s="13" t="n">
         <v>26</v>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="E77" s="13" t="n">
-        <v>2723</v>
+        <v>2722</v>
       </c>
       <c r="F77" s="13" t="n">
         <v>22</v>
@@ -4860,7 +4860,7 @@
         </is>
       </c>
       <c r="E78" s="13" t="n">
-        <v>2748</v>
+        <v>2747</v>
       </c>
       <c r="F78" s="13" t="n">
         <v>23</v>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="E79" s="13" t="n">
-        <v>2774</v>
+        <v>2773</v>
       </c>
       <c r="F79" s="13" t="n">
         <v>21</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="E80" s="13" t="n">
-        <v>2799</v>
+        <v>2798</v>
       </c>
       <c r="F80" s="13" t="n">
         <v>24</v>
@@ -4944,7 +4944,7 @@
         </is>
       </c>
       <c r="E81" s="13" t="n">
-        <v>2826</v>
+        <v>2825</v>
       </c>
       <c r="F81" s="13" t="n">
         <v>25</v>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="E82" s="13" t="n">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="F82" s="13" t="n">
         <v>30</v>
@@ -5000,7 +5000,7 @@
         </is>
       </c>
       <c r="E83" s="13" t="n">
-        <v>2888</v>
+        <v>2887</v>
       </c>
       <c r="F83" s="13" t="n">
         <v>31</v>
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="E84" s="13" t="n">
-        <v>2923</v>
+        <v>2922</v>
       </c>
       <c r="F84" s="13" t="n">
         <v>25</v>
@@ -5056,7 +5056,7 @@
         </is>
       </c>
       <c r="E85" s="13" t="n">
-        <v>2951</v>
+        <v>2950</v>
       </c>
       <c r="F85" s="13" t="n">
         <v>23</v>
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="E86" s="13" t="n">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="F86" s="13" t="n">
         <v>27</v>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="E87" s="13" t="n">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="F87" s="13" t="n">
         <v>28</v>
@@ -5140,7 +5140,7 @@
         </is>
       </c>
       <c r="E88" s="13" t="n">
-        <v>3039</v>
+        <v>3038</v>
       </c>
       <c r="F88" s="13" t="n">
         <v>22</v>
@@ -5168,7 +5168,7 @@
         </is>
       </c>
       <c r="E89" s="13" t="n">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="F89" s="13" t="n">
         <v>21</v>
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="E90" s="13" t="n">
-        <v>3088</v>
+        <v>3087</v>
       </c>
       <c r="F90" s="13" t="n">
         <v>26</v>
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="E91" s="13" t="n">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="F91" s="13" t="n">
         <v>22</v>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="E92" s="13" t="n">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="F92" s="13" t="n">
         <v>25</v>
@@ -5280,7 +5280,7 @@
         </is>
       </c>
       <c r="E93" s="13" t="n">
-        <v>3171</v>
+        <v>3170</v>
       </c>
       <c r="F93" s="13" t="n">
         <v>18</v>
@@ -5308,7 +5308,7 @@
         </is>
       </c>
       <c r="E94" s="13" t="n">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="F94" s="13" t="n">
         <v>18</v>
@@ -5336,7 +5336,7 @@
         </is>
       </c>
       <c r="E95" s="13" t="n">
-        <v>3213</v>
+        <v>3212</v>
       </c>
       <c r="F95" s="13" t="n">
         <v>21</v>
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="E96" s="13" t="n">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="F96" s="13" t="n">
         <v>27</v>
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="E97" s="13" t="n">
-        <v>3268</v>
+        <v>3267</v>
       </c>
       <c r="F97" s="13" t="n">
         <v>18</v>
@@ -5420,7 +5420,7 @@
         </is>
       </c>
       <c r="E98" s="13" t="n">
-        <v>3289</v>
+        <v>3288</v>
       </c>
       <c r="F98" s="13" t="n">
         <v>21</v>
@@ -5448,7 +5448,7 @@
         </is>
       </c>
       <c r="E99" s="13" t="n">
-        <v>3313</v>
+        <v>3312</v>
       </c>
       <c r="F99" s="13" t="n">
         <v>20</v>
@@ -5476,7 +5476,7 @@
         </is>
       </c>
       <c r="E100" s="13" t="n">
-        <v>3336</v>
+        <v>3335</v>
       </c>
       <c r="F100" s="13" t="n">
         <v>18</v>
@@ -5504,7 +5504,7 @@
         </is>
       </c>
       <c r="E101" s="13" t="n">
-        <v>3357</v>
+        <v>3356</v>
       </c>
       <c r="F101" s="13" t="n">
         <v>21</v>
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="E102" s="13" t="n">
-        <v>3381</v>
+        <v>3380</v>
       </c>
       <c r="F102" s="13" t="n">
         <v>20</v>
@@ -5560,7 +5560,7 @@
         </is>
       </c>
       <c r="E103" s="13" t="n">
-        <v>3404</v>
+        <v>3403</v>
       </c>
       <c r="F103" s="13" t="n">
         <v>22</v>
@@ -5588,7 +5588,7 @@
         </is>
       </c>
       <c r="E104" s="13" t="n">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="F104" s="13" t="n">
         <v>23</v>
@@ -5616,7 +5616,7 @@
         </is>
       </c>
       <c r="E105" s="13" t="n">
-        <v>3456</v>
+        <v>3455</v>
       </c>
       <c r="F105" s="13" t="n">
         <v>14</v>
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c r="E106" s="13" t="n">
-        <v>3473</v>
+        <v>3472</v>
       </c>
       <c r="F106" s="13" t="n">
         <v>17</v>
@@ -5672,7 +5672,7 @@
         </is>
       </c>
       <c r="E107" s="13" t="n">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="F107" s="13" t="n">
         <v>14</v>
@@ -5700,7 +5700,7 @@
         </is>
       </c>
       <c r="E108" s="13" t="n">
-        <v>3510</v>
+        <v>3509</v>
       </c>
       <c r="F108" s="13" t="n">
         <v>20</v>
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E109" s="13" t="n">
-        <v>3533</v>
+        <v>3532</v>
       </c>
       <c r="F109" s="13" t="n">
         <v>22</v>
@@ -5756,7 +5756,7 @@
         </is>
       </c>
       <c r="E110" s="13" t="n">
-        <v>3558</v>
+        <v>3557</v>
       </c>
       <c r="F110" s="13" t="n">
         <v>20</v>
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="E111" s="13" t="n">
-        <v>3581</v>
+        <v>3580</v>
       </c>
       <c r="F111" s="13" t="n">
         <v>19</v>
@@ -5812,7 +5812,7 @@
         </is>
       </c>
       <c r="E112" s="13" t="n">
-        <v>3603</v>
+        <v>3602</v>
       </c>
       <c r="F112" s="13" t="n">
         <v>17</v>
@@ -5840,7 +5840,7 @@
         </is>
       </c>
       <c r="E113" s="13" t="n">
-        <v>3623</v>
+        <v>3622</v>
       </c>
       <c r="F113" s="13" t="n">
         <v>19</v>
@@ -5868,7 +5868,7 @@
         </is>
       </c>
       <c r="E114" s="13" t="n">
-        <v>3645</v>
+        <v>3644</v>
       </c>
       <c r="F114" s="13" t="n">
         <v>15</v>
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="E115" s="13" t="n">
-        <v>3663</v>
+        <v>3662</v>
       </c>
       <c r="F115" s="13" t="n">
         <v>18</v>
@@ -5924,7 +5924,7 @@
         </is>
       </c>
       <c r="E116" s="13" t="n">
-        <v>3684</v>
+        <v>3683</v>
       </c>
       <c r="F116" s="13" t="n">
         <v>13</v>
@@ -5952,7 +5952,7 @@
         </is>
       </c>
       <c r="E117" s="13" t="n">
-        <v>3699</v>
+        <v>3698</v>
       </c>
       <c r="F117" s="13" t="n">
         <v>19</v>
@@ -5980,7 +5980,7 @@
         </is>
       </c>
       <c r="E118" s="13" t="n">
-        <v>3721</v>
+        <v>3720</v>
       </c>
       <c r="F118" s="13" t="n">
         <v>19</v>
@@ -6008,7 +6008,7 @@
         </is>
       </c>
       <c r="E119" s="13" t="n">
-        <v>3743</v>
+        <v>3742</v>
       </c>
       <c r="F119" s="13" t="n">
         <v>19</v>
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="E120" s="13" t="n">
-        <v>3765</v>
+        <v>3764</v>
       </c>
       <c r="F120" s="13" t="n">
         <v>19</v>
@@ -6064,7 +6064,7 @@
         </is>
       </c>
       <c r="E121" s="13" t="n">
-        <v>3787</v>
+        <v>3786</v>
       </c>
       <c r="F121" s="13" t="n">
         <v>17</v>
@@ -6092,7 +6092,7 @@
         </is>
       </c>
       <c r="E122" s="13" t="n">
-        <v>3807</v>
+        <v>3806</v>
       </c>
       <c r="F122" s="13" t="n">
         <v>13</v>
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="E123" s="13" t="n">
-        <v>3823</v>
+        <v>3822</v>
       </c>
       <c r="F123" s="13" t="n">
         <v>10</v>
@@ -6148,7 +6148,7 @@
         </is>
       </c>
       <c r="E124" s="13" t="n">
-        <v>3835</v>
+        <v>3834</v>
       </c>
       <c r="F124" s="13" t="n">
         <v>18</v>
@@ -6176,7 +6176,7 @@
         </is>
       </c>
       <c r="E125" s="13" t="n">
-        <v>3856</v>
+        <v>3855</v>
       </c>
       <c r="F125" s="13" t="n">
         <v>23</v>
@@ -6204,7 +6204,7 @@
         </is>
       </c>
       <c r="E126" s="13" t="n">
-        <v>3883</v>
+        <v>3882</v>
       </c>
       <c r="F126" s="13" t="n">
         <v>20</v>
@@ -6232,7 +6232,7 @@
         </is>
       </c>
       <c r="E127" s="13" t="n">
-        <v>3906</v>
+        <v>3905</v>
       </c>
       <c r="F127" s="13" t="n">
         <v>16</v>
@@ -6260,7 +6260,7 @@
         </is>
       </c>
       <c r="E128" s="13" t="n">
-        <v>3925</v>
+        <v>3924</v>
       </c>
       <c r="F128" s="13" t="n">
         <v>20</v>
@@ -6288,7 +6288,7 @@
         </is>
       </c>
       <c r="E129" s="13" t="n">
-        <v>3948</v>
+        <v>3947</v>
       </c>
       <c r="F129" s="13" t="n">
         <v>16</v>
@@ -6316,7 +6316,7 @@
         </is>
       </c>
       <c r="E130" s="13" t="n">
-        <v>3967</v>
+        <v>3966</v>
       </c>
       <c r="F130" s="13" t="n">
         <v>22</v>
@@ -6344,7 +6344,7 @@
         </is>
       </c>
       <c r="E131" s="13" t="n">
-        <v>3992</v>
+        <v>3991</v>
       </c>
       <c r="F131" s="13" t="n">
         <v>13</v>
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="E132" s="13" t="n">
-        <v>4007</v>
+        <v>4006</v>
       </c>
       <c r="F132" s="13" t="n">
         <v>12</v>
@@ -6400,7 +6400,7 @@
         </is>
       </c>
       <c r="E133" s="13" t="n">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="F133" s="13" t="n">
         <v>15</v>
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="E134" s="13" t="n">
-        <v>4040</v>
+        <v>4039</v>
       </c>
       <c r="F134" s="13" t="n">
         <v>16</v>
@@ -6456,7 +6456,7 @@
         </is>
       </c>
       <c r="E135" s="13" t="n">
-        <v>4059</v>
+        <v>4058</v>
       </c>
       <c r="F135" s="13" t="n">
         <v>12</v>
@@ -6484,7 +6484,7 @@
         </is>
       </c>
       <c r="E136" s="13" t="n">
-        <v>4073</v>
+        <v>4072</v>
       </c>
       <c r="F136" s="13" t="n">
         <v>14</v>
@@ -6512,7 +6512,7 @@
         </is>
       </c>
       <c r="E137" s="13" t="n">
-        <v>4090</v>
+        <v>4089</v>
       </c>
       <c r="F137" s="13" t="n">
         <v>10</v>
@@ -6540,7 +6540,7 @@
         </is>
       </c>
       <c r="E138" s="13" t="n">
-        <v>4103</v>
+        <v>4102</v>
       </c>
       <c r="F138" s="13" t="n">
         <v>12</v>
@@ -6568,7 +6568,7 @@
         </is>
       </c>
       <c r="E139" s="13" t="n">
-        <v>4117</v>
+        <v>4116</v>
       </c>
       <c r="F139" s="13" t="n">
         <v>12</v>
@@ -6596,7 +6596,7 @@
         </is>
       </c>
       <c r="E140" s="13" t="n">
-        <v>4132</v>
+        <v>4131</v>
       </c>
       <c r="F140" s="13" t="n">
         <v>18</v>
@@ -6624,7 +6624,7 @@
         </is>
       </c>
       <c r="E141" s="13" t="n">
-        <v>4153</v>
+        <v>4152</v>
       </c>
       <c r="F141" s="13" t="n">
         <v>15</v>
@@ -6652,7 +6652,7 @@
         </is>
       </c>
       <c r="E142" s="13" t="n">
-        <v>4171</v>
+        <v>4170</v>
       </c>
       <c r="F142" s="13" t="n">
         <v>14</v>
@@ -6680,7 +6680,7 @@
         </is>
       </c>
       <c r="E143" s="13" t="n">
-        <v>4188</v>
+        <v>4187</v>
       </c>
       <c r="F143" s="13" t="n">
         <v>10</v>
@@ -6708,7 +6708,7 @@
         </is>
       </c>
       <c r="E144" s="13" t="n">
-        <v>4200</v>
+        <v>4199</v>
       </c>
       <c r="F144" s="13" t="n">
         <v>15</v>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="E145" s="13" t="n">
-        <v>4218</v>
+        <v>4217</v>
       </c>
       <c r="F145" s="13" t="n">
         <v>11</v>
@@ -6764,7 +6764,7 @@
         </is>
       </c>
       <c r="E146" s="13" t="n">
-        <v>4232</v>
+        <v>4231</v>
       </c>
       <c r="F146" s="13" t="n">
         <v>11</v>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="E147" s="13" t="n">
-        <v>4245</v>
+        <v>4244</v>
       </c>
       <c r="F147" s="13" t="n">
         <v>13</v>
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="E148" s="13" t="n">
-        <v>4261</v>
+        <v>4260</v>
       </c>
       <c r="F148" s="13" t="n">
         <v>12</v>
@@ -6848,7 +6848,7 @@
         </is>
       </c>
       <c r="E149" s="13" t="n">
-        <v>4276</v>
+        <v>4275</v>
       </c>
       <c r="F149" s="13" t="n">
         <v>10</v>
@@ -6876,7 +6876,7 @@
         </is>
       </c>
       <c r="E150" s="13" t="n">
-        <v>4288</v>
+        <v>4287</v>
       </c>
       <c r="F150" s="13" t="n">
         <v>8</v>
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="E151" s="13" t="n">
-        <v>4299</v>
+        <v>4298</v>
       </c>
       <c r="F151" s="13" t="n">
         <v>12</v>
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="E152" s="13" t="n">
-        <v>4314</v>
+        <v>4313</v>
       </c>
       <c r="F152" s="13" t="n">
         <v>11</v>
@@ -6960,7 +6960,7 @@
         </is>
       </c>
       <c r="E153" s="13" t="n">
-        <v>4327</v>
+        <v>4326</v>
       </c>
       <c r="F153" s="13" t="n">
         <v>9</v>
@@ -6988,7 +6988,7 @@
         </is>
       </c>
       <c r="E154" s="13" t="n">
-        <v>4339</v>
+        <v>4338</v>
       </c>
       <c r="F154" s="13" t="n">
         <v>19</v>
@@ -7016,7 +7016,7 @@
         </is>
       </c>
       <c r="E155" s="13" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F155" s="13" t="n">
         <v>10</v>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="E156" s="13" t="n">
-        <v>4375</v>
+        <v>4374</v>
       </c>
       <c r="F156" s="13" t="n">
         <v>11</v>
@@ -7072,7 +7072,7 @@
         </is>
       </c>
       <c r="E157" s="13" t="n">
-        <v>4388</v>
+        <v>4387</v>
       </c>
       <c r="F157" s="13" t="n">
         <v>10</v>
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="E158" s="13" t="n">
-        <v>4401</v>
+        <v>4400</v>
       </c>
       <c r="F158" s="13" t="n">
         <v>8</v>
@@ -7128,7 +7128,7 @@
         </is>
       </c>
       <c r="E159" s="13" t="n">
-        <v>4411</v>
+        <v>4410</v>
       </c>
       <c r="F159" s="13" t="n">
         <v>7</v>
@@ -7156,7 +7156,7 @@
         </is>
       </c>
       <c r="E160" s="13" t="n">
-        <v>4421</v>
+        <v>4420</v>
       </c>
       <c r="F160" s="13" t="n">
         <v>19</v>
@@ -7184,7 +7184,7 @@
         </is>
       </c>
       <c r="E161" s="13" t="n">
-        <v>4442</v>
+        <v>4441</v>
       </c>
       <c r="F161" s="13" t="n">
         <v>12</v>
@@ -7212,7 +7212,7 @@
         </is>
       </c>
       <c r="E162" s="13" t="n">
-        <v>4456</v>
+        <v>4455</v>
       </c>
       <c r="F162" s="13" t="n">
         <v>12</v>
@@ -7240,7 +7240,7 @@
         </is>
       </c>
       <c r="E163" s="13" t="n">
-        <v>4471</v>
+        <v>4470</v>
       </c>
       <c r="F163" s="13" t="n">
         <v>11</v>
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="E164" s="13" t="n">
-        <v>4485</v>
+        <v>4484</v>
       </c>
       <c r="F164" s="13" t="n">
         <v>10</v>
@@ -7296,7 +7296,7 @@
         </is>
       </c>
       <c r="E165" s="13" t="n">
-        <v>4497</v>
+        <v>4496</v>
       </c>
       <c r="F165" s="13" t="n">
         <v>9</v>
@@ -7324,7 +7324,7 @@
         </is>
       </c>
       <c r="E166" s="13" t="n">
-        <v>4509</v>
+        <v>4508</v>
       </c>
       <c r="F166" s="13" t="n">
         <v>8</v>
@@ -7352,7 +7352,7 @@
         </is>
       </c>
       <c r="E167" s="13" t="n">
-        <v>4519</v>
+        <v>4518</v>
       </c>
       <c r="F167" s="13" t="n">
         <v>10</v>
@@ -7380,7 +7380,7 @@
         </is>
       </c>
       <c r="E168" s="13" t="n">
-        <v>4532</v>
+        <v>4531</v>
       </c>
       <c r="F168" s="13" t="n">
         <v>11</v>
@@ -7408,7 +7408,7 @@
         </is>
       </c>
       <c r="E169" s="13" t="n">
-        <v>4546</v>
+        <v>4545</v>
       </c>
       <c r="F169" s="13" t="n">
         <v>12</v>
@@ -7436,7 +7436,7 @@
         </is>
       </c>
       <c r="E170" s="13" t="n">
-        <v>4561</v>
+        <v>4560</v>
       </c>
       <c r="F170" s="13" t="n">
         <v>9</v>
@@ -7464,7 +7464,7 @@
         </is>
       </c>
       <c r="E171" s="13" t="n">
-        <v>4572</v>
+        <v>4571</v>
       </c>
       <c r="F171" s="13" t="n">
         <v>10</v>
@@ -7492,7 +7492,7 @@
         </is>
       </c>
       <c r="E172" s="13" t="n">
-        <v>4585</v>
+        <v>4584</v>
       </c>
       <c r="F172" s="13" t="n">
         <v>9</v>
@@ -7520,7 +7520,7 @@
         </is>
       </c>
       <c r="E173" s="13" t="n">
-        <v>4597</v>
+        <v>4596</v>
       </c>
       <c r="F173" s="13" t="n">
         <v>10</v>
@@ -7548,7 +7548,7 @@
         </is>
       </c>
       <c r="E174" s="13" t="n">
-        <v>4609</v>
+        <v>4608</v>
       </c>
       <c r="F174" s="13" t="n">
         <v>17</v>
@@ -7576,7 +7576,7 @@
         </is>
       </c>
       <c r="E175" s="13" t="n">
-        <v>4629</v>
+        <v>4628</v>
       </c>
       <c r="F175" s="13" t="n">
         <v>18</v>
@@ -7604,7 +7604,7 @@
         </is>
       </c>
       <c r="E176" s="13" t="n">
-        <v>4650</v>
+        <v>4649</v>
       </c>
       <c r="F176" s="13" t="n">
         <v>16</v>
@@ -7632,7 +7632,7 @@
         </is>
       </c>
       <c r="E177" s="13" t="n">
-        <v>4669</v>
+        <v>4668</v>
       </c>
       <c r="F177" s="13" t="n">
         <v>14</v>
@@ -7660,7 +7660,7 @@
         </is>
       </c>
       <c r="E178" s="13" t="n">
-        <v>4686</v>
+        <v>4685</v>
       </c>
       <c r="F178" s="13" t="n">
         <v>11</v>
@@ -7688,7 +7688,7 @@
         </is>
       </c>
       <c r="E179" s="13" t="n">
-        <v>4699</v>
+        <v>4698</v>
       </c>
       <c r="F179" s="13" t="n">
         <v>16</v>
@@ -7716,7 +7716,7 @@
         </is>
       </c>
       <c r="E180" s="13" t="n">
-        <v>4717</v>
+        <v>4716</v>
       </c>
       <c r="F180" s="13" t="n">
         <v>13</v>
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="E181" s="13" t="n">
-        <v>4733</v>
+        <v>4732</v>
       </c>
       <c r="F181" s="13" t="n">
         <v>15</v>
@@ -7772,7 +7772,7 @@
         </is>
       </c>
       <c r="E182" s="13" t="n">
-        <v>4751</v>
+        <v>4750</v>
       </c>
       <c r="F182" s="13" t="n">
         <v>15</v>
@@ -7800,7 +7800,7 @@
         </is>
       </c>
       <c r="E183" s="13" t="n">
-        <v>4769</v>
+        <v>4768</v>
       </c>
       <c r="F183" s="13" t="n">
         <v>12</v>
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="E184" s="13" t="n">
-        <v>4783</v>
+        <v>4782</v>
       </c>
       <c r="F184" s="13" t="n">
         <v>12</v>
@@ -7856,7 +7856,7 @@
         </is>
       </c>
       <c r="E185" s="13" t="n">
-        <v>4798</v>
+        <v>4797</v>
       </c>
       <c r="F185" s="13" t="n">
         <v>13</v>
@@ -7884,7 +7884,7 @@
         </is>
       </c>
       <c r="E186" s="13" t="n">
-        <v>4814</v>
+        <v>4813</v>
       </c>
       <c r="F186" s="13" t="n">
         <v>12</v>
@@ -7912,7 +7912,7 @@
         </is>
       </c>
       <c r="E187" s="13" t="n">
-        <v>4828</v>
+        <v>4827</v>
       </c>
       <c r="F187" s="13" t="n">
         <v>12</v>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="E188" s="13" t="n">
-        <v>4842</v>
+        <v>4841</v>
       </c>
       <c r="F188" s="13" t="n">
         <v>11</v>
@@ -7968,7 +7968,7 @@
         </is>
       </c>
       <c r="E189" s="13" t="n">
-        <v>4856</v>
+        <v>4855</v>
       </c>
       <c r="F189" s="13" t="n">
         <v>12</v>
@@ -7996,7 +7996,7 @@
         </is>
       </c>
       <c r="E190" s="13" t="n">
-        <v>4870</v>
+        <v>4869</v>
       </c>
       <c r="F190" s="13" t="n">
         <v>12</v>
@@ -8024,7 +8024,7 @@
         </is>
       </c>
       <c r="E191" s="13" t="n">
-        <v>4884</v>
+        <v>4883</v>
       </c>
       <c r="F191" s="13" t="n">
         <v>13</v>
@@ -8052,7 +8052,7 @@
         </is>
       </c>
       <c r="E192" s="13" t="n">
-        <v>4900</v>
+        <v>4899</v>
       </c>
       <c r="F192" s="13" t="n">
         <v>10</v>
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="E193" s="13" t="n">
-        <v>4912</v>
+        <v>4911</v>
       </c>
       <c r="F193" s="13" t="n">
         <v>12</v>
@@ -8108,7 +8108,7 @@
         </is>
       </c>
       <c r="E194" s="13" t="n">
-        <v>4926</v>
+        <v>4925</v>
       </c>
       <c r="F194" s="13" t="n">
         <v>10</v>
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="E195" s="13" t="n">
-        <v>4939</v>
+        <v>4938</v>
       </c>
       <c r="F195" s="13" t="n">
         <v>12</v>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="E196" s="13" t="n">
-        <v>4953</v>
+        <v>4952</v>
       </c>
       <c r="F196" s="13" t="n">
         <v>12</v>
@@ -8192,7 +8192,7 @@
         </is>
       </c>
       <c r="E197" s="13" t="n">
-        <v>4968</v>
+        <v>4967</v>
       </c>
       <c r="F197" s="13" t="n">
         <v>12</v>
@@ -8220,7 +8220,7 @@
         </is>
       </c>
       <c r="E198" s="13" t="n">
-        <v>4983</v>
+        <v>4982</v>
       </c>
       <c r="F198" s="13" t="n">
         <v>10</v>
@@ -8248,7 +8248,7 @@
         </is>
       </c>
       <c r="E199" s="13" t="n">
-        <v>4995</v>
+        <v>4994</v>
       </c>
       <c r="F199" s="13" t="n">
         <v>10</v>
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="E200" s="13" t="n">
-        <v>5008</v>
+        <v>5007</v>
       </c>
       <c r="F200" s="13" t="n">
         <v>14</v>
@@ -8304,7 +8304,7 @@
         </is>
       </c>
       <c r="E201" s="13" t="n">
-        <v>5025</v>
+        <v>5024</v>
       </c>
       <c r="F201" s="13" t="n">
         <v>12</v>
@@ -8332,7 +8332,7 @@
         </is>
       </c>
       <c r="E202" s="13" t="n">
-        <v>5039</v>
+        <v>5038</v>
       </c>
       <c r="F202" s="13" t="n">
         <v>19</v>
@@ -8360,7 +8360,7 @@
         </is>
       </c>
       <c r="E203" s="13" t="n">
-        <v>5061</v>
+        <v>5060</v>
       </c>
       <c r="F203" s="13" t="n">
         <v>15</v>
@@ -8388,7 +8388,7 @@
         </is>
       </c>
       <c r="E204" s="13" t="n">
-        <v>5079</v>
+        <v>5078</v>
       </c>
       <c r="F204" s="13" t="n">
         <v>13</v>
@@ -8416,7 +8416,7 @@
         </is>
       </c>
       <c r="E205" s="13" t="n">
-        <v>5095</v>
+        <v>5094</v>
       </c>
       <c r="F205" s="13" t="n">
         <v>14</v>
@@ -8444,7 +8444,7 @@
         </is>
       </c>
       <c r="E206" s="13" t="n">
-        <v>5112</v>
+        <v>5111</v>
       </c>
       <c r="F206" s="13" t="n">
         <v>10</v>
@@ -8472,7 +8472,7 @@
         </is>
       </c>
       <c r="E207" s="13" t="n">
-        <v>5124</v>
+        <v>5123</v>
       </c>
       <c r="F207" s="13" t="n">
         <v>15</v>
@@ -8500,7 +8500,7 @@
         </is>
       </c>
       <c r="E208" s="13" t="n">
-        <v>5142</v>
+        <v>5141</v>
       </c>
       <c r="F208" s="13" t="n">
         <v>10</v>
@@ -8528,7 +8528,7 @@
         </is>
       </c>
       <c r="E209" s="13" t="n">
-        <v>5155</v>
+        <v>5154</v>
       </c>
       <c r="F209" s="13" t="n">
         <v>13</v>
@@ -8556,7 +8556,7 @@
         </is>
       </c>
       <c r="E210" s="13" t="n">
-        <v>5170</v>
+        <v>5169</v>
       </c>
       <c r="F210" s="13" t="n">
         <v>11</v>
@@ -8584,7 +8584,7 @@
         </is>
       </c>
       <c r="E211" s="13" t="n">
-        <v>5184</v>
+        <v>5183</v>
       </c>
       <c r="F211" s="13" t="n">
         <v>12</v>
@@ -8612,7 +8612,7 @@
         </is>
       </c>
       <c r="E212" s="13" t="n">
-        <v>5199</v>
+        <v>5198</v>
       </c>
       <c r="F212" s="13" t="n">
         <v>10</v>
@@ -8640,7 +8640,7 @@
         </is>
       </c>
       <c r="E213" s="13" t="n">
-        <v>5211</v>
+        <v>5210</v>
       </c>
       <c r="F213" s="13" t="n">
         <v>11</v>
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="E214" s="13" t="n">
-        <v>5225</v>
+        <v>5224</v>
       </c>
       <c r="F214" s="13" t="n">
         <v>12</v>
@@ -8696,7 +8696,7 @@
         </is>
       </c>
       <c r="E215" s="13" t="n">
-        <v>5240</v>
+        <v>5239</v>
       </c>
       <c r="F215" s="13" t="n">
         <v>11</v>
@@ -8724,7 +8724,7 @@
         </is>
       </c>
       <c r="E216" s="13" t="n">
-        <v>5253</v>
+        <v>5252</v>
       </c>
       <c r="F216" s="13" t="n">
         <v>10</v>
@@ -8752,7 +8752,7 @@
         </is>
       </c>
       <c r="E217" s="13" t="n">
-        <v>5266</v>
+        <v>5265</v>
       </c>
       <c r="F217" s="13" t="n">
         <v>10</v>
@@ -8780,7 +8780,7 @@
         </is>
       </c>
       <c r="E218" s="13" t="n">
-        <v>5278</v>
+        <v>5277</v>
       </c>
       <c r="F218" s="13" t="n">
         <v>12</v>
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="E219" s="13" t="n">
-        <v>5293</v>
+        <v>5292</v>
       </c>
       <c r="F219" s="13" t="n">
         <v>13</v>
@@ -8836,7 +8836,7 @@
         </is>
       </c>
       <c r="E220" s="13" t="n">
-        <v>5309</v>
+        <v>5308</v>
       </c>
       <c r="F220" s="13" t="n">
         <v>10</v>
@@ -8864,7 +8864,7 @@
         </is>
       </c>
       <c r="E221" s="13" t="n">
-        <v>5321</v>
+        <v>5320</v>
       </c>
       <c r="F221" s="13" t="n">
         <v>13</v>
@@ -8892,7 +8892,7 @@
         </is>
       </c>
       <c r="E222" s="13" t="n">
-        <v>5337</v>
+        <v>5336</v>
       </c>
       <c r="F222" s="13" t="n">
         <v>10</v>
@@ -8920,7 +8920,7 @@
         </is>
       </c>
       <c r="E223" s="13" t="n">
-        <v>5349</v>
+        <v>5348</v>
       </c>
       <c r="F223" s="13" t="n">
         <v>11</v>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="E224" s="13" t="n">
-        <v>5362</v>
+        <v>5361</v>
       </c>
       <c r="F224" s="13" t="n">
         <v>13</v>
@@ -8976,7 +8976,7 @@
         </is>
       </c>
       <c r="E225" s="13" t="n">
-        <v>5378</v>
+        <v>5377</v>
       </c>
       <c r="F225" s="13" t="n">
         <v>9</v>
@@ -9004,7 +9004,7 @@
         </is>
       </c>
       <c r="E226" s="13" t="n">
-        <v>5389</v>
+        <v>5388</v>
       </c>
       <c r="F226" s="13" t="n">
         <v>13</v>
@@ -9032,7 +9032,7 @@
         </is>
       </c>
       <c r="E227" s="13" t="n">
-        <v>5405</v>
+        <v>5404</v>
       </c>
       <c r="F227" s="13" t="n">
         <v>11</v>
@@ -9060,7 +9060,7 @@
         </is>
       </c>
       <c r="E228" s="13" t="n">
-        <v>5419</v>
+        <v>5418</v>
       </c>
       <c r="F228" s="13" t="n">
         <v>11</v>
@@ -9088,7 +9088,7 @@
         </is>
       </c>
       <c r="E229" s="13" t="n">
-        <v>5432</v>
+        <v>5431</v>
       </c>
       <c r="F229" s="13" t="n">
         <v>10</v>
@@ -9116,7 +9116,7 @@
         </is>
       </c>
       <c r="E230" s="13" t="n">
-        <v>5445</v>
+        <v>5444</v>
       </c>
       <c r="F230" s="13" t="n">
         <v>11</v>
@@ -9144,7 +9144,7 @@
         </is>
       </c>
       <c r="E231" s="13" t="n">
-        <v>5459</v>
+        <v>5458</v>
       </c>
       <c r="F231" s="13" t="n">
         <v>12</v>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="E232" s="13" t="n">
-        <v>5473</v>
+        <v>5472</v>
       </c>
       <c r="F232" s="13" t="n">
         <v>11</v>
@@ -9200,7 +9200,7 @@
         </is>
       </c>
       <c r="E233" s="13" t="n">
-        <v>5487</v>
+        <v>5486</v>
       </c>
       <c r="F233" s="13" t="n">
         <v>10</v>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="E234" s="13" t="n">
-        <v>5499</v>
+        <v>5498</v>
       </c>
       <c r="F234" s="13" t="n">
         <v>11</v>
@@ -9256,7 +9256,7 @@
         </is>
       </c>
       <c r="E235" s="13" t="n">
-        <v>5512</v>
+        <v>5511</v>
       </c>
       <c r="F235" s="13" t="n">
         <v>13</v>
@@ -9284,7 +9284,7 @@
         </is>
       </c>
       <c r="E236" s="13" t="n">
-        <v>5528</v>
+        <v>5527</v>
       </c>
       <c r="F236" s="13" t="n">
         <v>12</v>
@@ -9312,7 +9312,7 @@
         </is>
       </c>
       <c r="E237" s="13" t="n">
-        <v>5542</v>
+        <v>5541</v>
       </c>
       <c r="F237" s="13" t="n">
         <v>10</v>
@@ -9340,7 +9340,7 @@
         </is>
       </c>
       <c r="E238" s="13" t="n">
-        <v>5555</v>
+        <v>5554</v>
       </c>
       <c r="F238" s="13" t="n">
         <v>10</v>
@@ -9368,7 +9368,7 @@
         </is>
       </c>
       <c r="E239" s="13" t="n">
-        <v>5568</v>
+        <v>5567</v>
       </c>
       <c r="F239" s="13" t="n">
         <v>11</v>
@@ -9396,7 +9396,7 @@
         </is>
       </c>
       <c r="E240" s="13" t="n">
-        <v>5581</v>
+        <v>5580</v>
       </c>
       <c r="F240" s="13" t="n">
         <v>9</v>
@@ -9424,7 +9424,7 @@
         </is>
       </c>
       <c r="E241" s="13" t="n">
-        <v>5593</v>
+        <v>5592</v>
       </c>
       <c r="F241" s="13" t="n">
         <v>9</v>
@@ -9452,7 +9452,7 @@
         </is>
       </c>
       <c r="E242" s="13" t="n">
-        <v>5604</v>
+        <v>5603</v>
       </c>
       <c r="F242" s="13" t="n">
         <v>10</v>
@@ -9480,7 +9480,7 @@
         </is>
       </c>
       <c r="E243" s="13" t="n">
-        <v>5617</v>
+        <v>5616</v>
       </c>
       <c r="F243" s="13" t="n">
         <v>16</v>
@@ -9508,7 +9508,7 @@
         </is>
       </c>
       <c r="E244" s="13" t="n">
-        <v>5636</v>
+        <v>5635</v>
       </c>
       <c r="F244" s="13" t="n">
         <v>16</v>
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="E245" s="13" t="n">
-        <v>5655</v>
+        <v>5654</v>
       </c>
       <c r="F245" s="13" t="n">
         <v>14</v>
@@ -9564,7 +9564,7 @@
         </is>
       </c>
       <c r="E246" s="13" t="n">
-        <v>5671</v>
+        <v>5670</v>
       </c>
       <c r="F246" s="13" t="n">
         <v>10</v>
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="E247" s="13" t="n">
-        <v>5684</v>
+        <v>5683</v>
       </c>
       <c r="F247" s="13" t="n">
         <v>8</v>
@@ -9620,7 +9620,7 @@
         </is>
       </c>
       <c r="E248" s="13" t="n">
-        <v>5694</v>
+        <v>5693</v>
       </c>
       <c r="F248" s="13" t="n">
         <v>13</v>
@@ -9648,7 +9648,7 @@
         </is>
       </c>
       <c r="E249" s="13" t="n">
-        <v>5709</v>
+        <v>5708</v>
       </c>
       <c r="F249" s="13" t="n">
         <v>10</v>
@@ -9676,7 +9676,7 @@
         </is>
       </c>
       <c r="E250" s="13" t="n">
-        <v>5722</v>
+        <v>5721</v>
       </c>
       <c r="F250" s="13" t="n">
         <v>11</v>
@@ -9704,7 +9704,7 @@
         </is>
       </c>
       <c r="E251" s="13" t="n">
-        <v>5735</v>
+        <v>5734</v>
       </c>
       <c r="F251" s="13" t="n">
         <v>11</v>
@@ -9732,7 +9732,7 @@
         </is>
       </c>
       <c r="E252" s="13" t="n">
-        <v>5749</v>
+        <v>5748</v>
       </c>
       <c r="F252" s="13" t="n">
         <v>11</v>
@@ -9760,7 +9760,7 @@
         </is>
       </c>
       <c r="E253" s="13" t="n">
-        <v>5762</v>
+        <v>5761</v>
       </c>
       <c r="F253" s="13" t="n">
         <v>11</v>
@@ -9788,7 +9788,7 @@
         </is>
       </c>
       <c r="E254" s="13" t="n">
-        <v>5775</v>
+        <v>5774</v>
       </c>
       <c r="F254" s="13" t="n">
         <v>10</v>
@@ -9816,7 +9816,7 @@
         </is>
       </c>
       <c r="E255" s="13" t="n">
-        <v>5788</v>
+        <v>5787</v>
       </c>
       <c r="F255" s="13" t="n">
         <v>9</v>
@@ -9844,7 +9844,7 @@
         </is>
       </c>
       <c r="E256" s="13" t="n">
-        <v>5799</v>
+        <v>5798</v>
       </c>
       <c r="F256" s="13" t="n">
         <v>10</v>
@@ -9872,7 +9872,7 @@
         </is>
       </c>
       <c r="E257" s="13" t="n">
-        <v>5812</v>
+        <v>5811</v>
       </c>
       <c r="F257" s="13" t="n">
         <v>10</v>
@@ -9900,7 +9900,7 @@
         </is>
       </c>
       <c r="E258" s="13" t="n">
-        <v>5824</v>
+        <v>5823</v>
       </c>
       <c r="F258" s="13" t="n">
         <v>11</v>
@@ -9928,7 +9928,7 @@
         </is>
       </c>
       <c r="E259" s="13" t="n">
-        <v>5838</v>
+        <v>5837</v>
       </c>
       <c r="F259" s="13" t="n">
         <v>12</v>
@@ -9956,7 +9956,7 @@
         </is>
       </c>
       <c r="E260" s="13" t="n">
-        <v>5853</v>
+        <v>5852</v>
       </c>
       <c r="F260" s="13" t="n">
         <v>5</v>
@@ -9984,7 +9984,7 @@
         </is>
       </c>
       <c r="E261" s="13" t="n">
-        <v>5860</v>
+        <v>5859</v>
       </c>
       <c r="F261" s="13" t="n">
         <v>6</v>
@@ -10012,7 +10012,7 @@
         </is>
       </c>
       <c r="E262" s="13" t="n">
-        <v>5869</v>
+        <v>5868</v>
       </c>
       <c r="F262" s="13" t="n">
         <v>31</v>
@@ -10040,7 +10040,7 @@
         </is>
       </c>
       <c r="E263" s="13" t="n">
-        <v>5904</v>
+        <v>5903</v>
       </c>
       <c r="F263" s="13" t="n">
         <v>22</v>
@@ -10068,7 +10068,7 @@
         </is>
       </c>
       <c r="E264" s="13" t="n">
-        <v>5929</v>
+        <v>5928</v>
       </c>
       <c r="F264" s="13" t="n">
         <v>15</v>
@@ -10096,7 +10096,7 @@
         </is>
       </c>
       <c r="E265" s="13" t="n">
-        <v>5946</v>
+        <v>5945</v>
       </c>
       <c r="F265" s="13" t="n">
         <v>7</v>
@@ -10124,7 +10124,7 @@
         </is>
       </c>
       <c r="E266" s="13" t="n">
-        <v>5955</v>
+        <v>5954</v>
       </c>
       <c r="F266" s="13" t="n">
         <v>17</v>
@@ -10152,7 +10152,7 @@
         </is>
       </c>
       <c r="E267" s="13" t="n">
-        <v>5975</v>
+        <v>5974</v>
       </c>
       <c r="F267" s="13" t="n">
         <v>16</v>
@@ -10180,7 +10180,7 @@
         </is>
       </c>
       <c r="E268" s="13" t="n">
-        <v>5994</v>
+        <v>5993</v>
       </c>
       <c r="F268" s="13" t="n">
         <v>17</v>
@@ -10208,7 +10208,7 @@
         </is>
       </c>
       <c r="E269" s="13" t="n">
-        <v>6014</v>
+        <v>6013</v>
       </c>
       <c r="F269" s="13" t="n">
         <v>25</v>
@@ -10236,7 +10236,7 @@
         </is>
       </c>
       <c r="E270" s="13" t="n">
-        <v>6042</v>
+        <v>6041</v>
       </c>
       <c r="F270" s="13" t="n">
         <v>13</v>
@@ -10264,7 +10264,7 @@
         </is>
       </c>
       <c r="E271" s="13" t="n">
-        <v>6058</v>
+        <v>6057</v>
       </c>
       <c r="F271" s="13" t="n">
         <v>11</v>
@@ -10292,7 +10292,7 @@
         </is>
       </c>
       <c r="E272" s="13" t="n">
-        <v>6072</v>
+        <v>6071</v>
       </c>
       <c r="F272" s="13" t="n">
         <v>16</v>
@@ -10320,7 +10320,7 @@
         </is>
       </c>
       <c r="E273" s="13" t="n">
-        <v>6090</v>
+        <v>6089</v>
       </c>
       <c r="F273" s="13" t="n">
         <v>11</v>
@@ -10348,7 +10348,7 @@
         </is>
       </c>
       <c r="E274" s="13" t="n">
-        <v>6104</v>
+        <v>6103</v>
       </c>
       <c r="F274" s="13" t="n">
         <v>16</v>
@@ -10376,7 +10376,7 @@
         </is>
       </c>
       <c r="E275" s="13" t="n">
-        <v>6123</v>
+        <v>6122</v>
       </c>
       <c r="F275" s="13" t="n">
         <v>10</v>
@@ -10404,7 +10404,7 @@
         </is>
       </c>
       <c r="E276" s="13" t="n">
-        <v>6136</v>
+        <v>6135</v>
       </c>
       <c r="F276" s="13" t="n">
         <v>13</v>
@@ -10432,7 +10432,7 @@
         </is>
       </c>
       <c r="E277" s="13" t="n">
-        <v>6151</v>
+        <v>6150</v>
       </c>
       <c r="F277" s="13" t="n">
         <v>10</v>
@@ -10460,7 +10460,7 @@
         </is>
       </c>
       <c r="E278" s="13" t="n">
-        <v>6164</v>
+        <v>6163</v>
       </c>
       <c r="F278" s="13" t="n">
         <v>14</v>
@@ -10488,7 +10488,7 @@
         </is>
       </c>
       <c r="E279" s="13" t="n">
-        <v>6181</v>
+        <v>6180</v>
       </c>
       <c r="F279" s="13" t="n">
         <v>14</v>
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="E280" s="13" t="n">
-        <v>6197</v>
+        <v>6196</v>
       </c>
       <c r="F280" s="13" t="n">
         <v>9</v>
@@ -10544,7 +10544,7 @@
         </is>
       </c>
       <c r="E281" s="13" t="n">
-        <v>6209</v>
+        <v>6208</v>
       </c>
       <c r="F281" s="13" t="n">
         <v>11</v>
@@ -10572,7 +10572,7 @@
         </is>
       </c>
       <c r="E282" s="13" t="n">
-        <v>6222</v>
+        <v>6221</v>
       </c>
       <c r="F282" s="13" t="n">
         <v>10</v>
@@ -10600,7 +10600,7 @@
         </is>
       </c>
       <c r="E283" s="13" t="n">
-        <v>6234</v>
+        <v>6233</v>
       </c>
       <c r="F283" s="13" t="n">
         <v>9</v>
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="E284" s="13" t="n">
-        <v>6245</v>
+        <v>6244</v>
       </c>
       <c r="F284" s="13" t="n">
         <v>11</v>
@@ -10656,7 +10656,7 @@
         </is>
       </c>
       <c r="E285" s="13" t="n">
-        <v>6259</v>
+        <v>6258</v>
       </c>
       <c r="F285" s="13" t="n">
         <v>11</v>
@@ -10684,7 +10684,7 @@
         </is>
       </c>
       <c r="E286" s="13" t="n">
-        <v>6273</v>
+        <v>6272</v>
       </c>
       <c r="F286" s="13" t="n">
         <v>17</v>
@@ -10712,7 +10712,7 @@
         </is>
       </c>
       <c r="E287" s="13" t="n">
-        <v>6292</v>
+        <v>6291</v>
       </c>
       <c r="F287" s="13" t="n">
         <v>9</v>
@@ -10740,7 +10740,7 @@
         </is>
       </c>
       <c r="E288" s="13" t="n">
-        <v>6303</v>
+        <v>6302</v>
       </c>
       <c r="F288" s="13" t="n">
         <v>9</v>
@@ -10768,7 +10768,7 @@
         </is>
       </c>
       <c r="E289" s="13" t="n">
-        <v>6315</v>
+        <v>6314</v>
       </c>
       <c r="F289" s="13" t="n">
         <v>11</v>
@@ -10796,7 +10796,7 @@
         </is>
       </c>
       <c r="E290" s="13" t="n">
-        <v>6328</v>
+        <v>6327</v>
       </c>
       <c r="F290" s="13" t="n">
         <v>12</v>
@@ -10824,7 +10824,7 @@
         </is>
       </c>
       <c r="E291" s="13" t="n">
-        <v>6343</v>
+        <v>6342</v>
       </c>
       <c r="F291" s="13" t="n">
         <v>13</v>
@@ -10852,7 +10852,7 @@
         </is>
       </c>
       <c r="E292" s="13" t="n">
-        <v>6359</v>
+        <v>6358</v>
       </c>
       <c r="F292" s="13" t="n">
         <v>20</v>
@@ -10880,7 +10880,7 @@
         </is>
       </c>
       <c r="E293" s="13" t="n">
-        <v>6382</v>
+        <v>6381</v>
       </c>
       <c r="F293" s="13" t="n">
         <v>10</v>
@@ -10908,7 +10908,7 @@
         </is>
       </c>
       <c r="E294" s="13" t="n">
-        <v>6394</v>
+        <v>6393</v>
       </c>
       <c r="F294" s="13" t="n">
         <v>18</v>
@@ -10936,7 +10936,7 @@
         </is>
       </c>
       <c r="E295" s="13" t="n">
-        <v>6415</v>
+        <v>6414</v>
       </c>
       <c r="F295" s="13" t="n">
         <v>10</v>
@@ -10964,7 +10964,7 @@
         </is>
       </c>
       <c r="E296" s="13" t="n">
-        <v>6428</v>
+        <v>6427</v>
       </c>
       <c r="F296" s="13" t="n">
         <v>10</v>
@@ -10992,7 +10992,7 @@
         </is>
       </c>
       <c r="E297" s="13" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F297" s="13" t="n">
         <v>33</v>
@@ -11020,7 +11020,7 @@
         </is>
       </c>
       <c r="E298" s="13" t="n">
-        <v>6477</v>
+        <v>6476</v>
       </c>
       <c r="F298" s="13" t="n">
         <v>12</v>
@@ -11048,7 +11048,7 @@
         </is>
       </c>
       <c r="E299" s="13" t="n">
-        <v>6491</v>
+        <v>6490</v>
       </c>
       <c r="F299" s="13" t="n">
         <v>13</v>
@@ -11076,7 +11076,7 @@
         </is>
       </c>
       <c r="E300" s="13" t="n">
-        <v>6507</v>
+        <v>6506</v>
       </c>
       <c r="F300" s="13" t="n">
         <v>14</v>
@@ -11104,7 +11104,7 @@
         </is>
       </c>
       <c r="E301" s="13" t="n">
-        <v>6524</v>
+        <v>6523</v>
       </c>
       <c r="F301" s="13" t="n">
         <v>11</v>
@@ -11132,7 +11132,7 @@
         </is>
       </c>
       <c r="E302" s="13" t="n">
-        <v>6537</v>
+        <v>6536</v>
       </c>
       <c r="F302" s="13" t="n">
         <v>12</v>
@@ -11160,7 +11160,7 @@
         </is>
       </c>
       <c r="E303" s="13" t="n">
-        <v>6552</v>
+        <v>6551</v>
       </c>
       <c r="F303" s="13" t="n">
         <v>13</v>
@@ -11188,7 +11188,7 @@
         </is>
       </c>
       <c r="E304" s="13" t="n">
-        <v>6567</v>
+        <v>6566</v>
       </c>
       <c r="F304" s="13" t="n">
         <v>13</v>
@@ -11216,7 +11216,7 @@
         </is>
       </c>
       <c r="E305" s="13" t="n">
-        <v>6582</v>
+        <v>6581</v>
       </c>
       <c r="F305" s="13" t="n">
         <v>14</v>
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="E306" s="13" t="n">
-        <v>6599</v>
+        <v>6598</v>
       </c>
       <c r="F306" s="13" t="n">
         <v>11</v>
@@ -11272,7 +11272,7 @@
         </is>
       </c>
       <c r="E307" s="13" t="n">
-        <v>6612</v>
+        <v>6611</v>
       </c>
       <c r="F307" s="13" t="n">
         <v>15</v>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="E308" s="13" t="n">
-        <v>6630</v>
+        <v>6629</v>
       </c>
       <c r="F308" s="13" t="n">
         <v>13</v>
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="E309" s="13" t="n">
-        <v>6646</v>
+        <v>6645</v>
       </c>
       <c r="F309" s="13" t="n">
         <v>11</v>
@@ -11356,7 +11356,7 @@
         </is>
       </c>
       <c r="E310" s="13" t="n">
-        <v>6659</v>
+        <v>6658</v>
       </c>
       <c r="F310" s="13" t="n">
         <v>13</v>
@@ -11384,7 +11384,7 @@
         </is>
       </c>
       <c r="E311" s="13" t="n">
-        <v>6674</v>
+        <v>6673</v>
       </c>
       <c r="F311" s="13" t="n">
         <v>10</v>
@@ -11412,7 +11412,7 @@
         </is>
       </c>
       <c r="E312" s="13" t="n">
-        <v>6687</v>
+        <v>6686</v>
       </c>
       <c r="F312" s="13" t="n">
         <v>10</v>
@@ -11440,7 +11440,7 @@
         </is>
       </c>
       <c r="E313" s="13" t="n">
-        <v>6699</v>
+        <v>6698</v>
       </c>
       <c r="F313" s="13" t="n">
         <v>15</v>
@@ -11468,7 +11468,7 @@
         </is>
       </c>
       <c r="E314" s="13" t="n">
-        <v>6717</v>
+        <v>6716</v>
       </c>
       <c r="F314" s="13" t="n">
         <v>12</v>
@@ -11496,7 +11496,7 @@
         </is>
       </c>
       <c r="E315" s="13" t="n">
-        <v>6732</v>
+        <v>6731</v>
       </c>
       <c r="F315" s="13" t="n">
         <v>12</v>
@@ -11524,7 +11524,7 @@
         </is>
       </c>
       <c r="E316" s="13" t="n">
-        <v>6746</v>
+        <v>6745</v>
       </c>
       <c r="F316" s="13" t="n">
         <v>13</v>
@@ -11552,7 +11552,7 @@
         </is>
       </c>
       <c r="E317" s="13" t="n">
-        <v>6762</v>
+        <v>6761</v>
       </c>
       <c r="F317" s="13" t="n">
         <v>12</v>
@@ -11580,7 +11580,7 @@
         </is>
       </c>
       <c r="E318" s="13" t="n">
-        <v>6777</v>
+        <v>6776</v>
       </c>
       <c r="F318" s="13" t="n">
         <v>13</v>
@@ -11608,7 +11608,7 @@
         </is>
       </c>
       <c r="E319" s="13" t="n">
-        <v>6792</v>
+        <v>6791</v>
       </c>
       <c r="F319" s="13" t="n">
         <v>11</v>
@@ -11636,7 +11636,7 @@
         </is>
       </c>
       <c r="E320" s="13" t="n">
-        <v>6806</v>
+        <v>6805</v>
       </c>
       <c r="F320" s="13" t="n">
         <v>9</v>
@@ -11664,7 +11664,7 @@
         </is>
       </c>
       <c r="E321" s="13" t="n">
-        <v>6817</v>
+        <v>6816</v>
       </c>
       <c r="F321" s="13" t="n">
         <v>11</v>
@@ -11692,7 +11692,7 @@
         </is>
       </c>
       <c r="E322" s="13" t="n">
-        <v>6831</v>
+        <v>6830</v>
       </c>
       <c r="F322" s="13" t="n">
         <v>10</v>
@@ -11720,7 +11720,7 @@
         </is>
       </c>
       <c r="E323" s="13" t="n">
-        <v>6843</v>
+        <v>6842</v>
       </c>
       <c r="F323" s="13" t="n">
         <v>12</v>
@@ -11748,7 +11748,7 @@
         </is>
       </c>
       <c r="E324" s="13" t="n">
-        <v>6857</v>
+        <v>6856</v>
       </c>
       <c r="F324" s="13" t="n">
         <v>16</v>
@@ -11776,7 +11776,7 @@
         </is>
       </c>
       <c r="E325" s="13" t="n">
-        <v>6876</v>
+        <v>6875</v>
       </c>
       <c r="F325" s="13" t="n">
         <v>17</v>
@@ -11804,7 +11804,7 @@
         </is>
       </c>
       <c r="E326" s="13" t="n">
-        <v>6895</v>
+        <v>6894</v>
       </c>
       <c r="F326" s="13" t="n">
         <v>12</v>
@@ -11832,7 +11832,7 @@
         </is>
       </c>
       <c r="E327" s="13" t="n">
-        <v>6909</v>
+        <v>6908</v>
       </c>
       <c r="F327" s="13" t="n">
         <v>10</v>
@@ -11860,7 +11860,7 @@
         </is>
       </c>
       <c r="E328" s="13" t="n">
-        <v>6922</v>
+        <v>6921</v>
       </c>
       <c r="F328" s="13" t="n">
         <v>15</v>
@@ -11888,7 +11888,7 @@
         </is>
       </c>
       <c r="E329" s="13" t="n">
-        <v>6940</v>
+        <v>6939</v>
       </c>
       <c r="F329" s="13" t="n">
         <v>23</v>
@@ -11916,7 +11916,7 @@
         </is>
       </c>
       <c r="E330" s="13" t="n">
-        <v>6966</v>
+        <v>6965</v>
       </c>
       <c r="F330" s="13" t="n">
         <v>20</v>
@@ -11944,7 +11944,7 @@
         </is>
       </c>
       <c r="E331" s="13" t="n">
-        <v>6989</v>
+        <v>6988</v>
       </c>
       <c r="F331" s="13" t="n">
         <v>15</v>
@@ -11972,7 +11972,7 @@
         </is>
       </c>
       <c r="E332" s="13" t="n">
-        <v>7007</v>
+        <v>7006</v>
       </c>
       <c r="F332" s="13" t="n">
         <v>11</v>
@@ -12000,7 +12000,7 @@
         </is>
       </c>
       <c r="E333" s="13" t="n">
-        <v>7021</v>
+        <v>7020</v>
       </c>
       <c r="F333" s="13" t="n">
         <v>17</v>
@@ -12028,7 +12028,7 @@
         </is>
       </c>
       <c r="E334" s="13" t="n">
-        <v>7041</v>
+        <v>7040</v>
       </c>
       <c r="F334" s="13" t="n">
         <v>18</v>
@@ -12056,7 +12056,7 @@
         </is>
       </c>
       <c r="E335" s="13" t="n">
-        <v>7062</v>
+        <v>7061</v>
       </c>
       <c r="F335" s="13" t="n">
         <v>16</v>
@@ -12084,7 +12084,7 @@
         </is>
       </c>
       <c r="E336" s="13" t="n">
-        <v>7080</v>
+        <v>7079</v>
       </c>
       <c r="F336" s="13" t="n">
         <v>16</v>
@@ -12112,7 +12112,7 @@
         </is>
       </c>
       <c r="E337" s="13" t="n">
-        <v>7099</v>
+        <v>7098</v>
       </c>
       <c r="F337" s="13" t="n">
         <v>16</v>
@@ -12140,7 +12140,7 @@
         </is>
       </c>
       <c r="E338" s="13" t="n">
-        <v>7118</v>
+        <v>7117</v>
       </c>
       <c r="F338" s="13" t="n">
         <v>13</v>
@@ -12168,7 +12168,7 @@
         </is>
       </c>
       <c r="E339" s="13" t="n">
-        <v>7134</v>
+        <v>7133</v>
       </c>
       <c r="F339" s="13" t="n">
         <v>13</v>
@@ -12196,7 +12196,7 @@
         </is>
       </c>
       <c r="E340" s="13" t="n">
-        <v>7150</v>
+        <v>7149</v>
       </c>
       <c r="F340" s="13" t="n">
         <v>17</v>
@@ -12224,7 +12224,7 @@
         </is>
       </c>
       <c r="E341" s="13" t="n">
-        <v>7170</v>
+        <v>7169</v>
       </c>
       <c r="F341" s="13" t="n">
         <v>14</v>
@@ -12252,7 +12252,7 @@
         </is>
       </c>
       <c r="E342" s="13" t="n">
-        <v>7187</v>
+        <v>7186</v>
       </c>
       <c r="F342" s="13" t="n">
         <v>13</v>
@@ -12280,7 +12280,7 @@
         </is>
       </c>
       <c r="E343" s="13" t="n">
-        <v>7202</v>
+        <v>7201</v>
       </c>
       <c r="F343" s="13" t="n">
         <v>10</v>
@@ -12308,7 +12308,7 @@
         </is>
       </c>
       <c r="E344" s="13" t="n">
-        <v>7215</v>
+        <v>7214</v>
       </c>
       <c r="F344" s="13" t="n">
         <v>11</v>
@@ -12336,7 +12336,7 @@
         </is>
       </c>
       <c r="E345" s="13" t="n">
-        <v>7229</v>
+        <v>7228</v>
       </c>
       <c r="F345" s="13" t="n">
         <v>11</v>
@@ -12364,7 +12364,7 @@
         </is>
       </c>
       <c r="E346" s="13" t="n">
-        <v>7242</v>
+        <v>7241</v>
       </c>
       <c r="F346" s="13" t="n">
         <v>13</v>
@@ -12392,7 +12392,7 @@
         </is>
       </c>
       <c r="E347" s="13" t="n">
-        <v>7258</v>
+        <v>7257</v>
       </c>
       <c r="F347" s="13" t="n">
         <v>13</v>
@@ -12420,7 +12420,7 @@
         </is>
       </c>
       <c r="E348" s="13" t="n">
-        <v>7274</v>
+        <v>7273</v>
       </c>
       <c r="F348" s="13" t="n">
         <v>12</v>
@@ -12448,7 +12448,7 @@
         </is>
       </c>
       <c r="E349" s="13" t="n">
-        <v>7289</v>
+        <v>7288</v>
       </c>
       <c r="F349" s="13" t="n">
         <v>11</v>
@@ -12476,7 +12476,7 @@
         </is>
       </c>
       <c r="E350" s="13" t="n">
-        <v>7302</v>
+        <v>7301</v>
       </c>
       <c r="F350" s="13" t="n">
         <v>13</v>
@@ -12504,7 +12504,7 @@
         </is>
       </c>
       <c r="E351" s="13" t="n">
-        <v>7318</v>
+        <v>7317</v>
       </c>
       <c r="F351" s="13" t="n">
         <v>10</v>
@@ -12532,7 +12532,7 @@
         </is>
       </c>
       <c r="E352" s="13" t="n">
-        <v>7331</v>
+        <v>7330</v>
       </c>
       <c r="F352" s="13" t="n">
         <v>11</v>
@@ -12560,7 +12560,7 @@
         </is>
       </c>
       <c r="E353" s="13" t="n">
-        <v>7344</v>
+        <v>7343</v>
       </c>
       <c r="F353" s="13" t="n">
         <v>12</v>
@@ -12588,7 +12588,7 @@
         </is>
       </c>
       <c r="E354" s="13" t="n">
-        <v>7359</v>
+        <v>7358</v>
       </c>
       <c r="F354" s="13" t="n">
         <v>19</v>
@@ -12616,7 +12616,7 @@
         </is>
       </c>
       <c r="E355" s="13" t="n">
-        <v>7381</v>
+        <v>7380</v>
       </c>
       <c r="F355" s="13" t="n">
         <v>11</v>
@@ -12644,7 +12644,7 @@
         </is>
       </c>
       <c r="E356" s="13" t="n">
-        <v>7395</v>
+        <v>7394</v>
       </c>
       <c r="F356" s="13" t="n">
         <v>13</v>
@@ -12672,7 +12672,7 @@
         </is>
       </c>
       <c r="E357" s="13" t="n">
-        <v>7411</v>
+        <v>7410</v>
       </c>
       <c r="F357" s="13" t="n">
         <v>13</v>
@@ -12700,7 +12700,7 @@
         </is>
       </c>
       <c r="E358" s="13" t="n">
-        <v>7426</v>
+        <v>7425</v>
       </c>
       <c r="F358" s="13" t="n">
         <v>14</v>
@@ -12728,7 +12728,7 @@
         </is>
       </c>
       <c r="E359" s="13" t="n">
-        <v>7443</v>
+        <v>7442</v>
       </c>
       <c r="F359" s="13" t="n">
         <v>15</v>
@@ -12756,7 +12756,7 @@
         </is>
       </c>
       <c r="E360" s="13" t="n">
-        <v>7461</v>
+        <v>7460</v>
       </c>
       <c r="F360" s="13" t="n">
         <v>15</v>
@@ -12784,7 +12784,7 @@
         </is>
       </c>
       <c r="E361" s="13" t="n">
-        <v>7479</v>
+        <v>7478</v>
       </c>
       <c r="F361" s="13" t="n">
         <v>14</v>
@@ -12812,7 +12812,7 @@
         </is>
       </c>
       <c r="E362" s="13" t="n">
-        <v>7496</v>
+        <v>7495</v>
       </c>
       <c r="F362" s="13" t="n">
         <v>14</v>
@@ -12840,7 +12840,7 @@
         </is>
       </c>
       <c r="E363" s="13" t="n">
-        <v>7512</v>
+        <v>7511</v>
       </c>
       <c r="F363" s="13" t="n">
         <v>16</v>
@@ -12868,7 +12868,7 @@
         </is>
       </c>
       <c r="E364" s="13" t="n">
-        <v>7531</v>
+        <v>7530</v>
       </c>
       <c r="F364" s="13" t="n">
         <v>15</v>
@@ -12896,7 +12896,7 @@
         </is>
       </c>
       <c r="E365" s="13" t="n">
-        <v>7549</v>
+        <v>7548</v>
       </c>
       <c r="F365" s="13" t="n">
         <v>16</v>
@@ -12924,7 +12924,7 @@
         </is>
       </c>
       <c r="E366" s="13" t="n">
-        <v>7568</v>
+        <v>7567</v>
       </c>
       <c r="F366" s="13" t="n">
         <v>18</v>
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="E367" s="13" t="n">
-        <v>7589</v>
+        <v>7588</v>
       </c>
       <c r="F367" s="13" t="n">
         <v>19</v>
@@ -12980,7 +12980,7 @@
         </is>
       </c>
       <c r="E368" s="13" t="n">
-        <v>7611</v>
+        <v>7610</v>
       </c>
       <c r="F368" s="13" t="n">
         <v>14</v>
@@ -13008,7 +13008,7 @@
         </is>
       </c>
       <c r="E369" s="13" t="n">
-        <v>7628</v>
+        <v>7627</v>
       </c>
       <c r="F369" s="13" t="n">
         <v>13</v>
@@ -13036,7 +13036,7 @@
         </is>
       </c>
       <c r="E370" s="13" t="n">
-        <v>7644</v>
+        <v>7643</v>
       </c>
       <c r="F370" s="13" t="n">
         <v>12</v>
@@ -13064,7 +13064,7 @@
         </is>
       </c>
       <c r="E371" s="13" t="n">
-        <v>7658</v>
+        <v>7657</v>
       </c>
       <c r="F371" s="13" t="n">
         <v>10</v>
@@ -13092,7 +13092,7 @@
         </is>
       </c>
       <c r="E372" s="13" t="n">
-        <v>7671</v>
+        <v>7670</v>
       </c>
       <c r="F372" s="13" t="n">
         <v>11</v>
@@ -13120,7 +13120,7 @@
         </is>
       </c>
       <c r="E373" s="13" t="n">
-        <v>7685</v>
+        <v>7684</v>
       </c>
       <c r="F373" s="13" t="n">
         <v>11</v>
@@ -13148,7 +13148,7 @@
         </is>
       </c>
       <c r="E374" s="13" t="n">
-        <v>7698</v>
+        <v>7697</v>
       </c>
       <c r="F374" s="13" t="n">
         <v>13</v>
@@ -13176,7 +13176,7 @@
         </is>
       </c>
       <c r="E375" s="13" t="n">
-        <v>7714</v>
+        <v>7713</v>
       </c>
       <c r="F375" s="13" t="n">
         <v>18</v>
@@ -13204,7 +13204,7 @@
         </is>
       </c>
       <c r="E376" s="13" t="n">
-        <v>7735</v>
+        <v>7734</v>
       </c>
       <c r="F376" s="13" t="n">
         <v>10</v>
@@ -13232,7 +13232,7 @@
         </is>
       </c>
       <c r="E377" s="13" t="n">
-        <v>7748</v>
+        <v>7747</v>
       </c>
       <c r="F377" s="13" t="n">
         <v>12</v>
@@ -13260,7 +13260,7 @@
         </is>
       </c>
       <c r="E378" s="13" t="n">
-        <v>7762</v>
+        <v>7761</v>
       </c>
       <c r="F378" s="13" t="n">
         <v>9</v>
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="E379" s="13" t="n">
-        <v>7774</v>
+        <v>7773</v>
       </c>
       <c r="F379" s="13" t="n">
         <v>10</v>
@@ -13316,7 +13316,7 @@
         </is>
       </c>
       <c r="E380" s="13" t="n">
-        <v>7786</v>
+        <v>7785</v>
       </c>
       <c r="F380" s="13" t="n">
         <v>10</v>
@@ -13344,7 +13344,7 @@
         </is>
       </c>
       <c r="E381" s="13" t="n">
-        <v>7798</v>
+        <v>7797</v>
       </c>
       <c r="F381" s="13" t="n">
         <v>11</v>
@@ -13372,7 +13372,7 @@
         </is>
       </c>
       <c r="E382" s="13" t="n">
-        <v>7812</v>
+        <v>7811</v>
       </c>
       <c r="F382" s="13" t="n">
         <v>14</v>
@@ -13400,7 +13400,7 @@
         </is>
       </c>
       <c r="E383" s="13" t="n">
-        <v>7828</v>
+        <v>7827</v>
       </c>
       <c r="F383" s="13" t="n">
         <v>11</v>
@@ -13428,7 +13428,7 @@
         </is>
       </c>
       <c r="E384" s="13" t="n">
-        <v>7842</v>
+        <v>7841</v>
       </c>
       <c r="F384" s="13" t="n">
         <v>12</v>
@@ -13456,7 +13456,7 @@
         </is>
       </c>
       <c r="E385" s="13" t="n">
-        <v>7857</v>
+        <v>7856</v>
       </c>
       <c r="F385" s="13" t="n">
         <v>11</v>
@@ -13484,7 +13484,7 @@
         </is>
       </c>
       <c r="E386" s="13" t="n">
-        <v>7870</v>
+        <v>7869</v>
       </c>
       <c r="F386" s="13" t="n">
         <v>11</v>
@@ -13512,7 +13512,7 @@
         </is>
       </c>
       <c r="E387" s="13" t="n">
-        <v>7883</v>
+        <v>7882</v>
       </c>
       <c r="F387" s="13" t="n">
         <v>10</v>
@@ -13540,7 +13540,7 @@
         </is>
       </c>
       <c r="E388" s="13" t="n">
-        <v>7896</v>
+        <v>7895</v>
       </c>
       <c r="F388" s="13" t="n">
         <v>11</v>
@@ -13568,7 +13568,7 @@
         </is>
       </c>
       <c r="E389" s="13" t="n">
-        <v>7909</v>
+        <v>7908</v>
       </c>
       <c r="F389" s="13" t="n">
         <v>11</v>
@@ -13596,7 +13596,7 @@
         </is>
       </c>
       <c r="E390" s="13" t="n">
-        <v>7923</v>
+        <v>7922</v>
       </c>
       <c r="F390" s="13" t="n">
         <v>11</v>
@@ -13624,7 +13624,7 @@
         </is>
       </c>
       <c r="E391" s="13" t="n">
-        <v>7937</v>
+        <v>7936</v>
       </c>
       <c r="F391" s="13" t="n">
         <v>11</v>
@@ -13652,7 +13652,7 @@
         </is>
       </c>
       <c r="E392" s="13" t="n">
-        <v>7950</v>
+        <v>7949</v>
       </c>
       <c r="F392" s="13" t="n">
         <v>23</v>
@@ -13680,7 +13680,7 @@
         </is>
       </c>
       <c r="E393" s="13" t="n">
-        <v>7976</v>
+        <v>7975</v>
       </c>
       <c r="F393" s="13" t="n">
         <v>13</v>
@@ -13708,7 +13708,7 @@
         </is>
       </c>
       <c r="E394" s="13" t="n">
-        <v>7992</v>
+        <v>7991</v>
       </c>
       <c r="F394" s="13" t="n">
         <v>12</v>
@@ -13736,7 +13736,7 @@
         </is>
       </c>
       <c r="E395" s="13" t="n">
-        <v>8007</v>
+        <v>8006</v>
       </c>
       <c r="F395" s="13" t="n">
         <v>15</v>
@@ -13764,7 +13764,7 @@
         </is>
       </c>
       <c r="E396" s="13" t="n">
-        <v>8025</v>
+        <v>8024</v>
       </c>
       <c r="F396" s="13" t="n">
         <v>12</v>
@@ -13792,7 +13792,7 @@
         </is>
       </c>
       <c r="E397" s="13" t="n">
-        <v>8039</v>
+        <v>8038</v>
       </c>
       <c r="F397" s="13" t="n">
         <v>16</v>
@@ -13820,7 +13820,7 @@
         </is>
       </c>
       <c r="E398" s="13" t="n">
-        <v>8058</v>
+        <v>8057</v>
       </c>
       <c r="F398" s="13" t="n">
         <v>13</v>
@@ -13848,7 +13848,7 @@
         </is>
       </c>
       <c r="E399" s="13" t="n">
-        <v>8074</v>
+        <v>8073</v>
       </c>
       <c r="F399" s="13" t="n">
         <v>12</v>
@@ -13876,7 +13876,7 @@
         </is>
       </c>
       <c r="E400" s="13" t="n">
-        <v>8089</v>
+        <v>8088</v>
       </c>
       <c r="F400" s="13" t="n">
         <v>12</v>
@@ -13904,7 +13904,7 @@
         </is>
       </c>
       <c r="E401" s="13" t="n">
-        <v>8103</v>
+        <v>8102</v>
       </c>
       <c r="F401" s="13" t="n">
         <v>12</v>
@@ -13932,7 +13932,7 @@
         </is>
       </c>
       <c r="E402" s="13" t="n">
-        <v>8118</v>
+        <v>8117</v>
       </c>
       <c r="F402" s="13" t="n">
         <v>10</v>
@@ -13960,7 +13960,7 @@
         </is>
       </c>
       <c r="E403" s="13" t="n">
-        <v>8131</v>
+        <v>8130</v>
       </c>
       <c r="F403" s="13" t="n">
         <v>12</v>
@@ -13988,7 +13988,7 @@
         </is>
       </c>
       <c r="E404" s="13" t="n">
-        <v>8145</v>
+        <v>8144</v>
       </c>
       <c r="F404" s="13" t="n">
         <v>13</v>
@@ -14016,7 +14016,7 @@
         </is>
       </c>
       <c r="E405" s="13" t="n">
-        <v>8161</v>
+        <v>8160</v>
       </c>
       <c r="F405" s="13" t="n">
         <v>12</v>
@@ -14044,7 +14044,7 @@
         </is>
       </c>
       <c r="E406" s="13" t="n">
-        <v>8176</v>
+        <v>8175</v>
       </c>
       <c r="F406" s="13" t="n">
         <v>10</v>
@@ -14072,7 +14072,7 @@
         </is>
       </c>
       <c r="E407" s="13" t="n">
-        <v>8188</v>
+        <v>8187</v>
       </c>
       <c r="F407" s="13" t="n">
         <v>13</v>
@@ -14100,7 +14100,7 @@
         </is>
       </c>
       <c r="E408" s="13" t="n">
-        <v>8204</v>
+        <v>8203</v>
       </c>
       <c r="F408" s="13" t="n">
         <v>12</v>
@@ -14128,7 +14128,7 @@
         </is>
       </c>
       <c r="E409" s="13" t="n">
-        <v>8219</v>
+        <v>8218</v>
       </c>
       <c r="F409" s="13" t="n">
         <v>15</v>
@@ -14156,7 +14156,7 @@
         </is>
       </c>
       <c r="E410" s="13" t="n">
-        <v>8236</v>
+        <v>8235</v>
       </c>
       <c r="F410" s="13" t="n">
         <v>10</v>
@@ -14184,7 +14184,7 @@
         </is>
       </c>
       <c r="E411" s="13" t="n">
-        <v>8248</v>
+        <v>8247</v>
       </c>
       <c r="F411" s="13" t="n">
         <v>13</v>
@@ -14212,7 +14212,7 @@
         </is>
       </c>
       <c r="E412" s="13" t="n">
-        <v>8264</v>
+        <v>8263</v>
       </c>
       <c r="F412" s="13" t="n">
         <v>8</v>
@@ -14240,7 +14240,7 @@
         </is>
       </c>
       <c r="E413" s="13" t="n">
-        <v>8274</v>
+        <v>8273</v>
       </c>
       <c r="F413" s="13" t="n">
         <v>21</v>
@@ -14268,7 +14268,7 @@
         </is>
       </c>
       <c r="E414" s="13" t="n">
-        <v>8298</v>
+        <v>8297</v>
       </c>
       <c r="F414" s="13" t="n">
         <v>17</v>
@@ -14296,7 +14296,7 @@
         </is>
       </c>
       <c r="E415" s="13" t="n">
-        <v>8318</v>
+        <v>8317</v>
       </c>
       <c r="F415" s="13" t="n">
         <v>10</v>
@@ -14324,7 +14324,7 @@
         </is>
       </c>
       <c r="E416" s="13" t="n">
-        <v>8331</v>
+        <v>8330</v>
       </c>
       <c r="F416" s="13" t="n">
         <v>15</v>
@@ -14352,7 +14352,7 @@
         </is>
       </c>
       <c r="E417" s="13" t="n">
-        <v>8349</v>
+        <v>8348</v>
       </c>
       <c r="F417" s="13" t="n">
         <v>9</v>
@@ -14380,7 +14380,7 @@
         </is>
       </c>
       <c r="E418" s="13" t="n">
-        <v>8360</v>
+        <v>8359</v>
       </c>
       <c r="F418" s="13" t="n">
         <v>16</v>
@@ -14408,7 +14408,7 @@
         </is>
       </c>
       <c r="E419" s="13" t="n">
-        <v>8379</v>
+        <v>8378</v>
       </c>
       <c r="F419" s="13" t="n">
         <v>12</v>
@@ -14436,7 +14436,7 @@
         </is>
       </c>
       <c r="E420" s="13" t="n">
-        <v>8394</v>
+        <v>8393</v>
       </c>
       <c r="F420" s="13" t="n">
         <v>13</v>
@@ -14464,7 +14464,7 @@
         </is>
       </c>
       <c r="E421" s="13" t="n">
-        <v>8410</v>
+        <v>8409</v>
       </c>
       <c r="F421" s="13" t="n">
         <v>12</v>
@@ -14492,7 +14492,7 @@
         </is>
       </c>
       <c r="E422" s="13" t="n">
-        <v>8424</v>
+        <v>8423</v>
       </c>
       <c r="F422" s="13" t="n">
         <v>12</v>
@@ -14520,7 +14520,7 @@
         </is>
       </c>
       <c r="E423" s="13" t="n">
-        <v>8438</v>
+        <v>8437</v>
       </c>
       <c r="F423" s="13" t="n">
         <v>8</v>
@@ -14548,7 +14548,7 @@
         </is>
       </c>
       <c r="E424" s="13" t="n">
-        <v>8449</v>
+        <v>8448</v>
       </c>
       <c r="F424" s="13" t="n">
         <v>21</v>
@@ -14576,7 +14576,7 @@
         </is>
       </c>
       <c r="E425" s="13" t="n">
-        <v>8473</v>
+        <v>8472</v>
       </c>
       <c r="F425" s="13" t="n">
         <v>15</v>
@@ -14604,7 +14604,7 @@
         </is>
       </c>
       <c r="E426" s="13" t="n">
-        <v>8491</v>
+        <v>8490</v>
       </c>
       <c r="F426" s="13" t="n">
         <v>12</v>
@@ -14632,7 +14632,7 @@
         </is>
       </c>
       <c r="E427" s="13" t="n">
-        <v>8506</v>
+        <v>8505</v>
       </c>
       <c r="F427" s="13" t="n">
         <v>12</v>
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="E428" s="13" t="n">
-        <v>8520</v>
+        <v>8519</v>
       </c>
       <c r="F428" s="13" t="n">
         <v>14</v>
@@ -14688,7 +14688,7 @@
         </is>
       </c>
       <c r="E429" s="13" t="n">
-        <v>8537</v>
+        <v>8536</v>
       </c>
       <c r="F429" s="13" t="n">
         <v>14</v>
@@ -14716,7 +14716,7 @@
         </is>
       </c>
       <c r="E430" s="13" t="n">
-        <v>8554</v>
+        <v>8553</v>
       </c>
       <c r="F430" s="13" t="n">
         <v>19</v>
@@ -14744,7 +14744,7 @@
         </is>
       </c>
       <c r="E431" s="13" t="n">
-        <v>8576</v>
+        <v>8575</v>
       </c>
       <c r="F431" s="13" t="n">
         <v>16</v>
@@ -14772,7 +14772,7 @@
         </is>
       </c>
       <c r="E432" s="13" t="n">
-        <v>8595</v>
+        <v>8594</v>
       </c>
       <c r="F432" s="13" t="n">
         <v>16</v>
@@ -14800,7 +14800,7 @@
         </is>
       </c>
       <c r="E433" s="13" t="n">
-        <v>8614</v>
+        <v>8613</v>
       </c>
       <c r="F433" s="13" t="n">
         <v>12</v>
@@ -14828,7 +14828,7 @@
         </is>
       </c>
       <c r="E434" s="13" t="n">
-        <v>8628</v>
+        <v>8627</v>
       </c>
       <c r="F434" s="13" t="n">
         <v>13</v>
@@ -14856,7 +14856,7 @@
         </is>
       </c>
       <c r="E435" s="13" t="n">
-        <v>8644</v>
+        <v>8643</v>
       </c>
       <c r="F435" s="13" t="n">
         <v>17</v>
@@ -14884,7 +14884,7 @@
         </is>
       </c>
       <c r="E436" s="13" t="n">
-        <v>8664</v>
+        <v>8663</v>
       </c>
       <c r="F436" s="13" t="n">
         <v>17</v>
@@ -14912,7 +14912,7 @@
         </is>
       </c>
       <c r="E437" s="13" t="n">
-        <v>8684</v>
+        <v>8683</v>
       </c>
       <c r="F437" s="13" t="n">
         <v>20</v>
@@ -14940,7 +14940,7 @@
         </is>
       </c>
       <c r="E438" s="13" t="n">
-        <v>8707</v>
+        <v>8706</v>
       </c>
       <c r="F438" s="13" t="n">
         <v>23</v>
@@ -14968,7 +14968,7 @@
         </is>
       </c>
       <c r="E439" s="13" t="n">
-        <v>8733</v>
+        <v>8732</v>
       </c>
       <c r="F439" s="13" t="n">
         <v>21</v>
@@ -14996,7 +14996,7 @@
         </is>
       </c>
       <c r="E440" s="13" t="n">
-        <v>8757</v>
+        <v>8756</v>
       </c>
       <c r="F440" s="13" t="n">
         <v>19</v>
@@ -15024,7 +15024,7 @@
         </is>
       </c>
       <c r="E441" s="13" t="n">
-        <v>8779</v>
+        <v>8778</v>
       </c>
       <c r="F441" s="13" t="n">
         <v>15</v>
@@ -15052,7 +15052,7 @@
         </is>
       </c>
       <c r="E442" s="13" t="n">
-        <v>8797</v>
+        <v>8796</v>
       </c>
       <c r="F442" s="13" t="n">
         <v>20</v>
@@ -15080,7 +15080,7 @@
         </is>
       </c>
       <c r="E443" s="13" t="n">
-        <v>8820</v>
+        <v>8819</v>
       </c>
       <c r="F443" s="13" t="n">
         <v>17</v>
@@ -15108,7 +15108,7 @@
         </is>
       </c>
       <c r="E444" s="13" t="n">
-        <v>8840</v>
+        <v>8839</v>
       </c>
       <c r="F444" s="13" t="n">
         <v>19</v>
@@ -15136,7 +15136,7 @@
         </is>
       </c>
       <c r="E445" s="13" t="n">
-        <v>8861</v>
+        <v>8860</v>
       </c>
       <c r="F445" s="13" t="n">
         <v>19</v>
@@ -15164,7 +15164,7 @@
         </is>
       </c>
       <c r="E446" s="13" t="n">
-        <v>8883</v>
+        <v>8882</v>
       </c>
       <c r="F446" s="13" t="n">
         <v>10</v>
@@ -15192,7 +15192,7 @@
         </is>
       </c>
       <c r="E447" s="13" t="n">
-        <v>8895</v>
+        <v>8894</v>
       </c>
       <c r="F447" s="13" t="n">
         <v>11</v>
@@ -15220,7 +15220,7 @@
         </is>
       </c>
       <c r="E448" s="13" t="n">
-        <v>8909</v>
+        <v>8908</v>
       </c>
       <c r="F448" s="13" t="n">
         <v>12</v>
@@ -15248,7 +15248,7 @@
         </is>
       </c>
       <c r="E449" s="13" t="n">
-        <v>8923</v>
+        <v>8922</v>
       </c>
       <c r="F449" s="13" t="n">
         <v>10</v>
@@ -15276,7 +15276,7 @@
         </is>
       </c>
       <c r="E450" s="13" t="n">
-        <v>8935</v>
+        <v>8934</v>
       </c>
       <c r="F450" s="13" t="n">
         <v>12</v>
@@ -15304,7 +15304,7 @@
         </is>
       </c>
       <c r="E451" s="13" t="n">
-        <v>8950</v>
+        <v>8949</v>
       </c>
       <c r="F451" s="13" t="n">
         <v>9</v>
@@ -15332,7 +15332,7 @@
         </is>
       </c>
       <c r="E452" s="13" t="n">
-        <v>8961</v>
+        <v>8960</v>
       </c>
       <c r="F452" s="13" t="n">
         <v>12</v>
@@ -15360,7 +15360,7 @@
         </is>
       </c>
       <c r="E453" s="13" t="n">
-        <v>8976</v>
+        <v>8975</v>
       </c>
       <c r="F453" s="13" t="n">
         <v>10</v>
@@ -15388,7 +15388,7 @@
         </is>
       </c>
       <c r="E454" s="13" t="n">
-        <v>8989</v>
+        <v>8988</v>
       </c>
       <c r="F454" s="13" t="n">
         <v>9</v>
@@ -15416,7 +15416,7 @@
         </is>
       </c>
       <c r="E455" s="13" t="n">
-        <v>9000</v>
+        <v>8999</v>
       </c>
       <c r="F455" s="13" t="n">
         <v>17</v>
@@ -15444,7 +15444,7 @@
         </is>
       </c>
       <c r="E456" s="13" t="n">
-        <v>9020</v>
+        <v>9019</v>
       </c>
       <c r="F456" s="13" t="n">
         <v>13</v>
@@ -15472,7 +15472,7 @@
         </is>
       </c>
       <c r="E457" s="13" t="n">
-        <v>9036</v>
+        <v>9035</v>
       </c>
       <c r="F457" s="13" t="n">
         <v>15</v>
@@ -15500,7 +15500,7 @@
         </is>
       </c>
       <c r="E458" s="13" t="n">
-        <v>9053</v>
+        <v>9052</v>
       </c>
       <c r="F458" s="13" t="n">
         <v>22</v>
@@ -15528,7 +15528,7 @@
         </is>
       </c>
       <c r="E459" s="13" t="n">
-        <v>9077</v>
+        <v>9076</v>
       </c>
       <c r="F459" s="13" t="n">
         <v>15</v>
@@ -15556,7 +15556,7 @@
         </is>
       </c>
       <c r="E460" s="13" t="n">
-        <v>9094</v>
+        <v>9093</v>
       </c>
       <c r="F460" s="13" t="n">
         <v>17</v>
@@ -15584,7 +15584,7 @@
         </is>
       </c>
       <c r="E461" s="13" t="n">
-        <v>9114</v>
+        <v>9113</v>
       </c>
       <c r="F461" s="13" t="n">
         <v>20</v>
@@ -15612,7 +15612,7 @@
         </is>
       </c>
       <c r="E462" s="13" t="n">
-        <v>9137</v>
+        <v>9136</v>
       </c>
       <c r="F462" s="13" t="n">
         <v>13</v>
@@ -15640,7 +15640,7 @@
         </is>
       </c>
       <c r="E463" s="13" t="n">
-        <v>9153</v>
+        <v>9152</v>
       </c>
       <c r="F463" s="13" t="n">
         <v>12</v>
@@ -15668,7 +15668,7 @@
         </is>
       </c>
       <c r="E464" s="13" t="n">
-        <v>9168</v>
+        <v>9167</v>
       </c>
       <c r="F464" s="13" t="n">
         <v>11</v>
@@ -15696,7 +15696,7 @@
         </is>
       </c>
       <c r="E465" s="13" t="n">
-        <v>9181</v>
+        <v>9180</v>
       </c>
       <c r="F465" s="13" t="n">
         <v>8</v>
@@ -15724,7 +15724,7 @@
         </is>
       </c>
       <c r="E466" s="13" t="n">
-        <v>9192</v>
+        <v>9191</v>
       </c>
       <c r="F466" s="13" t="n">
         <v>23</v>
@@ -15752,7 +15752,7 @@
         </is>
       </c>
       <c r="E467" s="13" t="n">
-        <v>9218</v>
+        <v>9217</v>
       </c>
       <c r="F467" s="13" t="n">
         <v>13</v>
@@ -15780,7 +15780,7 @@
         </is>
       </c>
       <c r="E468" s="13" t="n">
-        <v>9234</v>
+        <v>9233</v>
       </c>
       <c r="F468" s="13" t="n">
         <v>7</v>
@@ -15808,7 +15808,7 @@
         </is>
       </c>
       <c r="E469" s="13" t="n">
-        <v>9243</v>
+        <v>9242</v>
       </c>
       <c r="F469" s="13" t="n">
         <v>10</v>
@@ -15836,7 +15836,7 @@
         </is>
       </c>
       <c r="E470" s="13" t="n">
-        <v>9256</v>
+        <v>9255</v>
       </c>
       <c r="F470" s="13" t="n">
         <v>10</v>
@@ -15864,7 +15864,7 @@
         </is>
       </c>
       <c r="E471" s="13" t="n">
-        <v>9269</v>
+        <v>9268</v>
       </c>
       <c r="F471" s="13" t="n">
         <v>10</v>
@@ -15892,7 +15892,7 @@
         </is>
       </c>
       <c r="E472" s="13" t="n">
-        <v>9281</v>
+        <v>9280</v>
       </c>
       <c r="F472" s="13" t="n">
         <v>7</v>
@@ -15920,7 +15920,7 @@
         </is>
       </c>
       <c r="E473" s="13" t="n">
-        <v>9291</v>
+        <v>9290</v>
       </c>
       <c r="F473" s="13" t="n">
         <v>17</v>
@@ -15948,7 +15948,7 @@
         </is>
       </c>
       <c r="E474" s="13" t="n">
-        <v>9310</v>
+        <v>9309</v>
       </c>
       <c r="F474" s="13" t="n">
         <v>15</v>
@@ -15976,7 +15976,7 @@
         </is>
       </c>
       <c r="E475" s="13" t="n">
-        <v>9327</v>
+        <v>9326</v>
       </c>
       <c r="F475" s="13" t="n">
         <v>14</v>
@@ -16004,7 +16004,7 @@
         </is>
       </c>
       <c r="E476" s="13" t="n">
-        <v>9344</v>
+        <v>9343</v>
       </c>
       <c r="F476" s="13" t="n">
         <v>21</v>
@@ -16032,7 +16032,7 @@
         </is>
       </c>
       <c r="E477" s="13" t="n">
-        <v>9368</v>
+        <v>9367</v>
       </c>
       <c r="F477" s="13" t="n">
         <v>13</v>
@@ -16060,7 +16060,7 @@
         </is>
       </c>
       <c r="E478" s="13" t="n">
-        <v>9384</v>
+        <v>9383</v>
       </c>
       <c r="F478" s="13" t="n">
         <v>16</v>
@@ -16088,7 +16088,7 @@
         </is>
       </c>
       <c r="E479" s="13" t="n">
-        <v>9403</v>
+        <v>9402</v>
       </c>
       <c r="F479" s="13" t="n">
         <v>15</v>
@@ -16116,7 +16116,7 @@
         </is>
       </c>
       <c r="E480" s="13" t="n">
-        <v>9421</v>
+        <v>9420</v>
       </c>
       <c r="F480" s="13" t="n">
         <v>17</v>
@@ -16144,7 +16144,7 @@
         </is>
       </c>
       <c r="E481" s="13" t="n">
-        <v>9441</v>
+        <v>9440</v>
       </c>
       <c r="F481" s="13" t="n">
         <v>18</v>
@@ -16172,7 +16172,7 @@
         </is>
       </c>
       <c r="E482" s="13" t="n">
-        <v>9461</v>
+        <v>9460</v>
       </c>
       <c r="F482" s="13" t="n">
         <v>16</v>
@@ -16200,7 +16200,7 @@
         </is>
       </c>
       <c r="E483" s="13" t="n">
-        <v>9480</v>
+        <v>9479</v>
       </c>
       <c r="F483" s="13" t="n">
         <v>17</v>
@@ -16228,7 +16228,7 @@
         </is>
       </c>
       <c r="E484" s="13" t="n">
-        <v>9500</v>
+        <v>9499</v>
       </c>
       <c r="F484" s="13" t="n">
         <v>11</v>
@@ -16256,7 +16256,7 @@
         </is>
       </c>
       <c r="E485" s="13" t="n">
-        <v>9514</v>
+        <v>9513</v>
       </c>
       <c r="F485" s="13" t="n">
         <v>13</v>
@@ -16284,7 +16284,7 @@
         </is>
       </c>
       <c r="E486" s="13" t="n">
-        <v>9530</v>
+        <v>9529</v>
       </c>
       <c r="F486" s="13" t="n">
         <v>16</v>
@@ -16312,7 +16312,7 @@
         </is>
       </c>
       <c r="E487" s="13" t="n">
-        <v>9549</v>
+        <v>9548</v>
       </c>
       <c r="F487" s="13" t="n">
         <v>20</v>
@@ -16340,7 +16340,7 @@
         </is>
       </c>
       <c r="E488" s="13" t="n">
-        <v>9572</v>
+        <v>9571</v>
       </c>
       <c r="F488" s="13" t="n">
         <v>10</v>
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="E489" s="13" t="n">
-        <v>9584</v>
+        <v>9583</v>
       </c>
       <c r="F489" s="13" t="n">
         <v>15</v>
@@ -16396,7 +16396,7 @@
         </is>
       </c>
       <c r="E490" s="13" t="n">
-        <v>9602</v>
+        <v>9601</v>
       </c>
       <c r="F490" s="13" t="n">
         <v>15</v>
@@ -16424,7 +16424,7 @@
         </is>
       </c>
       <c r="E491" s="13" t="n">
-        <v>9620</v>
+        <v>9619</v>
       </c>
       <c r="F491" s="13" t="n">
         <v>15</v>
@@ -16452,7 +16452,7 @@
         </is>
       </c>
       <c r="E492" s="13" t="n">
-        <v>9638</v>
+        <v>9637</v>
       </c>
       <c r="F492" s="13" t="n">
         <v>14</v>
@@ -16480,7 +16480,7 @@
         </is>
       </c>
       <c r="E493" s="13" t="n">
-        <v>9655</v>
+        <v>9654</v>
       </c>
       <c r="F493" s="13" t="n">
         <v>14</v>
@@ -16508,7 +16508,7 @@
         </is>
       </c>
       <c r="E494" s="13" t="n">
-        <v>9672</v>
+        <v>9671</v>
       </c>
       <c r="F494" s="13" t="n">
         <v>17</v>
@@ -16536,7 +16536,7 @@
         </is>
       </c>
       <c r="E495" s="13" t="n">
-        <v>9692</v>
+        <v>9691</v>
       </c>
       <c r="F495" s="13" t="n">
         <v>15</v>
@@ -16564,7 +16564,7 @@
         </is>
       </c>
       <c r="E496" s="13" t="n">
-        <v>9709</v>
+        <v>9708</v>
       </c>
       <c r="F496" s="13" t="n">
         <v>20</v>
@@ -16592,7 +16592,7 @@
         </is>
       </c>
       <c r="E497" s="13" t="n">
-        <v>9734</v>
+        <v>9733</v>
       </c>
       <c r="F497" s="13" t="n">
         <v>13</v>
@@ -16620,7 +16620,7 @@
         </is>
       </c>
       <c r="E498" s="13" t="n">
-        <v>9750</v>
+        <v>9749</v>
       </c>
       <c r="F498" s="13" t="n">
         <v>15</v>
@@ -16648,7 +16648,7 @@
         </is>
       </c>
       <c r="E499" s="13" t="n">
-        <v>9768</v>
+        <v>9767</v>
       </c>
       <c r="F499" s="13" t="n">
         <v>16</v>
@@ -16676,7 +16676,7 @@
         </is>
       </c>
       <c r="E500" s="13" t="n">
-        <v>9787</v>
+        <v>9786</v>
       </c>
       <c r="F500" s="13" t="n">
         <v>4</v>
@@ -16704,7 +16704,7 @@
         </is>
       </c>
       <c r="E501" s="13" t="n">
-        <v>9793</v>
+        <v>9792</v>
       </c>
       <c r="F501" s="13" t="n">
         <v>14</v>
@@ -16732,7 +16732,7 @@
         </is>
       </c>
       <c r="E502" s="13" t="n">
-        <v>9810</v>
+        <v>9809</v>
       </c>
       <c r="F502" s="13" t="n">
         <v>16</v>
@@ -16760,7 +16760,7 @@
         </is>
       </c>
       <c r="E503" s="13" t="n">
-        <v>9829</v>
+        <v>9828</v>
       </c>
       <c r="F503" s="13" t="n">
         <v>14</v>
@@ -16788,7 +16788,7 @@
         </is>
       </c>
       <c r="E504" s="13" t="n">
-        <v>9846</v>
+        <v>9845</v>
       </c>
       <c r="F504" s="13" t="n">
         <v>15</v>
@@ -16816,7 +16816,7 @@
         </is>
       </c>
       <c r="E505" s="13" t="n">
-        <v>9863</v>
+        <v>9862</v>
       </c>
       <c r="F505" s="13" t="n">
         <v>15</v>
@@ -16844,7 +16844,7 @@
         </is>
       </c>
       <c r="E506" s="13" t="n">
-        <v>9880</v>
+        <v>9879</v>
       </c>
       <c r="F506" s="13" t="n">
         <v>11</v>
@@ -16872,7 +16872,7 @@
         </is>
       </c>
       <c r="E507" s="13" t="n">
-        <v>9894</v>
+        <v>9893</v>
       </c>
       <c r="F507" s="13" t="n">
         <v>15</v>
@@ -16900,7 +16900,7 @@
         </is>
       </c>
       <c r="E508" s="13" t="n">
-        <v>9912</v>
+        <v>9911</v>
       </c>
       <c r="F508" s="13" t="n">
         <v>14</v>
@@ -16928,7 +16928,7 @@
         </is>
       </c>
       <c r="E509" s="13" t="n">
-        <v>9928</v>
+        <v>9927</v>
       </c>
       <c r="F509" s="13" t="n">
         <v>15</v>
@@ -16956,7 +16956,7 @@
         </is>
       </c>
       <c r="E510" s="13" t="n">
-        <v>9945</v>
+        <v>9944</v>
       </c>
       <c r="F510" s="13" t="n">
         <v>14</v>
@@ -16984,7 +16984,7 @@
         </is>
       </c>
       <c r="E511" s="13" t="n">
-        <v>9962</v>
+        <v>9961</v>
       </c>
       <c r="F511" s="13" t="n">
         <v>14</v>
@@ -17012,7 +17012,7 @@
         </is>
       </c>
       <c r="E512" s="13" t="n">
-        <v>9979</v>
+        <v>9978</v>
       </c>
       <c r="F512" s="13" t="n">
         <v>14</v>
@@ -17040,7 +17040,7 @@
         </is>
       </c>
       <c r="E513" s="13" t="n">
-        <v>9996</v>
+        <v>9995</v>
       </c>
       <c r="F513" s="13" t="n">
         <v>13</v>
@@ -17068,7 +17068,7 @@
         </is>
       </c>
       <c r="E514" s="13" t="n">
-        <v>10012</v>
+        <v>10011</v>
       </c>
       <c r="F514" s="13" t="n">
         <v>15</v>
@@ -17096,7 +17096,7 @@
         </is>
       </c>
       <c r="E515" s="13" t="n">
-        <v>10030</v>
+        <v>10029</v>
       </c>
       <c r="F515" s="13" t="n">
         <v>14</v>
@@ -17124,7 +17124,7 @@
         </is>
       </c>
       <c r="E516" s="13" t="n">
-        <v>10046</v>
+        <v>10045</v>
       </c>
       <c r="F516" s="13" t="n">
         <v>14</v>
@@ -17152,7 +17152,7 @@
         </is>
       </c>
       <c r="E517" s="13" t="n">
-        <v>10063</v>
+        <v>10062</v>
       </c>
       <c r="F517" s="13" t="n">
         <v>14</v>
@@ -17180,7 +17180,7 @@
         </is>
       </c>
       <c r="E518" s="13" t="n">
-        <v>10080</v>
+        <v>10079</v>
       </c>
       <c r="F518" s="13" t="n">
         <v>13</v>
@@ -17208,7 +17208,7 @@
         </is>
       </c>
       <c r="E519" s="13" t="n">
-        <v>10095</v>
+        <v>10094</v>
       </c>
       <c r="F519" s="13" t="n">
         <v>10</v>
@@ -17236,7 +17236,7 @@
         </is>
       </c>
       <c r="E520" s="13" t="n">
-        <v>10107</v>
+        <v>10106</v>
       </c>
       <c r="F520" s="13" t="n">
         <v>10</v>
@@ -17264,7 +17264,7 @@
         </is>
       </c>
       <c r="E521" s="13" t="n">
-        <v>10120</v>
+        <v>10119</v>
       </c>
       <c r="F521" s="13" t="n">
         <v>11</v>
@@ -17292,7 +17292,7 @@
         </is>
       </c>
       <c r="E522" s="13" t="n">
-        <v>10134</v>
+        <v>10133</v>
       </c>
       <c r="F522" s="13" t="n">
         <v>10</v>
@@ -17320,7 +17320,7 @@
         </is>
       </c>
       <c r="E523" s="13" t="n">
-        <v>10146</v>
+        <v>10145</v>
       </c>
       <c r="F523" s="13" t="n">
         <v>10</v>
@@ -17348,7 +17348,7 @@
         </is>
       </c>
       <c r="E524" s="13" t="n">
-        <v>10159</v>
+        <v>10158</v>
       </c>
       <c r="F524" s="13" t="n">
         <v>11</v>
@@ -17376,7 +17376,7 @@
         </is>
       </c>
       <c r="E525" s="13" t="n">
-        <v>10173</v>
+        <v>10172</v>
       </c>
       <c r="F525" s="13" t="n">
         <v>8</v>
@@ -17404,7 +17404,7 @@
         </is>
       </c>
       <c r="E526" s="13" t="n">
-        <v>10183</v>
+        <v>10182</v>
       </c>
       <c r="F526" s="13" t="n">
         <v>11</v>
@@ -17432,7 +17432,7 @@
         </is>
       </c>
       <c r="E527" s="13" t="n">
-        <v>10197</v>
+        <v>10196</v>
       </c>
       <c r="F527" s="13" t="n">
         <v>8</v>
@@ -17460,7 +17460,7 @@
         </is>
       </c>
       <c r="E528" s="13" t="n">
-        <v>10207</v>
+        <v>10206</v>
       </c>
       <c r="F528" s="13" t="n">
         <v>12</v>
@@ -17488,7 +17488,7 @@
         </is>
       </c>
       <c r="E529" s="13" t="n">
-        <v>10222</v>
+        <v>10221</v>
       </c>
       <c r="F529" s="13" t="n">
         <v>15</v>
@@ -17516,7 +17516,7 @@
         </is>
       </c>
       <c r="E530" s="13" t="n">
-        <v>10240</v>
+        <v>10239</v>
       </c>
       <c r="F530" s="13" t="n">
         <v>13</v>
@@ -17544,7 +17544,7 @@
         </is>
       </c>
       <c r="E531" s="13" t="n">
-        <v>10256</v>
+        <v>10255</v>
       </c>
       <c r="F531" s="13" t="n">
         <v>14</v>
@@ -17572,7 +17572,7 @@
         </is>
       </c>
       <c r="E532" s="13" t="n">
-        <v>10273</v>
+        <v>10272</v>
       </c>
       <c r="F532" s="13" t="n">
         <v>12</v>
@@ -17600,7 +17600,7 @@
         </is>
       </c>
       <c r="E533" s="13" t="n">
-        <v>10288</v>
+        <v>10287</v>
       </c>
       <c r="F533" s="13" t="n">
         <v>13</v>
@@ -17628,7 +17628,7 @@
         </is>
       </c>
       <c r="E534" s="13" t="n">
-        <v>10303</v>
+        <v>10302</v>
       </c>
       <c r="F534" s="13" t="n">
         <v>12</v>
@@ -17656,7 +17656,7 @@
         </is>
       </c>
       <c r="E535" s="13" t="n">
-        <v>10317</v>
+        <v>10316</v>
       </c>
       <c r="F535" s="13" t="n">
         <v>9</v>
@@ -17684,7 +17684,7 @@
         </is>
       </c>
       <c r="E536" s="13" t="n">
-        <v>10329</v>
+        <v>10328</v>
       </c>
       <c r="F536" s="13" t="n">
         <v>8</v>
@@ -17712,7 +17712,7 @@
         </is>
       </c>
       <c r="E537" s="13" t="n">
-        <v>10339</v>
+        <v>10338</v>
       </c>
       <c r="F537" s="13" t="n">
         <v>7</v>
@@ -17740,7 +17740,7 @@
         </is>
       </c>
       <c r="E538" s="13" t="n">
-        <v>10348</v>
+        <v>10347</v>
       </c>
       <c r="F538" s="13" t="n">
         <v>12</v>
@@ -17768,7 +17768,7 @@
         </is>
       </c>
       <c r="E539" s="13" t="n">
-        <v>10362</v>
+        <v>10361</v>
       </c>
       <c r="F539" s="13" t="n">
         <v>10</v>
@@ -17796,7 +17796,7 @@
         </is>
       </c>
       <c r="E540" s="13" t="n">
-        <v>10375</v>
+        <v>10374</v>
       </c>
       <c r="F540" s="13" t="n">
         <v>11</v>
@@ -17824,7 +17824,7 @@
         </is>
       </c>
       <c r="E541" s="13" t="n">
-        <v>10389</v>
+        <v>10388</v>
       </c>
       <c r="F541" s="13" t="n">
         <v>10</v>
@@ -17852,7 +17852,7 @@
         </is>
       </c>
       <c r="E542" s="13" t="n">
-        <v>10401</v>
+        <v>10400</v>
       </c>
       <c r="F542" s="13" t="n">
         <v>11</v>
@@ -17880,7 +17880,7 @@
         </is>
       </c>
       <c r="E543" s="13" t="n">
-        <v>10415</v>
+        <v>10414</v>
       </c>
       <c r="F543" s="13" t="n">
         <v>10</v>
@@ -17908,7 +17908,7 @@
         </is>
       </c>
       <c r="E544" s="13" t="n">
-        <v>10428</v>
+        <v>10427</v>
       </c>
       <c r="F544" s="13" t="n">
         <v>8</v>
@@ -17936,7 +17936,7 @@
         </is>
       </c>
       <c r="E545" s="13" t="n">
-        <v>10438</v>
+        <v>10437</v>
       </c>
       <c r="F545" s="13" t="n">
         <v>11</v>
@@ -17964,7 +17964,7 @@
         </is>
       </c>
       <c r="E546" s="13" t="n">
-        <v>10452</v>
+        <v>10451</v>
       </c>
       <c r="F546" s="13" t="n">
         <v>11</v>
@@ -17992,7 +17992,7 @@
         </is>
       </c>
       <c r="E547" s="13" t="n">
-        <v>10466</v>
+        <v>10465</v>
       </c>
       <c r="F547" s="13" t="n">
         <v>9</v>
@@ -18020,7 +18020,7 @@
         </is>
       </c>
       <c r="E548" s="13" t="n">
-        <v>10477</v>
+        <v>10476</v>
       </c>
       <c r="F548" s="13" t="n">
         <v>11</v>
@@ -18048,7 +18048,7 @@
         </is>
       </c>
       <c r="E549" s="13" t="n">
-        <v>10491</v>
+        <v>10490</v>
       </c>
       <c r="F549" s="13" t="n">
         <v>13</v>
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="E550" s="13" t="n">
-        <v>10507</v>
+        <v>10506</v>
       </c>
       <c r="F550" s="13" t="n">
         <v>10</v>
@@ -18104,7 +18104,7 @@
         </is>
       </c>
       <c r="E551" s="13" t="n">
-        <v>10519</v>
+        <v>10518</v>
       </c>
       <c r="F551" s="13" t="n">
         <v>12</v>
@@ -18132,7 +18132,7 @@
         </is>
       </c>
       <c r="E552" s="13" t="n">
-        <v>10534</v>
+        <v>10533</v>
       </c>
       <c r="F552" s="13" t="n">
         <v>10</v>
@@ -18160,7 +18160,7 @@
         </is>
       </c>
       <c r="E553" s="13" t="n">
-        <v>10547</v>
+        <v>10546</v>
       </c>
       <c r="F553" s="13" t="n">
         <v>10</v>
@@ -18188,7 +18188,7 @@
         </is>
       </c>
       <c r="E554" s="13" t="n">
-        <v>10559</v>
+        <v>10558</v>
       </c>
       <c r="F554" s="13" t="n">
         <v>10</v>
@@ -18216,7 +18216,7 @@
         </is>
       </c>
       <c r="E555" s="13" t="n">
-        <v>10572</v>
+        <v>10571</v>
       </c>
       <c r="F555" s="13" t="n">
         <v>10</v>
@@ -18244,7 +18244,7 @@
         </is>
       </c>
       <c r="E556" s="13" t="n">
-        <v>10585</v>
+        <v>10584</v>
       </c>
       <c r="F556" s="13" t="n">
         <v>8</v>
@@ -18272,7 +18272,7 @@
         </is>
       </c>
       <c r="E557" s="13" t="n">
-        <v>10595</v>
+        <v>10594</v>
       </c>
       <c r="F557" s="13" t="n">
         <v>11</v>
@@ -18300,7 +18300,7 @@
         </is>
       </c>
       <c r="E558" s="13" t="n">
-        <v>10609</v>
+        <v>10608</v>
       </c>
       <c r="F558" s="13" t="n">
         <v>8</v>
@@ -18328,7 +18328,7 @@
         </is>
       </c>
       <c r="E559" s="13" t="n">
-        <v>10619</v>
+        <v>10618</v>
       </c>
       <c r="F559" s="13" t="n">
         <v>10</v>
@@ -18356,7 +18356,7 @@
         </is>
       </c>
       <c r="E560" s="13" t="n">
-        <v>10631</v>
+        <v>10630</v>
       </c>
       <c r="F560" s="13" t="n">
         <v>11</v>
@@ -18384,7 +18384,7 @@
         </is>
       </c>
       <c r="E561" s="13" t="n">
-        <v>10645</v>
+        <v>10644</v>
       </c>
       <c r="F561" s="13" t="n">
         <v>7</v>
@@ -18412,7 +18412,7 @@
         </is>
       </c>
       <c r="E562" s="13" t="n">
-        <v>10654</v>
+        <v>10653</v>
       </c>
       <c r="F562" s="13" t="n">
         <v>6</v>
@@ -18440,7 +18440,7 @@
         </is>
       </c>
       <c r="E563" s="13" t="n">
-        <v>10663</v>
+        <v>10662</v>
       </c>
       <c r="F563" s="13" t="n">
         <v>4</v>
@@ -18468,7 +18468,7 @@
         </is>
       </c>
       <c r="E564" s="13" t="n">
-        <v>10669</v>
+        <v>10668</v>
       </c>
       <c r="F564" s="13" t="n">
         <v>5</v>
@@ -18496,7 +18496,7 @@
         </is>
       </c>
       <c r="E565" s="13" t="n">
-        <v>10676</v>
+        <v>10675</v>
       </c>
       <c r="F565" s="13" t="n">
         <v>1</v>
@@ -18524,7 +18524,7 @@
         </is>
       </c>
       <c r="E566" s="13" t="n">
-        <v>10679</v>
+        <v>10678</v>
       </c>
       <c r="F566" s="13" t="n">
         <v>8</v>
@@ -18552,7 +18552,7 @@
         </is>
       </c>
       <c r="E567" s="13" t="n">
-        <v>10690</v>
+        <v>10689</v>
       </c>
       <c r="F567" s="13" t="n">
         <v>9</v>
@@ -18580,7 +18580,7 @@
         </is>
       </c>
       <c r="E568" s="13" t="n">
-        <v>10702</v>
+        <v>10701</v>
       </c>
       <c r="F568" s="13" t="n">
         <v>8</v>
@@ -18608,7 +18608,7 @@
         </is>
       </c>
       <c r="E569" s="13" t="n">
-        <v>10712</v>
+        <v>10711</v>
       </c>
       <c r="F569" s="13" t="n">
         <v>8</v>
@@ -18636,7 +18636,7 @@
         </is>
       </c>
       <c r="E570" s="13" t="n">
-        <v>10723</v>
+        <v>10722</v>
       </c>
       <c r="F570" s="13" t="n">
         <v>8</v>
@@ -18664,7 +18664,7 @@
         </is>
       </c>
       <c r="E571" s="13" t="n">
-        <v>10733</v>
+        <v>10732</v>
       </c>
       <c r="F571" s="13" t="n">
         <v>8</v>
@@ -18692,7 +18692,7 @@
         </is>
       </c>
       <c r="E572" s="13" t="n">
-        <v>10744</v>
+        <v>10743</v>
       </c>
       <c r="F572" s="13" t="n">
         <v>8</v>
@@ -18720,7 +18720,7 @@
         </is>
       </c>
       <c r="E573" s="13" t="n">
-        <v>10754</v>
+        <v>10753</v>
       </c>
       <c r="F573" s="13" t="n">
         <v>9</v>
@@ -18748,7 +18748,7 @@
         </is>
       </c>
       <c r="E574" s="13" t="n">
-        <v>10766</v>
+        <v>10765</v>
       </c>
       <c r="F574" s="13" t="n">
         <v>8</v>
@@ -18776,7 +18776,7 @@
         </is>
       </c>
       <c r="E575" s="13" t="n">
-        <v>10776</v>
+        <v>10775</v>
       </c>
       <c r="F575" s="13" t="n">
         <v>8</v>
@@ -18804,7 +18804,7 @@
         </is>
       </c>
       <c r="E576" s="13" t="n">
-        <v>10787</v>
+        <v>10786</v>
       </c>
       <c r="F576" s="13" t="n">
         <v>8</v>
@@ -18832,7 +18832,7 @@
         </is>
       </c>
       <c r="E577" s="13" t="n">
-        <v>10798</v>
+        <v>10797</v>
       </c>
       <c r="F577" s="13" t="n">
         <v>8</v>
@@ -18860,7 +18860,7 @@
         </is>
       </c>
       <c r="E578" s="13" t="n">
-        <v>10808</v>
+        <v>10807</v>
       </c>
       <c r="F578" s="13" t="n">
         <v>8</v>
@@ -18888,7 +18888,7 @@
         </is>
       </c>
       <c r="E579" s="13" t="n">
-        <v>10819</v>
+        <v>10818</v>
       </c>
       <c r="F579" s="13" t="n">
         <v>8</v>
@@ -18916,7 +18916,7 @@
         </is>
       </c>
       <c r="E580" s="13" t="n">
-        <v>10829</v>
+        <v>10828</v>
       </c>
       <c r="F580" s="13" t="n">
         <v>8</v>
@@ -18944,7 +18944,7 @@
         </is>
       </c>
       <c r="E581" s="13" t="n">
-        <v>10840</v>
+        <v>10839</v>
       </c>
       <c r="F581" s="13" t="n">
         <v>6</v>
@@ -18972,7 +18972,7 @@
         </is>
       </c>
       <c r="E582" s="13" t="n">
-        <v>10848</v>
+        <v>10847</v>
       </c>
       <c r="F582" s="13" t="n">
         <v>2</v>
@@ -19000,7 +19000,7 @@
         </is>
       </c>
       <c r="E583" s="13" t="n">
-        <v>10852</v>
+        <v>10851</v>
       </c>
       <c r="F583" s="13" t="n">
         <v>8</v>
@@ -19028,7 +19028,7 @@
         </is>
       </c>
       <c r="E584" s="13" t="n">
-        <v>10863</v>
+        <v>10862</v>
       </c>
       <c r="F584" s="13" t="n">
         <v>1</v>
@@ -19056,7 +19056,7 @@
         </is>
       </c>
       <c r="E585" s="13" t="n">
-        <v>10866</v>
+        <v>10865</v>
       </c>
       <c r="F585" s="13" t="n">
         <v>4</v>
@@ -19084,7 +19084,7 @@
         </is>
       </c>
       <c r="E586" s="13" t="n">
-        <v>10872</v>
+        <v>10871</v>
       </c>
       <c r="F586" s="13" t="n">
         <v>1</v>
@@ -19112,7 +19112,7 @@
         </is>
       </c>
       <c r="E587" s="13" t="n">
-        <v>10875</v>
+        <v>10874</v>
       </c>
       <c r="F587" s="13" t="n">
         <v>1</v>
@@ -19140,7 +19140,7 @@
         </is>
       </c>
       <c r="E588" s="13" t="n">
-        <v>10879</v>
+        <v>10878</v>
       </c>
       <c r="F588" s="13" t="n">
         <v>1</v>
@@ -19168,7 +19168,7 @@
         </is>
       </c>
       <c r="E589" s="13" t="n">
-        <v>10882</v>
+        <v>10881</v>
       </c>
       <c r="F589" s="13" t="n">
         <v>1</v>
@@ -19196,7 +19196,7 @@
         </is>
       </c>
       <c r="E590" s="13" t="n">
-        <v>10885</v>
+        <v>10884</v>
       </c>
       <c r="F590" s="13" t="n">
         <v>10</v>
@@ -19224,7 +19224,7 @@
         </is>
       </c>
       <c r="E591" s="13" t="n">
-        <v>10897</v>
+        <v>10896</v>
       </c>
       <c r="F591" s="13" t="n">
         <v>8</v>
@@ -19252,7 +19252,7 @@
         </is>
       </c>
       <c r="E592" s="13" t="n">
-        <v>10907</v>
+        <v>10906</v>
       </c>
       <c r="F592" s="13" t="n">
         <v>11</v>
@@ -19280,7 +19280,7 @@
         </is>
       </c>
       <c r="E593" s="13" t="n">
-        <v>10921</v>
+        <v>10920</v>
       </c>
       <c r="F593" s="13" t="n">
         <v>6</v>
@@ -19308,7 +19308,7 @@
         </is>
       </c>
       <c r="E594" s="13" t="n">
-        <v>10929</v>
+        <v>10928</v>
       </c>
       <c r="F594" s="13" t="n">
         <v>8</v>
@@ -19336,7 +19336,7 @@
         </is>
       </c>
       <c r="E595" s="13" t="n">
-        <v>10940</v>
+        <v>10939</v>
       </c>
       <c r="F595" s="13" t="n">
         <v>5</v>
@@ -19364,7 +19364,7 @@
         </is>
       </c>
       <c r="E596" s="13" t="n">
-        <v>10947</v>
+        <v>10946</v>
       </c>
       <c r="F596" s="13" t="n">
         <v>4</v>
@@ -19392,7 +19392,7 @@
         </is>
       </c>
       <c r="E597" s="13" t="n">
-        <v>10953</v>
+        <v>10952</v>
       </c>
       <c r="F597" s="13" t="n">
         <v>1</v>
@@ -19420,7 +19420,7 @@
         </is>
       </c>
       <c r="E598" s="13" t="n">
-        <v>10956</v>
+        <v>10955</v>
       </c>
       <c r="F598" s="13" t="n">
         <v>8</v>
@@ -19448,7 +19448,7 @@
         </is>
       </c>
       <c r="E599" s="13" t="n">
-        <v>10966</v>
+        <v>10965</v>
       </c>
       <c r="F599" s="13" t="n">
         <v>8</v>
@@ -19476,7 +19476,7 @@
         </is>
       </c>
       <c r="E600" s="13" t="n">
-        <v>10977</v>
+        <v>10976</v>
       </c>
       <c r="F600" s="13" t="n">
         <v>8</v>
@@ -19504,7 +19504,7 @@
         </is>
       </c>
       <c r="E601" s="13" t="n">
-        <v>10987</v>
+        <v>10986</v>
       </c>
       <c r="F601" s="13" t="n">
         <v>7</v>
@@ -19532,7 +19532,7 @@
         </is>
       </c>
       <c r="E602" s="13" t="n">
-        <v>10997</v>
+        <v>10996</v>
       </c>
       <c r="F602" s="13" t="n">
         <v>8</v>
@@ -19560,7 +19560,7 @@
         </is>
       </c>
       <c r="E603" s="13" t="n">
-        <v>11007</v>
+        <v>11006</v>
       </c>
       <c r="F603" s="13" t="n">
         <v>8</v>
@@ -19588,7 +19588,7 @@
         </is>
       </c>
       <c r="E604" s="13" t="n">
-        <v>11018</v>
+        <v>11017</v>
       </c>
       <c r="F604" s="13" t="n">
         <v>4</v>
@@ -19616,7 +19616,7 @@
         </is>
       </c>
       <c r="E605" s="13" t="n">
-        <v>11024</v>
+        <v>11023</v>
       </c>
       <c r="F605" s="13" t="n">
         <v>32</v>
@@ -19644,7 +19644,7 @@
         </is>
       </c>
       <c r="E606" s="13" t="n">
-        <v>11060</v>
+        <v>11059</v>
       </c>
       <c r="F606" s="13" t="n">
         <v>20</v>
@@ -19672,7 +19672,7 @@
         </is>
       </c>
       <c r="E607" s="13" t="n">
-        <v>11083</v>
+        <v>11082</v>
       </c>
       <c r="F607" s="13" t="n">
         <v>59</v>
@@ -19700,7 +19700,7 @@
         </is>
       </c>
       <c r="E608" s="13" t="n">
-        <v>11147</v>
+        <v>11146</v>
       </c>
       <c r="F608" s="13" t="n">
         <v>58</v>
@@ -19728,7 +19728,7 @@
         </is>
       </c>
       <c r="E609" s="13" t="n">
-        <v>11211</v>
+        <v>11210</v>
       </c>
       <c r="F609" s="13" t="n">
         <v>24</v>
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="E610" s="13" t="n">
-        <v>11238</v>
+        <v>11237</v>
       </c>
       <c r="F610" s="13" t="n">
         <v>39</v>
@@ -19784,7 +19784,7 @@
         </is>
       </c>
       <c r="E611" s="13" t="n">
-        <v>11281</v>
+        <v>11280</v>
       </c>
       <c r="F611" s="13" t="n">
         <v>47</v>
@@ -19812,7 +19812,7 @@
         </is>
       </c>
       <c r="E612" s="13" t="n">
-        <v>11333</v>
+        <v>11332</v>
       </c>
       <c r="F612" s="13" t="n">
         <v>14</v>
@@ -19840,7 +19840,7 @@
         </is>
       </c>
       <c r="E613" s="13" t="n">
-        <v>11349</v>
+        <v>11348</v>
       </c>
       <c r="F613" s="13" t="n">
         <v>12</v>
@@ -19868,7 +19868,7 @@
         </is>
       </c>
       <c r="E614" s="13" t="n">
-        <v>11364</v>
+        <v>11363</v>
       </c>
       <c r="F614" s="13" t="n">
         <v>12</v>
@@ -19896,7 +19896,7 @@
         </is>
       </c>
       <c r="E615" s="13" t="n">
-        <v>11379</v>
+        <v>11378</v>
       </c>
       <c r="F615" s="13" t="n">
         <v>12</v>
@@ -19924,7 +19924,7 @@
         </is>
       </c>
       <c r="E616" s="13" t="n">
-        <v>11394</v>
+        <v>11393</v>
       </c>
       <c r="F616" s="13" t="n">
         <v>12</v>
@@ -19952,7 +19952,7 @@
         </is>
       </c>
       <c r="E617" s="13" t="n">
-        <v>11408</v>
+        <v>11407</v>
       </c>
       <c r="F617" s="13" t="n">
         <v>12</v>
@@ -19980,7 +19980,7 @@
         </is>
       </c>
       <c r="E618" s="13" t="n">
-        <v>11422</v>
+        <v>11421</v>
       </c>
       <c r="F618" s="13" t="n">
         <v>10</v>
@@ -20008,7 +20008,7 @@
         </is>
       </c>
       <c r="E619" s="13" t="n">
-        <v>11435</v>
+        <v>11434</v>
       </c>
       <c r="F619" s="13" t="n">
         <v>12</v>
@@ -20036,7 +20036,7 @@
         </is>
       </c>
       <c r="E620" s="13" t="n">
-        <v>11450</v>
+        <v>11449</v>
       </c>
       <c r="F620" s="13" t="n">
         <v>12</v>
@@ -20064,7 +20064,7 @@
         </is>
       </c>
       <c r="E621" s="13" t="n">
-        <v>11464</v>
+        <v>11463</v>
       </c>
       <c r="F621" s="13" t="n">
         <v>13</v>
@@ -20092,7 +20092,7 @@
         </is>
       </c>
       <c r="E622" s="13" t="n">
-        <v>11479</v>
+        <v>11478</v>
       </c>
       <c r="F622" s="13" t="n">
         <v>74</v>
@@ -20120,7 +20120,7 @@
         </is>
       </c>
       <c r="E623" s="13" t="n">
-        <v>11560</v>
+        <v>11559</v>
       </c>
       <c r="F623" s="13" t="n">
         <v>120</v>
@@ -20148,7 +20148,7 @@
         </is>
       </c>
       <c r="E624" s="13" t="n">
-        <v>11689</v>
+        <v>11688</v>
       </c>
       <c r="F624" s="13" t="n">
         <v>44</v>
@@ -20176,7 +20176,7 @@
         </is>
       </c>
       <c r="E625" s="13" t="n">
-        <v>11738</v>
+        <v>11737</v>
       </c>
       <c r="F625" s="13" t="n">
         <v>61</v>
@@ -20204,7 +20204,7 @@
         </is>
       </c>
       <c r="E626" s="13" t="n">
-        <v>11805</v>
+        <v>11804</v>
       </c>
       <c r="F626" s="13" t="n">
         <v>52</v>
@@ -20232,7 +20232,7 @@
         </is>
       </c>
       <c r="E627" s="13" t="n">
-        <v>11862</v>
+        <v>11861</v>
       </c>
       <c r="F627" s="13" t="n">
         <v>10</v>
@@ -20260,7 +20260,7 @@
         </is>
       </c>
       <c r="E628" s="13" t="n">
-        <v>11875</v>
+        <v>11874</v>
       </c>
       <c r="F628" s="13" t="n">
         <v>10</v>
@@ -20288,7 +20288,7 @@
         </is>
       </c>
       <c r="E629" s="13" t="n">
-        <v>11888</v>
+        <v>11887</v>
       </c>
       <c r="F629" s="13" t="n">
         <v>9</v>
@@ -20316,7 +20316,7 @@
         </is>
       </c>
       <c r="E630" s="13" t="n">
-        <v>11899</v>
+        <v>11898</v>
       </c>
       <c r="F630" s="13" t="n">
         <v>26</v>
@@ -20344,7 +20344,7 @@
         </is>
       </c>
       <c r="E631" s="13" t="n">
-        <v>11929</v>
+        <v>11928</v>
       </c>
       <c r="F631" s="13" t="n">
         <v>25</v>
@@ -20372,7 +20372,7 @@
         </is>
       </c>
       <c r="E632" s="13" t="n">
-        <v>11958</v>
+        <v>11957</v>
       </c>
       <c r="F632" s="13" t="n">
         <v>18</v>
@@ -20400,7 +20400,7 @@
         </is>
       </c>
       <c r="E633" s="13" t="n">
-        <v>11979</v>
+        <v>11978</v>
       </c>
       <c r="F633" s="13" t="n">
         <v>22</v>
@@ -20428,7 +20428,7 @@
         </is>
       </c>
       <c r="E634" s="13" t="n">
-        <v>12004</v>
+        <v>12003</v>
       </c>
       <c r="F634" s="13" t="n">
         <v>19</v>
@@ -20456,7 +20456,7 @@
         </is>
       </c>
       <c r="E635" s="13" t="n">
-        <v>12026</v>
+        <v>12025</v>
       </c>
       <c r="F635" s="13" t="n">
         <v>20</v>
@@ -20484,7 +20484,7 @@
         </is>
       </c>
       <c r="E636" s="13" t="n">
-        <v>12050</v>
+        <v>12049</v>
       </c>
       <c r="F636" s="13" t="n">
         <v>18</v>
@@ -20512,7 +20512,7 @@
         </is>
       </c>
       <c r="E637" s="13" t="n">
-        <v>12071</v>
+        <v>12070</v>
       </c>
       <c r="F637" s="13" t="n">
         <v>18</v>
@@ -20540,7 +20540,7 @@
         </is>
       </c>
       <c r="E638" s="13" t="n">
-        <v>12092</v>
+        <v>12091</v>
       </c>
       <c r="F638" s="13" t="n">
         <v>17</v>
@@ -20568,7 +20568,7 @@
         </is>
       </c>
       <c r="E639" s="13" t="n">
-        <v>12112</v>
+        <v>12111</v>
       </c>
       <c r="F639" s="13" t="n">
         <v>11</v>
@@ -20596,7 +20596,7 @@
         </is>
       </c>
       <c r="E640" s="13" t="n">
-        <v>12125</v>
+        <v>12124</v>
       </c>
       <c r="F640" s="13" t="n">
         <v>18</v>
@@ -20624,7 +20624,7 @@
         </is>
       </c>
       <c r="E641" s="13" t="n">
-        <v>12147</v>
+        <v>12146</v>
       </c>
       <c r="F641" s="13" t="n">
         <v>18</v>
@@ -20652,7 +20652,7 @@
         </is>
       </c>
       <c r="E642" s="13" t="n">
-        <v>12168</v>
+        <v>12167</v>
       </c>
       <c r="F642" s="13" t="n">
         <v>19</v>
@@ -20680,7 +20680,7 @@
         </is>
       </c>
       <c r="E643" s="13" t="n">
-        <v>12190</v>
+        <v>12189</v>
       </c>
       <c r="F643" s="13" t="n">
         <v>18</v>
@@ -20708,7 +20708,7 @@
         </is>
       </c>
       <c r="E644" s="13" t="n">
-        <v>12211</v>
+        <v>12210</v>
       </c>
       <c r="F644" s="13" t="n">
         <v>18</v>
@@ -20736,7 +20736,7 @@
         </is>
       </c>
       <c r="E645" s="13" t="n">
-        <v>12232</v>
+        <v>12231</v>
       </c>
       <c r="F645" s="13" t="n">
         <v>18</v>
@@ -20764,7 +20764,7 @@
         </is>
       </c>
       <c r="E646" s="13" t="n">
-        <v>12253</v>
+        <v>12252</v>
       </c>
       <c r="F646" s="13" t="n">
         <v>18</v>
@@ -20792,7 +20792,7 @@
         </is>
       </c>
       <c r="E647" s="13" t="n">
-        <v>12274</v>
+        <v>12273</v>
       </c>
       <c r="F647" s="13" t="n">
         <v>19</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="E648" s="13" t="n">
-        <v>12296</v>
+        <v>12295</v>
       </c>
       <c r="F648" s="13" t="n">
         <v>18</v>
@@ -20848,7 +20848,7 @@
         </is>
       </c>
       <c r="E649" s="13" t="n">
-        <v>12317</v>
+        <v>12316</v>
       </c>
       <c r="F649" s="13" t="n">
         <v>17</v>
@@ -20876,7 +20876,7 @@
         </is>
       </c>
       <c r="E650" s="13" t="n">
-        <v>12337</v>
+        <v>12336</v>
       </c>
       <c r="F650" s="13" t="n">
         <v>19</v>
@@ -20904,7 +20904,7 @@
         </is>
       </c>
       <c r="E651" s="13" t="n">
-        <v>12359</v>
+        <v>12358</v>
       </c>
       <c r="F651" s="13" t="n">
         <v>25</v>
@@ -20932,7 +20932,7 @@
         </is>
       </c>
       <c r="E652" s="13" t="n">
-        <v>12387</v>
+        <v>12386</v>
       </c>
       <c r="F652" s="13" t="n">
         <v>18</v>
@@ -20960,7 +20960,7 @@
         </is>
       </c>
       <c r="E653" s="13" t="n">
-        <v>12408</v>
+        <v>12407</v>
       </c>
       <c r="F653" s="13" t="n">
         <v>14</v>
@@ -20988,7 +20988,7 @@
         </is>
       </c>
       <c r="E654" s="13" t="n">
-        <v>12425</v>
+        <v>12424</v>
       </c>
       <c r="F654" s="13" t="n">
         <v>20</v>
@@ -21016,7 +21016,7 @@
         </is>
       </c>
       <c r="E655" s="13" t="n">
-        <v>12448</v>
+        <v>12447</v>
       </c>
       <c r="F655" s="13" t="n">
         <v>16</v>
@@ -21044,7 +21044,7 @@
         </is>
       </c>
       <c r="E656" s="13" t="n">
-        <v>12467</v>
+        <v>12466</v>
       </c>
       <c r="F656" s="13" t="n">
         <v>17</v>
@@ -21072,7 +21072,7 @@
         </is>
       </c>
       <c r="E657" s="13" t="n">
-        <v>12487</v>
+        <v>12486</v>
       </c>
       <c r="F657" s="13" t="n">
         <v>18</v>
@@ -21100,7 +21100,7 @@
         </is>
       </c>
       <c r="E658" s="13" t="n">
-        <v>12508</v>
+        <v>12507</v>
       </c>
       <c r="F658" s="13" t="n">
         <v>18</v>
@@ -21128,7 +21128,7 @@
         </is>
       </c>
       <c r="E659" s="13" t="n">
-        <v>12529</v>
+        <v>12528</v>
       </c>
       <c r="F659" s="13" t="n">
         <v>17</v>
@@ -21156,7 +21156,7 @@
         </is>
       </c>
       <c r="E660" s="13" t="n">
-        <v>12549</v>
+        <v>12548</v>
       </c>
       <c r="F660" s="13" t="n">
         <v>26</v>
@@ -21184,7 +21184,7 @@
         </is>
       </c>
       <c r="E661" s="13" t="n">
-        <v>12578</v>
+        <v>12577</v>
       </c>
       <c r="F661" s="13" t="n">
         <v>28</v>
@@ -21212,7 +21212,7 @@
         </is>
       </c>
       <c r="E662" s="13" t="n">
-        <v>12609</v>
+        <v>12608</v>
       </c>
       <c r="F662" s="13" t="n">
         <v>16</v>
@@ -21240,7 +21240,7 @@
         </is>
       </c>
       <c r="E663" s="13" t="n">
-        <v>12628</v>
+        <v>12627</v>
       </c>
       <c r="F663" s="13" t="n">
         <v>16</v>
@@ -21268,7 +21268,7 @@
         </is>
       </c>
       <c r="E664" s="13" t="n">
-        <v>12647</v>
+        <v>12646</v>
       </c>
       <c r="F664" s="13" t="n">
         <v>16</v>
@@ -21296,7 +21296,7 @@
         </is>
       </c>
       <c r="E665" s="13" t="n">
-        <v>12666</v>
+        <v>12665</v>
       </c>
       <c r="F665" s="13" t="n">
         <v>20</v>
@@ -21324,7 +21324,7 @@
         </is>
       </c>
       <c r="E666" s="13" t="n">
-        <v>12689</v>
+        <v>12688</v>
       </c>
       <c r="F666" s="13" t="n">
         <v>17</v>
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="E667" s="13" t="n">
-        <v>12709</v>
+        <v>12708</v>
       </c>
       <c r="F667" s="13" t="n">
         <v>16</v>
@@ -21380,7 +21380,7 @@
         </is>
       </c>
       <c r="E668" s="13" t="n">
-        <v>12728</v>
+        <v>12727</v>
       </c>
       <c r="F668" s="13" t="n">
         <v>17</v>
@@ -21408,7 +21408,7 @@
         </is>
       </c>
       <c r="E669" s="13" t="n">
-        <v>12748</v>
+        <v>12747</v>
       </c>
       <c r="F669" s="13" t="n">
         <v>17</v>
@@ -21436,7 +21436,7 @@
         </is>
       </c>
       <c r="E670" s="13" t="n">
-        <v>12768</v>
+        <v>12767</v>
       </c>
       <c r="F670" s="13" t="n">
         <v>10</v>
@@ -21464,7 +21464,7 @@
         </is>
       </c>
       <c r="E671" s="13" t="n">
-        <v>12781</v>
+        <v>12780</v>
       </c>
       <c r="F671" s="13" t="n">
         <v>16</v>
@@ -21492,7 +21492,7 @@
         </is>
       </c>
       <c r="E672" s="13" t="n">
-        <v>12800</v>
+        <v>12799</v>
       </c>
       <c r="F672" s="13" t="n">
         <v>17</v>
@@ -21520,7 +21520,7 @@
         </is>
       </c>
       <c r="E673" s="13" t="n">
-        <v>12820</v>
+        <v>12819</v>
       </c>
       <c r="F673" s="13" t="n">
         <v>14</v>
@@ -21548,7 +21548,7 @@
         </is>
       </c>
       <c r="E674" s="13" t="n">
-        <v>12837</v>
+        <v>12836</v>
       </c>
       <c r="F674" s="13" t="n">
         <v>18</v>
@@ -21576,7 +21576,7 @@
         </is>
       </c>
       <c r="E675" s="13" t="n">
-        <v>12858</v>
+        <v>12857</v>
       </c>
       <c r="F675" s="13" t="n">
         <v>17</v>
@@ -21604,7 +21604,7 @@
         </is>
       </c>
       <c r="E676" s="13" t="n">
-        <v>12878</v>
+        <v>12877</v>
       </c>
       <c r="F676" s="13" t="n">
         <v>15</v>
@@ -21632,7 +21632,7 @@
         </is>
       </c>
       <c r="E677" s="13" t="n">
-        <v>12896</v>
+        <v>12895</v>
       </c>
       <c r="F677" s="13" t="n">
         <v>8</v>
@@ -21660,7 +21660,7 @@
         </is>
       </c>
       <c r="E678" s="13" t="n">
-        <v>12906</v>
+        <v>12905</v>
       </c>
       <c r="F678" s="13" t="n">
         <v>14</v>
@@ -21688,7 +21688,7 @@
         </is>
       </c>
       <c r="E679" s="13" t="n">
-        <v>12923</v>
+        <v>12922</v>
       </c>
       <c r="F679" s="13" t="n">
         <v>16</v>
@@ -21716,7 +21716,7 @@
         </is>
       </c>
       <c r="E680" s="13" t="n">
-        <v>12943</v>
+        <v>12942</v>
       </c>
       <c r="F680" s="13" t="n">
         <v>17</v>
@@ -21744,7 +21744,7 @@
         </is>
       </c>
       <c r="E681" s="13" t="n">
-        <v>12963</v>
+        <v>12962</v>
       </c>
       <c r="F681" s="13" t="n">
         <v>16</v>
@@ -21772,7 +21772,7 @@
         </is>
       </c>
       <c r="E682" s="13" t="n">
-        <v>12983</v>
+        <v>12982</v>
       </c>
       <c r="F682" s="13" t="n">
         <v>7</v>
@@ -21800,7 +21800,7 @@
         </is>
       </c>
       <c r="E683" s="13" t="n">
-        <v>12992</v>
+        <v>12991</v>
       </c>
       <c r="F683" s="13" t="n">
         <v>9</v>
@@ -21828,7 +21828,7 @@
         </is>
       </c>
       <c r="E684" s="13" t="n">
-        <v>13004</v>
+        <v>13003</v>
       </c>
       <c r="F684" s="13" t="n">
         <v>10</v>
@@ -21856,7 +21856,7 @@
         </is>
       </c>
       <c r="E685" s="13" t="n">
-        <v>13016</v>
+        <v>13015</v>
       </c>
       <c r="F685" s="13" t="n">
         <v>27</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="E686" s="13" t="n">
-        <v>13047</v>
+        <v>13046</v>
       </c>
       <c r="F686" s="13" t="n">
         <v>17</v>
@@ -21912,7 +21912,7 @@
         </is>
       </c>
       <c r="E687" s="13" t="n">
-        <v>13067</v>
+        <v>13066</v>
       </c>
       <c r="F687" s="13" t="n">
         <v>18</v>
@@ -21940,7 +21940,7 @@
         </is>
       </c>
       <c r="E688" s="13" t="n">
-        <v>13088</v>
+        <v>13087</v>
       </c>
       <c r="F688" s="13" t="n">
         <v>18</v>
@@ -21968,7 +21968,7 @@
         </is>
       </c>
       <c r="E689" s="13" t="n">
-        <v>13109</v>
+        <v>13108</v>
       </c>
       <c r="F689" s="13" t="n">
         <v>11</v>
@@ -21996,7 +21996,7 @@
         </is>
       </c>
       <c r="E690" s="13" t="n">
-        <v>13122</v>
+        <v>13121</v>
       </c>
       <c r="F690" s="13" t="n">
         <v>18</v>
@@ -22024,7 +22024,7 @@
         </is>
       </c>
       <c r="E691" s="13" t="n">
-        <v>13143</v>
+        <v>13142</v>
       </c>
       <c r="F691" s="13" t="n">
         <v>9</v>
@@ -22052,7 +22052,7 @@
         </is>
       </c>
       <c r="E692" s="13" t="n">
-        <v>13155</v>
+        <v>13154</v>
       </c>
       <c r="F692" s="13" t="n">
         <v>10</v>
@@ -22080,7 +22080,7 @@
         </is>
       </c>
       <c r="E693" s="13" t="n">
-        <v>13167</v>
+        <v>13166</v>
       </c>
       <c r="F693" s="13" t="n">
         <v>10</v>
@@ -22108,7 +22108,7 @@
         </is>
       </c>
       <c r="E694" s="13" t="n">
-        <v>13180</v>
+        <v>13179</v>
       </c>
       <c r="F694" s="13" t="n">
         <v>21</v>
@@ -22136,7 +22136,7 @@
         </is>
       </c>
       <c r="E695" s="13" t="n">
-        <v>13204</v>
+        <v>13203</v>
       </c>
       <c r="F695" s="13" t="n">
         <v>11</v>
@@ -22164,7 +22164,7 @@
         </is>
       </c>
       <c r="E696" s="13" t="n">
-        <v>13218</v>
+        <v>13217</v>
       </c>
       <c r="F696" s="13" t="n">
         <v>9</v>
@@ -22192,7 +22192,7 @@
         </is>
       </c>
       <c r="E697" s="13" t="n">
-        <v>13229</v>
+        <v>13228</v>
       </c>
       <c r="F697" s="13" t="n">
         <v>10</v>
@@ -22220,7 +22220,7 @@
         </is>
       </c>
       <c r="E698" s="13" t="n">
-        <v>13242</v>
+        <v>13241</v>
       </c>
       <c r="F698" s="13" t="n">
         <v>10</v>
@@ -22248,7 +22248,7 @@
         </is>
       </c>
       <c r="E699" s="13" t="n">
-        <v>13255</v>
+        <v>13254</v>
       </c>
       <c r="F699" s="13" t="n">
         <v>29</v>
@@ -22276,7 +22276,7 @@
         </is>
       </c>
       <c r="E700" s="13" t="n">
-        <v>13287</v>
+        <v>13286</v>
       </c>
       <c r="F700" s="13" t="n">
         <v>16</v>
@@ -22304,7 +22304,7 @@
         </is>
       </c>
       <c r="E701" s="13" t="n">
-        <v>13306</v>
+        <v>13305</v>
       </c>
       <c r="F701" s="13" t="n">
         <v>15</v>
@@ -22332,10 +22332,10 @@
         </is>
       </c>
       <c r="E702" s="13" t="n">
-        <v>13324</v>
+        <v>13323</v>
       </c>
       <c r="F702" s="13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G702" s="15" t="inlineStr">
         <is>
@@ -22360,7 +22360,7 @@
         </is>
       </c>
       <c r="E703" s="13" t="n">
-        <v>13343</v>
+        <v>13342</v>
       </c>
       <c r="F703" s="13" t="n">
         <v>9</v>
@@ -22388,7 +22388,7 @@
         </is>
       </c>
       <c r="E704" s="13" t="n">
-        <v>13355</v>
+        <v>13354</v>
       </c>
       <c r="F704" s="13" t="n">
         <v>15</v>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="E705" s="13" t="n">
-        <v>13373</v>
+        <v>13372</v>
       </c>
       <c r="F705" s="13" t="n">
         <v>8</v>
@@ -22444,7 +22444,7 @@
         </is>
       </c>
       <c r="E706" s="13" t="n">
-        <v>13383</v>
+        <v>13382</v>
       </c>
       <c r="F706" s="13" t="n">
         <v>9</v>
@@ -22472,7 +22472,7 @@
         </is>
       </c>
       <c r="E707" s="13" t="n">
-        <v>13397</v>
+        <v>13396</v>
       </c>
       <c r="F707" s="13" t="n">
         <v>17</v>
@@ -22500,7 +22500,7 @@
         </is>
       </c>
       <c r="E708" s="13" t="n">
-        <v>13417</v>
+        <v>13416</v>
       </c>
       <c r="F708" s="13" t="n">
         <v>7</v>
@@ -22528,7 +22528,7 @@
         </is>
       </c>
       <c r="E709" s="13" t="n">
-        <v>13426</v>
+        <v>13425</v>
       </c>
       <c r="F709" s="13" t="n">
         <v>10</v>
@@ -22556,7 +22556,7 @@
         </is>
       </c>
       <c r="E710" s="13" t="n">
-        <v>13439</v>
+        <v>13438</v>
       </c>
       <c r="F710" s="13" t="n">
         <v>8</v>
@@ -22584,7 +22584,7 @@
         </is>
       </c>
       <c r="E711" s="13" t="n">
-        <v>13450</v>
+        <v>13449</v>
       </c>
       <c r="F711" s="13" t="n">
         <v>10</v>
@@ -22612,7 +22612,7 @@
         </is>
       </c>
       <c r="E712" s="13" t="n">
-        <v>13462</v>
+        <v>13461</v>
       </c>
       <c r="F712" s="13" t="n">
         <v>9</v>
@@ -22640,7 +22640,7 @@
         </is>
       </c>
       <c r="E713" s="13" t="n">
-        <v>13474</v>
+        <v>13473</v>
       </c>
       <c r="F713" s="13" t="n">
         <v>9</v>
@@ -22668,7 +22668,7 @@
         </is>
       </c>
       <c r="E714" s="13" t="n">
-        <v>13485</v>
+        <v>13484</v>
       </c>
       <c r="F714" s="13" t="n">
         <v>9</v>
@@ -22696,7 +22696,7 @@
         </is>
       </c>
       <c r="E715" s="13" t="n">
-        <v>13497</v>
+        <v>13496</v>
       </c>
       <c r="F715" s="13" t="n">
         <v>8</v>
@@ -22724,7 +22724,7 @@
         </is>
       </c>
       <c r="E716" s="13" t="n">
-        <v>13507</v>
+        <v>13506</v>
       </c>
       <c r="F716" s="13" t="n">
         <v>8</v>
@@ -22752,7 +22752,7 @@
         </is>
       </c>
       <c r="E717" s="13" t="n">
-        <v>13517</v>
+        <v>13516</v>
       </c>
       <c r="F717" s="13" t="n">
         <v>8</v>
@@ -22780,7 +22780,7 @@
         </is>
       </c>
       <c r="E718" s="13" t="n">
-        <v>13527</v>
+        <v>13526</v>
       </c>
       <c r="F718" s="13" t="n">
         <v>8</v>
@@ -22808,7 +22808,7 @@
         </is>
       </c>
       <c r="E719" s="13" t="n">
-        <v>13537</v>
+        <v>13536</v>
       </c>
       <c r="F719" s="13" t="n">
         <v>10</v>
@@ -22836,7 +22836,7 @@
         </is>
       </c>
       <c r="E720" s="13" t="n">
-        <v>13550</v>
+        <v>13549</v>
       </c>
       <c r="F720" s="13" t="n">
         <v>9</v>
@@ -22864,7 +22864,7 @@
         </is>
       </c>
       <c r="E721" s="13" t="n">
-        <v>13561</v>
+        <v>13560</v>
       </c>
       <c r="F721" s="13" t="n">
         <v>9</v>
@@ -22892,7 +22892,7 @@
         </is>
       </c>
       <c r="E722" s="13" t="n">
-        <v>13573</v>
+        <v>13572</v>
       </c>
       <c r="F722" s="13" t="n">
         <v>7</v>
@@ -22920,7 +22920,7 @@
         </is>
       </c>
       <c r="E723" s="13" t="n">
-        <v>13582</v>
+        <v>13581</v>
       </c>
       <c r="F723" s="13" t="n">
         <v>8</v>
@@ -22948,7 +22948,7 @@
         </is>
       </c>
       <c r="E724" s="13" t="n">
-        <v>13593</v>
+        <v>13592</v>
       </c>
       <c r="F724" s="13" t="n">
         <v>8</v>
@@ -22976,7 +22976,7 @@
         </is>
       </c>
       <c r="E725" s="13" t="n">
-        <v>13603</v>
+        <v>13602</v>
       </c>
       <c r="F725" s="13" t="n">
         <v>6</v>
@@ -23004,7 +23004,7 @@
         </is>
       </c>
       <c r="E726" s="13" t="n">
-        <v>13612</v>
+        <v>13611</v>
       </c>
       <c r="F726" s="13" t="n">
         <v>7</v>
@@ -23032,7 +23032,7 @@
         </is>
       </c>
       <c r="E727" s="13" t="n">
-        <v>13620</v>
+        <v>13619</v>
       </c>
       <c r="F727" s="13" t="n">
         <v>16</v>
@@ -23060,7 +23060,7 @@
         </is>
       </c>
       <c r="E728" s="13" t="n">
-        <v>13639</v>
+        <v>13638</v>
       </c>
       <c r="F728" s="13" t="n">
         <v>8</v>
@@ -23088,7 +23088,7 @@
         </is>
       </c>
       <c r="E729" s="13" t="n">
-        <v>13649</v>
+        <v>13648</v>
       </c>
       <c r="F729" s="13" t="n">
         <v>8</v>
@@ -23116,7 +23116,7 @@
         </is>
       </c>
       <c r="E730" s="13" t="n">
-        <v>13659</v>
+        <v>13658</v>
       </c>
       <c r="F730" s="13" t="n">
         <v>11</v>
@@ -23144,7 +23144,7 @@
         </is>
       </c>
       <c r="E731" s="13" t="n">
-        <v>13673</v>
+        <v>13672</v>
       </c>
       <c r="F731" s="13" t="n">
         <v>8</v>
@@ -23172,7 +23172,7 @@
         </is>
       </c>
       <c r="E732" s="13" t="n">
-        <v>13683</v>
+        <v>13682</v>
       </c>
       <c r="F732" s="13" t="n">
         <v>9</v>
@@ -23200,7 +23200,7 @@
         </is>
       </c>
       <c r="E733" s="13" t="n">
-        <v>13695</v>
+        <v>13694</v>
       </c>
       <c r="F733" s="13" t="n">
         <v>8</v>
@@ -23228,7 +23228,7 @@
         </is>
       </c>
       <c r="E734" s="13" t="n">
-        <v>13705</v>
+        <v>13704</v>
       </c>
       <c r="F734" s="13" t="n">
         <v>8</v>
@@ -23256,7 +23256,7 @@
         </is>
       </c>
       <c r="E735" s="13" t="n">
-        <v>13716</v>
+        <v>13715</v>
       </c>
       <c r="F735" s="13" t="n">
         <v>8</v>
@@ -23284,7 +23284,7 @@
         </is>
       </c>
       <c r="E736" s="13" t="n">
-        <v>13726</v>
+        <v>13725</v>
       </c>
       <c r="F736" s="13" t="n">
         <v>8</v>
@@ -23312,7 +23312,7 @@
         </is>
       </c>
       <c r="E737" s="13" t="n">
-        <v>13737</v>
+        <v>13736</v>
       </c>
       <c r="F737" s="13" t="n">
         <v>8</v>
@@ -23340,7 +23340,7 @@
         </is>
       </c>
       <c r="E738" s="13" t="n">
-        <v>13747</v>
+        <v>13746</v>
       </c>
       <c r="F738" s="13" t="n">
         <v>8</v>
@@ -23368,7 +23368,7 @@
         </is>
       </c>
       <c r="E739" s="13" t="n">
-        <v>13758</v>
+        <v>13757</v>
       </c>
       <c r="F739" s="13" t="n">
         <v>8</v>
@@ -23396,7 +23396,7 @@
         </is>
       </c>
       <c r="E740" s="13" t="n">
-        <v>13768</v>
+        <v>13767</v>
       </c>
       <c r="F740" s="13" t="n">
         <v>8</v>
@@ -23424,7 +23424,7 @@
         </is>
       </c>
       <c r="E741" s="13" t="n">
-        <v>13779</v>
+        <v>13778</v>
       </c>
       <c r="F741" s="13" t="n">
         <v>8</v>
@@ -23452,7 +23452,7 @@
         </is>
       </c>
       <c r="E742" s="13" t="n">
-        <v>13789</v>
+        <v>13788</v>
       </c>
       <c r="F742" s="13" t="n">
         <v>8</v>
@@ -23480,7 +23480,7 @@
         </is>
       </c>
       <c r="E743" s="13" t="n">
-        <v>13800</v>
+        <v>13799</v>
       </c>
       <c r="F743" s="13" t="n">
         <v>6</v>
@@ -23508,7 +23508,7 @@
         </is>
       </c>
       <c r="E744" s="13" t="n">
-        <v>13808</v>
+        <v>13807</v>
       </c>
       <c r="F744" s="13" t="n">
         <v>8</v>
@@ -23536,7 +23536,7 @@
         </is>
       </c>
       <c r="E745" s="13" t="n">
-        <v>13819</v>
+        <v>13818</v>
       </c>
       <c r="F745" s="13" t="n">
         <v>8</v>
@@ -23564,7 +23564,7 @@
         </is>
       </c>
       <c r="E746" s="13" t="n">
-        <v>13829</v>
+        <v>13828</v>
       </c>
       <c r="F746" s="13" t="n">
         <v>9</v>
@@ -23592,7 +23592,7 @@
         </is>
       </c>
       <c r="E747" s="13" t="n">
-        <v>13841</v>
+        <v>13840</v>
       </c>
       <c r="F747" s="13" t="n">
         <v>9</v>
@@ -23620,7 +23620,7 @@
         </is>
       </c>
       <c r="E748" s="13" t="n">
-        <v>13852</v>
+        <v>13851</v>
       </c>
       <c r="F748" s="13" t="n">
         <v>9</v>
@@ -23648,7 +23648,7 @@
         </is>
       </c>
       <c r="E749" s="13" t="n">
-        <v>13864</v>
+        <v>13863</v>
       </c>
       <c r="F749" s="13" t="n">
         <v>8</v>
@@ -23676,7 +23676,7 @@
         </is>
       </c>
       <c r="E750" s="13" t="n">
-        <v>13874</v>
+        <v>13873</v>
       </c>
       <c r="F750" s="13" t="n">
         <v>5</v>
@@ -23704,7 +23704,7 @@
         </is>
       </c>
       <c r="E751" s="13" t="n">
-        <v>13882</v>
+        <v>13881</v>
       </c>
       <c r="F751" s="13" t="n">
         <v>13</v>
@@ -23732,7 +23732,7 @@
         </is>
       </c>
       <c r="E752" s="13" t="n">
-        <v>13897</v>
+        <v>13896</v>
       </c>
       <c r="F752" s="13" t="n">
         <v>17</v>
@@ -23760,7 +23760,7 @@
         </is>
       </c>
       <c r="E753" s="13" t="n">
-        <v>13917</v>
+        <v>13916</v>
       </c>
       <c r="F753" s="13" t="n">
         <v>8</v>
@@ -23788,7 +23788,7 @@
         </is>
       </c>
       <c r="E754" s="13" t="n">
-        <v>13928</v>
+        <v>13927</v>
       </c>
       <c r="F754" s="13" t="n">
         <v>8</v>
@@ -23816,7 +23816,7 @@
         </is>
       </c>
       <c r="E755" s="13" t="n">
-        <v>13938</v>
+        <v>13937</v>
       </c>
       <c r="F755" s="13" t="n">
         <v>13</v>
@@ -23844,7 +23844,7 @@
         </is>
       </c>
       <c r="E756" s="13" t="n">
-        <v>13954</v>
+        <v>13953</v>
       </c>
       <c r="F756" s="13" t="n">
         <v>9</v>
@@ -23872,7 +23872,7 @@
         </is>
       </c>
       <c r="E757" s="13" t="n">
-        <v>13965</v>
+        <v>13964</v>
       </c>
       <c r="F757" s="13" t="n">
         <v>7</v>
@@ -23900,7 +23900,7 @@
         </is>
       </c>
       <c r="E758" s="13" t="n">
-        <v>13974</v>
+        <v>13973</v>
       </c>
       <c r="F758" s="13" t="n">
         <v>9</v>
@@ -23928,7 +23928,7 @@
         </is>
       </c>
       <c r="E759" s="13" t="n">
-        <v>13986</v>
+        <v>13985</v>
       </c>
       <c r="F759" s="13" t="n">
         <v>12</v>
@@ -23956,7 +23956,7 @@
         </is>
       </c>
       <c r="E760" s="13" t="n">
-        <v>14000</v>
+        <v>13999</v>
       </c>
       <c r="F760" s="13" t="n">
         <v>11</v>
@@ -23984,7 +23984,7 @@
         </is>
       </c>
       <c r="E761" s="13" t="n">
-        <v>14014</v>
+        <v>14013</v>
       </c>
       <c r="F761" s="13" t="n">
         <v>10</v>
@@ -24012,7 +24012,7 @@
         </is>
       </c>
       <c r="E762" s="13" t="n">
-        <v>14027</v>
+        <v>14026</v>
       </c>
       <c r="F762" s="13" t="n">
         <v>10</v>
@@ -24040,7 +24040,7 @@
         </is>
       </c>
       <c r="E763" s="13" t="n">
-        <v>14039</v>
+        <v>14038</v>
       </c>
       <c r="F763" s="13" t="n">
         <v>11</v>
@@ -24068,7 +24068,7 @@
         </is>
       </c>
       <c r="E764" s="13" t="n">
-        <v>14053</v>
+        <v>14052</v>
       </c>
       <c r="F764" s="13" t="n">
         <v>11</v>
@@ -24096,7 +24096,7 @@
         </is>
       </c>
       <c r="E765" s="13" t="n">
-        <v>14067</v>
+        <v>14066</v>
       </c>
       <c r="F765" s="13" t="n">
         <v>9</v>
@@ -24124,7 +24124,7 @@
         </is>
       </c>
       <c r="E766" s="13" t="n">
-        <v>14078</v>
+        <v>14077</v>
       </c>
       <c r="F766" s="13" t="n">
         <v>11</v>
@@ -24152,7 +24152,7 @@
         </is>
       </c>
       <c r="E767" s="13" t="n">
-        <v>14091</v>
+        <v>14090</v>
       </c>
       <c r="F767" s="13" t="n">
         <v>10</v>
@@ -24180,7 +24180,7 @@
         </is>
       </c>
       <c r="E768" s="13" t="n">
-        <v>14104</v>
+        <v>14103</v>
       </c>
       <c r="F768" s="13" t="n">
         <v>9</v>
@@ -24208,7 +24208,7 @@
         </is>
       </c>
       <c r="E769" s="13" t="n">
-        <v>14115</v>
+        <v>14114</v>
       </c>
       <c r="F769" s="13" t="n">
         <v>9</v>
@@ -24236,7 +24236,7 @@
         </is>
       </c>
       <c r="E770" s="13" t="n">
-        <v>14127</v>
+        <v>14126</v>
       </c>
       <c r="F770" s="13" t="n">
         <v>10</v>
@@ -24264,7 +24264,7 @@
         </is>
       </c>
       <c r="E771" s="13" t="n">
-        <v>14140</v>
+        <v>14139</v>
       </c>
       <c r="F771" s="13" t="n">
         <v>15</v>
@@ -24292,7 +24292,7 @@
         </is>
       </c>
       <c r="E772" s="13" t="n">
-        <v>14157</v>
+        <v>14156</v>
       </c>
       <c r="F772" s="13" t="n">
         <v>16</v>
@@ -24320,7 +24320,7 @@
         </is>
       </c>
       <c r="E773" s="13" t="n">
-        <v>14176</v>
+        <v>14175</v>
       </c>
       <c r="F773" s="13" t="n">
         <v>10</v>
@@ -24348,7 +24348,7 @@
         </is>
       </c>
       <c r="E774" s="13" t="n">
-        <v>14188</v>
+        <v>14187</v>
       </c>
       <c r="F774" s="13" t="n">
         <v>9</v>
@@ -24376,7 +24376,7 @@
         </is>
       </c>
       <c r="E775" s="13" t="n">
-        <v>14200</v>
+        <v>14199</v>
       </c>
       <c r="F775" s="13" t="n">
         <v>8</v>
@@ -24404,7 +24404,7 @@
         </is>
       </c>
       <c r="E776" s="13" t="n">
-        <v>14210</v>
+        <v>14209</v>
       </c>
       <c r="F776" s="13" t="n">
         <v>8</v>
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="E777" s="13" t="n">
-        <v>14221</v>
+        <v>14220</v>
       </c>
       <c r="F777" s="13" t="n">
         <v>8</v>
@@ -24460,7 +24460,7 @@
         </is>
       </c>
       <c r="E778" s="13" t="n">
-        <v>14231</v>
+        <v>14230</v>
       </c>
       <c r="F778" s="13" t="n">
         <v>9</v>
@@ -24488,7 +24488,7 @@
         </is>
       </c>
       <c r="E779" s="13" t="n">
-        <v>14243</v>
+        <v>14242</v>
       </c>
       <c r="F779" s="13" t="n">
         <v>8</v>
@@ -24516,7 +24516,7 @@
         </is>
       </c>
       <c r="E780" s="13" t="n">
-        <v>14253</v>
+        <v>14252</v>
       </c>
       <c r="F780" s="13" t="n">
         <v>8</v>
@@ -24544,7 +24544,7 @@
         </is>
       </c>
       <c r="E781" s="13" t="n">
-        <v>14264</v>
+        <v>14263</v>
       </c>
       <c r="F781" s="13" t="n">
         <v>8</v>
@@ -24572,7 +24572,7 @@
         </is>
       </c>
       <c r="E782" s="13" t="n">
-        <v>14274</v>
+        <v>14273</v>
       </c>
       <c r="F782" s="13" t="n">
         <v>8</v>
@@ -24600,7 +24600,7 @@
         </is>
       </c>
       <c r="E783" s="13" t="n">
-        <v>14285</v>
+        <v>14284</v>
       </c>
       <c r="F783" s="13" t="n">
         <v>8</v>
@@ -24628,7 +24628,7 @@
         </is>
       </c>
       <c r="E784" s="13" t="n">
-        <v>14295</v>
+        <v>14294</v>
       </c>
       <c r="F784" s="13" t="n">
         <v>8</v>
@@ -24656,7 +24656,7 @@
         </is>
       </c>
       <c r="E785" s="13" t="n">
-        <v>14306</v>
+        <v>14305</v>
       </c>
       <c r="F785" s="13" t="n">
         <v>8</v>
@@ -24684,7 +24684,7 @@
         </is>
       </c>
       <c r="E786" s="13" t="n">
-        <v>14316</v>
+        <v>14315</v>
       </c>
       <c r="F786" s="13" t="n">
         <v>8</v>
@@ -24712,7 +24712,7 @@
         </is>
       </c>
       <c r="E787" s="13" t="n">
-        <v>14327</v>
+        <v>14326</v>
       </c>
       <c r="F787" s="13" t="n">
         <v>7</v>
@@ -24740,7 +24740,7 @@
         </is>
       </c>
       <c r="E788" s="13" t="n">
-        <v>14336</v>
+        <v>14335</v>
       </c>
       <c r="F788" s="13" t="n">
         <v>8</v>
@@ -24768,7 +24768,7 @@
         </is>
       </c>
       <c r="E789" s="13" t="n">
-        <v>14347</v>
+        <v>14346</v>
       </c>
       <c r="F789" s="13" t="n">
         <v>7</v>
@@ -24796,7 +24796,7 @@
         </is>
       </c>
       <c r="E790" s="13" t="n">
-        <v>14356</v>
+        <v>14355</v>
       </c>
       <c r="F790" s="13" t="n">
         <v>6</v>
@@ -24824,7 +24824,7 @@
         </is>
       </c>
       <c r="E791" s="13" t="n">
-        <v>14365</v>
+        <v>14364</v>
       </c>
       <c r="F791" s="13" t="n">
         <v>8</v>
@@ -24852,7 +24852,7 @@
         </is>
       </c>
       <c r="E792" s="13" t="n">
-        <v>14375</v>
+        <v>14374</v>
       </c>
       <c r="F792" s="13" t="n">
         <v>15</v>
@@ -24880,7 +24880,7 @@
         </is>
       </c>
       <c r="E793" s="13" t="n">
-        <v>14393</v>
+        <v>14392</v>
       </c>
       <c r="F793" s="13" t="n">
         <v>9</v>
@@ -24908,7 +24908,7 @@
         </is>
       </c>
       <c r="E794" s="13" t="n">
-        <v>14405</v>
+        <v>14404</v>
       </c>
       <c r="F794" s="13" t="n">
         <v>9</v>
@@ -24936,7 +24936,7 @@
         </is>
       </c>
       <c r="E795" s="13" t="n">
-        <v>14416</v>
+        <v>14415</v>
       </c>
       <c r="F795" s="13" t="n">
         <v>9</v>
@@ -24964,7 +24964,7 @@
         </is>
       </c>
       <c r="E796" s="13" t="n">
-        <v>14428</v>
+        <v>14427</v>
       </c>
       <c r="F796" s="13" t="n">
         <v>8</v>
@@ -24992,7 +24992,7 @@
         </is>
       </c>
       <c r="E797" s="13" t="n">
-        <v>14438</v>
+        <v>14437</v>
       </c>
       <c r="F797" s="13" t="n">
         <v>8</v>
@@ -25020,7 +25020,7 @@
         </is>
       </c>
       <c r="E798" s="13" t="n">
-        <v>14449</v>
+        <v>14448</v>
       </c>
       <c r="F798" s="13" t="n">
         <v>9</v>
@@ -25048,7 +25048,7 @@
         </is>
       </c>
       <c r="E799" s="13" t="n">
-        <v>14460</v>
+        <v>14459</v>
       </c>
       <c r="F799" s="13" t="n">
         <v>9</v>
@@ -25076,7 +25076,7 @@
         </is>
       </c>
       <c r="E800" s="13" t="n">
-        <v>14472</v>
+        <v>14471</v>
       </c>
       <c r="F800" s="13" t="n">
         <v>8</v>
@@ -25104,7 +25104,7 @@
         </is>
       </c>
       <c r="E801" s="13" t="n">
-        <v>14482</v>
+        <v>14481</v>
       </c>
       <c r="F801" s="13" t="n">
         <v>9</v>
@@ -25132,7 +25132,7 @@
         </is>
       </c>
       <c r="E802" s="13" t="n">
-        <v>14494</v>
+        <v>14493</v>
       </c>
       <c r="F802" s="13" t="n">
         <v>9</v>
@@ -25160,7 +25160,7 @@
         </is>
       </c>
       <c r="E803" s="13" t="n">
-        <v>14505</v>
+        <v>14504</v>
       </c>
       <c r="F803" s="13" t="n">
         <v>9</v>
@@ -25188,7 +25188,7 @@
         </is>
       </c>
       <c r="E804" s="13" t="n">
-        <v>14517</v>
+        <v>14516</v>
       </c>
       <c r="F804" s="13" t="n">
         <v>9</v>
@@ -25216,7 +25216,7 @@
         </is>
       </c>
       <c r="E805" s="13" t="n">
-        <v>14528</v>
+        <v>14527</v>
       </c>
       <c r="F805" s="13" t="n">
         <v>8</v>
@@ -25244,7 +25244,7 @@
         </is>
       </c>
       <c r="E806" s="13" t="n">
-        <v>14539</v>
+        <v>14538</v>
       </c>
       <c r="F806" s="13" t="n">
         <v>7</v>
@@ -25272,7 +25272,7 @@
         </is>
       </c>
       <c r="E807" s="13" t="n">
-        <v>14548</v>
+        <v>14547</v>
       </c>
       <c r="F807" s="13" t="n">
         <v>7</v>
@@ -25300,7 +25300,7 @@
         </is>
       </c>
       <c r="E808" s="13" t="n">
-        <v>14558</v>
+        <v>14557</v>
       </c>
       <c r="F808" s="13" t="n">
         <v>8</v>
@@ -25328,7 +25328,7 @@
         </is>
       </c>
       <c r="E809" s="13" t="n">
-        <v>14568</v>
+        <v>14567</v>
       </c>
       <c r="F809" s="13" t="n">
         <v>9</v>
@@ -25356,7 +25356,7 @@
         </is>
       </c>
       <c r="E810" s="13" t="n">
-        <v>14580</v>
+        <v>14579</v>
       </c>
       <c r="F810" s="13" t="n">
         <v>8</v>
@@ -25384,7 +25384,7 @@
         </is>
       </c>
       <c r="E811" s="13" t="n">
-        <v>14590</v>
+        <v>14589</v>
       </c>
       <c r="F811" s="13" t="n">
         <v>10</v>
@@ -25412,7 +25412,7 @@
         </is>
       </c>
       <c r="E812" s="13" t="n">
-        <v>14603</v>
+        <v>14602</v>
       </c>
       <c r="F812" s="13" t="n">
         <v>9</v>
@@ -25440,7 +25440,7 @@
         </is>
       </c>
       <c r="E813" s="13" t="n">
-        <v>14614</v>
+        <v>14613</v>
       </c>
       <c r="F813" s="13" t="n">
         <v>8</v>
@@ -25468,7 +25468,7 @@
         </is>
       </c>
       <c r="E814" s="13" t="n">
-        <v>14625</v>
+        <v>14624</v>
       </c>
       <c r="F814" s="13" t="n">
         <v>8</v>
@@ -25496,7 +25496,7 @@
         </is>
       </c>
       <c r="E815" s="13" t="n">
-        <v>14635</v>
+        <v>14634</v>
       </c>
       <c r="F815" s="13" t="n">
         <v>7</v>
@@ -25524,7 +25524,7 @@
         </is>
       </c>
       <c r="E816" s="13" t="n">
-        <v>14645</v>
+        <v>14644</v>
       </c>
       <c r="F816" s="13" t="n">
         <v>9</v>
@@ -25552,7 +25552,7 @@
         </is>
       </c>
       <c r="E817" s="13" t="n">
-        <v>14656</v>
+        <v>14655</v>
       </c>
       <c r="F817" s="13" t="n">
         <v>9</v>
@@ -25580,7 +25580,7 @@
         </is>
       </c>
       <c r="E818" s="13" t="n">
-        <v>14668</v>
+        <v>14667</v>
       </c>
       <c r="F818" s="13" t="n">
         <v>8</v>
@@ -25608,7 +25608,7 @@
         </is>
       </c>
       <c r="E819" s="13" t="n">
-        <v>14678</v>
+        <v>14677</v>
       </c>
       <c r="F819" s="13" t="n">
         <v>8</v>
@@ -25636,7 +25636,7 @@
         </is>
       </c>
       <c r="E820" s="13" t="n">
-        <v>14689</v>
+        <v>14688</v>
       </c>
       <c r="F820" s="13" t="n">
         <v>9</v>
@@ -25664,7 +25664,7 @@
         </is>
       </c>
       <c r="E821" s="13" t="n">
-        <v>14700</v>
+        <v>14699</v>
       </c>
       <c r="F821" s="13" t="n">
         <v>8</v>
@@ -25692,7 +25692,7 @@
         </is>
       </c>
       <c r="E822" s="13" t="n">
-        <v>14711</v>
+        <v>14710</v>
       </c>
       <c r="F822" s="13" t="n">
         <v>8</v>
@@ -25720,7 +25720,7 @@
         </is>
       </c>
       <c r="E823" s="13" t="n">
-        <v>14721</v>
+        <v>14720</v>
       </c>
       <c r="F823" s="13" t="n">
         <v>8</v>
@@ -25748,7 +25748,7 @@
         </is>
       </c>
       <c r="E824" s="13" t="n">
-        <v>14732</v>
+        <v>14731</v>
       </c>
       <c r="F824" s="13" t="n">
         <v>8</v>
@@ -25776,7 +25776,7 @@
         </is>
       </c>
       <c r="E825" s="13" t="n">
-        <v>14742</v>
+        <v>14741</v>
       </c>
       <c r="F825" s="13" t="n">
         <v>8</v>
@@ -25804,7 +25804,7 @@
         </is>
       </c>
       <c r="E826" s="13" t="n">
-        <v>14753</v>
+        <v>14752</v>
       </c>
       <c r="F826" s="13" t="n">
         <v>8</v>
@@ -25832,7 +25832,7 @@
         </is>
       </c>
       <c r="E827" s="13" t="n">
-        <v>14763</v>
+        <v>14762</v>
       </c>
       <c r="F827" s="13" t="n">
         <v>6</v>
@@ -25860,7 +25860,7 @@
         </is>
       </c>
       <c r="E828" s="13" t="n">
-        <v>14772</v>
+        <v>14771</v>
       </c>
       <c r="F828" s="13" t="n">
         <v>7</v>
@@ -25888,7 +25888,7 @@
         </is>
       </c>
       <c r="E829" s="13" t="n">
-        <v>14781</v>
+        <v>14780</v>
       </c>
       <c r="F829" s="13" t="n">
         <v>8</v>
@@ -25916,7 +25916,7 @@
         </is>
       </c>
       <c r="E830" s="13" t="n">
-        <v>14792</v>
+        <v>14791</v>
       </c>
       <c r="F830" s="13" t="n">
         <v>8</v>
@@ -25944,7 +25944,7 @@
         </is>
       </c>
       <c r="E831" s="13" t="n">
-        <v>14802</v>
+        <v>14801</v>
       </c>
       <c r="F831" s="13" t="n">
         <v>9</v>
@@ -25972,7 +25972,7 @@
         </is>
       </c>
       <c r="E832" s="13" t="n">
-        <v>14814</v>
+        <v>14813</v>
       </c>
       <c r="F832" s="13" t="n">
         <v>7</v>
@@ -26000,7 +26000,7 @@
         </is>
       </c>
       <c r="E833" s="13" t="n">
-        <v>14823</v>
+        <v>14822</v>
       </c>
       <c r="F833" s="13" t="n">
         <v>9</v>
@@ -26028,7 +26028,7 @@
         </is>
       </c>
       <c r="E834" s="13" t="n">
-        <v>14835</v>
+        <v>14834</v>
       </c>
       <c r="F834" s="13" t="n">
         <v>8</v>
@@ -26056,7 +26056,7 @@
         </is>
       </c>
       <c r="E835" s="13" t="n">
-        <v>14845</v>
+        <v>14844</v>
       </c>
       <c r="F835" s="13" t="n">
         <v>6</v>
@@ -26084,7 +26084,7 @@
         </is>
       </c>
       <c r="E836" s="13" t="n">
-        <v>14854</v>
+        <v>14853</v>
       </c>
       <c r="F836" s="13" t="n">
         <v>8</v>
@@ -26112,7 +26112,7 @@
         </is>
       </c>
       <c r="E837" s="13" t="n">
-        <v>14864</v>
+        <v>14863</v>
       </c>
       <c r="F837" s="13" t="n">
         <v>9</v>
@@ -26140,7 +26140,7 @@
         </is>
       </c>
       <c r="E838" s="13" t="n">
-        <v>14876</v>
+        <v>14875</v>
       </c>
       <c r="F838" s="13" t="n">
         <v>7</v>
@@ -26168,7 +26168,7 @@
         </is>
       </c>
       <c r="E839" s="13" t="n">
-        <v>14885</v>
+        <v>14884</v>
       </c>
       <c r="F839" s="13" t="n">
         <v>8</v>
@@ -26196,7 +26196,7 @@
         </is>
       </c>
       <c r="E840" s="13" t="n">
-        <v>14896</v>
+        <v>14895</v>
       </c>
       <c r="F840" s="13" t="n">
         <v>7</v>
@@ -26224,7 +26224,7 @@
         </is>
       </c>
       <c r="E841" s="13" t="n">
-        <v>14905</v>
+        <v>14904</v>
       </c>
       <c r="F841" s="13" t="n">
         <v>7</v>
@@ -26252,7 +26252,7 @@
         </is>
       </c>
       <c r="E842" s="13" t="n">
-        <v>14915</v>
+        <v>14914</v>
       </c>
       <c r="F842" s="13" t="n">
         <v>8</v>
@@ -26280,7 +26280,7 @@
         </is>
       </c>
       <c r="E843" s="13" t="n">
-        <v>14925</v>
+        <v>14924</v>
       </c>
       <c r="F843" s="13" t="n">
         <v>9</v>
@@ -26308,7 +26308,7 @@
         </is>
       </c>
       <c r="E844" s="13" t="n">
-        <v>14937</v>
+        <v>14936</v>
       </c>
       <c r="F844" s="13" t="n">
         <v>8</v>
@@ -26336,7 +26336,7 @@
         </is>
       </c>
       <c r="E845" s="13" t="n">
-        <v>14947</v>
+        <v>14946</v>
       </c>
       <c r="F845" s="13" t="n">
         <v>6</v>
@@ -26364,7 +26364,7 @@
         </is>
       </c>
       <c r="E846" s="13" t="n">
-        <v>14956</v>
+        <v>14955</v>
       </c>
       <c r="F846" s="13" t="n">
         <v>7</v>
@@ -26392,7 +26392,7 @@
         </is>
       </c>
       <c r="E847" s="13" t="n">
-        <v>14965</v>
+        <v>14964</v>
       </c>
       <c r="F847" s="13" t="n">
         <v>8</v>
@@ -26420,7 +26420,7 @@
         </is>
       </c>
       <c r="E848" s="13" t="n">
-        <v>14975</v>
+        <v>14974</v>
       </c>
       <c r="F848" s="13" t="n">
         <v>7</v>
@@ -26448,7 +26448,7 @@
         </is>
       </c>
       <c r="E849" s="13" t="n">
-        <v>14984</v>
+        <v>14983</v>
       </c>
       <c r="F849" s="13" t="n">
         <v>8</v>
@@ -26476,7 +26476,7 @@
         </is>
       </c>
       <c r="E850" s="13" t="n">
-        <v>14994</v>
+        <v>14993</v>
       </c>
       <c r="F850" s="13" t="n">
         <v>8</v>
@@ -26504,7 +26504,7 @@
         </is>
       </c>
       <c r="E851" s="13" t="n">
-        <v>15005</v>
+        <v>15004</v>
       </c>
       <c r="F851" s="13" t="n">
         <v>7</v>
@@ -26532,7 +26532,7 @@
         </is>
       </c>
       <c r="E852" s="13" t="n">
-        <v>15014</v>
+        <v>15013</v>
       </c>
       <c r="F852" s="13" t="n">
         <v>7</v>
@@ -26560,7 +26560,7 @@
         </is>
       </c>
       <c r="E853" s="13" t="n">
-        <v>15024</v>
+        <v>15023</v>
       </c>
       <c r="F853" s="13" t="n">
         <v>7</v>
@@ -26588,7 +26588,7 @@
         </is>
       </c>
       <c r="E854" s="13" t="n">
-        <v>15033</v>
+        <v>15032</v>
       </c>
       <c r="F854" s="13" t="n">
         <v>8</v>
@@ -26616,7 +26616,7 @@
         </is>
       </c>
       <c r="E855" s="13" t="n">
-        <v>15044</v>
+        <v>15043</v>
       </c>
       <c r="F855" s="13" t="n">
         <v>8</v>
@@ -26644,7 +26644,7 @@
         </is>
       </c>
       <c r="E856" s="13" t="n">
-        <v>15054</v>
+        <v>15053</v>
       </c>
       <c r="F856" s="13" t="n">
         <v>8</v>
@@ -26672,7 +26672,7 @@
         </is>
       </c>
       <c r="E857" s="13" t="n">
-        <v>15065</v>
+        <v>15064</v>
       </c>
       <c r="F857" s="13" t="n">
         <v>8</v>
@@ -26700,7 +26700,7 @@
         </is>
       </c>
       <c r="E858" s="13" t="n">
-        <v>15075</v>
+        <v>15074</v>
       </c>
       <c r="F858" s="13" t="n">
         <v>9</v>
@@ -26728,7 +26728,7 @@
         </is>
       </c>
       <c r="E859" s="13" t="n">
-        <v>15087</v>
+        <v>15086</v>
       </c>
       <c r="F859" s="13" t="n">
         <v>9</v>
@@ -26756,7 +26756,7 @@
         </is>
       </c>
       <c r="E860" s="13" t="n">
-        <v>15098</v>
+        <v>15097</v>
       </c>
       <c r="F860" s="13" t="n">
         <v>9</v>
@@ -26784,7 +26784,7 @@
         </is>
       </c>
       <c r="E861" s="13" t="n">
-        <v>15110</v>
+        <v>15109</v>
       </c>
       <c r="F861" s="13" t="n">
         <v>9</v>
@@ -26812,7 +26812,7 @@
         </is>
       </c>
       <c r="E862" s="13" t="n">
-        <v>15121</v>
+        <v>15120</v>
       </c>
       <c r="F862" s="13" t="n">
         <v>8</v>
@@ -26840,7 +26840,7 @@
         </is>
       </c>
       <c r="E863" s="13" t="n">
-        <v>15132</v>
+        <v>15131</v>
       </c>
       <c r="F863" s="13" t="n">
         <v>7</v>
@@ -26868,7 +26868,7 @@
         </is>
       </c>
       <c r="E864" s="13" t="n">
-        <v>15141</v>
+        <v>15140</v>
       </c>
       <c r="F864" s="13" t="n">
         <v>8</v>
@@ -26896,7 +26896,7 @@
         </is>
       </c>
       <c r="E865" s="13" t="n">
-        <v>15152</v>
+        <v>15151</v>
       </c>
       <c r="F865" s="13" t="n">
         <v>7</v>
@@ -26924,7 +26924,7 @@
         </is>
       </c>
       <c r="E866" s="13" t="n">
-        <v>15161</v>
+        <v>15160</v>
       </c>
       <c r="F866" s="13" t="n">
         <v>7</v>
@@ -26952,7 +26952,7 @@
         </is>
       </c>
       <c r="E867" s="13" t="n">
-        <v>15170</v>
+        <v>15169</v>
       </c>
       <c r="F867" s="13" t="n">
         <v>6</v>
@@ -26980,7 +26980,7 @@
         </is>
       </c>
       <c r="E868" s="13" t="n">
-        <v>15179</v>
+        <v>15178</v>
       </c>
       <c r="F868" s="13" t="n">
         <v>5</v>
@@ -27008,7 +27008,7 @@
         </is>
       </c>
       <c r="E869" s="13" t="n">
-        <v>15186</v>
+        <v>15185</v>
       </c>
       <c r="F869" s="13" t="n">
         <v>7</v>
@@ -27036,7 +27036,7 @@
         </is>
       </c>
       <c r="E870" s="13" t="n">
-        <v>15195</v>
+        <v>15194</v>
       </c>
       <c r="F870" s="13" t="n">
         <v>6</v>
@@ -27064,7 +27064,7 @@
         </is>
       </c>
       <c r="E871" s="13" t="n">
-        <v>15204</v>
+        <v>15203</v>
       </c>
       <c r="F871" s="13" t="n">
         <v>7</v>
@@ -27092,7 +27092,7 @@
         </is>
       </c>
       <c r="E872" s="13" t="n">
-        <v>15213</v>
+        <v>15212</v>
       </c>
       <c r="F872" s="13" t="n">
         <v>8</v>
@@ -27120,7 +27120,7 @@
         </is>
       </c>
       <c r="E873" s="13" t="n">
-        <v>15224</v>
+        <v>15223</v>
       </c>
       <c r="F873" s="13" t="n">
         <v>7</v>
@@ -27148,7 +27148,7 @@
         </is>
       </c>
       <c r="E874" s="13" t="n">
-        <v>15233</v>
+        <v>15232</v>
       </c>
       <c r="F874" s="13" t="n">
         <v>14</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="E875" s="13" t="n">
-        <v>15250</v>
+        <v>15249</v>
       </c>
       <c r="F875" s="13" t="n">
         <v>7</v>
@@ -27204,7 +27204,7 @@
         </is>
       </c>
       <c r="E876" s="13" t="n">
-        <v>15259</v>
+        <v>15258</v>
       </c>
       <c r="F876" s="13" t="n">
         <v>8</v>
@@ -27232,7 +27232,7 @@
         </is>
       </c>
       <c r="E877" s="13" t="n">
-        <v>15270</v>
+        <v>15269</v>
       </c>
       <c r="F877" s="13" t="n">
         <v>6</v>
@@ -27260,7 +27260,7 @@
         </is>
       </c>
       <c r="E878" s="13" t="n">
-        <v>15278</v>
+        <v>15277</v>
       </c>
       <c r="F878" s="13" t="n">
         <v>7</v>
@@ -27288,7 +27288,7 @@
         </is>
       </c>
       <c r="E879" s="13" t="n">
-        <v>15287</v>
+        <v>15286</v>
       </c>
       <c r="F879" s="13" t="n">
         <v>5</v>
@@ -27316,7 +27316,7 @@
         </is>
       </c>
       <c r="E880" s="13" t="n">
-        <v>15295</v>
+        <v>15294</v>
       </c>
       <c r="F880" s="13" t="n">
         <v>7</v>
@@ -27344,7 +27344,7 @@
         </is>
       </c>
       <c r="E881" s="13" t="n">
-        <v>15304</v>
+        <v>15303</v>
       </c>
       <c r="F881" s="13" t="n">
         <v>7</v>
@@ -27372,7 +27372,7 @@
         </is>
       </c>
       <c r="E882" s="13" t="n">
-        <v>15314</v>
+        <v>15313</v>
       </c>
       <c r="F882" s="13" t="n">
         <v>8</v>
@@ -27400,7 +27400,7 @@
         </is>
       </c>
       <c r="E883" s="13" t="n">
-        <v>15324</v>
+        <v>15323</v>
       </c>
       <c r="F883" s="13" t="n">
         <v>8</v>
@@ -27428,7 +27428,7 @@
         </is>
       </c>
       <c r="E884" s="13" t="n">
-        <v>15335</v>
+        <v>15334</v>
       </c>
       <c r="F884" s="13" t="n">
         <v>7</v>
@@ -27456,7 +27456,7 @@
         </is>
       </c>
       <c r="E885" s="13" t="n">
-        <v>15344</v>
+        <v>15343</v>
       </c>
       <c r="F885" s="13" t="n">
         <v>7</v>
@@ -27484,7 +27484,7 @@
         </is>
       </c>
       <c r="E886" s="13" t="n">
-        <v>15353</v>
+        <v>15352</v>
       </c>
       <c r="F886" s="13" t="n">
         <v>7</v>
@@ -27512,7 +27512,7 @@
         </is>
       </c>
       <c r="E887" s="13" t="n">
-        <v>15362</v>
+        <v>15361</v>
       </c>
       <c r="F887" s="13" t="n">
         <v>5</v>
@@ -27540,7 +27540,7 @@
         </is>
       </c>
       <c r="E888" s="13" t="n">
-        <v>15369</v>
+        <v>15368</v>
       </c>
       <c r="F888" s="13" t="n">
         <v>15</v>
@@ -27568,7 +27568,7 @@
         </is>
       </c>
       <c r="E889" s="13" t="n">
-        <v>15387</v>
+        <v>15386</v>
       </c>
       <c r="F889" s="13" t="n">
         <v>15</v>
@@ -27596,7 +27596,7 @@
         </is>
       </c>
       <c r="E890" s="13" t="n">
-        <v>15405</v>
+        <v>15404</v>
       </c>
       <c r="F890" s="13" t="n">
         <v>8</v>
@@ -27624,7 +27624,7 @@
         </is>
       </c>
       <c r="E891" s="13" t="n">
-        <v>15415</v>
+        <v>15414</v>
       </c>
       <c r="F891" s="13" t="n">
         <v>7</v>
@@ -27652,7 +27652,7 @@
         </is>
       </c>
       <c r="E892" s="13" t="n">
-        <v>15425</v>
+        <v>15424</v>
       </c>
       <c r="F892" s="13" t="n">
         <v>6</v>
@@ -27680,7 +27680,7 @@
         </is>
       </c>
       <c r="E893" s="13" t="n">
-        <v>15433</v>
+        <v>15432</v>
       </c>
       <c r="F893" s="13" t="n">
         <v>6</v>
@@ -27708,7 +27708,7 @@
         </is>
       </c>
       <c r="E894" s="13" t="n">
-        <v>15441</v>
+        <v>15440</v>
       </c>
       <c r="F894" s="13" t="n">
         <v>7</v>
@@ -27736,7 +27736,7 @@
         </is>
       </c>
       <c r="E895" s="13" t="n">
-        <v>15451</v>
+        <v>15450</v>
       </c>
       <c r="F895" s="13" t="n">
         <v>4</v>
@@ -27764,7 +27764,7 @@
         </is>
       </c>
       <c r="E896" s="13" t="n">
-        <v>15457</v>
+        <v>15456</v>
       </c>
       <c r="F896" s="13" t="n">
         <v>6</v>
@@ -27792,7 +27792,7 @@
         </is>
       </c>
       <c r="E897" s="13" t="n">
-        <v>15465</v>
+        <v>15464</v>
       </c>
       <c r="F897" s="13" t="n">
         <v>7</v>
@@ -27820,7 +27820,7 @@
         </is>
       </c>
       <c r="E898" s="13" t="n">
-        <v>15475</v>
+        <v>15474</v>
       </c>
       <c r="F898" s="13" t="n">
         <v>6</v>
@@ -27848,7 +27848,7 @@
         </is>
       </c>
       <c r="E899" s="13" t="n">
-        <v>15483</v>
+        <v>15482</v>
       </c>
       <c r="F899" s="13" t="n">
         <v>9</v>
@@ -27876,7 +27876,7 @@
         </is>
       </c>
       <c r="E900" s="13" t="n">
-        <v>15495</v>
+        <v>15494</v>
       </c>
       <c r="F900" s="13" t="n">
         <v>6</v>
@@ -27904,7 +27904,7 @@
         </is>
       </c>
       <c r="E901" s="13" t="n">
-        <v>15503</v>
+        <v>15502</v>
       </c>
       <c r="F901" s="13" t="n">
         <v>7</v>
@@ -27932,7 +27932,7 @@
         </is>
       </c>
       <c r="E902" s="13" t="n">
-        <v>15512</v>
+        <v>15511</v>
       </c>
       <c r="F902" s="13" t="n">
         <v>6</v>
@@ -27960,7 +27960,7 @@
         </is>
       </c>
       <c r="E903" s="13" t="n">
-        <v>15520</v>
+        <v>15519</v>
       </c>
       <c r="F903" s="13" t="n">
         <v>6</v>
@@ -27988,7 +27988,7 @@
         </is>
       </c>
       <c r="E904" s="13" t="n">
-        <v>15528</v>
+        <v>15527</v>
       </c>
       <c r="F904" s="13" t="n">
         <v>7</v>
@@ -28016,7 +28016,7 @@
         </is>
       </c>
       <c r="E905" s="13" t="n">
-        <v>15538</v>
+        <v>15537</v>
       </c>
       <c r="F905" s="13" t="n">
         <v>7</v>
@@ -28044,7 +28044,7 @@
         </is>
       </c>
       <c r="E906" s="13" t="n">
-        <v>15547</v>
+        <v>15546</v>
       </c>
       <c r="F906" s="13" t="n">
         <v>7</v>
@@ -28072,7 +28072,7 @@
         </is>
       </c>
       <c r="E907" s="13" t="n">
-        <v>15556</v>
+        <v>15555</v>
       </c>
       <c r="F907" s="13" t="n">
         <v>7</v>
@@ -28100,7 +28100,7 @@
         </is>
       </c>
       <c r="E908" s="13" t="n">
-        <v>15565</v>
+        <v>15564</v>
       </c>
       <c r="F908" s="13" t="n">
         <v>7</v>
@@ -28128,7 +28128,7 @@
         </is>
       </c>
       <c r="E909" s="13" t="n">
-        <v>15574</v>
+        <v>15573</v>
       </c>
       <c r="F909" s="13" t="n">
         <v>5</v>
@@ -28156,7 +28156,7 @@
         </is>
       </c>
       <c r="E910" s="13" t="n">
-        <v>15582</v>
+        <v>15581</v>
       </c>
       <c r="F910" s="13" t="n">
         <v>5</v>
@@ -28184,7 +28184,7 @@
         </is>
       </c>
       <c r="E911" s="13" t="n">
-        <v>15589</v>
+        <v>15588</v>
       </c>
       <c r="F911" s="13" t="n">
         <v>5</v>
@@ -28212,7 +28212,7 @@
         </is>
       </c>
       <c r="E912" s="13" t="n">
-        <v>15597</v>
+        <v>15596</v>
       </c>
       <c r="F912" s="13" t="n">
         <v>6</v>
@@ -28240,7 +28240,7 @@
         </is>
       </c>
       <c r="E913" s="13" t="n">
-        <v>15605</v>
+        <v>15604</v>
       </c>
       <c r="F913" s="13" t="n">
         <v>7</v>
@@ -28268,7 +28268,7 @@
         </is>
       </c>
       <c r="E914" s="13" t="n">
-        <v>15614</v>
+        <v>15613</v>
       </c>
       <c r="F914" s="13" t="n">
         <v>6</v>
@@ -28296,7 +28296,7 @@
         </is>
       </c>
       <c r="E915" s="13" t="n">
-        <v>15622</v>
+        <v>15621</v>
       </c>
       <c r="F915" s="13" t="n">
         <v>7</v>
@@ -28324,7 +28324,7 @@
         </is>
       </c>
       <c r="E916" s="13" t="n">
-        <v>15631</v>
+        <v>15630</v>
       </c>
       <c r="F916" s="13" t="n">
         <v>8</v>
@@ -28352,7 +28352,7 @@
         </is>
       </c>
       <c r="E917" s="13" t="n">
-        <v>15642</v>
+        <v>15641</v>
       </c>
       <c r="F917" s="13" t="n">
         <v>7</v>
@@ -28380,7 +28380,7 @@
         </is>
       </c>
       <c r="E918" s="13" t="n">
-        <v>15651</v>
+        <v>15650</v>
       </c>
       <c r="F918" s="13" t="n">
         <v>6</v>
@@ -28408,7 +28408,7 @@
         </is>
       </c>
       <c r="E919" s="13" t="n">
-        <v>15660</v>
+        <v>15659</v>
       </c>
       <c r="F919" s="13" t="n">
         <v>7</v>
@@ -28436,7 +28436,7 @@
         </is>
       </c>
       <c r="E920" s="13" t="n">
-        <v>15669</v>
+        <v>15668</v>
       </c>
       <c r="F920" s="13" t="n">
         <v>6</v>
@@ -28464,7 +28464,7 @@
         </is>
       </c>
       <c r="E921" s="13" t="n">
-        <v>15677</v>
+        <v>15676</v>
       </c>
       <c r="F921" s="13" t="n">
         <v>7</v>
@@ -28492,7 +28492,7 @@
         </is>
       </c>
       <c r="E922" s="13" t="n">
-        <v>15687</v>
+        <v>15686</v>
       </c>
       <c r="F922" s="13" t="n">
         <v>7</v>
@@ -28520,7 +28520,7 @@
         </is>
       </c>
       <c r="E923" s="13" t="n">
-        <v>15696</v>
+        <v>15695</v>
       </c>
       <c r="F923" s="13" t="n">
         <v>3</v>
@@ -28548,7 +28548,7 @@
         </is>
       </c>
       <c r="E924" s="13" t="n">
-        <v>15702</v>
+        <v>15701</v>
       </c>
       <c r="F924" s="13" t="n">
         <v>2</v>
@@ -28576,7 +28576,7 @@
         </is>
       </c>
       <c r="E925" s="13" t="n">
-        <v>15706</v>
+        <v>15705</v>
       </c>
       <c r="F925" s="13" t="n">
         <v>5</v>
@@ -28604,7 +28604,7 @@
         </is>
       </c>
       <c r="E926" s="13" t="n">
-        <v>15713</v>
+        <v>15712</v>
       </c>
       <c r="F926" s="13" t="n">
         <v>13</v>
@@ -28632,7 +28632,7 @@
         </is>
       </c>
       <c r="E927" s="13" t="n">
-        <v>15729</v>
+        <v>15728</v>
       </c>
       <c r="F927" s="13" t="n">
         <v>24</v>
@@ -28660,7 +28660,7 @@
         </is>
       </c>
       <c r="E928" s="13" t="n">
-        <v>15756</v>
+        <v>15755</v>
       </c>
       <c r="F928" s="13" t="n">
         <v>23</v>
@@ -28688,7 +28688,7 @@
         </is>
       </c>
       <c r="E929" s="13" t="n">
-        <v>15783</v>
+        <v>15782</v>
       </c>
       <c r="F929" s="13" t="n">
         <v>19</v>
@@ -28716,7 +28716,7 @@
         </is>
       </c>
       <c r="E930" s="13" t="n">
-        <v>15805</v>
+        <v>15804</v>
       </c>
       <c r="F930" s="13" t="n">
         <v>18</v>
@@ -28744,7 +28744,7 @@
         </is>
       </c>
       <c r="E931" s="13" t="n">
-        <v>15826</v>
+        <v>15825</v>
       </c>
       <c r="F931" s="13" t="n">
         <v>19</v>

--- a/알바로_부작_화_목록.xlsx
+++ b/알바로_부작_화_목록.xlsx
@@ -568,11 +568,11 @@
         <v>7</v>
       </c>
       <c r="F2" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A2)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A2)</f>
         <v/>
       </c>
       <c r="G2" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A2,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A2,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H2" s="15" t="inlineStr">
@@ -603,11 +603,11 @@
         <v>13</v>
       </c>
       <c r="F3" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A3)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A3)</f>
         <v/>
       </c>
       <c r="G3" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A3,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A3,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H3" s="15" t="inlineStr">
@@ -638,11 +638,11 @@
         <v>25</v>
       </c>
       <c r="F4" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A4)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A4)</f>
         <v/>
       </c>
       <c r="G4" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A4,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A4,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H4" s="15" t="inlineStr">
@@ -673,11 +673,11 @@
         <v>52</v>
       </c>
       <c r="F5" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A5)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A5)</f>
         <v/>
       </c>
       <c r="G5" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A5,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A5,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H5" s="17" t="inlineStr">
@@ -708,11 +708,11 @@
         <v>61</v>
       </c>
       <c r="F6" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A6)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A6)</f>
         <v/>
       </c>
       <c r="G6" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A6,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A6,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H6" s="15" t="inlineStr">
@@ -743,11 +743,11 @@
         <v>85</v>
       </c>
       <c r="F7" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A7)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A7)</f>
         <v/>
       </c>
       <c r="G7" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A7,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A7,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H7" s="10" t="inlineStr">
@@ -777,11 +777,11 @@
         <v>90</v>
       </c>
       <c r="F8" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A8)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A8)</f>
         <v/>
       </c>
       <c r="G8" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A8,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A8,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H8" s="15" t="inlineStr">
@@ -812,11 +812,11 @@
         <v>119</v>
       </c>
       <c r="F9" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A9)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A9)</f>
         <v/>
       </c>
       <c r="G9" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A9,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A9,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H9" s="15" t="inlineStr">
@@ -847,11 +847,11 @@
         <v>141</v>
       </c>
       <c r="F10" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A10)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A10)</f>
         <v/>
       </c>
       <c r="G10" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A10,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A10,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H10" s="15" t="inlineStr">
@@ -886,11 +886,11 @@
         <v>148</v>
       </c>
       <c r="F11" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A11)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A11)</f>
         <v/>
       </c>
       <c r="G11" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A11,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A11,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H11" s="15" t="inlineStr">
@@ -921,11 +921,11 @@
         <v>157</v>
       </c>
       <c r="F12" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A12)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A12)</f>
         <v/>
       </c>
       <c r="G12" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A12,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A12,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H12" s="15" t="inlineStr">
@@ -960,11 +960,11 @@
         <v>165</v>
       </c>
       <c r="F13" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A13)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A13)</f>
         <v/>
       </c>
       <c r="G13" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A13,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A13,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H13" s="15" t="inlineStr">
@@ -995,11 +995,11 @@
         <v>173</v>
       </c>
       <c r="F14" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A14)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A14)</f>
         <v/>
       </c>
       <c r="G14" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A14,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A14,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H14" s="15" t="inlineStr">
@@ -1034,11 +1034,11 @@
         <v>180</v>
       </c>
       <c r="F15" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A15)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A15)</f>
         <v/>
       </c>
       <c r="G15" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A15,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A15,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H15" s="17" t="inlineStr">
@@ -1069,11 +1069,11 @@
         <v>186</v>
       </c>
       <c r="F16" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A16)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A16)</f>
         <v/>
       </c>
       <c r="G16" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A16,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A16,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H16" s="15" t="inlineStr">
@@ -1104,11 +1104,11 @@
         <v>192</v>
       </c>
       <c r="F17" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A17)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A17)</f>
         <v/>
       </c>
       <c r="G17" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A17,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A17,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H17" s="15" t="inlineStr">
@@ -1139,11 +1139,11 @@
         <v>195</v>
       </c>
       <c r="F18" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A18)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A18)</f>
         <v/>
       </c>
       <c r="G18" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A18,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A18,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H18" s="15" t="inlineStr">
@@ -1174,11 +1174,11 @@
         <v>200</v>
       </c>
       <c r="F19" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A19)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A19)</f>
         <v/>
       </c>
       <c r="G19" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A19,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A19,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H19" s="15" t="inlineStr">
@@ -1209,11 +1209,11 @@
         <v>207</v>
       </c>
       <c r="F20" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A20)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A20)</f>
         <v/>
       </c>
       <c r="G20" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A20,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A20,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H20" s="15" t="inlineStr">
@@ -1244,11 +1244,11 @@
         <v>223</v>
       </c>
       <c r="F21" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A21)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A21)</f>
         <v/>
       </c>
       <c r="G21" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A21,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A21,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H21" s="15" t="inlineStr">
@@ -1279,11 +1279,11 @@
         <v>229</v>
       </c>
       <c r="F22" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A22)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A22)</f>
         <v/>
       </c>
       <c r="G22" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A22,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A22,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H22" s="15" t="inlineStr">
@@ -1314,11 +1314,11 @@
         <v>246</v>
       </c>
       <c r="F23" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A23)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A23)</f>
         <v/>
       </c>
       <c r="G23" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A23,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A23,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H23" s="15" t="inlineStr">
@@ -1349,11 +1349,11 @@
         <v>272</v>
       </c>
       <c r="F24" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A24)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A24)</f>
         <v/>
       </c>
       <c r="G24" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A24,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A24,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H24" s="15" t="inlineStr">
@@ -1384,11 +1384,11 @@
         <v>298</v>
       </c>
       <c r="F25" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A25)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A25)</f>
         <v/>
       </c>
       <c r="G25" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A25,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A25,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H25" s="17" t="inlineStr">
@@ -1419,11 +1419,11 @@
         <v>326</v>
       </c>
       <c r="F26" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A26)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A26)</f>
         <v/>
       </c>
       <c r="G26" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A26,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A26,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H26" s="15" t="inlineStr">
@@ -1454,11 +1454,11 @@
         <v>359</v>
       </c>
       <c r="F27" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A27)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A27)</f>
         <v/>
       </c>
       <c r="G27" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A27,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A27,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H27" s="15" t="inlineStr">
@@ -1493,11 +1493,11 @@
         <v>443</v>
       </c>
       <c r="F28" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A28)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A28)</f>
         <v/>
       </c>
       <c r="G28" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A28,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A28,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H28" s="15" t="inlineStr">
@@ -1532,11 +1532,11 @@
         <v>468</v>
       </c>
       <c r="F29" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A29)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A29)</f>
         <v/>
       </c>
       <c r="G29" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A29,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A29,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H29" s="15" t="inlineStr">
@@ -1567,11 +1567,11 @@
         <v>478</v>
       </c>
       <c r="F30" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A30)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A30)</f>
         <v/>
       </c>
       <c r="G30" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A30,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A30,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H30" s="15" t="inlineStr">
@@ -1602,11 +1602,11 @@
         <v>487</v>
       </c>
       <c r="F31" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A31)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A31)</f>
         <v/>
       </c>
       <c r="G31" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A31,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A31,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H31" s="15" t="inlineStr">
@@ -1637,11 +1637,11 @@
         <v>492</v>
       </c>
       <c r="F32" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A32)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A32)</f>
         <v/>
       </c>
       <c r="G32" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A32,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A32,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H32" s="15" t="inlineStr">
@@ -1672,11 +1672,11 @@
         <v>506</v>
       </c>
       <c r="F33" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A33)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A33)</f>
         <v/>
       </c>
       <c r="G33" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A33,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A33,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H33" s="15" t="inlineStr">
@@ -1707,11 +1707,11 @@
         <v>532</v>
       </c>
       <c r="F34" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A34)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A34)</f>
         <v/>
       </c>
       <c r="G34" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A34,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A34,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H34" s="15" t="inlineStr">
@@ -1742,11 +1742,11 @@
         <v>542</v>
       </c>
       <c r="F35" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A35)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A35)</f>
         <v/>
       </c>
       <c r="G35" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A35,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A35,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H35" s="15" t="inlineStr">
@@ -1777,11 +1777,11 @@
         <v>569</v>
       </c>
       <c r="F36" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A36)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A36)</f>
         <v/>
       </c>
       <c r="G36" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A36,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A36,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H36" s="15" t="inlineStr">
@@ -1812,11 +1812,11 @@
         <v>580</v>
       </c>
       <c r="F37" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A37)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A37)</f>
         <v/>
       </c>
       <c r="G37" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A37,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A37,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H37" s="15" t="inlineStr">
@@ -1847,11 +1847,11 @@
         <v>597</v>
       </c>
       <c r="F38" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A38)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A38)</f>
         <v/>
       </c>
       <c r="G38" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A38,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A38,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H38" s="15" t="inlineStr">
@@ -1882,11 +1882,11 @@
         <v>636</v>
       </c>
       <c r="F39" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A39)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A39)</f>
         <v/>
       </c>
       <c r="G39" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A39,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A39,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H39" s="15" t="inlineStr">
@@ -1917,11 +1917,11 @@
         <v>640</v>
       </c>
       <c r="F40" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A40)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A40)</f>
         <v/>
       </c>
       <c r="G40" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A40,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A40,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H40" s="15" t="inlineStr">
@@ -1952,11 +1952,11 @@
         <v>643</v>
       </c>
       <c r="F41" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A41)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A41)</f>
         <v/>
       </c>
       <c r="G41" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A41,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A41,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H41" s="15" t="inlineStr">
@@ -1987,11 +1987,11 @@
         <v>653</v>
       </c>
       <c r="F42" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A42)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A42)</f>
         <v/>
       </c>
       <c r="G42" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A42,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A42,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H42" s="15" t="inlineStr">
@@ -2022,11 +2022,11 @@
         <v>655</v>
       </c>
       <c r="F43" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A43)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A43)</f>
         <v/>
       </c>
       <c r="G43" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A43,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A43,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H43" s="15" t="inlineStr">
@@ -2057,11 +2057,11 @@
         <v>661</v>
       </c>
       <c r="F44" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A44)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A44)</f>
         <v/>
       </c>
       <c r="G44" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A44,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A44,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H44" s="15" t="inlineStr">
@@ -2092,11 +2092,11 @@
         <v>672</v>
       </c>
       <c r="F45" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A45)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A45)</f>
         <v/>
       </c>
       <c r="G45" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A45,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A45,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H45" s="15" t="inlineStr">
@@ -2127,11 +2127,11 @@
         <v>683</v>
       </c>
       <c r="F46" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A46)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A46)</f>
         <v/>
       </c>
       <c r="G46" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A46,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A46,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H46" s="15" t="inlineStr">
@@ -2162,11 +2162,11 @@
         <v>693</v>
       </c>
       <c r="F47" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A47)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A47)</f>
         <v/>
       </c>
       <c r="G47" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A47,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A47,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H47" s="15" t="inlineStr">
@@ -2197,11 +2197,11 @@
         <v>704</v>
       </c>
       <c r="F48" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A48)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A48)</f>
         <v/>
       </c>
       <c r="G48" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A48,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A48,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H48" s="15" t="inlineStr">
@@ -2232,11 +2232,11 @@
         <v>720</v>
       </c>
       <c r="F49" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A49)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A49)</f>
         <v/>
       </c>
       <c r="G49" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A49,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A49,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H49" s="15" t="inlineStr">
@@ -2267,11 +2267,11 @@
         <v>734</v>
       </c>
       <c r="F50" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A50)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A50)</f>
         <v/>
       </c>
       <c r="G50" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A50,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A50,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H50" s="15" t="inlineStr">
@@ -2302,11 +2302,11 @@
         <v>759</v>
       </c>
       <c r="F51" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A51)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A51)</f>
         <v/>
       </c>
       <c r="G51" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A51,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A51,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H51" s="15" t="inlineStr">
@@ -2337,11 +2337,11 @@
         <v>784</v>
       </c>
       <c r="F52" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A52)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A52)</f>
         <v/>
       </c>
       <c r="G52" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A52,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A52,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H52" s="15" t="inlineStr">
@@ -2372,11 +2372,11 @@
         <v>806</v>
       </c>
       <c r="F53" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A53)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A53)</f>
         <v/>
       </c>
       <c r="G53" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A53,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A53,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H53" s="15" t="inlineStr">
@@ -2407,11 +2407,11 @@
         <v>826</v>
       </c>
       <c r="F54" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A54)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A54)</f>
         <v/>
       </c>
       <c r="G54" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A54,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A54,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H54" s="15" t="inlineStr">
@@ -2442,11 +2442,11 @@
         <v>846</v>
       </c>
       <c r="F55" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A55)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A55)</f>
         <v/>
       </c>
       <c r="G55" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A55,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A55,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H55" s="15" t="inlineStr">
@@ -2477,11 +2477,11 @@
         <v>871</v>
       </c>
       <c r="F56" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A56)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A56)</f>
         <v/>
       </c>
       <c r="G56" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A56,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A56,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H56" s="15" t="inlineStr">
@@ -2512,11 +2512,11 @@
         <v>894</v>
       </c>
       <c r="F57" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A57)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A57)</f>
         <v/>
       </c>
       <c r="G57" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A57,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A57,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H57" s="15" t="inlineStr">
@@ -2547,11 +2547,11 @@
         <v>932</v>
       </c>
       <c r="F58" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A58)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A58)</f>
         <v/>
       </c>
       <c r="G58" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A58,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A58,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H58" s="15" t="inlineStr">
@@ -2582,11 +2582,11 @@
         <v>949</v>
       </c>
       <c r="F59" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A59)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A59)</f>
         <v/>
       </c>
       <c r="G59" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A59,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A59,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H59" s="15" t="inlineStr">
@@ -2617,11 +2617,11 @@
         <v>961</v>
       </c>
       <c r="F60" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A60)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A60)</f>
         <v/>
       </c>
       <c r="G60" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A60,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A60,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H60" s="15" t="inlineStr">
@@ -2649,14 +2649,14 @@
         <v>962</v>
       </c>
       <c r="E61" s="16" t="n">
-        <v>966</v>
+        <v>985</v>
       </c>
       <c r="F61" s="13">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A61)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A61)</f>
         <v/>
       </c>
       <c r="G61" s="13">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A61,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A61,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H61" s="15" t="inlineStr">
@@ -2681,17 +2681,17 @@
         </is>
       </c>
       <c r="D62" s="10" t="n">
-        <v>967</v>
+        <v>986</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>986</v>
+        <v>1005</v>
       </c>
       <c r="F62" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A62)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A62)</f>
         <v/>
       </c>
       <c r="G62" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A62,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A62,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H62" s="10" t="inlineStr">
@@ -2715,17 +2715,17 @@
         </is>
       </c>
       <c r="D63" s="10" t="n">
-        <v>987</v>
+        <v>1006</v>
       </c>
       <c r="E63" s="10" t="n">
-        <v>994</v>
+        <v>1013</v>
       </c>
       <c r="F63" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A63)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A63)</f>
         <v/>
       </c>
       <c r="G63" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A63,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A63,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H63" s="10" t="inlineStr">
@@ -2749,17 +2749,17 @@
         </is>
       </c>
       <c r="D64" s="10" t="n">
-        <v>995</v>
+        <v>1014</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>995</v>
+        <v>1014</v>
       </c>
       <c r="F64" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A64)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A64)</f>
         <v/>
       </c>
       <c r="G64" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A64,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A64,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H64" s="10" t="inlineStr">
@@ -2783,17 +2783,17 @@
         </is>
       </c>
       <c r="D65" s="10" t="n">
-        <v>996</v>
+        <v>1015</v>
       </c>
       <c r="E65" s="10" t="n">
-        <v>1003</v>
+        <v>1022</v>
       </c>
       <c r="F65" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A65)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A65)</f>
         <v/>
       </c>
       <c r="G65" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A65,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A65,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H65" s="10" t="inlineStr">
@@ -2817,17 +2817,17 @@
         </is>
       </c>
       <c r="D66" s="10" t="n">
-        <v>1004</v>
+        <v>1023</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>1011</v>
+        <v>1030</v>
       </c>
       <c r="F66" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A66)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A66)</f>
         <v/>
       </c>
       <c r="G66" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A66,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A66,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H66" s="10" t="inlineStr">
@@ -2851,17 +2851,17 @@
         </is>
       </c>
       <c r="D67" s="10" t="n">
-        <v>1012</v>
+        <v>1031</v>
       </c>
       <c r="E67" s="10" t="n">
-        <v>1019</v>
+        <v>1038</v>
       </c>
       <c r="F67" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A67)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A67)</f>
         <v/>
       </c>
       <c r="G67" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A67,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A67,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H67" s="10" t="inlineStr">
@@ -2885,17 +2885,17 @@
         </is>
       </c>
       <c r="D68" s="10" t="n">
-        <v>1020</v>
+        <v>1039</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>1020</v>
+        <v>1039</v>
       </c>
       <c r="F68" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A68)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A68)</f>
         <v/>
       </c>
       <c r="G68" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A68,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A68,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H68" s="10" t="inlineStr">
@@ -2919,17 +2919,17 @@
         </is>
       </c>
       <c r="D69" s="10" t="n">
-        <v>1021</v>
+        <v>1040</v>
       </c>
       <c r="E69" s="10" t="n">
-        <v>1028</v>
+        <v>1047</v>
       </c>
       <c r="F69" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A69)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A69)</f>
         <v/>
       </c>
       <c r="G69" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A69,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A69,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H69" s="10" t="inlineStr">
@@ -2953,17 +2953,17 @@
         </is>
       </c>
       <c r="D70" s="10" t="n">
-        <v>1029</v>
+        <v>1048</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>1036</v>
+        <v>1055</v>
       </c>
       <c r="F70" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A70)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A70)</f>
         <v/>
       </c>
       <c r="G70" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A70,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A70,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H70" s="10" t="inlineStr">
@@ -2987,17 +2987,17 @@
         </is>
       </c>
       <c r="D71" s="10" t="n">
-        <v>1037</v>
+        <v>1056</v>
       </c>
       <c r="E71" s="10" t="n">
-        <v>1041</v>
+        <v>1060</v>
       </c>
       <c r="F71" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A71)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A71)</f>
         <v/>
       </c>
       <c r="G71" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A71,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A71,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H71" s="10" t="inlineStr">
@@ -3021,17 +3021,17 @@
         </is>
       </c>
       <c r="D72" s="10" t="n">
-        <v>1042</v>
+        <v>1061</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>1046</v>
+        <v>1065</v>
       </c>
       <c r="F72" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A72)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A72)</f>
         <v/>
       </c>
       <c r="G72" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A72,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A72,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H72" s="10" t="inlineStr">
@@ -3055,17 +3055,17 @@
         </is>
       </c>
       <c r="D73" s="10" t="n">
-        <v>1047</v>
+        <v>1066</v>
       </c>
       <c r="E73" s="10" t="n">
-        <v>1051</v>
+        <v>1070</v>
       </c>
       <c r="F73" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A73)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A73)</f>
         <v/>
       </c>
       <c r="G73" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A73,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A73,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H73" s="10" t="inlineStr">
@@ -3089,17 +3089,17 @@
         </is>
       </c>
       <c r="D74" s="10" t="n">
-        <v>1052</v>
+        <v>1071</v>
       </c>
       <c r="E74" s="10" t="n">
-        <v>1056</v>
+        <v>1075</v>
       </c>
       <c r="F74" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A74)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A74)</f>
         <v/>
       </c>
       <c r="G74" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A74,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A74,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H74" s="10" t="inlineStr">
@@ -3123,17 +3123,17 @@
         </is>
       </c>
       <c r="D75" s="10" t="n">
-        <v>1057</v>
+        <v>1076</v>
       </c>
       <c r="E75" s="10" t="n">
-        <v>1061</v>
+        <v>1080</v>
       </c>
       <c r="F75" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A75)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A75)</f>
         <v/>
       </c>
       <c r="G75" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A75,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A75,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H75" s="10" t="inlineStr">
@@ -3157,17 +3157,17 @@
         </is>
       </c>
       <c r="D76" s="10" t="n">
-        <v>1062</v>
+        <v>1081</v>
       </c>
       <c r="E76" s="10" t="n">
-        <v>1066</v>
+        <v>1085</v>
       </c>
       <c r="F76" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A76)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A76)</f>
         <v/>
       </c>
       <c r="G76" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A76,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A76,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H76" s="10" t="inlineStr">
@@ -3191,17 +3191,17 @@
         </is>
       </c>
       <c r="D77" s="10" t="n">
-        <v>1067</v>
+        <v>1086</v>
       </c>
       <c r="E77" s="10" t="n">
-        <v>1071</v>
+        <v>1090</v>
       </c>
       <c r="F77" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A77)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A77)</f>
         <v/>
       </c>
       <c r="G77" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A77,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A77,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H77" s="10" t="inlineStr">
@@ -3225,17 +3225,17 @@
         </is>
       </c>
       <c r="D78" s="10" t="n">
-        <v>1072</v>
+        <v>1091</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>1076</v>
+        <v>1095</v>
       </c>
       <c r="F78" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A78)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A78)</f>
         <v/>
       </c>
       <c r="G78" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A78,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A78,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H78" s="10" t="inlineStr">
@@ -3259,17 +3259,17 @@
         </is>
       </c>
       <c r="D79" s="10" t="n">
-        <v>1077</v>
+        <v>1096</v>
       </c>
       <c r="E79" s="10" t="n">
-        <v>1081</v>
+        <v>1100</v>
       </c>
       <c r="F79" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A79)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A79)</f>
         <v/>
       </c>
       <c r="G79" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A79,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A79,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H79" s="10" t="inlineStr">
@@ -3293,17 +3293,17 @@
         </is>
       </c>
       <c r="D80" s="10" t="n">
-        <v>1082</v>
+        <v>1101</v>
       </c>
       <c r="E80" s="10" t="n">
-        <v>1086</v>
+        <v>1105</v>
       </c>
       <c r="F80" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A80)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A80)</f>
         <v/>
       </c>
       <c r="G80" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A80,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A80,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H80" s="10" t="inlineStr">
@@ -3327,17 +3327,17 @@
         </is>
       </c>
       <c r="D81" s="10" t="n">
-        <v>1087</v>
+        <v>1106</v>
       </c>
       <c r="E81" s="10" t="n">
-        <v>1091</v>
+        <v>1110</v>
       </c>
       <c r="F81" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A81)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A81)</f>
         <v/>
       </c>
       <c r="G81" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A81,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A81,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H81" s="10" t="inlineStr">
@@ -3361,17 +3361,17 @@
         </is>
       </c>
       <c r="D82" s="10" t="n">
-        <v>1092</v>
+        <v>1111</v>
       </c>
       <c r="E82" s="10" t="n">
-        <v>1096</v>
+        <v>1115</v>
       </c>
       <c r="F82" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A82)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A82)</f>
         <v/>
       </c>
       <c r="G82" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A82,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A82,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H82" s="10" t="inlineStr">
@@ -3395,17 +3395,17 @@
         </is>
       </c>
       <c r="D83" s="10" t="n">
-        <v>1097</v>
+        <v>1116</v>
       </c>
       <c r="E83" s="10" t="n">
-        <v>1101</v>
+        <v>1120</v>
       </c>
       <c r="F83" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A83)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A83)</f>
         <v/>
       </c>
       <c r="G83" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A83,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A83,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H83" s="10" t="inlineStr">
@@ -3429,17 +3429,17 @@
         </is>
       </c>
       <c r="D84" s="10" t="n">
-        <v>1102</v>
+        <v>1121</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>1106</v>
+        <v>1125</v>
       </c>
       <c r="F84" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A84)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A84)</f>
         <v/>
       </c>
       <c r="G84" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A84,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A84,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H84" s="10" t="inlineStr">
@@ -3463,17 +3463,17 @@
         </is>
       </c>
       <c r="D85" s="10" t="n">
-        <v>1107</v>
+        <v>1126</v>
       </c>
       <c r="E85" s="10" t="n">
-        <v>1111</v>
+        <v>1130</v>
       </c>
       <c r="F85" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A85)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A85)</f>
         <v/>
       </c>
       <c r="G85" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A85,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A85,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H85" s="10" t="inlineStr">
@@ -3497,17 +3497,17 @@
         </is>
       </c>
       <c r="D86" s="10" t="n">
-        <v>1112</v>
+        <v>1131</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>1116</v>
+        <v>1135</v>
       </c>
       <c r="F86" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A86)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A86)</f>
         <v/>
       </c>
       <c r="G86" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A86,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A86,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H86" s="10" t="inlineStr">
@@ -3531,17 +3531,17 @@
         </is>
       </c>
       <c r="D87" s="10" t="n">
-        <v>1117</v>
+        <v>1136</v>
       </c>
       <c r="E87" s="10" t="n">
-        <v>1121</v>
+        <v>1140</v>
       </c>
       <c r="F87" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A87)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A87)</f>
         <v/>
       </c>
       <c r="G87" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A87,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A87,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H87" s="10" t="inlineStr">
@@ -3565,17 +3565,17 @@
         </is>
       </c>
       <c r="D88" s="10" t="n">
-        <v>1122</v>
+        <v>1141</v>
       </c>
       <c r="E88" s="10" t="n">
-        <v>1122</v>
+        <v>1141</v>
       </c>
       <c r="F88" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A88)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A88)</f>
         <v/>
       </c>
       <c r="G88" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A88,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A88,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H88" s="10" t="inlineStr">
@@ -3599,17 +3599,17 @@
         </is>
       </c>
       <c r="D89" s="10" t="n">
-        <v>1123</v>
+        <v>1142</v>
       </c>
       <c r="E89" s="10" t="n">
-        <v>1127</v>
+        <v>1146</v>
       </c>
       <c r="F89" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A89)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A89)</f>
         <v/>
       </c>
       <c r="G89" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A89,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A89,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H89" s="10" t="inlineStr">
@@ -3633,17 +3633,17 @@
         </is>
       </c>
       <c r="D90" s="10" t="n">
-        <v>1128</v>
+        <v>1147</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>1132</v>
+        <v>1151</v>
       </c>
       <c r="F90" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A90)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A90)</f>
         <v/>
       </c>
       <c r="G90" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A90,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A90,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H90" s="10" t="inlineStr">
@@ -3667,17 +3667,17 @@
         </is>
       </c>
       <c r="D91" s="10" t="n">
-        <v>1133</v>
+        <v>1152</v>
       </c>
       <c r="E91" s="10" t="n">
-        <v>1137</v>
+        <v>1156</v>
       </c>
       <c r="F91" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A91)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A91)</f>
         <v/>
       </c>
       <c r="G91" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A91,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A91,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H91" s="10" t="inlineStr">
@@ -3701,17 +3701,17 @@
         </is>
       </c>
       <c r="D92" s="10" t="n">
-        <v>1138</v>
+        <v>1157</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>1142</v>
+        <v>1161</v>
       </c>
       <c r="F92" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A92)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A92)</f>
         <v/>
       </c>
       <c r="G92" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A92,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A92,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H92" s="10" t="inlineStr">
@@ -3735,17 +3735,17 @@
         </is>
       </c>
       <c r="D93" s="10" t="n">
-        <v>1143</v>
+        <v>1162</v>
       </c>
       <c r="E93" s="10" t="n">
-        <v>1147</v>
+        <v>1166</v>
       </c>
       <c r="F93" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A93)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A93)</f>
         <v/>
       </c>
       <c r="G93" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A93,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A93,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H93" s="10" t="inlineStr">
@@ -3769,17 +3769,17 @@
         </is>
       </c>
       <c r="D94" s="10" t="n">
-        <v>1148</v>
+        <v>1167</v>
       </c>
       <c r="E94" s="10" t="n">
-        <v>1148</v>
+        <v>1167</v>
       </c>
       <c r="F94" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A94)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A94)</f>
         <v/>
       </c>
       <c r="G94" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A94,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A94,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H94" s="10" t="inlineStr">
@@ -3803,17 +3803,17 @@
         </is>
       </c>
       <c r="D95" s="10" t="n">
-        <v>1149</v>
+        <v>1168</v>
       </c>
       <c r="E95" s="10" t="n">
-        <v>1153</v>
+        <v>1172</v>
       </c>
       <c r="F95" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A95)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A95)</f>
         <v/>
       </c>
       <c r="G95" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A95,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A95,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H95" s="10" t="inlineStr">
@@ -3837,17 +3837,17 @@
         </is>
       </c>
       <c r="D96" s="10" t="n">
-        <v>1154</v>
+        <v>1173</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>1158</v>
+        <v>1177</v>
       </c>
       <c r="F96" s="10">
-        <f>COUNTIF('화 목록'!$B$2:$B$1159,A96)</f>
+        <f>COUNTIF('화 목록'!$B$2:$B$1178,A96)</f>
         <v/>
       </c>
       <c r="G96" s="10">
-        <f>SUMIF('화 목록'!$B$2:$B$1159,A96,'화 목록'!$F$2:$F$1159)</f>
+        <f>SUMIF('화 목록'!$B$2:$B$1178,A96,'화 목록'!$F$2:$F$1178)</f>
         <v/>
       </c>
       <c r="H96" s="10" t="inlineStr">
@@ -3885,7 +3885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G1159"/>
+  <dimension ref="A1:G1178"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="10" min="1" max="1"/>
@@ -30986,7 +30986,7 @@
         <v>967</v>
       </c>
       <c r="B968" s="10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C968" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B968)</f>
@@ -30994,18 +30994,18 @@
       </c>
       <c r="D968" s="10" t="inlineStr">
         <is>
-          <t>F 시즌2 라 세르피엔테</t>
+          <t>E 빅토르 안전가옥 세션</t>
         </is>
       </c>
       <c r="E968" s="10" t="n">
         <v>31832</v>
       </c>
       <c r="F968" s="10" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G968" s="10" t="inlineStr">
         <is>
-          <t>며칠 후. 면회 시리즈가 끝난 뒤 처음으로 팀 전체가 안전가옥에 모입니다. 테이블 위에는 빅토르가 남긴 여행용 체스판이 그대로 있고, 사라진 흑색 폰 자리에는 여전히 병아리콩 하나가 놓여 있습니다. 카를로스는 로셀요가 편지로 전해 온 이름을 처음으로 화이트보드에 적고, 증인보호 담당관 아벨라르도 루아노가 입회한 화면 너머에서 빅토르가 그 이름을 조용히 소리 내어 읽습니다.</t>
+          <t>며칠 후. 알바로가 정기 면회 중 로셀요에게 세계 체스 선수권 결승전 기사를 화제로 꺼냅니다.</t>
         </is>
       </c>
     </row>
@@ -31014,7 +31014,7 @@
         <v>968</v>
       </c>
       <c r="B969" s="10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C969" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B969)</f>
@@ -31022,18 +31022,18 @@
       </c>
       <c r="D969" s="10" t="inlineStr">
         <is>
-          <t>F 시즌2 라 세르피엔테</t>
+          <t>E 빅토르 안전가옥 세션</t>
         </is>
       </c>
       <c r="E969" s="10" t="n">
-        <v>31891</v>
+        <v>31886</v>
       </c>
       <c r="F969" s="10" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G969" s="10" t="inlineStr">
         <is>
-          <t>다음 날 오전. 마르코스와 카밀라가 밤새 모은 공개 기록을 세션에서 보고합니다. 레안드로 이바롤라 세넨트는 실존했던 발렌시아의 조선 기사였고, 12년 전 데니아 앞바다에서 요트 사고로 숨졌습니다. 사망 기록과 지역 신문 부고, 묘지의 벽감 번호까지 모든 것이 맞아떨어지는 순간, 팀은 몇 주 동안 기다려 온 이름이 무덤 앞에서 끝나 버렸다는 사실을 받아들여야 합니다.</t>
+          <t>며칠 후. 알바로가 정기 면회 중 로셀요에게 한 대형 암호화폐 거래소가 붕괴하고 고객 자금이 동결되었다는 기사를 화제로 꺼냅니다.</t>
         </is>
       </c>
     </row>
@@ -31042,7 +31042,7 @@
         <v>969</v>
       </c>
       <c r="B970" s="10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C970" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B970)</f>
@@ -31050,18 +31050,18 @@
       </c>
       <c r="D970" s="10" t="inlineStr">
         <is>
-          <t>F 시즌2 라 세르피엔테</t>
+          <t>E 빅토르 안전가옥 세션</t>
         </is>
       </c>
       <c r="E970" s="10" t="n">
-        <v>31947</v>
+        <v>31938</v>
       </c>
       <c r="F970" s="10" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G970" s="10" t="inlineStr">
         <is>
-          <t>며칠 후. 알바로는 정기 면회에서, 사망 신고가 누락된 노인 명의로 수년간 연금이 지급되어 온 사기 사건 기사를 화제로 꺼냅니다. 로셀요는 이름의 주인이 이미 죽었다는 말을 듣고도 놀라지 않고, 기사 속 "죽은 세입자들"에 대해 이상할 만큼 오래 이야기합니다. 돌아온 알바로의 보고를 두고, 팀은 그것이 도움인지 조종인지를 놓고 처음으로 정면에서 갈라집니다.</t>
+          <t>며칠 후. 알바로가 정기 면회 중 로셀요에게 발트해 해저 통신 케이블 파손이 사보타주로 의심된다는 기사를 화제로 꺼냅니다.</t>
         </is>
       </c>
     </row>
@@ -31070,7 +31070,7 @@
         <v>970</v>
       </c>
       <c r="B971" s="10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C971" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B971)</f>
@@ -31078,18 +31078,18 @@
       </c>
       <c r="D971" s="10" t="inlineStr">
         <is>
-          <t>F 시즌2 라 세르피엔테</t>
+          <t>E 빅토르 안전가옥 세션</t>
         </is>
       </c>
       <c r="E971" s="10" t="n">
-        <v>32004</v>
+        <v>31992</v>
       </c>
       <c r="F971" s="10" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="G971" s="10" t="inlineStr">
         <is>
-          <t>그 주 토요일, 발렌시아. 알바로가 루사파의 한 카페에서 레안드로 이바롤라의 딸 마리벨을 만납니다. 처음에는 외투도 벗지 않은 채 경계하던 그녀는, 아버지의 여권이 평생 세 번이나 "분실"되었다는 이야기와, 아버지가 죽고 5년 뒤 트리에스테에서 날아온 교통 범칙금, 그리고 장례식에 와서 녹색 잉크로 조문록에 서명하고 사라진 낯선 노인에 대해 하나씩 털어놓습니다.</t>
+          <t>며칠 후. 알바로가 정기 면회 중 가벼운 마음으로 로셀요에게 전날 밤 열린 엘 클라시코 결과 기사를 화제로 꺼냅니다.</t>
         </is>
       </c>
     </row>
@@ -31098,7 +31098,7 @@
         <v>971</v>
       </c>
       <c r="B972" s="10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C972" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B972)</f>
@@ -31106,18 +31106,18 @@
       </c>
       <c r="D972" s="10" t="inlineStr">
         <is>
-          <t>F 시즌2 라 세르피엔테</t>
+          <t>E 빅토르 안전가옥 세션</t>
         </is>
       </c>
       <c r="E972" s="10" t="n">
-        <v>32063</v>
+        <v>32043</v>
       </c>
       <c r="F972" s="10" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G972" s="10" t="inlineStr">
         <is>
-          <t>며칠 후, 마드리드. 하비에르가 이주민 지원단체 「Asociación Senda Acogida」에서 들어온 제보를 알바로에게 넘깁니다. 단체 사무실의 작은 상담실에서, 알바로는 6,000유로를 내고 받은 체류증이 가짜였다는 사실을 경찰 검문에서야 알게 된 세네갈 출신 아미나타 사르를 만납니다. 단체 변호사가 곁에 앉은 채, 그녀는 우세라의 한 행정 대행사무소와, 빚을 다 갚을 때까지 돌려받지 못한 자신의 여권에 대해 이야기합니다.</t>
+          <t>며칠 후. 알바로가 정기 면회 중 로셀요에게 정부의 임대료 상한제와 '주거 긴장 지역' 지정 확대에 관한 신문 기사를 화제로 꺼냅니다.</t>
         </is>
       </c>
     </row>
@@ -31126,7 +31126,7 @@
         <v>972</v>
       </c>
       <c r="B973" s="10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C973" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B973)</f>
@@ -31134,18 +31134,18 @@
       </c>
       <c r="D973" s="10" t="inlineStr">
         <is>
-          <t>F 시즌2 라 세르피엔테</t>
+          <t>E 빅토르 안전가옥 세션</t>
         </is>
       </c>
       <c r="E973" s="10" t="n">
-        <v>32121</v>
+        <v>32096</v>
       </c>
       <c r="F973" s="10" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="G973" s="10" t="inlineStr">
         <is>
-          <t>일주일 후. 신문사가 독자 검증을 위해 의뢰한 퇴직 문서감정가 헤르미니아 토르데시야스가 자택 한쪽을 개조한 작업실에서 알바로와 카밀라를 맞습니다. 루페와 자외선 램프 아래 아미나타의 체류증 컬러 사본, 트리에스테 범칙금에 첨부된 렌트 계약서, 그리고 이바롤라 장례식의 조문록 원본이 나란히 놓이고, 헤르미니아는 기본기 수업부터 천천히 시작한 끝에 마이크로 인쇄된 글자들 사이에서 갈라진 "e" 하나를 손끝으로 가리킵니다.</t>
+          <t>며칠 후. 알바로가 정기 면회 중 로셀요에게 스페인 '골든 비자' 제도의 공식 폐지와 그 여파를 다룬 기사를 화제로 꺼냅니다.</t>
         </is>
       </c>
     </row>
@@ -31154,7 +31154,7 @@
         <v>973</v>
       </c>
       <c r="B974" s="10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C974" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B974)</f>
@@ -31162,18 +31162,18 @@
       </c>
       <c r="D974" s="10" t="inlineStr">
         <is>
-          <t>F 시즌2 라 세르피엔테</t>
+          <t>E 빅토르 안전가옥 세션</t>
         </is>
       </c>
       <c r="E974" s="10" t="n">
-        <v>32180</v>
+        <v>32145</v>
       </c>
       <c r="F974" s="10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G974" s="10" t="inlineStr">
         <is>
-          <t>상대편 콜드 오픈. 어느 항구 도시, 블라인드를 반쯤 내린 빈 사무실. 엘 사스트레가 코르소에게, 발렌시아에서 한 기자가 죽은 기사의 딸을 만났다는 사실을 전합니다. 테이블 끝에서는 아무 말 없는 누군가의 손이 귤을 천천히 까고 있습니다. — 같은 날 오후, 알바로는 면회실에서 이제 아프리카로 날아가지 않고 쓰레기 매립지 곁에서 겨울을 나는 황새에 관한 기사를 꺼내고, 로셀요는 새가 아니라 매립지를 찾으라고 말한 뒤 처음으로 알바로에게 질문을 던집니다. 저녁 세션에서 팀은 그 질문이 무엇을 뜻하는지 따져 봅니다.</t>
+          <t>며칠 후. 알바로가 정기 면회 중 로셀요에게 미슐랭 가이드 발표와 산세바스티안의 미식 순위를 다룬 가벼운 기사를 화제로 꺼냅니다.</t>
         </is>
       </c>
     </row>
@@ -31182,7 +31182,7 @@
         <v>974</v>
       </c>
       <c r="B975" s="10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C975" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B975)</f>
@@ -31190,18 +31190,18 @@
       </c>
       <c r="D975" s="10" t="inlineStr">
         <is>
-          <t>F 시즌2 라 세르피엔테</t>
+          <t>E 빅토르 안전가옥 세션</t>
         </is>
       </c>
       <c r="E975" s="10" t="n">
-        <v>32242</v>
+        <v>32197</v>
       </c>
       <c r="F975" s="10" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G975" s="10" t="inlineStr">
         <is>
-          <t>2주 후. 아미나타의 고소장과 헤르미니아의 감정서가 경찰로 넘어가자, 국가경찰 UCRIF의 레이레 사가스타 반장이 카를로스를 통해 알바로를 만납니다. 그녀는 아무것도 알려 주지 않지만, 알바로가 공개적으로 취재하는 것을 막지도 않습니다. 같은 주, 알바로는 코슬라다 산업단지의 인쇄소를 찾아가 대표에게 정식으로 인터뷰를 요청하고, 거절당해 돌아 나오던 길에 라미네이팅 기계 냄새를 풍기는 젊은 여직원과 주차장에서 눈이 마주칩니다.</t>
+          <t>며칠 후. 알바로가 정기 면회 중 로셀요에게 선거를 앞두고 적발된 허위정보 봇 캠페인에 관한 기사를 화제로 꺼냅니다.</t>
         </is>
       </c>
     </row>
@@ -31210,7 +31210,7 @@
         <v>975</v>
       </c>
       <c r="B976" s="10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C976" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B976)</f>
@@ -31218,18 +31218,18 @@
       </c>
       <c r="D976" s="10" t="inlineStr">
         <is>
-          <t>F 시즌2 라 세르피엔테</t>
+          <t>E 빅토르 안전가옥 세션</t>
         </is>
       </c>
       <c r="E976" s="10" t="n">
-        <v>32303</v>
+        <v>32252</v>
       </c>
       <c r="F976" s="10" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G976" s="10" t="inlineStr">
         <is>
-          <t>다음 날 저녁, 코슬라다 시립도서관 열람실 구석. 셀마는 휴대전화 속 사진들을 보여 주며 녹색 표지 장부와 엑셀 파일이 무엇인지 설명합니다. 알바로는 무엇도 더 가져오라고 하지 않습니다. 그날 밤 신문사 회의실에서 마르타는 받은 자료와 받아서는 안 되는 것을 하나씩 구분하고, 카밀라는 1,900건의 항목 사이에서 고객 코드 S7과, 2021년 날짜가 찍힌 한 줄 "IBARROLA S., L."을 찾아냅니다.</t>
+          <t>며칠 후. 알바로가 정기 면회 중 로셀요에게 스페인 교도소의 과밀 수용과 수감자 처우를 고발한 보고서 기사를 화제로 꺼냅니다. 평소처럼 '전문가'로서 분석하던 로셀요는 자신의 감방과 일과, 혼자 걷는 운동장 이야기를 하며 드물게 개인적인 속내를 드러냅니다.</t>
         </is>
       </c>
     </row>
@@ -31238,7 +31238,7 @@
         <v>976</v>
       </c>
       <c r="B977" s="10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C977" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B977)</f>
@@ -31246,18 +31246,18 @@
       </c>
       <c r="D977" s="10" t="inlineStr">
         <is>
-          <t>F 시즌2 라 세르피엔테</t>
+          <t>E 빅토르 안전가옥 세션</t>
         </is>
       </c>
       <c r="E977" s="10" t="n">
-        <v>32365</v>
+        <v>32311</v>
       </c>
       <c r="F977" s="10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G977" s="10" t="inlineStr">
         <is>
-          <t>며칠 후, 프로그램 채널로 연결된 화면 너머에서 빅토르가 S7의 주문 패턴을 보고 오래 말이 없습니다. 그는 옛 기관의 문서고 담당자라면 "이바롤라"가 누구의 커버 네임이었는지 확인해 줄 수 있다고 말하지만, 카를로스와 아벨라르도는 단호하게 거절하고, 알바로는 아무 말도 하지 않습니다. 그날 밤, 어딘지 모를 나라의 작은 부엌에서 빅토르는 혼자 체스 문제 하나를 써서, 이십 년 동안 한 번도 쓰지 않았던 방식으로 보냅니다. [상대편] 그리고 그 문제를 읽는 사람은 빅토르가 기다린 사람만이 아닙니다.</t>
+          <t>며칠 후. 알바로가 정기 면회 중 로셀요에게 국제 미술품 경매에서 한 초상화가 사상 최고가에 낙찰되었다는 기사를 화제로 꺼냅니다. 로셀요는 '그림은 가장 조용한 금고'라며 미술품이 가치를 옮기는 방식을 해부하고, 알바로의 옛 경매회사 위장 취재까지 들추며 응수합니다.</t>
         </is>
       </c>
     </row>
@@ -31266,7 +31266,7 @@
         <v>977</v>
       </c>
       <c r="B978" s="10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C978" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B978)</f>
@@ -31274,18 +31274,18 @@
       </c>
       <c r="D978" s="10" t="inlineStr">
         <is>
-          <t>F 시즌2 라 세르피엔테</t>
+          <t>E 빅토르 안전가옥 세션</t>
         </is>
       </c>
       <c r="E978" s="10" t="n">
-        <v>32427</v>
+        <v>32363</v>
       </c>
       <c r="F978" s="10" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G978" s="10" t="inlineStr">
         <is>
-          <t>일주일 후. 알바로는 정기 면회에서 리스본의 신축 아파트 분양 사기 기사를 꺼내고, 로셀요는 견본주택에서는 모든 것이 작동하지만 아무도 살지 않는다고, 같은 말을 두 번 되풀이합니다. 같은 날 오후 안전가옥, 프로그램 채널로 연결된 화면 너머에서 아벨라르도가 잠시 자리를 비운 사이, 빅토르는 아벨라르도에게 알리지 않고 받은 답장의 내용을 팀에게 털어놓습니다. "이바롤라"는 확실히 노인의 커버 네임이었고, 셀마가 넘긴 장부 속 S7 키트의 가장 최근 배송지는 리스본입니다. 팀은 로셀요의 말이 경고였는지 미끼였는지 알지 못한 채, 조금씩 리스본 쪽으로 기웁니다.</t>
+          <t>며칠 후. 알바로가 정기 면회 중 로셀요에게 두 나라가 서로 외교관과 정보요원을 맞추방한 기사를 화제로 꺼냅니다. 로셀요는 스파이 세계의 '예절'을 체스처럼 풀어내며 옛 '동료들'을 에둘러 언급하지만, 알바로가 옛 프로그램을 파고들자 입을 닫고 알바로는 면회 시간이 끝나기 전에 자리를 뜹니다.</t>
         </is>
       </c>
     </row>
@@ -31294,7 +31294,7 @@
         <v>978</v>
       </c>
       <c r="B979" s="10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C979" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B979)</f>
@@ -31302,18 +31302,18 @@
       </c>
       <c r="D979" s="10" t="inlineStr">
         <is>
-          <t>F 시즌2 라 세르피엔테</t>
+          <t>E 빅토르 안전가옥 세션</t>
         </is>
       </c>
       <c r="E979" s="10" t="n">
-        <v>32491</v>
+        <v>32421</v>
       </c>
       <c r="F979" s="10" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="G979" s="10" t="inlineStr">
         <is>
-          <t>2주 후, 12월 초의 이른 아침. 유럽수사명령을 받은 포르투갈 사법경찰이 레이레 반장의 팀과 함께 리스본 알칸타라의 아파트 문을 엽니다. 알바로는 마드리드 편집국에서 레이레가 약속한 짧은 문자 하나만 기다리고, 하비에르의 화면에는 열흘 전부터 "준비된" 기사 초안이 열려 있습니다. 그러나 문 뒤의 집은 갓 청소한 냄새만 남은 빈집이고, 부엌 식탁 위에는 12년 전 발렌시아 신문에 실린 레안드로 이바롤라의 부고 한 장만 놓여 있습니다. 오후, 국립법원 검사 킨타나르는 카를로스와 레이레를 불러 이 실패의 값을 정확한 법률 용어로 계산하고, 그날 밤 카를로스의 전화가 울립니다.</t>
+          <t>며칠 후. 알바로가 정기 면회 중 로셀요에게 프라도 미술관의 한 작품 복원을 둘러싼 논란 기사를 화제로 꺼냅니다. 무엇이 '원본'인가를 두고 이야기하던 로셀요는 바니시와 덧칠, 밑그림의 비유로 자기 자신을 이야기하고, 처음으로 알바로에게 어떤 버전의 자신을 쓸 것인지 되묻습니다.</t>
         </is>
       </c>
     </row>
@@ -31322,7 +31322,7 @@
         <v>979</v>
       </c>
       <c r="B980" s="10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C980" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B980)</f>
@@ -31330,18 +31330,18 @@
       </c>
       <c r="D980" s="10" t="inlineStr">
         <is>
-          <t>F 시즌2 라 세르피엔테</t>
+          <t>E 빅토르 안전가옥 세션</t>
         </is>
       </c>
       <c r="E980" s="10" t="n">
-        <v>32554</v>
+        <v>32477</v>
       </c>
       <c r="F980" s="10" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="G980" s="10" t="inlineStr">
         <is>
-          <t>그 전날 밤, 빅토르의 새 집 우편함에서 보낸 사람 없는 봉투 하나가 발견되었습니다. 안에는 그가 이십 년 전 어느 기차역에서 잃어버렸던 것과 같은 크기의 흑색 체스 폰 하나가 들어 있었습니다. 프로그램은 그를 밤사이 다른 나라로 옮겼고, 몇 달 동안 쌓아 온 새 이름과 새 삶은 하룻밤에 끝났습니다. 다음 날 새벽, 낯선 호텔 방에서 연결된 화면 너머로 빅토르는 처음으로 늙어 보이고, 안전가옥의 팀은 이번에는 분명히 졌다는 사실을 각자의 방식으로 받아들입니다. 통화가 끝나기 직전, 헤르미니아의 전화가 리스본 항목이 적힌 장부 한 페이지에 대해 마지막 한 가지를 더 알려 줍니다.</t>
+          <t>며칠 후. 알바로가 정기 면회 중 로셀요에게 제재를 피해 다니는 '그림자 선단' 유조선들에 관한 기사를 화제로 꺼냅니다.</t>
         </is>
       </c>
     </row>
@@ -31350,7 +31350,7 @@
         <v>980</v>
       </c>
       <c r="B981" s="10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C981" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B981)</f>
@@ -31358,18 +31358,18 @@
       </c>
       <c r="D981" s="10" t="inlineStr">
         <is>
-          <t>F 시즌2 라 세르피엔테</t>
+          <t>E 빅토르 안전가옥 세션</t>
         </is>
       </c>
       <c r="E981" s="10" t="n">
-        <v>32618</v>
+        <v>32528</v>
       </c>
       <c r="F981" s="10" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="G981" s="10" t="inlineStr">
         <is>
-          <t>2주 후, 크리스마스 직전의 안전가옥. 옆집 텔레비전에서는 성탄 복권 추첨 노래가 희미하게 들려오고, 화면 앞 빅토르의 의자는 비어 있습니다. 카를로스는 화이트보드를 지우는 대신 "확실한 것"과 "믿고 싶은 것" 두 칸으로 나누고, 카밀라는 안도라에서 리스본, 루가노로 이어지는 돈의 경로를 다시 그립니다. 레이레와 검사 킨타나르는 이번에는 공방 자체의 증거만으로, 증거가 지워지기 전에 움직이기로 합니다. [상대편] 같은 시각, 어느 항구 도시의 사무실에서 엘 사스트레는 우르비나에게 장부를 태우라는 전화를 겁니다.</t>
+          <t>며칠 후. 스페인 전역을 마비시킨 대정전 직후, 알바로가 정기 면회 중 로셀요에게 그날 밤과 정전이 드러낸 것에 관한 기사를 화제로 꺼냅니다.</t>
         </is>
       </c>
     </row>
@@ -31378,7 +31378,7 @@
         <v>981</v>
       </c>
       <c r="B982" s="10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C982" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B982)</f>
@@ -31386,18 +31386,18 @@
       </c>
       <c r="D982" s="10" t="inlineStr">
         <is>
-          <t>F 시즌2 라 세르피엔테</t>
+          <t>E 빅토르 안전가옥 세션</t>
         </is>
       </c>
       <c r="E982" s="10" t="n">
-        <v>32684</v>
+        <v>32582</v>
       </c>
       <c r="F982" s="10" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="G982" s="10" t="inlineStr">
         <is>
-          <t>1월 중순의 어느 새벽. UCRIF가 판사의 영장을 들고 코슬라다의 그라피카스 시에르소와 우세라의 게스토리아에 동시에 들어갑니다. 알바로는 다른 기자들과 똑같이 경찰 통제선 밖 영하의 추위 속에 서 있고, 몇 시간 뒤 단체 사무실의 텔레비전 앞에서 아미나타는 화면 속 수갑 찬 하신토 로베라를 말없이 바라봅니다. 그날 저녁, 레이레는 기사에는 쓰지 않는다는 조건으로, 장부 원본이 불에 타기 직전의 금속통에서 발견되었다고만 짧게 확인해 줍니다.</t>
+          <t>며칠 후. 알바로가 정기 면회 중 로셀요에게 사면법을 둘러싼 정치권의 격렬한 논쟁에 관한 기사를 화제로 꺼냅니다.</t>
         </is>
       </c>
     </row>
@@ -31406,7 +31406,7 @@
         <v>982</v>
       </c>
       <c r="B983" s="10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C983" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B983)</f>
@@ -31414,18 +31414,18 @@
       </c>
       <c r="D983" s="10" t="inlineStr">
         <is>
-          <t>F 시즌2 라 세르피엔테</t>
+          <t>E 빅토르 안전가옥 세션</t>
         </is>
       </c>
       <c r="E983" s="10" t="n">
-        <v>32749</v>
+        <v>32638</v>
       </c>
       <c r="F983" s="10" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G983" s="10" t="inlineStr">
         <is>
-          <t>2주 후, 1월 말. 알바로는 정기 면회에서, 독일이 여권 사진 합성(모핑)을 막기 위해 관청이나 인증된 사진관에서 찍어 암호화 전송한 디지털 사진만 받도록 한 규정의 성과를 다룬 기사를 꺼냅니다. 로셀요는 "두 얼굴로 만든 얼굴은 누구의 것도 아니지만, 두 사람 모두에게 쓸모 있다"고 말하고, 리스본 이야기가 나오자 자신은 분명히 "아무도 살지 않는다"고 말했다며 물러서지 않습니다. 그날 오후 안전가옥에서는 유로폴의 바우트 페르하겐이 화상으로 합류한 회의가 열리고, 공방에서 압수된 S7 서류 사진 31장이 모두 합성이라는 사실과, 그중 여러 장에 공통으로 섞인 한 얼굴이 70대 노인의 것이라는 분석이 처음으로 테이블에 오릅니다.</t>
+          <t>며칠 후. 알바로가 정기 면회 중 로셀요에게 바로 그와 같은 사람을 잡기 위해 만들어진 EU 자금세탁방지청(AMLA)의 본격 출범 기사를 화제로 꺼냅니다.</t>
         </is>
       </c>
     </row>
@@ -31434,7 +31434,7 @@
         <v>983</v>
       </c>
       <c r="B984" s="10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C984" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B984)</f>
@@ -31442,18 +31442,18 @@
       </c>
       <c r="D984" s="10" t="inlineStr">
         <is>
-          <t>F 시즌2 라 세르피엔테</t>
+          <t>E 빅토르 안전가옥 세션</t>
         </is>
       </c>
       <c r="E984" s="10" t="n">
-        <v>32808</v>
+        <v>32690</v>
       </c>
       <c r="F984" s="10" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G984" s="10" t="inlineStr">
         <is>
-          <t>일주일 후, 2월 초. 카밀라가 신청했던 루가노(티치노 주) 상업등기의 등본과 첨부 서류 사본이 도착하고, 그녀는 알바트로스 해상위험 컨설팅사의 단독 이사 이름을 소리 내어 읽습니다. 카시미로 아르테아가 룬드, 1949년 탕헤르 국제구역 출생. 2022년 등기 서류에 첨부된 스위스 체류허가 사본 속 흐릿한 사진은 장례식 뒷줄의 노인, 그리고 역분해된 반쪽 얼굴과 똑같이 고개를 조금 왼쪽으로 숙이고 있습니다. 하비에르는 이제 기사라고 말하고, 알바로는 아직 아니라고 말합니다. [상대편] 같은 날 밤, 어느 항구 도시의 셋방에서 엘 사스트레는 짐을 꾸리며 코르소에게 노인이 남긴 녹색 잉크 메모를 읽어 줍니다.</t>
+          <t>며칠 후. 알바로가 정기 면회 중 로셀요에게 그의 옛 동업자인 메리디안의 로비스트 카살스가 벨기에에서 형기 3분의 1을 채우고 조건부 석방을 허가받았다는 기사를 화제로 꺼냅니다.</t>
         </is>
       </c>
     </row>
@@ -31462,7 +31462,7 @@
         <v>984</v>
       </c>
       <c r="B985" s="10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C985" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B985)</f>
@@ -31470,18 +31470,18 @@
       </c>
       <c r="D985" s="10" t="inlineStr">
         <is>
-          <t>F 시즌2 라 세르피엔테</t>
+          <t>E 빅토르 안전가옥 세션</t>
         </is>
       </c>
       <c r="E985" s="10" t="n">
-        <v>32867</v>
+        <v>32746</v>
       </c>
       <c r="F985" s="10" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G985" s="10" t="inlineStr">
         <is>
-          <t>며칠 후. 알바로는 50년 만에 산탄데르의 한 시립도서관으로 익명 반납된 콘래드의 『로드 짐』에 관한 짧은 기사를 들고 면회실에 앉습니다. 책 여백을 가득 채운 녹색 잉크 메모 이야기를 꺼내자, 로셀요는 처음으로 대답보다 먼저 두 손을 탁자 위에서 거둬들이고, 알바로가 말한 적도 없는 "이름"을 모른다고 말합니다. 같은 주, 프로그램의 공식 승인을 받아 다시 연결된 화면 너머에서 빅토르는 단 한 장의 사진 앞에서 오래 침묵하다가, 자신이 확인할 수 있는 것과 없는 것을 정확히 나누어 말합니다.</t>
+          <t>몇 주 후. 알바로가 정기 면회 중 로셀요에게 그의 상고가 대법원에서 기각되어 판결이 확정되었다는 소식과, 칸타브리아 저택에서 압수된 시계 컬렉션이 공매에 부쳐진다는 기사를 화제로 꺼냅니다.</t>
         </is>
       </c>
     </row>
@@ -31490,7 +31490,7 @@
         <v>985</v>
       </c>
       <c r="B986" s="10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C986" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B986)</f>
@@ -31498,18 +31498,18 @@
       </c>
       <c r="D986" s="10" t="inlineStr">
         <is>
-          <t>F 시즌2 라 세르피엔테</t>
+          <t>E 빅토르 안전가옥 세션</t>
         </is>
       </c>
       <c r="E986" s="10" t="n">
-        <v>32928</v>
+        <v>32806</v>
       </c>
       <c r="F986" s="10" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G986" s="10" t="inlineStr">
         <is>
-          <t>3월 초, 신문사 회의실. 마르타는 기사 초안을 문장 단위로 잘라 출력해 테이블에 펼치고, 하비에르와 편집국장, 알바로는 단어 하나하나를 두고 다툽니다. 오후에는 국립법원 검찰청의 킨타나르 검사가 원고는 보지도 듣지도 않은 채 오직 시각과 안전만 묻고, 보도 시점은 판사의 국제체포영장 발부와 서류 경보 등록 이후로 정해집니다. 저녁 화상회의에서 미레유와 클라우스가 파리와 베를린의 마감을 맞추는 동안, 이틀 전 발송한 질문서의 기한 2분 전에 아르테아가의 변호사가 보낸 답장이 도착합니다. 단 세 줄입니다.</t>
+          <t>몇 주 후. 알바로가 정기 면회 중 로셀요에게 스위스 은행 비밀주의가 정보 자동교환 체제로 사실상 막을 내렸음을 다룬 기획 기사를 화제로 꺼냅니다.</t>
         </is>
       </c>
     </row>
@@ -31530,14 +31530,14 @@
         </is>
       </c>
       <c r="E987" s="10" t="n">
-        <v>32989</v>
+        <v>32866</v>
       </c>
       <c r="F987" s="10" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G987" s="10" t="inlineStr">
         <is>
-          <t>새벽 6시, 마드리드와 파리와 베를린에서 같은 얼굴이 동시에 1면에 실립니다. 편집국에는 환호 대신 식어 가는 커피와 키보드 소리뿐입니다. 하루 사이 스위스 당국은 알바트로스의 계좌를 동결하고, 이탈리아 경찰이 들어간 트리에스테의 집은 비어 있었으며, 그가 질문서를 받은 다음 날인 화요일에 이미 솅겐 지역 밖으로 나갔다는 사실이 확인됩니다. 체포는 없지만, 이제 그의 얼굴로는 어떤 국경도 넘을 수 없습니다. [상대편] 어느 항구의 빈 사무실에서 엘 사스트레는 신문을 접어 탁자에 두고 떠나고, 몇 주 뒤 알바로는 면회실에서 그 1면을 로셀요 앞에 펼쳐 놓습니다.</t>
+          <t>며칠 후. 면회 시리즈가 끝난 뒤 처음으로 팀 전체가 안전가옥에 모입니다. 테이블 위에는 빅토르가 남긴 여행용 체스판이 그대로 있고, 사라진 흑색 폰 자리에는 여전히 병아리콩 하나가 놓여 있습니다. 카를로스는 로셀요가 편지로 전해 온 이름을 처음으로 화이트보드에 적고, 증인보호 담당관 아벨라르도 루아노가 입회한 화면 너머에서 빅토르가 그 이름을 조용히 소리 내어 읽습니다.</t>
         </is>
       </c>
     </row>
@@ -31546,7 +31546,7 @@
         <v>987</v>
       </c>
       <c r="B988" s="10" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C988" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B988)</f>
@@ -31554,18 +31554,18 @@
       </c>
       <c r="D988" s="10" t="inlineStr">
         <is>
-          <t>G 시즌2 독립 취재</t>
+          <t>F 시즌2 라 세르피엔테</t>
         </is>
       </c>
       <c r="E988" s="10" t="n">
-        <v>33050</v>
+        <v>32925</v>
       </c>
       <c r="F988" s="10" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G988" s="10" t="inlineStr">
         <is>
-          <t>새로운 취재. 하비에르가 경제면 기자에게서 흘러나온 소문 하나를 들고 옵니다. 코슬라다에 본사를 둔 중견 공조설비 기업 '클리마티사시온 벤티스카'가 단 한 번의 화상회의 끝에 380만 유로를 해외로 송금했고, 회사는 이를 '전산 사고'라고만 발표했다는 것입니다. 그날 밤 알바로는 카밀라에게 'CEO 사기'의 구조를 묻습니다.</t>
+          <t>다음 날 오전. 마르코스와 카밀라가 밤새 모은 공개 기록을 세션에서 보고합니다. 레안드로 이바롤라 세넨트는 실존했던 발렌시아의 조선 기사였고, 12년 전 데니아 앞바다에서 요트 사고로 숨졌습니다. 사망 기록과 지역 신문 부고, 묘지의 벽감 번호까지 모든 것이 맞아떨어지는 순간, 팀은 몇 주 동안 기다려 온 이름이 무덤 앞에서 끝나 버렸다는 사실을 받아들여야 합니다.</t>
         </is>
       </c>
     </row>
@@ -31574,7 +31574,7 @@
         <v>988</v>
       </c>
       <c r="B989" s="10" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C989" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B989)</f>
@@ -31582,18 +31582,18 @@
       </c>
       <c r="D989" s="10" t="inlineStr">
         <is>
-          <t>G 시즌2 독립 취재</t>
+          <t>F 시즌2 라 세르피엔테</t>
         </is>
       </c>
       <c r="E989" s="10" t="n">
-        <v>33103</v>
+        <v>32981</v>
       </c>
       <c r="F989" s="10" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="G989" s="10" t="inlineStr">
         <is>
-          <t>며칠 후, 나탈리아 에스카르틴이 익명을 조건으로 만남에 응합니다. 마드리드 참베리의 조용한 카페 구석에서, 그녀는 그날의 화상회의를 처음으로 처음부터 끝까지 이야기합니다.</t>
+          <t>며칠 후. 알바로는 정기 면회에서, 사망 신고가 누락된 노인 명의로 수년간 연금이 지급되어 온 사기 사건 기사를 화제로 꺼냅니다. 로셀요는 이름의 주인이 이미 죽었다는 말을 듣고도 놀라지 않고, 기사 속 "죽은 세입자들"에 대해 이상할 만큼 오래 이야기합니다. 돌아온 알바로의 보고를 두고, 팀은 그것이 도움인지 조종인지를 놓고 처음으로 정면에서 갈라집니다.</t>
         </is>
       </c>
     </row>
@@ -31602,7 +31602,7 @@
         <v>989</v>
       </c>
       <c r="B990" s="10" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C990" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B990)</f>
@@ -31610,18 +31610,18 @@
       </c>
       <c r="D990" s="10" t="inlineStr">
         <is>
-          <t>G 시즌2 독립 취재</t>
+          <t>F 시즌2 라 세르피엔테</t>
         </is>
       </c>
       <c r="E990" s="10" t="n">
-        <v>33154</v>
+        <v>33038</v>
       </c>
       <c r="F990" s="10" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G990" s="10" t="inlineStr">
         <is>
-          <t>마르코스가 녹화본을 프레임 단위로 분석합니다. 실시간 얼굴 합성과 음성 복제의 흔적을 하나씩 짚어 내던 그는, 기사에 쓸 시연 영상을 만들자고 제안하고, 편집국 안에서 작은 윤리 논쟁이 벌어집니다.</t>
+          <t>그 주 토요일, 발렌시아. 알바로가 루사파의 한 카페에서 레안드로 이바롤라의 딸 마리벨을 만납니다. 처음에는 외투도 벗지 않은 채 경계하던 그녀는, 아버지의 여권이 평생 세 번이나 "분실"되었다는 이야기와, 아버지가 죽고 5년 뒤 트리에스테에서 날아온 교통 범칙금, 그리고 장례식에 와서 녹색 잉크로 조문록에 서명하고 사라진 낯선 노인에 대해 하나씩 털어놓습니다.</t>
         </is>
       </c>
     </row>
@@ -31630,7 +31630,7 @@
         <v>990</v>
       </c>
       <c r="B991" s="10" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C991" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B991)</f>
@@ -31638,18 +31638,18 @@
       </c>
       <c r="D991" s="10" t="inlineStr">
         <is>
-          <t>G 시즌2 독립 취재</t>
+          <t>F 시즌2 라 세르피엔테</t>
         </is>
       </c>
       <c r="E991" s="10" t="n">
-        <v>33203</v>
+        <v>33097</v>
       </c>
       <c r="F991" s="10" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G991" s="10" t="inlineStr">
         <is>
-          <t>카밀라와 하비에르가 나탈리아가 건넨 은행 서신을 토대로 돈의 흐름을 재구성합니다. 리투아니아 핀테크 계좌에서 스페인의 '머니 뮬' 계좌 열네 개로 쪼개진 돈의 끝에는 마드리드의 한 가상화폐 장외거래소가 있고, 알바로는 뮬 중 한 명인 열아홉 살 청년 브라이스 테이헤이로의 집을 찾아갑니다.</t>
+          <t>며칠 후, 마드리드. 하비에르가 이주민 지원단체 「Asociación Senda Acogida」에서 들어온 제보를 알바로에게 넘깁니다. 단체 사무실의 작은 상담실에서, 알바로는 6,000유로를 내고 받은 체류증이 가짜였다는 사실을 경찰 검문에서야 알게 된 세네갈 출신 아미나타 사르를 만납니다. 단체 변호사가 곁에 앉은 채, 그녀는 우세라의 한 행정 대행사무소와, 빚을 다 갚을 때까지 돌려받지 못한 자신의 여권에 대해 이야기합니다.</t>
         </is>
       </c>
     </row>
@@ -31658,7 +31658,7 @@
         <v>991</v>
       </c>
       <c r="B992" s="10" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C992" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B992)</f>
@@ -31666,18 +31666,18 @@
       </c>
       <c r="D992" s="10" t="inlineStr">
         <is>
-          <t>G 시즌2 독립 취재</t>
+          <t>F 시즌2 라 세르피엔테</t>
         </is>
       </c>
       <c r="E992" s="10" t="n">
-        <v>33255</v>
+        <v>33155</v>
       </c>
       <c r="F992" s="10" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G992" s="10" t="inlineStr">
         <is>
-          <t>알바로가 푸엔히롤라로 내려가 아르헨티나 출신의 전직 콜센터 직원 라우타로 이바르구렌을 만납니다. 그는 '소포르테 코스타솔'이라는 간판 뒤에서 벌어지던 일을 털어놓다가, 자신이 바로 브라이스를 끌어들인 '레오'였다고 고백합니다. 마드리드로 돌아온 알바로에게 카를로스가 경찰 수사 사실을 귀띔합니다.</t>
+          <t>일주일 후. 신문사가 독자 검증을 위해 의뢰한 퇴직 문서감정가 헤르미니아 토르데시야스가 자택 한쪽을 개조한 작업실에서 알바로와 카밀라를 맞습니다. 루페와 자외선 램프 아래 아미나타의 체류증 컬러 사본, 트리에스테 범칙금에 첨부된 렌트 계약서, 그리고 이바롤라 장례식의 조문록 원본이 나란히 놓이고, 헤르미니아는 기본기 수업부터 천천히 시작한 끝에 마이크로 인쇄된 글자들 사이에서 갈라진 "e" 하나를 손끝으로 가리킵니다.</t>
         </is>
       </c>
     </row>
@@ -31686,7 +31686,7 @@
         <v>992</v>
       </c>
       <c r="B993" s="10" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C993" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B993)</f>
@@ -31694,18 +31694,18 @@
       </c>
       <c r="D993" s="10" t="inlineStr">
         <is>
-          <t>G 시즌2 독립 취재</t>
+          <t>F 시즌2 라 세르피엔테</t>
         </is>
       </c>
       <c r="E993" s="10" t="n">
-        <v>33304</v>
+        <v>33214</v>
       </c>
       <c r="F993" s="10" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="G993" s="10" t="inlineStr">
         <is>
-          <t>마르코스의 시연은 예상보다 훨씬 쉽게 성공하고, 알바로는 은행 쪽으로 방향을 돌립니다. 반카 알코라 사기방지팀 출신 내부자는 그날 경보가 울렸었다고 증언하고, 은행 홍보책임자는 공식 인터뷰에서 모든 책임을 고객에게 돌립니다.</t>
+          <t>상대편 콜드 오픈. 어느 항구 도시, 블라인드를 반쯤 내린 빈 사무실. 엘 사스트레가 코르소에게, 발렌시아에서 한 기자가 죽은 기사의 딸을 만났다는 사실을 전합니다. 테이블 끝에서는 아무 말 없는 누군가의 손이 귤을 천천히 까고 있습니다. — 같은 날 오후, 알바로는 면회실에서 이제 아프리카로 날아가지 않고 쓰레기 매립지 곁에서 겨울을 나는 황새에 관한 기사를 꺼내고, 로셀요는 새가 아니라 매립지를 찾으라고 말한 뒤 처음으로 알바로에게 질문을 던집니다. 저녁 세션에서 팀은 그 질문이 무엇을 뜻하는지 따져 봅니다.</t>
         </is>
       </c>
     </row>
@@ -31714,7 +31714,7 @@
         <v>993</v>
       </c>
       <c r="B994" s="10" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C994" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B994)</f>
@@ -31722,18 +31722,18 @@
       </c>
       <c r="D994" s="10" t="inlineStr">
         <is>
-          <t>G 시즌2 독립 취재</t>
+          <t>F 시즌2 라 세르피엔테</t>
         </is>
       </c>
       <c r="E994" s="10" t="n">
-        <v>33352</v>
+        <v>33276</v>
       </c>
       <c r="F994" s="10" t="n">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="G994" s="10" t="inlineStr">
         <is>
-          <t>알바로가 반론권 인터뷰를 위해 벤티스카의 우고 살다냐 대표를 만납니다. 같은 날 저녁, 회사가 비밀유지 조건의 합의금을 제시했다며 나탈리아가 협조를 철회하고, 편집국에서는 마르타와 편집장이 무엇을 내보낼 수 있는지 한 줄씩 따지기 시작합니다.</t>
+          <t>2주 후. 아미나타의 고소장과 헤르미니아의 감정서가 경찰로 넘어가자, 국가경찰 UCRIF의 레이레 사가스타 반장이 카를로스를 통해 알바로를 만납니다. 그녀는 아무것도 알려 주지 않지만, 알바로가 공개적으로 취재하는 것을 막지도 않습니다. 같은 주, 알바로는 코슬라다 산업단지의 인쇄소를 찾아가 대표에게 정식으로 인터뷰를 요청하고, 거절당해 돌아 나오던 길에 라미네이팅 기계 냄새를 풍기는 젊은 여직원과 주차장에서 눈이 마주칩니다.</t>
         </is>
       </c>
     </row>
@@ -31742,7 +31742,7 @@
         <v>994</v>
       </c>
       <c r="B995" s="10" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C995" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B995)</f>
@@ -31750,18 +31750,18 @@
       </c>
       <c r="D995" s="10" t="inlineStr">
         <is>
-          <t>G 시즌2 독립 취재</t>
+          <t>F 시즌2 라 세르피엔테</t>
         </is>
       </c>
       <c r="E995" s="10" t="n">
-        <v>33400</v>
+        <v>33337</v>
       </c>
       <c r="F995" s="10" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="G995" s="10" t="inlineStr">
         <is>
-          <t>첫 기사가 나간 지 3주 뒤, 국가경찰이 푸엔히롤라의 콜센터를 급습하고 알바로는 약속대로 두 시간 안에 2부를 내보냅니다. 돌려받은 돈은 일부에 그치고 나탈리아는 끝내 이름을 드러내지 않지만, 그날 밤 알바로와 카밀라는 부엌 식탁에서 아주 사적인 약속 하나를 정합니다.</t>
+          <t>다음 날 저녁, 코슬라다 시립도서관 열람실 구석. 셀마는 휴대전화 속 사진들을 보여 주며 녹색 표지 장부와 엑셀 파일이 무엇인지 설명합니다. 알바로는 무엇도 더 가져오라고 하지 않습니다. 그날 밤 신문사 회의실에서 마르타는 받은 자료와 받아서는 안 되는 것을 하나씩 구분하고, 카밀라는 1,900건의 항목 사이에서 고객 코드 S7과, 2021년 날짜가 찍힌 한 줄 "IBARROLA S., L."을 찾아냅니다.</t>
         </is>
       </c>
     </row>
@@ -31770,7 +31770,7 @@
         <v>995</v>
       </c>
       <c r="B996" s="10" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C996" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B996)</f>
@@ -31778,18 +31778,18 @@
       </c>
       <c r="D996" s="10" t="inlineStr">
         <is>
-          <t>G 시즌2 독립 취재</t>
+          <t>F 시즌2 라 세르피엔테</t>
         </is>
       </c>
       <c r="E996" s="10" t="n">
-        <v>33449</v>
+        <v>33399</v>
       </c>
       <c r="F996" s="10" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G996" s="10" t="inlineStr">
         <is>
-          <t>일상 에피소드. 어느 토요일 아침, 알바로가 약속대로 필라르 이모를 모시고 동네 시장에 장을 보러 갑니다. 이모는 단골 가게마다 들르며 값을 묻고 흥정하고, 알바로는 시장에서 쓰는 말과 '-ito' 축소사를 이모에게서 새삼 배우게 됩니다.</t>
+          <t>며칠 후, 프로그램 채널로 연결된 화면 너머에서 빅토르가 S7의 주문 패턴을 보고 오래 말이 없습니다. 그는 옛 기관의 문서고 담당자라면 "이바롤라"가 누구의 커버 네임이었는지 확인해 줄 수 있다고 말하지만, 카를로스와 아벨라르도는 단호하게 거절하고, 알바로는 아무 말도 하지 않습니다. 그날 밤, 어딘지 모를 나라의 작은 부엌에서 빅토르는 혼자 체스 문제 하나를 써서, 이십 년 동안 한 번도 쓰지 않았던 방식으로 보냅니다. [상대편] 그리고 그 문제를 읽는 사람은 빅토르가 기다린 사람만이 아닙니다.</t>
         </is>
       </c>
     </row>
@@ -31798,7 +31798,7 @@
         <v>996</v>
       </c>
       <c r="B997" s="10" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C997" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B997)</f>
@@ -31806,18 +31806,18 @@
       </c>
       <c r="D997" s="10" t="inlineStr">
         <is>
-          <t>G 시즌2 독립 취재</t>
+          <t>F 시즌2 라 세르피엔테</t>
         </is>
       </c>
       <c r="E997" s="10" t="n">
-        <v>33508</v>
+        <v>33461</v>
       </c>
       <c r="F997" s="10" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G997" s="10" t="inlineStr">
         <is>
-          <t>새로운 취재. 하비에르가 이탈리아 에라스무스 교환학생 줄리아 페라레시의 제보 메일을 받습니다. 마드리드에 도착한 첫날, 석 달 치 돈을 미리 보낸 방이 존재하지 않는다는 사실을 알게 된 그녀를 알바로와 하비에르가 대학가 근처 카페에서 만납니다.</t>
+          <t>일주일 후. 알바로는 정기 면회에서 리스본의 신축 아파트 분양 사기 기사를 꺼내고, 로셀요는 견본주택에서는 모든 것이 작동하지만 아무도 살지 않는다고, 같은 말을 두 번 되풀이합니다. 같은 날 오후 안전가옥, 프로그램 채널로 연결된 화면 너머에서 아벨라르도가 잠시 자리를 비운 사이, 빅토르는 아벨라르도에게 알리지 않고 받은 답장의 내용을 팀에게 털어놓습니다. "이바롤라"는 확실히 노인의 커버 네임이었고, 셀마가 넘긴 장부 속 S7 키트의 가장 최근 배송지는 리스본입니다. 팀은 로셀요의 말이 경고였는지 미끼였는지 알지 못한 채, 조금씩 리스본 쪽으로 기웁니다.</t>
         </is>
       </c>
     </row>
@@ -31826,7 +31826,7 @@
         <v>997</v>
       </c>
       <c r="B998" s="10" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C998" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B998)</f>
@@ -31834,18 +31834,18 @@
       </c>
       <c r="D998" s="10" t="inlineStr">
         <is>
-          <t>G 시즌2 독립 취재</t>
+          <t>F 시즌2 라 세르피엔테</t>
         </is>
       </c>
       <c r="E998" s="10" t="n">
-        <v>33568</v>
+        <v>33525</v>
       </c>
       <c r="F998" s="10" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G998" s="10" t="inlineStr">
         <is>
-          <t>일주일 후, 알바로와 하비에르가 라바피에스의 세입자 단체 '테초 후스토'를 찾아갑니다. 자원봉사 변호사 팔로마 에스쿠라가 같은 수법에 당한 피해자들을 모았고, 멕시코 출신 간호사 이첼과 모로코 출신 물류 노동자 하미드가 저마다의 억양으로 사연을 털어놓습니다.</t>
+          <t>2주 후, 12월 초의 이른 아침. 유럽수사명령을 받은 포르투갈 사법경찰이 레이레 반장의 팀과 함께 리스본 알칸타라의 아파트 문을 엽니다. 알바로는 마드리드 편집국에서 레이레가 약속한 짧은 문자 하나만 기다리고, 하비에르의 화면에는 열흘 전부터 "준비된" 기사 초안이 열려 있습니다. 그러나 문 뒤의 집은 갓 청소한 냄새만 남은 빈집이고, 부엌 식탁 위에는 12년 전 발렌시아 신문에 실린 레안드로 이바롤라의 부고 한 장만 놓여 있습니다. 오후, 국립법원 검사 킨타나르는 카를로스와 레이레를 불러 이 실패의 값을 정확한 법률 용어로 계산하고, 그날 밤 카를로스의 전화가 울립니다.</t>
         </is>
       </c>
     </row>
@@ -31854,7 +31854,7 @@
         <v>998</v>
       </c>
       <c r="B999" s="10" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C999" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B999)</f>
@@ -31862,18 +31862,18 @@
       </c>
       <c r="D999" s="10" t="inlineStr">
         <is>
-          <t>G 시즌2 독립 취재</t>
+          <t>F 시즌2 라 세르피엔테</t>
         </is>
       </c>
       <c r="E999" s="10" t="n">
-        <v>33628</v>
+        <v>33588</v>
       </c>
       <c r="F999" s="10" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="G999" s="10" t="inlineStr">
         <is>
-          <t>마르코스가 피해자들이 넘긴 매물 사진과 계약서 PDF를 분석하자, 사진이 2년 전 실제 매매 광고에서 통째로 복제되었다는 사실이 드러납니다. 알바로는 사진 속 집의 전 주인을 찾아가고, 그날 밤 카밀라가 돈의 흐름을 짚어 줍니다.</t>
+          <t>그 전날 밤, 빅토르의 새 집 우편함에서 보낸 사람 없는 봉투 하나가 발견되었습니다. 안에는 그가 이십 년 전 어느 기차역에서 잃어버렸던 것과 같은 크기의 흑색 체스 폰 하나가 들어 있었습니다. 프로그램은 그를 밤사이 다른 나라로 옮겼고, 몇 달 동안 쌓아 온 새 이름과 새 삶은 하룻밤에 끝났습니다. 다음 날 새벽, 낯선 호텔 방에서 연결된 화면 너머로 빅토르는 처음으로 늙어 보이고, 안전가옥의 팀은 이번에는 분명히 졌다는 사실을 각자의 방식으로 받아들입니다. 통화가 끝나기 직전, 헤르미니아의 전화가 리스본 항목이 적힌 장부 한 페이지에 대해 마지막 한 가지를 더 알려 줍니다.</t>
         </is>
       </c>
     </row>
@@ -31882,7 +31882,7 @@
         <v>999</v>
       </c>
       <c r="B1000" s="10" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C1000" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1000)</f>
@@ -31890,18 +31890,18 @@
       </c>
       <c r="D1000" s="10" t="inlineStr">
         <is>
-          <t>G 시즌2 독립 취재</t>
+          <t>F 시즌2 라 세르피엔테</t>
         </is>
       </c>
       <c r="E1000" s="10" t="n">
-        <v>33678</v>
+        <v>33652</v>
       </c>
       <c r="F1000" s="10" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="G1000" s="10" t="inlineStr">
         <is>
-          <t>알바로와 하비에르가 계약서에 집주인으로 이름이 오른 은퇴 교사 엔카르나시온 칼비요를 알칼라 데 에나레스의 자택으로 찾아갑니다. 이어 계좌 명의자인 콜롬비아 유학생 예페르손 아랑고를 만나면서, 피해자이자 가담자인 그를 어떻게 보도할지 윤리적 딜레마에 부딪힙니다.</t>
+          <t>2주 후, 크리스마스 직전의 안전가옥. 옆집 텔레비전에서는 성탄 복권 추첨 노래가 희미하게 들려오고, 화면 앞 빅토르의 의자는 비어 있습니다. 카를로스는 화이트보드를 지우는 대신 "확실한 것"과 "믿고 싶은 것" 두 칸으로 나누고, 카밀라는 안도라에서 리스본, 루가노로 이어지는 돈의 경로를 다시 그립니다. 레이레와 검사 킨타나르는 이번에는 공방 자체의 증거만으로, 증거가 지워지기 전에 움직이기로 합니다. [상대편] 같은 시각, 어느 항구 도시의 사무실에서 엘 사스트레는 우르비나에게 장부를 태우라는 전화를 겁니다.</t>
         </is>
       </c>
     </row>
@@ -31910,7 +31910,7 @@
         <v>1000</v>
       </c>
       <c r="B1001" s="10" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C1001" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1001)</f>
@@ -31918,18 +31918,18 @@
       </c>
       <c r="D1001" s="10" t="inlineStr">
         <is>
-          <t>G 시즌2 독립 취재</t>
+          <t>F 시즌2 라 세르피엔테</t>
         </is>
       </c>
       <c r="E1001" s="10" t="n">
-        <v>33728</v>
+        <v>33718</v>
       </c>
       <c r="F1001" s="10" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="G1001" s="10" t="inlineStr">
         <is>
-          <t>알바로와 하비에르가 임대 플랫폼 '피소야'의 신뢰·안전 책임자 노엘리아 사라비아를 만나 반론과 데이터를 요청하고, 신문사 변호사 마르타가 보도의 법적 선을 점검합니다. 그러나 확인 전화 한 통이 조직에 경고가 되었는지, 하룻밤 사이에 사이트와 연락처가 모두 사라집니다.</t>
+          <t>1월 중순의 어느 새벽. UCRIF가 판사의 영장을 들고 코슬라다의 그라피카스 시에르소와 우세라의 게스토리아에 동시에 들어갑니다. 알바로는 다른 기자들과 똑같이 경찰 통제선 밖 영하의 추위 속에 서 있고, 몇 시간 뒤 단체 사무실의 텔레비전 앞에서 아미나타는 화면 속 수갑 찬 하신토 로베라를 말없이 바라봅니다. 그날 저녁, 레이레는 기사에는 쓰지 않는다는 조건으로, 장부 원본이 불에 타기 직전의 금속통에서 발견되었다고만 짧게 확인해 줍니다.</t>
         </is>
       </c>
     </row>
@@ -31938,7 +31938,7 @@
         <v>1001</v>
       </c>
       <c r="B1002" s="10" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C1002" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1002)</f>
@@ -31946,18 +31946,18 @@
       </c>
       <c r="D1002" s="10" t="inlineStr">
         <is>
-          <t>G 시즌2 독립 취재</t>
+          <t>F 시즌2 라 세르피엔테</t>
         </is>
       </c>
       <c r="E1002" s="10" t="n">
-        <v>33778</v>
+        <v>33783</v>
       </c>
       <c r="F1002" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G1002" s="10" t="inlineStr">
         <is>
-          <t>3주 후, 이첼이 병원 신규 간호사들의 단체 대화방에서 똑같은 문구의 새 매물을 발견합니다. 이번에는 가짜 사진이 아니라 하루짜리 단기 임대 아파트에서 실제 내람을 열고 있었고, 알바로는 조카의 방을 구하는 손님으로 공개 내람에 참석합니다.</t>
+          <t>2주 후, 1월 말. 알바로는 정기 면회에서, 독일이 여권 사진 합성(모핑)을 막기 위해 관청이나 인증된 사진관에서 찍어 암호화 전송한 디지털 사진만 받도록 한 규정의 성과를 다룬 기사를 꺼냅니다. 로셀요는 "두 얼굴로 만든 얼굴은 누구의 것도 아니지만, 두 사람 모두에게 쓸모 있다"고 말하고, 리스본 이야기가 나오자 자신은 분명히 "아무도 살지 않는다"고 말했다며 물러서지 않습니다. 그날 오후 안전가옥에서는 유로폴의 바우트 페르하겐이 화상으로 합류한 회의가 열리고, 공방에서 압수된 S7 서류 사진 31장이 모두 합성이라는 사실과, 그중 여러 장에 공통으로 섞인 한 얼굴이 70대 노인의 것이라는 분석이 처음으로 테이블에 오릅니다.</t>
         </is>
       </c>
     </row>
@@ -31966,7 +31966,7 @@
         <v>1002</v>
       </c>
       <c r="B1003" s="10" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C1003" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1003)</f>
@@ -31974,18 +31974,18 @@
       </c>
       <c r="D1003" s="10" t="inlineStr">
         <is>
-          <t>G 시즌2 독립 취재</t>
+          <t>F 시즌2 라 세르피엔테</t>
         </is>
       </c>
       <c r="E1003" s="10" t="n">
-        <v>33836</v>
+        <v>33842</v>
       </c>
       <c r="F1003" s="10" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G1003" s="10" t="inlineStr">
         <is>
-          <t>알바로와 하비에르가 모든 자료를 정리해 국가경찰 사기 전담반의 이네스 코르발란 경감에게 넘기고, 린데로 측에 보낼 반론 질의서를 준비합니다. 경찰은 흩어져 있던 고소 수십 건을 하나로 묶어 움직이고, 마르타와 편집국장은 기사 출고를 두고 마지막 결정을 내립니다.</t>
+          <t>일주일 후, 2월 초. 카밀라가 신청했던 루가노(티치노 주) 상업등기의 등본과 첨부 서류 사본이 도착하고, 그녀는 알바트로스 해상위험 컨설팅사의 단독 이사 이름을 소리 내어 읽습니다. 카시미로 아르테아가 룬드, 1949년 탕헤르 국제구역 출생. 2022년 등기 서류에 첨부된 스위스 체류허가 사본 속 흐릿한 사진은 장례식 뒷줄의 노인, 그리고 역분해된 반쪽 얼굴과 똑같이 고개를 조금 왼쪽으로 숙이고 있습니다. 하비에르는 이제 기사라고 말하고, 알바로는 아직 아니라고 말합니다. [상대편] 같은 날 밤, 어느 항구 도시의 셋방에서 엘 사스트레는 짐을 꾸리며 코르소에게 노인이 남긴 녹색 잉크 메모를 읽어 줍니다.</t>
         </is>
       </c>
     </row>
@@ -31994,7 +31994,7 @@
         <v>1003</v>
       </c>
       <c r="B1004" s="10" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C1004" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1004)</f>
@@ -32002,18 +32002,18 @@
       </c>
       <c r="D1004" s="10" t="inlineStr">
         <is>
-          <t>G 시즌2 독립 취재</t>
+          <t>F 시즌2 라 세르피엔테</t>
         </is>
       </c>
       <c r="E1004" s="10" t="n">
-        <v>33887</v>
+        <v>33901</v>
       </c>
       <c r="F1004" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="G1004" s="10" t="inlineStr">
         <is>
-          <t>기사가 나간 뒤 몇 주가 흐릅니다. 피해 금액은 대부분 돌아오지 않았지만 테초 후스토에는 새 제보가 이어지고, 알바로와 하비에르는 줄리아와 이첼, 하미드가 새로 도착한 유학생과 이주민들에게 직접 '집 구하는 법'을 가르치는 워크숍을 찾아갑니다.</t>
+          <t>며칠 후. 알바로는 50년 만에 산탄데르의 한 시립도서관으로 익명 반납된 콘래드의 『로드 짐』에 관한 짧은 기사를 들고 면회실에 앉습니다. 책 여백을 가득 채운 녹색 잉크 메모 이야기를 꺼내자, 로셀요는 처음으로 대답보다 먼저 두 손을 탁자 위에서 거둬들이고, 알바로가 말한 적도 없는 "이름"을 모른다고 말합니다. 같은 주, 프로그램의 공식 승인을 받아 다시 연결된 화면 너머에서 빅토르는 단 한 장의 사진 앞에서 오래 침묵하다가, 자신이 확인할 수 있는 것과 없는 것을 정확히 나누어 말합니다.</t>
         </is>
       </c>
     </row>
@@ -32022,7 +32022,7 @@
         <v>1004</v>
       </c>
       <c r="B1005" s="10" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C1005" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1005)</f>
@@ -32030,18 +32030,18 @@
       </c>
       <c r="D1005" s="10" t="inlineStr">
         <is>
-          <t>G 시즌2 독립 취재</t>
+          <t>F 시즌2 라 세르피엔테</t>
         </is>
       </c>
       <c r="E1005" s="10" t="n">
-        <v>33939</v>
+        <v>33962</v>
       </c>
       <c r="F1005" s="10" t="n">
         <v>59</v>
       </c>
       <c r="G1005" s="10" t="inlineStr">
         <is>
-          <t>새로운 취재. 하비에르가 세비야 근교 도스 에르마나스에 사는 방문요양보호사 마카레나 에스테파의 편지를 알바로에게 건넵니다. 십오 년 동안 사고 한 번 없던 그녀의 자동차보험료가 일 년 만에 다섯 배로 뛰었고, 다른 보험사들은 아예 가입을 거절했다는 내용입니다. 알바로는 세비야로 내려가, 그녀에게 그날 아침의 일을 처음부터 다시 들려 달라고 부탁합니다.</t>
+          <t>3월 초, 신문사 회의실. 마르타는 기사 초안을 문장 단위로 잘라 출력해 테이블에 펼치고, 하비에르와 편집국장, 알바로는 단어 하나하나를 두고 다툽니다. 오후에는 국립법원 검찰청의 킨타나르 검사가 원고는 보지도 듣지도 않은 채 오직 시각과 안전만 묻고, 보도 시점은 판사의 국제체포영장 발부와 서류 경보 등록 이후로 정해집니다. 저녁 화상회의에서 미레유와 클라우스가 파리와 베를린의 마감을 맞추는 동안, 이틀 전 발송한 질문서의 기한 2분 전에 아르테아가의 변호사가 보낸 답장이 도착합니다. 단 세 줄입니다.</t>
         </is>
       </c>
     </row>
@@ -32050,7 +32050,7 @@
         <v>1005</v>
       </c>
       <c r="B1006" s="10" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C1006" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1006)</f>
@@ -32058,18 +32058,18 @@
       </c>
       <c r="D1006" s="10" t="inlineStr">
         <is>
-          <t>G 시즌2 독립 취재</t>
+          <t>F 시즌2 라 세르피엔테</t>
         </is>
       </c>
       <c r="E1006" s="10" t="n">
-        <v>34000</v>
+        <v>34023</v>
       </c>
       <c r="F1006" s="10" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G1006" s="10" t="inlineStr">
         <is>
-          <t>마드리드로 돌아온 알바로는 마르코스, 하비에르와 함께 마카레나가 지역 운전자 페이스북 그룹에 올린 하소연 글을 따라갑니다. 비슷한 사고를 당한 운전자 여섯 명이 보내온 사고 합의서 속에서, 같은 번호판과 같은 동승자 이름, 같은 의사와 같은 정비소가 계속 겹쳐 나타납니다. 그날 밤 카밀라는 상업등기부를 뒤지다 세 업체를 잇는 뜻밖의 연결고리를 찾아냅니다.</t>
+          <t>새벽 6시, 마드리드와 파리와 베를린에서 같은 얼굴이 동시에 1면에 실립니다. 편집국에는 환호 대신 식어 가는 커피와 키보드 소리뿐입니다. 하루 사이 스위스 당국은 알바트로스의 계좌를 동결하고, 이탈리아 경찰이 들어간 트리에스테의 집은 비어 있었으며, 그가 질문서를 받은 다음 날인 화요일에 이미 솅겐 지역 밖으로 나갔다는 사실이 확인됩니다. 체포는 없지만, 이제 그의 얼굴로는 어떤 국경도 넘을 수 없습니다. [상대편] 어느 항구의 빈 사무실에서 엘 사스트레는 신문을 접어 탁자에 두고 떠나고, 몇 주 뒤 알바로는 면회실에서 그 1면을 로셀요 앞에 펼쳐 놓습니다.</t>
         </is>
       </c>
     </row>
@@ -32078,7 +32078,7 @@
         <v>1006</v>
       </c>
       <c r="B1007" s="10" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C1007" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1007)</f>
@@ -32090,14 +32090,14 @@
         </is>
       </c>
       <c r="E1007" s="10" t="n">
-        <v>34056</v>
+        <v>34084</v>
       </c>
       <c r="F1007" s="10" t="n">
         <v>51</v>
       </c>
       <c r="G1007" s="10" t="inlineStr">
         <is>
-          <t>하비에르가 수년 전 보험사기 관련 세미나에서 발표했던 말라가의 한 보험사 사기조사관을 찾아냅니다. 알바로는 페드레갈레호 해변의 한 치링기토에서 '세구로스 알카사바'의 조사관 롤라 티라도를 만납니다. 그녀는 내부 자료는 줄 수 없다고 선을 그으면서도, 이 조직이 어떻게 움직이는지, 그리고 기자가 어디를 봐야 하는지를 알려 줍니다.</t>
+          <t>새로운 취재. 하비에르가 경제면 기자에게서 흘러나온 소문 하나를 들고 옵니다. 코슬라다에 본사를 둔 중견 공조설비 기업 '클리마티사시온 벤티스카'가 단 한 번의 화상회의 끝에 380만 유로를 해외로 송금했고, 회사는 이를 '전산 사고'라고만 발표했다는 것입니다. 그날 밤 알바로는 카밀라에게 'CEO 사기'의 구조를 묻습니다.</t>
         </is>
       </c>
     </row>
@@ -32106,7 +32106,7 @@
         <v>1007</v>
       </c>
       <c r="B1008" s="10" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C1008" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1008)</f>
@@ -32118,14 +32118,14 @@
         </is>
       </c>
       <c r="E1008" s="10" t="n">
-        <v>34109</v>
+        <v>34137</v>
       </c>
       <c r="F1008" s="10" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="G1008" s="10" t="inlineStr">
         <is>
-          <t>알바로와 하비에르가 세비야 동쪽의 문제의 회전교차로에서 현장 취재를 합니다. 교차로 옆 신문가판대 주인 마놀리는 이른 아침마다 같은 흰 차가 교차로를 맴도는 것을 봐 왔다고 말합니다. 두 사람은 오래된 중고차 광고 사진들 속에서 같은 찌그러짐을 확인한 뒤, 알칼라 데 과다이라의 정비소 뒤편에서 실제 그 차를 발견하지만, 정비소 주인 쿠로가 그들의 차 번호판을 휴대전화로 찍습니다.</t>
+          <t>며칠 후, 나탈리아 에스카르틴이 익명을 조건으로 만남에 응합니다. 마드리드 참베리의 조용한 카페 구석에서, 그녀는 그날의 화상회의를 처음으로 처음부터 끝까지 이야기합니다.</t>
         </is>
       </c>
     </row>
@@ -32134,7 +32134,7 @@
         <v>1008</v>
       </c>
       <c r="B1009" s="10" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C1009" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1009)</f>
@@ -32146,14 +32146,14 @@
         </is>
       </c>
       <c r="E1009" s="10" t="n">
-        <v>34169</v>
+        <v>34188</v>
       </c>
       <c r="F1009" s="10" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="G1009" s="10" t="inlineStr">
         <is>
-          <t>하비에르가 찾아낸 '부상 동승자' 이반 토스카노가 트리아나의 한 바에서 알바로를 만나는 데 동의합니다. 스물세 살의 이반은 사고 한 번에 삼백 유로를 받고 차에 탔고, 클리닉에는 첫날 한 번만 갔으며, 서류는 변호사 사무실에서 서명했다고 털어놓습니다. 그는 실명은 절대 안 된다며, 자신도 감옥에 가게 되느냐고 묻습니다.</t>
+          <t>마르코스가 녹화본을 프레임 단위로 분석합니다. 실시간 얼굴 합성과 음성 복제의 흔적을 하나씩 짚어 내던 그는, 기사에 쓸 시연 영상을 만들자고 제안하고, 편집국 안에서 작은 윤리 논쟁이 벌어집니다.</t>
         </is>
       </c>
     </row>
@@ -32162,7 +32162,7 @@
         <v>1009</v>
       </c>
       <c r="B1010" s="10" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C1010" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1010)</f>
@@ -32174,14 +32174,14 @@
         </is>
       </c>
       <c r="E1010" s="10" t="n">
-        <v>34228</v>
+        <v>34237</v>
       </c>
       <c r="F1010" s="10" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G1010" s="10" t="inlineStr">
         <is>
-          <t>며칠 후, 일이 꼬이기 시작합니다. 세바요스 변호사 사무소가 신문사와 마카레나 앞으로 명예훼손 고소를 경고하는 내용증명을 보내고, 겁에 질린 마카레나는 취재에서 빠지고 싶다고 연락해 옵니다. 마드리드에서는 마르타가 지금까지 모은 자료 중 무엇을 기사에 쓸 수 있고 무엇은 쓸 수 없는지 하나씩 가려냅니다.</t>
+          <t>카밀라와 하비에르가 나탈리아가 건넨 은행 서신을 토대로 돈의 흐름을 재구성합니다. 리투아니아 핀테크 계좌에서 스페인의 '머니 뮬' 계좌 열네 개로 쪼개진 돈의 끝에는 마드리드의 한 가상화폐 장외거래소가 있고, 알바로는 뮬 중 한 명인 열아홉 살 청년 브라이스 테이헤이로의 집을 찾아갑니다.</t>
         </is>
       </c>
     </row>
@@ -32190,7 +32190,7 @@
         <v>1010</v>
       </c>
       <c r="B1011" s="10" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C1011" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1011)</f>
@@ -32202,14 +32202,14 @@
         </is>
       </c>
       <c r="E1011" s="10" t="n">
-        <v>34283</v>
+        <v>34289</v>
       </c>
       <c r="F1011" s="10" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="G1011" s="10" t="inlineStr">
         <is>
-          <t>알바로가 직접 내려가 마카레나와 이야기한 끝에, 그녀는 먼저 경찰에 정식으로 고소장을 내고 나서 기사에 실명으로 나오기로 결심합니다. 신문사는 루피노 의사, 세바요스 변호사, 베누메아 정비소, 마카레나의 보험사에 반론권 질의서를 보냅니다. 루피노는 뜻밖에도 알바로를 클리닉으로 직접 불러 해명하겠다고 합니다.</t>
+          <t>알바로가 푸엔히롤라로 내려가 아르헨티나 출신의 전직 콜센터 직원 라우타로 이바르구렌을 만납니다. 그는 '소포르테 코스타솔'이라는 간판 뒤에서 벌어지던 일을 털어놓다가, 자신이 바로 브라이스를 끌어들인 '레오'였다고 고백합니다. 마드리드로 돌아온 알바로에게 카를로스가 경찰 수사 사실을 귀띔합니다.</t>
         </is>
       </c>
     </row>
@@ -32218,7 +32218,7 @@
         <v>1011</v>
       </c>
       <c r="B1012" s="10" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C1012" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1012)</f>
@@ -32230,14 +32230,14 @@
         </is>
       </c>
       <c r="E1012" s="10" t="n">
-        <v>34344</v>
+        <v>34338</v>
       </c>
       <c r="F1012" s="10" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G1012" s="10" t="inlineStr">
         <is>
-          <t>기사가 나가고 열흘 뒤, 국가경찰 세비야 사기수사팀이 오래전부터 진행해 온 수사에 따라 열한 명을 체포합니다. 그 명단에는 이반도 들어 있습니다. 마카레나는 경찰서에서 피해자로서 정식 진술을 하고, 알바로는 밖에서 기다립니다. 마지막 날, 막 운전면허를 딴 마카레나의 딸 칸델라가 알바로를 산타 후스타 역까지 태워다 줍니다.</t>
+          <t>마르코스의 시연은 예상보다 훨씬 쉽게 성공하고, 알바로는 은행 쪽으로 방향을 돌립니다. 반카 알코라 사기방지팀 출신 내부자는 그날 경보가 울렸었다고 증언하고, 은행 홍보책임자는 공식 인터뷰에서 모든 책임을 고객에게 돌립니다.</t>
         </is>
       </c>
     </row>
@@ -32246,7 +32246,7 @@
         <v>1012</v>
       </c>
       <c r="B1013" s="10" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C1013" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1013)</f>
@@ -32258,14 +32258,14 @@
         </is>
       </c>
       <c r="E1013" s="10" t="n">
-        <v>34403</v>
+        <v>34386</v>
       </c>
       <c r="F1013" s="10" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="G1013" s="10" t="inlineStr">
         <is>
-          <t>새로운 취재. 일요일 오후, 하비에르가 어린 시절부터 응원해 온 마드리드 남쪽의 3부 리그(프리메라 RFEF) 팀 CD 토레알바의 홈 경기에 알바로를 억지로 끌고 갑니다. 1대0으로 앞서던 경기는 막판 스무 살 골키퍼의 어이없는 실수와 주장의 이해할 수 없는 핸드볼 반칙으로 뒤집히고, 알바로는 관중석에서 휴대폰 두 대만 들여다보던 낯선 남자를 수상하게 여깁니다.</t>
+          <t>알바로가 반론권 인터뷰를 위해 벤티스카의 우고 살다냐 대표를 만납니다. 같은 날 저녁, 회사가 비밀유지 조건의 합의금을 제시했다며 나탈리아가 협조를 철회하고, 편집국에서는 마르타와 편집장이 무엇을 내보낼 수 있는지 한 줄씩 따지기 시작합니다.</t>
         </is>
       </c>
     </row>
@@ -32274,7 +32274,7 @@
         <v>1013</v>
       </c>
       <c r="B1014" s="10" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C1014" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1014)</f>
@@ -32286,14 +32286,14 @@
         </is>
       </c>
       <c r="E1014" s="10" t="n">
-        <v>34459</v>
+        <v>34434</v>
       </c>
       <c r="F1014" s="10" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G1014" s="10" t="inlineStr">
         <is>
-          <t>다음 날 아침, 하비에르가 밤새 해외 베팅 사이트의 배당률 기록을 뒤졌다며 충혈된 눈으로 편집국에 나타납니다. 마르코스의 소개로 스포츠 베팅 감시업체 '비히아 데이터'의 분석가 호세파 바라치나를 만난 두 사람은, 토레알바 경기에 아시아 불법 베팅 시장의 비정상적인 자금이 경기 전부터 몰렸다는 데이터를 확인합니다.</t>
+          <t>첫 기사가 나간 지 3주 뒤, 국가경찰이 푸엔히롤라의 콜센터를 급습하고 알바로는 약속대로 두 시간 안에 2부를 내보냅니다. 돌려받은 돈은 일부에 그치고 나탈리아는 끝내 이름을 드러내지 않지만, 그날 밤 알바로와 카밀라는 부엌 식탁에서 아주 사적인 약속 하나를 정합니다.</t>
         </is>
       </c>
     </row>
@@ -32302,7 +32302,7 @@
         <v>1014</v>
       </c>
       <c r="B1015" s="10" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C1015" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1015)</f>
@@ -32314,14 +32314,14 @@
         </is>
       </c>
       <c r="E1015" s="10" t="n">
-        <v>34507</v>
+        <v>34483</v>
       </c>
       <c r="F1015" s="10" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G1015" s="10" t="inlineStr">
         <is>
-          <t>주말, 알바로와 하비에르가 토레알바 마을의 서포터즈 바와 공개 훈련장을 찾아 현장 취재에 나섭니다. 밀린 임금과 함께, 선수단 절반을 관리하며 구단에 돈까지 빌려준 에이전트 라우레아노 야마스의 이름이 떠오르고, 하비에르는 겁에 질린 젊은 골키퍼에게 몰래 명함을 건넵니다. 그날 밤 카밀라는 구단의 공개 재무제표에서 수상한 대출을 찾아냅니다.</t>
+          <t>일상 에피소드. 어느 토요일 아침, 알바로가 약속대로 필라르 이모를 모시고 동네 시장에 장을 보러 갑니다. 이모는 단골 가게마다 들르며 값을 묻고 흥정하고, 알바로는 시장에서 쓰는 말과 '-ito' 축소사를 이모에게서 새삼 배우게 됩니다.</t>
         </is>
       </c>
     </row>
@@ -32330,7 +32330,7 @@
         <v>1015</v>
       </c>
       <c r="B1016" s="10" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C1016" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1016)</f>
@@ -32342,14 +32342,14 @@
         </is>
       </c>
       <c r="E1016" s="10" t="n">
-        <v>34569</v>
+        <v>34542</v>
       </c>
       <c r="F1016" s="10" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G1016" s="10" t="inlineStr">
         <is>
-          <t>며칠 후 새벽 한 시, 하비에르의 휴대폰에 모르는 번호로 "얘기할 수 있을까요?"라는 메시지가 옵니다. 고속도로 주유소 주차장에 세운 차 안에서 크리스티안은 자신이 돈을 받고 일부러 골을 내줬다고 털어놓고, 다음 경기에서 더 큰 요구와 협박을 받고 있다고 고백합니다.</t>
+          <t>새로운 취재. 하비에르가 이탈리아 에라스무스 교환학생 줄리아 페라레시의 제보 메일을 받습니다. 마드리드에 도착한 첫날, 석 달 치 돈을 미리 보낸 방이 존재하지 않는다는 사실을 알게 된 그녀를 알바로와 하비에르가 대학가 근처 카페에서 만납니다.</t>
         </is>
       </c>
     </row>
@@ -32358,7 +32358,7 @@
         <v>1016</v>
       </c>
       <c r="B1017" s="10" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C1017" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1017)</f>
@@ -32370,14 +32370,14 @@
         </is>
       </c>
       <c r="E1017" s="10" t="n">
-        <v>34625</v>
+        <v>34602</v>
       </c>
       <c r="F1017" s="10" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="G1017" s="10" t="inlineStr">
         <is>
-          <t>다음 날 아침, 편집국 회의실에서 마르타와 국장이 크리스티안의 고백과 캡처 사진을 검토합니다. 제보자가 동시에 범행 가담자라는 사실, 지금 보도하면 수사가 무너질 위험, 그리고 일요일 경기 전에 언론이 어디까지 해야 하는지를 두고 격론이 벌어지고, 알바로는 결국 라리가 인테그리티 부서에 먼저 전화를 겁니다.</t>
+          <t>일주일 후, 알바로와 하비에르가 라바피에스의 세입자 단체 '테초 후스토'를 찾아갑니다. 자원봉사 변호사 팔로마 에스쿠라가 같은 수법에 당한 피해자들을 모았고, 멕시코 출신 간호사 이첼과 모로코 출신 물류 노동자 하미드가 저마다의 억양으로 사연을 털어놓습니다.</t>
         </is>
       </c>
     </row>
@@ -32386,7 +32386,7 @@
         <v>1017</v>
       </c>
       <c r="B1018" s="10" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C1018" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1018)</f>
@@ -32398,14 +32398,14 @@
         </is>
       </c>
       <c r="E1018" s="10" t="n">
-        <v>34673</v>
+        <v>34662</v>
       </c>
       <c r="F1018" s="10" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G1018" s="10" t="inlineStr">
         <is>
-          <t>토요일 밤, 크리스티안의 차 유리가 박살 나고 어머니의 휴대폰에 협박 음성 메시지가 도착합니다. 겁에 질린 크리스티안은 연락을 끊고, 일요일 선두팀과의 경기에서 벤치에 앉습니다. 알바로와 하비에르는 편집국에서 호세파의 실시간 데이터를 보며 '예고된' 대패를 무력하게 지켜봅니다.</t>
+          <t>마르코스가 피해자들이 넘긴 매물 사진과 계약서 PDF를 분석하자, 사진이 2년 전 실제 매매 광고에서 통째로 복제되었다는 사실이 드러납니다. 알바로는 사진 속 집의 전 주인을 찾아가고, 그날 밤 카밀라가 돈의 흐름을 짚어 줍니다.</t>
         </is>
       </c>
     </row>
@@ -32414,7 +32414,7 @@
         <v>1018</v>
       </c>
       <c r="B1019" s="10" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C1019" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1019)</f>
@@ -32426,14 +32426,14 @@
         </is>
       </c>
       <c r="E1019" s="10" t="n">
-        <v>34726</v>
+        <v>34712</v>
       </c>
       <c r="F1019" s="10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G1019" s="10" t="inlineStr">
         <is>
-          <t>월요일, 크리스티안과 어머니 에우헤니아가 변호사와 함께 라리가 인테그리티 부서와 경찰청 UDEF 수사관에게 진술합니다. 기자들은 길 건너 카페에서 기다리고, 이스마엘 킨타나 경감은 알바로에게 열흘간의 보도 유예를 요청하며, 뒤늦게 도착한 마르타가 그 조건을 하나하나 협상합니다.</t>
+          <t>알바로와 하비에르가 계약서에 집주인으로 이름이 오른 은퇴 교사 엔카르나시온 칼비요를 알칼라 데 에나레스의 자택으로 찾아갑니다. 이어 계좌 명의자인 콜롬비아 유학생 예페르손 아랑고를 만나면서, 피해자이자 가담자인 그를 어떻게 보도할지 윤리적 딜레마에 부딪힙니다.</t>
         </is>
       </c>
     </row>
@@ -32442,7 +32442,7 @@
         <v>1019</v>
       </c>
       <c r="B1020" s="10" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C1020" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1020)</f>
@@ -32454,14 +32454,14 @@
         </is>
       </c>
       <c r="E1020" s="10" t="n">
-        <v>34774</v>
+        <v>34762</v>
       </c>
       <c r="F1020" s="10" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="G1020" s="10" t="inlineStr">
         <is>
-          <t>열흘 뒤 새벽, 경찰청이 '오프사이드 작전'을 개시해 라우레아노 야마스와 호세미 가야르도를 포함한 다섯 명을 체포합니다. 알바로는 구단 회장과 야마스의 변호인에게 반론권을 보장한 뒤 기사를 내보내고, 주말에는 하비에르와 함께 유소년 선수들로 급히 꾸려진 토레알바의 경기를 보러 엘 프라디요로 향합니다.</t>
+          <t>알바로와 하비에르가 임대 플랫폼 '피소야'의 신뢰·안전 책임자 노엘리아 사라비아를 만나 반론과 데이터를 요청하고, 신문사 변호사 마르타가 보도의 법적 선을 점검합니다. 그러나 확인 전화 한 통이 조직에 경고가 되었는지, 하룻밤 사이에 사이트와 연락처가 모두 사라집니다.</t>
         </is>
       </c>
     </row>
@@ -32470,7 +32470,7 @@
         <v>1020</v>
       </c>
       <c r="B1021" s="10" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C1021" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1021)</f>
@@ -32482,14 +32482,14 @@
         </is>
       </c>
       <c r="E1021" s="10" t="n">
-        <v>34835</v>
+        <v>34812</v>
       </c>
       <c r="F1021" s="10" t="n">
         <v>56</v>
       </c>
       <c r="G1021" s="10" t="inlineStr">
         <is>
-          <t>일상 에피소드. 알바로와 카밀라가 함께 사는 아파트의 임대 계약 만료가 다가오고, 집주인 올메도 씨가 계약 갱신 이야기를 하러 찾아옵니다. 두 사람은 집세 인상과 계약 조건을 정중하게 협상하는 한편, 몇 주째 고쳐지지 않은 보일러와 욕실 습기 문제도 꺼내기로 합니다.</t>
+          <t>3주 후, 이첼이 병원 신규 간호사들의 단체 대화방에서 똑같은 문구의 새 매물을 발견합니다. 이번에는 가짜 사진이 아니라 하루짜리 단기 임대 아파트에서 실제 내람을 열고 있었고, 알바로는 조카의 방을 구하는 손님으로 공개 내람에 참석합니다.</t>
         </is>
       </c>
     </row>
@@ -32498,7 +32498,7 @@
         <v>1021</v>
       </c>
       <c r="B1022" s="10" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C1022" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1022)</f>
@@ -32510,14 +32510,14 @@
         </is>
       </c>
       <c r="E1022" s="10" t="n">
-        <v>34893</v>
+        <v>34870</v>
       </c>
       <c r="F1022" s="10" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G1022" s="10" t="inlineStr">
         <is>
-          <t>새로운 취재. 하비에르가 마드리드의 고서 경매장 '카사 데 수바스타스 페냘베르'의 가을 카탈로그를 들고 알바로의 책상으로 옵니다. 표지에는 '미겔 데 세르반테스의 미공개 자필 편지'라는 문구가 큼직하게 박혀 있고, 가상의 국립 대학인 발데올모스 대학교 도서관이 공적 자금으로 이 편지를 사들일 예정이라는 소문이 돌고 있습니다.</t>
+          <t>알바로와 하비에르가 모든 자료를 정리해 국가경찰 사기 전담반의 이네스 코르발란 경감에게 넘기고, 린데로 측에 보낼 반론 질의서를 준비합니다. 경찰은 흩어져 있던 고소 수십 건을 하나로 묶어 움직이고, 마르타와 편집국장은 기사 출고를 두고 마지막 결정을 내립니다.</t>
         </is>
       </c>
     </row>
@@ -32526,7 +32526,7 @@
         <v>1022</v>
       </c>
       <c r="B1023" s="10" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C1023" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1023)</f>
@@ -32538,14 +32538,14 @@
         </is>
       </c>
       <c r="E1023" s="10" t="n">
-        <v>34948</v>
+        <v>34921</v>
       </c>
       <c r="F1023" s="10" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G1023" s="10" t="inlineStr">
         <is>
-          <t>며칠 후, 알바로가 발데올모스 대학교 도서관장 이네스 카르바할을 인터뷰합니다. 이네스는 편지 구입을 도서관 역사상 가장 중요한 순간이라 부르며 들떠 있고, 구입 전 상태 보고서를 맡은 보존 처리 전문가 오르텐시아 빌체스를 알바로에게 소개합니다.</t>
+          <t>기사가 나간 뒤 몇 주가 흐릅니다. 피해 금액은 대부분 돌아오지 않았지만 테초 후스토에는 새 제보가 이어지고, 알바로와 하비에르는 줄리아와 이첼, 하미드가 새로 도착한 유학생과 이주민들에게 직접 '집 구하는 법'을 가르치는 워크숍을 찾아갑니다.</t>
         </is>
       </c>
     </row>
@@ -32554,7 +32554,7 @@
         <v>1023</v>
       </c>
       <c r="B1024" s="10" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C1024" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1024)</f>
@@ -32566,14 +32566,14 @@
         </is>
       </c>
       <c r="E1024" s="10" t="n">
-        <v>35004</v>
+        <v>34973</v>
       </c>
       <c r="F1024" s="10" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G1024" s="10" t="inlineStr">
         <is>
-          <t>일주일 후, 도서관 복원 작업실. 오르텐시아가 레오노르를 외부 자문으로 초청하고, 형광 X선 분석 결과와 필적 감정이 같은 탁자 위에 펼쳐집니다. 알바로는 기록만 한다는 조건으로 그 자리에 함께합니다.</t>
+          <t>새로운 취재. 하비에르가 세비야 근교 도스 에르마나스에 사는 방문요양보호사 마카레나 에스테파의 편지를 알바로에게 건넵니다. 십오 년 동안 사고 한 번 없던 그녀의 자동차보험료가 일 년 만에 다섯 배로 뛰었고, 다른 보험사들은 아예 가입을 거절했다는 내용입니다. 알바로는 세비야로 내려가, 그녀에게 그날 아침의 일을 처음부터 다시 들려 달라고 부탁합니다.</t>
         </is>
       </c>
     </row>
@@ -32582,7 +32582,7 @@
         <v>1024</v>
       </c>
       <c r="B1025" s="10" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C1025" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1025)</f>
@@ -32594,14 +32594,14 @@
         </is>
       </c>
       <c r="E1025" s="10" t="n">
-        <v>35061</v>
+        <v>35034</v>
       </c>
       <c r="F1025" s="10" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G1025" s="10" t="inlineStr">
         <is>
-          <t>이틀 후, 레오노르와 하비에르는 세비야의 한 공증 기록 보관소에서 원본 문서철을 직접 확인하고, 마드리드에 남은 알바로는 마르코스와 함께 편지의 출처를 추적합니다. 그 과정에서 같은 경로로 '로페 데 베가의 편지'를 산 멕시코 수집가가 나타납니다.</t>
+          <t>마드리드로 돌아온 알바로는 마르코스, 하비에르와 함께 마카레나가 지역 운전자 페이스북 그룹에 올린 하소연 글을 따라갑니다. 비슷한 사고를 당한 운전자 여섯 명이 보내온 사고 합의서 속에서, 같은 번호판과 같은 동승자 이름, 같은 의사와 같은 정비소가 계속 겹쳐 나타납니다. 그날 밤 카밀라는 상업등기부를 뒤지다 세 업체를 잇는 뜻밖의 연결고리를 찾아냅니다.</t>
         </is>
       </c>
     </row>
@@ -32610,7 +32610,7 @@
         <v>1025</v>
       </c>
       <c r="B1026" s="10" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C1026" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1026)</f>
@@ -32622,14 +32622,14 @@
         </is>
       </c>
       <c r="E1026" s="10" t="n">
-        <v>35115</v>
+        <v>35090</v>
       </c>
       <c r="F1026" s="10" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G1026" s="10" t="inlineStr">
         <is>
-          <t>며칠 후, 알바로는 기자 신분을 밝힌 채 톨레도 근교의 작은 마을에 있는 바르톨로메 말도나도의 제본 공방을 찾아갑니다. 하비에르는 차 안에서 기다리고, 알바로는 녹음기를 탁자 위에 올려놓고 인터뷰를 시작합니다.</t>
+          <t>하비에르가 수년 전 보험사기 관련 세미나에서 발표했던 말라가의 한 보험사 사기조사관을 찾아냅니다. 알바로는 페드레갈레호 해변의 한 치링기토에서 '세구로스 알카사바'의 조사관 롤라 티라도를 만납니다. 그녀는 내부 자료는 줄 수 없다고 선을 그으면서도, 이 조직이 어떻게 움직이는지, 그리고 기자가 어디를 봐야 하는지를 알려 줍니다.</t>
         </is>
       </c>
     </row>
@@ -32638,7 +32638,7 @@
         <v>1026</v>
       </c>
       <c r="B1027" s="10" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C1027" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1027)</f>
@@ -32650,14 +32650,14 @@
         </is>
       </c>
       <c r="E1027" s="10" t="n">
-        <v>35171</v>
+        <v>35143</v>
       </c>
       <c r="F1027" s="10" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G1027" s="10" t="inlineStr">
         <is>
-          <t>다음 주, 카밀라가 '레가도스 이스팔렌세스'의 공개 재무제표를 분석하고, 알바로는 페냘베르 경매장의 전직 목록 담당 직원을 찾아 비공개 증언을 독립적으로 확인하려 합니다. 그러나 대학 이사회가 표결을 하루 앞당기면서, 신문사는 마르타의 법률 검토를 서둘러야 하는 압박에 놓입니다.</t>
+          <t>알바로와 하비에르가 세비야 동쪽의 문제의 회전교차로에서 현장 취재를 합니다. 교차로 옆 신문가판대 주인 마놀리는 이른 아침마다 같은 흰 차가 교차로를 맴도는 것을 봐 왔다고 말합니다. 두 사람은 오래된 중고차 광고 사진들 속에서 같은 찌그러짐을 확인한 뒤, 알칼라 데 과다이라의 정비소 뒤편에서 실제 그 차를 발견하지만, 정비소 주인 쿠로가 그들의 차 번호판을 휴대전화로 찍습니다.</t>
         </is>
       </c>
     </row>
@@ -32666,7 +32666,7 @@
         <v>1027</v>
       </c>
       <c r="B1028" s="10" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C1028" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1028)</f>
@@ -32678,14 +32678,14 @@
         </is>
       </c>
       <c r="E1028" s="10" t="n">
-        <v>35229</v>
+        <v>35203</v>
       </c>
       <c r="F1028" s="10" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G1028" s="10" t="inlineStr">
         <is>
-          <t>반론권 기한 마지막 날. 경매장 대표 루시오 페냘베르가 직접 전화를 걸어오고, 바르톨로메 말도나도는 17세기 문체로 쓴 긴 답장을 보내옵니다. 레오노르가 그 고어체 편지를 한 줄씩 풀어 읽는 동안, 기사는 마지막 손질을 거칩니다.</t>
+          <t>하비에르가 찾아낸 '부상 동승자' 이반 토스카노가 트리아나의 한 바에서 알바로를 만나는 데 동의합니다. 스물세 살의 이반은 사고 한 번에 삼백 유로를 받고 차에 탔고, 클리닉에는 첫날 한 번만 갔으며, 서류는 변호사 사무실에서 서명했다고 털어놓습니다. 그는 실명은 절대 안 된다며, 자신도 감옥에 가게 되느냐고 묻습니다.</t>
         </is>
       </c>
     </row>
@@ -32694,7 +32694,7 @@
         <v>1028</v>
       </c>
       <c r="B1029" s="10" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C1029" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1029)</f>
@@ -32706,14 +32706,14 @@
         </is>
       </c>
       <c r="E1029" s="10" t="n">
-        <v>35282</v>
+        <v>35262</v>
       </c>
       <c r="F1029" s="10" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G1029" s="10" t="inlineStr">
         <is>
-          <t>몇 주 후. 경찰 수사가 진행되고 바르톨로메 말도나도는 판사 앞에 피의자로 출석합니다. 알바로는 마지막 후속 기사를 준비하며 에프라인 우갈데, 이네스, 레오노르를 차례로 만나고, 이야기는 축배 대신 세비야 기록 보관소의 낡은 문서 한 장 앞에서 끝납니다.</t>
+          <t>며칠 후, 일이 꼬이기 시작합니다. 세바요스 변호사 사무소가 신문사와 마카레나 앞으로 명예훼손 고소를 경고하는 내용증명을 보내고, 겁에 질린 마카레나는 취재에서 빠지고 싶다고 연락해 옵니다. 마드리드에서는 마르타가 지금까지 모은 자료 중 무엇을 기사에 쓸 수 있고 무엇은 쓸 수 없는지 하나씩 가려냅니다.</t>
         </is>
       </c>
     </row>
@@ -32722,7 +32722,7 @@
         <v>1029</v>
       </c>
       <c r="B1030" s="10" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C1030" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1030)</f>
@@ -32734,14 +32734,14 @@
         </is>
       </c>
       <c r="E1030" s="10" t="n">
-        <v>35336</v>
+        <v>35317</v>
       </c>
       <c r="F1030" s="10" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G1030" s="10" t="inlineStr">
         <is>
-          <t>새로운 취재. 8월 말, 알바로와 하비에르가 베니도름 구시가지의 작은 기념품·아이스크림 가게를 찾아갑니다. 주인 페파 몰토는 성수기 단 한 주말에 위조 50유로 지폐 세 장을 받았고, 은행에 입금하려다 그 돈을 고스란히 잃었다고 털어놓습니다.</t>
+          <t>알바로가 직접 내려가 마카레나와 이야기한 끝에, 그녀는 먼저 경찰에 정식으로 고소장을 내고 나서 기사에 실명으로 나오기로 결심합니다. 신문사는 루피노 의사, 세바요스 변호사, 베누메아 정비소, 마카레나의 보험사에 반론권 질의서를 보냅니다. 루피노는 뜻밖에도 알바로를 클리닉으로 직접 불러 해명하겠다고 합니다.</t>
         </is>
       </c>
     </row>
@@ -32750,7 +32750,7 @@
         <v>1030</v>
       </c>
       <c r="B1031" s="10" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C1031" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1031)</f>
@@ -32762,14 +32762,14 @@
         </is>
       </c>
       <c r="E1031" s="10" t="n">
-        <v>35392</v>
+        <v>35378</v>
       </c>
       <c r="F1031" s="10" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G1031" s="10" t="inlineStr">
         <is>
-          <t>일주일 후, 알바로가 마드리드 스페인은행의 위조화폐 분석 센터를 방문합니다. 기술 분석관 젬마 벨베르가 진짜와 가짜 50유로를 나란히 놓고 워터마크, 보안선, 에메랄드 그린 숫자를 하나씩 설명하며, 이번 위조지폐가 왜 '보통 수준이 아닌지'를 보여 줍니다.</t>
+          <t>기사가 나가고 열흘 뒤, 국가경찰 세비야 사기수사팀이 오래전부터 진행해 온 수사에 따라 열한 명을 체포합니다. 그 명단에는 이반도 들어 있습니다. 마카레나는 경찰서에서 피해자로서 정식 진술을 하고, 알바로는 밖에서 기다립니다. 마지막 날, 막 운전면허를 딴 마카레나의 딸 칸델라가 알바로를 산타 후스타 역까지 태워다 줍니다.</t>
         </is>
       </c>
     </row>
@@ -32778,7 +32778,7 @@
         <v>1031</v>
       </c>
       <c r="B1032" s="10" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C1032" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1032)</f>
@@ -32790,14 +32790,14 @@
         </is>
       </c>
       <c r="E1032" s="10" t="n">
-        <v>35445</v>
+        <v>35437</v>
       </c>
       <c r="F1032" s="10" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G1032" s="10" t="inlineStr">
         <is>
-          <t>며칠 후, 알바로의 집. 금융 분석가 카밀라가 각 지역 경찰서와 상인 협회에서 모은 위조지폐 신고 날짜와 장소를 표로 정리해, 지폐가 휴가철 페리와 저가 항공 노선을 따라 움직인다는 사실을 발견합니다. 알바로는 이비사와 그란카나리아의 상인들과 화상 통화로 이야기를 나눕니다.</t>
+          <t>새로운 취재. 일요일 오후, 하비에르가 어린 시절부터 응원해 온 마드리드 남쪽의 3부 리그(프리메라 RFEF) 팀 CD 토레알바의 홈 경기에 알바로를 억지로 끌고 갑니다. 1대0으로 앞서던 경기는 막판 스무 살 골키퍼의 어이없는 실수와 주장의 이해할 수 없는 핸드볼 반칙으로 뒤집히고, 알바로는 관중석에서 휴대폰 두 대만 들여다보던 낯선 남자를 수상하게 여깁니다.</t>
         </is>
       </c>
     </row>
@@ -32806,7 +32806,7 @@
         <v>1032</v>
       </c>
       <c r="B1033" s="10" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C1033" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1033)</f>
@@ -32818,14 +32818,14 @@
         </is>
       </c>
       <c r="E1033" s="10" t="n">
-        <v>35497</v>
+        <v>35493</v>
       </c>
       <c r="F1033" s="10" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G1033" s="10" t="inlineStr">
         <is>
-          <t>알바로가 경찰청 '스페인은행 수사대'의 아벨 코로차노 경감을 만납니다. 경감은 고소 접수, 증거물 보관 절차, 유로폴과의 협력 등 수사 절차를 설명한 뒤, 진행 중인 작전을 위해 보도를 미뤄 달라고 요청합니다. 신문사에서는 편집장과 마르타가 상인들에게 경고하는 일과 수사를 지키는 일 사이에서 논쟁을 벌입니다.</t>
+          <t>다음 날 아침, 하비에르가 밤새 해외 베팅 사이트의 배당률 기록을 뒤졌다며 충혈된 눈으로 편집국에 나타납니다. 마르코스의 소개로 스포츠 베팅 감시업체 '비히아 데이터'의 분석가 호세파 바라치나를 만난 두 사람은, 토레알바 경기에 아시아 불법 베팅 시장의 비정상적인 자금이 경기 전부터 몰렸다는 데이터를 확인합니다.</t>
         </is>
       </c>
     </row>
@@ -32834,7 +32834,7 @@
         <v>1033</v>
       </c>
       <c r="B1034" s="10" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C1034" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1034)</f>
@@ -32846,14 +32846,14 @@
         </is>
       </c>
       <c r="E1034" s="10" t="n">
-        <v>35544</v>
+        <v>35541</v>
       </c>
       <c r="F1034" s="10" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G1034" s="10" t="inlineStr">
         <is>
-          <t>일요일 기사가 나간 뒤, 마르코스가 '소품용 지폐'를 판다는 온라인 판매 글과 택배 송장 사진에서 갈리시아 랄린의 주소를 찾아냅니다. 알바로와 하비에르는 그 주소와 이어진 인쇄소 '그라피카스 브라냐스'를 찾아가 반론 기회를 주지만, 사장 안쇼의 해명과 마르타의 경고 속에서 이 단서가 잘못된 것이었음을 깨닫습니다.</t>
+          <t>주말, 알바로와 하비에르가 토레알바 마을의 서포터즈 바와 공개 훈련장을 찾아 현장 취재에 나섭니다. 밀린 임금과 함께, 선수단 절반을 관리하며 구단에 돈까지 빌려준 에이전트 라우레아노 야마스의 이름이 떠오르고, 하비에르는 겁에 질린 젊은 골키퍼에게 몰래 명함을 건넵니다. 그날 밤 카밀라는 구단의 공개 재무제표에서 수상한 대출을 찾아냅니다.</t>
         </is>
       </c>
     </row>
@@ -32862,7 +32862,7 @@
         <v>1034</v>
       </c>
       <c r="B1035" s="10" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C1035" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1035)</f>
@@ -32874,14 +32874,14 @@
         </is>
       </c>
       <c r="E1035" s="10" t="n">
-        <v>35597</v>
+        <v>35603</v>
       </c>
       <c r="F1035" s="10" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G1035" s="10" t="inlineStr">
         <is>
-          <t>다음 날, 안쇼 브라냐스의 소개로 알바로가 빌라가르시아 근처의 작은 카페에서 젊은 인쇄 기술자 우시아 보우사스를 만납니다. 그녀는 몇 달 전까지 한 인쇄소의 야간 작업에 동원되었다고 고백하지만, 신원이 드러날까 두려워합니다. 알바로는 증언의 가치와 그녀를 보호해야 할 책임 사이에서 고민합니다.</t>
+          <t>며칠 후 새벽 한 시, 하비에르의 휴대폰에 모르는 번호로 "얘기할 수 있을까요?"라는 메시지가 옵니다. 고속도로 주유소 주차장에 세운 차 안에서 크리스티안은 자신이 돈을 받고 일부러 골을 내줬다고 털어놓고, 다음 경기에서 더 큰 요구와 협박을 받고 있다고 고백합니다.</t>
         </is>
       </c>
     </row>
@@ -32890,7 +32890,7 @@
         <v>1035</v>
       </c>
       <c r="B1036" s="10" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C1036" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1036)</f>
@@ -32902,14 +32902,14 @@
         </is>
       </c>
       <c r="E1036" s="10" t="n">
-        <v>35644</v>
+        <v>35659</v>
       </c>
       <c r="F1036" s="10" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="G1036" s="10" t="inlineStr">
         <is>
-          <t>알바로는 마르타와 함께 우시아의 신원을 노출하지 않으면서 무엇을 경찰에 넘길 수 있는지 검토합니다. 코로차노 경감은 판사의 영장으로 경찰이 작전을 진행할 때까지 기다려 달라고 하고, 작전 후 알바로는 압수 수량과 피의자 측 변호인의 반론을 확인하며 기사를 완성합니다.</t>
+          <t>다음 날 아침, 편집국 회의실에서 마르타와 국장이 크리스티안의 고백과 캡처 사진을 검토합니다. 제보자가 동시에 범행 가담자라는 사실, 지금 보도하면 수사가 무너질 위험, 그리고 일요일 경기 전에 언론이 어디까지 해야 하는지를 두고 격론이 벌어지고, 알바로는 결국 라리가 인테그리티 부서에 먼저 전화를 겁니다.</t>
         </is>
       </c>
     </row>
@@ -32918,7 +32918,7 @@
         <v>1036</v>
       </c>
       <c r="B1037" s="10" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C1037" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1037)</f>
@@ -32930,14 +32930,14 @@
         </is>
       </c>
       <c r="E1037" s="10" t="n">
-        <v>35700</v>
+        <v>35707</v>
       </c>
       <c r="F1037" s="10" t="n">
         <v>51</v>
       </c>
       <c r="G1037" s="10" t="inlineStr">
         <is>
-          <t>몇 주 후, 가을이 되어 한산해진 베니도름. 알바로가 기사를 들고 페파의 가게를 다시 찾습니다. 공장은 문을 닫았지만 상인들이 잃은 돈은 돌아오지 않았고, 페파는 그래도 자신의 방식으로 이 일을 마무리합니다.</t>
+          <t>토요일 밤, 크리스티안의 차 유리가 박살 나고 어머니의 휴대폰에 협박 음성 메시지가 도착합니다. 겁에 질린 크리스티안은 연락을 끊고, 일요일 선두팀과의 경기에서 벤치에 앉습니다. 알바로와 하비에르는 편집국에서 호세파의 실시간 데이터를 보며 '예고된' 대패를 무력하게 지켜봅니다.</t>
         </is>
       </c>
     </row>
@@ -32946,7 +32946,7 @@
         <v>1037</v>
       </c>
       <c r="B1038" s="10" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C1038" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1038)</f>
@@ -32958,14 +32958,14 @@
         </is>
       </c>
       <c r="E1038" s="10" t="n">
-        <v>35753</v>
+        <v>35760</v>
       </c>
       <c r="F1038" s="10" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G1038" s="10" t="inlineStr">
         <is>
-          <t>새로운 취재. 신문사 독자 메일함에 한 통의 편지가 도착합니다. 마드리드 남부 몬테스클라로스 지구에 사는 페트라 리사라수가, 가슴 통증으로 응급실을 찾은 아버지가 일곱 시간을 기다린 끝에 숨졌다고 호소합니다. 알바로는 병원 근처 카페에서 그녀를 만나고, 하비에르는 '같은 증상이라도 동네에 따라 대기 시간이 다르다'는 가설을 데이터로 검증하자고 제안합니다.</t>
+          <t>월요일, 크리스티안과 어머니 에우헤니아가 변호사와 함께 라리가 인테그리티 부서와 경찰청 UDEF 수사관에게 진술합니다. 기자들은 길 건너 카페에서 기다리고, 이스마엘 킨타나 경감은 알바로에게 열흘간의 보도 유예를 요청하며, 뒤늦게 도착한 마르타가 그 조건을 하나하나 협상합니다.</t>
         </is>
       </c>
     </row>
@@ -32974,7 +32974,7 @@
         <v>1038</v>
       </c>
       <c r="B1039" s="10" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C1039" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1039)</f>
@@ -32986,14 +32986,14 @@
         </is>
       </c>
       <c r="E1039" s="10" t="n">
-        <v>35805</v>
+        <v>35808</v>
       </c>
       <c r="F1039" s="10" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G1039" s="10" t="inlineStr">
         <is>
-          <t>5주 후, 컨세헤리아(지방 보건부)가 정보공개 청구에 일부만 응답하고, 하비에르는 투명성위원회에 이의신청을 냅니다. 그 사이 알바로는 로스 알멘드로스 응급실 간호사 아란차 레스카노를 만나 과밀 상황을 듣고, 하비에르의 첫 분석 결과가 나옵니다.</t>
+          <t>열흘 뒤 새벽, 경찰청이 '오프사이드 작전'을 개시해 라우레아노 야마스와 호세미 가야르도를 포함한 다섯 명을 체포합니다. 알바로는 구단 회장과 야마스의 변호인에게 반론권을 보장한 뒤 기사를 내보내고, 주말에는 하비에르와 함께 유소년 선수들로 급히 꾸려진 토레알바의 경기를 보러 엘 프라디요로 향합니다.</t>
         </is>
       </c>
     </row>
@@ -33002,7 +33002,7 @@
         <v>1039</v>
       </c>
       <c r="B1040" s="10" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C1040" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1040)</f>
@@ -33014,14 +33014,14 @@
         </is>
       </c>
       <c r="E1040" s="10" t="n">
-        <v>35856</v>
+        <v>35869</v>
       </c>
       <c r="F1040" s="10" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G1040" s="10" t="inlineStr">
         <is>
-          <t>석 달 후, 투명성위원회가 신문사의 손을 들어주고, 완전한 데이터가 도착합니다. 하비에르의 분석은 '네 배'라는 충격적인 수치를 보여 주지만, 역학자 네레아 올라바리아가 검토 과정에서 두 병원의 기록 방식이 다르다는 치명적인 문제를 찾아냅니다. 편집장은 헤드라인을 서두르고, 알바로는 숫자를 다시 계산하기로 합니다.</t>
+          <t>일상 에피소드. 알바로와 카밀라가 함께 사는 아파트의 임대 계약 만료가 다가오고, 집주인 올메도 씨가 계약 갱신 이야기를 하러 찾아옵니다. 두 사람은 집세 인상과 계약 조건을 정중하게 협상하는 한편, 몇 주째 고쳐지지 않은 보일러와 욕실 습기 문제도 꺼내기로 합니다.</t>
         </is>
       </c>
     </row>
@@ -33030,7 +33030,7 @@
         <v>1040</v>
       </c>
       <c r="B1041" s="10" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C1041" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1041)</f>
@@ -33042,14 +33042,14 @@
         </is>
       </c>
       <c r="E1041" s="10" t="n">
-        <v>35907</v>
+        <v>35927</v>
       </c>
       <c r="F1041" s="10" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G1041" s="10" t="inlineStr">
         <is>
-          <t>3주 후, 알바로가 로스 알멘드로스 응급실 의사 하산 벨카디를 인터뷰하고, 신문사 변호사 마르타와 함께 기사의 법률 검토를 진행합니다. 페트라는 아버지를 노란색으로 분류한 간호사의 이름을 기사에 넣어 달라고 요구하고, 알바로는 개인이 아닌 구조의 책임을 다루겠다며 거절합니다.</t>
+          <t>새로운 취재. 하비에르가 마드리드의 고서 경매장 '카사 데 수바스타스 페냘베르'의 가을 카탈로그를 들고 알바로의 책상으로 옵니다. 표지에는 '미겔 데 세르반테스의 미공개 자필 편지'라는 문구가 큼직하게 박혀 있고, 가상의 국립 대학인 발데올모스 대학교 도서관이 공적 자금으로 이 편지를 사들일 예정이라는 소문이 돌고 있습니다.</t>
         </is>
       </c>
     </row>
@@ -33058,7 +33058,7 @@
         <v>1041</v>
       </c>
       <c r="B1042" s="10" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C1042" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1042)</f>
@@ -33070,14 +33070,14 @@
         </is>
       </c>
       <c r="E1042" s="10" t="n">
-        <v>35955</v>
+        <v>35982</v>
       </c>
       <c r="F1042" s="10" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G1042" s="10" t="inlineStr">
         <is>
-          <t>일주일 후, 알바로는 컨세헤리아의 의료지원국장 레안드로 살세도에게 반론권 인터뷰를 진행합니다. 살세도는 인구 구성과 독감 시즌을 탓하지만, 데이터 앞에서 일부를 인정합니다. 기사가 나가고 몇 주 뒤, 알바로와 페트라는 로스 알멘드로스 대기실에서 다시 만납니다.</t>
+          <t>며칠 후, 알바로가 발데올모스 대학교 도서관장 이네스 카르바할을 인터뷰합니다. 이네스는 편지 구입을 도서관 역사상 가장 중요한 순간이라 부르며 들떠 있고, 구입 전 상태 보고서를 맡은 보존 처리 전문가 오르텐시아 빌체스를 알바로에게 소개합니다.</t>
         </is>
       </c>
     </row>
@@ -33086,7 +33086,7 @@
         <v>1042</v>
       </c>
       <c r="B1043" s="10" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C1043" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1043)</f>
@@ -33098,14 +33098,14 @@
         </is>
       </c>
       <c r="E1043" s="10" t="n">
-        <v>36009</v>
+        <v>36038</v>
       </c>
       <c r="F1043" s="10" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="G1043" s="10" t="inlineStr">
         <is>
-          <t>새로운 취재. 마드리드 남부의 가상 도시 토레베르메하에서 세입자협회 대변인 마이테 오수나가 신문사에 연락해 옵니다. 1999년 시가 지은 임대 공공주택 단지 '로스 틸로스' 312세대가 2014년 한 투자회사에 팔린 뒤 임대료가 두 배로 뛰고 퇴거가 잇따르고 있다는 것입니다. 알바로는 단지 안뜰에서 퇴거 날짜를 받아 둔 레히나 멘디빌과 에콰도르 출신 세입자 윌메르 치카이사를 만납니다.</t>
+          <t>일주일 후, 도서관 복원 작업실. 오르텐시아가 레오노르를 외부 자문으로 초청하고, 형광 X선 분석 결과와 필적 감정이 같은 탁자 위에 펼쳐집니다. 알바로는 기록만 한다는 조건으로 그 자리에 함께합니다.</t>
         </is>
       </c>
     </row>
@@ -33114,7 +33114,7 @@
         <v>1043</v>
       </c>
       <c r="B1044" s="10" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C1044" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1044)</f>
@@ -33126,14 +33126,14 @@
         </is>
       </c>
       <c r="E1044" s="10" t="n">
-        <v>36058</v>
+        <v>36095</v>
       </c>
       <c r="F1044" s="10" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G1044" s="10" t="inlineStr">
         <is>
-          <t>며칠 후, 알바로와 하비에르가 부동산 등기소에서 '노타 심플레(등기부 요약본)'를 떼어 로스 틸로스의 소유권 변동 이력을 추적합니다. 이어 시청 기록보관소에서 2014년 시의회 회의록을 열람하고, 그날 밤 카밀라가 매각 가격의 타당성을 분석합니다.</t>
+          <t>이틀 후, 레오노르와 하비에르는 세비야의 한 공증 기록 보관소에서 원본 문서철을 직접 확인하고, 마드리드에 남은 알바로는 마르코스와 함께 편지의 출처를 추적합니다. 그 과정에서 같은 경로로 '로페 데 베가의 편지'를 산 멕시코 수집가가 나타납니다.</t>
         </is>
       </c>
     </row>
@@ -33142,7 +33142,7 @@
         <v>1044</v>
       </c>
       <c r="B1045" s="10" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C1045" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1045)</f>
@@ -33154,14 +33154,14 @@
         </is>
       </c>
       <c r="E1045" s="10" t="n">
-        <v>36109</v>
+        <v>36149</v>
       </c>
       <c r="F1045" s="10" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G1045" s="10" t="inlineStr">
         <is>
-          <t>1주일 후, 알바로는 첫 번째 감정평가사 욜란다 가르멘디아를 인터뷰하고, 하비에르는 상업등기 관보에서 전 재무담당 시의원 우르키수가 펀드 계열 회사의 이사로 들어간 사실을 확인합니다. 그런데 퇴거를 앞둔 레히나가 갑자기 인터뷰를 철회하겠다고 알려 와, 알바로는 윤리적 딜레마에 빠집니다.</t>
+          <t>며칠 후, 알바로는 기자 신분을 밝힌 채 톨레도 근교의 작은 마을에 있는 바르톨로메 말도나도의 제본 공방을 찾아갑니다. 하비에르는 차 안에서 기다리고, 알바로는 녹음기를 탁자 위에 올려놓고 인터뷰를 시작합니다.</t>
         </is>
       </c>
     </row>
@@ -33170,7 +33170,7 @@
         <v>1045</v>
       </c>
       <c r="B1046" s="10" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C1046" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1046)</f>
@@ -33182,14 +33182,14 @@
         </is>
       </c>
       <c r="E1046" s="10" t="n">
-        <v>36157</v>
+        <v>36205</v>
       </c>
       <c r="F1046" s="10" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G1046" s="10" t="inlineStr">
         <is>
-          <t>2주 후, 마이테와 윌메르가 법률 클리닉 학생 다니엘라 텔레체아의 도움을 받아 옴부즈만과 검찰에 낼 공식 진정서를 작성합니다. 변호사 마르타는 기자가 진정서 작성에 관여해서는 안 된다고 선을 긋고, 알바로는 펀드 홍보책임자 올리비아 브란트와 전 시의원 우르키수에게 반론 기회를 줍니다.</t>
+          <t>다음 주, 카밀라가 '레가도스 이스팔렌세스'의 공개 재무제표를 분석하고, 알바로는 페냘베르 경매장의 전직 목록 담당 직원을 찾아 비공개 증언을 독립적으로 확인하려 합니다. 그러나 대학 이사회가 표결을 하루 앞당기면서, 신문사는 마르타의 법률 검토를 서둘러야 하는 압박에 놓입니다.</t>
         </is>
       </c>
     </row>
@@ -33198,7 +33198,7 @@
         <v>1046</v>
       </c>
       <c r="B1047" s="10" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C1047" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1047)</f>
@@ -33210,14 +33210,14 @@
         </is>
       </c>
       <c r="E1047" s="10" t="n">
-        <v>36205</v>
+        <v>36263</v>
       </c>
       <c r="F1047" s="10" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G1047" s="10" t="inlineStr">
         <is>
-          <t>몇 주 후, 기사가 나가자 검찰이 예비 조사에 착수하고 시의회는 매각 문제를 놓고 격론을 벌입니다. 그러나 레히나의 퇴거 날은 예정대로 찾아오고, 알바로는 그 아침 현장에 기자로서 증인이 됩니다.</t>
+          <t>반론권 기한 마지막 날. 경매장 대표 루시오 페냘베르가 직접 전화를 걸어오고, 바르톨로메 말도나도는 17세기 문체로 쓴 긴 답장을 보내옵니다. 레오노르가 그 고어체 편지를 한 줄씩 풀어 읽는 동안, 기사는 마지막 손질을 거칩니다.</t>
         </is>
       </c>
     </row>
@@ -33226,7 +33226,7 @@
         <v>1047</v>
       </c>
       <c r="B1048" s="10" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C1048" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1048)</f>
@@ -33238,14 +33238,14 @@
         </is>
       </c>
       <c r="E1048" s="10" t="n">
-        <v>36256</v>
+        <v>36316</v>
       </c>
       <c r="F1048" s="10" t="n">
         <v>52</v>
       </c>
       <c r="G1048" s="10" t="inlineStr">
         <is>
-          <t>새로운 취재. 마드리드 도심의 가상 동네 '산 바르톨로' 주민회가 신문사에 편지를 보내옵니다. 지난 십 년 사이 이웃들이 하나둘 떠나고 그 자리를 관광용 단기 임대 아파트가 채우고 있다는 내용입니다. 알바로와 하비에르는 주민회 대표 니카노르의 안내로 동네를 걸으며 첫 취재를 시작합니다.</t>
+          <t>몇 주 후. 경찰 수사가 진행되고 바르톨로메 말도나도는 판사 앞에 피의자로 출석합니다. 알바로는 마지막 후속 기사를 준비하며 에프라인 우갈데, 이네스, 레오노르를 차례로 만나고, 이야기는 축배 대신 세비야 기록 보관소의 낡은 문서 한 장 앞에서 끝납니다.</t>
         </is>
       </c>
     </row>
@@ -33254,7 +33254,7 @@
         <v>1048</v>
       </c>
       <c r="B1049" s="10" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C1049" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1049)</f>
@@ -33266,14 +33266,14 @@
         </is>
       </c>
       <c r="E1049" s="10" t="n">
-        <v>36310</v>
+        <v>36370</v>
       </c>
       <c r="F1049" s="10" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G1049" s="10" t="inlineStr">
         <is>
-          <t>알바로가 기술 분석가 마르코스, 도시지리학자 카리다드 아라발과 함께 데이터로 동네의 변화를 지도에 옮깁니다. 주민등록(파드론) 통계와 숙박 플랫폼 광고, 시청 허가 목록을 대조하던 중 첫 번째 지도에 중대한 오류가 발견됩니다. 카밀라는 '계절 임대'라는 법의 빈틈을 짚어 줍니다.</t>
+          <t>새로운 취재. 8월 말, 알바로와 하비에르가 베니도름 구시가지의 작은 기념품·아이스크림 가게를 찾아갑니다. 주인 페파 몰토는 성수기 단 한 주말에 위조 50유로 지폐 세 장을 받았고, 은행에 입금하려다 그 돈을 고스란히 잃었다고 털어놓습니다.</t>
         </is>
       </c>
     </row>
@@ -33282,7 +33282,7 @@
         <v>1049</v>
       </c>
       <c r="B1050" s="10" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C1050" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1050)</f>
@@ -33294,14 +33294,14 @@
         </is>
       </c>
       <c r="E1050" s="10" t="n">
-        <v>36362</v>
+        <v>36426</v>
       </c>
       <c r="F1050" s="10" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G1050" s="10" t="inlineStr">
         <is>
-          <t>일주일 후, 무허가로 관광 아파트를 운영하는 리사르도 야마사레스가 익명을 조건으로 인터뷰에 응합니다. 알바로는 그의 반론을 경청하고, 이어 관광객 덕분에 장사가 살아난 바 주인 고요와 아파트 청소로 생계를 꾸리는 콜롬비아 출신 발렌티나를 만납니다. 데이터로 그의 신원이 드러날 수 있다는 윤리적 딜레마가 생깁니다.</t>
+          <t>일주일 후, 알바로가 마드리드 스페인은행의 위조화폐 분석 센터를 방문합니다. 기술 분석관 젬마 벨베르가 진짜와 가짜 50유로를 나란히 놓고 워터마크, 보안선, 에메랄드 그린 숫자를 하나씩 설명하며, 이번 위조지폐가 왜 '보통 수준이 아닌지'를 보여 줍니다.</t>
         </is>
       </c>
     </row>
@@ -33310,7 +33310,7 @@
         <v>1050</v>
       </c>
       <c r="B1051" s="10" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C1051" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1051)</f>
@@ -33322,14 +33322,14 @@
         </is>
       </c>
       <c r="E1051" s="10" t="n">
-        <v>36416</v>
+        <v>36479</v>
       </c>
       <c r="F1051" s="10" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G1051" s="10" t="inlineStr">
         <is>
-          <t>부동산 펀드 토렐루스가 레메이에게 임대차 계약을 갱신하지 않겠다는 내용증명(부로팍스)을 보냅니다. 알바로는 펀드와 시청, 플랫폼에 반론권을 보장하기 위해 질문을 보내고, 신문사 변호사 마르타와 함께 기사 문구 하나하나를 법적으로 검토합니다.</t>
+          <t>며칠 후, 알바로의 집. 금융 분석가 카밀라가 각 지역 경찰서와 상인 협회에서 모은 위조지폐 신고 날짜와 장소를 표로 정리해, 지폐가 휴가철 페리와 저가 항공 노선을 따라 움직인다는 사실을 발견합니다. 알바로는 이비사와 그란카나리아의 상인들과 화상 통화로 이야기를 나눕니다.</t>
         </is>
       </c>
     </row>
@@ -33338,7 +33338,7 @@
         <v>1051</v>
       </c>
       <c r="B1052" s="10" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C1052" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1052)</f>
@@ -33350,14 +33350,14 @@
         </is>
       </c>
       <c r="E1052" s="10" t="n">
-        <v>36471</v>
+        <v>36531</v>
       </c>
       <c r="F1052" s="10" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G1052" s="10" t="inlineStr">
         <is>
-          <t>기사가 일요일판에 실린 뒤 동네는 찬반으로 갈라집니다. 주민회 회의에서는 고요와 리사르도의 목소리까지 엇갈리고, 시청은 단속을 약속하지만 레메이의 사정은 크게 달라지지 않습니다. 마지막으로 알바로는 그녀의 발코니에서 제라늄 화분을 건네받습니다.</t>
+          <t>알바로가 경찰청 '스페인은행 수사대'의 아벨 코로차노 경감을 만납니다. 경감은 고소 접수, 증거물 보관 절차, 유로폴과의 협력 등 수사 절차를 설명한 뒤, 진행 중인 작전을 위해 보도를 미뤄 달라고 요청합니다. 신문사에서는 편집장과 마르타가 상인들에게 경고하는 일과 수사를 지키는 일 사이에서 논쟁을 벌입니다.</t>
         </is>
       </c>
     </row>
@@ -33366,7 +33366,7 @@
         <v>1052</v>
       </c>
       <c r="B1053" s="10" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C1053" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1053)</f>
@@ -33378,14 +33378,14 @@
         </is>
       </c>
       <c r="E1053" s="10" t="n">
-        <v>36528</v>
+        <v>36578</v>
       </c>
       <c r="F1053" s="10" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G1053" s="10" t="inlineStr">
         <is>
-          <t>새로운 취재. 여든네 살의 로레토 에레로가 낡은 구두 상자 하나를 들고 신문사를 찾아옵니다. 1971년 가상의 '산 마카리오 병원'에서 낳은 딸이 태어나자마자 죽었다는 말을 들었지만, 그녀는 한 번도 아이의 시신을 보지 못했습니다. 아들 가스파르는 어머니가 또다시 상처받을까 걱정하며 곁을 지킵니다.</t>
+          <t>일요일 기사가 나간 뒤, 마르코스가 '소품용 지폐'를 판다는 온라인 판매 글과 택배 송장 사진에서 갈리시아 랄린의 주소를 찾아냅니다. 알바로와 하비에르는 그 주소와 이어진 인쇄소 '그라피카스 브라냐스'를 찾아가 반론 기회를 주지만, 사장 안쇼의 해명과 마르타의 경고 속에서 이 단서가 잘못된 것이었음을 깨닫습니다.</t>
         </is>
       </c>
     </row>
@@ -33394,7 +33394,7 @@
         <v>1053</v>
       </c>
       <c r="B1054" s="10" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C1054" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1054)</f>
@@ -33406,14 +33406,14 @@
         </is>
       </c>
       <c r="E1054" s="10" t="n">
-        <v>36580</v>
+        <v>36631</v>
       </c>
       <c r="F1054" s="10" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G1054" s="10" t="inlineStr">
         <is>
-          <t>알바로와 하비에르가 기록 보관소를 뒤집니다. 민원 등기소에서는 '사산아 기록부'에 이상한 흔적이 나오지만, 묘지 기록에는 아기의 매장 기록이 없습니다. 피해자 단체의 실비아가 당시의 수법을 설명해 주고, 문서관 풀헨시오의 도움으로 병원 분만 대장을 찾아내지만 1971년 10월의 한 장이 찢겨 나가 있습니다.</t>
+          <t>다음 날, 안쇼 브라냐스의 소개로 알바로가 빌라가르시아 근처의 작은 카페에서 젊은 인쇄 기술자 우시아 보우사스를 만납니다. 그녀는 몇 달 전까지 한 인쇄소의 야간 작업에 동원되었다고 고백하지만, 신원이 드러날까 두려워합니다. 알바로는 증언의 가치와 그녀를 보호해야 할 책임 사이에서 고민합니다.</t>
         </is>
       </c>
     </row>
@@ -33422,7 +33422,7 @@
         <v>1054</v>
       </c>
       <c r="B1055" s="10" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C1055" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1055)</f>
@@ -33434,14 +33434,14 @@
         </is>
       </c>
       <c r="E1055" s="10" t="n">
-        <v>36636</v>
+        <v>36678</v>
       </c>
       <c r="F1055" s="10" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G1055" s="10" t="inlineStr">
         <is>
-          <t>알바로가 아흔한 살의 은퇴 수녀 소르 비시타시온을 요양 시설에서 찾아냅니다. 오십오 년간 침묵해 온 그녀는 떨리는 목소리로 당시 병원에서 있었던 일을 털어놓고, 수도회 본원에 '원장의 장부'가 남아 있다고 알려 줍니다. 수도회 측과의 줄다리기 끝에 열람한 장부에서 결정적인 한 줄이 나옵니다.</t>
+          <t>알바로는 마르타와 함께 우시아의 신원을 노출하지 않으면서 무엇을 경찰에 넘길 수 있는지 검토합니다. 코로차노 경감은 판사의 영장으로 경찰이 작전을 진행할 때까지 기다려 달라고 하고, 작전 후 알바로는 압수 수량과 피의자 측 변호인의 반론을 확인하며 기사를 완성합니다.</t>
         </is>
       </c>
     </row>
@@ -33450,7 +33450,7 @@
         <v>1055</v>
       </c>
       <c r="B1056" s="10" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C1056" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1056)</f>
@@ -33462,14 +33462,14 @@
         </is>
       </c>
       <c r="E1056" s="10" t="n">
-        <v>36689</v>
+        <v>36734</v>
       </c>
       <c r="F1056" s="10" t="n">
         <v>51</v>
       </c>
       <c r="G1056" s="10" t="inlineStr">
         <is>
-          <t>로레토가 유전자 검사를 받지만, 국가 유전자 데이터베이스에서 일치하는 사람은 나오지 않습니다. 알바로와 하비에르는 발렌시아 교구 세례 기록을 통해 1971년 10월생 여성 아순시온 페란디스를 찾아내지만, 그녀의 신원을 공개하거나 먼저 연락하는 것이 옳은지 깊은 윤리적 고민에 빠집니다. 의사의 아들 셀레도니오는 반론권 인터뷰에서 아버지를 강하게 옹호합니다.</t>
+          <t>몇 주 후, 가을이 되어 한산해진 베니도름. 알바로가 기사를 들고 페파의 가게를 다시 찾습니다. 공장은 문을 닫았지만 상인들이 잃은 돈은 돌아오지 않았고, 페파는 그래도 자신의 방식으로 이 일을 마무리합니다.</t>
         </is>
       </c>
     </row>
@@ -33478,7 +33478,7 @@
         <v>1056</v>
       </c>
       <c r="B1057" s="10" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C1057" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1057)</f>
@@ -33490,14 +33490,14 @@
         </is>
       </c>
       <c r="E1057" s="10" t="n">
-        <v>36742</v>
+        <v>36787</v>
       </c>
       <c r="F1057" s="10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G1057" s="10" t="inlineStr">
         <is>
-          <t>기사가 실린 뒤, 실비아가 중재자로서 로레토의 편지를 아순시온에게 전달합니다. 몇 주 동안의 기다림 끝에 짧은 답장이 도착하지만, 그 안에 완전한 해답은 없습니다. 로레토는 늘 꽃을 놓던 묘지 담장을 다시 찾아갑니다.</t>
+          <t>새로운 취재. 신문사 독자 메일함에 한 통의 편지가 도착합니다. 마드리드 남부 몬테스클라로스 지구에 사는 페트라 리사라수가, 가슴 통증으로 응급실을 찾은 아버지가 일곱 시간을 기다린 끝에 숨졌다고 호소합니다. 알바로는 병원 근처 카페에서 그녀를 만나고, 하비에르는 '같은 증상이라도 동네에 따라 대기 시간이 다르다'는 가설을 데이터로 검증하자고 제안합니다.</t>
         </is>
       </c>
     </row>
@@ -33506,7 +33506,7 @@
         <v>1057</v>
       </c>
       <c r="B1058" s="10" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C1058" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1058)</f>
@@ -33518,14 +33518,14 @@
         </is>
       </c>
       <c r="E1058" s="10" t="n">
-        <v>36799</v>
+        <v>36839</v>
       </c>
       <c r="F1058" s="10" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G1058" s="10" t="inlineStr">
         <is>
-          <t>새로운 취재. 하비에르가 한 통의 손편지를 알바로에게 건넵니다. 카스티야 내륙의 가상 마을 '발데시에르소'에서 1936년 가을 사라진 일곱 남자가 마을 외곽의 들판에 묻혀 있다는 내용으로, 손녀 세대는 발굴을 원하고 노인들은 침묵을 원한다고 적혀 있습니다. 알바로는 마을을 찾아가 양쪽의 이야기를 처음으로 듣습니다.</t>
+          <t>5주 후, 컨세헤리아(지방 보건부)가 정보공개 청구에 일부만 응답하고, 하비에르는 투명성위원회에 이의신청을 냅니다. 그 사이 알바로는 로스 알멘드로스 응급실 간호사 아란차 레스카노를 만나 과밀 상황을 듣고, 하비에르의 첫 분석 결과가 나옵니다.</t>
         </is>
       </c>
     </row>
@@ -33534,7 +33534,7 @@
         <v>1058</v>
       </c>
       <c r="B1059" s="10" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C1059" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1059)</f>
@@ -33546,14 +33546,14 @@
         </is>
       </c>
       <c r="E1059" s="10" t="n">
-        <v>36851</v>
+        <v>36890</v>
       </c>
       <c r="F1059" s="10" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="G1059" s="10" t="inlineStr">
         <is>
-          <t>알바로가 발데시에르소에 사흘 더 머뭅니다. 은퇴한 교사이자 향토사가인 베니그노의 구술 기록 노트를 보고, 들판의 주인 몬카요가 출입을 거부하며, 법의고고학자 이치아르가 발굴 절차를 설명합니다. 그리고 마침내 피델라가 문을 엽니다.</t>
+          <t>석 달 후, 투명성위원회가 신문사의 손을 들어주고, 완전한 데이터가 도착합니다. 하비에르의 분석은 '네 배'라는 충격적인 수치를 보여 주지만, 역학자 네레아 올라바리아가 검토 과정에서 두 병원의 기록 방식이 다르다는 치명적인 문제를 찾아냅니다. 편집장은 헤드라인을 서두르고, 알바로는 숫자를 다시 계산하기로 합니다.</t>
         </is>
       </c>
     </row>
@@ -33562,7 +33562,7 @@
         <v>1059</v>
       </c>
       <c r="B1060" s="10" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C1060" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1060)</f>
@@ -33574,14 +33574,14 @@
         </is>
       </c>
       <c r="E1060" s="10" t="n">
-        <v>36911</v>
+        <v>36941</v>
       </c>
       <c r="F1060" s="10" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="G1060" s="10" t="inlineStr">
         <is>
-          <t>마드리드로 돌아온 알바로가 지방 문서보관소와 군사법원 기록에서 결정적인 서류를 찾습니다. 그러나 그 서류에는 에르미니오 집안의 이름이 있습니다. 편집국에서는 국장과 마르타가 용어 선택과 고인의 명예 문제를 놓고 알바로와 긴 회의를 엽니다. 그리고 예상치 못한 차질이 생깁니다.</t>
+          <t>3주 후, 알바로가 로스 알멘드로스 응급실 의사 하산 벨카디를 인터뷰하고, 신문사 변호사 마르타와 함께 기사의 법률 검토를 진행합니다. 페트라는 아버지를 노란색으로 분류한 간호사의 이름을 기사에 넣어 달라고 요구하고, 알바로는 개인이 아닌 구조의 책임을 다루겠다며 거절합니다.</t>
         </is>
       </c>
     </row>
@@ -33590,7 +33590,7 @@
         <v>1060</v>
       </c>
       <c r="B1061" s="10" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C1061" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1061)</f>
@@ -33602,14 +33602,14 @@
         </is>
       </c>
       <c r="E1061" s="10" t="n">
-        <v>36973</v>
+        <v>36989</v>
       </c>
       <c r="F1061" s="10" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G1061" s="10" t="inlineStr">
         <is>
-          <t>알바로가 다시 마을을 찾아 에르미니오와 마주 앉습니다. 노인은 아버지가 평생 지고 산 짐을 처음으로 털어놓습니다. 같은 주, 마을 회관에서 열린 임시 의회는 발굴 문제로 격하게 갈라지고, 알바로는 기사 제목 하나를 두고 다시 고민합니다.</t>
+          <t>일주일 후, 알바로는 컨세헤리아의 의료지원국장 레안드로 살세도에게 반론권 인터뷰를 진행합니다. 살세도는 인구 구성과 독감 시즌을 탓하지만, 데이터 앞에서 일부를 인정합니다. 기사가 나가고 몇 주 뒤, 알바로와 페트라는 로스 알멘드로스 대기실에서 다시 만납니다.</t>
         </is>
       </c>
     </row>
@@ -33618,7 +33618,7 @@
         <v>1061</v>
       </c>
       <c r="B1062" s="10" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C1062" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1062)</f>
@@ -33630,14 +33630,14 @@
         </is>
       </c>
       <c r="E1062" s="10" t="n">
-        <v>37031</v>
+        <v>37043</v>
       </c>
       <c r="F1062" s="10" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="G1062" s="10" t="inlineStr">
         <is>
-          <t>몇 주 후, 지표투과레이더 조사에서 이상 징후가 확인되고 발굴 허가가 나옵니다. 알바로는 마르타와 함께 최종 기사를 검토하며 에르미니오 부친의 이름 문제에 결론을 내립니다. 발굴 첫날, 알바로는 들판 가장자리에 선 마을 사람들을 지켜보며 기사의 마지막 문장을 끝내 쓰지 않습니다.</t>
+          <t>새로운 취재. 마드리드 남부의 가상 도시 토레베르메하에서 세입자협회 대변인 마이테 오수나가 신문사에 연락해 옵니다. 1999년 시가 지은 임대 공공주택 단지 '로스 틸로스' 312세대가 2014년 한 투자회사에 팔린 뒤 임대료가 두 배로 뛰고 퇴거가 잇따르고 있다는 것입니다. 알바로는 단지 안뜰에서 퇴거 날짜를 받아 둔 레히나 멘디빌과 에콰도르 출신 세입자 윌메르 치카이사를 만납니다.</t>
         </is>
       </c>
     </row>
@@ -33646,7 +33646,7 @@
         <v>1062</v>
       </c>
       <c r="B1063" s="10" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C1063" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1063)</f>
@@ -33661,11 +33661,11 @@
         <v>37092</v>
       </c>
       <c r="F1063" s="10" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="G1063" s="10" t="inlineStr">
         <is>
-          <t>새로운 취재. 마르코스가 배달 라이더들의 메신저 채널에서 모은 수백 장의 화면 캡처를 알바로에게 보여 줍니다. 가상의 배달 앱 '사스카(Zasca)'에서 사고를 당한 라이더들이 몇 주 뒤 줄줄이 계정 정지를 당했다는 내용입니다. 알바로는 노동 전문 변호사 모니카와 함께 사고 후 해고된 라이더 예이손을 만나고, 직접 라이더로 일해 보기로 결심합니다.</t>
+          <t>며칠 후, 알바로와 하비에르가 부동산 등기소에서 '노타 심플레(등기부 요약본)'를 떼어 로스 틸로스의 소유권 변동 이력을 추적합니다. 이어 시청 기록보관소에서 2014년 시의회 회의록을 열람하고, 그날 밤 카밀라가 매각 가격의 타당성을 분석합니다.</t>
         </is>
       </c>
     </row>
@@ -33674,7 +33674,7 @@
         <v>1063</v>
       </c>
       <c r="B1064" s="10" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C1064" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1064)</f>
@@ -33686,14 +33686,14 @@
         </is>
       </c>
       <c r="E1064" s="10" t="n">
-        <v>37152</v>
+        <v>37143</v>
       </c>
       <c r="F1064" s="10" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G1064" s="10" t="inlineStr">
         <is>
-          <t>다음 주 월요일, 알바로가 마드리드 남부 산업단지에 있는 '로히스티카 리켈메'에서 계약서에 서명하고 앱에 등록합니다. 첫 이틀 동안 그는 광장의 '대기 장소'에서 젊은 라이더 예라이와 베네수엘라 출신 다야나를 만나, 그들의 은어와 일하는 방식을 배우고 자신이 기자라는 사실을 밝힙니다.</t>
+          <t>1주일 후, 알바로는 첫 번째 감정평가사 욜란다 가르멘디아를 인터뷰하고, 하비에르는 상업등기 관보에서 전 재무담당 시의원 우르키수가 펀드 계열 회사의 이사로 들어간 사실을 확인합니다. 그런데 퇴거를 앞둔 레히나가 갑자기 인터뷰를 철회하겠다고 알려 와, 알바로는 윤리적 딜레마에 빠집니다.</t>
         </is>
       </c>
     </row>
@@ -33702,7 +33702,7 @@
         <v>1064</v>
       </c>
       <c r="B1065" s="10" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C1065" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1065)</f>
@@ -33714,14 +33714,14 @@
         </is>
       </c>
       <c r="E1065" s="10" t="n">
-        <v>37211</v>
+        <v>37191</v>
       </c>
       <c r="F1065" s="10" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="G1065" s="10" t="inlineStr">
         <is>
-          <t>라이더로 일한 지 나흘째, 빗길에서 예라이가 트램 선로에 미끄러져 넘어집니다. 알바로는 그를 응급실에 데려가고, 그 사이 자신의 주문이 '포기'로 처리되어 지수가 떨어집니다. 마르코스는 라이더 200여 명의 지수 기록을 분석하고, 계정을 빌려 일하는 아브두는 알바로에게 어려운 부탁을 합니다.</t>
+          <t>2주 후, 마이테와 윌메르가 법률 클리닉 학생 다니엘라 텔레체아의 도움을 받아 옴부즈만과 검찰에 낼 공식 진정서를 작성합니다. 변호사 마르타는 기자가 진정서 작성에 관여해서는 안 된다고 선을 긋고, 알바로는 펀드 홍보책임자 올리비아 브란트와 전 시의원 우르키수에게 반론 기회를 줍니다.</t>
         </is>
       </c>
     </row>
@@ -33730,7 +33730,7 @@
         <v>1065</v>
       </c>
       <c r="B1066" s="10" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C1066" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1066)</f>
@@ -33742,14 +33742,14 @@
         </is>
       </c>
       <c r="E1066" s="10" t="n">
-        <v>37266</v>
+        <v>37239</v>
       </c>
       <c r="F1066" s="10" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G1066" s="10" t="inlineStr">
         <is>
-          <t>전직 사스카 데이터 과학자 카탈리나가 내부고발자로 알바로를 만나 '신뢰도 지수' 모델의 구조를 설명합니다. 모니카는 관련 노동법을 정리하고, 마르타는 문서의 신빙성과 제보자 보호를 꼼꼼히 검토합니다. 그 사이 알바로의 계정이 갑자기 정지되는 차질이 생깁니다.</t>
+          <t>몇 주 후, 기사가 나가자 검찰이 예비 조사에 착수하고 시의회는 매각 문제를 놓고 격론을 벌입니다. 그러나 레히나의 퇴거 날은 예정대로 찾아오고, 알바로는 그 아침 현장에 기자로서 증인이 됩니다.</t>
         </is>
       </c>
     </row>
@@ -33758,7 +33758,7 @@
         <v>1066</v>
       </c>
       <c r="B1067" s="10" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C1067" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1067)</f>
@@ -33770,14 +33770,14 @@
         </is>
       </c>
       <c r="E1067" s="10" t="n">
-        <v>37320</v>
+        <v>37290</v>
       </c>
       <c r="F1067" s="10" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G1067" s="10" t="inlineStr">
         <is>
-          <t>알바로가 사스카 본사에서 공공정책 담당 이사 보르하와 반론 인터뷰를 합니다. 기사가 나간 뒤 회사는 사고 관련 신고를 지수 계산에서 제외하겠다고 발표하지만, 예이손의 복직은 여전히 법원의 판단을 기다립니다. 알바로는 배낭을 반납하러 물류센터를 찾고, 월요일 아침 열 시, 다야나의 휴대전화 화면에서 근무 시간대가 30초 만에 사라지는 것을 지켜봅니다.</t>
+          <t>새로운 취재. 마드리드 도심의 가상 동네 '산 바르톨로' 주민회가 신문사에 편지를 보내옵니다. 지난 십 년 사이 이웃들이 하나둘 떠나고 그 자리를 관광용 단기 임대 아파트가 채우고 있다는 내용입니다. 알바로와 하비에르는 주민회 대표 니카노르의 안내로 동네를 걸으며 첫 취재를 시작합니다.</t>
         </is>
       </c>
     </row>
@@ -33786,7 +33786,7 @@
         <v>1067</v>
       </c>
       <c r="B1068" s="10" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C1068" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1068)</f>
@@ -33798,14 +33798,14 @@
         </is>
       </c>
       <c r="E1068" s="10" t="n">
-        <v>37382</v>
+        <v>37344</v>
       </c>
       <c r="F1068" s="10" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G1068" s="10" t="inlineStr">
         <is>
-          <t>새로운 취재. 마드리드 근교의 가상 도시 토레시야 데 라 베가에서, 공립 고등학교 'IES 로스 알멘드로스'의 학부모회(AMPA) 회장 마틸데가 하비에르를 통해 연락해 옵니다. 지역 교육청이 6월 추가시험(convocatoria extraordinaria)에 도입한 온라인 시험감독 AI '투텔리아'가 특정 학생들만 골라 부정행위자로 표시했다는 것입니다. 알바로는 학교 체육관에서 열리는 긴급 학부모 총회에 직접 참석합니다.</t>
+          <t>알바로가 기술 분석가 마르코스, 도시지리학자 카리다드 아라발과 함께 데이터로 동네의 변화를 지도에 옮깁니다. 주민등록(파드론) 통계와 숙박 플랫폼 광고, 시청 허가 목록을 대조하던 중 첫 번째 지도에 중대한 오류가 발견됩니다. 카밀라는 '계절 임대'라는 법의 빈틈을 짚어 줍니다.</t>
         </is>
       </c>
     </row>
@@ -33814,7 +33814,7 @@
         <v>1068</v>
       </c>
       <c r="B1069" s="10" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C1069" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1069)</f>
@@ -33826,14 +33826,14 @@
         </is>
       </c>
       <c r="E1069" s="10" t="n">
-        <v>37432</v>
+        <v>37396</v>
       </c>
       <c r="F1069" s="10" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G1069" s="10" t="inlineStr">
         <is>
-          <t>일주일 후, AMPA가 모은 사례 자료를 들고 알바로가 신문사 데이터 분석가 마르코스, 그리고 대학 통계학자 케랄트와 마주 앉습니다. 숫자는 학부모들의 의심을 뒷받침하는 듯하지만, 케랄트는 표본의 한계부터 경고합니다. 그날 밤, 상담교사 비르투데스가 교육청 내부 시범운영 보고서를 들고 나타나고, 알바로는 제보자의 안전이라는 문제에 부딪힙니다.</t>
+          <t>일주일 후, 무허가로 관광 아파트를 운영하는 리사르도 야마사레스가 익명을 조건으로 인터뷰에 응합니다. 알바로는 그의 반론을 경청하고, 이어 관광객 덕분에 장사가 살아난 바 주인 고요와 아파트 청소로 생계를 꾸리는 콜롬비아 출신 발렌티나를 만납니다. 데이터로 그의 신원이 드러날 수 있다는 윤리적 딜레마가 생깁니다.</t>
         </is>
       </c>
     </row>
@@ -33842,7 +33842,7 @@
         <v>1069</v>
       </c>
       <c r="B1070" s="10" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C1070" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1070)</f>
@@ -33854,14 +33854,14 @@
         </is>
       </c>
       <c r="E1070" s="10" t="n">
-        <v>37482</v>
+        <v>37450</v>
       </c>
       <c r="F1070" s="10" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="G1070" s="10" t="inlineStr">
         <is>
-          <t>알바로가 교육청 평가국장 세바스티안 페냐우베르와 공식 인터뷰를 합니다. 공보담당 이랏체가 배석한 가운데 국장은 행정 용어로 무장한 답변을 이어 갑니다. 인터뷰가 끝난 뒤 알바로는 부모의 동의를 얻어 투렛 증후군을 가진 학생 토비아스와 직접 이야기를 나눕니다.</t>
+          <t>부동산 펀드 토렐루스가 레메이에게 임대차 계약을 갱신하지 않겠다는 내용증명(부로팍스)을 보냅니다. 알바로는 펀드와 시청, 플랫폼에 반론권을 보장하기 위해 질문을 보내고, 신문사 변호사 마르타와 함께 기사 문구 하나하나를 법적으로 검토합니다.</t>
         </is>
       </c>
     </row>
@@ -33870,7 +33870,7 @@
         <v>1070</v>
       </c>
       <c r="B1071" s="10" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C1071" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1071)</f>
@@ -33882,14 +33882,14 @@
         </is>
       </c>
       <c r="E1071" s="10" t="n">
-        <v>37544</v>
+        <v>37505</v>
       </c>
       <c r="F1071" s="10" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="G1071" s="10" t="inlineStr">
         <is>
-          <t>알바로가 변호사 마르타, 편집국장과 함께 기사의 법적 위험을 점검합니다. 미성년자 보호, 개인정보, 그리고 내부 문서 취급이 쟁점입니다. 그런데 투텔리아의 법률 대리인이 경고 서한을 보내오고, 두 번째 출처를 확보하지 못하면 핵심 문서를 쓸 수 없다는 결론이 납니다.</t>
+          <t>기사가 일요일판에 실린 뒤 동네는 찬반으로 갈라집니다. 주민회 회의에서는 고요와 리사르도의 목소리까지 엇갈리고, 시청은 단속을 약속하지만 레메이의 사정은 크게 달라지지 않습니다. 마지막으로 알바로는 그녀의 발코니에서 제라늄 화분을 건네받습니다.</t>
         </is>
       </c>
     </row>
@@ -33898,7 +33898,7 @@
         <v>1071</v>
       </c>
       <c r="B1072" s="10" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C1072" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1072)</f>
@@ -33910,14 +33910,14 @@
         </is>
       </c>
       <c r="E1072" s="10" t="n">
-        <v>37593</v>
+        <v>37562</v>
       </c>
       <c r="F1072" s="10" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G1072" s="10" t="inlineStr">
         <is>
-          <t>기사가 나간 뒤, 교육청은 투텔리아의 사용을 잠정 중단하고 무효 처리된 시험을 재검토하겠다고 발표합니다. 그러나 학부모 총회는 둘로 갈라지고, 기사의 대가는 예상치 못한 곳에서 돌아옵니다. 알바로는 학교 정문 앞에서 이 취재가 남긴 것들을 마주합니다.</t>
+          <t>새로운 취재. 여든네 살의 로레토 에레로가 낡은 구두 상자 하나를 들고 신문사를 찾아옵니다. 1971년 가상의 '산 마카리오 병원'에서 낳은 딸이 태어나자마자 죽었다는 말을 들었지만, 그녀는 한 번도 아이의 시신을 보지 못했습니다. 아들 가스파르는 어머니가 또다시 상처받을까 걱정하며 곁을 지킵니다.</t>
         </is>
       </c>
     </row>
@@ -33926,7 +33926,7 @@
         <v>1072</v>
       </c>
       <c r="B1073" s="10" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C1073" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1073)</f>
@@ -33938,14 +33938,14 @@
         </is>
       </c>
       <c r="E1073" s="10" t="n">
-        <v>37643</v>
+        <v>37614</v>
       </c>
       <c r="F1073" s="10" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G1073" s="10" t="inlineStr">
         <is>
-          <t>새로운 취재. "알마르사 강이 우리 아이들을 죽이고 있다"는 영상이 SNS에서 수십만 회 퍼집니다. 강 상류 화학공장 '키미르사' 아래쪽 마을 비야르 데 알마르사에서 소아암이 잇따랐다는 내용입니다. 편집국장은 빨리 쓰라고 재촉하지만, 알바로는 영상을 올린 노아와 백혈병 환아의 어머니 파울라를 먼저 만나러 갑니다.</t>
+          <t>알바로와 하비에르가 기록 보관소를 뒤집니다. 민원 등기소에서는 '사산아 기록부'에 이상한 흔적이 나오지만, 묘지 기록에는 아기의 매장 기록이 없습니다. 피해자 단체의 실비아가 당시의 수법을 설명해 주고, 문서관 풀헨시오의 도움으로 병원 분만 대장을 찾아내지만 1971년 10월의 한 장이 찢겨 나가 있습니다.</t>
         </is>
       </c>
     </row>
@@ -33954,7 +33954,7 @@
         <v>1073</v>
       </c>
       <c r="B1074" s="10" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C1074" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1074)</f>
@@ -33966,14 +33966,14 @@
         </is>
       </c>
       <c r="E1074" s="10" t="n">
-        <v>37693</v>
+        <v>37670</v>
       </c>
       <c r="F1074" s="10" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G1074" s="10" t="inlineStr">
         <is>
-          <t>며칠 후, 알바로가 바르셀로나의 역학자 몬세라트 프라츠를 찾아가 '군집(cluster)'을 어떻게 판단하는지 배웁니다. 관찰 건수와 기대 건수, 신뢰구간, 그리고 '텍사스 명사수의 오류'까지. 숫자는 무언가를 말하지만, 그것이 원인을 말해 주지는 않습니다.</t>
+          <t>알바로가 아흔한 살의 은퇴 수녀 소르 비시타시온을 요양 시설에서 찾아냅니다. 오십오 년간 침묵해 온 그녀는 떨리는 목소리로 당시 병원에서 있었던 일을 털어놓고, 수도회 본원에 '원장의 장부'가 남아 있다고 알려 줍니다. 수도회 측과의 줄다리기 끝에 열람한 장부에서 결정적인 한 줄이 나옵니다.</t>
         </is>
       </c>
     </row>
@@ -33982,7 +33982,7 @@
         <v>1074</v>
       </c>
       <c r="B1075" s="10" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C1075" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1075)</f>
@@ -33994,14 +33994,14 @@
         </is>
       </c>
       <c r="E1075" s="10" t="n">
-        <v>37743</v>
+        <v>37723</v>
       </c>
       <c r="F1075" s="10" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G1075" s="10" t="inlineStr">
         <is>
-          <t>알바로가 서류와 현장을 뒤집니다. 하천 관리청의 수질 분석 기록, 2018년 과징금 처분, 그리고 1990년대에 밤마다 탱크를 비웠다고 증언하는 전 공장 노동자 레미히오. 이어 키미르사의 환경담당 이사 오라시오 타보아다가 반론권을 행사하며 뜻밖에 자료를 내놓습니다.</t>
+          <t>로레토가 유전자 검사를 받지만, 국가 유전자 데이터베이스에서 일치하는 사람은 나오지 않습니다. 알바로와 하비에르는 발렌시아 교구 세례 기록을 통해 1971년 10월생 여성 아순시온 페란디스를 찾아내지만, 그녀의 신원을 공개하거나 먼저 연락하는 것이 옳은지 깊은 윤리적 고민에 빠집니다. 의사의 아들 셀레도니오는 반론권 인터뷰에서 아버지를 강하게 옹호합니다.</t>
         </is>
       </c>
     </row>
@@ -34010,7 +34010,7 @@
         <v>1075</v>
       </c>
       <c r="B1076" s="10" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C1076" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1076)</f>
@@ -34022,14 +34022,14 @@
         </is>
       </c>
       <c r="E1076" s="10" t="n">
-        <v>37793</v>
+        <v>37776</v>
       </c>
       <c r="F1076" s="10" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="G1076" s="10" t="inlineStr">
         <is>
-          <t>편집회의에서 알바로와 편집국장이 제목을 두고 정면으로 부딪힙니다. 변호사 마르타와 역학자 몬세라트의 조언 사이에서 기사의 표현 하나하나가 저울질됩니다. 그리고 그날 밤, 파울라는 신중한 기사 초안을 읽고 배신감을 토로합니다.</t>
+          <t>기사가 실린 뒤, 실비아가 중재자로서 로레토의 편지를 아순시온에게 전달합니다. 몇 주 동안의 기다림 끝에 짧은 답장이 도착하지만, 그 안에 완전한 해답은 없습니다. 로레토는 늘 꽃을 놓던 묘지 담장을 다시 찾아갑니다.</t>
         </is>
       </c>
     </row>
@@ -34038,7 +34038,7 @@
         <v>1076</v>
       </c>
       <c r="B1077" s="10" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C1077" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1077)</f>
@@ -34050,14 +34050,14 @@
         </is>
       </c>
       <c r="E1077" s="10" t="n">
-        <v>37842</v>
+        <v>37833</v>
       </c>
       <c r="F1077" s="10" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G1077" s="10" t="inlineStr">
         <is>
-          <t>기사가 나간 뒤, 지역 보건당국은 공식 역학조사를 발표하지만 결과까지는 2년이 걸린다고 말합니다. 노아는 알바로를 "미지근한 기자"라 부르고, 공장은 기사를 자신에게 유리하게 해석합니다. 알바로는 집에서 카밀라와 '불확실성'에 대해 이야기한 뒤, 마지막으로 소아암 병동의 파울라를 찾아갑니다.</t>
+          <t>새로운 취재. 하비에르가 한 통의 손편지를 알바로에게 건넵니다. 카스티야 내륙의 가상 마을 '발데시에르소'에서 1936년 가을 사라진 일곱 남자가 마을 외곽의 들판에 묻혀 있다는 내용으로, 손녀 세대는 발굴을 원하고 노인들은 침묵을 원한다고 적혀 있습니다. 알바로는 마을을 찾아가 양쪽의 이야기를 처음으로 듣습니다.</t>
         </is>
       </c>
     </row>
@@ -34066,7 +34066,7 @@
         <v>1077</v>
       </c>
       <c r="B1078" s="10" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C1078" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1078)</f>
@@ -34078,14 +34078,14 @@
         </is>
       </c>
       <c r="E1078" s="10" t="n">
-        <v>37897</v>
+        <v>37885</v>
       </c>
       <c r="F1078" s="10" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G1078" s="10" t="inlineStr">
         <is>
-          <t>새로운 취재. 3년째 이어지는 가뭄 속에, 과달키비르강 하류의 보호 습지 '마리스마 데 로스 알바라네스' 옆 마을 비야누에바 델 루시오에서 소농 토니 모야노가 신문사에 손편지를 보냅니다. 알바로와 하비에르는 직접 차를 몰고 내려가, 바닥이 드러난 석호와 밤마다 울리는 펌프 소리를 확인합니다.</t>
+          <t>알바로가 발데시에르소에 사흘 더 머뭅니다. 은퇴한 교사이자 향토사가인 베니그노의 구술 기록 노트를 보고, 들판의 주인 몬카요가 출입을 거부하며, 법의고고학자 이치아르가 발굴 절차를 설명합니다. 그리고 마침내 피델라가 문을 엽니다.</t>
         </is>
       </c>
     </row>
@@ -34094,7 +34094,7 @@
         <v>1078</v>
       </c>
       <c r="B1079" s="10" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C1079" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1079)</f>
@@ -34106,14 +34106,14 @@
         </is>
       </c>
       <c r="E1079" s="10" t="n">
-        <v>37958</v>
+        <v>37945</v>
       </c>
       <c r="F1079" s="10" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G1079" s="10" t="inlineStr">
         <is>
-          <t>몇 주 후 마드리드. 알바로는 마르코스와 함께 무료로 공개된 위성 사진을 분석해, 석호가 줄어드는 동안 아그로알바르의 관개 면적이 두 배로 늘어난 사실을 확인합니다. 이어 지역 배전회사 기술자 플로렌시오가 익명으로 넘긴 전력 소비 자료를 두고, 마르타와 함께 자료의 정당성과 제보자 보호 문제를 따집니다.</t>
+          <t>마드리드로 돌아온 알바로가 지방 문서보관소와 군사법원 기록에서 결정적인 서류를 찾습니다. 그러나 그 서류에는 에르미니오 집안의 이름이 있습니다. 편집국에서는 국장과 마르타가 용어 선택과 고인의 명예 문제를 놓고 알바로와 긴 회의를 엽니다. 그리고 예상치 못한 차질이 생깁니다.</t>
         </is>
       </c>
     </row>
@@ -34122,7 +34122,7 @@
         <v>1079</v>
       </c>
       <c r="B1080" s="10" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C1080" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1080)</f>
@@ -34134,14 +34134,14 @@
         </is>
       </c>
       <c r="E1080" s="10" t="n">
-        <v>38014</v>
+        <v>38007</v>
       </c>
       <c r="F1080" s="10" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G1080" s="10" t="inlineStr">
         <is>
-          <t>몇 주 후, 알바로는 다시 마을로 내려가 은퇴한 우물 굴착공 피델 킨테로를 만나 밤에 몰래 판 '관정'의 실체를 듣습니다. 그러나 소농 협동조합 모임에서 기사가 마을 전체의 생계를 끝장낼 것이라는 반발에 부딪히고, 토니마저 자기 밭에도 허가 없는 작은 우물이 있다고 털어놓으며 알바로는 딜레마에 빠집니다.</t>
+          <t>알바로가 다시 마을을 찾아 에르미니오와 마주 앉습니다. 노인은 아버지가 평생 지고 산 짐을 처음으로 털어놓습니다. 같은 주, 마을 회관에서 열린 임시 의회는 발굴 문제로 격하게 갈라지고, 알바로는 기사 제목 하나를 두고 다시 고민합니다.</t>
         </is>
       </c>
     </row>
@@ -34150,7 +34150,7 @@
         <v>1080</v>
       </c>
       <c r="B1081" s="10" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C1081" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1081)</f>
@@ -34162,14 +34162,14 @@
         </is>
       </c>
       <c r="E1081" s="10" t="n">
-        <v>38066</v>
+        <v>38065</v>
       </c>
       <c r="F1081" s="10" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G1081" s="10" t="inlineStr">
         <is>
-          <t>몇 주 후, 알바로는 대학의 수문지질학자 아이노아 살바티에라와 함께 습지의 지하수 관측공을 확인하고, 지하수위가 18미터나 낮아진 '양수 원뿔'의 증거를 얻습니다. 이어 세비야의 아그로알바르 본사에서 다미안 오헤다 대표에게 반론권을 보장하는 인터뷰를 하고, 마르타와 함께 기사의 표현 하나하나를 검토합니다.</t>
+          <t>몇 주 후, 지표투과레이더 조사에서 이상 징후가 확인되고 발굴 허가가 나옵니다. 알바로는 마르타와 함께 최종 기사를 검토하며 에르미니오 부친의 이름 문제에 결론을 내립니다. 발굴 첫날, 알바로는 들판 가장자리에 선 마을 사람들을 지켜보며 기사의 마지막 문장을 끝내 쓰지 않습니다.</t>
         </is>
       </c>
     </row>
@@ -34178,7 +34178,7 @@
         <v>1081</v>
       </c>
       <c r="B1082" s="10" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C1082" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1082)</f>
@@ -34190,14 +34190,14 @@
         </is>
       </c>
       <c r="E1082" s="10" t="n">
-        <v>38123</v>
+        <v>38126</v>
       </c>
       <c r="F1082" s="10" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="G1082" s="10" t="inlineStr">
         <is>
-          <t>몇 주 후, 기사가 나가고 유역 수자원청과 치안대 환경보호반(SEPRONA)이 합동 단속을 벌여 무허가 관정 19곳을 봉인합니다. 아그로알바르 직원들이 '마드리드 기자'에 항의하는 시위를 벌이고 마을은 둘로 갈라지지만, 토니는 스스로 자기 우물을 신고합니다. 마지막 장면, 알바로와 토니는 여전히 메마른 석호 가에 섭니다.</t>
+          <t>새로운 취재. 마르코스가 배달 라이더들의 메신저 채널에서 모은 수백 장의 화면 캡처를 알바로에게 보여 줍니다. 가상의 배달 앱 '사스카(Zasca)'에서 사고를 당한 라이더들이 몇 주 뒤 줄줄이 계정 정지를 당했다는 내용입니다. 알바로는 노동 전문 변호사 모니카와 함께 사고 후 해고된 라이더 예이손을 만나고, 직접 라이더로 일해 보기로 결심합니다.</t>
         </is>
       </c>
     </row>
@@ -34206,7 +34206,7 @@
         <v>1082</v>
       </c>
       <c r="B1083" s="10" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C1083" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1083)</f>
@@ -34218,14 +34218,14 @@
         </is>
       </c>
       <c r="E1083" s="10" t="n">
-        <v>38172</v>
+        <v>38186</v>
       </c>
       <c r="F1083" s="10" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G1083" s="10" t="inlineStr">
         <is>
-          <t>새로운 취재는 이번에는 실패에서 시작합니다. 알바로가 지역 의료조달청장 테레사 킨타니야가 1,400만 유로짜리 병상 계약을 특정 업체에 몰아줬다고 보도한 다음 날 아침, 기사의 핵심 증거였던 이메일이 위조됐다는 반박과 내용증명이 편집국에 도착합니다.</t>
+          <t>다음 주 월요일, 알바로가 마드리드 남부 산업단지에 있는 '로히스티카 리켈메'에서 계약서에 서명하고 앱에 등록합니다. 첫 이틀 동안 그는 광장의 '대기 장소'에서 젊은 라이더 예라이와 베네수엘라 출신 다야나를 만나, 그들의 은어와 일하는 방식을 배우고 자신이 기자라는 사실을 밝힙니다.</t>
         </is>
       </c>
     </row>
@@ -34234,7 +34234,7 @@
         <v>1083</v>
       </c>
       <c r="B1084" s="10" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C1084" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1084)</f>
@@ -34246,14 +34246,14 @@
         </is>
       </c>
       <c r="E1084" s="10" t="n">
-        <v>38224</v>
+        <v>38245</v>
       </c>
       <c r="F1084" s="10" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G1084" s="10" t="inlineStr">
         <is>
-          <t>알바로가 하비에르와 함께 밤늦게 자신의 취재수첩과 메시지 기록을 처음부터 다시 훑으며, 제보자 니콜라스 페드로사가 어떻게 자신을 속였는지 거꾸로 추적합니다. 하나씩 짚을수록, 속은 것만이 아니라 스스로 확인을 건너뛴 순간들이 드러납니다.</t>
+          <t>라이더로 일한 지 나흘째, 빗길에서 예라이가 트램 선로에 미끄러져 넘어집니다. 알바로는 그를 응급실에 데려가고, 그 사이 자신의 주문이 '포기'로 처리되어 지수가 떨어집니다. 마르코스는 라이더 200여 명의 지수 기록을 분석하고, 계정을 빌려 일하는 아브두는 알바로에게 어려운 부탁을 합니다.</t>
         </is>
       </c>
     </row>
@@ -34262,7 +34262,7 @@
         <v>1084</v>
       </c>
       <c r="B1085" s="10" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C1085" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1085)</f>
@@ -34274,14 +34274,14 @@
         </is>
       </c>
       <c r="E1085" s="10" t="n">
-        <v>38272</v>
+        <v>38300</v>
       </c>
       <c r="F1085" s="10" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G1085" s="10" t="inlineStr">
         <is>
-          <t>알바로는 마르타, 편집장과 함께 '거짓말한 제보자에게도 취재원 보호 의무가 남아 있는가'라는 윤리적 문제를 두고 격론을 벌입니다. 이어 마침내 페드로사를 찾아내 직접 대면하지만, 그는 반성은커녕 체면을 살려줄 '진짜 증거'를 내밀며 알바로를 다시 유혹합니다.</t>
+          <t>전직 사스카 데이터 과학자 카탈리나가 내부고발자로 알바로를 만나 '신뢰도 지수' 모델의 구조를 설명합니다. 모니카는 관련 노동법을 정리하고, 마르타는 문서의 신빙성과 제보자 보호를 꼼꼼히 검토합니다. 그 사이 알바로의 계정이 갑자기 정지되는 차질이 생깁니다.</t>
         </is>
       </c>
     </row>
@@ -34290,7 +34290,7 @@
         <v>1085</v>
       </c>
       <c r="B1086" s="10" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C1086" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1086)</f>
@@ -34302,14 +34302,14 @@
         </is>
       </c>
       <c r="E1086" s="10" t="n">
-        <v>38320</v>
+        <v>38354</v>
       </c>
       <c r="F1086" s="10" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="G1086" s="10" t="inlineStr">
         <is>
-          <t>알바로는 편집장, 마르타, 독자권익위원 앙헬라 올리벤사와 함께 정정·사과문을 한 문장씩 다듬으며, 법적 책임을 우려하는 표현과 진심 어린 사과 사이에서 줄다리기를 합니다. 그리고 변호사 고로스티사가 동석한 자리에서 킨타니야를 직접 만나 사과합니다.</t>
+          <t>알바로가 사스카 본사에서 공공정책 담당 이사 보르하와 반론 인터뷰를 합니다. 기사가 나간 뒤 회사는 사고 관련 신고를 지수 계산에서 제외하겠다고 발표하지만, 예이손의 복직은 여전히 법원의 판단을 기다립니다. 알바로는 배낭을 반납하러 물류센터를 찾고, 월요일 아침 열 시, 다야나의 휴대전화 화면에서 근무 시간대가 30초 만에 사라지는 것을 지켜봅니다.</t>
         </is>
       </c>
     </row>
@@ -34318,7 +34318,7 @@
         <v>1086</v>
       </c>
       <c r="B1087" s="10" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C1087" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1087)</f>
@@ -34330,14 +34330,14 @@
         </is>
       </c>
       <c r="E1087" s="10" t="n">
-        <v>38369</v>
+        <v>38416</v>
       </c>
       <c r="F1087" s="10" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G1087" s="10" t="inlineStr">
         <is>
-          <t>정정보도가 1면에 실린 뒤, 알바로는 독자들의 반응과 동료들의 시선, 그리고 자신에 대한 실망을 고스란히 감당합니다. 카밀라와의 밤 대화 끝에, 그는 자신이 어떻게 속았는지를 독자에게 숨김없이 밝히는 긴 글을 쓰고 조용히 다음 걸음을 내딛습니다.</t>
+          <t>새로운 취재. 마드리드 근교의 가상 도시 토레시야 데 라 베가에서, 공립 고등학교 'IES 로스 알멘드로스'의 학부모회(AMPA) 회장 마틸데가 하비에르를 통해 연락해 옵니다. 지역 교육청이 6월 추가시험(convocatoria extraordinaria)에 도입한 온라인 시험감독 AI '투텔리아'가 특정 학생들만 골라 부정행위자로 표시했다는 것입니다. 알바로는 학교 체육관에서 열리는 긴급 학부모 총회에 직접 참석합니다.</t>
         </is>
       </c>
     </row>
@@ -34346,7 +34346,7 @@
         <v>1087</v>
       </c>
       <c r="B1088" s="10" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C1088" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1088)</f>
@@ -34358,14 +34358,14 @@
         </is>
       </c>
       <c r="E1088" s="10" t="n">
-        <v>38418</v>
+        <v>38466</v>
       </c>
       <c r="F1088" s="10" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G1088" s="10" t="inlineStr">
         <is>
-          <t>새로운 취재는 하비에르의 일요일 면회에서 시작됩니다. 투자펀드 알데바란 캐피털에 인수된 요양원 체인 '레시덴시아스 솔라스'에서 지내는 어머니 과달루페의 이마에 멍이 들어 있고, 몰라보게 야위었습니다. 야간 요양보호사 로사 우아만이 조심스럽게 털어놓은 인력 사정을 들은 하비에르는 알바로에게 전화를 겁니다.</t>
+          <t>일주일 후, AMPA가 모은 사례 자료를 들고 알바로가 신문사 데이터 분석가 마르코스, 그리고 대학 통계학자 케랄트와 마주 앉습니다. 숫자는 학부모들의 의심을 뒷받침하는 듯하지만, 케랄트는 표본의 한계부터 경고합니다. 그날 밤, 상담교사 비르투데스가 교육청 내부 시범운영 보고서를 들고 나타나고, 알바로는 제보자의 안전이라는 문제에 부딪힙니다.</t>
         </is>
       </c>
     </row>
@@ -34374,7 +34374,7 @@
         <v>1088</v>
       </c>
       <c r="B1089" s="10" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C1089" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1089)</f>
@@ -34386,14 +34386,14 @@
         </is>
       </c>
       <c r="E1089" s="10" t="n">
-        <v>38473</v>
+        <v>38516</v>
       </c>
       <c r="F1089" s="10" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="G1089" s="10" t="inlineStr">
         <is>
-          <t>편집국에서 편집장은 이해충돌을 이유로 하비에르가 이 취재를 이끌 수 없다고 선을 긋고, 알바로가 책임을 맡습니다. 카밀라는 펀드의 회계 구조(건물 매각 후 재임차, 운영사에 떠넘긴 부채)를, 마르코스는 정보공개청구로 받은 감사 보고서 데이터를 분석합니다.</t>
+          <t>알바로가 교육청 평가국장 세바스티안 페냐우베르와 공식 인터뷰를 합니다. 공보담당 이랏체가 배석한 가운데 국장은 행정 용어로 무장한 답변을 이어 갑니다. 인터뷰가 끝난 뒤 알바로는 부모의 동의를 얻어 투렛 증후군을 가진 학생 토비아스와 직접 이야기를 나눕니다.</t>
         </is>
       </c>
     </row>
@@ -34402,7 +34402,7 @@
         <v>1089</v>
       </c>
       <c r="B1090" s="10" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C1090" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1090)</f>
@@ -34414,14 +34414,14 @@
         </is>
       </c>
       <c r="E1090" s="10" t="n">
-        <v>38520</v>
+        <v>38578</v>
       </c>
       <c r="F1090" s="10" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G1090" s="10" t="inlineStr">
         <is>
-          <t>알바로가 현장 취재에 나섭니다. 가족협회 대표 엘로이 이루르순를 만나고 전직 조리사와 요양보호사들을 인터뷰하지만, 회사가 '언론 접촉 금지' 내부 지침을 내리자 핵심 증언자인 로사가 겁에 질려 증언을 철회하려 합니다. 알바로는 그녀를 보호하는 일과 기사의 힘 사이에서 갈등합니다.</t>
+          <t>알바로가 변호사 마르타, 편집국장과 함께 기사의 법적 위험을 점검합니다. 미성년자 보호, 개인정보, 그리고 내부 문서 취급이 쟁점입니다. 그런데 투텔리아의 법률 대리인이 경고 서한을 보내오고, 두 번째 출처를 확보하지 못하면 핵심 문서를 쓸 수 없다는 결론이 납니다.</t>
         </is>
       </c>
     </row>
@@ -34430,7 +34430,7 @@
         <v>1090</v>
       </c>
       <c r="B1091" s="10" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C1091" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1091)</f>
@@ -34442,14 +34442,14 @@
         </is>
       </c>
       <c r="E1091" s="10" t="n">
-        <v>38571</v>
+        <v>38627</v>
       </c>
       <c r="F1091" s="10" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G1091" s="10" t="inlineStr">
         <is>
-          <t>알바로는 공공-민간 위탁 구조를 파고듭니다. 자치정부 돌봄국장 루르데스 알멘드랄을 인터뷰해 감독 체계의 허점을 확인하고, 마르타가 동석한 가운데 솔라스 운영이사 헤르바시오 아르테체에게 반론권을 보장합니다. 아르테체는 하비에르의 어머니를 은근히 언급하며 압박합니다.</t>
+          <t>기사가 나간 뒤, 교육청은 투텔리아의 사용을 잠정 중단하고 무효 처리된 시험을 재검토하겠다고 발표합니다. 그러나 학부모 총회는 둘로 갈라지고, 기사의 대가는 예상치 못한 곳에서 돌아옵니다. 알바로는 학교 정문 앞에서 이 취재가 남긴 것들을 마주합니다.</t>
         </is>
       </c>
     </row>
@@ -34458,7 +34458,7 @@
         <v>1091</v>
       </c>
       <c r="B1092" s="10" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C1092" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1092)</f>
@@ -34470,14 +34470,14 @@
         </is>
       </c>
       <c r="E1092" s="10" t="n">
-        <v>38626</v>
+        <v>38677</v>
       </c>
       <c r="F1092" s="10" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G1092" s="10" t="inlineStr">
         <is>
-          <t>기사가 이해충돌 고지와 함께 일요일 1면에 실립니다. 자치정부의 불시 감사와 인력 기준 강화 발표가 이어지지만, 펀드는 체인을 다른 펀드에 매각할 준비를 합니다. 하비에르는 어머니 곁에서 저녁을 먹이며, 무엇이 바뀌었고 무엇이 그대로인지 조용히 되새깁니다.</t>
+          <t>새로운 취재. "알마르사 강이 우리 아이들을 죽이고 있다"는 영상이 SNS에서 수십만 회 퍼집니다. 강 상류 화학공장 '키미르사' 아래쪽 마을 비야르 데 알마르사에서 소아암이 잇따랐다는 내용입니다. 편집국장은 빨리 쓰라고 재촉하지만, 알바로는 영상을 올린 노아와 백혈병 환아의 어머니 파울라를 먼저 만나러 갑니다.</t>
         </is>
       </c>
     </row>
@@ -34486,7 +34486,7 @@
         <v>1092</v>
       </c>
       <c r="B1093" s="10" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C1093" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1093)</f>
@@ -34498,14 +34498,14 @@
         </is>
       </c>
       <c r="E1093" s="10" t="n">
-        <v>38679</v>
+        <v>38727</v>
       </c>
       <c r="F1093" s="10" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G1093" s="10" t="inlineStr">
         <is>
-          <t>새로운 취재. 마드리드의 한 대학에 다니는 생물학과 학생 바네사가 캠퍼스 곳곳에 붙은 난자 기증 '보상금' 광고 전단을 들고 신문사를 찾아옵니다. 알바로와 하비에르는 편집국 회의실에서 그녀와 함께 광고 문구를 한 줄씩 뜯어보기 시작합니다.</t>
+          <t>며칠 후, 알바로가 바르셀로나의 역학자 몬세라트 프라츠를 찾아가 '군집(cluster)'을 어떻게 판단하는지 배웁니다. 관찰 건수와 기대 건수, 신뢰구간, 그리고 '텍사스 명사수의 오류'까지. 숫자는 무언가를 말하지만, 그것이 원인을 말해 주지는 않습니다.</t>
         </is>
       </c>
     </row>
@@ -34514,7 +34514,7 @@
         <v>1093</v>
       </c>
       <c r="B1094" s="10" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C1094" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1094)</f>
@@ -34526,14 +34526,14 @@
         </is>
       </c>
       <c r="E1094" s="10" t="n">
-        <v>38728</v>
+        <v>38777</v>
       </c>
       <c r="F1094" s="10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G1094" s="10" t="inlineStr">
         <is>
-          <t>몇 주 후, 알바로가 기증을 일곱 번 한 카나리아 출신 학생 사이라를 대학가 근처의 조용한 카페에서 만납니다. 이어서 그는 의료윤리 전문가인 고니 박사와 통화하며 사이라의 경험을 윤리적 원칙에 비추어 정리합니다.</t>
+          <t>알바로가 서류와 현장을 뒤집니다. 하천 관리청의 수질 분석 기록, 2018년 과징금 처분, 그리고 1990년대에 밤마다 탱크를 비웠다고 증언하는 전 공장 노동자 레미히오. 이어 키미르사의 환경담당 이사 오라시오 타보아다가 반론권을 행사하며 뜻밖에 자료를 내놓습니다.</t>
         </is>
       </c>
     </row>
@@ -34542,7 +34542,7 @@
         <v>1094</v>
       </c>
       <c r="B1095" s="10" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C1095" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1095)</f>
@@ -34554,14 +34554,14 @@
         </is>
       </c>
       <c r="E1095" s="10" t="n">
-        <v>38776</v>
+        <v>38827</v>
       </c>
       <c r="F1095" s="10" t="n">
         <v>47</v>
       </c>
       <c r="G1095" s="10" t="inlineStr">
         <is>
-          <t>알바로는 그룹 '페르티비아'의 전직 기증자 코디네이터 에두르네를 만나, 그녀가 퇴사 전에 보관한 기증자 데이터 파일을 받습니다. 마르코스가 데이터를 분석하던 중 사이라가 갑자기 증언을 철회하겠다고 연락해 오고, 신문사는 민감한 의료 정보를 어떻게 다뤄야 할지 윤리적 딜레마에 빠집니다.</t>
+          <t>편집회의에서 알바로와 편집국장이 제목을 두고 정면으로 부딪힙니다. 변호사 마르타와 역학자 몬세라트의 조언 사이에서 기사의 표현 하나하나가 저울질됩니다. 그리고 그날 밤, 파울라는 신중한 기사 초안을 읽고 배신감을 토로합니다.</t>
         </is>
       </c>
     </row>
@@ -34570,7 +34570,7 @@
         <v>1095</v>
       </c>
       <c r="B1096" s="10" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C1096" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1096)</f>
@@ -34582,14 +34582,14 @@
         </is>
       </c>
       <c r="E1096" s="10" t="n">
-        <v>38825</v>
+        <v>38876</v>
       </c>
       <c r="F1096" s="10" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G1096" s="10" t="inlineStr">
         <is>
-          <t>알바로가 반론권 보장을 위해 클리니카 나탈리스의 의료 책임자 라스에라스 박사와 홍보 담당자를 인터뷰합니다. 그 뒤 마르타와 함께 원고를 한 문장씩 법률 검토합니다.</t>
+          <t>기사가 나간 뒤, 지역 보건당국은 공식 역학조사를 발표하지만 결과까지는 2년이 걸린다고 말합니다. 노아는 알바로를 "미지근한 기자"라 부르고, 공장은 기사를 자신에게 유리하게 해석합니다. 알바로는 집에서 카밀라와 '불확실성'에 대해 이야기한 뒤, 마지막으로 소아암 병동의 파울라를 찾아갑니다.</t>
         </is>
       </c>
     </row>
@@ -34598,7 +34598,7 @@
         <v>1096</v>
       </c>
       <c r="B1097" s="10" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C1097" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1097)</f>
@@ -34610,14 +34610,14 @@
         </is>
       </c>
       <c r="E1097" s="10" t="n">
-        <v>38873</v>
+        <v>38931</v>
       </c>
       <c r="F1097" s="10" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="G1097" s="10" t="inlineStr">
         <is>
-          <t>보도가 나간 지 열흘 후, 바네사의 대학에서 학생회가 난자 기증에 관한 공개 토론회를 엽니다. 알바로는 객석 뒤편에서 토론을 지켜보고, 행사가 끝난 뒤 뜻밖의 이메일 한 통을 받습니다.</t>
+          <t>새로운 취재. 3년째 이어지는 가뭄 속에, 과달키비르강 하류의 보호 습지 '마리스마 데 로스 알바라네스' 옆 마을 비야누에바 델 루시오에서 소농 토니 모야노가 신문사에 손편지를 보냅니다. 알바로와 하비에르는 직접 차를 몰고 내려가, 바닥이 드러난 석호와 밤마다 울리는 펌프 소리를 확인합니다.</t>
         </is>
       </c>
     </row>
@@ -34626,7 +34626,7 @@
         <v>1097</v>
       </c>
       <c r="B1098" s="10" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C1098" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1098)</f>
@@ -34638,14 +34638,14 @@
         </is>
       </c>
       <c r="E1098" s="10" t="n">
-        <v>38923</v>
+        <v>38992</v>
       </c>
       <c r="F1098" s="10" t="n">
         <v>54</v>
       </c>
       <c r="G1098" s="10" t="inlineStr">
         <is>
-          <t>새로운 취재. 마드리드 남부의 간호사 마루하가 알바로의 칼럼을 읽고 이메일을 보내옵니다. 열일곱 살 아들 하코보가 아버지의 신분증으로 온라인 스포츠 도박 계정을 만들어 4천 유로 넘게 잃었다는 내용입니다. 알바로는 그 가족의 부엌 식탁에 앉아 이야기를 듣습니다.</t>
+          <t>몇 주 후 마드리드. 알바로는 마르코스와 함께 무료로 공개된 위성 사진을 분석해, 석호가 줄어드는 동안 아그로알바르의 관개 면적이 두 배로 늘어난 사실을 확인합니다. 이어 지역 배전회사 기술자 플로렌시오가 익명으로 넘긴 전력 소비 자료를 두고, 마르타와 함께 자료의 정당성과 제보자 보호 문제를 따집니다.</t>
         </is>
       </c>
     </row>
@@ -34654,7 +34654,7 @@
         <v>1098</v>
       </c>
       <c r="B1099" s="10" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C1099" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1099)</f>
@@ -34666,14 +34666,14 @@
         </is>
       </c>
       <c r="E1099" s="10" t="n">
-        <v>38979</v>
+        <v>39048</v>
       </c>
       <c r="F1099" s="10" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G1099" s="10" t="inlineStr">
         <is>
-          <t>몇 주 후, 알바로와 하비에르는 마르코스와 카밀라가 만든 데이터 지도를 들고 마드리드 남부의 학교 주변 도박장들을 직접 둘러봅니다. 하교 시간에 도박장 앞을 관찰하고, 고등학교 진로상담 교사와 도박장 직원을 인터뷰합니다.</t>
+          <t>몇 주 후, 알바로는 다시 마을로 내려가 은퇴한 우물 굴착공 피델 킨테로를 만나 밤에 몰래 판 '관정'의 실체를 듣습니다. 그러나 소농 협동조합 모임에서 기사가 마을 전체의 생계를 끝장낼 것이라는 반발에 부딪히고, 토니마저 자기 밭에도 허가 없는 작은 우물이 있다고 털어놓으며 알바로는 딜레마에 빠집니다.</t>
         </is>
       </c>
     </row>
@@ -34682,7 +34682,7 @@
         <v>1099</v>
       </c>
       <c r="B1100" s="10" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C1100" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1100)</f>
@@ -34694,14 +34694,14 @@
         </is>
       </c>
       <c r="E1100" s="10" t="n">
-        <v>39026</v>
+        <v>39100</v>
       </c>
       <c r="F1100" s="10" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="G1100" s="10" t="inlineStr">
         <is>
-          <t>알바로가 공립병원 행동중독 클리닉의 아리사발라가 박사를 찾아가 도박 중독의 심리학적 메커니즘을 묻습니다. 이후 부모와 마르타가 정한 조건 아래, 하코보가 처음으로 알바로와 단둘이 이야기하며 텔레그램 '팁스터'의 실체를 보여 줍니다.</t>
+          <t>몇 주 후, 알바로는 대학의 수문지질학자 아이노아 살바티에라와 함께 습지의 지하수 관측공을 확인하고, 지하수위가 18미터나 낮아진 '양수 원뿔'의 증거를 얻습니다. 이어 세비야의 아그로알바르 본사에서 다미안 오헤다 대표에게 반론권을 보장하는 인터뷰를 하고, 마르타와 함께 기사의 표현 하나하나를 검토합니다.</t>
         </is>
       </c>
     </row>
@@ -34710,7 +34710,7 @@
         <v>1100</v>
       </c>
       <c r="B1101" s="10" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C1101" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1101)</f>
@@ -34722,14 +34722,14 @@
         </is>
       </c>
       <c r="E1101" s="10" t="n">
-        <v>39074</v>
+        <v>39157</v>
       </c>
       <c r="F1101" s="10" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G1101" s="10" t="inlineStr">
         <is>
-          <t>알바로가 국회 근처 레스토랑에서 온라인 도박업계 협회의 대관 담당 오리올 벤드렐과 점심 인터뷰를 합니다. 그런데 그날 저녁, 하코보가 다시 도박을 했다는 소식이 들려오고, 알바로는 자신의 취재가 가족에게 상처가 되고 있는 건 아닌지 고민에 빠집니다.</t>
+          <t>몇 주 후, 기사가 나가고 유역 수자원청과 치안대 환경보호반(SEPRONA)이 합동 단속을 벌여 무허가 관정 19곳을 봉인합니다. 아그로알바르 직원들이 '마드리드 기자'에 항의하는 시위를 벌이고 마을은 둘로 갈라지지만, 토니는 스스로 자기 우물을 신고합니다. 마지막 장면, 알바로와 토니는 여전히 메마른 석호 가에 섭니다.</t>
         </is>
       </c>
     </row>
@@ -34738,7 +34738,7 @@
         <v>1101</v>
       </c>
       <c r="B1102" s="10" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C1102" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1102)</f>
@@ -34750,14 +34750,14 @@
         </is>
       </c>
       <c r="E1102" s="10" t="n">
-        <v>39127</v>
+        <v>39206</v>
       </c>
       <c r="F1102" s="10" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G1102" s="10" t="inlineStr">
         <is>
-          <t>보도가 나간 지 한 달 후, 하원 위원회에서 도박 광고 규제 개정안 청문회가 열리고 알바로는 기자석에서 벤드렐과 아리사발라가 박사의 발언을 듣습니다. 그 주말, 그는 동네 축구장에서 일라리오와 하코보를 다시 만납니다.</t>
+          <t>새로운 취재는 이번에는 실패에서 시작합니다. 알바로가 지역 의료조달청장 테레사 킨타니야가 1,400만 유로짜리 병상 계약을 특정 업체에 몰아줬다고 보도한 다음 날 아침, 기사의 핵심 증거였던 이메일이 위조됐다는 반박과 내용증명이 편집국에 도착합니다.</t>
         </is>
       </c>
     </row>
@@ -34766,7 +34766,7 @@
         <v>1102</v>
       </c>
       <c r="B1103" s="10" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C1103" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1103)</f>
@@ -34778,14 +34778,14 @@
         </is>
       </c>
       <c r="E1103" s="10" t="n">
-        <v>39176</v>
+        <v>39258</v>
       </c>
       <c r="F1103" s="10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G1103" s="10" t="inlineStr">
         <is>
-          <t>새로운 취재. 가상의 지방 철도 노선 발데카스트로 커브에서 87명이 숨진 탈선 사고가 일어난 지 6년, 알바로가 아무 언론도 찾지 않는 추모식에 갑니다. 공식 원인은 '기관사 과실'로 정리되었지만, 희생자 가족 협회장 아센시온은 6년간 답을 얻지 못한 질문들이 담긴 상자를 그에게 건넵니다.</t>
+          <t>알바로가 하비에르와 함께 밤늦게 자신의 취재수첩과 메시지 기록을 처음부터 다시 훑으며, 제보자 니콜라스 페드로사가 어떻게 자신을 속였는지 거꾸로 추적합니다. 하나씩 짚을수록, 속은 것만이 아니라 스스로 확인을 건너뛴 순간들이 드러납니다.</t>
         </is>
       </c>
     </row>
@@ -34794,7 +34794,7 @@
         <v>1103</v>
       </c>
       <c r="B1104" s="10" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C1104" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1104)</f>
@@ -34806,14 +34806,14 @@
         </is>
       </c>
       <c r="E1104" s="10" t="n">
-        <v>39226</v>
+        <v>39306</v>
       </c>
       <c r="F1104" s="10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G1104" s="10" t="inlineStr">
         <is>
-          <t>며칠 후, 알바로와 하비에르가 아빌라에 사는 은퇴 철도 기술자 루포 킨타날을 찾아가 공식 사고조사 보고서를 읽는 법을 배웁니다. 그는 '직접 원인'과 '기여 요인'의 차이, 주어 없는 문장과 '확인되지 않음' 같은 책임 회피형 표현을 하나씩 짚어 주고, 공개본의 부록 목록에서 빠진 문서 하나를 찾게 합니다.</t>
+          <t>알바로는 마르타, 편집장과 함께 '거짓말한 제보자에게도 취재원 보호 의무가 남아 있는가'라는 윤리적 문제를 두고 격론을 벌입니다. 이어 마침내 페드로사를 찾아내 직접 대면하지만, 그는 반성은커녕 체면을 살려줄 '진짜 증거'를 내밀며 알바로를 다시 유혹합니다.</t>
         </is>
       </c>
     </row>
@@ -34822,7 +34822,7 @@
         <v>1104</v>
       </c>
       <c r="B1105" s="10" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C1105" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1105)</f>
@@ -34834,14 +34834,14 @@
         </is>
       </c>
       <c r="E1105" s="10" t="n">
-        <v>39276</v>
+        <v>39354</v>
       </c>
       <c r="F1105" s="10" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="G1105" s="10" t="inlineStr">
         <is>
-          <t>석 달 후, 정보공개 청구가 거절되자 알바로는 당시 안전 부서 기술자였던 이시드로 오찬디아노를 찾아냅니다. 그가 건넨 내부 투자위원회 회의록에는 커브의 자동 감속 장치 설치가 '예산 사정에 따른 재조정'으로 미뤄진 기록과, 그가 직접 쓴 위험 경고 보고서가 들어 있습니다. 마르코스가 문서를 검증하고 마르타가 법적 위험을 따지는 사이, 이시드로는 신원 노출을 두려워해 손을 떼겠다고 합니다.</t>
+          <t>알바로는 편집장, 마르타, 독자권익위원 앙헬라 올리벤사와 함께 정정·사과문을 한 문장씩 다듬으며, 법적 책임을 우려하는 표현과 진심 어린 사과 사이에서 줄다리기를 합니다. 그리고 변호사 고로스티사가 동석한 자리에서 킨타니야를 직접 만나 사과합니다.</t>
         </is>
       </c>
     </row>
@@ -34850,7 +34850,7 @@
         <v>1105</v>
       </c>
       <c r="B1106" s="10" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C1106" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1106)</f>
@@ -34862,14 +34862,14 @@
         </is>
       </c>
       <c r="E1106" s="10" t="n">
-        <v>39334</v>
+        <v>39403</v>
       </c>
       <c r="F1106" s="10" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="G1106" s="10" t="inlineStr">
         <is>
-          <t>1년 후, 기관사 미켈 비요드레의 재판이 다가옵니다. 알바로가 그를 인터뷰한 사실이 알려지자 협회 일부가 배신감을 느끼고, 아센시온과의 관계가 흔들립니다. 한편 카밀라는 공개된 예산·결산 자료만으로 연기된 투자의 흔적을 독립적으로 재구성하고, 인프라라일 대변인은 반론권 질의에 책임 회피형 문구로만 답합니다.</t>
+          <t>정정보도가 1면에 실린 뒤, 알바로는 독자들의 반응과 동료들의 시선, 그리고 자신에 대한 실망을 고스란히 감당합니다. 카밀라와의 밤 대화 끝에, 그는 자신이 어떻게 속았는지를 독자에게 숨김없이 밝히는 긴 글을 쓰고 조용히 다음 걸음을 내딛습니다.</t>
         </is>
       </c>
     </row>
@@ -34878,7 +34878,7 @@
         <v>1106</v>
       </c>
       <c r="B1107" s="10" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C1107" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1107)</f>
@@ -34890,14 +34890,14 @@
         </is>
       </c>
       <c r="E1107" s="10" t="n">
-        <v>39393</v>
+        <v>39452</v>
       </c>
       <c r="F1107" s="10" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G1107" s="10" t="inlineStr">
         <is>
-          <t>2년이 더 흐릅니다. 보도 이후 법원이 인프라라일 전 임원들에 대한 수사를 재개했지만 위원회 구성원들은 '형사상 인과관계 없음'으로 불기소되고, 미켈만 유죄 판결을 받습니다. 사고 9주기 추모식에서 알바로는 아센시온, 가우덴시오, 그리고 처음으로 모습을 드러낸 이시드로와 함께, 기사가 바꾸지 못한 것과 바꾼 것을 마주합니다.</t>
+          <t>새로운 취재는 하비에르의 일요일 면회에서 시작됩니다. 투자펀드 알데바란 캐피털에 인수된 요양원 체인 '레시덴시아스 솔라스'에서 지내는 어머니 과달루페의 이마에 멍이 들어 있고, 몰라보게 야위었습니다. 야간 요양보호사 로사 우아만이 조심스럽게 털어놓은 인력 사정을 들은 하비에르는 알바로에게 전화를 겁니다.</t>
         </is>
       </c>
     </row>
@@ -34906,7 +34906,7 @@
         <v>1107</v>
       </c>
       <c r="B1108" s="10" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C1108" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1108)</f>
@@ -34918,14 +34918,14 @@
         </is>
       </c>
       <c r="E1108" s="10" t="n">
-        <v>39447</v>
+        <v>39507</v>
       </c>
       <c r="F1108" s="10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G1108" s="10" t="inlineStr">
         <is>
-          <t>새로운 취재. 7월 폭염 속, 알바로가 발렌시아 내륙의 가상 마을 베니알코르의 산불 현장을 취재합니다. 진화대장 아구스틴 보르다요는 불길과 씨름하다 "이 비탈은 두세 해마다 탄다, 늘 같은 자리에서"라고 무심코 내뱉고, 마을 사람들은 벌써 한 목동을 범인으로 지목하고 있습니다.</t>
+          <t>편집국에서 편집장은 이해충돌을 이유로 하비에르가 이 취재를 이끌 수 없다고 선을 긋고, 알바로가 책임을 맡습니다. 카밀라는 펀드의 회계 구조(건물 매각 후 재임차, 운영사에 떠넘긴 부채)를, 마르코스는 정보공개청구로 받은 감사 보고서 데이터를 분석합니다.</t>
         </is>
       </c>
     </row>
@@ -34934,7 +34934,7 @@
         <v>1108</v>
       </c>
       <c r="B1109" s="10" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C1109" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1109)</f>
@@ -34946,14 +34946,14 @@
         </is>
       </c>
       <c r="E1109" s="10" t="n">
-        <v>39495</v>
+        <v>39554</v>
       </c>
       <c r="F1109" s="10" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G1109" s="10" t="inlineStr">
         <is>
-          <t>마드리드로 돌아온 알바로는 마르코스, 그리고 원격탐사 연구자 아마야 고에나가와 함께 15년치 위성 영상을 분석합니다. 연소 지수로 산불 흔적을 겹치자 세레타 비탈이 여러 번 탄 것이 드러나고, 지적도와 등기부를 겹쳐 보니 불이 난 뒤마다 그 땅이 하나의 회사로 조금씩 넘어간 사실이 보입니다.</t>
+          <t>알바로가 현장 취재에 나섭니다. 가족협회 대표 엘로이 이루르순를 만나고 전직 조리사와 요양보호사들을 인터뷰하지만, 회사가 '언론 접촉 금지' 내부 지침을 내리자 핵심 증언자인 로사가 겁에 질려 증언을 철회하려 합니다. 알바로는 그녀를 보호하는 일과 기사의 힘 사이에서 갈등합니다.</t>
         </is>
       </c>
     </row>
@@ -34962,7 +34962,7 @@
         <v>1109</v>
       </c>
       <c r="B1110" s="10" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C1110" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1110)</f>
@@ -34974,14 +34974,14 @@
         </is>
       </c>
       <c r="E1110" s="10" t="n">
-        <v>39544</v>
+        <v>39605</v>
       </c>
       <c r="F1110" s="10" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G1110" s="10" t="inlineStr">
         <is>
-          <t>몇 주 후, 하비에르와 알바로가 베니알코르 시청을 찾아 지난 15년간의 본회의 회의록을 열람합니다. 퇴직한 시청 서기 베르나르도 마스카렐이 도시계획 변경 절차를 설명해 주고, 두 사람은 '산불 피해 산림은 30년간 용도 변경 금지' 규정을 피해 간 예외 조항과, 불이 난 뒤에 '정정'된 회의록 한 장을 찾아냅니다. 그러나 마르타는 '방화'를 암시하는 순간 기사가 무너진다고 경고합니다.</t>
+          <t>알바로는 공공-민간 위탁 구조를 파고듭니다. 자치정부 돌봄국장 루르데스 알멘드랄을 인터뷰해 감독 체계의 허점을 확인하고, 마르타가 동석한 가운데 솔라스 운영이사 헤르바시오 아르테체에게 반론권을 보장합니다. 아르테체는 하비에르의 어머니를 은근히 언급하며 압박합니다.</t>
         </is>
       </c>
     </row>
@@ -34990,7 +34990,7 @@
         <v>1110</v>
       </c>
       <c r="B1111" s="10" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C1111" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1111)</f>
@@ -35002,14 +35002,14 @@
         </is>
       </c>
       <c r="E1111" s="10" t="n">
-        <v>39593</v>
+        <v>39660</v>
       </c>
       <c r="F1111" s="10" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G1111" s="10" t="inlineStr">
         <is>
-          <t>봄이 되어 알바로는 다시 베니알코르로 가서 반론 취재를 합니다. 군수 이히니오 세르베라는 절차가 합법이었다고 주장하고, 카밀라는 매 산불 직후 헐값 매입이 집중된 거래 패턴을 정리합니다. 그러나 2016년 산불이 낙뢰로 인한 것이었다는 사실이 드러나 기사의 틀을 고쳐야 하고, 지방선거를 앞둔 야당 의원 사그라리오는 보도 시점을 앞당기라고 압박합니다.</t>
+          <t>기사가 이해충돌 고지와 함께 일요일 1면에 실립니다. 자치정부의 불시 감사와 인력 기준 강화 발표가 이어지지만, 펀드는 체인을 다른 펀드에 매각할 준비를 합니다. 하비에르는 어머니 곁에서 저녁을 먹이며, 무엇이 바뀌었고 무엇이 그대로인지 조용히 되새깁니다.</t>
         </is>
       </c>
     </row>
@@ -35018,7 +35018,7 @@
         <v>1111</v>
       </c>
       <c r="B1112" s="10" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C1112" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1112)</f>
@@ -35030,14 +35030,14 @@
         </is>
       </c>
       <c r="E1112" s="10" t="n">
-        <v>39650</v>
+        <v>39713</v>
       </c>
       <c r="F1112" s="10" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G1112" s="10" t="inlineStr">
         <is>
-          <t>두 달여 뒤 기사가 나가고, 주 정부 도시계획위원회는 용도 변경 최종 승인을 보류하며 환경 검찰이 회의록 정정 경위를 조사하기 시작합니다. 그러나 이듬해 여름, 세레타 교차로에서 또다시 연기가 오릅니다. 알바로는 아구스틴과 함께 능선에서 진화를 지켜보며, 이번 불이 무엇을 의미하는지 아직 아무도 모른다는 사실을 받아들입니다.</t>
+          <t>새로운 취재. 마드리드의 한 대학에 다니는 생물학과 학생 바네사가 캠퍼스 곳곳에 붙은 난자 기증 '보상금' 광고 전단을 들고 신문사를 찾아옵니다. 알바로와 하비에르는 편집국 회의실에서 그녀와 함께 광고 문구를 한 줄씩 뜯어보기 시작합니다.</t>
         </is>
       </c>
     </row>
@@ -35046,7 +35046,7 @@
         <v>1112</v>
       </c>
       <c r="B1113" s="10" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C1113" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1113)</f>
@@ -35058,14 +35058,14 @@
         </is>
       </c>
       <c r="E1113" s="10" t="n">
-        <v>39700</v>
+        <v>39762</v>
       </c>
       <c r="F1113" s="10" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G1113" s="10" t="inlineStr">
         <is>
-          <t>새로운 취재. 하비에르가 은퇴 교사 카실다 아르나이스로부터 손편지 한 통을 받습니다. 가상의 마을 '산 키르세 델 바예'의 공립학교 '로스 알멘드로스'에서 31년간 아이들을 가르친 그녀는 학교 지붕의 석면 이야기를 하고 싶다며 알바로와 하비에르를 집으로 초대합니다.</t>
+          <t>몇 주 후, 알바로가 기증을 일곱 번 한 카나리아 출신 학생 사이라를 대학가 근처의 조용한 카페에서 만납니다. 이어서 그는 의료윤리 전문가인 고니 박사와 통화하며 사이라의 경험을 윤리적 원칙에 비추어 정리합니다.</t>
         </is>
       </c>
     </row>
@@ -35074,7 +35074,7 @@
         <v>1113</v>
       </c>
       <c r="B1114" s="10" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C1114" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1114)</f>
@@ -35086,14 +35086,14 @@
         </is>
       </c>
       <c r="E1114" s="10" t="n">
-        <v>39751</v>
+        <v>39810</v>
       </c>
       <c r="F1114" s="10" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G1114" s="10" t="inlineStr">
         <is>
-          <t>일주일 후, 카밀라와 마르코스가 교육청의 몇 년 치 예산 집행 자료를 분석한 결과를 알바로와 하비에르에게 보여 줍니다. 저녁에는 알바로가 석면 실태 조사를 맡았던 건축기사 올비도 에스테베를 조용한 카페에서 만납니다.</t>
+          <t>알바로는 그룹 '페르티비아'의 전직 기증자 코디네이터 에두르네를 만나, 그녀가 퇴사 전에 보관한 기증자 데이터 파일을 받습니다. 마르코스가 데이터를 분석하던 중 사이라가 갑자기 증언을 철회하겠다고 연락해 오고, 신문사는 민감한 의료 정보를 어떻게 다뤄야 할지 윤리적 딜레마에 빠집니다.</t>
         </is>
       </c>
     </row>
@@ -35102,7 +35102,7 @@
         <v>1114</v>
       </c>
       <c r="B1115" s="10" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C1115" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1115)</f>
@@ -35114,14 +35114,14 @@
         </is>
       </c>
       <c r="E1115" s="10" t="n">
-        <v>39805</v>
+        <v>39859</v>
       </c>
       <c r="F1115" s="10" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G1115" s="10" t="inlineStr">
         <is>
-          <t>며칠 후, 알바로가 독립 석면 전문 엔지니어 파티마 우르키사와 함께 로스 알멘드로스 학교를 찾아가 지붕 상태를 확인합니다. 그러나 그 직후, 교육청 홍보실이 카실다의 가족사를 흘리며 취재의 신뢰성을 흔들려 합니다.</t>
+          <t>알바로가 반론권 보장을 위해 클리니카 나탈리스의 의료 책임자 라스에라스 박사와 홍보 담당자를 인터뷰합니다. 그 뒤 마르타와 함께 원고를 한 문장씩 법률 검토합니다.</t>
         </is>
       </c>
     </row>
@@ -35130,7 +35130,7 @@
         <v>1115</v>
       </c>
       <c r="B1116" s="10" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C1116" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1116)</f>
@@ -35142,14 +35142,14 @@
         </is>
       </c>
       <c r="E1116" s="10" t="n">
-        <v>39854</v>
+        <v>39907</v>
       </c>
       <c r="F1116" s="10" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G1116" s="10" t="inlineStr">
         <is>
-          <t>보도를 앞두고 알바로가 교육청에 반론권 질의서를 보내고, 돌아온 관료적 서면 답변을 하비에르와 한 줄씩 해부합니다. 이어 기반시설국장 로레나 라레타의 기자회견에서 직접 추가 질문을 던지고, 신문사 변호사 마르타와 편집장은 학교 명단 공개 여부를 놓고 고민합니다.</t>
+          <t>보도가 나간 지 열흘 후, 바네사의 대학에서 학생회가 난자 기증에 관한 공개 토론회를 엽니다. 알바로는 객석 뒤편에서 토론을 지켜보고, 행사가 끝난 뒤 뜻밖의 이메일 한 통을 받습니다.</t>
         </is>
       </c>
     </row>
@@ -35158,7 +35158,7 @@
         <v>1116</v>
       </c>
       <c r="B1117" s="10" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C1117" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1117)</f>
@@ -35170,14 +35170,14 @@
         </is>
       </c>
       <c r="E1117" s="10" t="n">
-        <v>39903</v>
+        <v>39957</v>
       </c>
       <c r="F1117" s="10" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G1117" s="10" t="inlineStr">
         <is>
-          <t>기사가 나간 뒤, 학부모들의 분노와 교육감의 '긴급 대책' 발표가 이어지고 교육청 내부에서는 제보자 색출이 시작됩니다. 몇 달 뒤 여름방학, 알바로는 로스 알멘드로스 학교 울타리 밖에서 카실다와 함께 지붕 철거 작업을 지켜봅니다.</t>
+          <t>새로운 취재. 마드리드 남부의 간호사 마루하가 알바로의 칼럼을 읽고 이메일을 보내옵니다. 열일곱 살 아들 하코보가 아버지의 신분증으로 온라인 스포츠 도박 계정을 만들어 4천 유로 넘게 잃었다는 내용입니다. 알바로는 그 가족의 부엌 식탁에 앉아 이야기를 듣습니다.</t>
         </is>
       </c>
     </row>
@@ -35186,7 +35186,7 @@
         <v>1117</v>
       </c>
       <c r="B1118" s="10" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C1118" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1118)</f>
@@ -35198,14 +35198,14 @@
         </is>
       </c>
       <c r="E1118" s="10" t="n">
-        <v>39953</v>
+        <v>40013</v>
       </c>
       <c r="F1118" s="10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G1118" s="10" t="inlineStr">
         <is>
-          <t>새로운 취재. 고등학교 교사 암브로시오 발델로마르가 신문사에 연락해 옵니다. 지방정부 부지사이자 차기 지사 후보로 거론되는 노르베르토 몬타네르가 TV에서 자랑한 석사 학위를, 같은 과정을 함께 다녔다는 그는 한 번도 강의실에서 본 적이 없다는 것입니다.</t>
+          <t>몇 주 후, 알바로와 하비에르는 마르코스와 카밀라가 만든 데이터 지도를 들고 마드리드 남부의 학교 주변 도박장들을 직접 둘러봅니다. 하교 시간에 도박장 앞을 관찰하고, 고등학교 진로상담 교사와 도박장 직원을 인터뷰합니다.</t>
         </is>
       </c>
     </row>
@@ -35214,7 +35214,7 @@
         <v>1118</v>
       </c>
       <c r="B1119" s="10" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C1119" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1119)</f>
@@ -35226,14 +35226,14 @@
         </is>
       </c>
       <c r="E1119" s="10" t="n">
-        <v>40001</v>
+        <v>40060</v>
       </c>
       <c r="F1119" s="10" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G1119" s="10" t="inlineStr">
         <is>
-          <t>열흘 후, 대학의 정보공개 답변과 함께 몬타네르 측이 먼저 움직입니다. 그는 SNS에 자신의 성적증명서를 올리며 "논란 끝"을 선언하지만, 마르코스와 알바로는 그 증명서 안에서 오히려 새로운 의문을 찾아내고, 논문 심사위원으로 이름이 오른 가르비녜 산타크루스 교수를 찾아갑니다.</t>
+          <t>알바로가 공립병원 행동중독 클리닉의 아리사발라가 박사를 찾아가 도박 중독의 심리학적 메커니즘을 묻습니다. 이후 부모와 마르타가 정한 조건 아래, 하코보가 처음으로 알바로와 단둘이 이야기하며 텔레그램 '팁스터'의 실체를 보여 줍니다.</t>
         </is>
       </c>
     </row>
@@ -35242,7 +35242,7 @@
         <v>1119</v>
       </c>
       <c r="B1120" s="10" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C1120" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1120)</f>
@@ -35254,14 +35254,14 @@
         </is>
       </c>
       <c r="E1120" s="10" t="n">
-        <v>40050</v>
+        <v>40108</v>
       </c>
       <c r="F1120" s="10" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G1120" s="10" t="inlineStr">
         <is>
-          <t>며칠 후, 연구소 행정실 직원 타마라 테하다가 하비에르를 통해 만남을 요청합니다. 그녀는 2016년 상부의 지시로 성적을 바꿨다고 털어놓지만, 그 고백은 그녀 자신을 범죄 혐의로 몰아넣을 수도 있습니다. 한편 총장은 기자회견에서 서버 이전으로 기록이 남아 있지 않다고 발표합니다.</t>
+          <t>알바로가 국회 근처 레스토랑에서 온라인 도박업계 협회의 대관 담당 오리올 벤드렐과 점심 인터뷰를 합니다. 그런데 그날 저녁, 하코보가 다시 도박을 했다는 소식이 들려오고, 알바로는 자신의 취재가 가족에게 상처가 되고 있는 건 아닌지 고민에 빠집니다.</t>
         </is>
       </c>
     </row>
@@ -35270,7 +35270,7 @@
         <v>1120</v>
       </c>
       <c r="B1121" s="10" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C1121" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1121)</f>
@@ -35282,14 +35282,14 @@
         </is>
       </c>
       <c r="E1121" s="10" t="n">
-        <v>40099</v>
+        <v>40161</v>
       </c>
       <c r="F1121" s="10" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G1121" s="10" t="inlineStr">
         <is>
-          <t>신문이 첫 기사를 내보낸 다음 날, 몬타네르가 기자회견을 엽니다. 알바로는 질문권을 얻어 회피성 답변 하나하나에 추가 질문을 던지고, 몬타네르가 '증거'로 공개한 석사 논문은 곧 또 다른 문제를 드러냅니다.</t>
+          <t>보도가 나간 지 한 달 후, 하원 위원회에서 도박 광고 규제 개정안 청문회가 열리고 알바로는 기자석에서 벤드렐과 아리사발라가 박사의 발언을 듣습니다. 그 주말, 그는 동네 축구장에서 일라리오와 하코보를 다시 만납니다.</t>
         </is>
       </c>
     </row>
@@ -35298,7 +35298,7 @@
         <v>1121</v>
       </c>
       <c r="B1122" s="10" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C1122" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1122)</f>
@@ -35310,14 +35310,14 @@
         </is>
       </c>
       <c r="E1122" s="10" t="n">
-        <v>40147</v>
+        <v>40210</v>
       </c>
       <c r="F1122" s="10" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G1122" s="10" t="inlineStr">
         <is>
-          <t>몇 주 후, 검찰이 수사에 착수하고 타마라는 변호사와 함께 스스로 진술하기로 결심합니다. 몬타네르는 결국 부지사직에서 물러나지만 의원직은 지키며 끝까지 잘못을 인정하지 않고, 알바로는 이 사건이 남긴 것을 암브로시오 발델로마르의 교실에서 다시 생각하게 됩니다.</t>
+          <t>새로운 취재. 가상의 지방 철도 노선 발데카스트로 커브에서 87명이 숨진 탈선 사고가 일어난 지 6년, 알바로가 아무 언론도 찾지 않는 추모식에 갑니다. 공식 원인은 '기관사 과실'로 정리되었지만, 희생자 가족 협회장 아센시온은 6년간 답을 얻지 못한 질문들이 담긴 상자를 그에게 건넵니다.</t>
         </is>
       </c>
     </row>
@@ -35326,7 +35326,7 @@
         <v>1122</v>
       </c>
       <c r="B1123" s="10" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C1123" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1123)</f>
@@ -35338,14 +35338,14 @@
         </is>
       </c>
       <c r="E1123" s="10" t="n">
-        <v>40196</v>
+        <v>40260</v>
       </c>
       <c r="F1123" s="10" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="G1123" s="10" t="inlineStr">
         <is>
-          <t>일상 에피소드. 평범한 월요일 오후, 신문사 회의실에서 다음 날 지면을 정하는 편집 회의가 열립니다. 각 부서가 기사를 제안하고 1면 자리를 두고 의견이 엇갈리는 가운데, 편집국장이 최종 결정을 내립니다.</t>
+          <t>며칠 후, 알바로와 하비에르가 아빌라에 사는 은퇴 철도 기술자 루포 킨타날을 찾아가 공식 사고조사 보고서를 읽는 법을 배웁니다. 그는 '직접 원인'과 '기여 요인'의 차이, 주어 없는 문장과 '확인되지 않음' 같은 책임 회피형 표현을 하나씩 짚어 주고, 공개본의 부록 목록에서 빠진 문서 하나를 찾게 합니다.</t>
         </is>
       </c>
     </row>
@@ -35354,7 +35354,7 @@
         <v>1123</v>
       </c>
       <c r="B1124" s="10" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C1124" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1124)</f>
@@ -35366,14 +35366,14 @@
         </is>
       </c>
       <c r="E1124" s="10" t="n">
-        <v>40257</v>
+        <v>40310</v>
       </c>
       <c r="F1124" s="10" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G1124" s="10" t="inlineStr">
         <is>
-          <t>새로운 취재. 하비에르가 카스테욘 지역 신문의 작은 기사 하나를 들고 웃으며 편집국에 들어옵니다. 가상의 마을 '베니알파스'의 고깃집 체인 사장 헤르만 토르모가 4년 사이 열두 번째 복권 당첨금 수표를 들고 활짝 웃는 사진입니다. 알바로와 카밀라는 '확률'이라는 단어부터 따져 보기 시작합니다.</t>
+          <t>석 달 후, 정보공개 청구가 거절되자 알바로는 당시 안전 부서 기술자였던 이시드로 오찬디아노를 찾아냅니다. 그가 건넨 내부 투자위원회 회의록에는 커브의 자동 감속 장치 설치가 '예산 사정에 따른 재조정'으로 미뤄진 기록과, 그가 직접 쓴 위험 경고 보고서가 들어 있습니다. 마르코스가 문서를 검증하고 마르타가 법적 위험을 따지는 사이, 이시드로는 신원 노출을 두려워해 손을 떼겠다고 합니다.</t>
         </is>
       </c>
     </row>
@@ -35382,7 +35382,7 @@
         <v>1124</v>
       </c>
       <c r="B1125" s="10" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C1125" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1125)</f>
@@ -35394,14 +35394,14 @@
         </is>
       </c>
       <c r="E1125" s="10" t="n">
-        <v>40305</v>
+        <v>40368</v>
       </c>
       <c r="F1125" s="10" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="G1125" s="10" t="inlineStr">
         <is>
-          <t>몇 주 후, 알바로와 카밀라가 은퇴한 국세청 조사관 에스테르 에스카르틴을 발렌시아의 한 카페에서 만납니다. 그녀는 복권 당첨금에 대한 특별세, 원천징수, 소명되지 않은 자산 증가 같은 세무 용어로 이 수법의 구조를 설명합니다.</t>
+          <t>1년 후, 기관사 미켈 비요드레의 재판이 다가옵니다. 알바로가 그를 인터뷰한 사실이 알려지자 협회 일부가 배신감을 느끼고, 아센시온과의 관계가 흔들립니다. 한편 카밀라는 공개된 예산·결산 자료만으로 연기된 투자의 흔적을 독립적으로 재구성하고, 인프라라일 대변인은 반론권 질의에 책임 회피형 문구로만 답합니다.</t>
         </is>
       </c>
     </row>
@@ -35410,7 +35410,7 @@
         <v>1125</v>
       </c>
       <c r="B1126" s="10" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C1126" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1126)</f>
@@ -35422,14 +35422,14 @@
         </is>
       </c>
       <c r="E1126" s="10" t="n">
-        <v>40355</v>
+        <v>40427</v>
       </c>
       <c r="F1126" s="10" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G1126" s="10" t="inlineStr">
         <is>
-          <t>며칠 후, 알바로와 하비에르가 베니알파스를 찾아갑니다. 마을 바와 복권 판매소 '라 에라두라'를 돌며 현장 취재를 하던 중, 몇 년 전 당첨 복권을 토르모에게 웃돈을 받고 팔았다는 연금 생활자 엘리세오 페냐로하를 만나게 됩니다.</t>
+          <t>2년이 더 흐릅니다. 보도 이후 법원이 인프라라일 전 임원들에 대한 수사를 재개했지만 위원회 구성원들은 '형사상 인과관계 없음'으로 불기소되고, 미켈만 유죄 판결을 받습니다. 사고 9주기 추모식에서 알바로는 아센시온, 가우덴시오, 그리고 처음으로 모습을 드러낸 이시드로와 함께, 기사가 바꾸지 못한 것과 바꾼 것을 마주합니다.</t>
         </is>
       </c>
     </row>
@@ -35438,7 +35438,7 @@
         <v>1126</v>
       </c>
       <c r="B1127" s="10" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C1127" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1127)</f>
@@ -35450,14 +35450,14 @@
         </is>
       </c>
       <c r="E1127" s="10" t="n">
-        <v>40406</v>
+        <v>40481</v>
       </c>
       <c r="F1127" s="10" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G1127" s="10" t="inlineStr">
         <is>
-          <t>일주일 후, 마드리드 편집국. 데이터 인턴 글로리아가 열두 건의 당첨 기록과 토르모 회사의 현금 흐름을 겹쳐 보여 줍니다. 그러나 토르모 측 변호사의 경고장이 도착하고, 엘리세오는 가족의 압박에 증언을 철회하겠다고 합니다. 알바로는 변호사 마르타와 함께 무엇을 쓸 수 있고 무엇을 쓸 수 없는지 따집니다.</t>
+          <t>새로운 취재. 7월 폭염 속, 알바로가 발렌시아 내륙의 가상 마을 베니알코르의 산불 현장을 취재합니다. 진화대장 아구스틴 보르다요는 불길과 씨름하다 "이 비탈은 두세 해마다 탄다, 늘 같은 자리에서"라고 무심코 내뱉고, 마을 사람들은 벌써 한 목동을 범인으로 지목하고 있습니다.</t>
         </is>
       </c>
     </row>
@@ -35466,7 +35466,7 @@
         <v>1127</v>
       </c>
       <c r="B1128" s="10" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C1128" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1128)</f>
@@ -35478,14 +35478,14 @@
         </is>
       </c>
       <c r="E1128" s="10" t="n">
-        <v>40458</v>
+        <v>40529</v>
       </c>
       <c r="F1128" s="10" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="G1128" s="10" t="inlineStr">
         <is>
-          <t>2주 후, 알바로가 반론권 보장을 위해 베니알파스의 고깃집에서 토르모 본인과 그의 변호사를 만납니다. 토르모는 말발굽과 '행운의 별' 이야기로 시종일관 유쾌하게 버티지만, 알바로의 계산기 앞에서 이야기가 조금씩 엇나갑니다. 기사는 나가지만, 결말은 축배가 아니라 복권 판매소 앞에서의 짧은 장면입니다.</t>
+          <t>마드리드로 돌아온 알바로는 마르코스, 그리고 원격탐사 연구자 아마야 고에나가와 함께 15년치 위성 영상을 분석합니다. 연소 지수로 산불 흔적을 겹치자 세레타 비탈이 여러 번 탄 것이 드러나고, 지적도와 등기부를 겹쳐 보니 불이 난 뒤마다 그 땅이 하나의 회사로 조금씩 넘어간 사실이 보입니다.</t>
         </is>
       </c>
     </row>
@@ -35494,7 +35494,7 @@
         <v>1128</v>
       </c>
       <c r="B1129" s="10" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C1129" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1129)</f>
@@ -35506,14 +35506,14 @@
         </is>
       </c>
       <c r="E1129" s="10" t="n">
-        <v>40519</v>
+        <v>40578</v>
       </c>
       <c r="F1129" s="10" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G1129" s="10" t="inlineStr">
         <is>
-          <t>새로운 취재. 한 자치주 아동보호센터에서 일하는 사회교육사 아도라시온 가리고스가 하비에르를 통해 조심스럽게 연락해 옵니다. 그녀가 일하는 공립 보호시설의 십대 아이들이 밤마다 '무단 외출'을 반복하고, 문 앞에는 낯선 어른들의 차가 기다리는데, 시설은 침묵하고 있다는 것입니다. 알바로가 가장 먼저 묻는 것은 기사가 아니라 '오늘 밤 위험한 아이가 있는가'입니다.</t>
+          <t>몇 주 후, 하비에르와 알바로가 베니알코르 시청을 찾아 지난 15년간의 본회의 회의록을 열람합니다. 퇴직한 시청 서기 베르나르도 마스카렐이 도시계획 변경 절차를 설명해 주고, 두 사람은 '산불 피해 산림은 30년간 용도 변경 금지' 규정을 피해 간 예외 조항과, 불이 난 뒤에 '정정'된 회의록 한 장을 찾아냅니다. 그러나 마르타는 '방화'를 암시하는 순간 기사가 무너진다고 경고합니다.</t>
         </is>
       </c>
     </row>
@@ -35522,7 +35522,7 @@
         <v>1129</v>
       </c>
       <c r="B1130" s="10" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C1130" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1130)</f>
@@ -35534,14 +35534,14 @@
         </is>
       </c>
       <c r="E1130" s="10" t="n">
-        <v>40567</v>
+        <v>40627</v>
       </c>
       <c r="F1130" s="10" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="G1130" s="10" t="inlineStr">
         <is>
-          <t>일주일 후, 마드리드 편집국. 마르코스와 하비에르가 정보공개청구로 받은 자치주 전체 보호시설의 무단 외출 통계와 검찰 연례 보고서의 통보 건수를 비교합니다. 이어 아동 법심리 전문가 에울랄리아 푸이그베르트 박사가 착취의 징후와, 피해 아동을 보호하며 보도하는 원칙을 설명합니다. 편집국은 이 취재만의 규칙을 정합니다.</t>
+          <t>봄이 되어 알바로는 다시 베니알코르로 가서 반론 취재를 합니다. 군수 이히니오 세르베라는 절차가 합법이었다고 주장하고, 카밀라는 매 산불 직후 헐값 매입이 집중된 거래 패턴을 정리합니다. 그러나 2016년 산불이 낙뢰로 인한 것이었다는 사실이 드러나 기사의 틀을 고쳐야 하고, 지방선거를 앞둔 야당 의원 사그라리오는 보도 시점을 앞당기라고 압박합니다.</t>
         </is>
       </c>
     </row>
@@ -35550,7 +35550,7 @@
         <v>1130</v>
       </c>
       <c r="B1131" s="10" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C1131" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1131)</f>
@@ -35562,14 +35562,14 @@
         </is>
       </c>
       <c r="E1131" s="10" t="n">
-        <v>40616</v>
+        <v>40684</v>
       </c>
       <c r="F1131" s="10" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G1131" s="10" t="inlineStr">
         <is>
-          <t>며칠 후, 알바로가 십여 년 전 같은 보호시설망의 다른 센터에서 자란 27세 여성 소라이다를 만납니다. 동의 절차와 규칙을 먼저 정하고, 그녀가 겪은 일이 아니라 '아무도 묻지 않았던' 제도의 침묵에 대해 이야기를 듣습니다. 이어 소년 담당 검사 이치아르 아바이투아가 보호 절차와 통보 의무를 설명합니다.</t>
+          <t>두 달여 뒤 기사가 나가고, 주 정부 도시계획위원회는 용도 변경 최종 승인을 보류하며 환경 검찰이 회의록 정정 경위를 조사하기 시작합니다. 그러나 이듬해 여름, 세레타 교차로에서 또다시 연기가 오릅니다. 알바로는 아구스틴과 함께 능선에서 진화를 지켜보며, 이번 불이 무엇을 의미하는지 아직 아무도 모른다는 사실을 받아들입니다.</t>
         </is>
       </c>
     </row>
@@ -35578,7 +35578,7 @@
         <v>1131</v>
       </c>
       <c r="B1132" s="10" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C1132" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1132)</f>
@@ -35590,14 +35590,14 @@
         </is>
       </c>
       <c r="E1132" s="10" t="n">
-        <v>40669</v>
+        <v>40734</v>
       </c>
       <c r="F1132" s="10" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G1132" s="10" t="inlineStr">
         <is>
-          <t>일주일 후, 취재가 위기를 맞습니다. 주정부가 아도라시온에게 '정보 유출'을 이유로 징계 절차를 시작하고, 증언을 약속했던 또 다른 교육사 파우스토가 물러섭니다. 한편 한 방송사가 보호시설 앞 소녀를 모자이크 처리해 내보내는 일이 벌어집니다. 알바로와 마르타, 하비에르는 시설 이름을 공개할지, 경찰 수사를 위해 무엇을 미뤄야 할지를 놓고 격론을 벌입니다.</t>
+          <t>새로운 취재. 하비에르가 은퇴 교사 카실다 아르나이스로부터 손편지 한 통을 받습니다. 가상의 마을 '산 키르세 델 바예'의 공립학교 '로스 알멘드로스'에서 31년간 아이들을 가르친 그녀는 학교 지붕의 석면 이야기를 하고 싶다며 알바로와 하비에르를 집으로 초대합니다.</t>
         </is>
       </c>
     </row>
@@ -35606,7 +35606,7 @@
         <v>1132</v>
       </c>
       <c r="B1133" s="10" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C1133" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1133)</f>
@@ -35618,14 +35618,14 @@
         </is>
       </c>
       <c r="E1133" s="10" t="n">
-        <v>40719</v>
+        <v>40785</v>
       </c>
       <c r="F1133" s="10" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G1133" s="10" t="inlineStr">
         <is>
-          <t>열흘 후, 알바로가 주정부 아동국장 아르투로 테헤도르를 인터뷰하며 반론권을 보장합니다. 기사가 나간 뒤 지침은 철회되고 검찰은 조사에 착수하지만, 아도라시온의 징계 절차는 여전히 열려 있습니다. 결말은 축배가 아닌, 내부고발자 보호 기관 앞의 조용한 아침입니다.</t>
+          <t>일주일 후, 카밀라와 마르코스가 교육청의 몇 년 치 예산 집행 자료를 분석한 결과를 알바로와 하비에르에게 보여 줍니다. 저녁에는 알바로가 석면 실태 조사를 맡았던 건축기사 올비도 에스테베를 조용한 카페에서 만납니다.</t>
         </is>
       </c>
     </row>
@@ -35634,7 +35634,7 @@
         <v>1133</v>
       </c>
       <c r="B1134" s="10" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C1134" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1134)</f>
@@ -35646,14 +35646,14 @@
         </is>
       </c>
       <c r="E1134" s="10" t="n">
-        <v>40775</v>
+        <v>40839</v>
       </c>
       <c r="F1134" s="10" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G1134" s="10" t="inlineStr">
         <is>
-          <t>새로운 취재. 무기 수출 감시 단체 '아탈라야 센터'의 오픈소스 분석가 이차소 수비아우레가 내전 중인 가상의 국가 티하라에서 촬영된 영상 한 편을 들고 편집국을 찾아옵니다. 박격포탄 꼬리날개에 찍힌 각인은 아라곤의 한 탄약 제조사를 가리키지만, 스페인 정부의 공식 수출 통계에 적힌 최종 사용자는 걸프 국가 카시마르 토후국입니다.</t>
+          <t>며칠 후, 알바로가 독립 석면 전문 엔지니어 파티마 우르키사와 함께 로스 알멘드로스 학교를 찾아가 지붕 상태를 확인합니다. 그러나 그 직후, 교육청 홍보실이 카실다의 가족사를 흘리며 취재의 신뢰성을 흔들려 합니다.</t>
         </is>
       </c>
     </row>
@@ -35662,7 +35662,7 @@
         <v>1134</v>
       </c>
       <c r="B1135" s="10" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C1135" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1135)</f>
@@ -35674,14 +35674,14 @@
         </is>
       </c>
       <c r="E1135" s="10" t="n">
-        <v>40828</v>
+        <v>40888</v>
       </c>
       <c r="F1135" s="10" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="G1135" s="10" t="inlineStr">
         <is>
-          <t>며칠 후, 알바로와 마르코스가 그림자와 건물, 위성 사진으로 영상의 촬영 장소와 날짜를 검증하고, 첫 영상을 찍은 티하라의 현지 기자 함자 다르위시와 화상으로 연결합니다. 그러나 이차소가 덧붙인 네 번째 영상이 수십 년 전 합법적으로 다른 나라에 팔린 탄약으로 드러나며, 취재팀은 과욕의 위험을 실감합니다.</t>
+          <t>보도를 앞두고 알바로가 교육청에 반론권 질의서를 보내고, 돌아온 관료적 서면 답변을 하비에르와 한 줄씩 해부합니다. 이어 기반시설국장 로레나 라레타의 기자회견에서 직접 추가 질문을 던지고, 신문사 변호사 마르타와 편집장은 학교 명단 공개 여부를 놓고 고민합니다.</t>
         </is>
       </c>
     </row>
@@ -35690,7 +35690,7 @@
         <v>1135</v>
       </c>
       <c r="B1136" s="10" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C1136" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1136)</f>
@@ -35702,14 +35702,14 @@
         </is>
       </c>
       <c r="E1136" s="10" t="n">
-        <v>40887</v>
+        <v>40937</v>
       </c>
       <c r="F1136" s="10" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G1136" s="10" t="inlineStr">
         <is>
-          <t>일주일 후, 알바로가 수출 통제 위원회에 올라가는 서류를 준비하던 퇴직 공무원 세페리노 라스트라를 사라고사의 한 카페에서 만나 허가 절차가 실제로 어떻게 작동하는지 듣습니다. 같은 날 밤 카밀라는 EMJ의 재무제표에서 카시마르 현지 조립 공장 지분을 찾아내고, 완제품 대신 '부품과 키트'로 수출하는 합법적 우회로가 모습을 드러냅니다.</t>
+          <t>기사가 나간 뒤, 학부모들의 분노와 교육감의 '긴급 대책' 발표가 이어지고 교육청 내부에서는 제보자 색출이 시작됩니다. 몇 달 뒤 여름방학, 알바로는 로스 알멘드로스 학교 울타리 밖에서 카실다와 함께 지붕 철거 작업을 지켜봅니다.</t>
         </is>
       </c>
     </row>
@@ -35718,7 +35718,7 @@
         <v>1136</v>
       </c>
       <c r="B1137" s="10" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C1137" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1137)</f>
@@ -35730,14 +35730,14 @@
         </is>
       </c>
       <c r="E1137" s="10" t="n">
-        <v>40940</v>
+        <v>40987</v>
       </c>
       <c r="F1137" s="10" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="G1137" s="10" t="inlineStr">
         <is>
-          <t>열흘 후, 알바로는 유엔 안보리 티하라 전문가 패널 위원 안네커 피서르와 통화해 패널이 같은 로트를 기록했다는 사실을 확인하지만, 보고서 공개 전까지 보도를 미뤄 달라는 요청을 받고 편집국은 고민에 빠집니다. 이어 알바로는 아라곤의 EMJ 본사에서 홍보이사 고르카 레보야르의 반론을 듣고, 공장 앞에서 노동자위원회 위원장 에울로히오 알콘첼의 목소리를 듣습니다.</t>
+          <t>새로운 취재. 고등학교 교사 암브로시오 발델로마르가 신문사에 연락해 옵니다. 지방정부 부지사이자 차기 지사 후보로 거론되는 노르베르토 몬타네르가 TV에서 자랑한 석사 학위를, 같은 과정을 함께 다녔다는 그는 한 번도 강의실에서 본 적이 없다는 것입니다.</t>
         </is>
       </c>
     </row>
@@ -35746,7 +35746,7 @@
         <v>1137</v>
       </c>
       <c r="B1138" s="10" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C1138" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1138)</f>
@@ -35758,14 +35758,14 @@
         </is>
       </c>
       <c r="E1138" s="10" t="n">
-        <v>41000</v>
+        <v>41035</v>
       </c>
       <c r="F1138" s="10" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G1138" s="10" t="inlineStr">
         <is>
-          <t>3주 후, 유엔 전문가 패널 보고서가 공개된 다음 날 기사가 나가고, 알바로는 국무회의 후 열린 정부 대변인 에밀리아 에차니스의 기자회견에서 직접 질문을 던집니다. 정부는 '심사 중인 허가의 재검토'만 약속하고, 기사의 반향이 가라앉기도 전에 이차소에게서 새 영상이 도착합니다.</t>
+          <t>열흘 후, 대학의 정보공개 답변과 함께 몬타네르 측이 먼저 움직입니다. 그는 SNS에 자신의 성적증명서를 올리며 "논란 끝"을 선언하지만, 마르코스와 알바로는 그 증명서 안에서 오히려 새로운 의문을 찾아내고, 논문 심사위원으로 이름이 오른 가르비녜 산타크루스 교수를 찾아갑니다.</t>
         </is>
       </c>
     </row>
@@ -35774,7 +35774,7 @@
         <v>1138</v>
       </c>
       <c r="B1139" s="10" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C1139" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1139)</f>
@@ -35786,14 +35786,14 @@
         </is>
       </c>
       <c r="E1139" s="10" t="n">
-        <v>41050</v>
+        <v>41084</v>
       </c>
       <c r="F1139" s="10" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G1139" s="10" t="inlineStr">
         <is>
-          <t>새로운 취재. 신문사의 익명 제보함에 '현역 군인'이라고만 밝힌 제보가 들어오고, 알바로는 가상의 주둔지 발데카스트로에서 20킬로미터 떨어진 주유소 카페에서 카보 프리메로(선임 상병) 솔레다드 마이레나를 만납니다. 그녀는 사격장에서 시험 삼아 쏜 방탄판이 막아야 할 탄을 막지 못했고, 지휘 계통을 따라 보고했지만 아무 일도 일어나지 않았다고 말합니다.</t>
+          <t>며칠 후, 연구소 행정실 직원 타마라 테하다가 하비에르를 통해 만남을 요청합니다. 그녀는 2016년 상부의 지시로 성적을 바꿨다고 털어놓지만, 그 고백은 그녀 자신을 범죄 혐의로 몰아넣을 수도 있습니다. 한편 총장은 기자회견에서 서버 이전으로 기록이 남아 있지 않다고 발표합니다.</t>
         </is>
       </c>
     </row>
@@ -35802,7 +35802,7 @@
         <v>1139</v>
       </c>
       <c r="B1140" s="10" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C1140" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1140)</f>
@@ -35814,14 +35814,14 @@
         </is>
       </c>
       <c r="E1140" s="10" t="n">
-        <v>41102</v>
+        <v>41133</v>
       </c>
       <c r="F1140" s="10" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G1140" s="10" t="inlineStr">
         <is>
-          <t>며칠 후, 알바로는 퇴역 준위이자 부사관 직업 협회 회장인 펠릭스 비야에스쿠사에게서 계급 체계와 호칭, 군인의 권리와 내부고발자 보호 제도를 배웁니다. 한편 하비에르와 카밀라는 공공조달 플랫폼에서 프로바노르 사의 긴급 수의계약을 찾아내고, 이 신생 업체의 '전략 고문'이 장비 요구 조건을 정하던 부서의 수장 출신 퇴역 준장 세베리아노 카스트리요라는 사실을 확인합니다.</t>
+          <t>신문이 첫 기사를 내보낸 다음 날, 몬타네르가 기자회견을 엽니다. 알바로는 질문권을 얻어 회피성 답변 하나하나에 추가 질문을 던지고, 몬타네르가 '증거'로 공개한 석사 논문은 곧 또 다른 문제를 드러냅니다.</t>
         </is>
       </c>
     </row>
@@ -35830,7 +35830,7 @@
         <v>1140</v>
       </c>
       <c r="B1141" s="10" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C1141" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1141)</f>
@@ -35842,14 +35842,14 @@
         </is>
       </c>
       <c r="E1141" s="10" t="n">
-        <v>41154</v>
+        <v>41181</v>
       </c>
       <c r="F1141" s="10" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G1141" s="10" t="inlineStr">
         <is>
-          <t>2주 후, 마르타는 부대 창고의 방탄판을 몰래 넘겨받는 것은 군형법상 범죄가 될 수 있다며 솔레다드에게서 증거물을 받지 말라고 못 박습니다. 대신 알바로는 프로바노르가 같은 로트의 '잉여분'을 민간 경비업체에 판 사실을 알아내 합법적으로 두 장을 구입하고, 대학 탄도 실험실의 이스마엘 이리아르테 박사에게 시험을 맡깁니다.</t>
+          <t>몇 주 후, 검찰이 수사에 착수하고 타마라는 변호사와 함께 스스로 진술하기로 결심합니다. 몬타네르는 결국 부지사직에서 물러나지만 의원직은 지키며 끝까지 잘못을 인정하지 않고, 알바로는 이 사건이 남긴 것을 암브로시오 발델로마르의 교실에서 다시 생각하게 됩니다.</t>
         </is>
       </c>
     </row>
@@ -35858,7 +35858,7 @@
         <v>1141</v>
       </c>
       <c r="B1142" s="10" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C1142" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1142)</f>
@@ -35870,14 +35870,14 @@
         </is>
       </c>
       <c r="E1142" s="10" t="n">
-        <v>41207</v>
+        <v>41230</v>
       </c>
       <c r="F1142" s="10" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="G1142" s="10" t="inlineStr">
         <is>
-          <t>열흘 후, 알바로가 국방부에 보낸 반론 질문지에 적힌 사격 시연 날짜 때문에 솔레다드의 신원이 드러나고, 그녀는 중대장 아리아가 대위에게 불려가 징계 사전 조사가 시작된다는 통보를 받습니다. 자책하는 알바로에게 솔레다드는 오히려 보도를 서두르라고 하고, 며칠 뒤 퇴역 준장 카스트리요는 마드리드의 한 호텔에서 인터뷰에 응하지만 알바로가 내민 날짜 하나에 대화를 급히 끝냅니다.</t>
+          <t>일상 에피소드. 평범한 월요일 오후, 신문사 회의실에서 다음 날 지면을 정하는 편집 회의가 열립니다. 각 부서가 기사를 제안하고 1면 자리를 두고 의견이 엇갈리는 가운데, 편집국장이 최종 결정을 내립니다.</t>
         </is>
       </c>
     </row>
@@ -35886,7 +35886,7 @@
         <v>1142</v>
       </c>
       <c r="B1143" s="10" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C1143" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1143)</f>
@@ -35898,14 +35898,14 @@
         </is>
       </c>
       <c r="E1143" s="10" t="n">
-        <v>41261</v>
+        <v>41291</v>
       </c>
       <c r="F1143" s="10" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G1143" s="10" t="inlineStr">
         <is>
-          <t>3주 후, 보도를 하루 앞두고 국방부 공보 책임자 발렌틴 소티요가 해당 로트의 '예방적 사용 중지'를 미리 알려 오고, 기사가 나간 뒤 카스트리요는 프로바노르 고문직에서 물러납니다. 한 달 뒤 발트해로 떠나는 중대의 환송식에서, 징계 절차가 끝나지 않아 파병 명단에서 빠진 솔레다드가 관중석에서 알바로와 함께 버스를 지켜봅니다.</t>
+          <t>새로운 취재. 하비에르가 카스테욘 지역 신문의 작은 기사 하나를 들고 웃으며 편집국에 들어옵니다. 가상의 마을 '베니알파스'의 고깃집 체인 사장 헤르만 토르모가 4년 사이 열두 번째 복권 당첨금 수표를 들고 활짝 웃는 사진입니다. 알바로와 카밀라는 '확률'이라는 단어부터 따져 보기 시작합니다.</t>
         </is>
       </c>
     </row>
@@ -35914,7 +35914,7 @@
         <v>1143</v>
       </c>
       <c r="B1144" s="10" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C1144" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1144)</f>
@@ -35926,14 +35926,14 @@
         </is>
       </c>
       <c r="E1144" s="10" t="n">
-        <v>41314</v>
+        <v>41339</v>
       </c>
       <c r="F1144" s="10" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G1144" s="10" t="inlineStr">
         <is>
-          <t>새로운 취재. 알바로는 독자 편지 한 통을 따라 지방 도시 발데아라로 가서, 백 년 역사의 축구 클럽 '클루브 데포르티보 발데아라'의 홈구장 엘 아레날 관중석에 앉습니다. 2년 전 클럽을 단돈 1유로에 사들인 정체불명의 외국 펀드, 그리고 경기장 부지를 아파트 단지로 바꾸려 한다는 소문에 대해, 50년 차 회원 푸리 카라스코 할머니와 서포터즈 '그라다 노르테'의 리더 다니가 서로 전혀 다른 반응을 보입니다.</t>
+          <t>몇 주 후, 알바로와 카밀라가 은퇴한 국세청 조사관 에스테르 에스카르틴을 발렌시아의 한 카페에서 만납니다. 그녀는 복권 당첨금에 대한 특별세, 원천징수, 소명되지 않은 자산 증가 같은 세무 용어로 이 수법의 구조를 설명합니다.</t>
         </is>
       </c>
     </row>
@@ -35942,7 +35942,7 @@
         <v>1144</v>
       </c>
       <c r="B1145" s="10" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C1145" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1145)</f>
@@ -35954,14 +35954,14 @@
         </is>
       </c>
       <c r="E1145" s="10" t="n">
-        <v>41365</v>
+        <v>41389</v>
       </c>
       <c r="F1145" s="10" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G1145" s="10" t="inlineStr">
         <is>
-          <t>하비에르와 카밀라, 마르코스가 마드리드 편집국에서 발데아라 클럽의 소유 구조와 이적 데이터를 해부합니다. 1유로 매각 뒤에 숨은 룩셈부르크·델라웨어 법인의 사슬, 경기장 부지를 담보로 한 연 12% 고리 대출, 그리고 한 아르헨티나 에이전트에게 쏠린 수수료가 드러나지만, 핵심 증인인 전 재무이사 루스는 실명 증언을 거부합니다.</t>
+          <t>며칠 후, 알바로와 하비에르가 베니알파스를 찾아갑니다. 마을 바와 복권 판매소 '라 에라두라'를 돌며 현장 취재를 하던 중, 몇 년 전 당첨 복권을 토르모에게 웃돈을 받고 팔았다는 연금 생활자 엘리세오 페냐로하를 만나게 됩니다.</t>
         </is>
       </c>
     </row>
@@ -35970,7 +35970,7 @@
         <v>1145</v>
       </c>
       <c r="B1146" s="10" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C1146" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1146)</f>
@@ -35982,14 +35982,14 @@
         </is>
       </c>
       <c r="E1146" s="10" t="n">
-        <v>41414</v>
+        <v>41440</v>
       </c>
       <c r="F1146" s="10" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G1146" s="10" t="inlineStr">
         <is>
-          <t>알바로가 시청의 공문서 등록부와 시의회 회의록을 파고들며, 매각 석 달 전에 접수된 도시계획 협약의 흔적을 확인합니다. 도시계획 담당 시의원 아란스와 정면으로 마주한 뒤, 문제의 에이전트 막시 갈반을 마르베야의 호텔 바에서 만나 "클럽은 핑계, 진짜 사업은 벽돌"이라는 의외의 솔직한 말을 듣습니다.</t>
+          <t>일주일 후, 마드리드 편집국. 데이터 인턴 글로리아가 열두 건의 당첨 기록과 토르모 회사의 현금 흐름을 겹쳐 보여 줍니다. 그러나 토르모 측 변호사의 경고장이 도착하고, 엘리세오는 가족의 압박에 증언을 철회하겠다고 합니다. 알바로는 변호사 마르타와 함께 무엇을 쓸 수 있고 무엇을 쓸 수 없는지 따집니다.</t>
         </is>
       </c>
     </row>
@@ -35998,7 +35998,7 @@
         <v>1146</v>
       </c>
       <c r="B1147" s="10" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C1147" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1147)</f>
@@ -36010,14 +36010,14 @@
         </is>
       </c>
       <c r="E1147" s="10" t="n">
-        <v>41464</v>
+        <v>41492</v>
       </c>
       <c r="F1147" s="10" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="G1147" s="10" t="inlineStr">
         <is>
-          <t>마르코스가 그라다 노르테의 원정 버스와 티켓이 브렌무어 계열사의 '팬 활동 후원금'으로 지불되었다는 송장을 찾아내면서, 알바로는 가장 열정적인 팬들이 동시에 침묵의 대가를 받았다는 윤리적 딜레마에 빠집니다. 마르타와 함께 기사의 법적 표현을 검토하고 펀드 측에 반론권을 요청하는 사이, 다니가 직접 찾아와 보도하지 말아 달라고 애원합니다.</t>
+          <t>2주 후, 알바로가 반론권 보장을 위해 베니알파스의 고깃집에서 토르모 본인과 그의 변호사를 만납니다. 토르모는 말발굽과 '행운의 별' 이야기로 시종일관 유쾌하게 버티지만, 알바로의 계산기 앞에서 이야기가 조금씩 엇나갑니다. 기사는 나가지만, 결말은 축배가 아니라 복권 판매소 앞에서의 짧은 장면입니다.</t>
         </is>
       </c>
     </row>
@@ -36026,7 +36026,7 @@
         <v>1147</v>
       </c>
       <c r="B1148" s="10" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C1148" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1148)</f>
@@ -36038,14 +36038,14 @@
         </is>
       </c>
       <c r="E1148" s="10" t="n">
-        <v>41513</v>
+        <v>41553</v>
       </c>
       <c r="F1148" s="10" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G1148" s="10" t="inlineStr">
         <is>
-          <t>기사가 나간 뒤, 그라다 노르테는 총회 결정에 따라 후원금 반환을 발표하고 다니가 직접 사과문을 읽습니다. 시의회는 도시계획 변경 절차를 중단하고 검찰은 협약에 대한 예비 조사에 착수하지만, 클럽은 시즌 마지막 홈경기에서 결국 강등이 확정됩니다. 알바로는 경기장을 떠나지 않는 관중들 사이에서 푸리 할머니의 마지막 말을 기록합니다.</t>
+          <t>새로운 취재. 한 자치주 아동보호센터에서 일하는 사회교육사 아도라시온 가리고스가 하비에르를 통해 조심스럽게 연락해 옵니다. 그녀가 일하는 공립 보호시설의 십대 아이들이 밤마다 '무단 외출'을 반복하고, 문 앞에는 낯선 어른들의 차가 기다리는데, 시설은 침묵하고 있다는 것입니다. 알바로가 가장 먼저 묻는 것은 기사가 아니라 '오늘 밤 위험한 아이가 있는가'입니다.</t>
         </is>
       </c>
     </row>
@@ -36054,7 +36054,7 @@
         <v>1148</v>
       </c>
       <c r="B1149" s="10" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C1149" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1149)</f>
@@ -36066,14 +36066,14 @@
         </is>
       </c>
       <c r="E1149" s="10" t="n">
-        <v>41562</v>
+        <v>41601</v>
       </c>
       <c r="F1149" s="10" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="G1149" s="10" t="inlineStr">
         <is>
-          <t>일상 에피소드. 주말 오후, 알바로와 카밀라, 하비에르, 그리고 카밀라의 오빠 안드레스가 함께 축구장을 찾습니다. 스페인 경기장이 처음인 안드레스는 응원 문화에 금세 빠져들고, 네 사람은 골과 판정 하나하나에 함께 소리 지르며 오후를 보냅니다.</t>
+          <t>일주일 후, 마드리드 편집국. 마르코스와 하비에르가 정보공개청구로 받은 자치주 전체 보호시설의 무단 외출 통계와 검찰 연례 보고서의 통보 건수를 비교합니다. 이어 아동 법심리 전문가 에울랄리아 푸이그베르트 박사가 착취의 징후와, 피해 아동을 보호하며 보도하는 원칙을 설명합니다. 편집국은 이 취재만의 규칙을 정합니다.</t>
         </is>
       </c>
     </row>
@@ -36082,7 +36082,7 @@
         <v>1149</v>
       </c>
       <c r="B1150" s="10" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C1150" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1150)</f>
@@ -36094,14 +36094,14 @@
         </is>
       </c>
       <c r="E1150" s="10" t="n">
-        <v>41624</v>
+        <v>41650</v>
       </c>
       <c r="F1150" s="10" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G1150" s="10" t="inlineStr">
         <is>
-          <t>새로운 취재. 하비에르의 열여섯 살 조카 아이타나가 체육 시간에 심장이 두근거려 쓰러지고, 응급실에서 그녀가 수백만 팔로워 인플루언서 클로틸데 만세보가 "광고 아님, 내 경험"이라며 추천한 '칼미아 포커스' 젤리를 몇 주째 먹어 왔다는 사실이 드러납니다. 알바로는 하비에르와 함께 병원을 찾아, 저금을 다 털어 넣고 해지도 안 되는 정기구독에 묶인 아이타나의 이야기를 십대의 말투 그대로 듣습니다.</t>
+          <t>며칠 후, 알바로가 십여 년 전 같은 보호시설망의 다른 센터에서 자란 27세 여성 소라이다를 만납니다. 동의 절차와 규칙을 먼저 정하고, 그녀가 겪은 일이 아니라 '아무도 묻지 않았던' 제도의 침묵에 대해 이야기를 듣습니다. 이어 소년 담당 검사 이치아르 아바이투아가 보호 절차와 통보 의무를 설명합니다.</t>
         </is>
       </c>
     </row>
@@ -36110,7 +36110,7 @@
         <v>1150</v>
       </c>
       <c r="B1151" s="10" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C1151" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1151)</f>
@@ -36122,14 +36122,14 @@
         </is>
       </c>
       <c r="E1151" s="10" t="n">
-        <v>41674</v>
+        <v>41703</v>
       </c>
       <c r="F1151" s="10" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G1151" s="10" t="inlineStr">
         <is>
-          <t>알바로는 편집장과 함께 하비에르를 공식적으로 이 기사에서 배제하고, 마르코스와 카밀라가 데이터를 맡습니다. 인플루언서 40명의 게시물 수백 건을 분석하자 광고 표시는 극히 일부뿐이고 모두가 같은 대본을 읽고 있음이 드러나며, 대학 식품분석 연구소의 레쿠오나 교수는 젤리 속 카페인은 과다하고 광고된 '천연 성분'은 거의 없다는 결과를 내놓습니다.</t>
+          <t>일주일 후, 취재가 위기를 맞습니다. 주정부가 아도라시온에게 '정보 유출'을 이유로 징계 절차를 시작하고, 증언을 약속했던 또 다른 교육사 파우스토가 물러섭니다. 한편 한 방송사가 보호시설 앞 소녀를 모자이크 처리해 내보내는 일이 벌어집니다. 알바로와 마르타, 하비에르는 시설 이름을 공개할지, 경찰 수사를 위해 무엇을 미뤄야 할지를 놓고 격론을 벌입니다.</t>
         </is>
       </c>
     </row>
@@ -36138,7 +36138,7 @@
         <v>1151</v>
       </c>
       <c r="B1152" s="10" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C1152" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1152)</f>
@@ -36150,14 +36150,14 @@
         </is>
       </c>
       <c r="E1152" s="10" t="n">
-        <v>41723</v>
+        <v>41753</v>
       </c>
       <c r="F1152" s="10" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G1152" s="10" t="inlineStr">
         <is>
-          <t>알바로는 '사라이피트'라는 계정을 운영하는 열아홉 살 마이크로 인플루언서 사라이 프리에토와 접촉해, 풀포 탤런트가 보낸 대본과 "#광고 태그는 붙이지 마, 가짜 같아 보여"라는 지시, 위약금 조항이 담긴 계약서를 확인합니다. 이어 마르타와 함께 은밀한 광고 금지, 건강 효능 표시 규정, 14일 철회권과 해지 불가 구독 문제 등 소비자법의 쟁점을 하나하나 짚습니다.</t>
+          <t>열흘 후, 알바로가 주정부 아동국장 아르투로 테헤도르를 인터뷰하며 반론권을 보장합니다. 기사가 나간 뒤 지침은 철회되고 검찰은 조사에 착수하지만, 아도라시온의 징계 절차는 여전히 열려 있습니다. 결말은 축배가 아닌, 내부고발자 보호 기관 앞의 조용한 아침입니다.</t>
         </is>
       </c>
     </row>
@@ -36166,7 +36166,7 @@
         <v>1152</v>
       </c>
       <c r="B1153" s="10" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C1153" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1153)</f>
@@ -36178,14 +36178,14 @@
         </is>
       </c>
       <c r="E1153" s="10" t="n">
-        <v>41771</v>
+        <v>41809</v>
       </c>
       <c r="F1153" s="10" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G1153" s="10" t="inlineStr">
         <is>
-          <t>반론권을 요청하자 풀포 탤런트의 변호사가 내용증명을 보내고 클로틸데는 영상을 대거 삭제한 채 "혐오에 지쳤다"는 스토리를 올립니다. 게다가 클로틸데의 팬들이 유출자로 엉뚱한 소녀를 지목해 신상털기를 시작하자, 알바로는 사라이의 익명성과 기사 공개 시점 사이에서 고민하고, 결국 변호사를 대동한 클로틸데와 직접 인터뷰합니다.</t>
+          <t>새로운 취재. 무기 수출 감시 단체 '아탈라야 센터'의 오픈소스 분석가 이차소 수비아우레가 내전 중인 가상의 국가 티하라에서 촬영된 영상 한 편을 들고 편집국을 찾아옵니다. 박격포탄 꼬리날개에 찍힌 각인은 아라곤의 한 탄약 제조사를 가리키지만, 스페인 정부의 공식 수출 통계에 적힌 최종 사용자는 걸프 국가 카시마르 토후국입니다.</t>
         </is>
       </c>
     </row>
@@ -36194,7 +36194,7 @@
         <v>1153</v>
       </c>
       <c r="B1154" s="10" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C1154" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1154)</f>
@@ -36206,14 +36206,14 @@
         </is>
       </c>
       <c r="E1154" s="10" t="n">
-        <v>41825</v>
+        <v>41862</v>
       </c>
       <c r="F1154" s="10" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G1154" s="10" t="inlineStr">
         <is>
-          <t>기사가 나가자 소비자청이 업체와 에이전시를 상대로 제재 절차에 착수하고, 누트리벨리아는 제품을 회수하며 아이타나는 소비자 상담소를 통해 환불을 받습니다. 클로틸데는 메모장 캡처 형식의 매끈한 사과문을 올리지만, 알바로와 하비에르가 지켜보는 가운데 아이타나는 기사에 이름을 싣는 대신 같은 반 친구들을 위해 필터도 할인 코드도 없는 자신만의 영상을 찍기로 합니다.</t>
+          <t>며칠 후, 알바로와 마르코스가 그림자와 건물, 위성 사진으로 영상의 촬영 장소와 날짜를 검증하고, 첫 영상을 찍은 티하라의 현지 기자 함자 다르위시와 화상으로 연결합니다. 그러나 이차소가 덧붙인 네 번째 영상이 수십 년 전 합법적으로 다른 나라에 팔린 탄약으로 드러나며, 취재팀은 과욕의 위험을 실감합니다.</t>
         </is>
       </c>
     </row>
@@ -36222,7 +36222,7 @@
         <v>1154</v>
       </c>
       <c r="B1155" s="10" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C1155" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1155)</f>
@@ -36234,14 +36234,14 @@
         </is>
       </c>
       <c r="E1155" s="10" t="n">
-        <v>41874</v>
+        <v>41921</v>
       </c>
       <c r="F1155" s="10" t="n">
         <v>51</v>
       </c>
       <c r="G1155" s="10" t="inlineStr">
         <is>
-          <t>새로운 취재. 알바로는 바예카스에 사는 83세 아수세나 할머니가 자기도 모르게 전력회사 '루멘 에네르히아'로 계약이 바뀌어 요금 폭탄을 맞았다는 사연을 듣고, 방문판매 하청업체 출신의 카나리아 청년 헤나로를 만나 노인을 노린 서명 위조 영업의 실체를 듣습니다. 그런데 신문사로 돌아오자, 그날 아침 신문 3면 전면광고의 주인공이 바로 루멘입니다.</t>
+          <t>일주일 후, 알바로가 수출 통제 위원회에 올라가는 서류를 준비하던 퇴직 공무원 세페리노 라스트라를 사라고사의 한 카페에서 만나 허가 절차가 실제로 어떻게 작동하는지 듣습니다. 같은 날 밤 카밀라는 EMJ의 재무제표에서 카시마르 현지 조립 공장 지분을 찾아내고, 완제품 대신 '부품과 키트'로 수출하는 합법적 우회로가 모습을 드러냅니다.</t>
         </is>
       </c>
     </row>
@@ -36250,7 +36250,7 @@
         <v>1155</v>
       </c>
       <c r="B1156" s="10" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C1156" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1156)</f>
@@ -36262,14 +36262,14 @@
         </is>
       </c>
       <c r="E1156" s="10" t="n">
-        <v>41927</v>
+        <v>41974</v>
       </c>
       <c r="F1156" s="10" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="G1156" s="10" t="inlineStr">
         <is>
-          <t>일주일 후, 알바로는 소비자보호사무소 민원 자료와 내부 메신저 기록으로 기사를 다지고 루멘에 반론 질문서를 보냅니다. 다음 날, 루멘 홍보이사 세실리아의 정중한 전화가 오고, 곧이어 그룹 사장 그레고리오 멘다사와 광고 담당 이사 벨렌이 편집국장실에 나타나 '보도 연기'를 설득합니다. 알바로는 논리로 맞섭니다.</t>
+          <t>열흘 후, 알바로는 유엔 안보리 티하라 전문가 패널 위원 안네커 피서르와 통화해 패널이 같은 로트를 기록했다는 사실을 확인하지만, 보고서 공개 전까지 보도를 미뤄 달라는 요청을 받고 편집국은 고민에 빠집니다. 이어 알바로는 아라곤의 EMJ 본사에서 홍보이사 고르카 레보야르의 반론을 듣고, 공장 앞에서 노동자위원회 위원장 에울로히오 알콘첼의 목소리를 듣습니다.</t>
         </is>
       </c>
     </row>
@@ -36278,7 +36278,7 @@
         <v>1156</v>
       </c>
       <c r="B1157" s="10" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C1157" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1157)</f>
@@ -36290,14 +36290,14 @@
         </is>
       </c>
       <c r="E1157" s="10" t="n">
-        <v>41978</v>
+        <v>42034</v>
       </c>
       <c r="F1157" s="10" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G1157" s="10" t="inlineStr">
         <is>
-          <t>열흘 후, 아침 7시. 알바로는 웹사이트에 실린 자기 기사가 회사명이 빠진 제목, 잘린 피해자 사례, 삭제된 내부 메시지로 '다듬어진' 것을 발견합니다. 그날 밤 마감 데스크를 맡은 사람은 하비에르였고, 오랜 친구 사이에 처음으로 날 선 싸움이 벌어집니다. 집에서는 카밀라가 신문사의 재무 구조를 짚으며 알바로에게 냉정한 질문을 던집니다.</t>
+          <t>3주 후, 유엔 전문가 패널 보고서가 공개된 다음 날 기사가 나가고, 알바로는 국무회의 후 열린 정부 대변인 에밀리아 에차니스의 기자회견에서 직접 질문을 던집니다. 정부는 '심사 중인 허가의 재검토'만 약속하고, 기사의 반향이 가라앉기도 전에 이차소에게서 새 영상이 도착합니다.</t>
         </is>
       </c>
     </row>
@@ -36306,7 +36306,7 @@
         <v>1157</v>
       </c>
       <c r="B1158" s="10" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C1158" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1158)</f>
@@ -36318,14 +36318,14 @@
         </is>
       </c>
       <c r="E1158" s="10" t="n">
-        <v>42029</v>
+        <v>42084</v>
       </c>
       <c r="F1158" s="10" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G1158" s="10" t="inlineStr">
         <is>
-          <t>이틀 후, 마르타는 법적으로 기사에 아무 문제가 없었다는 검토 의견서를 내놓아, 삭제가 법률이 아니라 광고 때문이었음을 분명히 합니다. 그날 밤 하비에르가 광고국과 사장 사이의 내부 이메일을 들고 알바로의 집을 찾아와 사과하고, 두 사람은 편집위원회(코미테 데 레닥시온)에 안건을 올립니다. 기자 총회에서는 해고를 두려워하는 동료들과 격렬한 윤리 토론이 벌어집니다.</t>
+          <t>새로운 취재. 신문사의 익명 제보함에 '현역 군인'이라고만 밝힌 제보가 들어오고, 알바로는 가상의 주둔지 발데카스트로에서 20킬로미터 떨어진 주유소 카페에서 카보 프리메로(선임 상병) 솔레다드 마이레나를 만납니다. 그녀는 사격장에서 시험 삼아 쏜 방탄판이 막아야 할 탄을 막지 못했고, 지휘 계통을 따라 보고했지만 아무 일도 일어나지 않았다고 말합니다.</t>
         </is>
       </c>
     </row>
@@ -36334,7 +36334,7 @@
         <v>1158</v>
       </c>
       <c r="B1159" s="10" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C1159" s="10">
         <f>INDEX('부작 목록'!$C$2:$C$96,B1159)</f>
@@ -36346,12 +36346,544 @@
         </is>
       </c>
       <c r="E1159" s="10" t="n">
-        <v>42083</v>
+        <v>42136</v>
       </c>
       <c r="F1159" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1159" s="10" t="inlineStr">
+        <is>
+          <t>며칠 후, 알바로는 퇴역 준위이자 부사관 직업 협회 회장인 펠릭스 비야에스쿠사에게서 계급 체계와 호칭, 군인의 권리와 내부고발자 보호 제도를 배웁니다. 한편 하비에르와 카밀라는 공공조달 플랫폼에서 프로바노르 사의 긴급 수의계약을 찾아내고, 이 신생 업체의 '전략 고문'이 장비 요구 조건을 정하던 부서의 수장 출신 퇴역 준장 세베리아노 카스트리요라는 사실을 확인합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="n">
+        <v>1159</v>
+      </c>
+      <c r="B1160" t="n">
+        <v>91</v>
+      </c>
+      <c r="C1160">
+        <f>INDEX('부작 목록'!$C$2:$C$96,B1160)</f>
+        <v/>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>G 시즌2 독립 취재</t>
+        </is>
+      </c>
+      <c r="E1160" t="n">
+        <v>42188</v>
+      </c>
+      <c r="F1160" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1160" t="inlineStr">
+        <is>
+          <t>2주 후, 마르타는 부대 창고의 방탄판을 몰래 넘겨받는 것은 군형법상 범죄가 될 수 있다며 솔레다드에게서 증거물을 받지 말라고 못 박습니다. 대신 알바로는 프로바노르가 같은 로트의 '잉여분'을 민간 경비업체에 판 사실을 알아내 합법적으로 두 장을 구입하고, 대학 탄도 실험실의 이스마엘 이리아르테 박사에게 시험을 맡깁니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="n">
+        <v>1160</v>
+      </c>
+      <c r="B1161" t="n">
+        <v>91</v>
+      </c>
+      <c r="C1161">
+        <f>INDEX('부작 목록'!$C$2:$C$96,B1161)</f>
+        <v/>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>G 시즌2 독립 취재</t>
+        </is>
+      </c>
+      <c r="E1161" t="n">
+        <v>42241</v>
+      </c>
+      <c r="F1161" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1161" t="inlineStr">
+        <is>
+          <t>열흘 후, 알바로가 국방부에 보낸 반론 질문지에 적힌 사격 시연 날짜 때문에 솔레다드의 신원이 드러나고, 그녀는 중대장 아리아가 대위에게 불려가 징계 사전 조사가 시작된다는 통보를 받습니다. 자책하는 알바로에게 솔레다드는 오히려 보도를 서두르라고 하고, 며칠 뒤 퇴역 준장 카스트리요는 마드리드의 한 호텔에서 인터뷰에 응하지만 알바로가 내민 날짜 하나에 대화를 급히 끝냅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="n">
+        <v>1161</v>
+      </c>
+      <c r="B1162" t="n">
+        <v>91</v>
+      </c>
+      <c r="C1162">
+        <f>INDEX('부작 목록'!$C$2:$C$96,B1162)</f>
+        <v/>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>G 시즌2 독립 취재</t>
+        </is>
+      </c>
+      <c r="E1162" t="n">
+        <v>42295</v>
+      </c>
+      <c r="F1162" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1162" t="inlineStr">
+        <is>
+          <t>3주 후, 보도를 하루 앞두고 국방부 공보 책임자 발렌틴 소티요가 해당 로트의 '예방적 사용 중지'를 미리 알려 오고, 기사가 나간 뒤 카스트리요는 프로바노르 고문직에서 물러납니다. 한 달 뒤 발트해로 떠나는 중대의 환송식에서, 징계 절차가 끝나지 않아 파병 명단에서 빠진 솔레다드가 관중석에서 알바로와 함께 버스를 지켜봅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="n">
+        <v>1162</v>
+      </c>
+      <c r="B1163" t="n">
+        <v>92</v>
+      </c>
+      <c r="C1163">
+        <f>INDEX('부작 목록'!$C$2:$C$96,B1163)</f>
+        <v/>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>G 시즌2 독립 취재</t>
+        </is>
+      </c>
+      <c r="E1163" t="n">
+        <v>42348</v>
+      </c>
+      <c r="F1163" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1163" t="inlineStr">
+        <is>
+          <t>새로운 취재. 알바로는 독자 편지 한 통을 따라 지방 도시 발데아라로 가서, 백 년 역사의 축구 클럽 '클루브 데포르티보 발데아라'의 홈구장 엘 아레날 관중석에 앉습니다. 2년 전 클럽을 단돈 1유로에 사들인 정체불명의 외국 펀드, 그리고 경기장 부지를 아파트 단지로 바꾸려 한다는 소문에 대해, 50년 차 회원 푸리 카라스코 할머니와 서포터즈 '그라다 노르테'의 리더 다니가 서로 전혀 다른 반응을 보입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="n">
+        <v>1163</v>
+      </c>
+      <c r="B1164" t="n">
+        <v>92</v>
+      </c>
+      <c r="C1164">
+        <f>INDEX('부작 목록'!$C$2:$C$96,B1164)</f>
+        <v/>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>G 시즌2 독립 취재</t>
+        </is>
+      </c>
+      <c r="E1164" t="n">
+        <v>42399</v>
+      </c>
+      <c r="F1164" t="n">
+        <v>47</v>
+      </c>
+      <c r="G1164" t="inlineStr">
+        <is>
+          <t>하비에르와 카밀라, 마르코스가 마드리드 편집국에서 발데아라 클럽의 소유 구조와 이적 데이터를 해부합니다. 1유로 매각 뒤에 숨은 룩셈부르크·델라웨어 법인의 사슬, 경기장 부지를 담보로 한 연 12% 고리 대출, 그리고 한 아르헨티나 에이전트에게 쏠린 수수료가 드러나지만, 핵심 증인인 전 재무이사 루스는 실명 증언을 거부합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="n">
+        <v>1164</v>
+      </c>
+      <c r="B1165" t="n">
+        <v>92</v>
+      </c>
+      <c r="C1165">
+        <f>INDEX('부작 목록'!$C$2:$C$96,B1165)</f>
+        <v/>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>G 시즌2 독립 취재</t>
+        </is>
+      </c>
+      <c r="E1165" t="n">
+        <v>42448</v>
+      </c>
+      <c r="F1165" t="n">
+        <v>48</v>
+      </c>
+      <c r="G1165" t="inlineStr">
+        <is>
+          <t>알바로가 시청의 공문서 등록부와 시의회 회의록을 파고들며, 매각 석 달 전에 접수된 도시계획 협약의 흔적을 확인합니다. 도시계획 담당 시의원 아란스와 정면으로 마주한 뒤, 문제의 에이전트 막시 갈반을 마르베야의 호텔 바에서 만나 "클럽은 핑계, 진짜 사업은 벽돌"이라는 의외의 솔직한 말을 듣습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="n">
+        <v>1165</v>
+      </c>
+      <c r="B1166" t="n">
+        <v>92</v>
+      </c>
+      <c r="C1166">
+        <f>INDEX('부작 목록'!$C$2:$C$96,B1166)</f>
+        <v/>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>G 시즌2 독립 취재</t>
+        </is>
+      </c>
+      <c r="E1166" t="n">
+        <v>42498</v>
+      </c>
+      <c r="F1166" t="n">
+        <v>47</v>
+      </c>
+      <c r="G1166" t="inlineStr">
+        <is>
+          <t>마르코스가 그라다 노르테의 원정 버스와 티켓이 브렌무어 계열사의 '팬 활동 후원금'으로 지불되었다는 송장을 찾아내면서, 알바로는 가장 열정적인 팬들이 동시에 침묵의 대가를 받았다는 윤리적 딜레마에 빠집니다. 마르타와 함께 기사의 법적 표현을 검토하고 펀드 측에 반론권을 요청하는 사이, 다니가 직접 찾아와 보도하지 말아 달라고 애원합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="n">
+        <v>1166</v>
+      </c>
+      <c r="B1167" t="n">
+        <v>92</v>
+      </c>
+      <c r="C1167">
+        <f>INDEX('부작 목록'!$C$2:$C$96,B1167)</f>
+        <v/>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>G 시즌2 독립 취재</t>
+        </is>
+      </c>
+      <c r="E1167" t="n">
+        <v>42547</v>
+      </c>
+      <c r="F1167" t="n">
+        <v>47</v>
+      </c>
+      <c r="G1167" t="inlineStr">
+        <is>
+          <t>기사가 나간 뒤, 그라다 노르테는 총회 결정에 따라 후원금 반환을 발표하고 다니가 직접 사과문을 읽습니다. 시의회는 도시계획 변경 절차를 중단하고 검찰은 협약에 대한 예비 조사에 착수하지만, 클럽은 시즌 마지막 홈경기에서 결국 강등이 확정됩니다. 알바로는 경기장을 떠나지 않는 관중들 사이에서 푸리 할머니의 마지막 말을 기록합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="n">
+        <v>1167</v>
+      </c>
+      <c r="B1168" t="n">
+        <v>93</v>
+      </c>
+      <c r="C1168">
+        <f>INDEX('부작 목록'!$C$2:$C$96,B1168)</f>
+        <v/>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>G 시즌2 독립 취재</t>
+        </is>
+      </c>
+      <c r="E1168" t="n">
+        <v>42596</v>
+      </c>
+      <c r="F1168" t="n">
+        <v>60</v>
+      </c>
+      <c r="G1168" t="inlineStr">
+        <is>
+          <t>일상 에피소드. 주말 오후, 알바로와 카밀라, 하비에르, 그리고 카밀라의 오빠 안드레스가 함께 축구장을 찾습니다. 스페인 경기장이 처음인 안드레스는 응원 문화에 금세 빠져들고, 네 사람은 골과 판정 하나하나에 함께 소리 지르며 오후를 보냅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="n">
+        <v>1168</v>
+      </c>
+      <c r="B1169" t="n">
+        <v>94</v>
+      </c>
+      <c r="C1169">
+        <f>INDEX('부작 목록'!$C$2:$C$96,B1169)</f>
+        <v/>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>G 시즌2 독립 취재</t>
+        </is>
+      </c>
+      <c r="E1169" t="n">
+        <v>42658</v>
+      </c>
+      <c r="F1169" t="n">
+        <v>48</v>
+      </c>
+      <c r="G1169" t="inlineStr">
+        <is>
+          <t>새로운 취재. 하비에르의 열여섯 살 조카 아이타나가 체육 시간에 심장이 두근거려 쓰러지고, 응급실에서 그녀가 수백만 팔로워 인플루언서 클로틸데 만세보가 "광고 아님, 내 경험"이라며 추천한 '칼미아 포커스' 젤리를 몇 주째 먹어 왔다는 사실이 드러납니다. 알바로는 하비에르와 함께 병원을 찾아, 저금을 다 털어 넣고 해지도 안 되는 정기구독에 묶인 아이타나의 이야기를 십대의 말투 그대로 듣습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="n">
+        <v>1169</v>
+      </c>
+      <c r="B1170" t="n">
+        <v>94</v>
+      </c>
+      <c r="C1170">
+        <f>INDEX('부작 목록'!$C$2:$C$96,B1170)</f>
+        <v/>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>G 시즌2 독립 취재</t>
+        </is>
+      </c>
+      <c r="E1170" t="n">
+        <v>42708</v>
+      </c>
+      <c r="F1170" t="n">
+        <v>47</v>
+      </c>
+      <c r="G1170" t="inlineStr">
+        <is>
+          <t>알바로는 편집장과 함께 하비에르를 공식적으로 이 기사에서 배제하고, 마르코스와 카밀라가 데이터를 맡습니다. 인플루언서 40명의 게시물 수백 건을 분석하자 광고 표시는 극히 일부뿐이고 모두가 같은 대본을 읽고 있음이 드러나며, 대학 식품분석 연구소의 레쿠오나 교수는 젤리 속 카페인은 과다하고 광고된 '천연 성분'은 거의 없다는 결과를 내놓습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="n">
+        <v>1170</v>
+      </c>
+      <c r="B1171" t="n">
+        <v>94</v>
+      </c>
+      <c r="C1171">
+        <f>INDEX('부작 목록'!$C$2:$C$96,B1171)</f>
+        <v/>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>G 시즌2 독립 취재</t>
+        </is>
+      </c>
+      <c r="E1171" t="n">
+        <v>42757</v>
+      </c>
+      <c r="F1171" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1171" t="inlineStr">
+        <is>
+          <t>알바로는 '사라이피트'라는 계정을 운영하는 열아홉 살 마이크로 인플루언서 사라이 프리에토와 접촉해, 풀포 탤런트가 보낸 대본과 "#광고 태그는 붙이지 마, 가짜 같아 보여"라는 지시, 위약금 조항이 담긴 계약서를 확인합니다. 이어 마르타와 함께 은밀한 광고 금지, 건강 효능 표시 규정, 14일 철회권과 해지 불가 구독 문제 등 소비자법의 쟁점을 하나하나 짚습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="n">
+        <v>1171</v>
+      </c>
+      <c r="B1172" t="n">
+        <v>94</v>
+      </c>
+      <c r="C1172">
+        <f>INDEX('부작 목록'!$C$2:$C$96,B1172)</f>
+        <v/>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>G 시즌2 독립 취재</t>
+        </is>
+      </c>
+      <c r="E1172" t="n">
+        <v>42805</v>
+      </c>
+      <c r="F1172" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1172" t="inlineStr">
+        <is>
+          <t>반론권을 요청하자 풀포 탤런트의 변호사가 내용증명을 보내고 클로틸데는 영상을 대거 삭제한 채 "혐오에 지쳤다"는 스토리를 올립니다. 게다가 클로틸데의 팬들이 유출자로 엉뚱한 소녀를 지목해 신상털기를 시작하자, 알바로는 사라이의 익명성과 기사 공개 시점 사이에서 고민하고, 결국 변호사를 대동한 클로틸데와 직접 인터뷰합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="n">
+        <v>1172</v>
+      </c>
+      <c r="B1173" t="n">
+        <v>94</v>
+      </c>
+      <c r="C1173">
+        <f>INDEX('부작 목록'!$C$2:$C$96,B1173)</f>
+        <v/>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>G 시즌2 독립 취재</t>
+        </is>
+      </c>
+      <c r="E1173" t="n">
+        <v>42859</v>
+      </c>
+      <c r="F1173" t="n">
+        <v>47</v>
+      </c>
+      <c r="G1173" t="inlineStr">
+        <is>
+          <t>기사가 나가자 소비자청이 업체와 에이전시를 상대로 제재 절차에 착수하고, 누트리벨리아는 제품을 회수하며 아이타나는 소비자 상담소를 통해 환불을 받습니다. 클로틸데는 메모장 캡처 형식의 매끈한 사과문을 올리지만, 알바로와 하비에르가 지켜보는 가운데 아이타나는 기사에 이름을 싣는 대신 같은 반 친구들을 위해 필터도 할인 코드도 없는 자신만의 영상을 찍기로 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="n">
+        <v>1173</v>
+      </c>
+      <c r="B1174" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1174">
+        <f>INDEX('부작 목록'!$C$2:$C$96,B1174)</f>
+        <v/>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>G 시즌2 독립 취재</t>
+        </is>
+      </c>
+      <c r="E1174" t="n">
+        <v>42908</v>
+      </c>
+      <c r="F1174" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1174" t="inlineStr">
+        <is>
+          <t>새로운 취재. 알바로는 바예카스에 사는 83세 아수세나 할머니가 자기도 모르게 전력회사 '루멘 에네르히아'로 계약이 바뀌어 요금 폭탄을 맞았다는 사연을 듣고, 방문판매 하청업체 출신의 카나리아 청년 헤나로를 만나 노인을 노린 서명 위조 영업의 실체를 듣습니다. 그런데 신문사로 돌아오자, 그날 아침 신문 3면 전면광고의 주인공이 바로 루멘입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="n">
+        <v>1174</v>
+      </c>
+      <c r="B1175" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1175">
+        <f>INDEX('부작 목록'!$C$2:$C$96,B1175)</f>
+        <v/>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>G 시즌2 독립 취재</t>
+        </is>
+      </c>
+      <c r="E1175" t="n">
+        <v>42961</v>
+      </c>
+      <c r="F1175" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1175" t="inlineStr">
+        <is>
+          <t>일주일 후, 알바로는 소비자보호사무소 민원 자료와 내부 메신저 기록으로 기사를 다지고 루멘에 반론 질문서를 보냅니다. 다음 날, 루멘 홍보이사 세실리아의 정중한 전화가 오고, 곧이어 그룹 사장 그레고리오 멘다사와 광고 담당 이사 벨렌이 편집국장실에 나타나 '보도 연기'를 설득합니다. 알바로는 논리로 맞섭니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="n">
+        <v>1175</v>
+      </c>
+      <c r="B1176" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1176">
+        <f>INDEX('부작 목록'!$C$2:$C$96,B1176)</f>
+        <v/>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>G 시즌2 독립 취재</t>
+        </is>
+      </c>
+      <c r="E1176" t="n">
+        <v>43012</v>
+      </c>
+      <c r="F1176" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1176" t="inlineStr">
+        <is>
+          <t>열흘 후, 아침 7시. 알바로는 웹사이트에 실린 자기 기사가 회사명이 빠진 제목, 잘린 피해자 사례, 삭제된 내부 메시지로 '다듬어진' 것을 발견합니다. 그날 밤 마감 데스크를 맡은 사람은 하비에르였고, 오랜 친구 사이에 처음으로 날 선 싸움이 벌어집니다. 집에서는 카밀라가 신문사의 재무 구조를 짚으며 알바로에게 냉정한 질문을 던집니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="n">
+        <v>1176</v>
+      </c>
+      <c r="B1177" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1177">
+        <f>INDEX('부작 목록'!$C$2:$C$96,B1177)</f>
+        <v/>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>G 시즌2 독립 취재</t>
+        </is>
+      </c>
+      <c r="E1177" t="n">
+        <v>43063</v>
+      </c>
+      <c r="F1177" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1177" t="inlineStr">
+        <is>
+          <t>이틀 후, 마르타는 법적으로 기사에 아무 문제가 없었다는 검토 의견서를 내놓아, 삭제가 법률이 아니라 광고 때문이었음을 분명히 합니다. 그날 밤 하비에르가 광고국과 사장 사이의 내부 이메일을 들고 알바로의 집을 찾아와 사과하고, 두 사람은 편집위원회(코미테 데 레닥시온)에 안건을 올립니다. 기자 총회에서는 해고를 두려워하는 동료들과 격렬한 윤리 토론이 벌어집니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="n">
+        <v>1177</v>
+      </c>
+      <c r="B1178" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1178">
+        <f>INDEX('부작 목록'!$C$2:$C$96,B1178)</f>
+        <v/>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>G 시즌2 독립 취재</t>
+        </is>
+      </c>
+      <c r="E1178" t="n">
+        <v>43117</v>
+      </c>
+      <c r="F1178" t="n">
         <v>57</v>
       </c>
-      <c r="G1159" s="10" t="inlineStr">
+      <c r="G1178" t="inlineStr">
         <is>
           <t>다음 주, 편집국장은 사장과 마지막 담판을 벌인 끝에 투명성 공지를 붙여 기사 전문을 2부로 싣기로 결정합니다. 루멘은 광고를 철회하고 소비자 당국이 조사에 착수하지만, 2주 뒤 편집국장은 '이사회 자문역'으로 밀려나 짐을 쌉니다. 그리고 한 달 뒤, 신문 7면에 루멘 광고가 다시 실립니다.</t>
         </is>
@@ -36397,7 +36929,7 @@
     <row r="4" ht="14.9" customHeight="1" s="11">
       <c r="A4" s="20" t="inlineStr">
         <is>
-          <t>- 화: 문서에서 장면마다 붙은 한국어 상황 설명 문단 1개 = 1화 (총 1158화).</t>
+          <t>- 화: 문서에서 장면마다 붙은 한국어 상황 설명 문단 1개 = 1화 (총 1177화).</t>
         </is>
       </c>
     </row>
